--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$134</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="379">
   <si>
     <t>N°</t>
   </si>
@@ -1025,6 +1025,36 @@
   </si>
   <si>
     <t>0556831346</t>
+  </si>
+  <si>
+    <t>REGUIEG ZAKARIA</t>
+  </si>
+  <si>
+    <t>reguiegzakaria10@gmail.com</t>
+  </si>
+  <si>
+    <t>0792070651</t>
+  </si>
+  <si>
+    <t>SEMMAK ABDELKADER</t>
+  </si>
+  <si>
+    <t>abdelkader_semmak@hotmail.fr</t>
+  </si>
+  <si>
+    <t>0772111809</t>
+  </si>
+  <si>
+    <t>BENMESSAOUD LEYLA</t>
+  </si>
+  <si>
+    <t>l_benmessaoud@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0553714385</t>
+  </si>
+  <si>
+    <t>0655206865</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1151,7 +1181,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1231,6 +1261,13 @@
       <color rgb="FFFF0000"/>
       <name val="Cambria"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1785,13 +1822,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1800,115 +1834,118 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2050,15 +2087,14 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5158,4156 +5194,3187 @@
         <v>330</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
-      <c r="A131" s="49"/>
-      <c r="D131" s="17"/>
-    </row>
-    <row r="132" spans="1:7">
-      <c r="A132" s="49"/>
-      <c r="D132" s="17"/>
-    </row>
-    <row r="133" spans="1:7">
-      <c r="A133" s="49"/>
-      <c r="D133" s="17"/>
-    </row>
-    <row r="134" spans="1:7">
-      <c r="A134" s="49"/>
-      <c r="D134" s="17"/>
+    <row r="131" ht="15.75" spans="1:7">
+      <c r="B131" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="C131" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E131" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F131" s="49" t="s">
+        <v>332</v>
+      </c>
+      <c r="G131" s="52" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" spans="1:7">
+      <c r="B132" s="17" t="s">
+        <v>334</v>
+      </c>
+      <c r="C132" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132" s="17" t="s">
+        <v>335</v>
+      </c>
+      <c r="G132" s="52" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" spans="1:7">
+      <c r="B133" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="C133" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E133" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F133" s="49" t="s">
+        <v>338</v>
+      </c>
+      <c r="G133" s="52" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" spans="1:7">
+      <c r="B134" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="C134" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E134" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F134" s="49" t="s">
+        <v>314</v>
+      </c>
+      <c r="G134" s="52" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="135" spans="1:7">
-      <c r="A135" s="49"/>
       <c r="D135" s="17"/>
     </row>
     <row r="136" spans="1:7">
-      <c r="A136" s="49"/>
       <c r="D136" s="17"/>
     </row>
     <row r="137" spans="1:7">
-      <c r="A137" s="49"/>
       <c r="D137" s="17"/>
     </row>
     <row r="138" spans="1:7">
-      <c r="A138" s="49"/>
       <c r="D138" s="17"/>
     </row>
     <row r="139" spans="1:7">
-      <c r="A139" s="49"/>
       <c r="D139" s="17"/>
     </row>
     <row r="140" spans="1:7">
-      <c r="A140" s="49"/>
       <c r="D140" s="17"/>
     </row>
     <row r="141" spans="1:7">
-      <c r="A141" s="49"/>
       <c r="D141" s="17"/>
     </row>
     <row r="142" spans="1:7">
-      <c r="A142" s="49"/>
       <c r="D142" s="17"/>
     </row>
     <row r="143" spans="1:7">
-      <c r="A143" s="49"/>
       <c r="D143" s="17"/>
     </row>
     <row r="144" spans="1:7">
-      <c r="A144" s="49"/>
       <c r="D144" s="17"/>
     </row>
-    <row r="145" spans="1:4">
-      <c r="A145" s="49"/>
+    <row r="145" spans="4:4">
       <c r="D145" s="17"/>
     </row>
-    <row r="146" spans="1:4">
-      <c r="A146" s="49"/>
+    <row r="146" spans="4:4">
       <c r="D146" s="17"/>
     </row>
-    <row r="147" spans="1:4">
-      <c r="A147" s="49"/>
+    <row r="147" spans="4:4">
       <c r="D147" s="17"/>
     </row>
-    <row r="148" spans="1:4">
-      <c r="A148" s="49"/>
+    <row r="148" spans="4:4">
       <c r="D148" s="17"/>
     </row>
-    <row r="149" spans="1:4">
-      <c r="A149" s="49"/>
+    <row r="149" spans="4:4">
       <c r="D149" s="17"/>
     </row>
-    <row r="150" spans="1:4">
-      <c r="A150" s="49"/>
+    <row r="150" spans="4:4">
       <c r="D150" s="17"/>
     </row>
-    <row r="151" spans="1:4">
-      <c r="A151" s="49"/>
+    <row r="151" spans="4:4">
       <c r="D151" s="17"/>
     </row>
-    <row r="152" spans="1:4">
-      <c r="A152" s="49"/>
+    <row r="152" spans="4:4">
       <c r="D152" s="17"/>
     </row>
-    <row r="153" spans="1:4">
-      <c r="A153" s="49"/>
+    <row r="153" spans="4:4">
       <c r="D153" s="17"/>
     </row>
-    <row r="154" spans="1:4">
-      <c r="A154" s="49"/>
+    <row r="154" spans="4:4">
       <c r="D154" s="17"/>
     </row>
-    <row r="155" spans="1:4">
-      <c r="A155" s="49"/>
+    <row r="155" spans="4:4">
       <c r="D155" s="17"/>
     </row>
-    <row r="156" spans="1:4">
-      <c r="A156" s="49"/>
+    <row r="156" spans="4:4">
       <c r="D156" s="17"/>
     </row>
-    <row r="157" spans="1:4">
-      <c r="A157" s="49"/>
+    <row r="157" spans="4:4">
       <c r="D157" s="17"/>
     </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="49"/>
+    <row r="158" spans="4:4">
       <c r="D158" s="17"/>
     </row>
-    <row r="159" spans="1:4">
-      <c r="A159" s="49"/>
+    <row r="159" spans="4:4">
       <c r="D159" s="17"/>
     </row>
-    <row r="160" spans="1:4">
-      <c r="A160" s="49"/>
+    <row r="160" spans="4:4">
       <c r="D160" s="17"/>
     </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="49"/>
+    <row r="161" spans="4:4">
       <c r="D161" s="17"/>
     </row>
-    <row r="162" spans="1:4">
-      <c r="A162" s="49"/>
+    <row r="162" spans="4:4">
       <c r="D162" s="17"/>
     </row>
-    <row r="163" spans="1:4">
-      <c r="A163" s="49"/>
+    <row r="163" spans="4:4">
       <c r="D163" s="17"/>
     </row>
-    <row r="164" spans="1:4">
-      <c r="A164" s="49"/>
+    <row r="164" spans="4:4">
       <c r="D164" s="17"/>
     </row>
-    <row r="165" spans="1:4">
-      <c r="A165" s="49"/>
+    <row r="165" spans="4:4">
       <c r="D165" s="17"/>
     </row>
-    <row r="166" spans="1:4">
-      <c r="A166" s="49"/>
+    <row r="166" spans="4:4">
       <c r="D166" s="17"/>
     </row>
-    <row r="167" spans="1:4">
-      <c r="A167" s="49"/>
+    <row r="167" spans="4:4">
       <c r="D167" s="17"/>
     </row>
-    <row r="168" spans="1:4">
-      <c r="A168" s="49"/>
+    <row r="168" spans="4:4">
       <c r="D168" s="17"/>
     </row>
-    <row r="169" spans="1:4">
-      <c r="A169" s="49"/>
+    <row r="169" spans="4:4">
       <c r="D169" s="17"/>
     </row>
-    <row r="170" spans="1:4">
-      <c r="A170" s="49"/>
+    <row r="170" spans="4:4">
       <c r="D170" s="17"/>
     </row>
-    <row r="171" spans="1:4">
-      <c r="A171" s="49"/>
+    <row r="171" spans="4:4">
       <c r="D171" s="17"/>
     </row>
-    <row r="172" spans="1:4">
-      <c r="A172" s="49"/>
+    <row r="172" spans="4:4">
       <c r="D172" s="17"/>
     </row>
-    <row r="173" spans="1:4">
-      <c r="A173" s="49"/>
+    <row r="173" spans="4:4">
       <c r="D173" s="17"/>
     </row>
-    <row r="174" spans="1:4">
-      <c r="A174" s="49"/>
+    <row r="174" spans="4:4">
       <c r="D174" s="17"/>
     </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="49"/>
+    <row r="175" spans="4:4">
       <c r="D175" s="17"/>
     </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="49"/>
+    <row r="176" spans="4:4">
       <c r="D176" s="17"/>
     </row>
-    <row r="177" spans="1:4">
-      <c r="A177" s="49"/>
+    <row r="177" spans="4:4">
       <c r="D177" s="17"/>
     </row>
-    <row r="178" spans="1:4">
-      <c r="A178" s="49"/>
+    <row r="178" spans="4:4">
       <c r="D178" s="17"/>
     </row>
-    <row r="179" spans="1:4">
-      <c r="A179" s="49"/>
+    <row r="179" spans="4:4">
       <c r="D179" s="17"/>
     </row>
-    <row r="180" spans="1:4">
-      <c r="A180" s="49"/>
+    <row r="180" spans="4:4">
       <c r="D180" s="17"/>
     </row>
-    <row r="181" spans="1:4">
-      <c r="A181" s="49"/>
+    <row r="181" spans="4:4">
       <c r="D181" s="17"/>
     </row>
-    <row r="182" spans="1:4">
-      <c r="A182" s="49"/>
+    <row r="182" spans="4:4">
       <c r="D182" s="17"/>
     </row>
-    <row r="183" spans="1:4">
-      <c r="A183" s="49"/>
+    <row r="183" spans="4:4">
       <c r="D183" s="17"/>
     </row>
-    <row r="184" spans="1:4">
-      <c r="A184" s="49"/>
+    <row r="184" spans="4:4">
       <c r="D184" s="17"/>
     </row>
-    <row r="185" spans="1:4">
-      <c r="A185" s="49"/>
+    <row r="185" spans="4:4">
       <c r="D185" s="17"/>
     </row>
-    <row r="186" spans="1:4">
-      <c r="A186" s="49"/>
+    <row r="186" spans="4:4">
       <c r="D186" s="17"/>
     </row>
-    <row r="187" spans="1:4">
-      <c r="A187" s="49"/>
+    <row r="187" spans="4:4">
       <c r="D187" s="17"/>
     </row>
-    <row r="188" spans="1:4">
-      <c r="A188" s="49"/>
+    <row r="188" spans="4:4">
       <c r="D188" s="17"/>
     </row>
-    <row r="189" spans="1:4">
-      <c r="A189" s="49"/>
+    <row r="189" spans="4:4">
       <c r="D189" s="17"/>
     </row>
-    <row r="190" spans="1:4">
-      <c r="A190" s="49"/>
+    <row r="190" spans="4:4">
       <c r="D190" s="17"/>
     </row>
-    <row r="191" spans="1:4">
-      <c r="A191" s="49"/>
+    <row r="191" spans="4:4">
       <c r="D191" s="17"/>
     </row>
-    <row r="192" spans="1:4">
-      <c r="A192" s="49"/>
+    <row r="192" spans="4:4">
       <c r="D192" s="17"/>
     </row>
-    <row r="193" spans="1:4">
-      <c r="A193" s="49"/>
+    <row r="193" spans="4:4">
       <c r="D193" s="17"/>
     </row>
-    <row r="194" spans="1:4">
-      <c r="A194" s="49"/>
+    <row r="194" spans="4:4">
       <c r="D194" s="17"/>
     </row>
-    <row r="195" spans="1:4">
-      <c r="A195" s="49"/>
+    <row r="195" spans="4:4">
       <c r="D195" s="17"/>
     </row>
-    <row r="196" spans="1:4">
-      <c r="A196" s="49"/>
+    <row r="196" spans="4:4">
       <c r="D196" s="17"/>
     </row>
-    <row r="197" spans="1:4">
-      <c r="A197" s="49"/>
+    <row r="197" spans="4:4">
       <c r="D197" s="17"/>
     </row>
-    <row r="198" spans="1:4">
-      <c r="A198" s="49"/>
+    <row r="198" spans="4:4">
       <c r="D198" s="17"/>
     </row>
-    <row r="199" spans="1:4">
-      <c r="A199" s="49"/>
+    <row r="199" spans="4:4">
       <c r="D199" s="17"/>
     </row>
-    <row r="200" spans="1:4">
-      <c r="A200" s="49"/>
+    <row r="200" spans="4:4">
       <c r="D200" s="17"/>
     </row>
-    <row r="201" spans="1:4">
-      <c r="A201" s="49"/>
+    <row r="201" spans="4:4">
       <c r="D201" s="17"/>
     </row>
-    <row r="202" spans="1:4">
-      <c r="A202" s="49"/>
+    <row r="202" spans="4:4">
       <c r="D202" s="17"/>
     </row>
-    <row r="203" spans="1:4">
-      <c r="A203" s="49"/>
+    <row r="203" spans="4:4">
       <c r="D203" s="17"/>
     </row>
-    <row r="204" spans="1:4">
-      <c r="A204" s="49"/>
+    <row r="204" spans="4:4">
       <c r="D204" s="17"/>
     </row>
-    <row r="205" spans="1:4">
-      <c r="A205" s="49"/>
+    <row r="205" spans="4:4">
       <c r="D205" s="17"/>
     </row>
-    <row r="206" spans="1:4">
-      <c r="A206" s="49"/>
+    <row r="206" spans="4:4">
       <c r="D206" s="17"/>
     </row>
-    <row r="207" spans="1:4">
-      <c r="A207" s="49"/>
+    <row r="207" spans="4:4">
       <c r="D207" s="17"/>
     </row>
-    <row r="208" spans="1:4">
-      <c r="A208" s="49"/>
+    <row r="208" spans="4:4">
       <c r="D208" s="17"/>
     </row>
-    <row r="209" spans="1:4">
-      <c r="A209" s="49"/>
+    <row r="209" spans="4:4">
       <c r="D209" s="17"/>
     </row>
-    <row r="210" spans="1:4">
-      <c r="A210" s="49"/>
+    <row r="210" spans="4:4">
       <c r="D210" s="17"/>
     </row>
-    <row r="211" spans="1:4">
-      <c r="A211" s="49"/>
+    <row r="211" spans="4:4">
       <c r="D211" s="17"/>
     </row>
-    <row r="212" spans="1:4">
-      <c r="A212" s="49"/>
+    <row r="212" spans="4:4">
       <c r="D212" s="17"/>
     </row>
-    <row r="213" spans="1:4">
-      <c r="A213" s="49"/>
+    <row r="213" spans="4:4">
       <c r="D213" s="17"/>
     </row>
-    <row r="214" spans="1:4">
-      <c r="A214" s="49"/>
+    <row r="214" spans="4:4">
       <c r="D214" s="17"/>
     </row>
-    <row r="215" spans="1:4">
-      <c r="A215" s="49"/>
+    <row r="215" spans="4:4">
       <c r="D215" s="17"/>
     </row>
-    <row r="216" spans="1:4">
-      <c r="A216" s="49"/>
+    <row r="216" spans="4:4">
       <c r="D216" s="17"/>
     </row>
-    <row r="217" spans="1:4">
-      <c r="A217" s="49"/>
+    <row r="217" spans="4:4">
       <c r="D217" s="17"/>
     </row>
-    <row r="218" spans="1:4">
-      <c r="A218" s="49"/>
+    <row r="218" spans="4:4">
       <c r="D218" s="17"/>
     </row>
-    <row r="219" spans="1:4">
-      <c r="A219" s="49"/>
+    <row r="219" spans="4:4">
       <c r="D219" s="17"/>
     </row>
-    <row r="220" spans="1:4">
-      <c r="A220" s="49"/>
+    <row r="220" spans="4:4">
       <c r="D220" s="17"/>
     </row>
-    <row r="221" spans="1:4">
-      <c r="A221" s="49"/>
+    <row r="221" spans="4:4">
       <c r="D221" s="17"/>
     </row>
-    <row r="222" spans="1:4">
-      <c r="A222" s="49"/>
+    <row r="222" spans="4:4">
       <c r="D222" s="17"/>
     </row>
-    <row r="223" spans="1:4">
-      <c r="A223" s="49"/>
+    <row r="223" spans="4:4">
       <c r="D223" s="17"/>
     </row>
-    <row r="224" spans="1:4">
-      <c r="A224" s="49"/>
+    <row r="224" spans="4:4">
       <c r="D224" s="17"/>
     </row>
-    <row r="225" spans="1:4">
-      <c r="A225" s="49"/>
+    <row r="225" spans="4:4">
       <c r="D225" s="17"/>
     </row>
-    <row r="226" spans="1:4">
-      <c r="A226" s="49"/>
+    <row r="226" spans="4:4">
       <c r="D226" s="17"/>
     </row>
-    <row r="227" spans="1:4">
-      <c r="A227" s="49"/>
+    <row r="227" spans="4:4">
       <c r="D227" s="17"/>
     </row>
-    <row r="228" spans="1:4">
-      <c r="A228" s="49"/>
+    <row r="228" spans="4:4">
       <c r="D228" s="17"/>
     </row>
-    <row r="229" spans="1:4">
-      <c r="A229" s="49"/>
+    <row r="229" spans="4:4">
       <c r="D229" s="17"/>
     </row>
-    <row r="230" spans="1:4">
-      <c r="A230" s="49"/>
+    <row r="230" spans="4:4">
       <c r="D230" s="17"/>
     </row>
-    <row r="231" spans="1:4">
-      <c r="A231" s="49"/>
+    <row r="231" spans="4:4">
       <c r="D231" s="17"/>
     </row>
-    <row r="232" spans="1:4">
-      <c r="A232" s="49"/>
+    <row r="232" spans="4:4">
       <c r="D232" s="17"/>
     </row>
-    <row r="233" spans="1:4">
-      <c r="A233" s="49"/>
+    <row r="233" spans="4:4">
       <c r="D233" s="17"/>
     </row>
-    <row r="234" spans="1:4">
-      <c r="A234" s="49"/>
+    <row r="234" spans="4:4">
       <c r="D234" s="17"/>
     </row>
-    <row r="235" spans="1:4">
-      <c r="A235" s="49"/>
+    <row r="235" spans="4:4">
       <c r="D235" s="17"/>
     </row>
-    <row r="236" spans="1:4">
-      <c r="A236" s="49"/>
+    <row r="236" spans="4:4">
       <c r="D236" s="17"/>
     </row>
-    <row r="237" spans="1:4">
-      <c r="A237" s="49"/>
+    <row r="237" spans="4:4">
       <c r="D237" s="17"/>
     </row>
-    <row r="238" spans="1:4">
-      <c r="A238" s="49"/>
+    <row r="238" spans="4:4">
       <c r="D238" s="17"/>
     </row>
-    <row r="239" spans="1:4">
-      <c r="A239" s="49"/>
+    <row r="239" spans="4:4">
       <c r="D239" s="17"/>
     </row>
-    <row r="240" spans="1:4">
-      <c r="A240" s="49"/>
+    <row r="240" spans="4:4">
       <c r="D240" s="17"/>
     </row>
-    <row r="241" spans="1:4">
-      <c r="A241" s="49"/>
+    <row r="241" spans="4:4">
       <c r="D241" s="17"/>
     </row>
-    <row r="242" spans="1:4">
-      <c r="A242" s="49"/>
+    <row r="242" spans="4:4">
       <c r="D242" s="17"/>
     </row>
-    <row r="243" spans="1:4">
-      <c r="A243" s="49"/>
+    <row r="243" spans="4:4">
       <c r="D243" s="17"/>
     </row>
-    <row r="244" spans="1:4">
-      <c r="A244" s="49"/>
+    <row r="244" spans="4:4">
       <c r="D244" s="17"/>
     </row>
-    <row r="245" spans="1:4">
-      <c r="A245" s="49"/>
+    <row r="245" spans="4:4">
       <c r="D245" s="17"/>
     </row>
-    <row r="246" spans="1:4">
-      <c r="A246" s="49"/>
+    <row r="246" spans="4:4">
       <c r="D246" s="17"/>
     </row>
-    <row r="247" spans="1:4">
-      <c r="A247" s="49"/>
+    <row r="247" spans="4:4">
       <c r="D247" s="17"/>
     </row>
-    <row r="248" spans="1:4">
-      <c r="A248" s="49"/>
+    <row r="248" spans="4:4">
       <c r="D248" s="17"/>
     </row>
-    <row r="249" spans="1:4">
-      <c r="A249" s="49"/>
+    <row r="249" spans="4:4">
       <c r="D249" s="17"/>
     </row>
-    <row r="250" spans="1:4">
-      <c r="A250" s="49"/>
+    <row r="250" spans="4:4">
       <c r="D250" s="17"/>
     </row>
-    <row r="251" spans="1:4">
-      <c r="A251" s="49"/>
+    <row r="251" spans="4:4">
       <c r="D251" s="17"/>
     </row>
-    <row r="252" spans="1:4">
-      <c r="A252" s="49"/>
+    <row r="252" spans="4:4">
       <c r="D252" s="17"/>
     </row>
-    <row r="253" spans="1:4">
-      <c r="A253" s="49"/>
+    <row r="253" spans="4:4">
       <c r="D253" s="17"/>
     </row>
-    <row r="254" spans="1:4">
-      <c r="A254" s="49"/>
+    <row r="254" spans="4:4">
       <c r="D254" s="17"/>
     </row>
-    <row r="255" spans="1:4">
-      <c r="A255" s="49"/>
+    <row r="255" spans="4:4">
       <c r="D255" s="17"/>
     </row>
-    <row r="256" spans="1:4">
-      <c r="A256" s="49"/>
+    <row r="256" spans="4:4">
       <c r="D256" s="17"/>
     </row>
-    <row r="257" spans="1:4">
-      <c r="A257" s="49"/>
+    <row r="257" spans="4:4">
       <c r="D257" s="17"/>
     </row>
-    <row r="258" spans="1:4">
-      <c r="A258" s="49"/>
+    <row r="258" spans="4:4">
       <c r="D258" s="17"/>
     </row>
-    <row r="259" spans="1:4">
-      <c r="A259" s="49"/>
+    <row r="259" spans="4:4">
       <c r="D259" s="17"/>
     </row>
-    <row r="260" spans="1:4">
-      <c r="A260" s="49"/>
+    <row r="260" spans="4:4">
       <c r="D260" s="17"/>
     </row>
-    <row r="261" spans="1:4">
-      <c r="A261" s="49"/>
+    <row r="261" spans="4:4">
       <c r="D261" s="17"/>
     </row>
-    <row r="262" spans="1:4">
-      <c r="A262" s="49"/>
+    <row r="262" spans="4:4">
       <c r="D262" s="17"/>
     </row>
-    <row r="263" spans="1:4">
-      <c r="A263" s="49"/>
+    <row r="263" spans="4:4">
       <c r="D263" s="17"/>
     </row>
-    <row r="264" spans="1:4">
-      <c r="A264" s="49"/>
+    <row r="264" spans="4:4">
       <c r="D264" s="17"/>
     </row>
-    <row r="265" spans="1:4">
-      <c r="A265" s="49"/>
+    <row r="265" spans="4:4">
       <c r="D265" s="17"/>
     </row>
-    <row r="266" spans="1:4">
-      <c r="A266" s="49"/>
+    <row r="266" spans="4:4">
       <c r="D266" s="17"/>
     </row>
-    <row r="267" spans="1:4">
-      <c r="A267" s="49"/>
+    <row r="267" spans="4:4">
       <c r="D267" s="17"/>
     </row>
-    <row r="268" spans="1:4">
-      <c r="A268" s="49"/>
+    <row r="268" spans="4:4">
       <c r="D268" s="17"/>
     </row>
-    <row r="269" spans="1:4">
-      <c r="A269" s="49"/>
+    <row r="269" spans="4:4">
       <c r="D269" s="17"/>
     </row>
-    <row r="270" spans="1:4">
-      <c r="A270" s="49"/>
+    <row r="270" spans="4:4">
       <c r="D270" s="17"/>
     </row>
-    <row r="271" spans="1:4">
-      <c r="A271" s="49"/>
+    <row r="271" spans="4:4">
       <c r="D271" s="17"/>
     </row>
-    <row r="272" spans="1:4">
-      <c r="A272" s="49"/>
+    <row r="272" spans="4:4">
       <c r="D272" s="17"/>
     </row>
-    <row r="273" spans="1:4">
-      <c r="A273" s="49"/>
+    <row r="273" spans="4:4">
       <c r="D273" s="17"/>
     </row>
-    <row r="274" spans="1:4">
-      <c r="A274" s="49"/>
+    <row r="274" spans="4:4">
       <c r="D274" s="17"/>
     </row>
-    <row r="275" spans="1:4">
-      <c r="A275" s="49"/>
+    <row r="275" spans="4:4">
       <c r="D275" s="17"/>
     </row>
-    <row r="276" spans="1:4">
-      <c r="A276" s="49"/>
+    <row r="276" spans="4:4">
       <c r="D276" s="17"/>
     </row>
-    <row r="277" spans="1:4">
-      <c r="A277" s="49"/>
+    <row r="277" spans="4:4">
       <c r="D277" s="17"/>
     </row>
-    <row r="278" spans="1:4">
-      <c r="A278" s="49"/>
+    <row r="278" spans="4:4">
       <c r="D278" s="17"/>
     </row>
-    <row r="279" spans="1:4">
-      <c r="A279" s="49"/>
+    <row r="279" spans="4:4">
       <c r="D279" s="17"/>
     </row>
-    <row r="280" spans="1:4">
-      <c r="A280" s="49"/>
+    <row r="280" spans="4:4">
       <c r="D280" s="17"/>
     </row>
-    <row r="281" spans="1:4">
-      <c r="A281" s="49"/>
+    <row r="281" spans="4:4">
       <c r="D281" s="17"/>
     </row>
-    <row r="282" spans="1:4">
-      <c r="A282" s="49"/>
+    <row r="282" spans="4:4">
       <c r="D282" s="17"/>
     </row>
-    <row r="283" spans="1:4">
-      <c r="A283" s="49"/>
+    <row r="283" spans="4:4">
       <c r="D283" s="17"/>
     </row>
-    <row r="284" spans="1:4">
-      <c r="A284" s="49"/>
+    <row r="284" spans="4:4">
       <c r="D284" s="17"/>
     </row>
-    <row r="285" spans="1:4">
-      <c r="A285" s="49"/>
+    <row r="285" spans="4:4">
       <c r="D285" s="17"/>
     </row>
-    <row r="286" spans="1:4">
-      <c r="A286" s="49"/>
+    <row r="286" spans="4:4">
       <c r="D286" s="17"/>
     </row>
-    <row r="287" spans="1:4">
-      <c r="A287" s="49"/>
+    <row r="287" spans="4:4">
       <c r="D287" s="17"/>
     </row>
-    <row r="288" spans="1:4">
-      <c r="A288" s="49"/>
+    <row r="288" spans="4:4">
       <c r="D288" s="17"/>
     </row>
-    <row r="289" spans="1:4">
-      <c r="A289" s="49"/>
+    <row r="289" spans="4:4">
       <c r="D289" s="17"/>
     </row>
-    <row r="290" spans="1:4">
-      <c r="A290" s="49"/>
+    <row r="290" spans="4:4">
       <c r="D290" s="17"/>
     </row>
-    <row r="291" spans="1:4">
-      <c r="A291" s="49"/>
+    <row r="291" spans="4:4">
       <c r="D291" s="17"/>
     </row>
-    <row r="292" spans="1:4">
-      <c r="A292" s="49"/>
+    <row r="292" spans="4:4">
       <c r="D292" s="17"/>
     </row>
-    <row r="293" spans="1:4">
-      <c r="A293" s="49"/>
+    <row r="293" spans="4:4">
       <c r="D293" s="17"/>
     </row>
-    <row r="294" spans="1:4">
-      <c r="A294" s="49"/>
+    <row r="294" spans="4:4">
       <c r="D294" s="17"/>
     </row>
-    <row r="295" spans="1:4">
-      <c r="A295" s="49"/>
+    <row r="295" spans="4:4">
       <c r="D295" s="17"/>
     </row>
-    <row r="296" spans="1:4">
-      <c r="A296" s="49"/>
+    <row r="296" spans="4:4">
       <c r="D296" s="17"/>
     </row>
-    <row r="297" spans="1:4">
-      <c r="A297" s="49"/>
+    <row r="297" spans="4:4">
       <c r="D297" s="17"/>
     </row>
-    <row r="298" spans="1:4">
-      <c r="A298" s="49"/>
+    <row r="298" spans="4:4">
       <c r="D298" s="17"/>
     </row>
-    <row r="299" spans="1:4">
-      <c r="A299" s="49"/>
+    <row r="299" spans="4:4">
       <c r="D299" s="17"/>
     </row>
-    <row r="300" spans="1:4">
-      <c r="A300" s="49"/>
+    <row r="300" spans="4:4">
       <c r="D300" s="17"/>
     </row>
-    <row r="301" spans="1:4">
-      <c r="A301" s="49"/>
+    <row r="301" spans="4:4">
       <c r="D301" s="17"/>
     </row>
-    <row r="302" spans="1:4">
-      <c r="A302" s="49"/>
+    <row r="302" spans="4:4">
       <c r="D302" s="17"/>
     </row>
-    <row r="303" spans="1:4">
-      <c r="A303" s="49"/>
+    <row r="303" spans="4:4">
       <c r="D303" s="17"/>
     </row>
-    <row r="304" spans="1:4">
-      <c r="A304" s="49"/>
+    <row r="304" spans="4:4">
       <c r="D304" s="17"/>
     </row>
-    <row r="305" spans="1:4">
-      <c r="A305" s="49"/>
+    <row r="305" spans="4:4">
       <c r="D305" s="17"/>
     </row>
-    <row r="306" spans="1:4">
-      <c r="A306" s="49"/>
+    <row r="306" spans="4:4">
       <c r="D306" s="17"/>
     </row>
-    <row r="307" spans="1:4">
-      <c r="A307" s="49"/>
+    <row r="307" spans="4:4">
       <c r="D307" s="17"/>
     </row>
-    <row r="308" spans="1:4">
-      <c r="A308" s="49"/>
+    <row r="308" spans="4:4">
       <c r="D308" s="17"/>
     </row>
-    <row r="309" spans="1:4">
-      <c r="A309" s="49"/>
+    <row r="309" spans="4:4">
       <c r="D309" s="17"/>
     </row>
-    <row r="310" spans="1:4">
-      <c r="A310" s="49"/>
+    <row r="310" spans="4:4">
       <c r="D310" s="17"/>
     </row>
-    <row r="311" spans="1:4">
-      <c r="A311" s="49"/>
+    <row r="311" spans="4:4">
       <c r="D311" s="17"/>
     </row>
-    <row r="312" spans="1:4">
-      <c r="A312" s="49"/>
+    <row r="312" spans="4:4">
       <c r="D312" s="17"/>
     </row>
-    <row r="313" spans="1:4">
-      <c r="A313" s="49"/>
+    <row r="313" spans="4:4">
       <c r="D313" s="17"/>
     </row>
-    <row r="314" spans="1:4">
-      <c r="A314" s="49"/>
+    <row r="314" spans="4:4">
       <c r="D314" s="17"/>
     </row>
-    <row r="315" spans="1:4">
-      <c r="A315" s="49"/>
+    <row r="315" spans="4:4">
       <c r="D315" s="17"/>
     </row>
-    <row r="316" spans="1:4">
-      <c r="A316" s="49"/>
+    <row r="316" spans="4:4">
       <c r="D316" s="17"/>
     </row>
-    <row r="317" spans="1:4">
-      <c r="A317" s="49"/>
+    <row r="317" spans="4:4">
       <c r="D317" s="17"/>
     </row>
-    <row r="318" spans="1:4">
-      <c r="A318" s="49"/>
+    <row r="318" spans="4:4">
       <c r="D318" s="17"/>
     </row>
-    <row r="319" spans="1:4">
-      <c r="A319" s="49"/>
+    <row r="319" spans="4:4">
       <c r="D319" s="17"/>
     </row>
-    <row r="320" spans="1:4">
-      <c r="A320" s="49"/>
+    <row r="320" spans="4:4">
       <c r="D320" s="17"/>
     </row>
-    <row r="321" spans="1:4">
-      <c r="A321" s="49"/>
+    <row r="321" spans="4:4">
       <c r="D321" s="17"/>
     </row>
-    <row r="322" spans="1:4">
-      <c r="A322" s="49"/>
+    <row r="322" spans="4:4">
       <c r="D322" s="17"/>
     </row>
-    <row r="323" spans="1:4">
-      <c r="A323" s="49"/>
+    <row r="323" spans="4:4">
       <c r="D323" s="17"/>
     </row>
-    <row r="324" spans="1:4">
-      <c r="A324" s="49"/>
+    <row r="324" spans="4:4">
       <c r="D324" s="17"/>
     </row>
-    <row r="325" spans="1:4">
-      <c r="A325" s="49"/>
+    <row r="325" spans="4:4">
       <c r="D325" s="17"/>
     </row>
-    <row r="326" spans="1:4">
-      <c r="A326" s="49"/>
+    <row r="326" spans="4:4">
       <c r="D326" s="17"/>
     </row>
-    <row r="327" spans="1:4">
-      <c r="A327" s="49"/>
+    <row r="327" spans="4:4">
       <c r="D327" s="17"/>
     </row>
-    <row r="328" spans="1:4">
-      <c r="A328" s="49"/>
+    <row r="328" spans="4:4">
       <c r="D328" s="17"/>
     </row>
-    <row r="329" spans="1:4">
-      <c r="A329" s="49"/>
+    <row r="329" spans="4:4">
       <c r="D329" s="17"/>
     </row>
-    <row r="330" spans="1:4">
-      <c r="A330" s="49"/>
+    <row r="330" spans="4:4">
       <c r="D330" s="17"/>
     </row>
-    <row r="331" spans="1:4">
-      <c r="A331" s="49"/>
+    <row r="331" spans="4:4">
       <c r="D331" s="17"/>
     </row>
-    <row r="332" spans="1:4">
-      <c r="A332" s="49"/>
+    <row r="332" spans="4:4">
       <c r="D332" s="17"/>
     </row>
-    <row r="333" spans="1:4">
-      <c r="A333" s="49"/>
+    <row r="333" spans="4:4">
       <c r="D333" s="17"/>
     </row>
-    <row r="334" spans="1:4">
-      <c r="A334" s="49"/>
+    <row r="334" spans="4:4">
       <c r="D334" s="17"/>
     </row>
-    <row r="335" spans="1:4">
-      <c r="A335" s="49"/>
+    <row r="335" spans="4:4">
       <c r="D335" s="17"/>
     </row>
-    <row r="336" spans="1:4">
-      <c r="A336" s="49"/>
+    <row r="336" spans="4:4">
       <c r="D336" s="17"/>
     </row>
-    <row r="337" spans="1:4">
-      <c r="A337" s="49"/>
+    <row r="337" spans="4:4">
       <c r="D337" s="17"/>
     </row>
-    <row r="338" spans="1:4">
-      <c r="A338" s="49"/>
+    <row r="338" spans="4:4">
       <c r="D338" s="17"/>
     </row>
-    <row r="339" spans="1:4">
-      <c r="A339" s="49"/>
+    <row r="339" spans="4:4">
       <c r="D339" s="17"/>
     </row>
-    <row r="340" spans="1:4">
-      <c r="A340" s="49"/>
+    <row r="340" spans="4:4">
       <c r="D340" s="17"/>
     </row>
-    <row r="341" spans="1:4">
-      <c r="A341" s="49"/>
+    <row r="341" spans="4:4">
       <c r="D341" s="17"/>
     </row>
-    <row r="342" spans="1:4">
-      <c r="A342" s="49"/>
+    <row r="342" spans="4:4">
       <c r="D342" s="17"/>
     </row>
-    <row r="343" spans="1:4">
-      <c r="A343" s="49"/>
+    <row r="343" spans="4:4">
       <c r="D343" s="17"/>
     </row>
-    <row r="344" spans="1:4">
-      <c r="A344" s="49"/>
+    <row r="344" spans="4:4">
       <c r="D344" s="17"/>
     </row>
-    <row r="345" spans="1:4">
-      <c r="A345" s="49"/>
+    <row r="345" spans="4:4">
       <c r="D345" s="17"/>
     </row>
-    <row r="346" spans="1:4">
-      <c r="A346" s="49"/>
+    <row r="346" spans="4:4">
       <c r="D346" s="17"/>
     </row>
-    <row r="347" spans="1:4">
-      <c r="A347" s="49"/>
+    <row r="347" spans="4:4">
       <c r="D347" s="17"/>
     </row>
-    <row r="348" spans="1:4">
-      <c r="A348" s="49"/>
+    <row r="348" spans="4:4">
       <c r="D348" s="17"/>
     </row>
-    <row r="349" spans="1:4">
-      <c r="A349" s="49"/>
+    <row r="349" spans="4:4">
       <c r="D349" s="17"/>
     </row>
-    <row r="350" spans="1:4">
-      <c r="A350" s="49"/>
+    <row r="350" spans="4:4">
       <c r="D350" s="17"/>
     </row>
-    <row r="351" spans="1:4">
-      <c r="A351" s="49"/>
+    <row r="351" spans="4:4">
       <c r="D351" s="17"/>
     </row>
-    <row r="352" spans="1:4">
-      <c r="A352" s="49"/>
+    <row r="352" spans="4:4">
       <c r="D352" s="17"/>
     </row>
-    <row r="353" spans="1:4">
-      <c r="A353" s="49"/>
+    <row r="353" spans="4:4">
       <c r="D353" s="17"/>
     </row>
-    <row r="354" spans="1:4">
-      <c r="A354" s="49"/>
+    <row r="354" spans="4:4">
       <c r="D354" s="17"/>
     </row>
-    <row r="355" spans="1:4">
-      <c r="A355" s="49"/>
+    <row r="355" spans="4:4">
       <c r="D355" s="17"/>
     </row>
-    <row r="356" spans="1:4">
-      <c r="A356" s="49"/>
+    <row r="356" spans="4:4">
       <c r="D356" s="17"/>
     </row>
-    <row r="357" spans="1:4">
-      <c r="A357" s="49"/>
+    <row r="357" spans="4:4">
       <c r="D357" s="17"/>
     </row>
-    <row r="358" spans="1:4">
-      <c r="A358" s="49"/>
+    <row r="358" spans="4:4">
       <c r="D358" s="17"/>
     </row>
-    <row r="359" spans="1:4">
-      <c r="A359" s="49"/>
+    <row r="359" spans="4:4">
       <c r="D359" s="17"/>
     </row>
-    <row r="360" spans="1:4">
-      <c r="A360" s="49"/>
+    <row r="360" spans="4:4">
       <c r="D360" s="17"/>
     </row>
-    <row r="361" spans="1:4">
-      <c r="A361" s="49"/>
+    <row r="361" spans="4:4">
       <c r="D361" s="17"/>
     </row>
-    <row r="362" spans="1:4">
-      <c r="A362" s="49"/>
+    <row r="362" spans="4:4">
       <c r="D362" s="17"/>
     </row>
-    <row r="363" spans="1:4">
-      <c r="A363" s="49"/>
+    <row r="363" spans="4:4">
       <c r="D363" s="17"/>
     </row>
-    <row r="364" spans="1:4">
-      <c r="A364" s="49"/>
+    <row r="364" spans="4:4">
       <c r="D364" s="17"/>
     </row>
-    <row r="365" spans="1:4">
-      <c r="A365" s="49"/>
+    <row r="365" spans="4:4">
       <c r="D365" s="17"/>
     </row>
-    <row r="366" spans="1:4">
-      <c r="A366" s="49"/>
+    <row r="366" spans="4:4">
       <c r="D366" s="17"/>
     </row>
-    <row r="367" spans="1:4">
-      <c r="A367" s="49"/>
+    <row r="367" spans="4:4">
       <c r="D367" s="17"/>
     </row>
-    <row r="368" spans="1:4">
-      <c r="A368" s="49"/>
+    <row r="368" spans="4:4">
       <c r="D368" s="17"/>
     </row>
-    <row r="369" spans="1:4">
-      <c r="A369" s="49"/>
+    <row r="369" spans="4:4">
       <c r="D369" s="17"/>
     </row>
-    <row r="370" spans="1:4">
-      <c r="A370" s="49"/>
+    <row r="370" spans="4:4">
       <c r="D370" s="17"/>
     </row>
-    <row r="371" spans="1:4">
-      <c r="A371" s="49"/>
+    <row r="371" spans="4:4">
       <c r="D371" s="17"/>
     </row>
-    <row r="372" spans="1:4">
-      <c r="A372" s="49"/>
+    <row r="372" spans="4:4">
       <c r="D372" s="17"/>
     </row>
-    <row r="373" spans="1:4">
-      <c r="A373" s="49"/>
+    <row r="373" spans="4:4">
       <c r="D373" s="17"/>
     </row>
-    <row r="374" spans="1:4">
-      <c r="A374" s="49"/>
+    <row r="374" spans="4:4">
       <c r="D374" s="17"/>
     </row>
-    <row r="375" spans="1:4">
-      <c r="A375" s="49"/>
+    <row r="375" spans="4:4">
       <c r="D375" s="17"/>
     </row>
-    <row r="376" spans="1:4">
-      <c r="A376" s="49"/>
+    <row r="376" spans="4:4">
       <c r="D376" s="17"/>
     </row>
-    <row r="377" spans="1:4">
-      <c r="A377" s="49"/>
+    <row r="377" spans="4:4">
       <c r="D377" s="17"/>
     </row>
-    <row r="378" spans="1:4">
-      <c r="A378" s="49"/>
+    <row r="378" spans="4:4">
       <c r="D378" s="17"/>
     </row>
-    <row r="379" spans="1:4">
-      <c r="A379" s="49"/>
+    <row r="379" spans="4:4">
       <c r="D379" s="17"/>
     </row>
-    <row r="380" spans="1:4">
-      <c r="A380" s="49"/>
+    <row r="380" spans="4:4">
       <c r="D380" s="17"/>
     </row>
-    <row r="381" spans="1:4">
-      <c r="A381" s="49"/>
+    <row r="381" spans="4:4">
       <c r="D381" s="17"/>
     </row>
-    <row r="382" spans="1:4">
-      <c r="A382" s="49"/>
+    <row r="382" spans="4:4">
       <c r="D382" s="17"/>
     </row>
-    <row r="383" spans="1:4">
-      <c r="A383" s="49"/>
+    <row r="383" spans="4:4">
       <c r="D383" s="17"/>
     </row>
-    <row r="384" spans="1:4">
-      <c r="A384" s="49"/>
+    <row r="384" spans="4:4">
       <c r="D384" s="17"/>
     </row>
-    <row r="385" spans="1:4">
-      <c r="A385" s="49"/>
+    <row r="385" spans="4:4">
       <c r="D385" s="17"/>
     </row>
-    <row r="386" spans="1:4">
-      <c r="A386" s="49"/>
+    <row r="386" spans="4:4">
       <c r="D386" s="17"/>
     </row>
-    <row r="387" spans="1:4">
-      <c r="A387" s="49"/>
+    <row r="387" spans="4:4">
       <c r="D387" s="17"/>
     </row>
-    <row r="388" spans="1:4">
-      <c r="A388" s="49"/>
+    <row r="388" spans="4:4">
       <c r="D388" s="17"/>
     </row>
-    <row r="389" spans="1:4">
-      <c r="A389" s="49"/>
+    <row r="389" spans="4:4">
       <c r="D389" s="17"/>
     </row>
-    <row r="390" spans="1:4">
-      <c r="A390" s="49"/>
+    <row r="390" spans="4:4">
       <c r="D390" s="17"/>
     </row>
-    <row r="391" spans="1:4">
-      <c r="A391" s="49"/>
+    <row r="391" spans="4:4">
       <c r="D391" s="17"/>
     </row>
-    <row r="392" spans="1:4">
-      <c r="A392" s="49"/>
+    <row r="392" spans="4:4">
       <c r="D392" s="17"/>
     </row>
-    <row r="393" spans="1:4">
-      <c r="A393" s="49"/>
+    <row r="393" spans="4:4">
       <c r="D393" s="17"/>
     </row>
-    <row r="394" spans="1:4">
-      <c r="A394" s="49"/>
+    <row r="394" spans="4:4">
       <c r="D394" s="17"/>
     </row>
-    <row r="395" spans="1:4">
-      <c r="A395" s="49"/>
+    <row r="395" spans="4:4">
       <c r="D395" s="17"/>
     </row>
-    <row r="396" spans="1:4">
-      <c r="A396" s="49"/>
+    <row r="396" spans="4:4">
       <c r="D396" s="17"/>
     </row>
-    <row r="397" spans="1:4">
-      <c r="A397" s="49"/>
+    <row r="397" spans="4:4">
       <c r="D397" s="17"/>
     </row>
-    <row r="398" spans="1:4">
-      <c r="A398" s="49"/>
+    <row r="398" spans="4:4">
       <c r="D398" s="17"/>
     </row>
-    <row r="399" spans="1:4">
-      <c r="A399" s="49"/>
+    <row r="399" spans="4:4">
       <c r="D399" s="17"/>
     </row>
-    <row r="400" spans="1:4">
-      <c r="A400" s="49"/>
+    <row r="400" spans="4:4">
       <c r="D400" s="17"/>
     </row>
-    <row r="401" spans="1:4">
-      <c r="A401" s="49"/>
+    <row r="401" spans="4:4">
       <c r="D401" s="17"/>
     </row>
-    <row r="402" spans="1:4">
-      <c r="A402" s="49"/>
+    <row r="402" spans="4:4">
       <c r="D402" s="17"/>
     </row>
-    <row r="403" spans="1:4">
-      <c r="A403" s="49"/>
+    <row r="403" spans="4:4">
       <c r="D403" s="17"/>
     </row>
-    <row r="404" spans="1:4">
-      <c r="A404" s="49"/>
+    <row r="404" spans="4:4">
       <c r="D404" s="17"/>
     </row>
-    <row r="405" spans="1:4">
-      <c r="A405" s="49"/>
+    <row r="405" spans="4:4">
       <c r="D405" s="17"/>
     </row>
-    <row r="406" spans="1:4">
-      <c r="A406" s="49"/>
+    <row r="406" spans="4:4">
       <c r="D406" s="17"/>
     </row>
-    <row r="407" spans="1:4">
-      <c r="A407" s="49"/>
+    <row r="407" spans="4:4">
       <c r="D407" s="17"/>
     </row>
-    <row r="408" spans="1:4">
-      <c r="A408" s="49"/>
+    <row r="408" spans="4:4">
       <c r="D408" s="17"/>
     </row>
-    <row r="409" spans="1:4">
-      <c r="A409" s="49"/>
+    <row r="409" spans="4:4">
       <c r="D409" s="17"/>
     </row>
-    <row r="410" spans="1:4">
-      <c r="A410" s="49"/>
+    <row r="410" spans="4:4">
       <c r="D410" s="17"/>
     </row>
-    <row r="411" spans="1:4">
-      <c r="A411" s="49"/>
+    <row r="411" spans="4:4">
       <c r="D411" s="17"/>
     </row>
-    <row r="412" spans="1:4">
-      <c r="A412" s="49"/>
+    <row r="412" spans="4:4">
       <c r="D412" s="17"/>
     </row>
-    <row r="413" spans="1:4">
-      <c r="A413" s="49"/>
+    <row r="413" spans="4:4">
       <c r="D413" s="17"/>
     </row>
-    <row r="414" spans="1:4">
-      <c r="A414" s="49"/>
+    <row r="414" spans="4:4">
       <c r="D414" s="17"/>
     </row>
-    <row r="415" spans="1:4">
-      <c r="A415" s="49"/>
+    <row r="415" spans="4:4">
       <c r="D415" s="17"/>
     </row>
-    <row r="416" spans="1:4">
-      <c r="A416" s="49"/>
+    <row r="416" spans="4:4">
       <c r="D416" s="17"/>
     </row>
-    <row r="417" spans="1:4">
-      <c r="A417" s="49"/>
+    <row r="417" spans="4:4">
       <c r="D417" s="17"/>
     </row>
-    <row r="418" spans="1:4">
-      <c r="A418" s="49"/>
+    <row r="418" spans="4:4">
       <c r="D418" s="17"/>
     </row>
-    <row r="419" spans="1:4">
-      <c r="A419" s="49"/>
+    <row r="419" spans="4:4">
       <c r="D419" s="17"/>
     </row>
-    <row r="420" spans="1:4">
-      <c r="A420" s="49"/>
+    <row r="420" spans="4:4">
       <c r="D420" s="17"/>
     </row>
-    <row r="421" spans="1:4">
-      <c r="A421" s="49"/>
+    <row r="421" spans="4:4">
       <c r="D421" s="17"/>
     </row>
-    <row r="422" spans="1:4">
-      <c r="A422" s="49"/>
+    <row r="422" spans="4:4">
       <c r="D422" s="17"/>
     </row>
-    <row r="423" spans="1:4">
-      <c r="A423" s="49"/>
+    <row r="423" spans="4:4">
       <c r="D423" s="17"/>
     </row>
-    <row r="424" spans="1:4">
-      <c r="A424" s="49"/>
+    <row r="424" spans="4:4">
       <c r="D424" s="17"/>
     </row>
-    <row r="425" spans="1:4">
-      <c r="A425" s="49"/>
+    <row r="425" spans="4:4">
       <c r="D425" s="17"/>
     </row>
-    <row r="426" spans="1:4">
-      <c r="A426" s="49"/>
+    <row r="426" spans="4:4">
       <c r="D426" s="17"/>
     </row>
-    <row r="427" spans="1:4">
-      <c r="A427" s="49"/>
+    <row r="427" spans="4:4">
       <c r="D427" s="17"/>
     </row>
-    <row r="428" spans="1:4">
-      <c r="A428" s="49"/>
+    <row r="428" spans="4:4">
       <c r="D428" s="17"/>
     </row>
-    <row r="429" spans="1:4">
-      <c r="A429" s="49"/>
+    <row r="429" spans="4:4">
       <c r="D429" s="17"/>
     </row>
-    <row r="430" spans="1:4">
-      <c r="A430" s="49"/>
+    <row r="430" spans="4:4">
       <c r="D430" s="17"/>
     </row>
-    <row r="431" spans="1:4">
-      <c r="A431" s="49"/>
+    <row r="431" spans="4:4">
       <c r="D431" s="17"/>
     </row>
-    <row r="432" spans="1:4">
-      <c r="A432" s="49"/>
+    <row r="432" spans="4:4">
       <c r="D432" s="17"/>
     </row>
-    <row r="433" spans="1:4">
-      <c r="A433" s="49"/>
+    <row r="433" spans="4:4">
       <c r="D433" s="17"/>
     </row>
-    <row r="434" spans="1:4">
-      <c r="A434" s="49"/>
+    <row r="434" spans="4:4">
       <c r="D434" s="17"/>
     </row>
-    <row r="435" spans="1:4">
-      <c r="A435" s="49"/>
+    <row r="435" spans="4:4">
       <c r="D435" s="17"/>
     </row>
-    <row r="436" spans="1:4">
-      <c r="A436" s="49"/>
+    <row r="436" spans="4:4">
       <c r="D436" s="17"/>
     </row>
-    <row r="437" spans="1:4">
-      <c r="A437" s="49"/>
+    <row r="437" spans="4:4">
       <c r="D437" s="17"/>
     </row>
-    <row r="438" spans="1:4">
-      <c r="A438" s="49"/>
+    <row r="438" spans="4:4">
       <c r="D438" s="17"/>
     </row>
-    <row r="439" spans="1:4">
-      <c r="A439" s="49"/>
+    <row r="439" spans="4:4">
       <c r="D439" s="17"/>
     </row>
-    <row r="440" spans="1:4">
-      <c r="A440" s="49"/>
+    <row r="440" spans="4:4">
       <c r="D440" s="17"/>
     </row>
-    <row r="441" spans="1:4">
-      <c r="A441" s="49"/>
+    <row r="441" spans="4:4">
       <c r="D441" s="17"/>
     </row>
-    <row r="442" spans="1:4">
-      <c r="A442" s="49"/>
+    <row r="442" spans="4:4">
       <c r="D442" s="17"/>
     </row>
-    <row r="443" spans="1:4">
-      <c r="A443" s="49"/>
+    <row r="443" spans="4:4">
       <c r="D443" s="17"/>
     </row>
-    <row r="444" spans="1:4">
-      <c r="A444" s="49"/>
+    <row r="444" spans="4:4">
       <c r="D444" s="17"/>
     </row>
-    <row r="445" spans="1:4">
-      <c r="A445" s="49"/>
+    <row r="445" spans="4:4">
       <c r="D445" s="17"/>
     </row>
-    <row r="446" spans="1:4">
-      <c r="A446" s="49"/>
+    <row r="446" spans="4:4">
       <c r="D446" s="17"/>
     </row>
-    <row r="447" spans="1:4">
-      <c r="A447" s="49"/>
+    <row r="447" spans="4:4">
       <c r="D447" s="17"/>
     </row>
-    <row r="448" spans="1:4">
-      <c r="A448" s="49"/>
+    <row r="448" spans="4:4">
       <c r="D448" s="17"/>
     </row>
-    <row r="449" spans="1:4">
-      <c r="A449" s="49"/>
+    <row r="449" spans="4:4">
       <c r="D449" s="17"/>
     </row>
-    <row r="450" spans="1:4">
-      <c r="A450" s="49"/>
+    <row r="450" spans="4:4">
       <c r="D450" s="17"/>
     </row>
-    <row r="451" spans="1:4">
-      <c r="A451" s="49"/>
+    <row r="451" spans="4:4">
       <c r="D451" s="17"/>
     </row>
-    <row r="452" spans="1:4">
-      <c r="A452" s="49"/>
+    <row r="452" spans="4:4">
       <c r="D452" s="17"/>
     </row>
-    <row r="453" spans="1:4">
-      <c r="A453" s="49"/>
+    <row r="453" spans="4:4">
       <c r="D453" s="17"/>
     </row>
-    <row r="454" spans="1:4">
-      <c r="A454" s="49"/>
+    <row r="454" spans="4:4">
       <c r="D454" s="17"/>
     </row>
-    <row r="455" spans="1:4">
-      <c r="A455" s="49"/>
+    <row r="455" spans="4:4">
       <c r="D455" s="17"/>
     </row>
-    <row r="456" spans="1:4">
-      <c r="A456" s="49"/>
+    <row r="456" spans="4:4">
       <c r="D456" s="17"/>
     </row>
-    <row r="457" spans="1:4">
-      <c r="A457" s="49"/>
+    <row r="457" spans="4:4">
       <c r="D457" s="17"/>
     </row>
-    <row r="458" spans="1:4">
-      <c r="A458" s="49"/>
+    <row r="458" spans="4:4">
       <c r="D458" s="17"/>
     </row>
-    <row r="459" spans="1:4">
-      <c r="A459" s="49"/>
+    <row r="459" spans="4:4">
       <c r="D459" s="17"/>
     </row>
-    <row r="460" spans="1:4">
-      <c r="A460" s="49"/>
+    <row r="460" spans="4:4">
       <c r="D460" s="17"/>
     </row>
-    <row r="461" spans="1:4">
-      <c r="A461" s="49"/>
+    <row r="461" spans="4:4">
       <c r="D461" s="17"/>
     </row>
-    <row r="462" spans="1:4">
-      <c r="A462" s="49"/>
+    <row r="462" spans="4:4">
       <c r="D462" s="17"/>
     </row>
-    <row r="463" spans="1:4">
-      <c r="A463" s="49"/>
+    <row r="463" spans="4:4">
       <c r="D463" s="17"/>
     </row>
-    <row r="464" spans="1:4">
-      <c r="A464" s="49"/>
+    <row r="464" spans="4:4">
       <c r="D464" s="17"/>
     </row>
-    <row r="465" spans="1:4">
-      <c r="A465" s="49"/>
+    <row r="465" spans="4:4">
       <c r="D465" s="17"/>
     </row>
-    <row r="466" spans="1:4">
-      <c r="A466" s="49"/>
+    <row r="466" spans="4:4">
       <c r="D466" s="17"/>
     </row>
-    <row r="467" spans="1:4">
-      <c r="A467" s="49"/>
+    <row r="467" spans="4:4">
       <c r="D467" s="17"/>
     </row>
-    <row r="468" spans="1:4">
-      <c r="A468" s="49"/>
+    <row r="468" spans="4:4">
       <c r="D468" s="17"/>
     </row>
-    <row r="469" spans="1:4">
-      <c r="A469" s="49"/>
+    <row r="469" spans="4:4">
       <c r="D469" s="17"/>
     </row>
-    <row r="470" spans="1:4">
-      <c r="A470" s="49"/>
+    <row r="470" spans="4:4">
       <c r="D470" s="17"/>
     </row>
-    <row r="471" spans="1:4">
-      <c r="A471" s="49"/>
+    <row r="471" spans="4:4">
       <c r="D471" s="17"/>
     </row>
-    <row r="472" spans="1:4">
-      <c r="A472" s="49"/>
+    <row r="472" spans="4:4">
       <c r="D472" s="17"/>
     </row>
-    <row r="473" spans="1:4">
-      <c r="A473" s="49"/>
+    <row r="473" spans="4:4">
       <c r="D473" s="17"/>
     </row>
-    <row r="474" spans="1:4">
-      <c r="A474" s="49"/>
+    <row r="474" spans="4:4">
       <c r="D474" s="17"/>
     </row>
-    <row r="475" spans="1:4">
-      <c r="A475" s="49"/>
+    <row r="475" spans="4:4">
       <c r="D475" s="17"/>
     </row>
-    <row r="476" spans="1:4">
-      <c r="A476" s="49"/>
+    <row r="476" spans="4:4">
       <c r="D476" s="17"/>
     </row>
-    <row r="477" spans="1:4">
-      <c r="A477" s="49"/>
+    <row r="477" spans="4:4">
       <c r="D477" s="17"/>
     </row>
-    <row r="478" spans="1:4">
-      <c r="A478" s="49"/>
+    <row r="478" spans="4:4">
       <c r="D478" s="17"/>
     </row>
-    <row r="479" spans="1:4">
-      <c r="A479" s="49"/>
+    <row r="479" spans="4:4">
       <c r="D479" s="17"/>
     </row>
-    <row r="480" spans="1:4">
-      <c r="A480" s="49"/>
+    <row r="480" spans="4:4">
       <c r="D480" s="17"/>
     </row>
-    <row r="481" spans="1:4">
-      <c r="A481" s="49"/>
+    <row r="481" spans="4:4">
       <c r="D481" s="17"/>
     </row>
-    <row r="482" spans="1:4">
-      <c r="A482" s="49"/>
+    <row r="482" spans="4:4">
       <c r="D482" s="17"/>
     </row>
-    <row r="483" spans="1:4">
-      <c r="A483" s="49"/>
+    <row r="483" spans="4:4">
       <c r="D483" s="17"/>
     </row>
-    <row r="484" spans="1:4">
-      <c r="A484" s="49"/>
+    <row r="484" spans="4:4">
       <c r="D484" s="17"/>
     </row>
-    <row r="485" spans="1:4">
-      <c r="A485" s="49"/>
+    <row r="485" spans="4:4">
       <c r="D485" s="17"/>
     </row>
-    <row r="486" spans="1:4">
-      <c r="A486" s="49"/>
+    <row r="486" spans="4:4">
       <c r="D486" s="17"/>
     </row>
-    <row r="487" spans="1:4">
-      <c r="A487" s="49"/>
+    <row r="487" spans="4:4">
       <c r="D487" s="17"/>
     </row>
-    <row r="488" spans="1:4">
-      <c r="A488" s="49"/>
+    <row r="488" spans="4:4">
       <c r="D488" s="17"/>
     </row>
-    <row r="489" spans="1:4">
-      <c r="A489" s="49"/>
+    <row r="489" spans="4:4">
       <c r="D489" s="17"/>
     </row>
-    <row r="490" spans="1:4">
-      <c r="A490" s="49"/>
+    <row r="490" spans="4:4">
       <c r="D490" s="17"/>
     </row>
-    <row r="491" spans="1:4">
-      <c r="A491" s="49"/>
+    <row r="491" spans="4:4">
       <c r="D491" s="17"/>
     </row>
-    <row r="492" spans="1:4">
-      <c r="A492" s="49"/>
+    <row r="492" spans="4:4">
       <c r="D492" s="17"/>
     </row>
-    <row r="493" spans="1:4">
-      <c r="A493" s="49"/>
+    <row r="493" spans="4:4">
       <c r="D493" s="17"/>
     </row>
-    <row r="494" spans="1:4">
-      <c r="A494" s="49"/>
+    <row r="494" spans="4:4">
       <c r="D494" s="17"/>
     </row>
-    <row r="495" spans="1:4">
-      <c r="A495" s="49"/>
+    <row r="495" spans="4:4">
       <c r="D495" s="17"/>
     </row>
-    <row r="496" spans="1:4">
-      <c r="A496" s="49"/>
+    <row r="496" spans="4:4">
       <c r="D496" s="17"/>
     </row>
-    <row r="497" spans="1:4">
-      <c r="A497" s="49"/>
+    <row r="497" spans="4:4">
       <c r="D497" s="17"/>
     </row>
-    <row r="498" spans="1:4">
-      <c r="A498" s="49"/>
+    <row r="498" spans="4:4">
       <c r="D498" s="17"/>
     </row>
-    <row r="499" spans="1:4">
-      <c r="A499" s="49"/>
+    <row r="499" spans="4:4">
       <c r="D499" s="17"/>
     </row>
-    <row r="500" spans="1:4">
-      <c r="A500" s="49"/>
+    <row r="500" spans="4:4">
       <c r="D500" s="17"/>
     </row>
-    <row r="501" spans="1:4">
-      <c r="A501" s="49"/>
+    <row r="501" spans="4:4">
       <c r="D501" s="17"/>
     </row>
-    <row r="502" spans="1:4">
-      <c r="A502" s="49"/>
+    <row r="502" spans="4:4">
       <c r="D502" s="17"/>
     </row>
-    <row r="503" spans="1:4">
-      <c r="A503" s="49"/>
+    <row r="503" spans="4:4">
       <c r="D503" s="17"/>
     </row>
-    <row r="504" spans="1:4">
-      <c r="A504" s="49"/>
+    <row r="504" spans="4:4">
       <c r="D504" s="17"/>
     </row>
-    <row r="505" spans="1:4">
-      <c r="A505" s="49"/>
+    <row r="505" spans="4:4">
       <c r="D505" s="17"/>
     </row>
-    <row r="506" spans="1:4">
-      <c r="A506" s="49"/>
+    <row r="506" spans="4:4">
       <c r="D506" s="17"/>
     </row>
-    <row r="507" spans="1:4">
-      <c r="A507" s="49"/>
+    <row r="507" spans="4:4">
       <c r="D507" s="17"/>
     </row>
-    <row r="508" spans="1:4">
-      <c r="A508" s="49"/>
+    <row r="508" spans="4:4">
       <c r="D508" s="17"/>
     </row>
-    <row r="509" spans="1:4">
-      <c r="A509" s="49"/>
+    <row r="509" spans="4:4">
       <c r="D509" s="17"/>
     </row>
-    <row r="510" spans="1:4">
-      <c r="A510" s="49"/>
+    <row r="510" spans="4:4">
       <c r="D510" s="17"/>
     </row>
-    <row r="511" spans="1:4">
-      <c r="A511" s="49"/>
+    <row r="511" spans="4:4">
       <c r="D511" s="17"/>
     </row>
-    <row r="512" spans="1:4">
-      <c r="A512" s="49"/>
+    <row r="512" spans="4:4">
       <c r="D512" s="17"/>
     </row>
-    <row r="513" spans="1:4">
-      <c r="A513" s="49"/>
+    <row r="513" spans="4:4">
       <c r="D513" s="17"/>
     </row>
-    <row r="514" spans="1:4">
-      <c r="A514" s="49"/>
+    <row r="514" spans="4:4">
       <c r="D514" s="17"/>
     </row>
-    <row r="515" spans="1:4">
-      <c r="A515" s="49"/>
+    <row r="515" spans="4:4">
       <c r="D515" s="17"/>
     </row>
-    <row r="516" spans="1:4">
-      <c r="A516" s="49"/>
+    <row r="516" spans="4:4">
       <c r="D516" s="17"/>
     </row>
-    <row r="517" spans="1:4">
-      <c r="A517" s="49"/>
+    <row r="517" spans="4:4">
       <c r="D517" s="17"/>
     </row>
-    <row r="518" spans="1:4">
-      <c r="A518" s="49"/>
+    <row r="518" spans="4:4">
       <c r="D518" s="17"/>
     </row>
-    <row r="519" spans="1:4">
-      <c r="A519" s="49"/>
+    <row r="519" spans="4:4">
       <c r="D519" s="17"/>
     </row>
-    <row r="520" spans="1:4">
-      <c r="A520" s="49"/>
+    <row r="520" spans="4:4">
       <c r="D520" s="17"/>
     </row>
-    <row r="521" spans="1:4">
-      <c r="A521" s="49"/>
+    <row r="521" spans="4:4">
       <c r="D521" s="17"/>
     </row>
-    <row r="522" spans="1:4">
-      <c r="A522" s="49"/>
+    <row r="522" spans="4:4">
       <c r="D522" s="17"/>
     </row>
-    <row r="523" spans="1:4">
-      <c r="A523" s="49"/>
+    <row r="523" spans="4:4">
       <c r="D523" s="17"/>
     </row>
-    <row r="524" spans="1:4">
-      <c r="A524" s="49"/>
+    <row r="524" spans="4:4">
       <c r="D524" s="17"/>
     </row>
-    <row r="525" spans="1:4">
-      <c r="A525" s="49"/>
+    <row r="525" spans="4:4">
       <c r="D525" s="17"/>
     </row>
-    <row r="526" spans="1:4">
-      <c r="A526" s="49"/>
+    <row r="526" spans="4:4">
       <c r="D526" s="17"/>
     </row>
-    <row r="527" spans="1:4">
-      <c r="A527" s="49"/>
+    <row r="527" spans="4:4">
       <c r="D527" s="17"/>
     </row>
-    <row r="528" spans="1:4">
-      <c r="A528" s="49"/>
+    <row r="528" spans="4:4">
       <c r="D528" s="17"/>
     </row>
-    <row r="529" spans="1:4">
-      <c r="A529" s="49"/>
+    <row r="529" spans="4:4">
       <c r="D529" s="17"/>
     </row>
-    <row r="530" spans="1:4">
-      <c r="A530" s="49"/>
+    <row r="530" spans="4:4">
       <c r="D530" s="17"/>
     </row>
-    <row r="531" spans="1:4">
-      <c r="A531" s="49"/>
+    <row r="531" spans="4:4">
       <c r="D531" s="17"/>
     </row>
-    <row r="532" spans="1:4">
-      <c r="A532" s="49"/>
+    <row r="532" spans="4:4">
       <c r="D532" s="17"/>
     </row>
-    <row r="533" spans="1:4">
-      <c r="A533" s="49"/>
+    <row r="533" spans="4:4">
       <c r="D533" s="17"/>
     </row>
-    <row r="534" spans="1:4">
-      <c r="A534" s="49"/>
+    <row r="534" spans="4:4">
       <c r="D534" s="17"/>
     </row>
-    <row r="535" spans="1:4">
-      <c r="A535" s="49"/>
+    <row r="535" spans="4:4">
       <c r="D535" s="17"/>
     </row>
-    <row r="536" spans="1:4">
-      <c r="A536" s="49"/>
+    <row r="536" spans="4:4">
       <c r="D536" s="17"/>
     </row>
-    <row r="537" spans="1:4">
-      <c r="A537" s="49"/>
+    <row r="537" spans="4:4">
       <c r="D537" s="17"/>
     </row>
-    <row r="538" spans="1:4">
-      <c r="A538" s="49"/>
+    <row r="538" spans="4:4">
       <c r="D538" s="17"/>
     </row>
-    <row r="539" spans="1:4">
-      <c r="A539" s="49"/>
+    <row r="539" spans="4:4">
       <c r="D539" s="17"/>
     </row>
-    <row r="540" spans="1:4">
-      <c r="A540" s="49"/>
+    <row r="540" spans="4:4">
       <c r="D540" s="17"/>
     </row>
-    <row r="541" spans="1:4">
-      <c r="A541" s="49"/>
+    <row r="541" spans="4:4">
       <c r="D541" s="17"/>
     </row>
-    <row r="542" spans="1:4">
-      <c r="A542" s="49"/>
+    <row r="542" spans="4:4">
       <c r="D542" s="17"/>
     </row>
-    <row r="543" spans="1:4">
-      <c r="A543" s="49"/>
+    <row r="543" spans="4:4">
       <c r="D543" s="17"/>
     </row>
-    <row r="544" spans="1:4">
-      <c r="A544" s="49"/>
+    <row r="544" spans="4:4">
       <c r="D544" s="17"/>
     </row>
-    <row r="545" spans="1:4">
-      <c r="A545" s="49"/>
+    <row r="545" spans="4:4">
       <c r="D545" s="17"/>
     </row>
-    <row r="546" spans="1:4">
-      <c r="A546" s="49"/>
+    <row r="546" spans="4:4">
       <c r="D546" s="17"/>
     </row>
-    <row r="547" spans="1:4">
-      <c r="A547" s="49"/>
+    <row r="547" spans="4:4">
       <c r="D547" s="17"/>
     </row>
-    <row r="548" spans="1:4">
-      <c r="A548" s="49"/>
+    <row r="548" spans="4:4">
       <c r="D548" s="17"/>
     </row>
-    <row r="549" spans="1:4">
-      <c r="A549" s="49"/>
+    <row r="549" spans="4:4">
       <c r="D549" s="17"/>
     </row>
-    <row r="550" spans="1:4">
-      <c r="A550" s="49"/>
+    <row r="550" spans="4:4">
       <c r="D550" s="17"/>
     </row>
-    <row r="551" spans="1:4">
-      <c r="A551" s="49"/>
+    <row r="551" spans="4:4">
       <c r="D551" s="17"/>
     </row>
-    <row r="552" spans="1:4">
-      <c r="A552" s="49"/>
+    <row r="552" spans="4:4">
       <c r="D552" s="17"/>
     </row>
-    <row r="553" spans="1:4">
-      <c r="A553" s="49"/>
+    <row r="553" spans="4:4">
       <c r="D553" s="17"/>
     </row>
-    <row r="554" spans="1:4">
-      <c r="A554" s="49"/>
+    <row r="554" spans="4:4">
       <c r="D554" s="17"/>
     </row>
-    <row r="555" spans="1:4">
-      <c r="A555" s="49"/>
+    <row r="555" spans="4:4">
       <c r="D555" s="17"/>
     </row>
-    <row r="556" spans="1:4">
-      <c r="A556" s="49"/>
+    <row r="556" spans="4:4">
       <c r="D556" s="17"/>
     </row>
-    <row r="557" spans="1:4">
-      <c r="A557" s="49"/>
+    <row r="557" spans="4:4">
       <c r="D557" s="17"/>
     </row>
-    <row r="558" spans="1:4">
-      <c r="A558" s="49"/>
+    <row r="558" spans="4:4">
       <c r="D558" s="17"/>
     </row>
-    <row r="559" spans="1:4">
-      <c r="A559" s="49"/>
+    <row r="559" spans="4:4">
       <c r="D559" s="17"/>
     </row>
-    <row r="560" spans="1:4">
-      <c r="A560" s="49"/>
+    <row r="560" spans="4:4">
       <c r="D560" s="17"/>
     </row>
-    <row r="561" spans="1:4">
-      <c r="A561" s="49"/>
+    <row r="561" spans="4:4">
       <c r="D561" s="17"/>
     </row>
-    <row r="562" spans="1:4">
-      <c r="A562" s="49"/>
+    <row r="562" spans="4:4">
       <c r="D562" s="17"/>
     </row>
-    <row r="563" spans="1:4">
-      <c r="A563" s="49"/>
+    <row r="563" spans="4:4">
       <c r="D563" s="17"/>
     </row>
-    <row r="564" spans="1:4">
-      <c r="A564" s="49"/>
+    <row r="564" spans="4:4">
       <c r="D564" s="17"/>
     </row>
-    <row r="565" spans="1:4">
-      <c r="A565" s="49"/>
+    <row r="565" spans="4:4">
       <c r="D565" s="17"/>
     </row>
-    <row r="566" spans="1:4">
-      <c r="A566" s="49"/>
+    <row r="566" spans="4:4">
       <c r="D566" s="17"/>
     </row>
-    <row r="567" spans="1:4">
-      <c r="A567" s="49"/>
+    <row r="567" spans="4:4">
       <c r="D567" s="17"/>
     </row>
-    <row r="568" spans="1:4">
-      <c r="A568" s="49"/>
+    <row r="568" spans="4:4">
       <c r="D568" s="17"/>
     </row>
-    <row r="569" spans="1:4">
-      <c r="A569" s="49"/>
+    <row r="569" spans="4:4">
       <c r="D569" s="17"/>
     </row>
-    <row r="570" spans="1:4">
-      <c r="A570" s="49"/>
+    <row r="570" spans="4:4">
       <c r="D570" s="17"/>
     </row>
-    <row r="571" spans="1:4">
-      <c r="A571" s="49"/>
+    <row r="571" spans="4:4">
       <c r="D571" s="17"/>
     </row>
-    <row r="572" spans="1:4">
-      <c r="A572" s="49"/>
+    <row r="572" spans="4:4">
       <c r="D572" s="17"/>
     </row>
-    <row r="573" spans="1:4">
-      <c r="A573" s="49"/>
+    <row r="573" spans="4:4">
       <c r="D573" s="17"/>
     </row>
-    <row r="574" spans="1:4">
-      <c r="A574" s="49"/>
+    <row r="574" spans="4:4">
       <c r="D574" s="17"/>
     </row>
-    <row r="575" spans="1:4">
-      <c r="A575" s="49"/>
+    <row r="575" spans="4:4">
       <c r="D575" s="17"/>
     </row>
-    <row r="576" spans="1:4">
-      <c r="A576" s="49"/>
+    <row r="576" spans="4:4">
       <c r="D576" s="17"/>
     </row>
-    <row r="577" spans="1:4">
-      <c r="A577" s="49"/>
+    <row r="577" spans="4:4">
       <c r="D577" s="17"/>
     </row>
-    <row r="578" spans="1:4">
-      <c r="A578" s="49"/>
+    <row r="578" spans="4:4">
       <c r="D578" s="17"/>
     </row>
-    <row r="579" spans="1:4">
-      <c r="A579" s="49"/>
+    <row r="579" spans="4:4">
       <c r="D579" s="17"/>
     </row>
-    <row r="580" spans="1:4">
-      <c r="A580" s="49"/>
+    <row r="580" spans="4:4">
       <c r="D580" s="17"/>
     </row>
-    <row r="581" spans="1:4">
-      <c r="A581" s="49"/>
+    <row r="581" spans="4:4">
       <c r="D581" s="17"/>
     </row>
-    <row r="582" spans="1:4">
-      <c r="A582" s="49"/>
+    <row r="582" spans="4:4">
       <c r="D582" s="17"/>
     </row>
-    <row r="583" spans="1:4">
-      <c r="A583" s="49"/>
+    <row r="583" spans="4:4">
       <c r="D583" s="17"/>
     </row>
-    <row r="584" spans="1:4">
-      <c r="A584" s="49"/>
+    <row r="584" spans="4:4">
       <c r="D584" s="17"/>
     </row>
-    <row r="585" spans="1:4">
-      <c r="A585" s="49"/>
+    <row r="585" spans="4:4">
       <c r="D585" s="17"/>
     </row>
-    <row r="586" spans="1:4">
-      <c r="A586" s="49"/>
+    <row r="586" spans="4:4">
       <c r="D586" s="17"/>
     </row>
-    <row r="587" spans="1:4">
-      <c r="A587" s="49"/>
+    <row r="587" spans="4:4">
       <c r="D587" s="17"/>
     </row>
-    <row r="588" spans="1:4">
-      <c r="A588" s="49"/>
+    <row r="588" spans="4:4">
       <c r="D588" s="17"/>
     </row>
-    <row r="589" spans="1:4">
-      <c r="A589" s="49"/>
+    <row r="589" spans="4:4">
       <c r="D589" s="17"/>
     </row>
-    <row r="590" spans="1:4">
-      <c r="A590" s="49"/>
+    <row r="590" spans="4:4">
       <c r="D590" s="17"/>
     </row>
-    <row r="591" spans="1:4">
-      <c r="A591" s="49"/>
+    <row r="591" spans="4:4">
       <c r="D591" s="17"/>
     </row>
-    <row r="592" spans="1:4">
-      <c r="A592" s="49"/>
+    <row r="592" spans="4:4">
       <c r="D592" s="17"/>
     </row>
-    <row r="593" spans="1:4">
-      <c r="A593" s="49"/>
+    <row r="593" spans="4:4">
       <c r="D593" s="17"/>
     </row>
-    <row r="594" spans="1:4">
-      <c r="A594" s="49"/>
+    <row r="594" spans="4:4">
       <c r="D594" s="17"/>
     </row>
-    <row r="595" spans="1:4">
-      <c r="A595" s="49"/>
+    <row r="595" spans="4:4">
       <c r="D595" s="17"/>
     </row>
-    <row r="596" spans="1:4">
-      <c r="A596" s="49"/>
+    <row r="596" spans="4:4">
       <c r="D596" s="17"/>
     </row>
-    <row r="597" spans="1:4">
-      <c r="A597" s="49"/>
+    <row r="597" spans="4:4">
       <c r="D597" s="17"/>
     </row>
-    <row r="598" spans="1:4">
-      <c r="A598" s="49"/>
+    <row r="598" spans="4:4">
       <c r="D598" s="17"/>
     </row>
-    <row r="599" spans="1:4">
-      <c r="A599" s="49"/>
+    <row r="599" spans="4:4">
       <c r="D599" s="17"/>
     </row>
-    <row r="600" spans="1:4">
-      <c r="A600" s="49"/>
+    <row r="600" spans="4:4">
       <c r="D600" s="17"/>
     </row>
-    <row r="601" spans="1:4">
-      <c r="A601" s="49"/>
+    <row r="601" spans="4:4">
       <c r="D601" s="17"/>
     </row>
-    <row r="602" spans="1:4">
-      <c r="A602" s="49"/>
+    <row r="602" spans="4:4">
       <c r="D602" s="17"/>
     </row>
-    <row r="603" spans="1:4">
-      <c r="A603" s="49"/>
+    <row r="603" spans="4:4">
       <c r="D603" s="17"/>
     </row>
-    <row r="604" spans="1:4">
-      <c r="A604" s="49"/>
+    <row r="604" spans="4:4">
       <c r="D604" s="17"/>
     </row>
-    <row r="605" spans="1:4">
-      <c r="A605" s="49"/>
+    <row r="605" spans="4:4">
       <c r="D605" s="17"/>
     </row>
-    <row r="606" spans="1:4">
-      <c r="A606" s="49"/>
+    <row r="606" spans="4:4">
       <c r="D606" s="17"/>
     </row>
-    <row r="607" spans="1:4">
-      <c r="A607" s="49"/>
+    <row r="607" spans="4:4">
       <c r="D607" s="17"/>
     </row>
-    <row r="608" spans="1:4">
-      <c r="A608" s="49"/>
+    <row r="608" spans="4:4">
       <c r="D608" s="17"/>
     </row>
-    <row r="609" spans="1:4">
-      <c r="A609" s="49"/>
+    <row r="609" spans="4:4">
       <c r="D609" s="17"/>
     </row>
-    <row r="610" spans="1:4">
-      <c r="A610" s="49"/>
+    <row r="610" spans="4:4">
       <c r="D610" s="17"/>
     </row>
-    <row r="611" spans="1:4">
-      <c r="A611" s="49"/>
+    <row r="611" spans="4:4">
       <c r="D611" s="17"/>
     </row>
-    <row r="612" spans="1:4">
-      <c r="A612" s="49"/>
+    <row r="612" spans="4:4">
       <c r="D612" s="17"/>
     </row>
-    <row r="613" spans="1:4">
-      <c r="A613" s="49"/>
+    <row r="613" spans="4:4">
       <c r="D613" s="17"/>
     </row>
-    <row r="614" spans="1:4">
-      <c r="A614" s="49"/>
+    <row r="614" spans="4:4">
       <c r="D614" s="17"/>
     </row>
-    <row r="615" spans="1:4">
-      <c r="A615" s="49"/>
+    <row r="615" spans="4:4">
       <c r="D615" s="17"/>
     </row>
-    <row r="616" spans="1:4">
-      <c r="A616" s="49"/>
+    <row r="616" spans="4:4">
       <c r="D616" s="17"/>
     </row>
-    <row r="617" spans="1:4">
-      <c r="A617" s="49"/>
+    <row r="617" spans="4:4">
       <c r="D617" s="17"/>
     </row>
-    <row r="618" spans="1:4">
-      <c r="A618" s="49"/>
+    <row r="618" spans="4:4">
       <c r="D618" s="17"/>
     </row>
-    <row r="619" spans="1:4">
-      <c r="A619" s="49"/>
+    <row r="619" spans="4:4">
       <c r="D619" s="17"/>
     </row>
-    <row r="620" spans="1:4">
-      <c r="A620" s="49"/>
+    <row r="620" spans="4:4">
       <c r="D620" s="17"/>
     </row>
-    <row r="621" spans="1:4">
-      <c r="A621" s="49"/>
+    <row r="621" spans="4:4">
       <c r="D621" s="17"/>
     </row>
-    <row r="622" spans="1:4">
-      <c r="A622" s="49"/>
+    <row r="622" spans="4:4">
       <c r="D622" s="17"/>
     </row>
-    <row r="623" spans="1:4">
-      <c r="A623" s="49"/>
+    <row r="623" spans="4:4">
       <c r="D623" s="17"/>
     </row>
-    <row r="624" spans="1:4">
-      <c r="A624" s="49"/>
+    <row r="624" spans="4:4">
       <c r="D624" s="17"/>
     </row>
-    <row r="625" spans="1:4">
-      <c r="A625" s="49"/>
+    <row r="625" spans="4:4">
       <c r="D625" s="17"/>
     </row>
-    <row r="626" spans="1:4">
-      <c r="A626" s="49"/>
+    <row r="626" spans="4:4">
       <c r="D626" s="17"/>
     </row>
-    <row r="627" spans="1:4">
-      <c r="A627" s="49"/>
+    <row r="627" spans="4:4">
       <c r="D627" s="17"/>
     </row>
-    <row r="628" spans="1:4">
-      <c r="A628" s="49"/>
+    <row r="628" spans="4:4">
       <c r="D628" s="17"/>
     </row>
-    <row r="629" spans="1:4">
-      <c r="A629" s="49"/>
+    <row r="629" spans="4:4">
       <c r="D629" s="17"/>
     </row>
-    <row r="630" spans="1:4">
-      <c r="A630" s="49"/>
+    <row r="630" spans="4:4">
       <c r="D630" s="17"/>
     </row>
-    <row r="631" spans="1:4">
-      <c r="A631" s="49"/>
+    <row r="631" spans="4:4">
       <c r="D631" s="17"/>
     </row>
-    <row r="632" spans="1:4">
-      <c r="A632" s="49"/>
+    <row r="632" spans="4:4">
       <c r="D632" s="17"/>
     </row>
-    <row r="633" spans="1:4">
-      <c r="A633" s="49"/>
+    <row r="633" spans="4:4">
       <c r="D633" s="17"/>
     </row>
-    <row r="634" spans="1:4">
-      <c r="A634" s="49"/>
+    <row r="634" spans="4:4">
       <c r="D634" s="17"/>
     </row>
-    <row r="635" spans="1:4">
-      <c r="A635" s="49"/>
+    <row r="635" spans="4:4">
       <c r="D635" s="17"/>
     </row>
-    <row r="636" spans="1:4">
-      <c r="A636" s="49"/>
+    <row r="636" spans="4:4">
       <c r="D636" s="17"/>
     </row>
-    <row r="637" spans="1:4">
-      <c r="A637" s="49"/>
+    <row r="637" spans="4:4">
       <c r="D637" s="17"/>
     </row>
-    <row r="638" spans="1:4">
-      <c r="A638" s="49"/>
+    <row r="638" spans="4:4">
       <c r="D638" s="17"/>
     </row>
-    <row r="639" spans="1:4">
-      <c r="A639" s="49"/>
+    <row r="639" spans="4:4">
       <c r="D639" s="17"/>
     </row>
-    <row r="640" spans="1:4">
-      <c r="A640" s="49"/>
+    <row r="640" spans="4:4">
       <c r="D640" s="17"/>
     </row>
-    <row r="641" spans="1:4">
-      <c r="A641" s="49"/>
+    <row r="641" spans="4:4">
       <c r="D641" s="17"/>
     </row>
-    <row r="642" spans="1:4">
-      <c r="A642" s="49"/>
+    <row r="642" spans="4:4">
       <c r="D642" s="17"/>
     </row>
-    <row r="643" spans="1:4">
-      <c r="A643" s="49"/>
+    <row r="643" spans="4:4">
       <c r="D643" s="17"/>
     </row>
-    <row r="644" spans="1:4">
-      <c r="A644" s="49"/>
+    <row r="644" spans="4:4">
       <c r="D644" s="17"/>
     </row>
-    <row r="645" spans="1:4">
-      <c r="A645" s="49"/>
+    <row r="645" spans="4:4">
       <c r="D645" s="17"/>
     </row>
-    <row r="646" spans="1:4">
-      <c r="A646" s="49"/>
+    <row r="646" spans="4:4">
       <c r="D646" s="17"/>
     </row>
-    <row r="647" spans="1:4">
-      <c r="A647" s="49"/>
+    <row r="647" spans="4:4">
       <c r="D647" s="17"/>
     </row>
-    <row r="648" spans="1:4">
-      <c r="A648" s="49"/>
+    <row r="648" spans="4:4">
       <c r="D648" s="17"/>
     </row>
-    <row r="649" spans="1:4">
-      <c r="A649" s="49"/>
+    <row r="649" spans="4:4">
       <c r="D649" s="17"/>
     </row>
-    <row r="650" spans="1:4">
-      <c r="A650" s="49"/>
+    <row r="650" spans="4:4">
       <c r="D650" s="17"/>
     </row>
-    <row r="651" spans="1:4">
-      <c r="A651" s="49"/>
+    <row r="651" spans="4:4">
       <c r="D651" s="17"/>
     </row>
-    <row r="652" spans="1:4">
-      <c r="A652" s="49"/>
+    <row r="652" spans="4:4">
       <c r="D652" s="17"/>
     </row>
-    <row r="653" spans="1:4">
-      <c r="A653" s="49"/>
+    <row r="653" spans="4:4">
       <c r="D653" s="17"/>
     </row>
-    <row r="654" spans="1:4">
-      <c r="A654" s="49"/>
+    <row r="654" spans="4:4">
       <c r="D654" s="17"/>
     </row>
-    <row r="655" spans="1:4">
-      <c r="A655" s="49"/>
+    <row r="655" spans="4:4">
       <c r="D655" s="17"/>
     </row>
-    <row r="656" spans="1:4">
-      <c r="A656" s="49"/>
+    <row r="656" spans="4:4">
       <c r="D656" s="17"/>
     </row>
-    <row r="657" spans="1:4">
-      <c r="A657" s="49"/>
+    <row r="657" spans="4:4">
       <c r="D657" s="17"/>
     </row>
-    <row r="658" spans="1:4">
-      <c r="A658" s="49"/>
+    <row r="658" spans="4:4">
       <c r="D658" s="17"/>
     </row>
-    <row r="659" spans="1:4">
-      <c r="A659" s="49"/>
+    <row r="659" spans="4:4">
       <c r="D659" s="17"/>
     </row>
-    <row r="660" spans="1:4">
-      <c r="A660" s="49"/>
+    <row r="660" spans="4:4">
       <c r="D660" s="17"/>
     </row>
-    <row r="661" spans="1:4">
-      <c r="A661" s="49"/>
+    <row r="661" spans="4:4">
       <c r="D661" s="17"/>
     </row>
-    <row r="662" spans="1:4">
-      <c r="A662" s="49"/>
+    <row r="662" spans="4:4">
       <c r="D662" s="17"/>
     </row>
-    <row r="663" spans="1:4">
-      <c r="A663" s="49"/>
+    <row r="663" spans="4:4">
       <c r="D663" s="17"/>
     </row>
-    <row r="664" spans="1:4">
-      <c r="A664" s="49"/>
+    <row r="664" spans="4:4">
       <c r="D664" s="17"/>
     </row>
-    <row r="665" spans="1:4">
-      <c r="A665" s="49"/>
+    <row r="665" spans="4:4">
       <c r="D665" s="17"/>
     </row>
-    <row r="666" spans="1:4">
-      <c r="A666" s="49"/>
+    <row r="666" spans="4:4">
       <c r="D666" s="17"/>
     </row>
-    <row r="667" spans="1:4">
-      <c r="A667" s="49"/>
+    <row r="667" spans="4:4">
       <c r="D667" s="17"/>
     </row>
-    <row r="668" spans="1:4">
-      <c r="A668" s="49"/>
+    <row r="668" spans="4:4">
       <c r="D668" s="17"/>
     </row>
-    <row r="669" spans="1:4">
-      <c r="A669" s="49"/>
+    <row r="669" spans="4:4">
       <c r="D669" s="17"/>
     </row>
-    <row r="670" spans="1:4">
-      <c r="A670" s="49"/>
+    <row r="670" spans="4:4">
       <c r="D670" s="17"/>
     </row>
-    <row r="671" spans="1:4">
-      <c r="A671" s="49"/>
+    <row r="671" spans="4:4">
       <c r="D671" s="17"/>
     </row>
-    <row r="672" spans="1:4">
-      <c r="A672" s="49"/>
+    <row r="672" spans="4:4">
       <c r="D672" s="17"/>
     </row>
-    <row r="673" spans="1:4">
-      <c r="A673" s="49"/>
+    <row r="673" spans="4:4">
       <c r="D673" s="17"/>
     </row>
-    <row r="674" spans="1:4">
-      <c r="A674" s="49"/>
+    <row r="674" spans="4:4">
       <c r="D674" s="17"/>
     </row>
-    <row r="675" spans="1:4">
-      <c r="A675" s="49"/>
+    <row r="675" spans="4:4">
       <c r="D675" s="17"/>
     </row>
-    <row r="676" spans="1:4">
-      <c r="A676" s="49"/>
+    <row r="676" spans="4:4">
       <c r="D676" s="17"/>
     </row>
-    <row r="677" spans="1:4">
-      <c r="A677" s="49"/>
+    <row r="677" spans="4:4">
       <c r="D677" s="17"/>
     </row>
-    <row r="678" spans="1:4">
-      <c r="A678" s="49"/>
+    <row r="678" spans="4:4">
       <c r="D678" s="17"/>
     </row>
-    <row r="679" spans="1:4">
-      <c r="A679" s="49"/>
+    <row r="679" spans="4:4">
       <c r="D679" s="17"/>
     </row>
-    <row r="680" spans="1:4">
-      <c r="A680" s="49"/>
+    <row r="680" spans="4:4">
       <c r="D680" s="17"/>
     </row>
-    <row r="681" spans="1:4">
-      <c r="A681" s="49"/>
+    <row r="681" spans="4:4">
       <c r="D681" s="17"/>
     </row>
-    <row r="682" spans="1:4">
-      <c r="A682" s="49"/>
+    <row r="682" spans="4:4">
       <c r="D682" s="17"/>
     </row>
-    <row r="683" spans="1:4">
-      <c r="A683" s="49"/>
+    <row r="683" spans="4:4">
       <c r="D683" s="17"/>
     </row>
-    <row r="684" spans="1:4">
-      <c r="A684" s="49"/>
+    <row r="684" spans="4:4">
       <c r="D684" s="17"/>
     </row>
-    <row r="685" spans="1:4">
-      <c r="A685" s="49"/>
+    <row r="685" spans="4:4">
       <c r="D685" s="17"/>
     </row>
-    <row r="686" spans="1:4">
-      <c r="A686" s="49"/>
+    <row r="686" spans="4:4">
       <c r="D686" s="17"/>
     </row>
-    <row r="687" spans="1:4">
-      <c r="A687" s="49"/>
+    <row r="687" spans="4:4">
       <c r="D687" s="17"/>
     </row>
-    <row r="688" spans="1:4">
-      <c r="A688" s="49"/>
+    <row r="688" spans="4:4">
       <c r="D688" s="17"/>
     </row>
-    <row r="689" spans="1:4">
-      <c r="A689" s="49"/>
+    <row r="689" spans="4:4">
       <c r="D689" s="17"/>
     </row>
-    <row r="690" spans="1:4">
-      <c r="A690" s="49"/>
+    <row r="690" spans="4:4">
       <c r="D690" s="17"/>
     </row>
-    <row r="691" spans="1:4">
-      <c r="A691" s="49"/>
+    <row r="691" spans="4:4">
       <c r="D691" s="17"/>
     </row>
-    <row r="692" spans="1:4">
-      <c r="A692" s="49"/>
+    <row r="692" spans="4:4">
       <c r="D692" s="17"/>
     </row>
-    <row r="693" spans="1:4">
-      <c r="A693" s="49"/>
+    <row r="693" spans="4:4">
       <c r="D693" s="17"/>
     </row>
-    <row r="694" spans="1:4">
-      <c r="A694" s="49"/>
+    <row r="694" spans="4:4">
       <c r="D694" s="17"/>
     </row>
-    <row r="695" spans="1:4">
-      <c r="A695" s="49"/>
+    <row r="695" spans="4:4">
       <c r="D695" s="17"/>
     </row>
-    <row r="696" spans="1:4">
-      <c r="A696" s="49"/>
+    <row r="696" spans="4:4">
       <c r="D696" s="17"/>
     </row>
-    <row r="697" spans="1:4">
-      <c r="A697" s="49"/>
+    <row r="697" spans="4:4">
       <c r="D697" s="17"/>
     </row>
-    <row r="698" spans="1:4">
-      <c r="A698" s="49"/>
+    <row r="698" spans="4:4">
       <c r="D698" s="17"/>
     </row>
-    <row r="699" spans="1:4">
-      <c r="A699" s="49"/>
+    <row r="699" spans="4:4">
       <c r="D699" s="17"/>
     </row>
-    <row r="700" spans="1:4">
-      <c r="A700" s="49"/>
+    <row r="700" spans="4:4">
       <c r="D700" s="17"/>
     </row>
-    <row r="701" spans="1:4">
-      <c r="A701" s="49"/>
+    <row r="701" spans="4:4">
       <c r="D701" s="17"/>
     </row>
-    <row r="702" spans="1:4">
-      <c r="A702" s="49"/>
+    <row r="702" spans="4:4">
       <c r="D702" s="17"/>
     </row>
-    <row r="703" spans="1:4">
-      <c r="A703" s="49"/>
+    <row r="703" spans="4:4">
       <c r="D703" s="17"/>
     </row>
-    <row r="704" spans="1:4">
-      <c r="A704" s="49"/>
+    <row r="704" spans="4:4">
       <c r="D704" s="17"/>
     </row>
-    <row r="705" spans="1:4">
-      <c r="A705" s="49"/>
+    <row r="705" spans="4:4">
       <c r="D705" s="17"/>
     </row>
-    <row r="706" spans="1:4">
-      <c r="A706" s="49"/>
+    <row r="706" spans="4:4">
       <c r="D706" s="17"/>
     </row>
-    <row r="707" spans="1:4">
-      <c r="A707" s="49"/>
+    <row r="707" spans="4:4">
       <c r="D707" s="17"/>
     </row>
-    <row r="708" spans="1:4">
-      <c r="A708" s="49"/>
+    <row r="708" spans="4:4">
       <c r="D708" s="17"/>
     </row>
-    <row r="709" spans="1:4">
-      <c r="A709" s="49"/>
+    <row r="709" spans="4:4">
       <c r="D709" s="17"/>
     </row>
-    <row r="710" spans="1:4">
-      <c r="A710" s="49"/>
+    <row r="710" spans="4:4">
       <c r="D710" s="17"/>
     </row>
-    <row r="711" spans="1:4">
-      <c r="A711" s="49"/>
+    <row r="711" spans="4:4">
       <c r="D711" s="17"/>
     </row>
-    <row r="712" spans="1:4">
-      <c r="A712" s="49"/>
+    <row r="712" spans="4:4">
       <c r="D712" s="17"/>
     </row>
-    <row r="713" spans="1:4">
-      <c r="A713" s="49"/>
+    <row r="713" spans="4:4">
       <c r="D713" s="17"/>
     </row>
-    <row r="714" spans="1:4">
-      <c r="A714" s="49"/>
+    <row r="714" spans="4:4">
       <c r="D714" s="17"/>
     </row>
-    <row r="715" spans="1:4">
-      <c r="A715" s="49"/>
+    <row r="715" spans="4:4">
       <c r="D715" s="17"/>
     </row>
-    <row r="716" spans="1:4">
-      <c r="A716" s="49"/>
+    <row r="716" spans="4:4">
       <c r="D716" s="17"/>
     </row>
-    <row r="717" spans="1:4">
-      <c r="A717" s="49"/>
+    <row r="717" spans="4:4">
       <c r="D717" s="17"/>
     </row>
-    <row r="718" spans="1:4">
-      <c r="A718" s="49"/>
+    <row r="718" spans="4:4">
       <c r="D718" s="17"/>
     </row>
-    <row r="719" spans="1:4">
-      <c r="A719" s="49"/>
+    <row r="719" spans="4:4">
       <c r="D719" s="17"/>
     </row>
-    <row r="720" spans="1:4">
-      <c r="A720" s="49"/>
+    <row r="720" spans="4:4">
       <c r="D720" s="17"/>
     </row>
-    <row r="721" spans="1:4">
-      <c r="A721" s="49"/>
+    <row r="721" spans="4:4">
       <c r="D721" s="17"/>
     </row>
-    <row r="722" spans="1:4">
-      <c r="A722" s="49"/>
+    <row r="722" spans="4:4">
       <c r="D722" s="17"/>
     </row>
-    <row r="723" spans="1:4">
-      <c r="A723" s="49"/>
+    <row r="723" spans="4:4">
       <c r="D723" s="17"/>
     </row>
-    <row r="724" spans="1:4">
-      <c r="A724" s="49"/>
+    <row r="724" spans="4:4">
       <c r="D724" s="17"/>
     </row>
-    <row r="725" spans="1:4">
-      <c r="A725" s="49"/>
+    <row r="725" spans="4:4">
       <c r="D725" s="17"/>
     </row>
-    <row r="726" spans="1:4">
-      <c r="A726" s="49"/>
+    <row r="726" spans="4:4">
       <c r="D726" s="17"/>
     </row>
-    <row r="727" spans="1:4">
-      <c r="A727" s="49"/>
+    <row r="727" spans="4:4">
       <c r="D727" s="17"/>
     </row>
-    <row r="728" spans="1:4">
-      <c r="A728" s="49"/>
+    <row r="728" spans="4:4">
       <c r="D728" s="17"/>
     </row>
-    <row r="729" spans="1:4">
-      <c r="A729" s="49"/>
+    <row r="729" spans="4:4">
       <c r="D729" s="17"/>
     </row>
-    <row r="730" spans="1:4">
-      <c r="A730" s="49"/>
+    <row r="730" spans="4:4">
       <c r="D730" s="17"/>
     </row>
-    <row r="731" spans="1:4">
-      <c r="A731" s="49"/>
+    <row r="731" spans="4:4">
       <c r="D731" s="17"/>
     </row>
-    <row r="732" spans="1:4">
-      <c r="A732" s="49"/>
+    <row r="732" spans="4:4">
       <c r="D732" s="17"/>
     </row>
-    <row r="733" spans="1:4">
-      <c r="A733" s="49"/>
+    <row r="733" spans="4:4">
       <c r="D733" s="17"/>
     </row>
-    <row r="734" spans="1:4">
-      <c r="A734" s="49"/>
+    <row r="734" spans="4:4">
       <c r="D734" s="17"/>
     </row>
-    <row r="735" spans="1:4">
-      <c r="A735" s="49"/>
+    <row r="735" spans="4:4">
       <c r="D735" s="17"/>
     </row>
-    <row r="736" spans="1:4">
-      <c r="A736" s="49"/>
+    <row r="736" spans="4:4">
       <c r="D736" s="17"/>
     </row>
-    <row r="737" spans="1:4">
-      <c r="A737" s="49"/>
+    <row r="737" spans="4:4">
       <c r="D737" s="17"/>
     </row>
-    <row r="738" spans="1:4">
-      <c r="A738" s="49"/>
+    <row r="738" spans="4:4">
       <c r="D738" s="17"/>
     </row>
-    <row r="739" spans="1:4">
-      <c r="A739" s="49"/>
+    <row r="739" spans="4:4">
       <c r="D739" s="17"/>
     </row>
-    <row r="740" spans="1:4">
-      <c r="A740" s="49"/>
+    <row r="740" spans="4:4">
       <c r="D740" s="17"/>
     </row>
-    <row r="741" spans="1:4">
-      <c r="A741" s="49"/>
+    <row r="741" spans="4:4">
       <c r="D741" s="17"/>
     </row>
-    <row r="742" spans="1:4">
-      <c r="A742" s="49"/>
+    <row r="742" spans="4:4">
       <c r="D742" s="17"/>
     </row>
-    <row r="743" spans="1:4">
-      <c r="A743" s="49"/>
+    <row r="743" spans="4:4">
       <c r="D743" s="17"/>
     </row>
-    <row r="744" spans="1:4">
-      <c r="A744" s="49"/>
+    <row r="744" spans="4:4">
       <c r="D744" s="17"/>
     </row>
-    <row r="745" spans="1:4">
-      <c r="A745" s="49"/>
+    <row r="745" spans="4:4">
       <c r="D745" s="17"/>
     </row>
-    <row r="746" spans="1:4">
-      <c r="A746" s="49"/>
+    <row r="746" spans="4:4">
       <c r="D746" s="17"/>
     </row>
-    <row r="747" spans="1:4">
-      <c r="A747" s="49"/>
+    <row r="747" spans="4:4">
       <c r="D747" s="17"/>
     </row>
-    <row r="748" spans="1:4">
-      <c r="A748" s="49"/>
+    <row r="748" spans="4:4">
       <c r="D748" s="17"/>
     </row>
-    <row r="749" spans="1:4">
-      <c r="A749" s="49"/>
+    <row r="749" spans="4:4">
       <c r="D749" s="17"/>
     </row>
-    <row r="750" spans="1:4">
-      <c r="A750" s="49"/>
+    <row r="750" spans="4:4">
       <c r="D750" s="17"/>
     </row>
-    <row r="751" spans="1:4">
-      <c r="A751" s="49"/>
+    <row r="751" spans="4:4">
       <c r="D751" s="17"/>
     </row>
-    <row r="752" spans="1:4">
-      <c r="A752" s="49"/>
+    <row r="752" spans="4:4">
       <c r="D752" s="17"/>
     </row>
-    <row r="753" spans="1:4">
-      <c r="A753" s="49"/>
+    <row r="753" spans="4:4">
       <c r="D753" s="17"/>
     </row>
-    <row r="754" spans="1:4">
-      <c r="A754" s="49"/>
+    <row r="754" spans="4:4">
       <c r="D754" s="17"/>
     </row>
-    <row r="755" spans="1:4">
-      <c r="A755" s="49"/>
+    <row r="755" spans="4:4">
       <c r="D755" s="17"/>
     </row>
-    <row r="756" spans="1:4">
-      <c r="A756" s="49"/>
+    <row r="756" spans="4:4">
       <c r="D756" s="17"/>
     </row>
-    <row r="757" spans="1:4">
-      <c r="A757" s="49"/>
+    <row r="757" spans="4:4">
       <c r="D757" s="17"/>
     </row>
-    <row r="758" spans="1:4">
-      <c r="A758" s="49"/>
+    <row r="758" spans="4:4">
       <c r="D758" s="17"/>
     </row>
-    <row r="759" spans="1:4">
-      <c r="A759" s="49"/>
+    <row r="759" spans="4:4">
       <c r="D759" s="17"/>
     </row>
-    <row r="760" spans="1:4">
-      <c r="A760" s="49"/>
+    <row r="760" spans="4:4">
       <c r="D760" s="17"/>
     </row>
-    <row r="761" spans="1:4">
-      <c r="A761" s="49"/>
+    <row r="761" spans="4:4">
       <c r="D761" s="17"/>
     </row>
-    <row r="762" spans="1:4">
-      <c r="A762" s="49"/>
+    <row r="762" spans="4:4">
       <c r="D762" s="17"/>
     </row>
-    <row r="763" spans="1:4">
-      <c r="A763" s="49"/>
+    <row r="763" spans="4:4">
       <c r="D763" s="17"/>
     </row>
-    <row r="764" spans="1:4">
-      <c r="A764" s="49"/>
+    <row r="764" spans="4:4">
       <c r="D764" s="17"/>
     </row>
-    <row r="765" spans="1:4">
-      <c r="A765" s="49"/>
+    <row r="765" spans="4:4">
       <c r="D765" s="17"/>
     </row>
-    <row r="766" spans="1:4">
-      <c r="A766" s="49"/>
+    <row r="766" spans="4:4">
       <c r="D766" s="17"/>
     </row>
-    <row r="767" spans="1:4">
-      <c r="A767" s="49"/>
+    <row r="767" spans="4:4">
       <c r="D767" s="17"/>
     </row>
-    <row r="768" spans="1:4">
-      <c r="A768" s="49"/>
+    <row r="768" spans="4:4">
       <c r="D768" s="17"/>
     </row>
-    <row r="769" spans="1:4">
-      <c r="A769" s="49"/>
+    <row r="769" spans="4:4">
       <c r="D769" s="17"/>
     </row>
-    <row r="770" spans="1:4">
-      <c r="A770" s="49"/>
+    <row r="770" spans="4:4">
       <c r="D770" s="17"/>
     </row>
-    <row r="771" spans="1:4">
-      <c r="A771" s="49"/>
+    <row r="771" spans="4:4">
       <c r="D771" s="17"/>
     </row>
-    <row r="772" spans="1:4">
-      <c r="A772" s="49"/>
+    <row r="772" spans="4:4">
       <c r="D772" s="17"/>
     </row>
-    <row r="773" spans="1:4">
-      <c r="A773" s="49"/>
+    <row r="773" spans="4:4">
       <c r="D773" s="17"/>
     </row>
-    <row r="774" spans="1:4">
-      <c r="A774" s="49"/>
+    <row r="774" spans="4:4">
       <c r="D774" s="17"/>
     </row>
-    <row r="775" spans="1:4">
-      <c r="A775" s="49"/>
+    <row r="775" spans="4:4">
       <c r="D775" s="17"/>
     </row>
-    <row r="776" spans="1:4">
-      <c r="A776" s="49"/>
+    <row r="776" spans="4:4">
       <c r="D776" s="17"/>
     </row>
-    <row r="777" spans="1:4">
-      <c r="A777" s="49"/>
+    <row r="777" spans="4:4">
       <c r="D777" s="17"/>
     </row>
-    <row r="778" spans="1:4">
-      <c r="A778" s="49"/>
+    <row r="778" spans="4:4">
       <c r="D778" s="17"/>
     </row>
-    <row r="779" spans="1:4">
-      <c r="A779" s="49"/>
+    <row r="779" spans="4:4">
       <c r="D779" s="17"/>
     </row>
-    <row r="780" spans="1:4">
-      <c r="A780" s="49"/>
+    <row r="780" spans="4:4">
       <c r="D780" s="17"/>
     </row>
-    <row r="781" spans="1:4">
-      <c r="A781" s="49"/>
+    <row r="781" spans="4:4">
       <c r="D781" s="17"/>
     </row>
-    <row r="782" spans="1:4">
-      <c r="A782" s="49"/>
+    <row r="782" spans="4:4">
       <c r="D782" s="17"/>
     </row>
-    <row r="783" spans="1:4">
-      <c r="A783" s="49"/>
+    <row r="783" spans="4:4">
       <c r="D783" s="17"/>
     </row>
-    <row r="784" spans="1:4">
-      <c r="A784" s="49"/>
+    <row r="784" spans="4:4">
       <c r="D784" s="17"/>
     </row>
-    <row r="785" spans="1:4">
-      <c r="A785" s="49"/>
+    <row r="785" spans="4:4">
       <c r="D785" s="17"/>
     </row>
-    <row r="786" spans="1:4">
-      <c r="A786" s="49"/>
+    <row r="786" spans="4:4">
       <c r="D786" s="17"/>
     </row>
-    <row r="787" spans="1:4">
-      <c r="A787" s="49"/>
+    <row r="787" spans="4:4">
       <c r="D787" s="17"/>
     </row>
-    <row r="788" spans="1:4">
-      <c r="A788" s="49"/>
+    <row r="788" spans="4:4">
       <c r="D788" s="17"/>
     </row>
-    <row r="789" spans="1:4">
-      <c r="A789" s="49"/>
+    <row r="789" spans="4:4">
       <c r="D789" s="17"/>
     </row>
-    <row r="790" spans="1:4">
-      <c r="A790" s="49"/>
+    <row r="790" spans="4:4">
       <c r="D790" s="17"/>
     </row>
-    <row r="791" spans="1:4">
-      <c r="A791" s="49"/>
+    <row r="791" spans="4:4">
       <c r="D791" s="17"/>
     </row>
-    <row r="792" spans="1:4">
-      <c r="A792" s="49"/>
+    <row r="792" spans="4:4">
       <c r="D792" s="17"/>
     </row>
-    <row r="793" spans="1:4">
-      <c r="A793" s="49"/>
+    <row r="793" spans="4:4">
       <c r="D793" s="17"/>
     </row>
-    <row r="794" spans="1:4">
-      <c r="A794" s="49"/>
+    <row r="794" spans="4:4">
       <c r="D794" s="17"/>
     </row>
-    <row r="795" spans="1:4">
-      <c r="A795" s="49"/>
+    <row r="795" spans="4:4">
       <c r="D795" s="17"/>
     </row>
-    <row r="796" spans="1:4">
-      <c r="A796" s="49"/>
+    <row r="796" spans="4:4">
       <c r="D796" s="17"/>
     </row>
-    <row r="797" spans="1:4">
-      <c r="A797" s="49"/>
+    <row r="797" spans="4:4">
       <c r="D797" s="17"/>
     </row>
-    <row r="798" spans="1:4">
-      <c r="A798" s="49"/>
+    <row r="798" spans="4:4">
       <c r="D798" s="17"/>
     </row>
-    <row r="799" spans="1:4">
-      <c r="A799" s="49"/>
+    <row r="799" spans="4:4">
       <c r="D799" s="17"/>
     </row>
-    <row r="800" spans="1:4">
-      <c r="A800" s="49"/>
+    <row r="800" spans="4:4">
       <c r="D800" s="17"/>
     </row>
-    <row r="801" spans="1:4">
-      <c r="A801" s="49"/>
+    <row r="801" spans="4:4">
       <c r="D801" s="17"/>
     </row>
-    <row r="802" spans="1:4">
-      <c r="A802" s="49"/>
+    <row r="802" spans="4:4">
       <c r="D802" s="17"/>
     </row>
-    <row r="803" spans="1:4">
-      <c r="A803" s="49"/>
+    <row r="803" spans="4:4">
       <c r="D803" s="17"/>
     </row>
-    <row r="804" spans="1:4">
-      <c r="A804" s="49"/>
+    <row r="804" spans="4:4">
       <c r="D804" s="17"/>
     </row>
-    <row r="805" spans="1:4">
-      <c r="A805" s="49"/>
+    <row r="805" spans="4:4">
       <c r="D805" s="17"/>
     </row>
-    <row r="806" spans="1:4">
-      <c r="A806" s="49"/>
+    <row r="806" spans="4:4">
       <c r="D806" s="17"/>
     </row>
-    <row r="807" spans="1:4">
-      <c r="A807" s="49"/>
+    <row r="807" spans="4:4">
       <c r="D807" s="17"/>
     </row>
-    <row r="808" spans="1:4">
-      <c r="A808" s="49"/>
+    <row r="808" spans="4:4">
       <c r="D808" s="17"/>
     </row>
-    <row r="809" spans="1:4">
-      <c r="A809" s="49"/>
+    <row r="809" spans="4:4">
       <c r="D809" s="17"/>
     </row>
-    <row r="810" spans="1:4">
-      <c r="A810" s="49"/>
+    <row r="810" spans="4:4">
       <c r="D810" s="17"/>
     </row>
-    <row r="811" spans="1:4">
-      <c r="A811" s="49"/>
+    <row r="811" spans="4:4">
       <c r="D811" s="17"/>
     </row>
-    <row r="812" spans="1:4">
-      <c r="A812" s="49"/>
+    <row r="812" spans="4:4">
       <c r="D812" s="17"/>
     </row>
-    <row r="813" spans="1:4">
-      <c r="A813" s="49"/>
+    <row r="813" spans="4:4">
       <c r="D813" s="17"/>
     </row>
-    <row r="814" spans="1:4">
-      <c r="A814" s="49"/>
+    <row r="814" spans="4:4">
       <c r="D814" s="17"/>
     </row>
-    <row r="815" spans="1:4">
-      <c r="A815" s="49"/>
+    <row r="815" spans="4:4">
       <c r="D815" s="17"/>
     </row>
-    <row r="816" spans="1:4">
-      <c r="A816" s="49"/>
+    <row r="816" spans="4:4">
       <c r="D816" s="17"/>
     </row>
-    <row r="817" spans="1:4">
-      <c r="A817" s="49"/>
+    <row r="817" spans="4:4">
       <c r="D817" s="17"/>
     </row>
-    <row r="818" spans="1:4">
-      <c r="A818" s="49"/>
+    <row r="818" spans="4:4">
       <c r="D818" s="17"/>
     </row>
-    <row r="819" spans="1:4">
-      <c r="A819" s="49"/>
+    <row r="819" spans="4:4">
       <c r="D819" s="17"/>
     </row>
-    <row r="820" spans="1:4">
-      <c r="A820" s="49"/>
+    <row r="820" spans="4:4">
       <c r="D820" s="17"/>
     </row>
-    <row r="821" spans="1:4">
-      <c r="A821" s="49"/>
+    <row r="821" spans="4:4">
       <c r="D821" s="17"/>
     </row>
-    <row r="822" spans="1:4">
-      <c r="A822" s="49"/>
+    <row r="822" spans="4:4">
       <c r="D822" s="17"/>
     </row>
-    <row r="823" spans="1:4">
-      <c r="A823" s="49"/>
+    <row r="823" spans="4:4">
       <c r="D823" s="17"/>
     </row>
-    <row r="824" spans="1:4">
-      <c r="A824" s="49"/>
+    <row r="824" spans="4:4">
       <c r="D824" s="17"/>
     </row>
-    <row r="825" spans="1:4">
-      <c r="A825" s="49"/>
+    <row r="825" spans="4:4">
       <c r="D825" s="17"/>
     </row>
-    <row r="826" spans="1:4">
-      <c r="A826" s="49"/>
+    <row r="826" spans="4:4">
       <c r="D826" s="17"/>
     </row>
-    <row r="827" spans="1:4">
-      <c r="A827" s="49"/>
+    <row r="827" spans="4:4">
       <c r="D827" s="17"/>
     </row>
-    <row r="828" spans="1:4">
-      <c r="A828" s="49"/>
+    <row r="828" spans="4:4">
       <c r="D828" s="17"/>
     </row>
-    <row r="829" spans="1:4">
-      <c r="A829" s="49"/>
+    <row r="829" spans="4:4">
       <c r="D829" s="17"/>
     </row>
-    <row r="830" spans="1:4">
-      <c r="A830" s="49"/>
+    <row r="830" spans="4:4">
       <c r="D830" s="17"/>
     </row>
-    <row r="831" spans="1:4">
-      <c r="A831" s="49"/>
+    <row r="831" spans="4:4">
       <c r="D831" s="17"/>
     </row>
-    <row r="832" spans="1:4">
-      <c r="A832" s="49"/>
+    <row r="832" spans="4:4">
       <c r="D832" s="17"/>
     </row>
-    <row r="833" spans="1:4">
-      <c r="A833" s="49"/>
+    <row r="833" spans="4:4">
       <c r="D833" s="17"/>
     </row>
-    <row r="834" spans="1:4">
-      <c r="A834" s="49"/>
+    <row r="834" spans="4:4">
       <c r="D834" s="17"/>
     </row>
-    <row r="835" spans="1:4">
-      <c r="A835" s="49"/>
+    <row r="835" spans="4:4">
       <c r="D835" s="17"/>
     </row>
-    <row r="836" spans="1:4">
-      <c r="A836" s="49"/>
+    <row r="836" spans="4:4">
       <c r="D836" s="17"/>
     </row>
-    <row r="837" spans="1:4">
-      <c r="A837" s="49"/>
+    <row r="837" spans="4:4">
       <c r="D837" s="17"/>
     </row>
-    <row r="838" spans="1:4">
-      <c r="A838" s="49"/>
+    <row r="838" spans="4:4">
       <c r="D838" s="17"/>
     </row>
-    <row r="839" spans="1:4">
-      <c r="A839" s="49"/>
+    <row r="839" spans="4:4">
       <c r="D839" s="17"/>
     </row>
-    <row r="840" spans="1:4">
-      <c r="A840" s="49"/>
+    <row r="840" spans="4:4">
       <c r="D840" s="17"/>
     </row>
-    <row r="841" spans="1:4">
-      <c r="A841" s="49"/>
+    <row r="841" spans="4:4">
       <c r="D841" s="17"/>
     </row>
-    <row r="842" spans="1:4">
-      <c r="A842" s="49"/>
+    <row r="842" spans="4:4">
       <c r="D842" s="17"/>
     </row>
-    <row r="843" spans="1:4">
-      <c r="A843" s="49"/>
+    <row r="843" spans="4:4">
       <c r="D843" s="17"/>
     </row>
-    <row r="844" spans="1:4">
-      <c r="A844" s="49"/>
+    <row r="844" spans="4:4">
       <c r="D844" s="17"/>
     </row>
-    <row r="845" spans="1:4">
-      <c r="A845" s="49"/>
+    <row r="845" spans="4:4">
       <c r="D845" s="17"/>
     </row>
-    <row r="846" spans="1:4">
-      <c r="A846" s="49"/>
+    <row r="846" spans="4:4">
       <c r="D846" s="17"/>
     </row>
-    <row r="847" spans="1:4">
-      <c r="A847" s="49"/>
+    <row r="847" spans="4:4">
       <c r="D847" s="17"/>
     </row>
-    <row r="848" spans="1:4">
-      <c r="A848" s="49"/>
+    <row r="848" spans="4:4">
       <c r="D848" s="17"/>
     </row>
-    <row r="849" spans="1:4">
-      <c r="A849" s="49"/>
+    <row r="849" spans="4:4">
       <c r="D849" s="17"/>
     </row>
-    <row r="850" spans="1:4">
-      <c r="A850" s="49"/>
+    <row r="850" spans="4:4">
       <c r="D850" s="17"/>
     </row>
-    <row r="851" spans="1:4">
-      <c r="A851" s="49"/>
+    <row r="851" spans="4:4">
       <c r="D851" s="17"/>
     </row>
-    <row r="852" spans="1:4">
-      <c r="A852" s="49"/>
+    <row r="852" spans="4:4">
       <c r="D852" s="17"/>
     </row>
-    <row r="853" spans="1:4">
-      <c r="A853" s="49"/>
+    <row r="853" spans="4:4">
       <c r="D853" s="17"/>
     </row>
-    <row r="854" spans="1:4">
-      <c r="A854" s="49"/>
+    <row r="854" spans="4:4">
       <c r="D854" s="17"/>
     </row>
-    <row r="855" spans="1:4">
-      <c r="A855" s="49"/>
+    <row r="855" spans="4:4">
       <c r="D855" s="17"/>
     </row>
-    <row r="856" spans="1:4">
-      <c r="A856" s="49"/>
+    <row r="856" spans="4:4">
       <c r="D856" s="17"/>
     </row>
-    <row r="857" spans="1:4">
-      <c r="A857" s="49"/>
+    <row r="857" spans="4:4">
       <c r="D857" s="17"/>
     </row>
-    <row r="858" spans="1:4">
-      <c r="A858" s="49"/>
+    <row r="858" spans="4:4">
       <c r="D858" s="17"/>
     </row>
-    <row r="859" spans="1:4">
-      <c r="A859" s="49"/>
+    <row r="859" spans="4:4">
       <c r="D859" s="17"/>
     </row>
-    <row r="860" spans="1:4">
-      <c r="A860" s="49"/>
+    <row r="860" spans="4:4">
       <c r="D860" s="17"/>
     </row>
-    <row r="861" spans="1:4">
-      <c r="A861" s="49"/>
+    <row r="861" spans="4:4">
       <c r="D861" s="17"/>
     </row>
-    <row r="862" spans="1:4">
-      <c r="A862" s="49"/>
+    <row r="862" spans="4:4">
       <c r="D862" s="17"/>
     </row>
-    <row r="863" spans="1:4">
-      <c r="A863" s="49"/>
+    <row r="863" spans="4:4">
       <c r="D863" s="17"/>
     </row>
-    <row r="864" spans="1:4">
-      <c r="A864" s="49"/>
+    <row r="864" spans="4:4">
       <c r="D864" s="17"/>
     </row>
-    <row r="865" spans="1:4">
-      <c r="A865" s="49"/>
+    <row r="865" spans="4:4">
       <c r="D865" s="17"/>
     </row>
-    <row r="866" spans="1:4">
-      <c r="A866" s="49"/>
+    <row r="866" spans="4:4">
       <c r="D866" s="17"/>
     </row>
-    <row r="867" spans="1:4">
-      <c r="A867" s="49"/>
+    <row r="867" spans="4:4">
       <c r="D867" s="17"/>
     </row>
-    <row r="868" spans="1:4">
-      <c r="A868" s="49"/>
+    <row r="868" spans="4:4">
       <c r="D868" s="17"/>
     </row>
-    <row r="869" spans="1:4">
-      <c r="A869" s="49"/>
+    <row r="869" spans="4:4">
       <c r="D869" s="17"/>
     </row>
-    <row r="870" spans="1:4">
-      <c r="A870" s="49"/>
+    <row r="870" spans="4:4">
       <c r="D870" s="17"/>
     </row>
-    <row r="871" spans="1:4">
-      <c r="A871" s="49"/>
+    <row r="871" spans="4:4">
       <c r="D871" s="17"/>
     </row>
-    <row r="872" spans="1:4">
-      <c r="A872" s="49"/>
+    <row r="872" spans="4:4">
       <c r="D872" s="17"/>
     </row>
-    <row r="873" spans="1:4">
-      <c r="A873" s="49"/>
+    <row r="873" spans="4:4">
       <c r="D873" s="17"/>
     </row>
-    <row r="874" spans="1:4">
-      <c r="A874" s="49"/>
+    <row r="874" spans="4:4">
       <c r="D874" s="17"/>
     </row>
-    <row r="875" spans="1:4">
-      <c r="A875" s="49"/>
+    <row r="875" spans="4:4">
       <c r="D875" s="17"/>
     </row>
-    <row r="876" spans="1:4">
-      <c r="A876" s="49"/>
+    <row r="876" spans="4:4">
       <c r="D876" s="17"/>
     </row>
-    <row r="877" spans="1:4">
-      <c r="A877" s="49"/>
+    <row r="877" spans="4:4">
       <c r="D877" s="17"/>
     </row>
-    <row r="878" spans="1:4">
-      <c r="A878" s="49"/>
+    <row r="878" spans="4:4">
       <c r="D878" s="17"/>
     </row>
-    <row r="879" spans="1:4">
-      <c r="A879" s="49"/>
+    <row r="879" spans="4:4">
       <c r="D879" s="17"/>
     </row>
-    <row r="880" spans="1:4">
-      <c r="A880" s="49"/>
+    <row r="880" spans="4:4">
       <c r="D880" s="17"/>
     </row>
-    <row r="881" spans="1:4">
-      <c r="A881" s="49"/>
+    <row r="881" spans="4:4">
       <c r="D881" s="17"/>
     </row>
-    <row r="882" spans="1:4">
-      <c r="A882" s="49"/>
+    <row r="882" spans="4:4">
       <c r="D882" s="17"/>
     </row>
-    <row r="883" spans="1:4">
-      <c r="A883" s="49"/>
+    <row r="883" spans="4:4">
       <c r="D883" s="17"/>
     </row>
-    <row r="884" spans="1:4">
-      <c r="A884" s="49"/>
+    <row r="884" spans="4:4">
       <c r="D884" s="17"/>
     </row>
-    <row r="885" spans="1:4">
-      <c r="A885" s="49"/>
+    <row r="885" spans="4:4">
       <c r="D885" s="17"/>
     </row>
-    <row r="886" spans="1:4">
-      <c r="A886" s="49"/>
+    <row r="886" spans="4:4">
       <c r="D886" s="17"/>
     </row>
-    <row r="887" spans="1:4">
-      <c r="A887" s="49"/>
+    <row r="887" spans="4:4">
       <c r="D887" s="17"/>
     </row>
-    <row r="888" spans="1:4">
-      <c r="A888" s="49"/>
+    <row r="888" spans="4:4">
       <c r="D888" s="17"/>
     </row>
-    <row r="889" spans="1:4">
-      <c r="A889" s="49"/>
+    <row r="889" spans="4:4">
       <c r="D889" s="17"/>
     </row>
-    <row r="890" spans="1:4">
-      <c r="A890" s="49"/>
+    <row r="890" spans="4:4">
       <c r="D890" s="17"/>
     </row>
-    <row r="891" spans="1:4">
-      <c r="A891" s="49"/>
+    <row r="891" spans="4:4">
       <c r="D891" s="17"/>
     </row>
-    <row r="892" spans="1:4">
-      <c r="A892" s="49"/>
+    <row r="892" spans="4:4">
       <c r="D892" s="17"/>
     </row>
-    <row r="893" spans="1:4">
-      <c r="A893" s="49"/>
+    <row r="893" spans="4:4">
       <c r="D893" s="17"/>
     </row>
-    <row r="894" spans="1:4">
-      <c r="A894" s="49"/>
+    <row r="894" spans="4:4">
       <c r="D894" s="17"/>
     </row>
-    <row r="895" spans="1:4">
-      <c r="A895" s="49"/>
+    <row r="895" spans="4:4">
       <c r="D895" s="17"/>
     </row>
-    <row r="896" spans="1:4">
-      <c r="A896" s="49"/>
+    <row r="896" spans="4:4">
       <c r="D896" s="17"/>
     </row>
-    <row r="897" spans="1:4">
-      <c r="A897" s="49"/>
+    <row r="897" spans="4:4">
       <c r="D897" s="17"/>
     </row>
-    <row r="898" spans="1:4">
-      <c r="A898" s="49"/>
+    <row r="898" spans="4:4">
       <c r="D898" s="17"/>
     </row>
-    <row r="899" spans="1:4">
-      <c r="A899" s="49"/>
+    <row r="899" spans="4:4">
       <c r="D899" s="17"/>
     </row>
-    <row r="900" spans="1:4">
-      <c r="A900" s="49"/>
+    <row r="900" spans="4:4">
       <c r="D900" s="17"/>
     </row>
-    <row r="901" spans="1:4">
-      <c r="A901" s="49"/>
+    <row r="901" spans="4:4">
       <c r="D901" s="17"/>
     </row>
-    <row r="902" spans="1:4">
-      <c r="A902" s="49"/>
+    <row r="902" spans="4:4">
       <c r="D902" s="17"/>
     </row>
-    <row r="903" spans="1:4">
-      <c r="A903" s="49"/>
+    <row r="903" spans="4:4">
       <c r="D903" s="17"/>
     </row>
-    <row r="904" spans="1:4">
-      <c r="A904" s="49"/>
+    <row r="904" spans="4:4">
       <c r="D904" s="17"/>
     </row>
-    <row r="905" spans="1:4">
-      <c r="A905" s="49"/>
+    <row r="905" spans="4:4">
       <c r="D905" s="17"/>
     </row>
-    <row r="906" spans="1:4">
-      <c r="A906" s="49"/>
+    <row r="906" spans="4:4">
       <c r="D906" s="17"/>
     </row>
-    <row r="907" spans="1:4">
-      <c r="A907" s="49"/>
+    <row r="907" spans="4:4">
       <c r="D907" s="17"/>
     </row>
-    <row r="908" spans="1:4">
-      <c r="A908" s="49"/>
+    <row r="908" spans="4:4">
       <c r="D908" s="17"/>
     </row>
-    <row r="909" spans="1:4">
-      <c r="A909" s="49"/>
+    <row r="909" spans="4:4">
       <c r="D909" s="17"/>
     </row>
-    <row r="910" spans="1:4">
-      <c r="A910" s="49"/>
+    <row r="910" spans="4:4">
       <c r="D910" s="17"/>
     </row>
-    <row r="911" spans="1:4">
-      <c r="A911" s="49"/>
+    <row r="911" spans="4:4">
       <c r="D911" s="17"/>
     </row>
-    <row r="912" spans="1:4">
-      <c r="A912" s="49"/>
+    <row r="912" spans="4:4">
       <c r="D912" s="17"/>
     </row>
-    <row r="913" spans="1:4">
-      <c r="A913" s="49"/>
+    <row r="913" spans="4:4">
       <c r="D913" s="17"/>
     </row>
-    <row r="914" spans="1:4">
-      <c r="A914" s="49"/>
+    <row r="914" spans="4:4">
       <c r="D914" s="17"/>
     </row>
-    <row r="915" spans="1:4">
-      <c r="A915" s="49"/>
+    <row r="915" spans="4:4">
       <c r="D915" s="17"/>
     </row>
-    <row r="916" spans="1:4">
-      <c r="A916" s="49"/>
+    <row r="916" spans="4:4">
       <c r="D916" s="17"/>
     </row>
-    <row r="917" spans="1:4">
-      <c r="A917" s="49"/>
+    <row r="917" spans="4:4">
       <c r="D917" s="17"/>
     </row>
-    <row r="918" spans="1:4">
-      <c r="A918" s="49"/>
+    <row r="918" spans="4:4">
       <c r="D918" s="17"/>
     </row>
-    <row r="919" spans="1:4">
-      <c r="A919" s="49"/>
+    <row r="919" spans="4:4">
       <c r="D919" s="17"/>
     </row>
-    <row r="920" spans="1:4">
-      <c r="A920" s="49"/>
+    <row r="920" spans="4:4">
       <c r="D920" s="17"/>
     </row>
-    <row r="921" spans="1:4">
-      <c r="A921" s="49"/>
+    <row r="921" spans="4:4">
       <c r="D921" s="17"/>
     </row>
-    <row r="922" spans="1:4">
-      <c r="A922" s="49"/>
+    <row r="922" spans="4:4">
       <c r="D922" s="17"/>
     </row>
-    <row r="923" spans="1:4">
-      <c r="A923" s="49"/>
+    <row r="923" spans="4:4">
       <c r="D923" s="17"/>
     </row>
-    <row r="924" spans="1:4">
-      <c r="A924" s="49"/>
+    <row r="924" spans="4:4">
       <c r="D924" s="17"/>
     </row>
-    <row r="925" spans="1:4">
-      <c r="A925" s="49"/>
+    <row r="925" spans="4:4">
       <c r="D925" s="17"/>
     </row>
-    <row r="926" spans="1:4">
-      <c r="A926" s="49"/>
+    <row r="926" spans="4:4">
       <c r="D926" s="17"/>
     </row>
-    <row r="927" spans="1:4">
-      <c r="A927" s="49"/>
+    <row r="927" spans="4:4">
       <c r="D927" s="17"/>
     </row>
-    <row r="928" spans="1:4">
-      <c r="A928" s="49"/>
+    <row r="928" spans="4:4">
       <c r="D928" s="17"/>
     </row>
-    <row r="929" spans="1:4">
-      <c r="A929" s="49"/>
+    <row r="929" spans="4:4">
       <c r="D929" s="17"/>
     </row>
-    <row r="930" spans="1:4">
-      <c r="A930" s="49"/>
+    <row r="930" spans="4:4">
       <c r="D930" s="17"/>
     </row>
-    <row r="931" spans="1:4">
-      <c r="A931" s="49"/>
+    <row r="931" spans="4:4">
       <c r="D931" s="17"/>
     </row>
-    <row r="932" spans="1:4">
-      <c r="A932" s="49"/>
+    <row r="932" spans="4:4">
       <c r="D932" s="17"/>
     </row>
-    <row r="933" spans="1:4">
-      <c r="A933" s="49"/>
+    <row r="933" spans="4:4">
       <c r="D933" s="17"/>
     </row>
-    <row r="934" spans="1:4">
-      <c r="A934" s="49"/>
+    <row r="934" spans="4:4">
       <c r="D934" s="17"/>
     </row>
-    <row r="935" spans="1:4">
-      <c r="A935" s="49"/>
+    <row r="935" spans="4:4">
       <c r="D935" s="17"/>
     </row>
-    <row r="936" spans="1:4">
-      <c r="A936" s="49"/>
+    <row r="936" spans="4:4">
       <c r="D936" s="17"/>
     </row>
-    <row r="937" spans="1:4">
-      <c r="A937" s="49"/>
+    <row r="937" spans="4:4">
       <c r="D937" s="17"/>
     </row>
-    <row r="938" spans="1:4">
-      <c r="A938" s="49"/>
+    <row r="938" spans="4:4">
       <c r="D938" s="17"/>
     </row>
-    <row r="939" spans="1:4">
-      <c r="A939" s="49"/>
+    <row r="939" spans="4:4">
       <c r="D939" s="17"/>
     </row>
-    <row r="940" spans="1:4">
-      <c r="A940" s="49"/>
+    <row r="940" spans="4:4">
       <c r="D940" s="17"/>
     </row>
-    <row r="941" spans="1:4">
-      <c r="A941" s="49"/>
+    <row r="941" spans="4:4">
       <c r="D941" s="17"/>
     </row>
-    <row r="942" spans="1:4">
-      <c r="A942" s="49"/>
+    <row r="942" spans="4:4">
       <c r="D942" s="17"/>
     </row>
-    <row r="943" spans="1:4">
-      <c r="A943" s="49"/>
+    <row r="943" spans="4:4">
       <c r="D943" s="17"/>
     </row>
-    <row r="944" spans="1:4">
-      <c r="A944" s="49"/>
+    <row r="944" spans="4:4">
       <c r="D944" s="17"/>
     </row>
-    <row r="945" spans="1:4">
-      <c r="A945" s="49"/>
+    <row r="945" spans="4:4">
       <c r="D945" s="17"/>
     </row>
-    <row r="946" spans="1:4">
-      <c r="A946" s="49"/>
+    <row r="946" spans="4:4">
       <c r="D946" s="17"/>
     </row>
-    <row r="947" spans="1:4">
-      <c r="A947" s="49"/>
+    <row r="947" spans="4:4">
       <c r="D947" s="17"/>
     </row>
-    <row r="948" spans="1:4">
-      <c r="A948" s="49"/>
+    <row r="948" spans="4:4">
       <c r="D948" s="17"/>
     </row>
-    <row r="949" spans="1:4">
-      <c r="A949" s="49"/>
+    <row r="949" spans="4:4">
       <c r="D949" s="17"/>
     </row>
-    <row r="950" spans="1:4">
-      <c r="A950" s="49"/>
+    <row r="950" spans="4:4">
       <c r="D950" s="17"/>
     </row>
-    <row r="951" spans="1:4">
-      <c r="A951" s="49"/>
+    <row r="951" spans="4:4">
       <c r="D951" s="17"/>
     </row>
-    <row r="952" spans="1:4">
-      <c r="A952" s="49"/>
+    <row r="952" spans="4:4">
       <c r="D952" s="17"/>
     </row>
-    <row r="953" spans="1:4">
-      <c r="A953" s="49"/>
+    <row r="953" spans="4:4">
       <c r="D953" s="17"/>
     </row>
-    <row r="954" spans="1:4">
-      <c r="A954" s="49"/>
+    <row r="954" spans="4:4">
       <c r="D954" s="17"/>
     </row>
-    <row r="955" spans="1:4">
-      <c r="A955" s="49"/>
+    <row r="955" spans="4:4">
       <c r="D955" s="17"/>
     </row>
-    <row r="956" spans="1:4">
-      <c r="A956" s="49"/>
+    <row r="956" spans="4:4">
       <c r="D956" s="17"/>
     </row>
-    <row r="957" spans="1:4">
-      <c r="A957" s="49"/>
+    <row r="957" spans="4:4">
       <c r="D957" s="17"/>
     </row>
-    <row r="958" spans="1:4">
-      <c r="A958" s="49"/>
+    <row r="958" spans="4:4">
       <c r="D958" s="17"/>
     </row>
-    <row r="959" spans="1:4">
-      <c r="A959" s="49"/>
+    <row r="959" spans="4:4">
       <c r="D959" s="17"/>
     </row>
-    <row r="960" spans="1:4">
-      <c r="A960" s="49"/>
+    <row r="960" spans="4:4">
       <c r="D960" s="17"/>
     </row>
-    <row r="961" spans="1:4">
-      <c r="A961" s="49"/>
+    <row r="961" spans="4:4">
       <c r="D961" s="17"/>
     </row>
-    <row r="962" spans="1:4">
-      <c r="A962" s="49"/>
+    <row r="962" spans="4:4">
       <c r="D962" s="17"/>
     </row>
-    <row r="963" spans="1:4">
-      <c r="A963" s="49"/>
+    <row r="963" spans="4:4">
       <c r="D963" s="17"/>
     </row>
-    <row r="964" spans="1:4">
-      <c r="A964" s="49"/>
+    <row r="964" spans="4:4">
       <c r="D964" s="17"/>
     </row>
-    <row r="965" spans="1:4">
-      <c r="A965" s="49"/>
+    <row r="965" spans="4:4">
       <c r="D965" s="17"/>
     </row>
-    <row r="966" spans="1:4">
-      <c r="A966" s="49"/>
+    <row r="966" spans="4:4">
       <c r="D966" s="17"/>
     </row>
-    <row r="967" spans="1:4">
-      <c r="A967" s="49"/>
+    <row r="967" spans="4:4">
       <c r="D967" s="17"/>
     </row>
-    <row r="968" spans="1:4">
-      <c r="A968" s="49"/>
+    <row r="968" spans="4:4">
       <c r="D968" s="17"/>
     </row>
-    <row r="969" spans="1:4">
-      <c r="A969" s="49"/>
+    <row r="969" spans="4:4">
       <c r="D969" s="17"/>
     </row>
-    <row r="970" spans="1:4">
-      <c r="A970" s="49"/>
+    <row r="970" spans="4:4">
       <c r="D970" s="17"/>
     </row>
-    <row r="971" spans="1:4">
-      <c r="A971" s="49"/>
+    <row r="971" spans="4:4">
       <c r="D971" s="17"/>
     </row>
-    <row r="972" spans="1:4">
-      <c r="A972" s="49"/>
+    <row r="972" spans="4:4">
       <c r="D972" s="17"/>
     </row>
-    <row r="973" spans="1:4">
-      <c r="A973" s="49"/>
+    <row r="973" spans="4:4">
       <c r="D973" s="17"/>
     </row>
-    <row r="974" spans="1:4">
-      <c r="A974" s="49"/>
+    <row r="974" spans="4:4">
       <c r="D974" s="17"/>
     </row>
-    <row r="975" spans="1:4">
-      <c r="A975" s="49"/>
+    <row r="975" spans="4:4">
       <c r="D975" s="17"/>
     </row>
-    <row r="976" spans="1:4">
-      <c r="A976" s="49"/>
+    <row r="976" spans="4:4">
       <c r="D976" s="17"/>
     </row>
-    <row r="977" spans="1:4">
-      <c r="A977" s="49"/>
+    <row r="977" spans="4:4">
       <c r="D977" s="17"/>
     </row>
-    <row r="978" spans="1:4">
-      <c r="A978" s="49"/>
+    <row r="978" spans="4:4">
       <c r="D978" s="17"/>
     </row>
-    <row r="979" spans="1:4">
-      <c r="A979" s="49"/>
+    <row r="979" spans="4:4">
       <c r="D979" s="17"/>
     </row>
-    <row r="980" spans="1:4">
-      <c r="A980" s="49"/>
+    <row r="980" spans="4:4">
       <c r="D980" s="17"/>
     </row>
-    <row r="981" spans="1:4">
-      <c r="A981" s="49"/>
+    <row r="981" spans="4:4">
       <c r="D981" s="17"/>
     </row>
-    <row r="982" spans="1:4">
-      <c r="A982" s="49"/>
+    <row r="982" spans="4:4">
       <c r="D982" s="17"/>
     </row>
-    <row r="983" spans="1:4">
-      <c r="A983" s="49"/>
+    <row r="983" spans="4:4">
       <c r="D983" s="17"/>
     </row>
-    <row r="984" spans="1:4">
-      <c r="A984" s="49"/>
+    <row r="984" spans="4:4">
       <c r="D984" s="17"/>
     </row>
-    <row r="985" spans="1:4">
-      <c r="A985" s="49"/>
+    <row r="985" spans="4:4">
       <c r="D985" s="17"/>
     </row>
-    <row r="986" spans="1:4">
-      <c r="A986" s="49"/>
+    <row r="986" spans="4:4">
       <c r="D986" s="17"/>
     </row>
-    <row r="987" spans="1:4">
-      <c r="A987" s="49"/>
+    <row r="987" spans="4:4">
       <c r="D987" s="17"/>
     </row>
-    <row r="988" spans="1:4">
-      <c r="A988" s="49"/>
+    <row r="988" spans="4:4">
       <c r="D988" s="17"/>
     </row>
-    <row r="989" spans="1:4">
-      <c r="A989" s="49"/>
+    <row r="989" spans="4:4">
       <c r="D989" s="17"/>
     </row>
-    <row r="990" spans="1:4">
-      <c r="A990" s="49"/>
+    <row r="990" spans="4:4">
       <c r="D990" s="17"/>
     </row>
-    <row r="991" spans="1:4">
-      <c r="A991" s="49"/>
+    <row r="991" spans="4:4">
       <c r="D991" s="17"/>
     </row>
-    <row r="992" spans="1:4">
-      <c r="A992" s="49"/>
+    <row r="992" spans="4:4">
       <c r="D992" s="17"/>
     </row>
-    <row r="993" spans="1:4">
-      <c r="A993" s="49"/>
+    <row r="993" spans="4:4">
       <c r="D993" s="17"/>
     </row>
-    <row r="994" spans="1:4">
-      <c r="A994" s="49"/>
+    <row r="994" spans="4:4">
       <c r="D994" s="17"/>
     </row>
-    <row r="995" spans="1:4">
-      <c r="A995" s="49"/>
+    <row r="995" spans="4:4">
       <c r="D995" s="17"/>
     </row>
-    <row r="996" spans="1:4">
-      <c r="A996" s="49"/>
+    <row r="996" spans="4:4">
       <c r="D996" s="17"/>
     </row>
-    <row r="997" spans="1:4">
-      <c r="A997" s="49"/>
+    <row r="997" spans="4:4">
       <c r="D997" s="17"/>
     </row>
-    <row r="998" spans="1:4">
-      <c r="A998" s="49"/>
+    <row r="998" spans="4:4">
       <c r="D998" s="17"/>
     </row>
-    <row r="999" spans="1:4">
-      <c r="A999" s="49"/>
+    <row r="999" spans="4:4">
       <c r="D999" s="17"/>
     </row>
-    <row r="1000" spans="1:4">
-      <c r="A1000" s="49"/>
+    <row r="1000" spans="4:4">
       <c r="D1000" s="17"/>
     </row>
-    <row r="1001" spans="1:4">
-      <c r="A1001" s="49"/>
+    <row r="1001" spans="4:4">
       <c r="D1001" s="17"/>
     </row>
-    <row r="1002" spans="1:4">
-      <c r="A1002" s="49"/>
+    <row r="1002" spans="4:4">
       <c r="D1002" s="17"/>
     </row>
-    <row r="1003" spans="1:4">
-      <c r="A1003" s="49"/>
+    <row r="1003" spans="4:4">
       <c r="D1003" s="17"/>
     </row>
-    <row r="1004" spans="1:4">
-      <c r="A1004" s="49"/>
+    <row r="1004" spans="4:4">
       <c r="D1004" s="17"/>
     </row>
-    <row r="1005" spans="1:4">
-      <c r="A1005" s="49"/>
+    <row r="1005" spans="4:4">
       <c r="D1005" s="17"/>
     </row>
-    <row r="1006" spans="1:4">
-      <c r="A1006" s="49"/>
+    <row r="1006" spans="4:4">
       <c r="D1006" s="17"/>
     </row>
-    <row r="1007" spans="1:4">
-      <c r="A1007" s="49"/>
+    <row r="1007" spans="4:4">
       <c r="D1007" s="17"/>
     </row>
-    <row r="1008" spans="1:4">
-      <c r="A1008" s="49"/>
+    <row r="1008" spans="4:4">
       <c r="D1008" s="17"/>
     </row>
-    <row r="1009" spans="1:4">
-      <c r="A1009" s="49"/>
+    <row r="1009" spans="4:4">
       <c r="D1009" s="17"/>
     </row>
-    <row r="1010" spans="1:4">
-      <c r="A1010" s="49"/>
+    <row r="1010" spans="4:4">
       <c r="D1010" s="17"/>
     </row>
-    <row r="1011" spans="1:4">
-      <c r="A1011" s="49"/>
+    <row r="1011" spans="4:4">
       <c r="D1011" s="17"/>
     </row>
-    <row r="1012" spans="1:4">
-      <c r="A1012" s="49"/>
+    <row r="1012" spans="4:4">
       <c r="D1012" s="17"/>
     </row>
-    <row r="1013" spans="1:4">
-      <c r="A1013" s="49"/>
+    <row r="1013" spans="4:4">
       <c r="D1013" s="17"/>
     </row>
-    <row r="1014" spans="1:4">
-      <c r="A1014" s="49"/>
+    <row r="1014" spans="4:4">
       <c r="D1014" s="17"/>
     </row>
-    <row r="1015" spans="1:4">
-      <c r="A1015" s="49"/>
+    <row r="1015" spans="4:4">
       <c r="D1015" s="17"/>
     </row>
-    <row r="1016" spans="1:4">
-      <c r="A1016" s="49"/>
+    <row r="1016" spans="4:4">
       <c r="D1016" s="17"/>
     </row>
-    <row r="1017" spans="1:4">
-      <c r="A1017" s="49"/>
+    <row r="1017" spans="4:4">
       <c r="D1017" s="17"/>
     </row>
-    <row r="1018" spans="1:4">
-      <c r="A1018" s="49"/>
+    <row r="1018" spans="4:4">
       <c r="D1018" s="17"/>
     </row>
-    <row r="1019" spans="1:4">
-      <c r="A1019" s="49"/>
+    <row r="1019" spans="4:4">
       <c r="D1019" s="17"/>
     </row>
-    <row r="1020" spans="1:4">
-      <c r="A1020" s="49"/>
+    <row r="1020" spans="4:4">
       <c r="D1020" s="17"/>
     </row>
-    <row r="1021" spans="1:4">
-      <c r="A1021" s="49"/>
+    <row r="1021" spans="4:4">
       <c r="D1021" s="17"/>
     </row>
-    <row r="1022" spans="1:4">
-      <c r="A1022" s="49"/>
+    <row r="1022" spans="4:4">
       <c r="D1022" s="17"/>
     </row>
-    <row r="1023" spans="1:4">
-      <c r="A1023" s="49"/>
+    <row r="1023" spans="4:4">
       <c r="D1023" s="17"/>
     </row>
-    <row r="1024" spans="1:4">
-      <c r="A1024" s="49"/>
+    <row r="1024" spans="4:4">
       <c r="D1024" s="17"/>
     </row>
-    <row r="1025" spans="1:4">
-      <c r="A1025" s="49"/>
+    <row r="1025" spans="4:4">
       <c r="D1025" s="17"/>
     </row>
-    <row r="1026" spans="1:4">
-      <c r="A1026" s="49"/>
+    <row r="1026" spans="4:4">
       <c r="D1026" s="17"/>
     </row>
-    <row r="1027" spans="1:4">
-      <c r="A1027" s="49"/>
+    <row r="1027" spans="4:4">
       <c r="D1027" s="17"/>
     </row>
-    <row r="1028" spans="1:4">
-      <c r="A1028" s="49"/>
+    <row r="1028" spans="4:4">
       <c r="D1028" s="17"/>
     </row>
-    <row r="1029" spans="1:4">
-      <c r="A1029" s="49"/>
+    <row r="1029" spans="4:4">
       <c r="D1029" s="17"/>
     </row>
-    <row r="1030" spans="1:4">
-      <c r="A1030" s="49"/>
+    <row r="1030" spans="4:4">
       <c r="D1030" s="17"/>
     </row>
-    <row r="1031" spans="1:4">
-      <c r="A1031" s="49"/>
+    <row r="1031" spans="4:4">
       <c r="D1031" s="17"/>
     </row>
-    <row r="1032" spans="1:4">
-      <c r="A1032" s="49"/>
+    <row r="1032" spans="4:4">
       <c r="D1032" s="17"/>
     </row>
-    <row r="1033" spans="1:4">
-      <c r="A1033" s="49"/>
+    <row r="1033" spans="4:4">
       <c r="D1033" s="17"/>
     </row>
-    <row r="1034" spans="1:4">
-      <c r="A1034" s="49"/>
+    <row r="1034" spans="4:4">
       <c r="D1034" s="17"/>
     </row>
-    <row r="1035" spans="1:4">
-      <c r="A1035" s="49"/>
+    <row r="1035" spans="4:4">
       <c r="D1035" s="17"/>
     </row>
-    <row r="1036" spans="1:4">
-      <c r="A1036" s="49"/>
+    <row r="1036" spans="4:4">
       <c r="D1036" s="17"/>
     </row>
-    <row r="1037" spans="1:4">
-      <c r="A1037" s="49"/>
+    <row r="1037" spans="4:4">
       <c r="D1037" s="17"/>
     </row>
-    <row r="1038" spans="1:4">
-      <c r="A1038" s="49"/>
+    <row r="1038" spans="4:4">
       <c r="D1038" s="17"/>
     </row>
-    <row r="1039" spans="1:4">
-      <c r="A1039" s="49"/>
+    <row r="1039" spans="4:4">
       <c r="D1039" s="17"/>
     </row>
-    <row r="1040" spans="1:4">
-      <c r="A1040" s="49"/>
+    <row r="1040" spans="4:4">
       <c r="D1040" s="17"/>
     </row>
-    <row r="1041" spans="1:4">
-      <c r="A1041" s="49"/>
+    <row r="1041" spans="4:4">
       <c r="D1041" s="17"/>
     </row>
-    <row r="1042" spans="1:4">
-      <c r="A1042" s="49"/>
+    <row r="1042" spans="4:4">
       <c r="D1042" s="17"/>
     </row>
-    <row r="1043" spans="1:4">
-      <c r="A1043" s="49"/>
+    <row r="1043" spans="4:4">
       <c r="D1043" s="17"/>
     </row>
-    <row r="1044" spans="1:4">
-      <c r="A1044" s="49"/>
+    <row r="1044" spans="4:4">
       <c r="D1044" s="17"/>
     </row>
-    <row r="1045" spans="1:4">
-      <c r="A1045" s="49"/>
+    <row r="1045" spans="4:4">
       <c r="D1045" s="17"/>
     </row>
-    <row r="1046" spans="1:4">
-      <c r="A1046" s="49"/>
+    <row r="1046" spans="4:4">
       <c r="D1046" s="17"/>
     </row>
-    <row r="1047" spans="1:4">
-      <c r="A1047" s="49"/>
+    <row r="1047" spans="4:4">
       <c r="D1047" s="17"/>
     </row>
-    <row r="1048" spans="1:4">
-      <c r="A1048" s="49"/>
+    <row r="1048" spans="4:4">
       <c r="D1048" s="17"/>
     </row>
-    <row r="1049" spans="1:4">
-      <c r="A1049" s="49"/>
+    <row r="1049" spans="4:4">
       <c r="D1049" s="17"/>
     </row>
-    <row r="1050" spans="1:4">
-      <c r="A1050" s="49"/>
+    <row r="1050" spans="4:4">
       <c r="D1050" s="17"/>
     </row>
-    <row r="1051" spans="1:4">
-      <c r="A1051" s="49"/>
+    <row r="1051" spans="4:4">
       <c r="D1051" s="17"/>
     </row>
-    <row r="1052" spans="1:4">
-      <c r="A1052" s="49"/>
+    <row r="1052" spans="4:4">
       <c r="D1052" s="17"/>
     </row>
-    <row r="1053" spans="1:4">
-      <c r="A1053" s="49"/>
+    <row r="1053" spans="4:4">
       <c r="D1053" s="17"/>
     </row>
-    <row r="1054" spans="1:4">
-      <c r="A1054" s="49"/>
+    <row r="1054" spans="4:4">
       <c r="D1054" s="17"/>
     </row>
-    <row r="1055" spans="1:4">
-      <c r="A1055" s="49"/>
+    <row r="1055" spans="4:4">
       <c r="D1055" s="17"/>
     </row>
-    <row r="1056" spans="1:4">
-      <c r="A1056" s="49"/>
+    <row r="1056" spans="4:4">
       <c r="D1056" s="17"/>
     </row>
-    <row r="1057" spans="1:4">
-      <c r="A1057" s="49"/>
+    <row r="1057" spans="4:4">
       <c r="D1057" s="17"/>
     </row>
-    <row r="1058" spans="1:4">
-      <c r="A1058" s="49"/>
+    <row r="1058" spans="4:4">
       <c r="D1058" s="17"/>
     </row>
-    <row r="1059" spans="1:4">
-      <c r="A1059" s="49"/>
+    <row r="1059" spans="4:4">
       <c r="D1059" s="17"/>
     </row>
-    <row r="1060" spans="1:4">
-      <c r="A1060" s="49"/>
+    <row r="1060" spans="4:4">
       <c r="D1060" s="17"/>
     </row>
-    <row r="1061" spans="1:4">
-      <c r="A1061" s="49"/>
+    <row r="1061" spans="4:4">
       <c r="D1061" s="17"/>
     </row>
-    <row r="1062" spans="1:4">
-      <c r="A1062" s="49"/>
+    <row r="1062" spans="4:4">
       <c r="D1062" s="17"/>
     </row>
-    <row r="1063" spans="1:4">
-      <c r="A1063" s="49"/>
+    <row r="1063" spans="4:4">
       <c r="D1063" s="17"/>
     </row>
-    <row r="1064" spans="1:4">
-      <c r="A1064" s="49"/>
+    <row r="1064" spans="4:4">
       <c r="D1064" s="17"/>
     </row>
-    <row r="1065" spans="1:4">
-      <c r="A1065" s="49"/>
+    <row r="1065" spans="4:4">
       <c r="D1065" s="17"/>
     </row>
-    <row r="1066" spans="1:4">
-      <c r="A1066" s="49"/>
+    <row r="1066" spans="4:4">
       <c r="D1066" s="17"/>
     </row>
-    <row r="1067" spans="1:4">
-      <c r="A1067" s="49"/>
+    <row r="1067" spans="4:4">
       <c r="D1067" s="17"/>
     </row>
-    <row r="1068" spans="1:4">
-      <c r="A1068" s="49"/>
+    <row r="1068" spans="4:4">
       <c r="D1068" s="17"/>
     </row>
-    <row r="1069" spans="1:4">
-      <c r="A1069" s="49"/>
+    <row r="1069" spans="4:4">
       <c r="D1069" s="17"/>
     </row>
-    <row r="1070" spans="1:4">
-      <c r="A1070" s="49"/>
+    <row r="1070" spans="4:4">
       <c r="D1070" s="17"/>
     </row>
-    <row r="1071" spans="1:4">
-      <c r="A1071" s="49"/>
+    <row r="1071" spans="4:4">
       <c r="D1071" s="17"/>
     </row>
-    <row r="1072" spans="1:4">
-      <c r="A1072" s="49"/>
+    <row r="1072" spans="4:4">
       <c r="D1072" s="17"/>
     </row>
-    <row r="1073" spans="1:4">
-      <c r="A1073" s="49"/>
+    <row r="1073" spans="4:4">
       <c r="D1073" s="17"/>
     </row>
-    <row r="1074" spans="1:4">
-      <c r="A1074" s="49"/>
+    <row r="1074" spans="4:4">
       <c r="D1074" s="17"/>
     </row>
-    <row r="1075" spans="1:4">
-      <c r="A1075" s="49"/>
+    <row r="1075" spans="4:4">
       <c r="D1075" s="17"/>
     </row>
-    <row r="1076" spans="1:4">
-      <c r="A1076" s="49"/>
+    <row r="1076" spans="4:4">
       <c r="D1076" s="17"/>
     </row>
-    <row r="1077" spans="1:4">
-      <c r="A1077" s="49"/>
+    <row r="1077" spans="4:4">
       <c r="D1077" s="17"/>
     </row>
-    <row r="1078" spans="1:4">
-      <c r="A1078" s="49"/>
+    <row r="1078" spans="4:4">
       <c r="D1078" s="17"/>
     </row>
-    <row r="1079" spans="1:4">
-      <c r="A1079" s="49"/>
+    <row r="1079" spans="4:4">
       <c r="D1079" s="17"/>
     </row>
-    <row r="1080" spans="1:4">
-      <c r="A1080" s="49"/>
+    <row r="1080" spans="4:4">
       <c r="D1080" s="17"/>
     </row>
-    <row r="1081" spans="1:4">
-      <c r="A1081" s="49"/>
+    <row r="1081" spans="4:4">
       <c r="D1081" s="17"/>
     </row>
-    <row r="1082" spans="1:4">
-      <c r="A1082" s="49"/>
+    <row r="1082" spans="4:4">
       <c r="D1082" s="17"/>
     </row>
-    <row r="1083" spans="1:4">
-      <c r="A1083" s="49"/>
+    <row r="1083" spans="4:4">
       <c r="D1083" s="17"/>
     </row>
-    <row r="1084" spans="1:4">
-      <c r="A1084" s="49"/>
+    <row r="1084" spans="4:4">
       <c r="D1084" s="17"/>
     </row>
-    <row r="1085" spans="1:4">
-      <c r="A1085" s="49"/>
+    <row r="1085" spans="4:4">
       <c r="D1085" s="17"/>
     </row>
-    <row r="1086" spans="1:4">
-      <c r="A1086" s="49"/>
+    <row r="1086" spans="4:4">
       <c r="D1086" s="17"/>
     </row>
-    <row r="1087" spans="1:4">
-      <c r="A1087" s="49"/>
+    <row r="1087" spans="4:4">
       <c r="D1087" s="17"/>
     </row>
-    <row r="1088" spans="1:4">
-      <c r="A1088" s="49"/>
+    <row r="1088" spans="4:4">
       <c r="D1088" s="17"/>
     </row>
-    <row r="1089" spans="1:4">
-      <c r="A1089" s="49"/>
+    <row r="1089" spans="4:4">
       <c r="D1089" s="17"/>
     </row>
-    <row r="1090" spans="1:4">
-      <c r="A1090" s="49"/>
+    <row r="1090" spans="4:4">
       <c r="D1090" s="17"/>
     </row>
-    <row r="1091" spans="1:4">
-      <c r="A1091" s="49"/>
+    <row r="1091" spans="4:4">
       <c r="D1091" s="17"/>
     </row>
-    <row r="1092" spans="1:4">
-      <c r="A1092" s="49"/>
+    <row r="1092" spans="4:4">
       <c r="D1092" s="17"/>
     </row>
-    <row r="1093" spans="1:4">
-      <c r="A1093" s="49"/>
+    <row r="1093" spans="4:4">
       <c r="D1093" s="17"/>
     </row>
-    <row r="1094" spans="1:4">
-      <c r="A1094" s="49"/>
+    <row r="1094" spans="4:4">
       <c r="D1094" s="17"/>
     </row>
-    <row r="1095" spans="1:4">
-      <c r="A1095" s="49"/>
+    <row r="1095" spans="4:4">
       <c r="D1095" s="17"/>
     </row>
-    <row r="1096" spans="1:4">
-      <c r="A1096" s="49"/>
+    <row r="1096" spans="4:4">
       <c r="D1096" s="17"/>
     </row>
-    <row r="1097" spans="1:4">
-      <c r="A1097" s="49"/>
+    <row r="1097" spans="4:4">
       <c r="D1097" s="17"/>
     </row>
-    <row r="1098" spans="1:4">
-      <c r="A1098" s="49"/>
+    <row r="1098" spans="4:4">
       <c r="D1098" s="17"/>
     </row>
-    <row r="1099" spans="1:4">
-      <c r="A1099" s="49"/>
+    <row r="1099" spans="4:4">
       <c r="D1099" s="17"/>
     </row>
-    <row r="1100" spans="1:4">
-      <c r="A1100" s="49"/>
+    <row r="1100" spans="4:4">
       <c r="D1100" s="17"/>
     </row>
-    <row r="1101" spans="1:4">
-      <c r="A1101" s="49"/>
+    <row r="1101" spans="4:4">
       <c r="D1101" s="17"/>
     </row>
-    <row r="1102" spans="1:4">
-      <c r="A1102" s="49"/>
+    <row r="1102" spans="4:4">
       <c r="D1102" s="17"/>
     </row>
-    <row r="1103" spans="1:4">
-      <c r="A1103" s="49"/>
+    <row r="1103" spans="4:4">
       <c r="D1103" s="17"/>
     </row>
-    <row r="1104" spans="1:4">
-      <c r="A1104" s="49"/>
+    <row r="1104" spans="4:4">
       <c r="D1104" s="17"/>
     </row>
-    <row r="1105" spans="1:4">
-      <c r="A1105" s="49"/>
+    <row r="1105" spans="4:4">
       <c r="D1105" s="17"/>
     </row>
-    <row r="1106" spans="1:4">
-      <c r="A1106" s="49"/>
+    <row r="1106" spans="4:4">
       <c r="D1106" s="17"/>
     </row>
-    <row r="1107" spans="1:4">
-      <c r="A1107" s="49"/>
+    <row r="1107" spans="4:4">
       <c r="D1107" s="17"/>
     </row>
-    <row r="1108" spans="1:4">
-      <c r="A1108" s="49"/>
+    <row r="1108" spans="4:4">
       <c r="D1108" s="17"/>
     </row>
-    <row r="1109" spans="1:4">
-      <c r="A1109" s="49"/>
+    <row r="1109" spans="4:4">
       <c r="D1109" s="17"/>
     </row>
-    <row r="1110" spans="1:4">
-      <c r="A1110" s="49"/>
+    <row r="1110" spans="4:4">
       <c r="D1110" s="17"/>
     </row>
-    <row r="1111" spans="1:4">
-      <c r="A1111" s="49"/>
+    <row r="1111" spans="4:4">
       <c r="D1111" s="17"/>
     </row>
-    <row r="1112" spans="1:4">
-      <c r="A1112" s="49"/>
+    <row r="1112" spans="4:4">
       <c r="D1112" s="17"/>
     </row>
-    <row r="1113" spans="1:4">
-      <c r="A1113" s="49"/>
+    <row r="1113" spans="4:4">
       <c r="D1113" s="17"/>
     </row>
-    <row r="1114" spans="1:4">
-      <c r="A1114" s="49"/>
+    <row r="1114" spans="4:4">
       <c r="D1114" s="17"/>
     </row>
-    <row r="1115" spans="1:4">
-      <c r="A1115" s="49"/>
+    <row r="1115" spans="4:4">
       <c r="D1115" s="17"/>
     </row>
-    <row r="1116" spans="1:4">
-      <c r="A1116" s="49"/>
+    <row r="1116" spans="4:4">
       <c r="D1116" s="17"/>
     </row>
-    <row r="1117" spans="1:4">
-      <c r="A1117" s="49"/>
+    <row r="1117" spans="4:4">
       <c r="D1117" s="17"/>
     </row>
-    <row r="1118" spans="1:4">
-      <c r="A1118" s="49"/>
+    <row r="1118" spans="4:4">
       <c r="D1118" s="17"/>
     </row>
-    <row r="1119" spans="1:4">
-      <c r="A1119" s="49"/>
+    <row r="1119" spans="4:4">
       <c r="D1119" s="17"/>
     </row>
-    <row r="1120" spans="1:4">
-      <c r="A1120" s="49"/>
+    <row r="1120" spans="4:4">
       <c r="D1120" s="17"/>
     </row>
-    <row r="1121" spans="1:4">
-      <c r="A1121" s="49"/>
+    <row r="1121" spans="4:4">
       <c r="D1121" s="17"/>
     </row>
-    <row r="1122" spans="1:4">
-      <c r="A1122" s="49"/>
+    <row r="1122" spans="4:4">
       <c r="D1122" s="17"/>
     </row>
-    <row r="1123" spans="1:4">
-      <c r="A1123" s="49"/>
+    <row r="1123" spans="4:4">
       <c r="D1123" s="17"/>
     </row>
-    <row r="1124" spans="1:4">
-      <c r="A1124" s="49"/>
+    <row r="1124" spans="4:4">
       <c r="D1124" s="17"/>
     </row>
-    <row r="1125" spans="1:4">
-      <c r="A1125" s="49"/>
+    <row r="1125" spans="4:4">
       <c r="D1125" s="17"/>
     </row>
-    <row r="1126" spans="1:4">
-      <c r="A1126" s="49"/>
+    <row r="1126" spans="4:4">
       <c r="D1126" s="17"/>
     </row>
-    <row r="1127" spans="1:4">
-      <c r="A1127" s="49"/>
+    <row r="1127" spans="4:4">
       <c r="D1127" s="17"/>
     </row>
-    <row r="1128" spans="1:4">
-      <c r="A1128" s="49"/>
+    <row r="1128" spans="4:4">
       <c r="D1128" s="17"/>
     </row>
-    <row r="1129" spans="1:4">
-      <c r="A1129" s="49"/>
+    <row r="1129" spans="4:4">
       <c r="D1129" s="17"/>
     </row>
-    <row r="1130" spans="1:4">
-      <c r="A1130" s="49"/>
+    <row r="1130" spans="4:4">
       <c r="D1130" s="17"/>
     </row>
-    <row r="1131" spans="1:4">
-      <c r="A1131" s="49"/>
+    <row r="1131" spans="4:4">
       <c r="D1131" s="17"/>
     </row>
-    <row r="1132" spans="1:4">
-      <c r="A1132" s="49"/>
+    <row r="1132" spans="4:4">
       <c r="D1132" s="17"/>
     </row>
-    <row r="1133" spans="1:4">
-      <c r="A1133" s="49"/>
+    <row r="1133" spans="4:4">
       <c r="D1133" s="17"/>
     </row>
-    <row r="1134" spans="1:4">
-      <c r="A1134" s="49"/>
+    <row r="1134" spans="4:4">
       <c r="D1134" s="17"/>
     </row>
-    <row r="1135" spans="1:4">
-      <c r="A1135" s="49"/>
+    <row r="1135" spans="4:4">
       <c r="D1135" s="17"/>
     </row>
-    <row r="1136" spans="1:4">
-      <c r="A1136" s="49"/>
+    <row r="1136" spans="4:4">
       <c r="D1136" s="17"/>
     </row>
-    <row r="1137" spans="1:4">
-      <c r="A1137" s="49"/>
+    <row r="1137" spans="4:4">
       <c r="D1137" s="17"/>
     </row>
-    <row r="1138" spans="1:4">
-      <c r="A1138" s="49"/>
+    <row r="1138" spans="4:4">
       <c r="D1138" s="17"/>
     </row>
-    <row r="1139" spans="1:4">
-      <c r="A1139" s="49"/>
+    <row r="1139" spans="4:4">
       <c r="D1139" s="17"/>
     </row>
-    <row r="1140" spans="1:4">
-      <c r="A1140" s="49"/>
+    <row r="1140" spans="4:4">
       <c r="D1140" s="17"/>
     </row>
-    <row r="1141" spans="1:4">
-      <c r="A1141" s="49"/>
+    <row r="1141" spans="4:4">
       <c r="D1141" s="17"/>
     </row>
-    <row r="1142" spans="1:4">
-      <c r="A1142" s="49"/>
+    <row r="1142" spans="4:4">
       <c r="D1142" s="17"/>
     </row>
-    <row r="1143" spans="1:4">
-      <c r="A1143" s="49"/>
+    <row r="1143" spans="4:4">
       <c r="D1143" s="17"/>
     </row>
-    <row r="1144" spans="1:4">
-      <c r="A1144" s="49"/>
+    <row r="1144" spans="4:4">
       <c r="D1144" s="17"/>
     </row>
-    <row r="1145" spans="1:4">
-      <c r="A1145" s="49"/>
+    <row r="1145" spans="4:4">
       <c r="D1145" s="17"/>
     </row>
-    <row r="1146" spans="1:4">
-      <c r="A1146" s="49"/>
+    <row r="1146" spans="4:4">
       <c r="D1146" s="17"/>
     </row>
-    <row r="1147" spans="1:4">
-      <c r="A1147" s="49"/>
+    <row r="1147" spans="4:4">
       <c r="D1147" s="17"/>
     </row>
-    <row r="1148" spans="1:4">
-      <c r="A1148" s="49"/>
+    <row r="1148" spans="4:4">
       <c r="D1148" s="17"/>
     </row>
-    <row r="1149" spans="1:4">
-      <c r="A1149" s="49"/>
+    <row r="1149" spans="4:4">
       <c r="D1149" s="17"/>
     </row>
-    <row r="1150" spans="1:4">
-      <c r="A1150" s="49"/>
+    <row r="1150" spans="4:4">
       <c r="D1150" s="17"/>
     </row>
-    <row r="1151" spans="1:4">
-      <c r="A1151" s="49"/>
+    <row r="1151" spans="4:4">
       <c r="D1151" s="17"/>
     </row>
-    <row r="1152" spans="1:4">
-      <c r="A1152" s="49"/>
+    <row r="1152" spans="4:4">
       <c r="D1152" s="17"/>
     </row>
-    <row r="1153" spans="1:4">
-      <c r="A1153" s="49"/>
+    <row r="1153" spans="4:4">
       <c r="D1153" s="17"/>
     </row>
-    <row r="1154" spans="1:4">
-      <c r="A1154" s="49"/>
+    <row r="1154" spans="4:4">
       <c r="D1154" s="17"/>
     </row>
-    <row r="1155" spans="1:4">
-      <c r="A1155" s="49"/>
+    <row r="1155" spans="4:4">
       <c r="D1155" s="17"/>
     </row>
-    <row r="1156" spans="1:4">
-      <c r="A1156" s="49"/>
+    <row r="1156" spans="4:4">
       <c r="D1156" s="17"/>
     </row>
-    <row r="1157" spans="1:4">
-      <c r="A1157" s="49"/>
+    <row r="1157" spans="4:4">
       <c r="D1157" s="17"/>
     </row>
-    <row r="1158" spans="1:4">
-      <c r="A1158" s="49"/>
+    <row r="1158" spans="4:4">
       <c r="D1158" s="17"/>
     </row>
-    <row r="1159" spans="1:4">
-      <c r="A1159" s="49"/>
+    <row r="1159" spans="4:4">
       <c r="D1159" s="17"/>
     </row>
-    <row r="1160" spans="1:4">
-      <c r="A1160" s="49"/>
+    <row r="1160" spans="4:4">
       <c r="D1160" s="17"/>
     </row>
-    <row r="1161" spans="1:4">
-      <c r="A1161" s="49"/>
+    <row r="1161" spans="4:4">
       <c r="D1161" s="17"/>
     </row>
-    <row r="1162" spans="1:4">
-      <c r="A1162" s="49"/>
+    <row r="1162" spans="4:4">
       <c r="D1162" s="17"/>
     </row>
-    <row r="1163" spans="1:4">
-      <c r="A1163" s="49"/>
+    <row r="1163" spans="4:4">
       <c r="D1163" s="17"/>
     </row>
-    <row r="1164" spans="1:4">
-      <c r="A1164" s="49"/>
+    <row r="1164" spans="4:4">
       <c r="D1164" s="17"/>
     </row>
-    <row r="1165" spans="1:4">
-      <c r="A1165" s="49"/>
+    <row r="1165" spans="4:4">
       <c r="D1165" s="17"/>
     </row>
-    <row r="1166" spans="1:4">
-      <c r="A1166" s="49"/>
+    <row r="1166" spans="4:4">
       <c r="D1166" s="17"/>
     </row>
-    <row r="1167" spans="1:4">
-      <c r="A1167" s="49"/>
+    <row r="1167" spans="4:4">
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G129" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G134" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -9380,202 +8447,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="B7" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>340</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$134</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="381">
   <si>
     <t>N°</t>
   </si>
@@ -634,7 +634,7 @@
     <t>05 41 77 21 68</t>
   </si>
   <si>
-    <t>MILOUA FATHI</t>
+    <t>MILOUA FETHI</t>
   </si>
   <si>
     <t>fethi22miloua@gmail.com</t>
@@ -1055,6 +1055,12 @@
   </si>
   <si>
     <t>0655206865</t>
+  </si>
+  <si>
+    <t>OUARI KHEIRA</t>
+  </si>
+  <si>
+    <t>ouari_k@yahoo.fr</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -5275,7 +5281,15 @@
       </c>
     </row>
     <row r="135" spans="1:7">
-      <c r="D135" s="17"/>
+      <c r="B135" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="F135" s="17" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="136" spans="1:7">
       <c r="D136" s="17"/>
@@ -8374,7 +8388,7 @@
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G134" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G135" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8447,202 +8461,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>353</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>353</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="393">
   <si>
     <t>N°</t>
   </si>
@@ -1061,6 +1061,42 @@
   </si>
   <si>
     <t>ouari_k@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SABOUNDJI Asmaa Hadjer</t>
+  </si>
+  <si>
+    <t>saboundjiasmaa@gmail.com</t>
+  </si>
+  <si>
+    <t>0655459306 /  0556562385</t>
+  </si>
+  <si>
+    <t>HACENE IMENE</t>
+  </si>
+  <si>
+    <t>hacene_imene12@yahoo.com</t>
+  </si>
+  <si>
+    <t>0542471563</t>
+  </si>
+  <si>
+    <t>BENKATLANE Aissa</t>
+  </si>
+  <si>
+    <t>a.benkatlane@gmail.com</t>
+  </si>
+  <si>
+    <t>0697113466</t>
+  </si>
+  <si>
+    <t>Fezazi Ismahene</t>
+  </si>
+  <si>
+    <t>ismahene.fezazi@gmail.com</t>
+  </si>
+  <si>
+    <t>0652652866</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2456,7 +2492,7 @@
     <col min="4" max="4" width="19.1428571428571" style="16" customWidth="1"/>
     <col min="5" max="5" width="21.552380952381" style="16" customWidth="1"/>
     <col min="6" max="6" width="38.8571428571429" style="17" customWidth="1"/>
-    <col min="7" max="7" width="18.2857142857143" style="17" customWidth="1"/>
+    <col min="7" max="7" width="24.2857142857143" style="17" customWidth="1"/>
     <col min="8" max="16384" width="11" style="18"/>
   </cols>
   <sheetData>
@@ -5280,28 +5316,102 @@
         <v>340</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" ht="15.75" spans="1:7">
       <c r="B135" s="17" t="s">
         <v>341</v>
       </c>
+      <c r="C135" s="23" t="s">
+        <v>8</v>
+      </c>
       <c r="D135" s="17" t="s">
         <v>21</v>
       </c>
+      <c r="E135" s="16" t="s">
+        <v>29</v>
+      </c>
       <c r="F135" s="17" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
-      <c r="D136" s="17"/>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="D137" s="17"/>
-    </row>
-    <row r="138" spans="1:7">
-      <c r="D138" s="17"/>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="D139" s="17"/>
+    <row r="136" ht="15.75" spans="1:7">
+      <c r="B136" s="17" t="s">
+        <v>343</v>
+      </c>
+      <c r="C136" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E136" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F136" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="G136" s="49" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" spans="1:7">
+      <c r="B137" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="C137" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E137" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F137" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G137" s="52" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" spans="1:7">
+      <c r="B138" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="C138" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E138" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F138" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="G138" s="52" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" spans="1:7">
+      <c r="B139" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="C139" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E139" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F139" s="49" t="s">
+        <v>353</v>
+      </c>
+      <c r="G139" s="52" t="s">
+        <v>354</v>
+      </c>
     </row>
     <row r="140" spans="1:7">
       <c r="D140" s="17"/>
@@ -8388,9 +8498,6 @@
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G135" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
   <hyperlinks>
     <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
     <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
@@ -8461,202 +8568,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$140</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="397">
   <si>
     <t>N°</t>
   </si>
@@ -250,7 +250,7 @@
     <t>HANAFI SALAH</t>
   </si>
   <si>
-    <t xml:space="preserve">sal_hanafi@outlook.com </t>
+    <t>udl.fge.vdpg@gmail.com</t>
   </si>
   <si>
     <t>HASSANI NAIMA</t>
@@ -982,9 +982,6 @@
     <t>RAIS ABDELMAJID</t>
   </si>
   <si>
-    <t>Retraité</t>
-  </si>
-  <si>
     <t>amrais@yahoo.com</t>
   </si>
   <si>
@@ -1006,9 +1003,6 @@
     <t>KADA KLOUCHA OMAR</t>
   </si>
   <si>
-    <t>Permenant Associé</t>
-  </si>
-  <si>
     <t>klomar05@yahoo.fr</t>
   </si>
   <si>
@@ -1097,6 +1091,24 @@
   </si>
   <si>
     <t>0652652866</t>
+  </si>
+  <si>
+    <t>ABID HAMZA</t>
+  </si>
+  <si>
+    <t>PrE</t>
+  </si>
+  <si>
+    <t>abid_hamza@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BELAIDI OUAFIA</t>
+  </si>
+  <si>
+    <t>belaidi.ouafia@outlook.fr</t>
+  </si>
+  <si>
+    <t>0668834015</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1991,7 +2003,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2130,6 +2142,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2137,6 +2150,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2643,7 +2657,7 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="50" t="s">
+      <c r="G7" s="51" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2666,7 +2680,7 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="G8" s="51" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2710,7 +2724,7 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="50" t="s">
+      <c r="G10" s="51" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3279,7 +3293,7 @@
       <c r="F37" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="G37" s="51" t="s">
+      <c r="G37" s="52" t="s">
         <v>89</v>
       </c>
     </row>
@@ -3323,7 +3337,7 @@
       <c r="F39" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="G39" s="50" t="s">
+      <c r="G39" s="51" t="s">
         <v>94</v>
       </c>
     </row>
@@ -3619,7 +3633,7 @@
       <c r="F53" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="G53" s="50" t="s">
+      <c r="G53" s="51" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3663,7 +3677,7 @@
       <c r="F55" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="G55" s="50" t="s">
+      <c r="G55" s="51" t="s">
         <v>130</v>
       </c>
     </row>
@@ -3879,7 +3893,7 @@
       <c r="F65" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="G65" s="50" t="s">
+      <c r="G65" s="51" t="s">
         <v>160</v>
       </c>
     </row>
@@ -3942,7 +3956,7 @@
       <c r="F68" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="G68" s="51" t="s">
+      <c r="G68" s="52" t="s">
         <v>169</v>
       </c>
     </row>
@@ -3986,7 +4000,7 @@
       <c r="F70" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="G70" s="50" t="s">
+      <c r="G70" s="51" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4007,7 +4021,7 @@
       <c r="F71" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="G71" s="50" t="s">
+      <c r="G71" s="51" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4028,7 +4042,7 @@
       <c r="F72" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="G72" s="50" t="s">
+      <c r="G72" s="51" t="s">
         <v>181</v>
       </c>
     </row>
@@ -4049,7 +4063,7 @@
       <c r="F73" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="G73" s="50" t="s">
+      <c r="G73" s="51" t="s">
         <v>184</v>
       </c>
     </row>
@@ -4072,7 +4086,7 @@
       <c r="F74" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G74" s="50" t="s">
+      <c r="G74" s="51" t="s">
         <v>187</v>
       </c>
     </row>
@@ -4137,7 +4151,7 @@
       <c r="F77" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="G77" s="50" t="s">
+      <c r="G77" s="51" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4202,7 +4216,7 @@
       <c r="F80" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="G80" s="50" t="s">
+      <c r="G80" s="51" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4414,7 +4428,7 @@
       <c r="F90" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="G90" s="50" t="s">
+      <c r="G90" s="51" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4458,7 +4472,7 @@
       <c r="F92" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="G92" s="50" t="s">
+      <c r="G92" s="51" t="s">
         <v>237</v>
       </c>
     </row>
@@ -4481,7 +4495,7 @@
       <c r="F93" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="G93" s="50" t="s">
+      <c r="G93" s="51" t="s">
         <v>241</v>
       </c>
     </row>
@@ -4525,7 +4539,7 @@
       <c r="F95" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="G95" s="50" t="s">
+      <c r="G95" s="51" t="s">
         <v>247</v>
       </c>
     </row>
@@ -4760,7 +4774,7 @@
       <c r="F106" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="G106" s="51" t="s">
+      <c r="G106" s="52" t="s">
         <v>278</v>
       </c>
     </row>
@@ -5121,13 +5135,13 @@
         <v>8</v>
       </c>
       <c r="D125" s="44" t="s">
-        <v>316</v>
+        <v>127</v>
       </c>
       <c r="E125" s="44" t="s">
         <v>10</v>
       </c>
       <c r="F125" s="46" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G125" s="27"/>
     </row>
@@ -5136,19 +5150,19 @@
         <v>125</v>
       </c>
       <c r="B126" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="44" t="s">
         <v>318</v>
-      </c>
-      <c r="C126" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="44" t="s">
-        <v>319</v>
       </c>
       <c r="E126" s="44" t="s">
         <v>29</v>
       </c>
       <c r="F126" s="46" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G126" s="27"/>
     </row>
@@ -5157,7 +5171,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C127" s="23" t="s">
         <v>8</v>
@@ -5167,78 +5181,78 @@
       </c>
       <c r="E127" s="45"/>
       <c r="F127" s="46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" ht="31.5" spans="1:7">
+    <row r="128" ht="15.75" spans="1:7">
       <c r="A128" s="22">
         <v>127</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C128" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="44" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
       <c r="E128" s="45" t="s">
         <v>29</v>
       </c>
       <c r="F128" s="46" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" ht="31.5" spans="1:7">
+    <row r="129" ht="15.75" spans="1:7">
       <c r="A129" s="22">
         <v>128</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C129" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="44" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
       <c r="E129" s="45" t="s">
         <v>29</v>
       </c>
       <c r="F129" s="46" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" ht="31.5" spans="1:7">
+    <row r="130" ht="15.75" spans="1:7">
       <c r="A130" s="22">
         <v>129</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C130" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="44" t="s">
-        <v>324</v>
+        <v>9</v>
       </c>
       <c r="E130" s="45" t="s">
         <v>10</v>
       </c>
       <c r="F130" s="48" t="s">
-        <v>329</v>
-      </c>
-      <c r="G130" s="50" t="s">
-        <v>330</v>
+        <v>327</v>
+      </c>
+      <c r="G130" s="51" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="131" ht="15.75" spans="1:7">
       <c r="B131" s="23" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C131" s="23" t="s">
         <v>8</v>
@@ -5250,15 +5264,15 @@
         <v>136</v>
       </c>
       <c r="F131" s="49" t="s">
-        <v>332</v>
-      </c>
-      <c r="G131" s="52" t="s">
-        <v>333</v>
+        <v>330</v>
+      </c>
+      <c r="G131" s="53" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="132" ht="15.75" spans="1:7">
       <c r="B132" s="17" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>8</v>
@@ -5270,15 +5284,15 @@
         <v>29</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="G132" s="52" t="s">
-        <v>336</v>
+        <v>333</v>
+      </c>
+      <c r="G132" s="53" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="133" ht="15.75" spans="1:7">
       <c r="B133" s="17" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C133" s="23" t="s">
         <v>8</v>
@@ -5290,10 +5304,10 @@
         <v>136</v>
       </c>
       <c r="F133" s="49" t="s">
-        <v>338</v>
-      </c>
-      <c r="G133" s="52" t="s">
-        <v>339</v>
+        <v>336</v>
+      </c>
+      <c r="G133" s="53" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:7">
@@ -5312,13 +5326,13 @@
       <c r="F134" s="49" t="s">
         <v>314</v>
       </c>
-      <c r="G134" s="52" t="s">
-        <v>340</v>
+      <c r="G134" s="53" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="135" ht="15.75" spans="1:7">
       <c r="B135" s="17" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C135" s="23" t="s">
         <v>8</v>
@@ -5330,12 +5344,12 @@
         <v>29</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="136" ht="15.75" spans="1:7">
       <c r="B136" s="17" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C136" s="23" t="s">
         <v>8</v>
@@ -5347,15 +5361,15 @@
         <v>136</v>
       </c>
       <c r="F136" s="49" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G136" s="49" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="137" ht="15.75" spans="1:7">
       <c r="B137" s="17" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C137" s="23" t="s">
         <v>8</v>
@@ -5367,15 +5381,15 @@
         <v>136</v>
       </c>
       <c r="F137" s="49" t="s">
-        <v>347</v>
-      </c>
-      <c r="G137" s="52" t="s">
-        <v>348</v>
+        <v>345</v>
+      </c>
+      <c r="G137" s="53" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="138" ht="15.75" spans="1:7">
       <c r="B138" s="17" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>8</v>
@@ -5387,15 +5401,15 @@
         <v>136</v>
       </c>
       <c r="F138" s="49" t="s">
-        <v>350</v>
-      </c>
-      <c r="G138" s="52" t="s">
-        <v>351</v>
+        <v>348</v>
+      </c>
+      <c r="G138" s="53" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="139" ht="15.75" spans="1:7">
       <c r="B139" s="17" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C139" s="23" t="s">
         <v>8</v>
@@ -5407,17 +5421,42 @@
         <v>136</v>
       </c>
       <c r="F139" s="49" t="s">
+        <v>351</v>
+      </c>
+      <c r="G139" s="53" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="B140" s="17" t="s">
         <v>353</v>
       </c>
-      <c r="G139" s="52" t="s">
+      <c r="D140" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="16" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="140" spans="1:7">
-      <c r="D140" s="17"/>
+      <c r="F140" s="49" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="141" spans="1:7">
-      <c r="D141" s="17"/>
+      <c r="B141" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D141" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E141" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F141" s="50" t="s">
+        <v>357</v>
+      </c>
+      <c r="G141" s="54" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="142" spans="1:7">
       <c r="D142" s="17"/>
@@ -8568,202 +8607,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,8 +11,8 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$140</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="396">
   <si>
     <t>N°</t>
   </si>
@@ -920,9 +920,6 @@
   </si>
   <si>
     <t>CHIKHI NAWEL</t>
-  </si>
-  <si>
-    <t>chikhi nawel75@yahoo.fr</t>
   </si>
   <si>
     <t>DELLOUM AMIRA</t>
@@ -4946,9 +4943,7 @@
         <v>127</v>
       </c>
       <c r="E115" s="45"/>
-      <c r="F115" s="46" t="s">
-        <v>296</v>
-      </c>
+      <c r="F115" s="46"/>
       <c r="G115" s="27"/>
     </row>
     <row r="116" ht="15.75" spans="1:7">
@@ -4956,7 +4951,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C116" s="23" t="s">
         <v>8</v>
@@ -4968,7 +4963,7 @@
         <v>140</v>
       </c>
       <c r="F116" s="46" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G116" s="27"/>
     </row>
@@ -4977,7 +4972,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C117" s="23" t="s">
         <v>8</v>
@@ -4987,7 +4982,7 @@
       </c>
       <c r="E117" s="45"/>
       <c r="F117" s="46" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G117" s="27"/>
     </row>
@@ -4996,7 +4991,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C118" s="23" t="s">
         <v>8</v>
@@ -5006,7 +5001,7 @@
       </c>
       <c r="E118" s="45"/>
       <c r="F118" s="46" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="G118" s="27"/>
     </row>
@@ -5015,7 +5010,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C119" s="23" t="s">
         <v>8</v>
@@ -5025,7 +5020,7 @@
       </c>
       <c r="E119" s="45"/>
       <c r="F119" s="46" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="G119" s="27"/>
     </row>
@@ -5034,7 +5029,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C120" s="23" t="s">
         <v>8</v>
@@ -5044,7 +5039,7 @@
       </c>
       <c r="E120" s="45"/>
       <c r="F120" s="46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G120" s="27"/>
     </row>
@@ -5053,7 +5048,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C121" s="23" t="s">
         <v>8</v>
@@ -5063,7 +5058,7 @@
       </c>
       <c r="E121" s="45"/>
       <c r="F121" s="46" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G121" s="27"/>
     </row>
@@ -5072,7 +5067,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C122" s="23" t="s">
         <v>8</v>
@@ -5082,7 +5077,7 @@
       </c>
       <c r="E122" s="45"/>
       <c r="F122" s="46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G122" s="27"/>
     </row>
@@ -5091,7 +5086,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C123" s="23" t="s">
         <v>8</v>
@@ -5101,7 +5096,7 @@
       </c>
       <c r="E123" s="45"/>
       <c r="F123" s="46" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G123" s="47"/>
     </row>
@@ -5110,7 +5105,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C124" s="23" t="s">
         <v>8</v>
@@ -5120,7 +5115,7 @@
       </c>
       <c r="E124" s="45"/>
       <c r="F124" s="46" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G124" s="27"/>
     </row>
@@ -5129,7 +5124,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C125" s="23" t="s">
         <v>8</v>
@@ -5141,7 +5136,7 @@
         <v>10</v>
       </c>
       <c r="F125" s="46" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G125" s="27"/>
     </row>
@@ -5150,19 +5145,19 @@
         <v>125</v>
       </c>
       <c r="B126" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="44" t="s">
         <v>317</v>
-      </c>
-      <c r="C126" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="44" t="s">
-        <v>318</v>
       </c>
       <c r="E126" s="44" t="s">
         <v>29</v>
       </c>
       <c r="F126" s="46" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G126" s="27"/>
     </row>
@@ -5171,7 +5166,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C127" s="23" t="s">
         <v>8</v>
@@ -5181,7 +5176,7 @@
       </c>
       <c r="E127" s="45"/>
       <c r="F127" s="46" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G127" s="27"/>
     </row>
@@ -5190,7 +5185,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C128" s="23" t="s">
         <v>8</v>
@@ -5202,7 +5197,7 @@
         <v>29</v>
       </c>
       <c r="F128" s="46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G128" s="27"/>
     </row>
@@ -5211,7 +5206,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C129" s="23" t="s">
         <v>8</v>
@@ -5223,7 +5218,7 @@
         <v>29</v>
       </c>
       <c r="F129" s="46" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G129" s="27"/>
     </row>
@@ -5232,7 +5227,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C130" s="23" t="s">
         <v>8</v>
@@ -5244,15 +5239,15 @@
         <v>10</v>
       </c>
       <c r="F130" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="G130" s="51" t="s">
         <v>327</v>
-      </c>
-      <c r="G130" s="51" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="131" ht="15.75" spans="1:7">
       <c r="B131" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C131" s="23" t="s">
         <v>8</v>
@@ -5264,15 +5259,15 @@
         <v>136</v>
       </c>
       <c r="F131" s="49" t="s">
+        <v>329</v>
+      </c>
+      <c r="G131" s="53" t="s">
         <v>330</v>
-      </c>
-      <c r="G131" s="53" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="132" ht="15.75" spans="1:7">
       <c r="B132" s="17" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>8</v>
@@ -5284,15 +5279,15 @@
         <v>29</v>
       </c>
       <c r="F132" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="G132" s="53" t="s">
         <v>333</v>
-      </c>
-      <c r="G132" s="53" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="133" ht="15.75" spans="1:7">
       <c r="B133" s="17" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C133" s="23" t="s">
         <v>8</v>
@@ -5304,15 +5299,15 @@
         <v>136</v>
       </c>
       <c r="F133" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="G133" s="53" t="s">
         <v>336</v>
-      </c>
-      <c r="G133" s="53" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:7">
       <c r="B134" s="17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C134" s="23" t="s">
         <v>8</v>
@@ -5324,15 +5319,15 @@
         <v>136</v>
       </c>
       <c r="F134" s="49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G134" s="53" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="135" ht="15.75" spans="1:7">
       <c r="B135" s="17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C135" s="23" t="s">
         <v>8</v>
@@ -5344,12 +5339,12 @@
         <v>29</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="136" ht="15.75" spans="1:7">
       <c r="B136" s="17" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C136" s="23" t="s">
         <v>8</v>
@@ -5361,15 +5356,15 @@
         <v>136</v>
       </c>
       <c r="F136" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="G136" s="49" t="s">
         <v>342</v>
-      </c>
-      <c r="G136" s="49" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="137" ht="15.75" spans="1:7">
       <c r="B137" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C137" s="23" t="s">
         <v>8</v>
@@ -5381,15 +5376,15 @@
         <v>136</v>
       </c>
       <c r="F137" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="G137" s="53" t="s">
         <v>345</v>
-      </c>
-      <c r="G137" s="53" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="138" ht="15.75" spans="1:7">
       <c r="B138" s="17" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>8</v>
@@ -5401,15 +5396,15 @@
         <v>136</v>
       </c>
       <c r="F138" s="49" t="s">
+        <v>347</v>
+      </c>
+      <c r="G138" s="53" t="s">
         <v>348</v>
-      </c>
-      <c r="G138" s="53" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="139" ht="15.75" spans="1:7">
       <c r="B139" s="17" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C139" s="23" t="s">
         <v>8</v>
@@ -5421,29 +5416,29 @@
         <v>136</v>
       </c>
       <c r="F139" s="49" t="s">
+        <v>350</v>
+      </c>
+      <c r="G139" s="53" t="s">
         <v>351</v>
-      </c>
-      <c r="G139" s="53" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="B140" s="17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D140" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E140" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="F140" s="49" t="s">
         <v>354</v>
-      </c>
-      <c r="F140" s="49" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="B141" s="17" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D141" s="17" t="s">
         <v>127</v>
@@ -5452,10 +5447,10 @@
         <v>136</v>
       </c>
       <c r="F141" s="50" t="s">
+        <v>356</v>
+      </c>
+      <c r="G141" s="54" t="s">
         <v>357</v>
-      </c>
-      <c r="G141" s="54" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -8537,6 +8532,9 @@
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G141" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
     <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
@@ -8607,202 +8605,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>365</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>368</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>371</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>375</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="C7" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>378</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="C9" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>382</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>384</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D11" s="7" t="s">
         <v>386</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>389</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>391</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>393</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>395</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -1081,7 +1081,7 @@
     <t>0697113466</t>
   </si>
   <si>
-    <t>Fezazi Ismahene</t>
+    <t>Fezazi ISMAHENE</t>
   </si>
   <si>
     <t>ismahene.fezazi@gmail.com</t>
@@ -5403,7 +5403,7 @@
       </c>
     </row>
     <row r="139" ht="15.75" spans="1:7">
-      <c r="B139" s="17" t="s">
+      <c r="B139" s="23" t="s">
         <v>349</v>
       </c>
       <c r="C139" s="23" t="s">

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="399">
   <si>
     <t>N°</t>
   </si>
@@ -922,6 +922,9 @@
     <t>CHIKHI NAWEL</t>
   </si>
   <si>
+    <t>chikhi_nawel75@yahoo.fr</t>
+  </si>
+  <si>
     <t>DELLOUM AMIRA</t>
   </si>
   <si>
@@ -1106,6 +1109,12 @@
   </si>
   <si>
     <t>0668834015</t>
+  </si>
+  <si>
+    <t>MEKHFI KHALIDA</t>
+  </si>
+  <si>
+    <t>mekhfikhalida87@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1232,7 +1241,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1308,6 +1317,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Cambria"/>
@@ -1319,6 +1334,12 @@
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Cambria"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1873,134 +1894,134 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2132,22 +2153,26 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2493,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr filterMode="1" codeName="Sheet1"/>
   <dimension ref="A1:G1167"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
@@ -2530,7 +2555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" spans="1:7">
+    <row r="2" ht="15.75" hidden="1" spans="1:7">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -2551,7 +2576,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" ht="15.75" spans="1:7">
+    <row r="3" ht="15.75" hidden="1" spans="1:7">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -2572,7 +2597,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" ht="15.75" spans="1:7">
+    <row r="4" ht="15.75" hidden="1" spans="1:7">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -2593,7 +2618,7 @@
       </c>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" ht="15.75" spans="1:7">
+    <row r="5" ht="15.75" hidden="1" spans="1:7">
       <c r="A5" s="22">
         <v>4</v>
       </c>
@@ -2614,7 +2639,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" ht="15.75" spans="1:7">
+    <row r="6" ht="15.75" hidden="1" spans="1:7">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -2635,7 +2660,7 @@
       </c>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" ht="15.75" spans="1:7">
+    <row r="7" ht="15.75" hidden="1" spans="1:7">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -2654,11 +2679,11 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="51" t="s">
+      <c r="G7" s="53" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:7">
+    <row r="8" ht="15.75" hidden="1" spans="1:7">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -2677,11 +2702,11 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="53" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:7">
+    <row r="9" ht="15.75" hidden="1" spans="1:7">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -2702,7 +2727,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" ht="15.75" spans="1:7">
+    <row r="10" ht="15.75" hidden="1" spans="1:7">
       <c r="A10" s="22">
         <v>9</v>
       </c>
@@ -2721,11 +2746,11 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="51" t="s">
+      <c r="G10" s="53" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" spans="1:7">
+    <row r="11" ht="15.75" hidden="1" spans="1:7">
       <c r="A11" s="22">
         <v>10</v>
       </c>
@@ -2746,7 +2771,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" ht="15.75" spans="1:7">
+    <row r="12" ht="15.75" hidden="1" spans="1:7">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -2767,7 +2792,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" ht="15.75" spans="1:7">
+    <row r="13" ht="15.75" hidden="1" spans="1:7">
       <c r="A13" s="22">
         <v>12</v>
       </c>
@@ -2788,7 +2813,7 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" ht="15.75" spans="1:7">
+    <row r="14" ht="15.75" hidden="1" spans="1:7">
       <c r="A14" s="22">
         <v>13</v>
       </c>
@@ -2809,7 +2834,7 @@
       </c>
       <c r="G14" s="25"/>
     </row>
-    <row r="15" ht="15.75" spans="1:7">
+    <row r="15" ht="15.75" hidden="1" spans="1:7">
       <c r="A15" s="22">
         <v>14</v>
       </c>
@@ -2830,7 +2855,7 @@
       </c>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" ht="31.5" spans="1:7">
+    <row r="16" ht="31.5" hidden="1" spans="1:7">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -2851,7 +2876,7 @@
       </c>
       <c r="G16" s="25"/>
     </row>
-    <row r="17" ht="15.75" spans="1:7">
+    <row r="17" ht="15.75" hidden="1" spans="1:7">
       <c r="A17" s="22">
         <v>16</v>
       </c>
@@ -2872,7 +2897,7 @@
       </c>
       <c r="G17" s="25"/>
     </row>
-    <row r="18" ht="15.75" spans="1:7">
+    <row r="18" ht="15.75" hidden="1" spans="1:7">
       <c r="A18" s="22">
         <v>17</v>
       </c>
@@ -2893,7 +2918,7 @@
       </c>
       <c r="G18" s="25"/>
     </row>
-    <row r="19" ht="15.75" spans="1:7">
+    <row r="19" ht="15.75" hidden="1" spans="1:7">
       <c r="A19" s="22">
         <v>18</v>
       </c>
@@ -2914,7 +2939,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" ht="31.5" spans="1:7">
+    <row r="20" ht="31.5" hidden="1" spans="1:7">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -2935,7 +2960,7 @@
       </c>
       <c r="G20" s="25"/>
     </row>
-    <row r="21" ht="15.75" spans="1:7">
+    <row r="21" ht="15.75" hidden="1" spans="1:7">
       <c r="A21" s="22">
         <v>20</v>
       </c>
@@ -2956,7 +2981,7 @@
       </c>
       <c r="G21" s="25"/>
     </row>
-    <row r="22" ht="15.75" spans="1:7">
+    <row r="22" ht="15.75" hidden="1" spans="1:7">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -2977,7 +3002,7 @@
       </c>
       <c r="G22" s="25"/>
     </row>
-    <row r="23" ht="15.75" spans="1:7">
+    <row r="23" ht="15.75" hidden="1" spans="1:7">
       <c r="A23" s="22">
         <v>22</v>
       </c>
@@ -2998,7 +3023,7 @@
       </c>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" ht="15.75" spans="1:7">
+    <row r="24" ht="15.75" hidden="1" spans="1:7">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -3019,7 +3044,7 @@
       </c>
       <c r="G24" s="25"/>
     </row>
-    <row r="25" ht="15.75" spans="1:7">
+    <row r="25" ht="15.75" hidden="1" spans="1:7">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -3040,7 +3065,7 @@
       </c>
       <c r="G25" s="25"/>
     </row>
-    <row r="26" ht="31.5" spans="1:7">
+    <row r="26" ht="31.5" hidden="1" spans="1:7">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -3061,7 +3086,7 @@
       </c>
       <c r="G26" s="25"/>
     </row>
-    <row r="27" ht="15.75" spans="1:7">
+    <row r="27" ht="15.75" hidden="1" spans="1:7">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -3082,7 +3107,7 @@
       </c>
       <c r="G27" s="25"/>
     </row>
-    <row r="28" ht="15.75" spans="1:7">
+    <row r="28" ht="15.75" hidden="1" spans="1:7">
       <c r="A28" s="22">
         <v>27</v>
       </c>
@@ -3103,7 +3128,7 @@
       </c>
       <c r="G28" s="25"/>
     </row>
-    <row r="29" ht="15.75" spans="1:7">
+    <row r="29" ht="15.75" hidden="1" spans="1:7">
       <c r="A29" s="22">
         <v>28</v>
       </c>
@@ -3124,7 +3149,7 @@
       </c>
       <c r="G29" s="25"/>
     </row>
-    <row r="30" ht="15.75" spans="1:7">
+    <row r="30" ht="15.75" hidden="1" spans="1:7">
       <c r="A30" s="22">
         <v>29</v>
       </c>
@@ -3145,7 +3170,7 @@
       </c>
       <c r="G30" s="25"/>
     </row>
-    <row r="31" ht="15.75" spans="1:7">
+    <row r="31" ht="15.75" hidden="1" spans="1:7">
       <c r="A31" s="22">
         <v>30</v>
       </c>
@@ -3166,7 +3191,7 @@
       </c>
       <c r="G31" s="25"/>
     </row>
-    <row r="32" ht="15.75" spans="1:7">
+    <row r="32" ht="15.75" hidden="1" spans="1:7">
       <c r="A32" s="22">
         <v>31</v>
       </c>
@@ -3187,7 +3212,7 @@
       </c>
       <c r="G32" s="25"/>
     </row>
-    <row r="33" ht="15.75" spans="1:7">
+    <row r="33" ht="15.75" hidden="1" spans="1:7">
       <c r="A33" s="22">
         <v>32</v>
       </c>
@@ -3208,7 +3233,7 @@
       </c>
       <c r="G33" s="25"/>
     </row>
-    <row r="34" ht="15.75" spans="1:7">
+    <row r="34" ht="15.75" hidden="1" spans="1:7">
       <c r="A34" s="22">
         <v>33</v>
       </c>
@@ -3229,7 +3254,7 @@
       </c>
       <c r="G34" s="25"/>
     </row>
-    <row r="35" ht="15.75" spans="1:7">
+    <row r="35" ht="15.75" hidden="1" spans="1:7">
       <c r="A35" s="22">
         <v>34</v>
       </c>
@@ -3250,7 +3275,7 @@
       </c>
       <c r="G35" s="25"/>
     </row>
-    <row r="36" ht="15.75" spans="1:7">
+    <row r="36" ht="15.75" hidden="1" spans="1:7">
       <c r="A36" s="22">
         <v>35</v>
       </c>
@@ -3271,7 +3296,7 @@
       </c>
       <c r="G36" s="25"/>
     </row>
-    <row r="37" ht="15.75" spans="1:7">
+    <row r="37" ht="15.75" hidden="1" spans="1:7">
       <c r="A37" s="22">
         <v>36</v>
       </c>
@@ -3290,11 +3315,11 @@
       <c r="F37" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="G37" s="52" t="s">
+      <c r="G37" s="54" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="38" ht="15.75" spans="1:7">
+    <row r="38" ht="15.75" hidden="1" spans="1:7">
       <c r="A38" s="22">
         <v>37</v>
       </c>
@@ -3315,7 +3340,7 @@
       </c>
       <c r="G38" s="25"/>
     </row>
-    <row r="39" ht="15.75" spans="1:7">
+    <row r="39" ht="15.75" hidden="1" spans="1:7">
       <c r="A39" s="22">
         <v>38</v>
       </c>
@@ -3334,11 +3359,11 @@
       <c r="F39" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="G39" s="51" t="s">
+      <c r="G39" s="53" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="40" ht="15.75" spans="1:7">
+    <row r="40" ht="15.75" hidden="1" spans="1:7">
       <c r="A40" s="22">
         <v>39</v>
       </c>
@@ -3359,7 +3384,7 @@
       </c>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" ht="15.75" spans="1:7">
+    <row r="41" ht="15.75" hidden="1" spans="1:7">
       <c r="A41" s="22">
         <v>40</v>
       </c>
@@ -3380,7 +3405,7 @@
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" ht="15.75" spans="1:7">
+    <row r="42" ht="15.75" hidden="1" spans="1:7">
       <c r="A42" s="22">
         <v>41</v>
       </c>
@@ -3401,7 +3426,7 @@
       </c>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" ht="15.75" spans="1:7">
+    <row r="43" ht="15.75" hidden="1" spans="1:7">
       <c r="A43" s="22">
         <v>42</v>
       </c>
@@ -3422,7 +3447,7 @@
       </c>
       <c r="G43" s="25"/>
     </row>
-    <row r="44" ht="15.75" spans="1:7">
+    <row r="44" ht="15.75" hidden="1" spans="1:7">
       <c r="A44" s="22">
         <v>43</v>
       </c>
@@ -3443,7 +3468,7 @@
       </c>
       <c r="G44" s="25"/>
     </row>
-    <row r="45" ht="15.75" spans="1:7">
+    <row r="45" ht="15.75" hidden="1" spans="1:7">
       <c r="A45" s="22">
         <v>44</v>
       </c>
@@ -3464,7 +3489,7 @@
       </c>
       <c r="G45" s="25"/>
     </row>
-    <row r="46" ht="15.75" spans="1:7">
+    <row r="46" ht="15.75" hidden="1" spans="1:7">
       <c r="A46" s="22">
         <v>45</v>
       </c>
@@ -3485,7 +3510,7 @@
       </c>
       <c r="G46" s="25"/>
     </row>
-    <row r="47" ht="15.75" spans="1:7">
+    <row r="47" ht="15.75" hidden="1" spans="1:7">
       <c r="A47" s="22">
         <v>46</v>
       </c>
@@ -3506,7 +3531,7 @@
       </c>
       <c r="G47" s="25"/>
     </row>
-    <row r="48" ht="15.75" spans="1:7">
+    <row r="48" ht="15.75" hidden="1" spans="1:7">
       <c r="A48" s="22">
         <v>47</v>
       </c>
@@ -3527,7 +3552,7 @@
       </c>
       <c r="G48" s="25"/>
     </row>
-    <row r="49" ht="15.75" spans="1:7">
+    <row r="49" ht="15.75" hidden="1" spans="1:7">
       <c r="A49" s="22">
         <v>48</v>
       </c>
@@ -3548,7 +3573,7 @@
       </c>
       <c r="G49" s="25"/>
     </row>
-    <row r="50" ht="15.75" spans="1:7">
+    <row r="50" ht="15.75" hidden="1" spans="1:7">
       <c r="A50" s="22">
         <v>49</v>
       </c>
@@ -3569,7 +3594,7 @@
       </c>
       <c r="G50" s="25"/>
     </row>
-    <row r="51" ht="15.75" spans="1:7">
+    <row r="51" ht="15.75" hidden="1" spans="1:7">
       <c r="A51" s="22">
         <v>50</v>
       </c>
@@ -3590,7 +3615,7 @@
       </c>
       <c r="G51" s="25"/>
     </row>
-    <row r="52" ht="15.75" spans="1:7">
+    <row r="52" ht="15.75" hidden="1" spans="1:7">
       <c r="A52" s="22">
         <v>51</v>
       </c>
@@ -3611,7 +3636,7 @@
       </c>
       <c r="G52" s="25"/>
     </row>
-    <row r="53" ht="15.75" spans="1:7">
+    <row r="53" ht="15.75" hidden="1" spans="1:7">
       <c r="A53" s="22">
         <v>52</v>
       </c>
@@ -3630,11 +3655,11 @@
       <c r="F53" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="G53" s="51" t="s">
+      <c r="G53" s="53" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="54" ht="15.75" spans="1:7">
+    <row r="54" ht="15.75" hidden="1" spans="1:7">
       <c r="A54" s="22">
         <v>53</v>
       </c>
@@ -3655,7 +3680,7 @@
       </c>
       <c r="G54" s="25"/>
     </row>
-    <row r="55" ht="15.75" spans="1:7">
+    <row r="55" ht="15.75" hidden="1" spans="1:7">
       <c r="A55" s="22">
         <v>54</v>
       </c>
@@ -3674,11 +3699,11 @@
       <c r="F55" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="G55" s="51" t="s">
+      <c r="G55" s="53" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="56" ht="15.75" spans="1:7">
+    <row r="56" ht="15.75" hidden="1" spans="1:7">
       <c r="A56" s="22">
         <v>55</v>
       </c>
@@ -3699,7 +3724,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" ht="15.75" spans="1:7">
+    <row r="57" ht="15.75" hidden="1" spans="1:7">
       <c r="A57" s="22">
         <v>56</v>
       </c>
@@ -3716,7 +3741,7 @@
       <c r="F57" s="34"/>
       <c r="G57" s="25"/>
     </row>
-    <row r="58" ht="15.75" spans="1:7">
+    <row r="58" ht="15.75" hidden="1" spans="1:7">
       <c r="A58" s="22">
         <v>57</v>
       </c>
@@ -3739,7 +3764,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" ht="15.75" spans="1:7">
+    <row r="59" ht="15.75" hidden="1" spans="1:7">
       <c r="A59" s="22">
         <v>58</v>
       </c>
@@ -3762,7 +3787,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" ht="15.75" spans="1:7">
+    <row r="60" ht="15.75" hidden="1" spans="1:7">
       <c r="A60" s="22">
         <v>59</v>
       </c>
@@ -3785,7 +3810,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="61" ht="15.75" spans="1:7">
+    <row r="61" ht="15.75" hidden="1" spans="1:7">
       <c r="A61" s="22">
         <v>60</v>
       </c>
@@ -3808,7 +3833,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="62" ht="15.75" spans="1:7">
+    <row r="62" ht="15.75" hidden="1" spans="1:7">
       <c r="A62" s="22">
         <v>61</v>
       </c>
@@ -3829,7 +3854,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" ht="31.5" spans="1:7">
+    <row r="63" ht="31.5" hidden="1" spans="1:7">
       <c r="A63" s="22">
         <v>62</v>
       </c>
@@ -3850,7 +3875,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="64" ht="15.75" spans="1:7">
+    <row r="64" ht="15.75" hidden="1" spans="1:7">
       <c r="A64" s="22">
         <v>63</v>
       </c>
@@ -3871,7 +3896,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="65" ht="15.75" spans="1:7">
+    <row r="65" ht="15.75" hidden="1" spans="1:7">
       <c r="A65" s="22">
         <v>64</v>
       </c>
@@ -3890,11 +3915,11 @@
       <c r="F65" s="41" t="s">
         <v>159</v>
       </c>
-      <c r="G65" s="51" t="s">
+      <c r="G65" s="53" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="66" ht="31.5" spans="1:7">
+    <row r="66" ht="31.5" hidden="1" spans="1:7">
       <c r="A66" s="22">
         <v>65</v>
       </c>
@@ -3915,7 +3940,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="67" ht="15.75" spans="1:7">
+    <row r="67" ht="15.75" hidden="1" spans="1:7">
       <c r="A67" s="22">
         <v>66</v>
       </c>
@@ -3936,7 +3961,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="68" ht="15.75" spans="1:7">
+    <row r="68" ht="15.75" hidden="1" spans="1:7">
       <c r="A68" s="22">
         <v>67</v>
       </c>
@@ -3953,11 +3978,11 @@
       <c r="F68" s="24" t="s">
         <v>168</v>
       </c>
-      <c r="G68" s="52" t="s">
+      <c r="G68" s="54" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="69" ht="15.75" spans="1:7">
+    <row r="69" ht="15.75" hidden="1" spans="1:7">
       <c r="A69" s="22">
         <v>68</v>
       </c>
@@ -3980,7 +4005,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="70" ht="15.75" spans="1:7">
+    <row r="70" ht="15.75" hidden="1" spans="1:7">
       <c r="A70" s="22">
         <v>69</v>
       </c>
@@ -3997,11 +4022,11 @@
       <c r="F70" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="G70" s="51" t="s">
+      <c r="G70" s="53" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="71" ht="15.75" spans="1:7">
+    <row r="71" ht="15.75" hidden="1" spans="1:7">
       <c r="A71" s="22">
         <v>70</v>
       </c>
@@ -4018,11 +4043,11 @@
       <c r="F71" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="G71" s="51" t="s">
+      <c r="G71" s="53" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="72" ht="31.5" spans="1:7">
+    <row r="72" ht="31.5" hidden="1" spans="1:7">
       <c r="A72" s="22">
         <v>71</v>
       </c>
@@ -4039,11 +4064,11 @@
       <c r="F72" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="G72" s="51" t="s">
+      <c r="G72" s="53" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="73" ht="15.75" spans="1:7">
+    <row r="73" ht="15.75" hidden="1" spans="1:7">
       <c r="A73" s="22">
         <v>72</v>
       </c>
@@ -4060,11 +4085,11 @@
       <c r="F73" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="G73" s="51" t="s">
+      <c r="G73" s="53" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="74" ht="15.75" spans="1:7">
+    <row r="74" ht="15.75" hidden="1" spans="1:7">
       <c r="A74" s="22">
         <v>73</v>
       </c>
@@ -4083,11 +4108,11 @@
       <c r="F74" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="G74" s="51" t="s">
+      <c r="G74" s="53" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="75" ht="15.75" spans="1:7">
+    <row r="75" ht="15.75" hidden="1" spans="1:7">
       <c r="A75" s="22">
         <v>74</v>
       </c>
@@ -4108,7 +4133,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="76" ht="15.75" spans="1:7">
+    <row r="76" ht="15.75" hidden="1" spans="1:7">
       <c r="A76" s="22">
         <v>75</v>
       </c>
@@ -4131,7 +4156,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="77" ht="15.75" spans="1:7">
+    <row r="77" ht="15.75" hidden="1" spans="1:7">
       <c r="A77" s="22">
         <v>76</v>
       </c>
@@ -4148,11 +4173,11 @@
       <c r="F77" s="32" t="s">
         <v>195</v>
       </c>
-      <c r="G77" s="51" t="s">
+      <c r="G77" s="53" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="78" ht="31.5" spans="1:7">
+    <row r="78" ht="31.5" hidden="1" spans="1:7">
       <c r="A78" s="22">
         <v>77</v>
       </c>
@@ -4175,7 +4200,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="79" ht="15.75" spans="1:7">
+    <row r="79" ht="15.75" hidden="1" spans="1:7">
       <c r="A79" s="22">
         <v>78</v>
       </c>
@@ -4194,7 +4219,7 @@
       </c>
       <c r="G79" s="25"/>
     </row>
-    <row r="80" ht="15.75" spans="1:7">
+    <row r="80" ht="15.75" hidden="1" spans="1:7">
       <c r="A80" s="22">
         <v>79</v>
       </c>
@@ -4213,11 +4238,11 @@
       <c r="F80" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="G80" s="51" t="s">
+      <c r="G80" s="53" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="81" ht="15.75" spans="1:7">
+    <row r="81" ht="15.75" hidden="1" spans="1:7">
       <c r="A81" s="22">
         <v>80</v>
       </c>
@@ -4240,7 +4265,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="82" ht="15.75" spans="1:7">
+    <row r="82" ht="15.75" hidden="1" spans="1:7">
       <c r="A82" s="22">
         <v>81</v>
       </c>
@@ -4261,7 +4286,7 @@
       </c>
       <c r="G82" s="25"/>
     </row>
-    <row r="83" ht="15.75" spans="1:7">
+    <row r="83" ht="15.75" hidden="1" spans="1:7">
       <c r="A83" s="22">
         <v>82</v>
       </c>
@@ -4282,7 +4307,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="84" ht="15.75" spans="1:7">
+    <row r="84" ht="15.75" hidden="1" spans="1:7">
       <c r="A84" s="22">
         <v>83</v>
       </c>
@@ -4305,7 +4330,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="85" ht="15.75" spans="1:7">
+    <row r="85" ht="15.75" hidden="1" spans="1:7">
       <c r="A85" s="22">
         <v>84</v>
       </c>
@@ -4324,7 +4349,7 @@
       </c>
       <c r="G85" s="25"/>
     </row>
-    <row r="86" ht="15.75" spans="1:7">
+    <row r="86" ht="15.75" hidden="1" spans="1:7">
       <c r="A86" s="22">
         <v>85</v>
       </c>
@@ -4347,7 +4372,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="87" ht="15.75" spans="1:7">
+    <row r="87" ht="15.75" hidden="1" spans="1:7">
       <c r="A87" s="22">
         <v>86</v>
       </c>
@@ -4366,7 +4391,7 @@
       </c>
       <c r="G87" s="25"/>
     </row>
-    <row r="88" ht="15.75" spans="1:7">
+    <row r="88" ht="15.75" hidden="1" spans="1:7">
       <c r="A88" s="22">
         <v>87</v>
       </c>
@@ -4387,7 +4412,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="89" ht="15.75" spans="1:7">
+    <row r="89" ht="15.75" hidden="1" spans="1:7">
       <c r="A89" s="22">
         <v>88</v>
       </c>
@@ -4408,7 +4433,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="90" ht="15.75" spans="1:7">
+    <row r="90" ht="15.75" hidden="1" spans="1:7">
       <c r="A90" s="22">
         <v>89</v>
       </c>
@@ -4425,11 +4450,11 @@
       <c r="F90" s="32" t="s">
         <v>230</v>
       </c>
-      <c r="G90" s="51" t="s">
+      <c r="G90" s="53" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="91" ht="15.75" spans="1:7">
+    <row r="91" ht="15.75" hidden="1" spans="1:7">
       <c r="A91" s="22">
         <v>90</v>
       </c>
@@ -4452,7 +4477,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="92" ht="15.75" spans="1:7">
+    <row r="92" ht="15.75" hidden="1" spans="1:7">
       <c r="A92" s="22">
         <v>91</v>
       </c>
@@ -4469,11 +4494,11 @@
       <c r="F92" s="32" t="s">
         <v>236</v>
       </c>
-      <c r="G92" s="51" t="s">
+      <c r="G92" s="53" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="93" ht="15.75" spans="1:7">
+    <row r="93" ht="15.75" hidden="1" spans="1:7">
       <c r="A93" s="22">
         <v>92</v>
       </c>
@@ -4492,11 +4517,11 @@
       <c r="F93" s="32" t="s">
         <v>240</v>
       </c>
-      <c r="G93" s="51" t="s">
+      <c r="G93" s="53" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="94" ht="15.75" spans="1:7">
+    <row r="94" ht="15.75" hidden="1" spans="1:7">
       <c r="A94" s="22">
         <v>93</v>
       </c>
@@ -4517,7 +4542,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="95" ht="15.75" spans="1:7">
+    <row r="95" ht="15.75" hidden="1" spans="1:7">
       <c r="A95" s="22">
         <v>94</v>
       </c>
@@ -4536,11 +4561,11 @@
       <c r="F95" s="43" t="s">
         <v>246</v>
       </c>
-      <c r="G95" s="51" t="s">
+      <c r="G95" s="53" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="96" ht="15.75" spans="1:7">
+    <row r="96" ht="15.75" hidden="1" spans="1:7">
       <c r="A96" s="22">
         <v>95</v>
       </c>
@@ -4561,7 +4586,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="97" ht="31.5" spans="1:7">
+    <row r="97" ht="31.5" hidden="1" spans="1:7">
       <c r="A97" s="22">
         <v>96</v>
       </c>
@@ -4584,7 +4609,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="98" ht="15.75" spans="1:7">
+    <row r="98" ht="15.75" hidden="1" spans="1:7">
       <c r="A98" s="22">
         <v>97</v>
       </c>
@@ -4607,7 +4632,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="99" ht="15.75" spans="1:7">
+    <row r="99" ht="15.75" hidden="1" spans="1:7">
       <c r="A99" s="22">
         <v>98</v>
       </c>
@@ -4630,7 +4655,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="100" ht="15.75" spans="1:7">
+    <row r="100" ht="15.75" hidden="1" spans="1:7">
       <c r="A100" s="22">
         <v>99</v>
       </c>
@@ -4647,7 +4672,7 @@
       <c r="F100" s="32"/>
       <c r="G100" s="25"/>
     </row>
-    <row r="101" ht="15.75" spans="1:7">
+    <row r="101" ht="15.75" hidden="1" spans="1:7">
       <c r="A101" s="22">
         <v>100</v>
       </c>
@@ -4668,7 +4693,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="102" ht="15.75" spans="1:7">
+    <row r="102" ht="15.75" hidden="1" spans="1:7">
       <c r="A102" s="22">
         <v>101</v>
       </c>
@@ -4687,7 +4712,7 @@
       </c>
       <c r="G102" s="25"/>
     </row>
-    <row r="103" ht="15.75" spans="1:7">
+    <row r="103" ht="15.75" hidden="1" spans="1:7">
       <c r="A103" s="22">
         <v>102</v>
       </c>
@@ -4708,7 +4733,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="104" ht="15.75" spans="1:7">
+    <row r="104" ht="15.75" hidden="1" spans="1:7">
       <c r="A104" s="22">
         <v>103</v>
       </c>
@@ -4731,7 +4756,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="105" ht="15.75" spans="1:7">
+    <row r="105" ht="15.75" hidden="1" spans="1:7">
       <c r="A105" s="22">
         <v>104</v>
       </c>
@@ -4752,7 +4777,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="106" ht="15.75" spans="1:7">
+    <row r="106" ht="15.75" hidden="1" spans="1:7">
       <c r="A106" s="22">
         <v>105</v>
       </c>
@@ -4771,11 +4796,11 @@
       <c r="F106" s="32" t="s">
         <v>277</v>
       </c>
-      <c r="G106" s="52" t="s">
+      <c r="G106" s="54" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="107" ht="15.75" spans="1:7">
+    <row r="107" ht="15.75" hidden="1" spans="1:7">
       <c r="A107" s="22">
         <v>106</v>
       </c>
@@ -4796,7 +4821,7 @@
       </c>
       <c r="G107" s="25"/>
     </row>
-    <row r="108" ht="15.75" spans="1:7">
+    <row r="108" ht="15.75" hidden="1" spans="1:7">
       <c r="A108" s="22">
         <v>107</v>
       </c>
@@ -4815,7 +4840,7 @@
       </c>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" ht="15.75" spans="1:7">
+    <row r="109" ht="15.75" hidden="1" spans="1:7">
       <c r="A109" s="22">
         <v>108</v>
       </c>
@@ -4834,7 +4859,7 @@
       </c>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" ht="31.5" spans="1:7">
+    <row r="110" ht="31.5" hidden="1" spans="1:7">
       <c r="A110" s="22">
         <v>109</v>
       </c>
@@ -4853,7 +4878,7 @@
       </c>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" ht="15.75" spans="1:7">
+    <row r="111" ht="15.75" hidden="1" spans="1:7">
       <c r="A111" s="22">
         <v>110</v>
       </c>
@@ -4872,7 +4897,7 @@
       </c>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" ht="31.5" spans="1:7">
+    <row r="112" ht="31.5" hidden="1" spans="1:7">
       <c r="A112" s="22">
         <v>111</v>
       </c>
@@ -4891,7 +4916,7 @@
       </c>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" ht="15.75" spans="1:7">
+    <row r="113" ht="15.75" hidden="1" spans="1:7">
       <c r="A113" s="22">
         <v>112</v>
       </c>
@@ -4910,7 +4935,7 @@
       </c>
       <c r="G113" s="27"/>
     </row>
-    <row r="114" ht="15.75" spans="1:7">
+    <row r="114" ht="15.75" hidden="1" spans="1:7">
       <c r="A114" s="22">
         <v>113</v>
       </c>
@@ -4943,15 +4968,17 @@
         <v>127</v>
       </c>
       <c r="E115" s="45"/>
-      <c r="F115" s="46"/>
+      <c r="F115" s="47" t="s">
+        <v>296</v>
+      </c>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" ht="15.75" spans="1:7">
+    <row r="116" ht="15.75" hidden="1" spans="1:7">
       <c r="A116" s="22">
         <v>115</v>
       </c>
       <c r="B116" s="23" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C116" s="23" t="s">
         <v>8</v>
@@ -4963,16 +4990,16 @@
         <v>140</v>
       </c>
       <c r="F116" s="46" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" ht="15.75" spans="1:7">
+    <row r="117" ht="15.75" hidden="1" spans="1:7">
       <c r="A117" s="22">
         <v>116</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C117" s="23" t="s">
         <v>8</v>
@@ -4982,16 +5009,16 @@
       </c>
       <c r="E117" s="45"/>
       <c r="F117" s="46" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" ht="15.75" spans="1:7">
+    <row r="118" ht="15.75" hidden="1" spans="1:7">
       <c r="A118" s="22">
         <v>117</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C118" s="23" t="s">
         <v>8</v>
@@ -5001,16 +5028,16 @@
       </c>
       <c r="E118" s="45"/>
       <c r="F118" s="46" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" ht="15.75" spans="1:7">
+    <row r="119" ht="15.75" hidden="1" spans="1:7">
       <c r="A119" s="22">
         <v>118</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C119" s="23" t="s">
         <v>8</v>
@@ -5020,16 +5047,16 @@
       </c>
       <c r="E119" s="45"/>
       <c r="F119" s="46" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" ht="15.75" spans="1:7">
+    <row r="120" ht="15.75" hidden="1" spans="1:7">
       <c r="A120" s="22">
         <v>119</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C120" s="23" t="s">
         <v>8</v>
@@ -5039,16 +5066,16 @@
       </c>
       <c r="E120" s="45"/>
       <c r="F120" s="46" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" ht="15.75" spans="1:7">
+    <row r="121" ht="15.75" hidden="1" spans="1:7">
       <c r="A121" s="22">
         <v>120</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C121" s="23" t="s">
         <v>8</v>
@@ -5058,16 +5085,16 @@
       </c>
       <c r="E121" s="45"/>
       <c r="F121" s="46" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" ht="15.75" spans="1:7">
+    <row r="122" ht="15.75" hidden="1" spans="1:7">
       <c r="A122" s="22">
         <v>121</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C122" s="23" t="s">
         <v>8</v>
@@ -5077,16 +5104,16 @@
       </c>
       <c r="E122" s="45"/>
       <c r="F122" s="46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" ht="15.75" spans="1:7">
+    <row r="123" ht="15.75" hidden="1" spans="1:7">
       <c r="A123" s="22">
         <v>122</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C123" s="23" t="s">
         <v>8</v>
@@ -5096,16 +5123,16 @@
       </c>
       <c r="E123" s="45"/>
       <c r="F123" s="46" t="s">
-        <v>311</v>
-      </c>
-      <c r="G123" s="47"/>
-    </row>
-    <row r="124" ht="15.75" spans="1:7">
+        <v>312</v>
+      </c>
+      <c r="G123" s="48"/>
+    </row>
+    <row r="124" ht="15.75" hidden="1" spans="1:7">
       <c r="A124" s="22">
         <v>123</v>
       </c>
       <c r="B124" s="23" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C124" s="23" t="s">
         <v>8</v>
@@ -5115,16 +5142,16 @@
       </c>
       <c r="E124" s="45"/>
       <c r="F124" s="46" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" ht="15.75" spans="1:7">
+    <row r="125" ht="15.75" hidden="1" spans="1:7">
       <c r="A125" s="22">
         <v>124</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C125" s="23" t="s">
         <v>8</v>
@@ -5136,37 +5163,37 @@
         <v>10</v>
       </c>
       <c r="F125" s="46" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" ht="31.5" spans="1:7">
+    <row r="126" ht="31.5" hidden="1" spans="1:7">
       <c r="A126" s="22">
         <v>125</v>
       </c>
       <c r="B126" s="23" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C126" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="44" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E126" s="44" t="s">
         <v>29</v>
       </c>
       <c r="F126" s="46" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" ht="15.75" spans="1:7">
+    <row r="127" ht="15.75" hidden="1" spans="1:7">
       <c r="A127" s="22">
         <v>126</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C127" s="23" t="s">
         <v>8</v>
@@ -5176,16 +5203,16 @@
       </c>
       <c r="E127" s="45"/>
       <c r="F127" s="46" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" ht="15.75" spans="1:7">
+    <row r="128" ht="15.75" hidden="1" spans="1:7">
       <c r="A128" s="22">
         <v>127</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C128" s="23" t="s">
         <v>8</v>
@@ -5197,16 +5224,16 @@
         <v>29</v>
       </c>
       <c r="F128" s="46" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" ht="15.75" spans="1:7">
+    <row r="129" ht="15.75" hidden="1" spans="1:7">
       <c r="A129" s="22">
         <v>128</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C129" s="23" t="s">
         <v>8</v>
@@ -5218,16 +5245,16 @@
         <v>29</v>
       </c>
       <c r="F129" s="46" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" ht="15.75" spans="1:7">
+    <row r="130" ht="15.75" hidden="1" spans="1:7">
       <c r="A130" s="22">
         <v>129</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C130" s="23" t="s">
         <v>8</v>
@@ -5238,16 +5265,16 @@
       <c r="E130" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F130" s="48" t="s">
-        <v>326</v>
-      </c>
-      <c r="G130" s="51" t="s">
+      <c r="F130" s="49" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="131" ht="15.75" spans="1:7">
+      <c r="G130" s="53" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" hidden="1" spans="1:7">
       <c r="B131" s="23" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C131" s="23" t="s">
         <v>8</v>
@@ -5258,16 +5285,16 @@
       <c r="E131" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F131" s="49" t="s">
-        <v>329</v>
-      </c>
-      <c r="G131" s="53" t="s">
+      <c r="F131" s="50" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="132" ht="15.75" spans="1:7">
+      <c r="G131" s="55" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" hidden="1" spans="1:7">
       <c r="B132" s="17" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>8</v>
@@ -5279,15 +5306,15 @@
         <v>29</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="G132" s="53" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="133" ht="15.75" spans="1:7">
+      <c r="G132" s="55" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" hidden="1" spans="1:7">
       <c r="B133" s="17" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C133" s="23" t="s">
         <v>8</v>
@@ -5298,16 +5325,16 @@
       <c r="E133" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F133" s="49" t="s">
-        <v>335</v>
-      </c>
-      <c r="G133" s="53" t="s">
+      <c r="F133" s="50" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="134" ht="15.75" spans="1:7">
+      <c r="G133" s="55" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" hidden="1" spans="1:7">
       <c r="B134" s="17" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C134" s="23" t="s">
         <v>8</v>
@@ -5318,16 +5345,16 @@
       <c r="E134" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F134" s="49" t="s">
-        <v>313</v>
-      </c>
-      <c r="G134" s="53" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="135" ht="15.75" spans="1:7">
+      <c r="F134" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="G134" s="55" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" hidden="1" spans="1:7">
       <c r="B135" s="17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C135" s="23" t="s">
         <v>8</v>
@@ -5339,12 +5366,12 @@
         <v>29</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="136" ht="15.75" spans="1:7">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" hidden="1" spans="1:7">
       <c r="B136" s="17" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C136" s="23" t="s">
         <v>8</v>
@@ -5355,16 +5382,16 @@
       <c r="E136" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F136" s="49" t="s">
-        <v>341</v>
-      </c>
-      <c r="G136" s="49" t="s">
+      <c r="F136" s="50" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="137" ht="15.75" spans="1:7">
+      <c r="G136" s="50" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" hidden="1" spans="1:7">
       <c r="B137" s="17" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C137" s="23" t="s">
         <v>8</v>
@@ -5375,16 +5402,16 @@
       <c r="E137" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F137" s="49" t="s">
-        <v>344</v>
-      </c>
-      <c r="G137" s="53" t="s">
+      <c r="F137" s="50" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="138" ht="15.75" spans="1:7">
+      <c r="G137" s="55" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" hidden="1" spans="1:7">
       <c r="B138" s="17" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>8</v>
@@ -5395,16 +5422,16 @@
       <c r="E138" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F138" s="49" t="s">
-        <v>347</v>
-      </c>
-      <c r="G138" s="53" t="s">
+      <c r="F138" s="50" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="139" ht="15.75" spans="1:7">
+      <c r="G138" s="55" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" hidden="1" spans="1:7">
       <c r="B139" s="23" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C139" s="23" t="s">
         <v>8</v>
@@ -5415,30 +5442,36 @@
       <c r="E139" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F139" s="49" t="s">
-        <v>350</v>
-      </c>
-      <c r="G139" s="53" t="s">
+      <c r="F139" s="50" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="140" spans="1:7">
+      <c r="G139" s="55" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" hidden="1" spans="1:7">
       <c r="B140" s="17" t="s">
-        <v>352</v>
+        <v>353</v>
+      </c>
+      <c r="C140" s="23" t="s">
+        <v>8</v>
       </c>
       <c r="D140" s="17" t="s">
         <v>9</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="F140" s="49" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="141" spans="1:7">
+      <c r="F140" s="50" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" hidden="1" spans="1:7">
       <c r="B141" s="17" t="s">
-        <v>355</v>
+        <v>356</v>
+      </c>
+      <c r="C141" s="23" t="s">
+        <v>8</v>
       </c>
       <c r="D141" s="17" t="s">
         <v>127</v>
@@ -5446,15 +5479,29 @@
       <c r="E141" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="F141" s="50" t="s">
-        <v>356</v>
-      </c>
-      <c r="G141" s="54" t="s">
+      <c r="F141" s="51" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="142" spans="1:7">
-      <c r="D142" s="17"/>
+      <c r="G141" s="56" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" hidden="1" spans="1:7">
+      <c r="B142" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="C142" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="E142" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="F142" s="52" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="143" spans="1:7">
       <c r="D143" s="17"/>
@@ -8532,7 +8579,12 @@
       <c r="D1167" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G141" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G142" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="CHIKHI NAWEL"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8583,6 +8635,7 @@
     <hyperlink ref="F10" r:id="rId45" display="beddadboucif@gmail.com"/>
     <hyperlink ref="F9" r:id="rId46" display="seyfeddine.electrotechnique@gmail.com"/>
     <hyperlink ref="F130" r:id="rId47" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F115" r:id="rId48" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8605,202 +8658,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -2518,7 +2518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G1167"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
@@ -2555,7 +2555,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" spans="1:7">
+    <row r="2" ht="15.75" spans="1:7">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" ht="15.75" hidden="1" spans="1:7">
+    <row r="3" ht="15.75" spans="1:7">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" ht="15.75" hidden="1" spans="1:7">
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" ht="15.75" hidden="1" spans="1:7">
+    <row r="5" ht="15.75" spans="1:7">
       <c r="A5" s="22">
         <v>4</v>
       </c>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" ht="15.75" hidden="1" spans="1:7">
+    <row r="6" ht="15.75" spans="1:7">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" ht="15.75" hidden="1" spans="1:7">
+    <row r="7" ht="15.75" spans="1:7">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" hidden="1" spans="1:7">
+    <row r="8" ht="15.75" spans="1:7">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -2706,7 +2706,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" hidden="1" spans="1:7">
+    <row r="9" ht="15.75" spans="1:7">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" ht="15.75" hidden="1" spans="1:7">
+    <row r="10" ht="15.75" spans="1:7">
       <c r="A10" s="22">
         <v>9</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" hidden="1" spans="1:7">
+    <row r="11" ht="15.75" spans="1:7">
       <c r="A11" s="22">
         <v>10</v>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" ht="15.75" hidden="1" spans="1:7">
+    <row r="12" ht="15.75" spans="1:7">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" ht="15.75" hidden="1" spans="1:7">
+    <row r="13" ht="15.75" spans="1:7">
       <c r="A13" s="22">
         <v>12</v>
       </c>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" ht="15.75" hidden="1" spans="1:7">
+    <row r="14" ht="15.75" spans="1:7">
       <c r="A14" s="22">
         <v>13</v>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="G14" s="25"/>
     </row>
-    <row r="15" ht="15.75" hidden="1" spans="1:7">
+    <row r="15" ht="15.75" spans="1:7">
       <c r="A15" s="22">
         <v>14</v>
       </c>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" ht="31.5" hidden="1" spans="1:7">
+    <row r="16" ht="31.5" spans="1:7">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G16" s="25"/>
     </row>
-    <row r="17" ht="15.75" hidden="1" spans="1:7">
+    <row r="17" ht="15.75" spans="1:7">
       <c r="A17" s="22">
         <v>16</v>
       </c>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="G17" s="25"/>
     </row>
-    <row r="18" ht="15.75" hidden="1" spans="1:7">
+    <row r="18" ht="15.75" spans="1:7">
       <c r="A18" s="22">
         <v>17</v>
       </c>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="G18" s="25"/>
     </row>
-    <row r="19" ht="15.75" hidden="1" spans="1:7">
+    <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="22">
         <v>18</v>
       </c>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" ht="31.5" hidden="1" spans="1:7">
+    <row r="20" ht="31.5" spans="1:7">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G20" s="25"/>
     </row>
-    <row r="21" ht="15.75" hidden="1" spans="1:7">
+    <row r="21" ht="15.75" spans="1:7">
       <c r="A21" s="22">
         <v>20</v>
       </c>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G21" s="25"/>
     </row>
-    <row r="22" ht="15.75" hidden="1" spans="1:7">
+    <row r="22" ht="15.75" spans="1:7">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G22" s="25"/>
     </row>
-    <row r="23" ht="15.75" hidden="1" spans="1:7">
+    <row r="23" ht="15.75" spans="1:7">
       <c r="A23" s="22">
         <v>22</v>
       </c>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" ht="15.75" hidden="1" spans="1:7">
+    <row r="24" ht="15.75" spans="1:7">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="G24" s="25"/>
     </row>
-    <row r="25" ht="15.75" hidden="1" spans="1:7">
+    <row r="25" ht="15.75" spans="1:7">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="G25" s="25"/>
     </row>
-    <row r="26" ht="31.5" hidden="1" spans="1:7">
+    <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G26" s="25"/>
     </row>
-    <row r="27" ht="15.75" hidden="1" spans="1:7">
+    <row r="27" ht="15.75" spans="1:7">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="G27" s="25"/>
     </row>
-    <row r="28" ht="15.75" hidden="1" spans="1:7">
+    <row r="28" ht="15.75" spans="1:7">
       <c r="A28" s="22">
         <v>27</v>
       </c>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="G28" s="25"/>
     </row>
-    <row r="29" ht="15.75" hidden="1" spans="1:7">
+    <row r="29" ht="15.75" spans="1:7">
       <c r="A29" s="22">
         <v>28</v>
       </c>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G29" s="25"/>
     </row>
-    <row r="30" ht="15.75" hidden="1" spans="1:7">
+    <row r="30" ht="15.75" spans="1:7">
       <c r="A30" s="22">
         <v>29</v>
       </c>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G30" s="25"/>
     </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
+    <row r="31" ht="15.75" spans="1:7">
       <c r="A31" s="22">
         <v>30</v>
       </c>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G31" s="25"/>
     </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
+    <row r="32" ht="15.75" spans="1:7">
       <c r="A32" s="22">
         <v>31</v>
       </c>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="G32" s="25"/>
     </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
+    <row r="33" ht="15.75" spans="1:7">
       <c r="A33" s="22">
         <v>32</v>
       </c>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="G33" s="25"/>
     </row>
-    <row r="34" ht="15.75" hidden="1" spans="1:7">
+    <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="22">
         <v>33</v>
       </c>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="G34" s="25"/>
     </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
+    <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="22">
         <v>34</v>
       </c>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="G35" s="25"/>
     </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
+    <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="22">
         <v>35</v>
       </c>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G36" s="25"/>
     </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="22">
         <v>36</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
+    <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="22">
         <v>37</v>
       </c>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="G38" s="25"/>
     </row>
-    <row r="39" ht="15.75" hidden="1" spans="1:7">
+    <row r="39" ht="15.75" spans="1:7">
       <c r="A39" s="22">
         <v>38</v>
       </c>
@@ -3363,7 +3363,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" ht="15.75" hidden="1" spans="1:7">
+    <row r="40" ht="15.75" spans="1:7">
       <c r="A40" s="22">
         <v>39</v>
       </c>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" ht="15.75" hidden="1" spans="1:7">
+    <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="22">
         <v>40</v>
       </c>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" ht="15.75" hidden="1" spans="1:7">
+    <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="22">
         <v>41</v>
       </c>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" ht="15.75" hidden="1" spans="1:7">
+    <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="22">
         <v>42</v>
       </c>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G43" s="25"/>
     </row>
-    <row r="44" ht="15.75" hidden="1" spans="1:7">
+    <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="22">
         <v>43</v>
       </c>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="G44" s="25"/>
     </row>
-    <row r="45" ht="15.75" hidden="1" spans="1:7">
+    <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="22">
         <v>44</v>
       </c>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="G45" s="25"/>
     </row>
-    <row r="46" ht="15.75" hidden="1" spans="1:7">
+    <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="22">
         <v>45</v>
       </c>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="G46" s="25"/>
     </row>
-    <row r="47" ht="15.75" hidden="1" spans="1:7">
+    <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="22">
         <v>46</v>
       </c>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="G47" s="25"/>
     </row>
-    <row r="48" ht="15.75" hidden="1" spans="1:7">
+    <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="22">
         <v>47</v>
       </c>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G48" s="25"/>
     </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
+    <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="22">
         <v>48</v>
       </c>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="G49" s="25"/>
     </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
+    <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="22">
         <v>49</v>
       </c>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G50" s="25"/>
     </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
+    <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="22">
         <v>50</v>
       </c>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="G51" s="25"/>
     </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
+    <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="22">
         <v>51</v>
       </c>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G52" s="25"/>
     </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
+    <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="22">
         <v>52</v>
       </c>
@@ -3659,7 +3659,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
+    <row r="54" ht="15.75" spans="1:7">
       <c r="A54" s="22">
         <v>53</v>
       </c>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G54" s="25"/>
     </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
+    <row r="55" ht="15.75" spans="1:7">
       <c r="A55" s="22">
         <v>54</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
+    <row r="56" ht="15.75" spans="1:7">
       <c r="A56" s="22">
         <v>55</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
+    <row r="57" ht="15.75" spans="1:7">
       <c r="A57" s="22">
         <v>56</v>
       </c>
@@ -3741,7 +3741,7 @@
       <c r="F57" s="34"/>
       <c r="G57" s="25"/>
     </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
+    <row r="58" ht="15.75" spans="1:7">
       <c r="A58" s="22">
         <v>57</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" ht="15.75" hidden="1" spans="1:7">
+    <row r="59" ht="15.75" spans="1:7">
       <c r="A59" s="22">
         <v>58</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="60" ht="15.75" hidden="1" spans="1:7">
+    <row r="60" ht="15.75" spans="1:7">
       <c r="A60" s="22">
         <v>59</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="61" ht="15.75" hidden="1" spans="1:7">
+    <row r="61" ht="15.75" spans="1:7">
       <c r="A61" s="22">
         <v>60</v>
       </c>
@@ -3833,7 +3833,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="62" ht="15.75" hidden="1" spans="1:7">
+    <row r="62" ht="15.75" spans="1:7">
       <c r="A62" s="22">
         <v>61</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" ht="31.5" hidden="1" spans="1:7">
+    <row r="63" ht="31.5" spans="1:7">
       <c r="A63" s="22">
         <v>62</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="64" ht="15.75" hidden="1" spans="1:7">
+    <row r="64" ht="15.75" spans="1:7">
       <c r="A64" s="22">
         <v>63</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="65" ht="15.75" hidden="1" spans="1:7">
+    <row r="65" ht="15.75" spans="1:7">
       <c r="A65" s="22">
         <v>64</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="66" ht="31.5" hidden="1" spans="1:7">
+    <row r="66" ht="31.5" spans="1:7">
       <c r="A66" s="22">
         <v>65</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="67" ht="15.75" hidden="1" spans="1:7">
+    <row r="67" ht="15.75" spans="1:7">
       <c r="A67" s="22">
         <v>66</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="68" ht="15.75" hidden="1" spans="1:7">
+    <row r="68" ht="15.75" spans="1:7">
       <c r="A68" s="22">
         <v>67</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="69" ht="15.75" hidden="1" spans="1:7">
+    <row r="69" ht="15.75" spans="1:7">
       <c r="A69" s="22">
         <v>68</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="70" ht="15.75" hidden="1" spans="1:7">
+    <row r="70" ht="15.75" spans="1:7">
       <c r="A70" s="22">
         <v>69</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="71" ht="15.75" hidden="1" spans="1:7">
+    <row r="71" ht="15.75" spans="1:7">
       <c r="A71" s="22">
         <v>70</v>
       </c>
@@ -4047,7 +4047,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="72" ht="31.5" hidden="1" spans="1:7">
+    <row r="72" ht="31.5" spans="1:7">
       <c r="A72" s="22">
         <v>71</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="73" ht="15.75" hidden="1" spans="1:7">
+    <row r="73" ht="15.75" spans="1:7">
       <c r="A73" s="22">
         <v>72</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="74" ht="15.75" hidden="1" spans="1:7">
+    <row r="74" ht="15.75" spans="1:7">
       <c r="A74" s="22">
         <v>73</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="75" ht="15.75" hidden="1" spans="1:7">
+    <row r="75" ht="15.75" spans="1:7">
       <c r="A75" s="22">
         <v>74</v>
       </c>
@@ -4133,7 +4133,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="76" ht="15.75" hidden="1" spans="1:7">
+    <row r="76" ht="15.75" spans="1:7">
       <c r="A76" s="22">
         <v>75</v>
       </c>
@@ -4156,7 +4156,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="77" ht="15.75" hidden="1" spans="1:7">
+    <row r="77" ht="15.75" spans="1:7">
       <c r="A77" s="22">
         <v>76</v>
       </c>
@@ -4177,7 +4177,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="78" ht="31.5" hidden="1" spans="1:7">
+    <row r="78" ht="31.5" spans="1:7">
       <c r="A78" s="22">
         <v>77</v>
       </c>
@@ -4200,7 +4200,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="79" ht="15.75" hidden="1" spans="1:7">
+    <row r="79" ht="15.75" spans="1:7">
       <c r="A79" s="22">
         <v>78</v>
       </c>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="G79" s="25"/>
     </row>
-    <row r="80" ht="15.75" hidden="1" spans="1:7">
+    <row r="80" ht="15.75" spans="1:7">
       <c r="A80" s="22">
         <v>79</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="81" ht="15.75" hidden="1" spans="1:7">
+    <row r="81" ht="15.75" spans="1:7">
       <c r="A81" s="22">
         <v>80</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="82" ht="15.75" hidden="1" spans="1:7">
+    <row r="82" ht="15.75" spans="1:7">
       <c r="A82" s="22">
         <v>81</v>
       </c>
@@ -4286,7 +4286,7 @@
       </c>
       <c r="G82" s="25"/>
     </row>
-    <row r="83" ht="15.75" hidden="1" spans="1:7">
+    <row r="83" ht="15.75" spans="1:7">
       <c r="A83" s="22">
         <v>82</v>
       </c>
@@ -4307,7 +4307,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="84" ht="15.75" hidden="1" spans="1:7">
+    <row r="84" ht="15.75" spans="1:7">
       <c r="A84" s="22">
         <v>83</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="85" ht="15.75" hidden="1" spans="1:7">
+    <row r="85" ht="15.75" spans="1:7">
       <c r="A85" s="22">
         <v>84</v>
       </c>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G85" s="25"/>
     </row>
-    <row r="86" ht="15.75" hidden="1" spans="1:7">
+    <row r="86" ht="15.75" spans="1:7">
       <c r="A86" s="22">
         <v>85</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="87" ht="15.75" hidden="1" spans="1:7">
+    <row r="87" ht="15.75" spans="1:7">
       <c r="A87" s="22">
         <v>86</v>
       </c>
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G87" s="25"/>
     </row>
-    <row r="88" ht="15.75" hidden="1" spans="1:7">
+    <row r="88" ht="15.75" spans="1:7">
       <c r="A88" s="22">
         <v>87</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="89" ht="15.75" hidden="1" spans="1:7">
+    <row r="89" ht="15.75" spans="1:7">
       <c r="A89" s="22">
         <v>88</v>
       </c>
@@ -4433,7 +4433,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="90" ht="15.75" hidden="1" spans="1:7">
+    <row r="90" ht="15.75" spans="1:7">
       <c r="A90" s="22">
         <v>89</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="91" ht="15.75" hidden="1" spans="1:7">
+    <row r="91" ht="15.75" spans="1:7">
       <c r="A91" s="22">
         <v>90</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="92" ht="15.75" hidden="1" spans="1:7">
+    <row r="92" ht="15.75" spans="1:7">
       <c r="A92" s="22">
         <v>91</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="93" ht="15.75" hidden="1" spans="1:7">
+    <row r="93" ht="15.75" spans="1:7">
       <c r="A93" s="22">
         <v>92</v>
       </c>
@@ -4521,7 +4521,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="94" ht="15.75" hidden="1" spans="1:7">
+    <row r="94" ht="15.75" spans="1:7">
       <c r="A94" s="22">
         <v>93</v>
       </c>
@@ -4542,7 +4542,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="95" ht="15.75" hidden="1" spans="1:7">
+    <row r="95" ht="15.75" spans="1:7">
       <c r="A95" s="22">
         <v>94</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="96" ht="15.75" hidden="1" spans="1:7">
+    <row r="96" ht="15.75" spans="1:7">
       <c r="A96" s="22">
         <v>95</v>
       </c>
@@ -4586,7 +4586,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="97" ht="31.5" hidden="1" spans="1:7">
+    <row r="97" ht="31.5" spans="1:7">
       <c r="A97" s="22">
         <v>96</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="98" ht="15.75" hidden="1" spans="1:7">
+    <row r="98" ht="15.75" spans="1:7">
       <c r="A98" s="22">
         <v>97</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="99" ht="15.75" hidden="1" spans="1:7">
+    <row r="99" ht="15.75" spans="1:7">
       <c r="A99" s="22">
         <v>98</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="100" ht="15.75" hidden="1" spans="1:7">
+    <row r="100" ht="15.75" spans="1:7">
       <c r="A100" s="22">
         <v>99</v>
       </c>
@@ -4672,7 +4672,7 @@
       <c r="F100" s="32"/>
       <c r="G100" s="25"/>
     </row>
-    <row r="101" ht="15.75" hidden="1" spans="1:7">
+    <row r="101" ht="15.75" spans="1:7">
       <c r="A101" s="22">
         <v>100</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="102" ht="15.75" hidden="1" spans="1:7">
+    <row r="102" ht="15.75" spans="1:7">
       <c r="A102" s="22">
         <v>101</v>
       </c>
@@ -4712,7 +4712,7 @@
       </c>
       <c r="G102" s="25"/>
     </row>
-    <row r="103" ht="15.75" hidden="1" spans="1:7">
+    <row r="103" ht="15.75" spans="1:7">
       <c r="A103" s="22">
         <v>102</v>
       </c>
@@ -4733,7 +4733,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="104" ht="15.75" hidden="1" spans="1:7">
+    <row r="104" ht="15.75" spans="1:7">
       <c r="A104" s="22">
         <v>103</v>
       </c>
@@ -4756,7 +4756,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="105" ht="15.75" hidden="1" spans="1:7">
+    <row r="105" ht="15.75" spans="1:7">
       <c r="A105" s="22">
         <v>104</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="106" ht="15.75" hidden="1" spans="1:7">
+    <row r="106" ht="15.75" spans="1:7">
       <c r="A106" s="22">
         <v>105</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="107" ht="15.75" hidden="1" spans="1:7">
+    <row r="107" ht="15.75" spans="1:7">
       <c r="A107" s="22">
         <v>106</v>
       </c>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="G107" s="25"/>
     </row>
-    <row r="108" ht="15.75" hidden="1" spans="1:7">
+    <row r="108" ht="15.75" spans="1:7">
       <c r="A108" s="22">
         <v>107</v>
       </c>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" ht="15.75" hidden="1" spans="1:7">
+    <row r="109" ht="15.75" spans="1:7">
       <c r="A109" s="22">
         <v>108</v>
       </c>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" ht="31.5" hidden="1" spans="1:7">
+    <row r="110" ht="31.5" spans="1:7">
       <c r="A110" s="22">
         <v>109</v>
       </c>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" ht="15.75" hidden="1" spans="1:7">
+    <row r="111" ht="15.75" spans="1:7">
       <c r="A111" s="22">
         <v>110</v>
       </c>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" ht="31.5" hidden="1" spans="1:7">
+    <row r="112" ht="31.5" spans="1:7">
       <c r="A112" s="22">
         <v>111</v>
       </c>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" ht="15.75" hidden="1" spans="1:7">
+    <row r="113" ht="15.75" spans="1:7">
       <c r="A113" s="22">
         <v>112</v>
       </c>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="G113" s="27"/>
     </row>
-    <row r="114" ht="15.75" hidden="1" spans="1:7">
+    <row r="114" ht="15.75" spans="1:7">
       <c r="A114" s="22">
         <v>113</v>
       </c>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" ht="15.75" hidden="1" spans="1:7">
+    <row r="116" ht="15.75" spans="1:7">
       <c r="A116" s="22">
         <v>115</v>
       </c>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" ht="15.75" hidden="1" spans="1:7">
+    <row r="117" ht="15.75" spans="1:7">
       <c r="A117" s="22">
         <v>116</v>
       </c>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" ht="15.75" hidden="1" spans="1:7">
+    <row r="118" ht="15.75" spans="1:7">
       <c r="A118" s="22">
         <v>117</v>
       </c>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" ht="15.75" hidden="1" spans="1:7">
+    <row r="119" ht="15.75" spans="1:7">
       <c r="A119" s="22">
         <v>118</v>
       </c>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" ht="15.75" hidden="1" spans="1:7">
+    <row r="120" ht="15.75" spans="1:7">
       <c r="A120" s="22">
         <v>119</v>
       </c>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" ht="15.75" hidden="1" spans="1:7">
+    <row r="121" ht="15.75" spans="1:7">
       <c r="A121" s="22">
         <v>120</v>
       </c>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" ht="15.75" hidden="1" spans="1:7">
+    <row r="122" ht="15.75" spans="1:7">
       <c r="A122" s="22">
         <v>121</v>
       </c>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" ht="15.75" hidden="1" spans="1:7">
+    <row r="123" ht="15.75" spans="1:7">
       <c r="A123" s="22">
         <v>122</v>
       </c>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G123" s="48"/>
     </row>
-    <row r="124" ht="15.75" hidden="1" spans="1:7">
+    <row r="124" ht="15.75" spans="1:7">
       <c r="A124" s="22">
         <v>123</v>
       </c>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" ht="15.75" hidden="1" spans="1:7">
+    <row r="125" ht="15.75" spans="1:7">
       <c r="A125" s="22">
         <v>124</v>
       </c>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" ht="31.5" hidden="1" spans="1:7">
+    <row r="126" ht="31.5" spans="1:7">
       <c r="A126" s="22">
         <v>125</v>
       </c>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" ht="15.75" hidden="1" spans="1:7">
+    <row r="127" ht="15.75" spans="1:7">
       <c r="A127" s="22">
         <v>126</v>
       </c>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" ht="15.75" hidden="1" spans="1:7">
+    <row r="128" ht="15.75" spans="1:7">
       <c r="A128" s="22">
         <v>127</v>
       </c>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" ht="15.75" hidden="1" spans="1:7">
+    <row r="129" ht="15.75" spans="1:7">
       <c r="A129" s="22">
         <v>128</v>
       </c>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" ht="15.75" hidden="1" spans="1:7">
+    <row r="130" ht="15.75" spans="1:7">
       <c r="A130" s="22">
         <v>129</v>
       </c>
@@ -5272,14 +5272,17 @@
         <v>328</v>
       </c>
     </row>
-    <row r="131" ht="15.75" hidden="1" spans="1:7">
+    <row r="131" ht="15.75" spans="1:7">
+      <c r="A131" s="22">
+        <v>130</v>
+      </c>
       <c r="B131" s="23" t="s">
         <v>329</v>
       </c>
       <c r="C131" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D131" s="17" t="s">
+      <c r="D131" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E131" s="16" t="s">
@@ -5292,14 +5295,17 @@
         <v>331</v>
       </c>
     </row>
-    <row r="132" ht="15.75" hidden="1" spans="1:7">
+    <row r="132" ht="15.75" spans="1:7">
+      <c r="A132" s="22">
+        <v>131</v>
+      </c>
       <c r="B132" s="17" t="s">
         <v>332</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D132" s="17" t="s">
+      <c r="D132" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E132" s="16" t="s">
@@ -5312,14 +5318,17 @@
         <v>334</v>
       </c>
     </row>
-    <row r="133" ht="15.75" hidden="1" spans="1:7">
+    <row r="133" ht="15.75" spans="1:7">
+      <c r="A133" s="22">
+        <v>132</v>
+      </c>
       <c r="B133" s="17" t="s">
         <v>335</v>
       </c>
       <c r="C133" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D133" s="17" t="s">
+      <c r="D133" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E133" s="16" t="s">
@@ -5332,14 +5341,17 @@
         <v>337</v>
       </c>
     </row>
-    <row r="134" ht="15.75" hidden="1" spans="1:7">
+    <row r="134" ht="15.75" spans="1:7">
+      <c r="A134" s="22">
+        <v>133</v>
+      </c>
       <c r="B134" s="17" t="s">
         <v>313</v>
       </c>
       <c r="C134" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D134" s="17" t="s">
+      <c r="D134" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E134" s="16" t="s">
@@ -5352,14 +5364,17 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" ht="15.75" hidden="1" spans="1:7">
+    <row r="135" ht="15.75" spans="1:7">
+      <c r="A135" s="22">
+        <v>134</v>
+      </c>
       <c r="B135" s="17" t="s">
         <v>339</v>
       </c>
       <c r="C135" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D135" s="17" t="s">
+      <c r="D135" s="16" t="s">
         <v>21</v>
       </c>
       <c r="E135" s="16" t="s">
@@ -5369,14 +5384,17 @@
         <v>340</v>
       </c>
     </row>
-    <row r="136" ht="15.75" hidden="1" spans="1:7">
+    <row r="136" ht="15.75" spans="1:7">
+      <c r="A136" s="22">
+        <v>135</v>
+      </c>
       <c r="B136" s="17" t="s">
         <v>341</v>
       </c>
       <c r="C136" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D136" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E136" s="16" t="s">
@@ -5389,14 +5407,17 @@
         <v>343</v>
       </c>
     </row>
-    <row r="137" ht="15.75" hidden="1" spans="1:7">
+    <row r="137" ht="15.75" spans="1:7">
+      <c r="A137" s="22">
+        <v>136</v>
+      </c>
       <c r="B137" s="17" t="s">
         <v>344</v>
       </c>
       <c r="C137" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D137" s="17" t="s">
+      <c r="D137" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E137" s="16" t="s">
@@ -5409,14 +5430,17 @@
         <v>346</v>
       </c>
     </row>
-    <row r="138" ht="15.75" hidden="1" spans="1:7">
+    <row r="138" ht="15.75" spans="1:7">
+      <c r="A138" s="22">
+        <v>137</v>
+      </c>
       <c r="B138" s="17" t="s">
         <v>347</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D138" s="17" t="s">
+      <c r="D138" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E138" s="16" t="s">
@@ -5429,14 +5453,17 @@
         <v>349</v>
       </c>
     </row>
-    <row r="139" ht="15.75" hidden="1" spans="1:7">
+    <row r="139" ht="15.75" spans="1:7">
+      <c r="A139" s="22">
+        <v>138</v>
+      </c>
       <c r="B139" s="23" t="s">
         <v>350</v>
       </c>
       <c r="C139" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D139" s="17" t="s">
+      <c r="D139" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E139" s="16" t="s">
@@ -5449,14 +5476,17 @@
         <v>352</v>
       </c>
     </row>
-    <row r="140" ht="15.75" hidden="1" spans="1:7">
+    <row r="140" ht="15.75" spans="1:7">
+      <c r="A140" s="22">
+        <v>139</v>
+      </c>
       <c r="B140" s="17" t="s">
         <v>353</v>
       </c>
       <c r="C140" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D140" s="17" t="s">
+      <c r="D140" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E140" s="16" t="s">
@@ -5466,14 +5496,17 @@
         <v>355</v>
       </c>
     </row>
-    <row r="141" ht="15.75" hidden="1" spans="1:7">
+    <row r="141" ht="15.75" spans="1:7">
+      <c r="A141" s="22">
+        <v>140</v>
+      </c>
       <c r="B141" s="17" t="s">
         <v>356</v>
       </c>
       <c r="C141" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D141" s="17" t="s">
+      <c r="D141" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E141" s="16" t="s">
@@ -5486,14 +5519,17 @@
         <v>358</v>
       </c>
     </row>
-    <row r="142" ht="15.75" hidden="1" spans="1:7">
+    <row r="142" ht="15.75" spans="1:7">
+      <c r="A142" s="22">
+        <v>141</v>
+      </c>
       <c r="B142" s="17" t="s">
         <v>359</v>
       </c>
       <c r="C142" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D142" s="17" t="s">
+      <c r="D142" s="16" t="s">
         <v>127</v>
       </c>
       <c r="E142" s="16" t="s">
@@ -8580,11 +8616,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G142" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="CHIKHI NAWEL"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="397">
   <si>
     <t>N°</t>
   </si>
@@ -277,12 +277,6 @@
     <t>nadjet_69@hotmail.fr</t>
   </si>
   <si>
-    <t>M.BRAHAMI MOSTEFA</t>
-  </si>
-  <si>
-    <t>mbrahami@yahoo.com</t>
-  </si>
-  <si>
     <t>MAAMMAR MOHAMED</t>
   </si>
   <si>
@@ -319,7 +313,7 @@
     <t>0558193860</t>
   </si>
   <si>
-    <t>MN.BRAHAMI NADJIB</t>
+    <t>BRAHAMI MOHAMED NADJIB</t>
   </si>
   <si>
     <t>nadjbrahami@gmail.com</t>
@@ -2519,7 +2513,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G1167"/>
+  <dimension ref="A1:G1166"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="16" customWidth="1"/>
@@ -3235,7 +3229,7 @@
     </row>
     <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="22">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="23" t="s">
         <v>81</v>
@@ -3247,7 +3241,7 @@
         <v>9</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F34" s="26" t="s">
         <v>82</v>
@@ -3256,7 +3250,7 @@
     </row>
     <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="22">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="23" t="s">
         <v>83</v>
@@ -3268,7 +3262,7 @@
         <v>9</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F35" s="26" t="s">
         <v>84</v>
@@ -3277,7 +3271,7 @@
     </row>
     <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="23" t="s">
         <v>85</v>
@@ -3294,14 +3288,16 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="25"/>
+      <c r="G36" s="54" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="23" t="s">
         <v>8</v>
@@ -3313,15 +3309,13 @@
         <v>10</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G37" s="54" t="s">
         <v>89</v>
       </c>
+      <c r="G37" s="25"/>
     </row>
     <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="22">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="23" t="s">
         <v>90</v>
@@ -3333,19 +3327,21 @@
         <v>9</v>
       </c>
       <c r="E38" s="22" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="25"/>
-    </row>
-    <row r="39" ht="15.75" spans="1:7">
+      <c r="G38" s="53" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" ht="31.5" spans="1:7">
       <c r="A39" s="22">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C39" s="23" t="s">
         <v>8</v>
@@ -3357,15 +3353,13 @@
         <v>29</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="G39" s="53" t="s">
         <v>94</v>
       </c>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" ht="15.75" spans="1:7">
       <c r="A40" s="22">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="23" t="s">
         <v>95</v>
@@ -3377,7 +3371,7 @@
         <v>9</v>
       </c>
       <c r="E40" s="22" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F40" s="26" t="s">
         <v>96</v>
@@ -3386,7 +3380,7 @@
     </row>
     <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="22">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="23" t="s">
         <v>97</v>
@@ -3407,7 +3401,7 @@
     </row>
     <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="22">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="23" t="s">
         <v>99</v>
@@ -3428,7 +3422,7 @@
     </row>
     <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="22">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="23" t="s">
         <v>101</v>
@@ -3437,7 +3431,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E43" s="22" t="s">
         <v>10</v>
@@ -3449,7 +3443,7 @@
     </row>
     <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="22">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="23" t="s">
         <v>103</v>
@@ -3458,7 +3452,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E44" s="22" t="s">
         <v>10</v>
@@ -3470,7 +3464,7 @@
     </row>
     <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="22">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="23" t="s">
         <v>105</v>
@@ -3491,7 +3485,7 @@
     </row>
     <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="22">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="23" t="s">
         <v>107</v>
@@ -3500,10 +3494,10 @@
         <v>8</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E46" s="22" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="F46" s="26" t="s">
         <v>108</v>
@@ -3512,7 +3506,7 @@
     </row>
     <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="22">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="23" t="s">
         <v>109</v>
@@ -3521,10 +3515,10 @@
         <v>8</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E47" s="22" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="F47" s="26" t="s">
         <v>110</v>
@@ -3533,7 +3527,7 @@
     </row>
     <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="22">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="23" t="s">
         <v>111</v>
@@ -3542,7 +3536,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E48" s="22" t="s">
         <v>10</v>
@@ -3554,7 +3548,7 @@
     </row>
     <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="22">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="23" t="s">
         <v>113</v>
@@ -3563,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E49" s="22" t="s">
         <v>10</v>
@@ -3575,7 +3569,7 @@
     </row>
     <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="22">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="23" t="s">
         <v>115</v>
@@ -3596,7 +3590,7 @@
     </row>
     <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="22">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="23" t="s">
         <v>117</v>
@@ -3617,7 +3611,7 @@
     </row>
     <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="22">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="23" t="s">
         <v>119</v>
@@ -3626,42 +3620,42 @@
         <v>8</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="25"/>
+      <c r="G52" s="53" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="22">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C53" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="G53" s="53" t="s">
         <v>123</v>
       </c>
+      <c r="G53" s="25"/>
     </row>
     <row r="54" ht="15.75" spans="1:7">
       <c r="A54" s="22">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="23" t="s">
         <v>124</v>
@@ -3669,540 +3663,538 @@
       <c r="C54" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D54" s="22" t="s">
-        <v>9</v>
+      <c r="D54" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="G54" s="25"/>
+        <v>126</v>
+      </c>
+      <c r="F54" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="G54" s="53" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="55" ht="15.75" spans="1:7">
       <c r="A55" s="22">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C55" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E55" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="F55" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="G55" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="33"/>
+      <c r="F55" s="26" t="s">
         <v>130</v>
+      </c>
+      <c r="G55" s="25" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="56" ht="15.75" spans="1:7">
       <c r="A56" s="22">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C56" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E56" s="33"/>
-      <c r="F56" s="26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G56" s="25" t="s">
-        <v>133</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E56" s="29"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="25"/>
     </row>
     <row r="57" ht="15.75" spans="1:7">
       <c r="A57" s="22">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E57" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C57" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E57" s="29"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="25"/>
+      <c r="F57" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="G57" s="25" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="58" ht="15.75" spans="1:7">
       <c r="A58" s="22">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C58" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E58" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F58" s="32" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G58" s="25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" ht="15.75" spans="1:7">
       <c r="A59" s="22">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C59" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E59" s="28" t="s">
-        <v>140</v>
+      <c r="D59" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>138</v>
       </c>
       <c r="F59" s="32" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G59" s="25" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="60" ht="15.75" spans="1:7">
       <c r="A60" s="22">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C60" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>140</v>
+        <v>125</v>
+      </c>
+      <c r="E60" s="35" t="s">
+        <v>134</v>
       </c>
       <c r="F60" s="32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G60" s="25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" ht="15.75" spans="1:7">
       <c r="A61" s="22">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C61" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E61" s="35" t="s">
-        <v>136</v>
-      </c>
+      <c r="D61" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E61" s="37"/>
       <c r="F61" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="G61" s="25" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="62" ht="15.75" spans="1:7">
+      <c r="G61" s="38" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" ht="31.5" spans="1:7">
       <c r="A62" s="22">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C62" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="36" t="s">
-        <v>127</v>
-      </c>
-      <c r="E62" s="37"/>
-      <c r="F62" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="G62" s="38" t="s">
+      <c r="D62" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E62" s="29"/>
+      <c r="F62" s="39" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="63" ht="31.5" spans="1:7">
+      <c r="G62" s="25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" spans="1:7">
       <c r="A63" s="22">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C63" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="E63" s="29"/>
-      <c r="F63" s="39" t="s">
-        <v>153</v>
+      <c r="D63" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E63" s="35"/>
+      <c r="F63" s="32" t="s">
+        <v>154</v>
       </c>
       <c r="G63" s="25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" ht="15.75" spans="1:7">
       <c r="A64" s="22">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C64" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E64" s="35"/>
-      <c r="F64" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="G64" s="25" t="s">
+      <c r="D64" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="E64" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="F64" s="41" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="65" ht="15.75" spans="1:7">
+      <c r="G64" s="53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" ht="31.5" spans="1:7">
       <c r="A65" s="22">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C65" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D65" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="E65" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="F65" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="G65" s="53" t="s">
+      <c r="D65" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E65" s="31"/>
+      <c r="F65" s="32" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="66" ht="31.5" spans="1:7">
+      <c r="G65" s="25" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" spans="1:7">
       <c r="A66" s="22">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C66" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E66" s="31"/>
-      <c r="F66" s="32" t="s">
-        <v>162</v>
+        <v>125</v>
+      </c>
+      <c r="E66" s="35"/>
+      <c r="F66" s="42" t="s">
+        <v>163</v>
       </c>
       <c r="G66" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" ht="15.75" spans="1:7">
       <c r="A67" s="22">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C67" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E67" s="35"/>
-      <c r="F67" s="42" t="s">
-        <v>165</v>
-      </c>
-      <c r="G67" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E67" s="31"/>
+      <c r="F67" s="24" t="s">
         <v>166</v>
+      </c>
+      <c r="G67" s="54" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="68" ht="15.75" spans="1:7">
       <c r="A68" s="22">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C68" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E68" s="31"/>
-      <c r="F68" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="G68" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F68" s="32" t="s">
         <v>169</v>
+      </c>
+      <c r="G68" s="25" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="69" ht="15.75" spans="1:7">
       <c r="A69" s="22">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C69" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E69" s="22" t="s">
-        <v>136</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E69" s="22"/>
       <c r="F69" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="G69" s="25" t="s">
         <v>172</v>
+      </c>
+      <c r="G69" s="53" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="70" ht="15.75" spans="1:7">
       <c r="A70" s="22">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C70" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E70" s="22"/>
       <c r="F70" s="32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G70" s="53" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" spans="1:7">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="71" ht="31.5" spans="1:7">
       <c r="A71" s="22">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C71" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D71" s="22" t="s">
-        <v>127</v>
+      <c r="D71" s="28" t="s">
+        <v>125</v>
       </c>
       <c r="E71" s="22"/>
-      <c r="F71" s="32" t="s">
-        <v>177</v>
+      <c r="F71" s="39" t="s">
+        <v>178</v>
       </c>
       <c r="G71" s="53" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="72" ht="31.5" spans="1:7">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" spans="1:7">
       <c r="A72" s="22">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C72" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D72" s="28" t="s">
-        <v>127</v>
+      <c r="D72" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="E72" s="22"/>
-      <c r="F72" s="39" t="s">
-        <v>180</v>
+      <c r="F72" s="26" t="s">
+        <v>181</v>
       </c>
       <c r="G72" s="53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" ht="15.75" spans="1:7">
       <c r="A73" s="22">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C73" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E73" s="22"/>
+        <v>125</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>134</v>
+      </c>
       <c r="F73" s="26" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G73" s="53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="74" ht="15.75" spans="1:7">
       <c r="A74" s="22">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C74" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E74" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="F74" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="G74" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="E74" s="22"/>
+      <c r="F74" s="32" t="s">
         <v>187</v>
+      </c>
+      <c r="G74" s="25" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="75" ht="15.75" spans="1:7">
       <c r="A75" s="22">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C75" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E75" s="22"/>
+        <v>125</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>134</v>
+      </c>
       <c r="F75" s="32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G75" s="25" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" ht="15.75" spans="1:7">
       <c r="A76" s="22">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C76" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E76" s="22" t="s">
-        <v>136</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E76" s="22"/>
       <c r="F76" s="32" t="s">
-        <v>192</v>
-      </c>
-      <c r="G76" s="25" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="77" ht="15.75" spans="1:7">
+      <c r="G76" s="53" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="77" ht="31.5" spans="1:7">
       <c r="A77" s="22">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C77" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E77" s="22"/>
+        <v>125</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>126</v>
+      </c>
       <c r="F77" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="G77" s="53" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="78" ht="31.5" spans="1:7">
+      <c r="G77" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" spans="1:7">
       <c r="A78" s="22">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C78" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E78" s="22" t="s">
-        <v>128</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E78" s="22"/>
       <c r="F78" s="32" t="s">
-        <v>198</v>
-      </c>
-      <c r="G78" s="25" t="s">
         <v>199</v>
       </c>
+      <c r="G78" s="25"/>
     </row>
     <row r="79" ht="15.75" spans="1:7">
       <c r="A79" s="22">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>200</v>
@@ -4211,63 +4203,65 @@
         <v>8</v>
       </c>
       <c r="D79" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E79" s="22"/>
+        <v>125</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>126</v>
+      </c>
       <c r="F79" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="G79" s="25"/>
+      <c r="G79" s="53" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="80" ht="15.75" spans="1:7">
       <c r="A80" s="22">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C80" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F80" s="32" t="s">
-        <v>203</v>
-      </c>
-      <c r="G80" s="53" t="s">
         <v>204</v>
+      </c>
+      <c r="G80" s="25" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="81" ht="15.75" spans="1:7">
       <c r="A81" s="22">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C81" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E81" s="22" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F81" s="32" t="s">
-        <v>206</v>
-      </c>
-      <c r="G81" s="25" t="s">
         <v>207</v>
       </c>
+      <c r="G81" s="25"/>
     </row>
     <row r="82" ht="15.75" spans="1:7">
       <c r="A82" s="22">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" s="23" t="s">
         <v>208</v>
@@ -4276,63 +4270,61 @@
         <v>8</v>
       </c>
       <c r="D82" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E82" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="F82" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E82" s="22"/>
+      <c r="F82" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="G82" s="25"/>
+      <c r="G82" s="25" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="83" ht="15.75" spans="1:7">
       <c r="A83" s="22">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C83" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E83" s="22"/>
-      <c r="F83" s="24" t="s">
-        <v>211</v>
+        <v>125</v>
+      </c>
+      <c r="E83" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F83" s="32" t="s">
+        <v>212</v>
       </c>
       <c r="G83" s="25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:7">
       <c r="A84" s="22">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C84" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E84" s="22" t="s">
-        <v>128</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E84" s="31"/>
       <c r="F84" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="G84" s="25" t="s">
         <v>215</v>
       </c>
+      <c r="G84" s="25"/>
     </row>
     <row r="85" ht="15.75" spans="1:7">
       <c r="A85" s="22">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B85" s="23" t="s">
         <v>216</v>
@@ -4341,40 +4333,40 @@
         <v>8</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E85" s="31"/>
-      <c r="F85" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E85" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F85" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="G85" s="25"/>
+      <c r="G85" s="25" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="86" ht="15.75" spans="1:7">
       <c r="A86" s="22">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C86" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D86" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E86" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="F86" s="43" t="s">
-        <v>219</v>
-      </c>
-      <c r="G86" s="25" t="s">
+      <c r="D86" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" s="31"/>
+      <c r="F86" s="32" t="s">
         <v>220</v>
       </c>
+      <c r="G86" s="25"/>
     </row>
     <row r="87" ht="15.75" spans="1:7">
       <c r="A87" s="22">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" s="23" t="s">
         <v>221</v>
@@ -4382,320 +4374,320 @@
       <c r="C87" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D87" s="28" t="s">
-        <v>127</v>
+      <c r="D87" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="E87" s="31"/>
       <c r="F87" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="G87" s="25"/>
+      <c r="G87" s="25" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="88" ht="15.75" spans="1:7">
       <c r="A88" s="22">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C88" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E88" s="31"/>
+        <v>125</v>
+      </c>
+      <c r="E88" s="35"/>
       <c r="F88" s="32" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G88" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89" ht="15.75" spans="1:7">
       <c r="A89" s="22">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C89" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E89" s="35"/>
+        <v>125</v>
+      </c>
+      <c r="E89" s="22"/>
       <c r="F89" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="G89" s="25" t="s">
         <v>228</v>
+      </c>
+      <c r="G89" s="53" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="90" ht="15.75" spans="1:7">
       <c r="A90" s="22">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C90" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E90" s="22"/>
+        <v>125</v>
+      </c>
+      <c r="E90" s="22" t="s">
+        <v>138</v>
+      </c>
       <c r="F90" s="32" t="s">
-        <v>230</v>
-      </c>
-      <c r="G90" s="53" t="s">
         <v>231</v>
+      </c>
+      <c r="G90" s="25" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="91" ht="15.75" spans="1:7">
       <c r="A91" s="22">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C91" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E91" s="22" t="s">
-        <v>140</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E91" s="22"/>
       <c r="F91" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="G91" s="25" t="s">
         <v>234</v>
+      </c>
+      <c r="G91" s="53" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="92" ht="15.75" spans="1:7">
       <c r="A92" s="22">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C92" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E92" s="22"/>
+        <v>125</v>
+      </c>
+      <c r="E92" s="22" t="s">
+        <v>237</v>
+      </c>
       <c r="F92" s="32" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G92" s="53" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" ht="15.75" spans="1:7">
       <c r="A93" s="22">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" s="23" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C93" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E93" s="22" t="s">
-        <v>239</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E93" s="22"/>
       <c r="F93" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="G93" s="53" t="s">
         <v>241</v>
+      </c>
+      <c r="G93" s="25" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="94" ht="15.75" spans="1:7">
       <c r="A94" s="22">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" s="23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C94" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E94" s="22"/>
-      <c r="F94" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="G94" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E94" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F94" s="43" t="s">
         <v>244</v>
+      </c>
+      <c r="G94" s="53" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="95" ht="15.75" spans="1:7">
       <c r="A95" s="22">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" s="23" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C95" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E95" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="F95" s="43" t="s">
-        <v>246</v>
-      </c>
-      <c r="G95" s="53" t="s">
+        <v>125</v>
+      </c>
+      <c r="E95" s="22"/>
+      <c r="F95" s="32" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="96" ht="15.75" spans="1:7">
+      <c r="G95" s="25" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="96" ht="31.5" spans="1:7">
       <c r="A96" s="22">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C96" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D96" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E96" s="22"/>
+      <c r="D96" s="28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E96" s="22" t="s">
+        <v>250</v>
+      </c>
       <c r="F96" s="32" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G96" s="25" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="97" ht="31.5" spans="1:7">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" spans="1:7">
       <c r="A97" s="22">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B97" s="23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C97" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D97" s="28" t="s">
-        <v>127</v>
+      <c r="D97" s="22" t="s">
+        <v>125</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>252</v>
+        <v>138</v>
       </c>
       <c r="F97" s="32" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G97" s="25" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" ht="15.75" spans="1:7">
       <c r="A98" s="22">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B98" s="23" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C98" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E98" s="22" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F98" s="32" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G98" s="25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="99" ht="15.75" spans="1:7">
       <c r="A99" s="22">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C99" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E99" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="F99" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="G99" s="25" t="s">
-        <v>260</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E99" s="22"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="25"/>
     </row>
     <row r="100" ht="15.75" spans="1:7">
       <c r="A100" s="22">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E100" s="35"/>
+      <c r="F100" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="C100" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E100" s="22"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="25"/>
+      <c r="G100" s="25" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="101" ht="15.75" spans="1:7">
       <c r="A101" s="22">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C101" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E101" s="35"/>
+        <v>125</v>
+      </c>
+      <c r="E101" s="31"/>
       <c r="F101" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="G101" s="25" t="s">
         <v>264</v>
       </c>
+      <c r="G101" s="25"/>
     </row>
     <row r="102" ht="15.75" spans="1:7">
       <c r="A102" s="22">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B102" s="23" t="s">
         <v>265</v>
@@ -4704,126 +4696,126 @@
         <v>8</v>
       </c>
       <c r="D102" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E102" s="31"/>
-      <c r="F102" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="E102" s="35"/>
+      <c r="F102" s="32" t="s">
         <v>266</v>
       </c>
-      <c r="G102" s="25"/>
+      <c r="G102" s="25" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="103" ht="15.75" spans="1:7">
       <c r="A103" s="22">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" s="23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C103" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E103" s="35"/>
+        <v>125</v>
+      </c>
+      <c r="E103" s="22" t="s">
+        <v>134</v>
+      </c>
       <c r="F103" s="32" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G103" s="25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" ht="15.75" spans="1:7">
       <c r="A104" s="22">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B104" s="23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C104" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E104" s="22" t="s">
-        <v>136</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E104" s="35"/>
       <c r="F104" s="32" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G104" s="25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" ht="15.75" spans="1:7">
       <c r="A105" s="22">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B105" s="23" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C105" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E105" s="35"/>
+        <v>125</v>
+      </c>
+      <c r="E105" s="22" t="s">
+        <v>138</v>
+      </c>
       <c r="F105" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="G105" s="25" t="s">
         <v>275</v>
+      </c>
+      <c r="G105" s="54" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="106" ht="15.75" spans="1:7">
       <c r="A106" s="22">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B106" s="23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C106" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E106" s="22" t="s">
-        <v>140</v>
+        <v>278</v>
       </c>
       <c r="F106" s="32" t="s">
-        <v>277</v>
-      </c>
-      <c r="G106" s="54" t="s">
-        <v>278</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="G106" s="25"/>
     </row>
     <row r="107" ht="15.75" spans="1:7">
       <c r="A107" s="22">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B107" s="23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C107" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D107" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="E107" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="F107" s="32" t="s">
+      <c r="D107" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="E107" s="45"/>
+      <c r="F107" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="G107" s="25"/>
+      <c r="G107" s="27"/>
     </row>
     <row r="108" ht="15.75" spans="1:7">
       <c r="A108" s="22">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B108" s="23" t="s">
         <v>282</v>
@@ -4832,7 +4824,7 @@
         <v>8</v>
       </c>
       <c r="D108" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E108" s="45"/>
       <c r="F108" s="46" t="s">
@@ -4840,9 +4832,9 @@
       </c>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" ht="15.75" spans="1:7">
+    <row r="109" ht="31.5" spans="1:7">
       <c r="A109" s="22">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B109" s="23" t="s">
         <v>284</v>
@@ -4851,7 +4843,7 @@
         <v>8</v>
       </c>
       <c r="D109" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E109" s="45"/>
       <c r="F109" s="46" t="s">
@@ -4859,9 +4851,9 @@
       </c>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" ht="31.5" spans="1:7">
+    <row r="110" ht="15.75" spans="1:7">
       <c r="A110" s="22">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B110" s="23" t="s">
         <v>286</v>
@@ -4870,7 +4862,7 @@
         <v>8</v>
       </c>
       <c r="D110" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E110" s="45"/>
       <c r="F110" s="46" t="s">
@@ -4878,9 +4870,9 @@
       </c>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" ht="15.75" spans="1:7">
+    <row r="111" ht="31.5" spans="1:7">
       <c r="A111" s="22">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B111" s="23" t="s">
         <v>288</v>
@@ -4889,7 +4881,7 @@
         <v>8</v>
       </c>
       <c r="D111" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E111" s="45"/>
       <c r="F111" s="46" t="s">
@@ -4897,9 +4889,9 @@
       </c>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" ht="31.5" spans="1:7">
+    <row r="112" ht="15.75" spans="1:7">
       <c r="A112" s="22">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B112" s="23" t="s">
         <v>290</v>
@@ -4908,7 +4900,7 @@
         <v>8</v>
       </c>
       <c r="D112" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E112" s="45"/>
       <c r="F112" s="46" t="s">
@@ -4918,7 +4910,7 @@
     </row>
     <row r="113" ht="15.75" spans="1:7">
       <c r="A113" s="22">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B113" s="23" t="s">
         <v>292</v>
@@ -4927,36 +4919,36 @@
         <v>8</v>
       </c>
       <c r="D113" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E113" s="45"/>
       <c r="F113" s="46" t="s">
+        <v>275</v>
+      </c>
+      <c r="G113" s="27"/>
+    </row>
+    <row r="114" s="15" customFormat="1" ht="15.75" spans="1:7">
+      <c r="A114" s="22">
+        <v>114</v>
+      </c>
+      <c r="B114" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="G113" s="27"/>
-    </row>
-    <row r="114" ht="15.75" spans="1:7">
-      <c r="A114" s="22">
-        <v>113</v>
-      </c>
-      <c r="B114" s="23" t="s">
+      <c r="C114" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="E114" s="45"/>
+      <c r="F114" s="47" t="s">
         <v>294</v>
       </c>
-      <c r="C114" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E114" s="45"/>
-      <c r="F114" s="46" t="s">
-        <v>277</v>
-      </c>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" s="15" customFormat="1" ht="15.75" spans="1:7">
+    <row r="115" ht="15.75" spans="1:7">
       <c r="A115" s="22">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B115" s="23" t="s">
         <v>295</v>
@@ -4965,17 +4957,19 @@
         <v>8</v>
       </c>
       <c r="D115" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E115" s="45"/>
-      <c r="F115" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="E115" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="F115" s="46" t="s">
         <v>296</v>
       </c>
       <c r="G115" s="27"/>
     </row>
     <row r="116" ht="15.75" spans="1:7">
       <c r="A116" s="22">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B116" s="23" t="s">
         <v>297</v>
@@ -4984,11 +4978,9 @@
         <v>8</v>
       </c>
       <c r="D116" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E116" s="44" t="s">
-        <v>140</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E116" s="45"/>
       <c r="F116" s="46" t="s">
         <v>298</v>
       </c>
@@ -4996,7 +4988,7 @@
     </row>
     <row r="117" ht="15.75" spans="1:7">
       <c r="A117" s="22">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B117" s="23" t="s">
         <v>299</v>
@@ -5005,7 +4997,7 @@
         <v>8</v>
       </c>
       <c r="D117" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E117" s="45"/>
       <c r="F117" s="46" t="s">
@@ -5015,7 +5007,7 @@
     </row>
     <row r="118" ht="15.75" spans="1:7">
       <c r="A118" s="22">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B118" s="23" t="s">
         <v>301</v>
@@ -5024,7 +5016,7 @@
         <v>8</v>
       </c>
       <c r="D118" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E118" s="45"/>
       <c r="F118" s="46" t="s">
@@ -5034,7 +5026,7 @@
     </row>
     <row r="119" ht="15.75" spans="1:7">
       <c r="A119" s="22">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B119" s="23" t="s">
         <v>303</v>
@@ -5043,7 +5035,7 @@
         <v>8</v>
       </c>
       <c r="D119" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E119" s="45"/>
       <c r="F119" s="46" t="s">
@@ -5053,7 +5045,7 @@
     </row>
     <row r="120" ht="15.75" spans="1:7">
       <c r="A120" s="22">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B120" s="23" t="s">
         <v>305</v>
@@ -5062,7 +5054,7 @@
         <v>8</v>
       </c>
       <c r="D120" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E120" s="45"/>
       <c r="F120" s="46" t="s">
@@ -5072,7 +5064,7 @@
     </row>
     <row r="121" ht="15.75" spans="1:7">
       <c r="A121" s="22">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B121" s="23" t="s">
         <v>307</v>
@@ -5081,7 +5073,7 @@
         <v>8</v>
       </c>
       <c r="D121" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E121" s="45"/>
       <c r="F121" s="46" t="s">
@@ -5091,7 +5083,7 @@
     </row>
     <row r="122" ht="15.75" spans="1:7">
       <c r="A122" s="22">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B122" s="23" t="s">
         <v>309</v>
@@ -5100,17 +5092,17 @@
         <v>8</v>
       </c>
       <c r="D122" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E122" s="45"/>
       <c r="F122" s="46" t="s">
         <v>310</v>
       </c>
-      <c r="G122" s="27"/>
+      <c r="G122" s="48"/>
     </row>
     <row r="123" ht="15.75" spans="1:7">
       <c r="A123" s="22">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B123" s="23" t="s">
         <v>311</v>
@@ -5119,17 +5111,17 @@
         <v>8</v>
       </c>
       <c r="D123" s="44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E123" s="45"/>
       <c r="F123" s="46" t="s">
         <v>312</v>
       </c>
-      <c r="G123" s="48"/>
+      <c r="G123" s="27"/>
     </row>
     <row r="124" ht="15.75" spans="1:7">
       <c r="A124" s="22">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B124" s="23" t="s">
         <v>313</v>
@@ -5138,17 +5130,19 @@
         <v>8</v>
       </c>
       <c r="D124" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E124" s="45"/>
+        <v>125</v>
+      </c>
+      <c r="E124" s="44" t="s">
+        <v>10</v>
+      </c>
       <c r="F124" s="46" t="s">
         <v>314</v>
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" ht="15.75" spans="1:7">
+    <row r="125" ht="31.5" spans="1:7">
       <c r="A125" s="22">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B125" s="23" t="s">
         <v>315</v>
@@ -5157,32 +5151,30 @@
         <v>8</v>
       </c>
       <c r="D125" s="44" t="s">
-        <v>127</v>
+        <v>316</v>
       </c>
       <c r="E125" s="44" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F125" s="46" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" ht="31.5" spans="1:7">
+    <row r="126" ht="15.75" spans="1:7">
       <c r="A126" s="22">
+        <v>126</v>
+      </c>
+      <c r="B126" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="B126" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="C126" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="44" t="s">
-        <v>318</v>
-      </c>
-      <c r="E126" s="44" t="s">
-        <v>29</v>
-      </c>
+      <c r="E126" s="45"/>
       <c r="F126" s="46" t="s">
         <v>319</v>
       </c>
@@ -5190,7 +5182,7 @@
     </row>
     <row r="127" ht="15.75" spans="1:7">
       <c r="A127" s="22">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B127" s="23" t="s">
         <v>320</v>
@@ -5199,9 +5191,11 @@
         <v>8</v>
       </c>
       <c r="D127" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="E127" s="45"/>
+        <v>9</v>
+      </c>
+      <c r="E127" s="45" t="s">
+        <v>29</v>
+      </c>
       <c r="F127" s="46" t="s">
         <v>321</v>
       </c>
@@ -5209,7 +5203,7 @@
     </row>
     <row r="128" ht="15.75" spans="1:7">
       <c r="A128" s="22">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B128" s="23" t="s">
         <v>322</v>
@@ -5230,7 +5224,7 @@
     </row>
     <row r="129" ht="15.75" spans="1:7">
       <c r="A129" s="22">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B129" s="23" t="s">
         <v>324</v>
@@ -5242,131 +5236,130 @@
         <v>9</v>
       </c>
       <c r="E129" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="F129" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="G129" s="27"/>
+      <c r="G129" s="53" t="s">
+        <v>326</v>
+      </c>
     </row>
     <row r="130" ht="15.75" spans="1:7">
       <c r="A130" s="22">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B130" s="23" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C130" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D130" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F130" s="49" t="s">
-        <v>327</v>
-      </c>
-      <c r="G130" s="53" t="s">
+      <c r="D130" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E130" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F130" s="50" t="s">
         <v>328</v>
+      </c>
+      <c r="G130" s="55" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="131" ht="15.75" spans="1:7">
       <c r="A131" s="22">
-        <v>130</v>
-      </c>
-      <c r="B131" s="23" t="s">
-        <v>329</v>
+        <v>131</v>
+      </c>
+      <c r="B131" s="17" t="s">
+        <v>330</v>
       </c>
       <c r="C131" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="E131" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F131" s="50" t="s">
-        <v>330</v>
+        <v>29</v>
+      </c>
+      <c r="F131" s="17" t="s">
+        <v>331</v>
       </c>
       <c r="G131" s="55" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="132" ht="15.75" spans="1:7">
       <c r="A132" s="22">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="16" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="E132" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F132" s="17" t="s">
-        <v>333</v>
+        <v>134</v>
+      </c>
+      <c r="F132" s="50" t="s">
+        <v>334</v>
       </c>
       <c r="G132" s="55" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="133" ht="15.75" spans="1:7">
       <c r="A133" s="22">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>335</v>
+        <v>311</v>
       </c>
       <c r="C133" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E133" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F133" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="G133" s="55" t="s">
         <v>336</v>
-      </c>
-      <c r="G133" s="55" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:7">
       <c r="A134" s="22">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C134" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="16" t="s">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="E134" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F134" s="50" t="s">
-        <v>314</v>
-      </c>
-      <c r="G134" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F134" s="17" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="135" ht="15.75" spans="1:7">
       <c r="A135" s="22">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B135" s="17" t="s">
         <v>339</v>
@@ -5375,169 +5368,152 @@
         <v>8</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="E135" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F135" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F135" s="50" t="s">
         <v>340</v>
+      </c>
+      <c r="G135" s="50" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="136" ht="15.75" spans="1:7">
       <c r="A136" s="22">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C136" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D136" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E136" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F136" s="50" t="s">
-        <v>342</v>
-      </c>
-      <c r="G136" s="50" t="s">
         <v>343</v>
+      </c>
+      <c r="G136" s="55" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="137" ht="15.75" spans="1:7">
       <c r="A137" s="22">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C137" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E137" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F137" s="50" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G137" s="55" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="138" ht="15.75" spans="1:7">
       <c r="A138" s="22">
-        <v>137</v>
-      </c>
-      <c r="B138" s="17" t="s">
-        <v>347</v>
+        <v>138</v>
+      </c>
+      <c r="B138" s="23" t="s">
+        <v>348</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F138" s="50" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G138" s="55" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="139" ht="15.75" spans="1:7">
       <c r="A139" s="22">
-        <v>138</v>
-      </c>
-      <c r="B139" s="23" t="s">
-        <v>350</v>
+        <v>139</v>
+      </c>
+      <c r="B139" s="17" t="s">
+        <v>351</v>
       </c>
       <c r="C139" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="E139" s="16" t="s">
-        <v>136</v>
+        <v>352</v>
       </c>
       <c r="F139" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="G139" s="55" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="140" ht="15.75" spans="1:7">
       <c r="A140" s="22">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C140" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="16" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="F140" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="F140" s="51" t="s">
         <v>355</v>
+      </c>
+      <c r="G140" s="56" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="141" ht="15.75" spans="1:7">
       <c r="A141" s="22">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C141" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E141" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="F141" s="51" t="s">
-        <v>357</v>
-      </c>
-      <c r="G141" s="56" t="s">
+        <v>237</v>
+      </c>
+      <c r="F141" s="52" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="142" ht="15.75" spans="1:7">
-      <c r="A142" s="22">
-        <v>141</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="C142" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E142" s="16" t="s">
-        <v>239</v>
-      </c>
-      <c r="F142" s="52" t="s">
-        <v>360</v>
-      </c>
+    <row r="142" spans="1:7">
+      <c r="D142" s="17"/>
     </row>
     <row r="143" spans="1:7">
       <c r="D143" s="17"/>
@@ -8611,62 +8587,59 @@
     <row r="1166" spans="4:4">
       <c r="D1166" s="17"/>
     </row>
-    <row r="1167" spans="4:4">
-      <c r="D1167" s="17"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G142" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G141" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
     <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
-    <hyperlink ref="F55" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
-    <hyperlink ref="F108" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
-    <hyperlink ref="F109" r:id="rId5" display="aliaissani97@gmail.com"/>
-    <hyperlink ref="F127" r:id="rId6" display="medzerdani@gmail.com"/>
-    <hyperlink ref="F124" r:id="rId7" display="turkibilal22@gmail.com"/>
-    <hyperlink ref="F123" r:id="rId8" display="sacihamza40@gmail.com"/>
-    <hyperlink ref="F122" r:id="rId9" display="Boba1620@hotmail.com"/>
-    <hyperlink ref="F98" r:id="rId10" display="khelifa-mir@outlook.fr"/>
-    <hyperlink ref="F79" r:id="rId11" display="fethi22miloua@gmail.com"/>
-    <hyperlink ref="F77" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
-    <hyperlink ref="F96" r:id="rId13" display="mehadjiameslem@gmail.com"/>
-    <hyperlink ref="F94" r:id="rId14" display="mekhalefleila@gmail.com"/>
-    <hyperlink ref="F93" r:id="rId15" display="khalidamet4@gmail.com"/>
-    <hyperlink ref="F121" r:id="rId16" display="layatimedi@gmail.com"/>
-    <hyperlink ref="F88" r:id="rId17" display="m_latreche@yahoo.com"/>
-    <hyperlink ref="F120" r:id="rId18" display="kadrirania51@gmail.com"/>
-    <hyperlink ref="F84" r:id="rId19" display="protoboy9999@gmail.com"/>
-    <hyperlink ref="F118" r:id="rId20" display="khadidjafezazi90@gmail"/>
-    <hyperlink ref="F78" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F75" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
-    <hyperlink ref="F70" r:id="rId23" display="douaaboularaf@gmail.com"/>
-    <hyperlink ref="F114" r:id="rId24" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F64" r:id="rId25" display="rawnakritedj@gmail.com" tooltip="mailto:rawnakritedj@gmail.com"/>
-    <hyperlink ref="F112" r:id="rId26" display="bkbhbb22@gmail.com"/>
-    <hyperlink ref="F61" r:id="rId27" display="bendida65@gmail.com"/>
-    <hyperlink ref="F60" r:id="rId28" display="sarrabencella@gmail.com"/>
-    <hyperlink ref="F62" r:id="rId29" display="ri123hab@gmail.com"/>
-    <hyperlink ref="F111" r:id="rId30" display="meriembelabed5@gmail.com"/>
-    <hyperlink ref="F46" r:id="rId31" display="rezoug.med@gmail.com"/>
-    <hyperlink ref="F87" r:id="rId32" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
-    <hyperlink ref="F59" r:id="rId33" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
-    <hyperlink ref="F103" r:id="rId34" display="zarebmohammedamine@gmail.com"/>
-    <hyperlink ref="F104" r:id="rId35" display="djamel71ziani@gmail.com"/>
-    <hyperlink ref="F68" r:id="rId36" display="ahmedboudali32@gmail.com"/>
-    <hyperlink ref="F72" r:id="rId37" display="chaouche.abdallah@gmail.com"/>
-    <hyperlink ref="F63" r:id="rId38" display="lakhdar_belhallouche@hotmail.fr"/>
-    <hyperlink ref="F83" r:id="rId39" display="ahmed.hadji22@yahoo.com"/>
-    <hyperlink ref="F106" r:id="rId40" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F54" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
+    <hyperlink ref="F107" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
+    <hyperlink ref="F108" r:id="rId5" display="aliaissani97@gmail.com"/>
+    <hyperlink ref="F126" r:id="rId6" display="medzerdani@gmail.com"/>
+    <hyperlink ref="F123" r:id="rId7" display="turkibilal22@gmail.com"/>
+    <hyperlink ref="F122" r:id="rId8" display="sacihamza40@gmail.com"/>
+    <hyperlink ref="F121" r:id="rId9" display="Boba1620@hotmail.com"/>
+    <hyperlink ref="F97" r:id="rId10" display="khelifa-mir@outlook.fr"/>
+    <hyperlink ref="F78" r:id="rId11" display="fethi22miloua@gmail.com"/>
+    <hyperlink ref="F76" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
+    <hyperlink ref="F95" r:id="rId13" display="mehadjiameslem@gmail.com"/>
+    <hyperlink ref="F93" r:id="rId14" display="mekhalefleila@gmail.com"/>
+    <hyperlink ref="F92" r:id="rId15" display="khalidamet4@gmail.com"/>
+    <hyperlink ref="F120" r:id="rId16" display="layatimedi@gmail.com"/>
+    <hyperlink ref="F87" r:id="rId17" display="m_latreche@yahoo.com"/>
+    <hyperlink ref="F119" r:id="rId18" display="kadrirania51@gmail.com"/>
+    <hyperlink ref="F83" r:id="rId19" display="protoboy9999@gmail.com"/>
+    <hyperlink ref="F117" r:id="rId20" display="khadidjafezazi90@gmail"/>
+    <hyperlink ref="F77" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F74" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F69" r:id="rId23" display="douaaboularaf@gmail.com"/>
+    <hyperlink ref="F113" r:id="rId24" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F63" r:id="rId25" display="rawnakritedj@gmail.com" tooltip="mailto:rawnakritedj@gmail.com"/>
+    <hyperlink ref="F111" r:id="rId26" display="bkbhbb22@gmail.com"/>
+    <hyperlink ref="F60" r:id="rId27" display="bendida65@gmail.com"/>
+    <hyperlink ref="F59" r:id="rId28" display="sarrabencella@gmail.com"/>
+    <hyperlink ref="F61" r:id="rId29" display="ri123hab@gmail.com"/>
+    <hyperlink ref="F110" r:id="rId30" display="meriembelabed5@gmail.com"/>
+    <hyperlink ref="F45" r:id="rId31" display="rezoug.med@gmail.com"/>
+    <hyperlink ref="F86" r:id="rId32" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
+    <hyperlink ref="F58" r:id="rId33" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
+    <hyperlink ref="F102" r:id="rId34" display="zarebmohammedamine@gmail.com"/>
+    <hyperlink ref="F103" r:id="rId35" display="djamel71ziani@gmail.com"/>
+    <hyperlink ref="F67" r:id="rId36" display="ahmedboudali32@gmail.com"/>
+    <hyperlink ref="F71" r:id="rId37" display="chaouche.abdallah@gmail.com"/>
+    <hyperlink ref="F62" r:id="rId38" display="lakhdar_belhallouche@hotmail.fr"/>
+    <hyperlink ref="F82" r:id="rId39" display="ahmed.hadji22@yahoo.com"/>
+    <hyperlink ref="F105" r:id="rId40" display="berhenen@yahoo.fr"/>
     <hyperlink ref="F32" r:id="rId41" display="khatir.mohamed1977@gmail.com"/>
     <hyperlink ref="F2" r:id="rId42" display="irecom_abid@yahoo.fr"/>
     <hyperlink ref="F7" r:id="rId43" display="karis483@hotmail.fr"/>
     <hyperlink ref="F8" r:id="rId44" display="bahlilmounir@yahoo.fr"/>
     <hyperlink ref="F10" r:id="rId45" display="beddadboucif@gmail.com"/>
     <hyperlink ref="F9" r:id="rId46" display="seyfeddine.electrotechnique@gmail.com"/>
-    <hyperlink ref="F130" r:id="rId47" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
-    <hyperlink ref="F115" r:id="rId48" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F129" r:id="rId47" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F114" r:id="rId48" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8689,202 +8662,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>362</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D2" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>372</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>379</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>383</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="399">
   <si>
     <t>N°</t>
   </si>
@@ -1109,6 +1109,12 @@
   </si>
   <si>
     <t>mekhfikhalida87@gmail.com</t>
+  </si>
+  <si>
+    <t>ZATLA HICHEM</t>
+  </si>
+  <si>
+    <t>hicham.zatla@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -5512,8 +5518,25 @@
         <v>358</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
-      <c r="D142" s="17"/>
+    <row r="142" ht="15.75" spans="1:7">
+      <c r="A142" s="22">
+        <v>142</v>
+      </c>
+      <c r="B142" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="C142" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142" s="52" t="s">
+        <v>360</v>
+      </c>
     </row>
     <row r="143" spans="1:7">
       <c r="D143" s="17"/>
@@ -8662,202 +8685,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>371</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>371</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$142</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="399">
   <si>
     <t>N°</t>
   </si>
@@ -5538,8 +5538,28 @@
         <v>360</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
-      <c r="D143" s="17"/>
+    <row r="143" ht="31.5" spans="1:7">
+      <c r="A143" s="22">
+        <v>143</v>
+      </c>
+      <c r="B143" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C143" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E143" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F143" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="G143" s="25" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="144" spans="1:7">
       <c r="D144" s="17"/>
@@ -8611,7 +8631,7 @@
       <c r="D1166" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G141" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G142" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8663,6 +8683,7 @@
     <hyperlink ref="F9" r:id="rId46" display="seyfeddine.electrotechnique@gmail.com"/>
     <hyperlink ref="F129" r:id="rId47" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
     <hyperlink ref="F114" r:id="rId48" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F143" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1027,7 +1027,7 @@
     <t>SEMMAK ABDELKADER</t>
   </si>
   <si>
-    <t>abdelkader_semmak@hotmail.fr</t>
+    <t>semmak.abdelkader@outlook.com</t>
   </si>
   <si>
     <t>0772111809</t>
@@ -2021,7 +2021,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2161,6 +2161,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2518,8 +2519,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G1166"/>
+  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <dimension ref="A1:G1165"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="16" customWidth="1"/>
@@ -2555,7 +2556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" spans="1:7">
+    <row r="2" ht="15.75" hidden="1" spans="1:7">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -2576,7 +2577,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" ht="15.75" spans="1:7">
+    <row r="3" ht="15.75" hidden="1" spans="1:7">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -2597,7 +2598,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" ht="15.75" spans="1:7">
+    <row r="4" ht="15.75" hidden="1" spans="1:7">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -2618,7 +2619,7 @@
       </c>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" ht="15.75" spans="1:7">
+    <row r="5" ht="15.75" hidden="1" spans="1:7">
       <c r="A5" s="22">
         <v>4</v>
       </c>
@@ -2639,7 +2640,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" ht="15.75" spans="1:7">
+    <row r="6" ht="15.75" hidden="1" spans="1:7">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -2660,7 +2661,7 @@
       </c>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" ht="15.75" spans="1:7">
+    <row r="7" ht="15.75" hidden="1" spans="1:7">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -2679,11 +2680,11 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="53" t="s">
+      <c r="G7" s="54" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:7">
+    <row r="8" ht="15.75" hidden="1" spans="1:7">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -2702,11 +2703,11 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="53" t="s">
+      <c r="G8" s="54" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:7">
+    <row r="9" ht="15.75" hidden="1" spans="1:7">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -2727,7 +2728,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" ht="15.75" spans="1:7">
+    <row r="10" ht="15.75" hidden="1" spans="1:7">
       <c r="A10" s="22">
         <v>9</v>
       </c>
@@ -2746,11 +2747,11 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="53" t="s">
+      <c r="G10" s="54" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" spans="1:7">
+    <row r="11" ht="15.75" hidden="1" spans="1:7">
       <c r="A11" s="22">
         <v>10</v>
       </c>
@@ -2771,7 +2772,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" ht="15.75" spans="1:7">
+    <row r="12" ht="15.75" hidden="1" spans="1:7">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -2792,7 +2793,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" ht="15.75" spans="1:7">
+    <row r="13" ht="15.75" hidden="1" spans="1:7">
       <c r="A13" s="22">
         <v>12</v>
       </c>
@@ -2813,7 +2814,7 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" ht="15.75" spans="1:7">
+    <row r="14" ht="15.75" hidden="1" spans="1:7">
       <c r="A14" s="22">
         <v>13</v>
       </c>
@@ -2834,7 +2835,7 @@
       </c>
       <c r="G14" s="25"/>
     </row>
-    <row r="15" ht="15.75" spans="1:7">
+    <row r="15" ht="15.75" hidden="1" spans="1:7">
       <c r="A15" s="22">
         <v>14</v>
       </c>
@@ -2855,7 +2856,7 @@
       </c>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" ht="31.5" spans="1:7">
+    <row r="16" ht="31.5" hidden="1" spans="1:7">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -2876,7 +2877,7 @@
       </c>
       <c r="G16" s="25"/>
     </row>
-    <row r="17" ht="15.75" spans="1:7">
+    <row r="17" ht="15.75" hidden="1" spans="1:7">
       <c r="A17" s="22">
         <v>16</v>
       </c>
@@ -2897,7 +2898,7 @@
       </c>
       <c r="G17" s="25"/>
     </row>
-    <row r="18" ht="15.75" spans="1:7">
+    <row r="18" ht="15.75" hidden="1" spans="1:7">
       <c r="A18" s="22">
         <v>17</v>
       </c>
@@ -2918,7 +2919,7 @@
       </c>
       <c r="G18" s="25"/>
     </row>
-    <row r="19" ht="15.75" spans="1:7">
+    <row r="19" ht="15.75" hidden="1" spans="1:7">
       <c r="A19" s="22">
         <v>18</v>
       </c>
@@ -2939,7 +2940,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" ht="31.5" spans="1:7">
+    <row r="20" ht="31.5" hidden="1" spans="1:7">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -2960,7 +2961,7 @@
       </c>
       <c r="G20" s="25"/>
     </row>
-    <row r="21" ht="15.75" spans="1:7">
+    <row r="21" ht="15.75" hidden="1" spans="1:7">
       <c r="A21" s="22">
         <v>20</v>
       </c>
@@ -2981,7 +2982,7 @@
       </c>
       <c r="G21" s="25"/>
     </row>
-    <row r="22" ht="15.75" spans="1:7">
+    <row r="22" ht="15.75" hidden="1" spans="1:7">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -3002,7 +3003,7 @@
       </c>
       <c r="G22" s="25"/>
     </row>
-    <row r="23" ht="15.75" spans="1:7">
+    <row r="23" ht="15.75" hidden="1" spans="1:7">
       <c r="A23" s="22">
         <v>22</v>
       </c>
@@ -3023,7 +3024,7 @@
       </c>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" ht="15.75" spans="1:7">
+    <row r="24" ht="15.75" hidden="1" spans="1:7">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -3044,7 +3045,7 @@
       </c>
       <c r="G24" s="25"/>
     </row>
-    <row r="25" ht="15.75" spans="1:7">
+    <row r="25" ht="15.75" hidden="1" spans="1:7">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -3065,7 +3066,7 @@
       </c>
       <c r="G25" s="25"/>
     </row>
-    <row r="26" ht="31.5" spans="1:7">
+    <row r="26" ht="31.5" hidden="1" spans="1:7">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -3086,7 +3087,7 @@
       </c>
       <c r="G26" s="25"/>
     </row>
-    <row r="27" ht="15.75" spans="1:7">
+    <row r="27" ht="15.75" hidden="1" spans="1:7">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -3107,7 +3108,7 @@
       </c>
       <c r="G27" s="25"/>
     </row>
-    <row r="28" ht="15.75" spans="1:7">
+    <row r="28" ht="15.75" hidden="1" spans="1:7">
       <c r="A28" s="22">
         <v>27</v>
       </c>
@@ -3128,7 +3129,7 @@
       </c>
       <c r="G28" s="25"/>
     </row>
-    <row r="29" ht="15.75" spans="1:7">
+    <row r="29" ht="15.75" hidden="1" spans="1:7">
       <c r="A29" s="22">
         <v>28</v>
       </c>
@@ -3149,7 +3150,7 @@
       </c>
       <c r="G29" s="25"/>
     </row>
-    <row r="30" ht="15.75" spans="1:7">
+    <row r="30" ht="15.75" hidden="1" spans="1:7">
       <c r="A30" s="22">
         <v>29</v>
       </c>
@@ -3170,7 +3171,7 @@
       </c>
       <c r="G30" s="25"/>
     </row>
-    <row r="31" ht="15.75" spans="1:7">
+    <row r="31" ht="15.75" hidden="1" spans="1:7">
       <c r="A31" s="22">
         <v>30</v>
       </c>
@@ -3191,7 +3192,7 @@
       </c>
       <c r="G31" s="25"/>
     </row>
-    <row r="32" ht="15.75" spans="1:7">
+    <row r="32" ht="15.75" hidden="1" spans="1:7">
       <c r="A32" s="22">
         <v>31</v>
       </c>
@@ -3212,7 +3213,7 @@
       </c>
       <c r="G32" s="25"/>
     </row>
-    <row r="33" ht="15.75" spans="1:7">
+    <row r="33" ht="15.75" hidden="1" spans="1:7">
       <c r="A33" s="22">
         <v>32</v>
       </c>
@@ -3233,7 +3234,7 @@
       </c>
       <c r="G33" s="25"/>
     </row>
-    <row r="34" ht="15.75" spans="1:7">
+    <row r="34" ht="15.75" hidden="1" spans="1:7">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -3254,7 +3255,7 @@
       </c>
       <c r="G34" s="25"/>
     </row>
-    <row r="35" ht="15.75" spans="1:7">
+    <row r="35" ht="15.75" hidden="1" spans="1:7">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -3275,7 +3276,7 @@
       </c>
       <c r="G35" s="25"/>
     </row>
-    <row r="36" ht="15.75" spans="1:7">
+    <row r="36" ht="15.75" hidden="1" spans="1:7">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -3294,11 +3295,11 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="54" t="s">
+      <c r="G36" s="55" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="15.75" spans="1:7">
+    <row r="37" ht="15.75" hidden="1" spans="1:7">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -3319,7 +3320,7 @@
       </c>
       <c r="G37" s="25"/>
     </row>
-    <row r="38" ht="15.75" spans="1:7">
+    <row r="38" ht="15.75" hidden="1" spans="1:7">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -3338,11 +3339,11 @@
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="53" t="s">
+      <c r="G38" s="54" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="31.5" spans="1:7">
+    <row r="39" ht="31.5" hidden="1" spans="1:7">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -3363,7 +3364,7 @@
       </c>
       <c r="G39" s="25"/>
     </row>
-    <row r="40" ht="15.75" spans="1:7">
+    <row r="40" ht="15.75" hidden="1" spans="1:7">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -3384,7 +3385,7 @@
       </c>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" ht="15.75" spans="1:7">
+    <row r="41" ht="15.75" hidden="1" spans="1:7">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -3405,7 +3406,7 @@
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" ht="15.75" spans="1:7">
+    <row r="42" ht="15.75" hidden="1" spans="1:7">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -3426,7 +3427,7 @@
       </c>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" ht="15.75" spans="1:7">
+    <row r="43" ht="15.75" hidden="1" spans="1:7">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -3447,7 +3448,7 @@
       </c>
       <c r="G43" s="25"/>
     </row>
-    <row r="44" ht="15.75" spans="1:7">
+    <row r="44" ht="15.75" hidden="1" spans="1:7">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -3468,7 +3469,7 @@
       </c>
       <c r="G44" s="25"/>
     </row>
-    <row r="45" ht="15.75" spans="1:7">
+    <row r="45" ht="15.75" hidden="1" spans="1:7">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -3489,7 +3490,7 @@
       </c>
       <c r="G45" s="25"/>
     </row>
-    <row r="46" ht="15.75" spans="1:7">
+    <row r="46" ht="15.75" hidden="1" spans="1:7">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -3510,7 +3511,7 @@
       </c>
       <c r="G46" s="25"/>
     </row>
-    <row r="47" ht="15.75" spans="1:7">
+    <row r="47" ht="15.75" hidden="1" spans="1:7">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -3531,7 +3532,7 @@
       </c>
       <c r="G47" s="25"/>
     </row>
-    <row r="48" ht="15.75" spans="1:7">
+    <row r="48" ht="15.75" hidden="1" spans="1:7">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -3552,7 +3553,7 @@
       </c>
       <c r="G48" s="25"/>
     </row>
-    <row r="49" ht="15.75" spans="1:7">
+    <row r="49" ht="15.75" hidden="1" spans="1:7">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -3573,7 +3574,7 @@
       </c>
       <c r="G49" s="25"/>
     </row>
-    <row r="50" ht="15.75" spans="1:7">
+    <row r="50" ht="15.75" hidden="1" spans="1:7">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -3594,7 +3595,7 @@
       </c>
       <c r="G50" s="25"/>
     </row>
-    <row r="51" ht="15.75" spans="1:7">
+    <row r="51" ht="15.75" hidden="1" spans="1:7">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -3615,7 +3616,7 @@
       </c>
       <c r="G51" s="25"/>
     </row>
-    <row r="52" ht="15.75" spans="1:7">
+    <row r="52" ht="15.75" hidden="1" spans="1:7">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -3634,11 +3635,11 @@
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="53" t="s">
+      <c r="G52" s="54" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="53" ht="15.75" spans="1:7">
+    <row r="53" ht="15.75" hidden="1" spans="1:7">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -3659,7 +3660,7 @@
       </c>
       <c r="G53" s="25"/>
     </row>
-    <row r="54" ht="15.75" spans="1:7">
+    <row r="54" ht="15.75" hidden="1" spans="1:7">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -3678,11 +3679,11 @@
       <c r="F54" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="53" t="s">
+      <c r="G54" s="54" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="55" ht="15.75" spans="1:7">
+    <row r="55" ht="15.75" hidden="1" spans="1:7">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -3703,7 +3704,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" ht="15.75" spans="1:7">
+    <row r="56" ht="15.75" hidden="1" spans="1:7">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -3720,7 +3721,7 @@
       <c r="F56" s="34"/>
       <c r="G56" s="25"/>
     </row>
-    <row r="57" ht="15.75" spans="1:7">
+    <row r="57" ht="15.75" hidden="1" spans="1:7">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -3743,7 +3744,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" ht="15.75" spans="1:7">
+    <row r="58" ht="15.75" hidden="1" spans="1:7">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -3766,7 +3767,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" ht="15.75" spans="1:7">
+    <row r="59" ht="15.75" hidden="1" spans="1:7">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -3789,7 +3790,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" ht="15.75" spans="1:7">
+    <row r="60" ht="15.75" hidden="1" spans="1:7">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -3812,7 +3813,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" ht="15.75" spans="1:7">
+    <row r="61" ht="15.75" hidden="1" spans="1:7">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -3833,7 +3834,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" ht="31.5" spans="1:7">
+    <row r="62" ht="31.5" hidden="1" spans="1:7">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -3854,7 +3855,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="63" ht="15.75" spans="1:7">
+    <row r="63" ht="15.75" hidden="1" spans="1:7">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -3875,7 +3876,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="64" ht="15.75" spans="1:7">
+    <row r="64" ht="15.75" hidden="1" spans="1:7">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -3894,11 +3895,11 @@
       <c r="F64" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="G64" s="53" t="s">
+      <c r="G64" s="54" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="65" ht="31.5" spans="1:7">
+    <row r="65" ht="31.5" hidden="1" spans="1:7">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -3919,7 +3920,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" ht="15.75" spans="1:7">
+    <row r="66" ht="15.75" hidden="1" spans="1:7">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -3940,7 +3941,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" ht="15.75" spans="1:7">
+    <row r="67" ht="15.75" hidden="1" spans="1:7">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -3957,11 +3958,11 @@
       <c r="F67" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="G67" s="54" t="s">
+      <c r="G67" s="55" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="68" ht="15.75" spans="1:7">
+    <row r="68" ht="15.75" hidden="1" spans="1:7">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -3984,7 +3985,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="69" ht="15.75" spans="1:7">
+    <row r="69" ht="15.75" hidden="1" spans="1:7">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -4001,11 +4002,11 @@
       <c r="F69" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="53" t="s">
+      <c r="G69" s="54" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" ht="15.75" spans="1:7">
+    <row r="70" ht="15.75" hidden="1" spans="1:7">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -4022,11 +4023,11 @@
       <c r="F70" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="53" t="s">
+      <c r="G70" s="54" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="71" ht="31.5" spans="1:7">
+    <row r="71" ht="31.5" hidden="1" spans="1:7">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -4043,11 +4044,11 @@
       <c r="F71" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="53" t="s">
+      <c r="G71" s="54" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="72" ht="15.75" spans="1:7">
+    <row r="72" ht="15.75" hidden="1" spans="1:7">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -4064,11 +4065,11 @@
       <c r="F72" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="53" t="s">
+      <c r="G72" s="54" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="73" ht="15.75" spans="1:7">
+    <row r="73" ht="15.75" hidden="1" spans="1:7">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -4087,11 +4088,11 @@
       <c r="F73" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="G73" s="53" t="s">
+      <c r="G73" s="54" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="74" ht="15.75" spans="1:7">
+    <row r="74" ht="15.75" hidden="1" spans="1:7">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -4112,7 +4113,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="75" ht="15.75" spans="1:7">
+    <row r="75" ht="15.75" hidden="1" spans="1:7">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -4135,7 +4136,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" ht="15.75" spans="1:7">
+    <row r="76" ht="15.75" hidden="1" spans="1:7">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -4152,11 +4153,11 @@
       <c r="F76" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="G76" s="53" t="s">
+      <c r="G76" s="54" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="77" ht="31.5" spans="1:7">
+    <row r="77" ht="31.5" hidden="1" spans="1:7">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -4179,7 +4180,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="78" ht="15.75" spans="1:7">
+    <row r="78" ht="15.75" hidden="1" spans="1:7">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -4198,7 +4199,7 @@
       </c>
       <c r="G78" s="25"/>
     </row>
-    <row r="79" ht="15.75" spans="1:7">
+    <row r="79" ht="15.75" hidden="1" spans="1:7">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -4217,11 +4218,11 @@
       <c r="F79" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="G79" s="53" t="s">
+      <c r="G79" s="54" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="80" ht="15.75" spans="1:7">
+    <row r="80" ht="15.75" hidden="1" spans="1:7">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="81" ht="15.75" spans="1:7">
+    <row r="81" ht="15.75" hidden="1" spans="1:7">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -4265,7 +4266,7 @@
       </c>
       <c r="G81" s="25"/>
     </row>
-    <row r="82" ht="15.75" spans="1:7">
+    <row r="82" ht="15.75" hidden="1" spans="1:7">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -4286,7 +4287,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" ht="15.75" spans="1:7">
+    <row r="83" ht="15.75" hidden="1" spans="1:7">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -4309,7 +4310,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="84" ht="15.75" spans="1:7">
+    <row r="84" ht="15.75" hidden="1" spans="1:7">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -4328,7 +4329,7 @@
       </c>
       <c r="G84" s="25"/>
     </row>
-    <row r="85" ht="15.75" spans="1:7">
+    <row r="85" ht="15.75" hidden="1" spans="1:7">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -4351,7 +4352,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" ht="15.75" spans="1:7">
+    <row r="86" ht="15.75" hidden="1" spans="1:7">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -4370,7 +4371,7 @@
       </c>
       <c r="G86" s="25"/>
     </row>
-    <row r="87" ht="15.75" spans="1:7">
+    <row r="87" ht="15.75" hidden="1" spans="1:7">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -4391,7 +4392,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" ht="15.75" spans="1:7">
+    <row r="88" ht="15.75" hidden="1" spans="1:7">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -4412,7 +4413,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="89" ht="15.75" spans="1:7">
+    <row r="89" ht="15.75" hidden="1" spans="1:7">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -4429,11 +4430,11 @@
       <c r="F89" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="G89" s="53" t="s">
+      <c r="G89" s="54" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="90" ht="15.75" spans="1:7">
+    <row r="90" ht="15.75" hidden="1" spans="1:7">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -4456,7 +4457,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="91" ht="15.75" spans="1:7">
+    <row r="91" ht="15.75" hidden="1" spans="1:7">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -4473,11 +4474,11 @@
       <c r="F91" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="G91" s="53" t="s">
+      <c r="G91" s="54" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="92" ht="15.75" spans="1:7">
+    <row r="92" ht="15.75" hidden="1" spans="1:7">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -4496,11 +4497,11 @@
       <c r="F92" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="G92" s="53" t="s">
+      <c r="G92" s="54" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="93" ht="15.75" spans="1:7">
+    <row r="93" ht="15.75" hidden="1" spans="1:7">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -4521,7 +4522,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="94" ht="15.75" spans="1:7">
+    <row r="94" ht="15.75" hidden="1" spans="1:7">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -4540,11 +4541,11 @@
       <c r="F94" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="G94" s="53" t="s">
+      <c r="G94" s="54" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="95" ht="15.75" spans="1:7">
+    <row r="95" ht="15.75" hidden="1" spans="1:7">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -4565,7 +4566,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="96" ht="31.5" spans="1:7">
+    <row r="96" ht="31.5" hidden="1" spans="1:7">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -4588,7 +4589,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="97" ht="15.75" spans="1:7">
+    <row r="97" ht="15.75" hidden="1" spans="1:7">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -4611,7 +4612,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="98" ht="15.75" spans="1:7">
+    <row r="98" ht="15.75" hidden="1" spans="1:7">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -4634,7 +4635,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="99" ht="15.75" spans="1:7">
+    <row r="99" ht="15.75" hidden="1" spans="1:7">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -4651,7 +4652,7 @@
       <c r="F99" s="32"/>
       <c r="G99" s="25"/>
     </row>
-    <row r="100" ht="15.75" spans="1:7">
+    <row r="100" ht="15.75" hidden="1" spans="1:7">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -4672,7 +4673,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="101" ht="15.75" spans="1:7">
+    <row r="101" ht="15.75" hidden="1" spans="1:7">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -4691,7 +4692,7 @@
       </c>
       <c r="G101" s="25"/>
     </row>
-    <row r="102" ht="15.75" spans="1:7">
+    <row r="102" ht="15.75" hidden="1" spans="1:7">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -4712,7 +4713,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="103" ht="15.75" spans="1:7">
+    <row r="103" ht="15.75" hidden="1" spans="1:7">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -4735,7 +4736,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" ht="15.75" spans="1:7">
+    <row r="104" ht="15.75" hidden="1" spans="1:7">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -4756,7 +4757,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="105" ht="15.75" spans="1:7">
+    <row r="105" ht="15.75" hidden="1" spans="1:7">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -4775,11 +4776,11 @@
       <c r="F105" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="G105" s="54" t="s">
+      <c r="G105" s="55" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="106" ht="15.75" spans="1:7">
+    <row r="106" ht="15.75" hidden="1" spans="1:7">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -4800,7 +4801,7 @@
       </c>
       <c r="G106" s="25"/>
     </row>
-    <row r="107" ht="15.75" spans="1:7">
+    <row r="107" ht="15.75" hidden="1" spans="1:7">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -4819,7 +4820,7 @@
       </c>
       <c r="G107" s="27"/>
     </row>
-    <row r="108" ht="15.75" spans="1:7">
+    <row r="108" ht="15.75" hidden="1" spans="1:7">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -4838,7 +4839,7 @@
       </c>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" ht="31.5" spans="1:7">
+    <row r="109" ht="31.5" hidden="1" spans="1:7">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -4857,7 +4858,7 @@
       </c>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" ht="15.75" spans="1:7">
+    <row r="110" ht="15.75" hidden="1" spans="1:7">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -4876,7 +4877,7 @@
       </c>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" ht="31.5" spans="1:7">
+    <row r="111" ht="31.5" hidden="1" spans="1:7">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -4895,7 +4896,7 @@
       </c>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" ht="15.75" spans="1:7">
+    <row r="112" ht="15.75" hidden="1" spans="1:7">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -4914,7 +4915,7 @@
       </c>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" ht="15.75" spans="1:7">
+    <row r="113" ht="15.75" hidden="1" spans="1:7">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -4933,7 +4934,7 @@
       </c>
       <c r="G113" s="27"/>
     </row>
-    <row r="114" s="15" customFormat="1" ht="15.75" spans="1:7">
+    <row r="114" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -4952,7 +4953,7 @@
       </c>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" ht="15.75" spans="1:7">
+    <row r="115" ht="15.75" hidden="1" spans="1:7">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -4973,7 +4974,7 @@
       </c>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" ht="15.75" spans="1:7">
+    <row r="116" ht="15.75" hidden="1" spans="1:7">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -4992,7 +4993,7 @@
       </c>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" ht="15.75" spans="1:7">
+    <row r="117" ht="15.75" hidden="1" spans="1:7">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -5011,7 +5012,7 @@
       </c>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" ht="15.75" spans="1:7">
+    <row r="118" ht="15.75" hidden="1" spans="1:7">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -5030,7 +5031,7 @@
       </c>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" ht="15.75" spans="1:7">
+    <row r="119" ht="15.75" hidden="1" spans="1:7">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -5049,7 +5050,7 @@
       </c>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" ht="15.75" spans="1:7">
+    <row r="120" ht="15.75" hidden="1" spans="1:7">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -5068,7 +5069,7 @@
       </c>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" ht="15.75" spans="1:7">
+    <row r="121" ht="15.75" hidden="1" spans="1:7">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -5087,7 +5088,7 @@
       </c>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" ht="15.75" spans="1:7">
+    <row r="122" ht="15.75" hidden="1" spans="1:7">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -5106,7 +5107,7 @@
       </c>
       <c r="G122" s="48"/>
     </row>
-    <row r="123" ht="15.75" spans="1:7">
+    <row r="123" ht="15.75" hidden="1" spans="1:7">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -5125,7 +5126,7 @@
       </c>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" ht="15.75" spans="1:7">
+    <row r="124" ht="15.75" hidden="1" spans="1:7">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -5146,7 +5147,7 @@
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" ht="31.5" spans="1:7">
+    <row r="125" ht="31.5" hidden="1" spans="1:7">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -5167,7 +5168,7 @@
       </c>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" ht="15.75" spans="1:7">
+    <row r="126" ht="15.75" hidden="1" spans="1:7">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -5186,7 +5187,7 @@
       </c>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" ht="15.75" spans="1:7">
+    <row r="127" ht="15.75" hidden="1" spans="1:7">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -5207,7 +5208,7 @@
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" ht="15.75" spans="1:7">
+    <row r="128" ht="15.75" hidden="1" spans="1:7">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -5228,7 +5229,7 @@
       </c>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" ht="15.75" spans="1:7">
+    <row r="129" ht="15.75" hidden="1" spans="1:7">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -5247,11 +5248,11 @@
       <c r="F129" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="G129" s="53" t="s">
+      <c r="G129" s="54" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="130" ht="15.75" spans="1:7">
+    <row r="130" ht="15.75" hidden="1" spans="1:7">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -5270,7 +5271,7 @@
       <c r="F130" s="50" t="s">
         <v>328</v>
       </c>
-      <c r="G130" s="55" t="s">
+      <c r="G130" s="56" t="s">
         <v>329</v>
       </c>
     </row>
@@ -5290,14 +5291,14 @@
       <c r="E131" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F131" s="17" t="s">
+      <c r="F131" s="51" t="s">
         <v>331</v>
       </c>
-      <c r="G131" s="55" t="s">
+      <c r="G131" s="56" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="132" ht="15.75" spans="1:7">
+    <row r="132" ht="15.75" hidden="1" spans="1:7">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -5316,11 +5317,11 @@
       <c r="F132" s="50" t="s">
         <v>334</v>
       </c>
-      <c r="G132" s="55" t="s">
+      <c r="G132" s="56" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="133" ht="15.75" spans="1:7">
+    <row r="133" ht="15.75" hidden="1" spans="1:7">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -5339,11 +5340,11 @@
       <c r="F133" s="50" t="s">
         <v>312</v>
       </c>
-      <c r="G133" s="55" t="s">
+      <c r="G133" s="56" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="134" ht="15.75" spans="1:7">
+    <row r="134" ht="15.75" hidden="1" spans="1:7">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -5363,7 +5364,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" ht="15.75" spans="1:7">
+    <row r="135" ht="15.75" hidden="1" spans="1:7">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -5386,7 +5387,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="136" ht="15.75" spans="1:7">
+    <row r="136" ht="15.75" hidden="1" spans="1:7">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -5405,11 +5406,11 @@
       <c r="F136" s="50" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="55" t="s">
+      <c r="G136" s="56" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="137" ht="15.75" spans="1:7">
+    <row r="137" ht="15.75" hidden="1" spans="1:7">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -5428,11 +5429,11 @@
       <c r="F137" s="50" t="s">
         <v>346</v>
       </c>
-      <c r="G137" s="55" t="s">
+      <c r="G137" s="56" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="138" ht="15.75" spans="1:7">
+    <row r="138" ht="15.75" hidden="1" spans="1:7">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -5451,11 +5452,11 @@
       <c r="F138" s="50" t="s">
         <v>349</v>
       </c>
-      <c r="G138" s="55" t="s">
+      <c r="G138" s="56" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="139" ht="15.75" spans="1:7">
+    <row r="139" ht="15.75" hidden="1" spans="1:7">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -5475,7 +5476,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" ht="15.75" spans="1:7">
+    <row r="140" ht="15.75" hidden="1" spans="1:7">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -5491,14 +5492,14 @@
       <c r="E140" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F140" s="51" t="s">
+      <c r="F140" s="52" t="s">
         <v>355</v>
       </c>
-      <c r="G140" s="56" t="s">
+      <c r="G140" s="57" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="141" ht="15.75" spans="1:7">
+    <row r="141" ht="15.75" hidden="1" spans="1:7">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -5514,11 +5515,11 @@
       <c r="E141" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="F141" s="52" t="s">
+      <c r="F141" s="53" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="142" ht="15.75" spans="1:7">
+    <row r="142" ht="15.75" hidden="1" spans="1:7">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -5534,11 +5535,11 @@
       <c r="E142" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F142" s="52" t="s">
+      <c r="F142" s="53" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="143" ht="31.5" spans="1:7">
+    <row r="143" ht="31.5" hidden="1" spans="1:7">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -8627,11 +8628,13 @@
     <row r="1165" spans="4:4">
       <c r="D1165" s="17"/>
     </row>
-    <row r="1166" spans="4:4">
-      <c r="D1166" s="17"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G142" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G143" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="SEMMAK ABDELKADER"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="401">
   <si>
     <t>N°</t>
   </si>
@@ -1115,6 +1115,12 @@
   </si>
   <si>
     <t>hicham.zatla@gmail.com</t>
+  </si>
+  <si>
+    <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>n_benseddik@yahoo.fr</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1241,7 +1247,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1339,6 +1345,13 @@
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Cambria"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1894,13 +1907,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1909,119 +1919,122 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2161,11 +2174,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2519,7 +2533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G1165"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
@@ -2556,7 +2570,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" spans="1:7">
+    <row r="2" ht="15.75" spans="1:7">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -2577,7 +2591,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" ht="15.75" hidden="1" spans="1:7">
+    <row r="3" ht="15.75" spans="1:7">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -2598,7 +2612,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" ht="15.75" hidden="1" spans="1:7">
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -2619,7 +2633,7 @@
       </c>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" ht="15.75" hidden="1" spans="1:7">
+    <row r="5" ht="15.75" spans="1:7">
       <c r="A5" s="22">
         <v>4</v>
       </c>
@@ -2640,7 +2654,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" ht="15.75" hidden="1" spans="1:7">
+    <row r="6" ht="15.75" spans="1:7">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -2661,7 +2675,7 @@
       </c>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" ht="15.75" hidden="1" spans="1:7">
+    <row r="7" ht="15.75" spans="1:7">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -2680,11 +2694,11 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="54" t="s">
+      <c r="G7" s="55" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" hidden="1" spans="1:7">
+    <row r="8" ht="15.75" spans="1:7">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -2703,11 +2717,11 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="55" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" hidden="1" spans="1:7">
+    <row r="9" ht="15.75" spans="1:7">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -2728,7 +2742,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" ht="15.75" hidden="1" spans="1:7">
+    <row r="10" ht="15.75" spans="1:7">
       <c r="A10" s="22">
         <v>9</v>
       </c>
@@ -2747,11 +2761,11 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="55" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" hidden="1" spans="1:7">
+    <row r="11" ht="15.75" spans="1:7">
       <c r="A11" s="22">
         <v>10</v>
       </c>
@@ -2772,7 +2786,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" ht="15.75" hidden="1" spans="1:7">
+    <row r="12" ht="15.75" spans="1:7">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -2793,7 +2807,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" ht="15.75" hidden="1" spans="1:7">
+    <row r="13" ht="15.75" spans="1:7">
       <c r="A13" s="22">
         <v>12</v>
       </c>
@@ -2814,7 +2828,7 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" ht="15.75" hidden="1" spans="1:7">
+    <row r="14" ht="15.75" spans="1:7">
       <c r="A14" s="22">
         <v>13</v>
       </c>
@@ -2835,7 +2849,7 @@
       </c>
       <c r="G14" s="25"/>
     </row>
-    <row r="15" ht="15.75" hidden="1" spans="1:7">
+    <row r="15" ht="15.75" spans="1:7">
       <c r="A15" s="22">
         <v>14</v>
       </c>
@@ -2856,7 +2870,7 @@
       </c>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" ht="31.5" hidden="1" spans="1:7">
+    <row r="16" ht="31.5" spans="1:7">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -2877,7 +2891,7 @@
       </c>
       <c r="G16" s="25"/>
     </row>
-    <row r="17" ht="15.75" hidden="1" spans="1:7">
+    <row r="17" ht="15.75" spans="1:7">
       <c r="A17" s="22">
         <v>16</v>
       </c>
@@ -2898,7 +2912,7 @@
       </c>
       <c r="G17" s="25"/>
     </row>
-    <row r="18" ht="15.75" hidden="1" spans="1:7">
+    <row r="18" ht="15.75" spans="1:7">
       <c r="A18" s="22">
         <v>17</v>
       </c>
@@ -2919,7 +2933,7 @@
       </c>
       <c r="G18" s="25"/>
     </row>
-    <row r="19" ht="15.75" hidden="1" spans="1:7">
+    <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="22">
         <v>18</v>
       </c>
@@ -2940,7 +2954,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" ht="31.5" hidden="1" spans="1:7">
+    <row r="20" ht="31.5" spans="1:7">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -2961,7 +2975,7 @@
       </c>
       <c r="G20" s="25"/>
     </row>
-    <row r="21" ht="15.75" hidden="1" spans="1:7">
+    <row r="21" ht="15.75" spans="1:7">
       <c r="A21" s="22">
         <v>20</v>
       </c>
@@ -2982,7 +2996,7 @@
       </c>
       <c r="G21" s="25"/>
     </row>
-    <row r="22" ht="15.75" hidden="1" spans="1:7">
+    <row r="22" ht="15.75" spans="1:7">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -3003,7 +3017,7 @@
       </c>
       <c r="G22" s="25"/>
     </row>
-    <row r="23" ht="15.75" hidden="1" spans="1:7">
+    <row r="23" ht="15.75" spans="1:7">
       <c r="A23" s="22">
         <v>22</v>
       </c>
@@ -3024,7 +3038,7 @@
       </c>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" ht="15.75" hidden="1" spans="1:7">
+    <row r="24" ht="15.75" spans="1:7">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -3045,7 +3059,7 @@
       </c>
       <c r="G24" s="25"/>
     </row>
-    <row r="25" ht="15.75" hidden="1" spans="1:7">
+    <row r="25" ht="15.75" spans="1:7">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -3066,7 +3080,7 @@
       </c>
       <c r="G25" s="25"/>
     </row>
-    <row r="26" ht="31.5" hidden="1" spans="1:7">
+    <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -3087,7 +3101,7 @@
       </c>
       <c r="G26" s="25"/>
     </row>
-    <row r="27" ht="15.75" hidden="1" spans="1:7">
+    <row r="27" ht="15.75" spans="1:7">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -3108,7 +3122,7 @@
       </c>
       <c r="G27" s="25"/>
     </row>
-    <row r="28" ht="15.75" hidden="1" spans="1:7">
+    <row r="28" ht="15.75" spans="1:7">
       <c r="A28" s="22">
         <v>27</v>
       </c>
@@ -3129,7 +3143,7 @@
       </c>
       <c r="G28" s="25"/>
     </row>
-    <row r="29" ht="15.75" hidden="1" spans="1:7">
+    <row r="29" ht="15.75" spans="1:7">
       <c r="A29" s="22">
         <v>28</v>
       </c>
@@ -3150,7 +3164,7 @@
       </c>
       <c r="G29" s="25"/>
     </row>
-    <row r="30" ht="15.75" hidden="1" spans="1:7">
+    <row r="30" ht="15.75" spans="1:7">
       <c r="A30" s="22">
         <v>29</v>
       </c>
@@ -3171,7 +3185,7 @@
       </c>
       <c r="G30" s="25"/>
     </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
+    <row r="31" ht="15.75" spans="1:7">
       <c r="A31" s="22">
         <v>30</v>
       </c>
@@ -3192,7 +3206,7 @@
       </c>
       <c r="G31" s="25"/>
     </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
+    <row r="32" ht="15.75" spans="1:7">
       <c r="A32" s="22">
         <v>31</v>
       </c>
@@ -3213,7 +3227,7 @@
       </c>
       <c r="G32" s="25"/>
     </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
+    <row r="33" ht="15.75" spans="1:7">
       <c r="A33" s="22">
         <v>32</v>
       </c>
@@ -3234,7 +3248,7 @@
       </c>
       <c r="G33" s="25"/>
     </row>
-    <row r="34" ht="15.75" hidden="1" spans="1:7">
+    <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -3255,7 +3269,7 @@
       </c>
       <c r="G34" s="25"/>
     </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
+    <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -3276,7 +3290,7 @@
       </c>
       <c r="G35" s="25"/>
     </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
+    <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -3295,11 +3309,11 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="55" t="s">
+      <c r="G36" s="56" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -3320,7 +3334,7 @@
       </c>
       <c r="G37" s="25"/>
     </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
+    <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -3339,11 +3353,11 @@
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="54" t="s">
+      <c r="G38" s="55" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="31.5" hidden="1" spans="1:7">
+    <row r="39" ht="31.5" spans="1:7">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -3364,7 +3378,7 @@
       </c>
       <c r="G39" s="25"/>
     </row>
-    <row r="40" ht="15.75" hidden="1" spans="1:7">
+    <row r="40" ht="15.75" spans="1:7">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -3385,7 +3399,7 @@
       </c>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" ht="15.75" hidden="1" spans="1:7">
+    <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -3406,7 +3420,7 @@
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" ht="15.75" hidden="1" spans="1:7">
+    <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -3427,7 +3441,7 @@
       </c>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" ht="15.75" hidden="1" spans="1:7">
+    <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -3448,7 +3462,7 @@
       </c>
       <c r="G43" s="25"/>
     </row>
-    <row r="44" ht="15.75" hidden="1" spans="1:7">
+    <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -3469,7 +3483,7 @@
       </c>
       <c r="G44" s="25"/>
     </row>
-    <row r="45" ht="15.75" hidden="1" spans="1:7">
+    <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -3490,7 +3504,7 @@
       </c>
       <c r="G45" s="25"/>
     </row>
-    <row r="46" ht="15.75" hidden="1" spans="1:7">
+    <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -3511,7 +3525,7 @@
       </c>
       <c r="G46" s="25"/>
     </row>
-    <row r="47" ht="15.75" hidden="1" spans="1:7">
+    <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -3532,7 +3546,7 @@
       </c>
       <c r="G47" s="25"/>
     </row>
-    <row r="48" ht="15.75" hidden="1" spans="1:7">
+    <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -3553,7 +3567,7 @@
       </c>
       <c r="G48" s="25"/>
     </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
+    <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -3574,7 +3588,7 @@
       </c>
       <c r="G49" s="25"/>
     </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
+    <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -3595,7 +3609,7 @@
       </c>
       <c r="G50" s="25"/>
     </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
+    <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -3616,7 +3630,7 @@
       </c>
       <c r="G51" s="25"/>
     </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
+    <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -3635,11 +3649,11 @@
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="54" t="s">
+      <c r="G52" s="55" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
+    <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -3660,7 +3674,7 @@
       </c>
       <c r="G53" s="25"/>
     </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
+    <row r="54" ht="15.75" spans="1:7">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -3679,11 +3693,11 @@
       <c r="F54" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="54" t="s">
+      <c r="G54" s="55" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
+    <row r="55" ht="15.75" spans="1:7">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -3704,7 +3718,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
+    <row r="56" ht="15.75" spans="1:7">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -3721,7 +3735,7 @@
       <c r="F56" s="34"/>
       <c r="G56" s="25"/>
     </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
+    <row r="57" ht="15.75" spans="1:7">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -3744,7 +3758,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
+    <row r="58" ht="15.75" spans="1:7">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -3767,7 +3781,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" ht="15.75" hidden="1" spans="1:7">
+    <row r="59" ht="15.75" spans="1:7">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -3790,7 +3804,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" ht="15.75" hidden="1" spans="1:7">
+    <row r="60" ht="15.75" spans="1:7">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -3813,7 +3827,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" ht="15.75" hidden="1" spans="1:7">
+    <row r="61" ht="15.75" spans="1:7">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -3834,7 +3848,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" ht="31.5" hidden="1" spans="1:7">
+    <row r="62" ht="31.5" spans="1:7">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -3855,7 +3869,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="63" ht="15.75" hidden="1" spans="1:7">
+    <row r="63" ht="15.75" spans="1:7">
       <c r="A63" s="22">
         <v>63</v>
       </c>
@@ -3876,7 +3890,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="64" ht="15.75" hidden="1" spans="1:7">
+    <row r="64" ht="15.75" spans="1:7">
       <c r="A64" s="22">
         <v>64</v>
       </c>
@@ -3895,11 +3909,11 @@
       <c r="F64" s="41" t="s">
         <v>157</v>
       </c>
-      <c r="G64" s="54" t="s">
+      <c r="G64" s="55" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="65" ht="31.5" hidden="1" spans="1:7">
+    <row r="65" ht="31.5" spans="1:7">
       <c r="A65" s="22">
         <v>65</v>
       </c>
@@ -3920,7 +3934,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" ht="15.75" hidden="1" spans="1:7">
+    <row r="66" ht="15.75" spans="1:7">
       <c r="A66" s="22">
         <v>66</v>
       </c>
@@ -3941,7 +3955,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" ht="15.75" hidden="1" spans="1:7">
+    <row r="67" ht="15.75" spans="1:7">
       <c r="A67" s="22">
         <v>67</v>
       </c>
@@ -3958,11 +3972,11 @@
       <c r="F67" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="G67" s="55" t="s">
+      <c r="G67" s="56" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="68" ht="15.75" hidden="1" spans="1:7">
+    <row r="68" ht="15.75" spans="1:7">
       <c r="A68" s="22">
         <v>68</v>
       </c>
@@ -3985,7 +3999,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="69" ht="15.75" hidden="1" spans="1:7">
+    <row r="69" ht="15.75" spans="1:7">
       <c r="A69" s="22">
         <v>69</v>
       </c>
@@ -4002,11 +4016,11 @@
       <c r="F69" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="54" t="s">
+      <c r="G69" s="55" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" ht="15.75" hidden="1" spans="1:7">
+    <row r="70" ht="15.75" spans="1:7">
       <c r="A70" s="22">
         <v>70</v>
       </c>
@@ -4023,11 +4037,11 @@
       <c r="F70" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="54" t="s">
+      <c r="G70" s="55" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="71" ht="31.5" hidden="1" spans="1:7">
+    <row r="71" ht="31.5" spans="1:7">
       <c r="A71" s="22">
         <v>71</v>
       </c>
@@ -4044,11 +4058,11 @@
       <c r="F71" s="39" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="54" t="s">
+      <c r="G71" s="55" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="72" ht="15.75" hidden="1" spans="1:7">
+    <row r="72" ht="15.75" spans="1:7">
       <c r="A72" s="22">
         <v>72</v>
       </c>
@@ -4065,11 +4079,11 @@
       <c r="F72" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="54" t="s">
+      <c r="G72" s="55" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="73" ht="15.75" hidden="1" spans="1:7">
+    <row r="73" ht="15.75" spans="1:7">
       <c r="A73" s="22">
         <v>73</v>
       </c>
@@ -4088,11 +4102,11 @@
       <c r="F73" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="G73" s="54" t="s">
+      <c r="G73" s="55" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="74" ht="15.75" hidden="1" spans="1:7">
+    <row r="74" ht="15.75" spans="1:7">
       <c r="A74" s="22">
         <v>74</v>
       </c>
@@ -4113,7 +4127,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="75" ht="15.75" hidden="1" spans="1:7">
+    <row r="75" ht="15.75" spans="1:7">
       <c r="A75" s="22">
         <v>75</v>
       </c>
@@ -4136,7 +4150,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" ht="15.75" hidden="1" spans="1:7">
+    <row r="76" ht="15.75" spans="1:7">
       <c r="A76" s="22">
         <v>76</v>
       </c>
@@ -4153,11 +4167,11 @@
       <c r="F76" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="G76" s="54" t="s">
+      <c r="G76" s="55" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="77" ht="31.5" hidden="1" spans="1:7">
+    <row r="77" ht="31.5" spans="1:7">
       <c r="A77" s="22">
         <v>77</v>
       </c>
@@ -4180,7 +4194,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="78" ht="15.75" hidden="1" spans="1:7">
+    <row r="78" ht="15.75" spans="1:7">
       <c r="A78" s="22">
         <v>78</v>
       </c>
@@ -4199,7 +4213,7 @@
       </c>
       <c r="G78" s="25"/>
     </row>
-    <row r="79" ht="15.75" hidden="1" spans="1:7">
+    <row r="79" ht="15.75" spans="1:7">
       <c r="A79" s="22">
         <v>79</v>
       </c>
@@ -4218,11 +4232,11 @@
       <c r="F79" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="G79" s="54" t="s">
+      <c r="G79" s="55" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="80" ht="15.75" hidden="1" spans="1:7">
+    <row r="80" ht="15.75" spans="1:7">
       <c r="A80" s="22">
         <v>80</v>
       </c>
@@ -4245,7 +4259,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="81" ht="15.75" hidden="1" spans="1:7">
+    <row r="81" ht="15.75" spans="1:7">
       <c r="A81" s="22">
         <v>81</v>
       </c>
@@ -4266,7 +4280,7 @@
       </c>
       <c r="G81" s="25"/>
     </row>
-    <row r="82" ht="15.75" hidden="1" spans="1:7">
+    <row r="82" ht="15.75" spans="1:7">
       <c r="A82" s="22">
         <v>82</v>
       </c>
@@ -4287,7 +4301,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" ht="15.75" hidden="1" spans="1:7">
+    <row r="83" ht="15.75" spans="1:7">
       <c r="A83" s="22">
         <v>83</v>
       </c>
@@ -4310,7 +4324,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="84" ht="15.75" hidden="1" spans="1:7">
+    <row r="84" ht="15.75" spans="1:7">
       <c r="A84" s="22">
         <v>84</v>
       </c>
@@ -4329,7 +4343,7 @@
       </c>
       <c r="G84" s="25"/>
     </row>
-    <row r="85" ht="15.75" hidden="1" spans="1:7">
+    <row r="85" ht="15.75" spans="1:7">
       <c r="A85" s="22">
         <v>85</v>
       </c>
@@ -4352,7 +4366,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="86" ht="15.75" hidden="1" spans="1:7">
+    <row r="86" ht="15.75" spans="1:7">
       <c r="A86" s="22">
         <v>86</v>
       </c>
@@ -4371,7 +4385,7 @@
       </c>
       <c r="G86" s="25"/>
     </row>
-    <row r="87" ht="15.75" hidden="1" spans="1:7">
+    <row r="87" ht="15.75" spans="1:7">
       <c r="A87" s="22">
         <v>87</v>
       </c>
@@ -4392,7 +4406,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" ht="15.75" hidden="1" spans="1:7">
+    <row r="88" ht="15.75" spans="1:7">
       <c r="A88" s="22">
         <v>88</v>
       </c>
@@ -4413,7 +4427,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="89" ht="15.75" hidden="1" spans="1:7">
+    <row r="89" ht="15.75" spans="1:7">
       <c r="A89" s="22">
         <v>89</v>
       </c>
@@ -4430,11 +4444,11 @@
       <c r="F89" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="G89" s="54" t="s">
+      <c r="G89" s="55" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="90" ht="15.75" hidden="1" spans="1:7">
+    <row r="90" ht="15.75" spans="1:7">
       <c r="A90" s="22">
         <v>90</v>
       </c>
@@ -4457,7 +4471,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="91" ht="15.75" hidden="1" spans="1:7">
+    <row r="91" ht="15.75" spans="1:7">
       <c r="A91" s="22">
         <v>91</v>
       </c>
@@ -4474,11 +4488,11 @@
       <c r="F91" s="32" t="s">
         <v>234</v>
       </c>
-      <c r="G91" s="54" t="s">
+      <c r="G91" s="55" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="92" ht="15.75" hidden="1" spans="1:7">
+    <row r="92" ht="15.75" spans="1:7">
       <c r="A92" s="22">
         <v>92</v>
       </c>
@@ -4497,11 +4511,11 @@
       <c r="F92" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="G92" s="54" t="s">
+      <c r="G92" s="55" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="93" ht="15.75" hidden="1" spans="1:7">
+    <row r="93" ht="15.75" spans="1:7">
       <c r="A93" s="22">
         <v>93</v>
       </c>
@@ -4522,7 +4536,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="94" ht="15.75" hidden="1" spans="1:7">
+    <row r="94" ht="15.75" spans="1:7">
       <c r="A94" s="22">
         <v>94</v>
       </c>
@@ -4541,11 +4555,11 @@
       <c r="F94" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="G94" s="54" t="s">
+      <c r="G94" s="55" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="95" ht="15.75" hidden="1" spans="1:7">
+    <row r="95" ht="15.75" spans="1:7">
       <c r="A95" s="22">
         <v>95</v>
       </c>
@@ -4566,7 +4580,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="96" ht="31.5" hidden="1" spans="1:7">
+    <row r="96" ht="31.5" spans="1:7">
       <c r="A96" s="22">
         <v>96</v>
       </c>
@@ -4589,7 +4603,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="97" ht="15.75" hidden="1" spans="1:7">
+    <row r="97" ht="15.75" spans="1:7">
       <c r="A97" s="22">
         <v>97</v>
       </c>
@@ -4612,7 +4626,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="98" ht="15.75" hidden="1" spans="1:7">
+    <row r="98" ht="15.75" spans="1:7">
       <c r="A98" s="22">
         <v>98</v>
       </c>
@@ -4635,7 +4649,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="99" ht="15.75" hidden="1" spans="1:7">
+    <row r="99" ht="15.75" spans="1:7">
       <c r="A99" s="22">
         <v>99</v>
       </c>
@@ -4652,7 +4666,7 @@
       <c r="F99" s="32"/>
       <c r="G99" s="25"/>
     </row>
-    <row r="100" ht="15.75" hidden="1" spans="1:7">
+    <row r="100" ht="15.75" spans="1:7">
       <c r="A100" s="22">
         <v>100</v>
       </c>
@@ -4673,7 +4687,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="101" ht="15.75" hidden="1" spans="1:7">
+    <row r="101" ht="15.75" spans="1:7">
       <c r="A101" s="22">
         <v>101</v>
       </c>
@@ -4692,7 +4706,7 @@
       </c>
       <c r="G101" s="25"/>
     </row>
-    <row r="102" ht="15.75" hidden="1" spans="1:7">
+    <row r="102" ht="15.75" spans="1:7">
       <c r="A102" s="22">
         <v>102</v>
       </c>
@@ -4713,7 +4727,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="103" ht="15.75" hidden="1" spans="1:7">
+    <row r="103" ht="15.75" spans="1:7">
       <c r="A103" s="22">
         <v>103</v>
       </c>
@@ -4736,7 +4750,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" ht="15.75" hidden="1" spans="1:7">
+    <row r="104" ht="15.75" spans="1:7">
       <c r="A104" s="22">
         <v>104</v>
       </c>
@@ -4757,7 +4771,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="105" ht="15.75" hidden="1" spans="1:7">
+    <row r="105" ht="15.75" spans="1:7">
       <c r="A105" s="22">
         <v>105</v>
       </c>
@@ -4776,11 +4790,11 @@
       <c r="F105" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="G105" s="55" t="s">
+      <c r="G105" s="56" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="106" ht="15.75" hidden="1" spans="1:7">
+    <row r="106" ht="15.75" spans="1:7">
       <c r="A106" s="22">
         <v>106</v>
       </c>
@@ -4801,7 +4815,7 @@
       </c>
       <c r="G106" s="25"/>
     </row>
-    <row r="107" ht="15.75" hidden="1" spans="1:7">
+    <row r="107" ht="15.75" spans="1:7">
       <c r="A107" s="22">
         <v>107</v>
       </c>
@@ -4820,7 +4834,7 @@
       </c>
       <c r="G107" s="27"/>
     </row>
-    <row r="108" ht="15.75" hidden="1" spans="1:7">
+    <row r="108" ht="15.75" spans="1:7">
       <c r="A108" s="22">
         <v>108</v>
       </c>
@@ -4839,7 +4853,7 @@
       </c>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" ht="31.5" hidden="1" spans="1:7">
+    <row r="109" ht="31.5" spans="1:7">
       <c r="A109" s="22">
         <v>109</v>
       </c>
@@ -4858,7 +4872,7 @@
       </c>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" ht="15.75" hidden="1" spans="1:7">
+    <row r="110" ht="15.75" spans="1:7">
       <c r="A110" s="22">
         <v>110</v>
       </c>
@@ -4877,7 +4891,7 @@
       </c>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" ht="31.5" hidden="1" spans="1:7">
+    <row r="111" ht="31.5" spans="1:7">
       <c r="A111" s="22">
         <v>111</v>
       </c>
@@ -4896,7 +4910,7 @@
       </c>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" ht="15.75" hidden="1" spans="1:7">
+    <row r="112" ht="15.75" spans="1:7">
       <c r="A112" s="22">
         <v>112</v>
       </c>
@@ -4915,7 +4929,7 @@
       </c>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" ht="15.75" hidden="1" spans="1:7">
+    <row r="113" ht="15.75" spans="1:7">
       <c r="A113" s="22">
         <v>113</v>
       </c>
@@ -4934,7 +4948,7 @@
       </c>
       <c r="G113" s="27"/>
     </row>
-    <row r="114" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
+    <row r="114" s="15" customFormat="1" ht="15.75" spans="1:7">
       <c r="A114" s="22">
         <v>114</v>
       </c>
@@ -4953,7 +4967,7 @@
       </c>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" ht="15.75" hidden="1" spans="1:7">
+    <row r="115" ht="15.75" spans="1:7">
       <c r="A115" s="22">
         <v>115</v>
       </c>
@@ -4974,7 +4988,7 @@
       </c>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" ht="15.75" hidden="1" spans="1:7">
+    <row r="116" ht="15.75" spans="1:7">
       <c r="A116" s="22">
         <v>116</v>
       </c>
@@ -4993,7 +5007,7 @@
       </c>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" ht="15.75" hidden="1" spans="1:7">
+    <row r="117" ht="15.75" spans="1:7">
       <c r="A117" s="22">
         <v>117</v>
       </c>
@@ -5012,7 +5026,7 @@
       </c>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" ht="15.75" hidden="1" spans="1:7">
+    <row r="118" ht="15.75" spans="1:7">
       <c r="A118" s="22">
         <v>118</v>
       </c>
@@ -5031,7 +5045,7 @@
       </c>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" ht="15.75" hidden="1" spans="1:7">
+    <row r="119" ht="15.75" spans="1:7">
       <c r="A119" s="22">
         <v>119</v>
       </c>
@@ -5050,7 +5064,7 @@
       </c>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" ht="15.75" hidden="1" spans="1:7">
+    <row r="120" ht="15.75" spans="1:7">
       <c r="A120" s="22">
         <v>120</v>
       </c>
@@ -5069,7 +5083,7 @@
       </c>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" ht="15.75" hidden="1" spans="1:7">
+    <row r="121" ht="15.75" spans="1:7">
       <c r="A121" s="22">
         <v>121</v>
       </c>
@@ -5088,7 +5102,7 @@
       </c>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" ht="15.75" hidden="1" spans="1:7">
+    <row r="122" ht="15.75" spans="1:7">
       <c r="A122" s="22">
         <v>122</v>
       </c>
@@ -5107,7 +5121,7 @@
       </c>
       <c r="G122" s="48"/>
     </row>
-    <row r="123" ht="15.75" hidden="1" spans="1:7">
+    <row r="123" ht="15.75" spans="1:7">
       <c r="A123" s="22">
         <v>123</v>
       </c>
@@ -5126,7 +5140,7 @@
       </c>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" ht="15.75" hidden="1" spans="1:7">
+    <row r="124" ht="15.75" spans="1:7">
       <c r="A124" s="22">
         <v>124</v>
       </c>
@@ -5147,7 +5161,7 @@
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" ht="31.5" hidden="1" spans="1:7">
+    <row r="125" ht="31.5" spans="1:7">
       <c r="A125" s="22">
         <v>125</v>
       </c>
@@ -5168,7 +5182,7 @@
       </c>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" ht="15.75" hidden="1" spans="1:7">
+    <row r="126" ht="15.75" spans="1:7">
       <c r="A126" s="22">
         <v>126</v>
       </c>
@@ -5187,7 +5201,7 @@
       </c>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" ht="15.75" hidden="1" spans="1:7">
+    <row r="127" ht="15.75" spans="1:7">
       <c r="A127" s="22">
         <v>127</v>
       </c>
@@ -5208,7 +5222,7 @@
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" ht="15.75" hidden="1" spans="1:7">
+    <row r="128" ht="15.75" spans="1:7">
       <c r="A128" s="22">
         <v>128</v>
       </c>
@@ -5229,7 +5243,7 @@
       </c>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" ht="15.75" hidden="1" spans="1:7">
+    <row r="129" ht="15.75" spans="1:7">
       <c r="A129" s="22">
         <v>129</v>
       </c>
@@ -5248,11 +5262,11 @@
       <c r="F129" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="G129" s="54" t="s">
+      <c r="G129" s="55" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="130" ht="15.75" hidden="1" spans="1:7">
+    <row r="130" ht="15.75" spans="1:7">
       <c r="A130" s="22">
         <v>130</v>
       </c>
@@ -5271,7 +5285,7 @@
       <c r="F130" s="50" t="s">
         <v>328</v>
       </c>
-      <c r="G130" s="56" t="s">
+      <c r="G130" s="57" t="s">
         <v>329</v>
       </c>
     </row>
@@ -5291,14 +5305,14 @@
       <c r="E131" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F131" s="51" t="s">
+      <c r="F131" s="42" t="s">
         <v>331</v>
       </c>
-      <c r="G131" s="56" t="s">
+      <c r="G131" s="57" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="132" ht="15.75" hidden="1" spans="1:7">
+    <row r="132" ht="15.75" spans="1:7">
       <c r="A132" s="22">
         <v>132</v>
       </c>
@@ -5317,11 +5331,11 @@
       <c r="F132" s="50" t="s">
         <v>334</v>
       </c>
-      <c r="G132" s="56" t="s">
+      <c r="G132" s="57" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="133" ht="15.75" hidden="1" spans="1:7">
+    <row r="133" ht="15.75" spans="1:7">
       <c r="A133" s="22">
         <v>133</v>
       </c>
@@ -5340,11 +5354,11 @@
       <c r="F133" s="50" t="s">
         <v>312</v>
       </c>
-      <c r="G133" s="56" t="s">
+      <c r="G133" s="57" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="134" ht="15.75" hidden="1" spans="1:7">
+    <row r="134" ht="15.75" spans="1:7">
       <c r="A134" s="22">
         <v>134</v>
       </c>
@@ -5364,7 +5378,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" ht="15.75" hidden="1" spans="1:7">
+    <row r="135" ht="15.75" spans="1:7">
       <c r="A135" s="22">
         <v>135</v>
       </c>
@@ -5387,7 +5401,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="136" ht="15.75" hidden="1" spans="1:7">
+    <row r="136" ht="15.75" spans="1:7">
       <c r="A136" s="22">
         <v>136</v>
       </c>
@@ -5406,11 +5420,11 @@
       <c r="F136" s="50" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="56" t="s">
+      <c r="G136" s="57" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="137" ht="15.75" hidden="1" spans="1:7">
+    <row r="137" ht="15.75" spans="1:7">
       <c r="A137" s="22">
         <v>137</v>
       </c>
@@ -5429,11 +5443,11 @@
       <c r="F137" s="50" t="s">
         <v>346</v>
       </c>
-      <c r="G137" s="56" t="s">
+      <c r="G137" s="57" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="138" ht="15.75" hidden="1" spans="1:7">
+    <row r="138" ht="15.75" spans="1:7">
       <c r="A138" s="22">
         <v>138</v>
       </c>
@@ -5452,11 +5466,11 @@
       <c r="F138" s="50" t="s">
         <v>349</v>
       </c>
-      <c r="G138" s="56" t="s">
+      <c r="G138" s="57" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="139" ht="15.75" hidden="1" spans="1:7">
+    <row r="139" ht="15.75" spans="1:7">
       <c r="A139" s="22">
         <v>139</v>
       </c>
@@ -5476,7 +5490,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" ht="15.75" hidden="1" spans="1:7">
+    <row r="140" ht="15.75" spans="1:7">
       <c r="A140" s="22">
         <v>140</v>
       </c>
@@ -5492,14 +5506,14 @@
       <c r="E140" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F140" s="52" t="s">
+      <c r="F140" s="51" t="s">
         <v>355</v>
       </c>
-      <c r="G140" s="57" t="s">
+      <c r="G140" s="58" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="141" ht="15.75" hidden="1" spans="1:7">
+    <row r="141" ht="15.75" spans="1:7">
       <c r="A141" s="22">
         <v>141</v>
       </c>
@@ -5515,11 +5529,11 @@
       <c r="E141" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="F141" s="53" t="s">
+      <c r="F141" s="52" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="142" ht="15.75" hidden="1" spans="1:7">
+    <row r="142" ht="15.75" spans="1:7">
       <c r="A142" s="22">
         <v>142</v>
       </c>
@@ -5535,11 +5549,11 @@
       <c r="E142" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F142" s="53" t="s">
+      <c r="F142" s="52" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="143" ht="31.5" hidden="1" spans="1:7">
+    <row r="143" ht="31.5" spans="1:7">
       <c r="A143" s="22">
         <v>143</v>
       </c>
@@ -5562,8 +5576,25 @@
         <v>197</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
-      <c r="D144" s="17"/>
+    <row r="144" ht="15.75" spans="1:7">
+      <c r="A144" s="22">
+        <v>144</v>
+      </c>
+      <c r="B144" s="53" t="s">
+        <v>361</v>
+      </c>
+      <c r="C144" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="E144" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144" s="54" t="s">
+        <v>362</v>
+      </c>
     </row>
     <row r="145" spans="4:4">
       <c r="D145" s="17"/>
@@ -8629,12 +8660,7 @@
       <c r="D1165" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G143" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="SEMMAK ABDELKADER"/>
-      </filters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G144" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8687,6 +8713,7 @@
     <hyperlink ref="F129" r:id="rId47" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
     <hyperlink ref="F114" r:id="rId48" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
     <hyperlink ref="F143" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F144" r:id="rId49" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8709,202 +8736,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>373</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>373</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$143</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="398">
   <si>
     <t>N°</t>
   </si>
@@ -493,19 +493,10 @@
     <t>06 96 0582 37</t>
   </si>
   <si>
-    <t>BENSALEM RITEDJ INES</t>
-  </si>
-  <si>
-    <t>rawnakritedj@gmail.com</t>
-  </si>
-  <si>
-    <t>07 91 88 64 96</t>
-  </si>
-  <si>
-    <t>BENSALEM ABDELHAMID</t>
-  </si>
-  <si>
-    <t>bensalemabdelhamid7@gmail.com</t>
+    <t>BENSALEM Mohammed Mustapha</t>
+  </si>
+  <si>
+    <t>bensalem.moh.mus@gmail.com</t>
   </si>
   <si>
     <t>0550114832</t>
@@ -1318,6 +1309,12 @@
     </font>
     <font>
       <sz val="10.5"/>
+      <color rgb="FF222222"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
       <color rgb="FF5E5E5E"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1345,13 +1342,6 @@
       <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Cambria"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2034,7 +2024,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2147,13 +2137,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2166,28 +2159,26 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2533,8 +2524,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G1165"/>
+  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <dimension ref="A1:G1164"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="16" customWidth="1"/>
@@ -2570,7 +2561,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" spans="1:7">
+    <row r="2" ht="15.75" hidden="1" spans="1:7">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -2591,7 +2582,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" ht="15.75" spans="1:7">
+    <row r="3" ht="15.75" hidden="1" spans="1:7">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -2612,7 +2603,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" ht="15.75" spans="1:7">
+    <row r="4" ht="15.75" hidden="1" spans="1:7">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -2633,7 +2624,7 @@
       </c>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" ht="15.75" spans="1:7">
+    <row r="5" ht="15.75" hidden="1" spans="1:7">
       <c r="A5" s="22">
         <v>4</v>
       </c>
@@ -2654,7 +2645,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" ht="15.75" spans="1:7">
+    <row r="6" ht="15.75" hidden="1" spans="1:7">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -2675,7 +2666,7 @@
       </c>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" ht="15.75" spans="1:7">
+    <row r="7" ht="15.75" hidden="1" spans="1:7">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -2694,11 +2685,11 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G7" s="54" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:7">
+    <row r="8" ht="15.75" hidden="1" spans="1:7">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -2717,11 +2708,11 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="55" t="s">
+      <c r="G8" s="54" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:7">
+    <row r="9" ht="15.75" hidden="1" spans="1:7">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -2742,7 +2733,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" ht="15.75" spans="1:7">
+    <row r="10" ht="15.75" hidden="1" spans="1:7">
       <c r="A10" s="22">
         <v>9</v>
       </c>
@@ -2761,11 +2752,11 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="54" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" spans="1:7">
+    <row r="11" ht="15.75" hidden="1" spans="1:7">
       <c r="A11" s="22">
         <v>10</v>
       </c>
@@ -2786,7 +2777,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" ht="15.75" spans="1:7">
+    <row r="12" ht="15.75" hidden="1" spans="1:7">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -2807,7 +2798,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" ht="15.75" spans="1:7">
+    <row r="13" ht="15.75" hidden="1" spans="1:7">
       <c r="A13" s="22">
         <v>12</v>
       </c>
@@ -2828,7 +2819,7 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" ht="15.75" spans="1:7">
+    <row r="14" ht="15.75" hidden="1" spans="1:7">
       <c r="A14" s="22">
         <v>13</v>
       </c>
@@ -2849,7 +2840,7 @@
       </c>
       <c r="G14" s="25"/>
     </row>
-    <row r="15" ht="15.75" spans="1:7">
+    <row r="15" ht="15.75" hidden="1" spans="1:7">
       <c r="A15" s="22">
         <v>14</v>
       </c>
@@ -2870,7 +2861,7 @@
       </c>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" ht="31.5" spans="1:7">
+    <row r="16" ht="31.5" hidden="1" spans="1:7">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -2891,7 +2882,7 @@
       </c>
       <c r="G16" s="25"/>
     </row>
-    <row r="17" ht="15.75" spans="1:7">
+    <row r="17" ht="15.75" hidden="1" spans="1:7">
       <c r="A17" s="22">
         <v>16</v>
       </c>
@@ -2912,7 +2903,7 @@
       </c>
       <c r="G17" s="25"/>
     </row>
-    <row r="18" ht="15.75" spans="1:7">
+    <row r="18" ht="15.75" hidden="1" spans="1:7">
       <c r="A18" s="22">
         <v>17</v>
       </c>
@@ -2933,7 +2924,7 @@
       </c>
       <c r="G18" s="25"/>
     </row>
-    <row r="19" ht="15.75" spans="1:7">
+    <row r="19" ht="15.75" hidden="1" spans="1:7">
       <c r="A19" s="22">
         <v>18</v>
       </c>
@@ -2954,7 +2945,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" ht="31.5" spans="1:7">
+    <row r="20" ht="31.5" hidden="1" spans="1:7">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -2975,7 +2966,7 @@
       </c>
       <c r="G20" s="25"/>
     </row>
-    <row r="21" ht="15.75" spans="1:7">
+    <row r="21" ht="15.75" hidden="1" spans="1:7">
       <c r="A21" s="22">
         <v>20</v>
       </c>
@@ -2996,7 +2987,7 @@
       </c>
       <c r="G21" s="25"/>
     </row>
-    <row r="22" ht="15.75" spans="1:7">
+    <row r="22" ht="15.75" hidden="1" spans="1:7">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -3017,7 +3008,7 @@
       </c>
       <c r="G22" s="25"/>
     </row>
-    <row r="23" ht="15.75" spans="1:7">
+    <row r="23" ht="15.75" hidden="1" spans="1:7">
       <c r="A23" s="22">
         <v>22</v>
       </c>
@@ -3038,7 +3029,7 @@
       </c>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" ht="15.75" spans="1:7">
+    <row r="24" ht="15.75" hidden="1" spans="1:7">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -3059,7 +3050,7 @@
       </c>
       <c r="G24" s="25"/>
     </row>
-    <row r="25" ht="15.75" spans="1:7">
+    <row r="25" ht="15.75" hidden="1" spans="1:7">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -3080,7 +3071,7 @@
       </c>
       <c r="G25" s="25"/>
     </row>
-    <row r="26" ht="31.5" spans="1:7">
+    <row r="26" ht="31.5" hidden="1" spans="1:7">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -3101,7 +3092,7 @@
       </c>
       <c r="G26" s="25"/>
     </row>
-    <row r="27" ht="15.75" spans="1:7">
+    <row r="27" ht="15.75" hidden="1" spans="1:7">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -3122,7 +3113,7 @@
       </c>
       <c r="G27" s="25"/>
     </row>
-    <row r="28" ht="15.75" spans="1:7">
+    <row r="28" ht="15.75" hidden="1" spans="1:7">
       <c r="A28" s="22">
         <v>27</v>
       </c>
@@ -3143,7 +3134,7 @@
       </c>
       <c r="G28" s="25"/>
     </row>
-    <row r="29" ht="15.75" spans="1:7">
+    <row r="29" ht="15.75" hidden="1" spans="1:7">
       <c r="A29" s="22">
         <v>28</v>
       </c>
@@ -3164,7 +3155,7 @@
       </c>
       <c r="G29" s="25"/>
     </row>
-    <row r="30" ht="15.75" spans="1:7">
+    <row r="30" ht="15.75" hidden="1" spans="1:7">
       <c r="A30" s="22">
         <v>29</v>
       </c>
@@ -3185,7 +3176,7 @@
       </c>
       <c r="G30" s="25"/>
     </row>
-    <row r="31" ht="15.75" spans="1:7">
+    <row r="31" ht="15.75" hidden="1" spans="1:7">
       <c r="A31" s="22">
         <v>30</v>
       </c>
@@ -3206,7 +3197,7 @@
       </c>
       <c r="G31" s="25"/>
     </row>
-    <row r="32" ht="15.75" spans="1:7">
+    <row r="32" ht="15.75" hidden="1" spans="1:7">
       <c r="A32" s="22">
         <v>31</v>
       </c>
@@ -3227,7 +3218,7 @@
       </c>
       <c r="G32" s="25"/>
     </row>
-    <row r="33" ht="15.75" spans="1:7">
+    <row r="33" ht="15.75" hidden="1" spans="1:7">
       <c r="A33" s="22">
         <v>32</v>
       </c>
@@ -3248,7 +3239,7 @@
       </c>
       <c r="G33" s="25"/>
     </row>
-    <row r="34" ht="15.75" spans="1:7">
+    <row r="34" ht="15.75" hidden="1" spans="1:7">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -3269,7 +3260,7 @@
       </c>
       <c r="G34" s="25"/>
     </row>
-    <row r="35" ht="15.75" spans="1:7">
+    <row r="35" ht="15.75" hidden="1" spans="1:7">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -3290,7 +3281,7 @@
       </c>
       <c r="G35" s="25"/>
     </row>
-    <row r="36" ht="15.75" spans="1:7">
+    <row r="36" ht="15.75" hidden="1" spans="1:7">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -3309,11 +3300,11 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="56" t="s">
+      <c r="G36" s="55" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="15.75" spans="1:7">
+    <row r="37" ht="15.75" hidden="1" spans="1:7">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -3334,7 +3325,7 @@
       </c>
       <c r="G37" s="25"/>
     </row>
-    <row r="38" ht="15.75" spans="1:7">
+    <row r="38" ht="15.75" hidden="1" spans="1:7">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -3353,11 +3344,11 @@
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="55" t="s">
+      <c r="G38" s="54" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="31.5" spans="1:7">
+    <row r="39" ht="31.5" hidden="1" spans="1:7">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -3378,7 +3369,7 @@
       </c>
       <c r="G39" s="25"/>
     </row>
-    <row r="40" ht="15.75" spans="1:7">
+    <row r="40" ht="15.75" hidden="1" spans="1:7">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -3399,7 +3390,7 @@
       </c>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" ht="15.75" spans="1:7">
+    <row r="41" ht="15.75" hidden="1" spans="1:7">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -3420,7 +3411,7 @@
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" ht="15.75" spans="1:7">
+    <row r="42" ht="15.75" hidden="1" spans="1:7">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -3441,7 +3432,7 @@
       </c>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" ht="15.75" spans="1:7">
+    <row r="43" ht="15.75" hidden="1" spans="1:7">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -3462,7 +3453,7 @@
       </c>
       <c r="G43" s="25"/>
     </row>
-    <row r="44" ht="15.75" spans="1:7">
+    <row r="44" ht="15.75" hidden="1" spans="1:7">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -3483,7 +3474,7 @@
       </c>
       <c r="G44" s="25"/>
     </row>
-    <row r="45" ht="15.75" spans="1:7">
+    <row r="45" ht="15.75" hidden="1" spans="1:7">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -3504,7 +3495,7 @@
       </c>
       <c r="G45" s="25"/>
     </row>
-    <row r="46" ht="15.75" spans="1:7">
+    <row r="46" ht="15.75" hidden="1" spans="1:7">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -3525,7 +3516,7 @@
       </c>
       <c r="G46" s="25"/>
     </row>
-    <row r="47" ht="15.75" spans="1:7">
+    <row r="47" ht="15.75" hidden="1" spans="1:7">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -3546,7 +3537,7 @@
       </c>
       <c r="G47" s="25"/>
     </row>
-    <row r="48" ht="15.75" spans="1:7">
+    <row r="48" ht="15.75" hidden="1" spans="1:7">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -3567,7 +3558,7 @@
       </c>
       <c r="G48" s="25"/>
     </row>
-    <row r="49" ht="15.75" spans="1:7">
+    <row r="49" ht="15.75" hidden="1" spans="1:7">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -3588,7 +3579,7 @@
       </c>
       <c r="G49" s="25"/>
     </row>
-    <row r="50" ht="15.75" spans="1:7">
+    <row r="50" ht="15.75" hidden="1" spans="1:7">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -3609,7 +3600,7 @@
       </c>
       <c r="G50" s="25"/>
     </row>
-    <row r="51" ht="15.75" spans="1:7">
+    <row r="51" ht="15.75" hidden="1" spans="1:7">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -3630,7 +3621,7 @@
       </c>
       <c r="G51" s="25"/>
     </row>
-    <row r="52" ht="15.75" spans="1:7">
+    <row r="52" ht="15.75" hidden="1" spans="1:7">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -3649,11 +3640,11 @@
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="55" t="s">
+      <c r="G52" s="54" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="53" ht="15.75" spans="1:7">
+    <row r="53" ht="15.75" hidden="1" spans="1:7">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -3674,7 +3665,7 @@
       </c>
       <c r="G53" s="25"/>
     </row>
-    <row r="54" ht="15.75" spans="1:7">
+    <row r="54" ht="15.75" hidden="1" spans="1:7">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -3693,11 +3684,11 @@
       <c r="F54" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="55" t="s">
+      <c r="G54" s="54" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="55" ht="15.75" spans="1:7">
+    <row r="55" ht="15.75" hidden="1" spans="1:7">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -3718,7 +3709,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" ht="15.75" spans="1:7">
+    <row r="56" ht="15.75" hidden="1" spans="1:7">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -3735,7 +3726,7 @@
       <c r="F56" s="34"/>
       <c r="G56" s="25"/>
     </row>
-    <row r="57" ht="15.75" spans="1:7">
+    <row r="57" ht="15.75" hidden="1" spans="1:7">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -3758,7 +3749,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" ht="15.75" spans="1:7">
+    <row r="58" ht="15.75" hidden="1" spans="1:7">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -3781,7 +3772,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" ht="15.75" spans="1:7">
+    <row r="59" ht="15.75" hidden="1" spans="1:7">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -3804,7 +3795,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" ht="15.75" spans="1:7">
+    <row r="60" ht="15.75" hidden="1" spans="1:7">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -3827,7 +3818,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" ht="15.75" spans="1:7">
+    <row r="61" ht="15.75" hidden="1" spans="1:7">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -3848,7 +3839,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" ht="31.5" spans="1:7">
+    <row r="62" ht="31.5" hidden="1" spans="1:7">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -3869,30 +3860,32 @@
         <v>152</v>
       </c>
     </row>
-    <row r="63" ht="15.75" spans="1:7">
+    <row r="63" ht="30" spans="1:7">
       <c r="A63" s="22">
-        <v>63</v>
-      </c>
-      <c r="B63" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" s="40" t="s">
         <v>153</v>
       </c>
       <c r="C63" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="E63" s="35"/>
-      <c r="F63" s="32" t="s">
+      <c r="E63" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="F63" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="G63" s="25" t="s">
+      <c r="G63" s="54" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="64" ht="15.75" spans="1:7">
+    <row r="64" ht="31.5" hidden="1" spans="1:7">
       <c r="A64" s="22">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" s="23" t="s">
         <v>156</v>
@@ -3900,22 +3893,20 @@
       <c r="C64" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D64" s="40" t="s">
+      <c r="D64" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E64" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="F64" s="41" t="s">
+      <c r="E64" s="31"/>
+      <c r="F64" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="G64" s="55" t="s">
+      <c r="G64" s="25" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="65" ht="31.5" spans="1:7">
+    <row r="65" ht="15.75" hidden="1" spans="1:7">
       <c r="A65" s="22">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B65" s="23" t="s">
         <v>159</v>
@@ -3926,17 +3917,17 @@
       <c r="D65" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E65" s="31"/>
-      <c r="F65" s="32" t="s">
+      <c r="E65" s="35"/>
+      <c r="F65" s="43" t="s">
         <v>160</v>
       </c>
       <c r="G65" s="25" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="66" ht="15.75" spans="1:7">
+    <row r="66" ht="15.75" hidden="1" spans="1:7">
       <c r="A66" s="22">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B66" s="23" t="s">
         <v>162</v>
@@ -3947,17 +3938,17 @@
       <c r="D66" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E66" s="35"/>
-      <c r="F66" s="42" t="s">
+      <c r="E66" s="31"/>
+      <c r="F66" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="G66" s="25" t="s">
+      <c r="G66" s="55" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="67" ht="15.75" spans="1:7">
+    <row r="67" ht="15.75" hidden="1" spans="1:7">
       <c r="A67" s="22">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B67" s="23" t="s">
         <v>165</v>
@@ -3968,17 +3959,19 @@
       <c r="D67" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E67" s="31"/>
-      <c r="F67" s="24" t="s">
+      <c r="E67" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F67" s="32" t="s">
         <v>166</v>
       </c>
-      <c r="G67" s="56" t="s">
+      <c r="G67" s="25" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="68" ht="15.75" spans="1:7">
+    <row r="68" ht="15.75" hidden="1" spans="1:7">
       <c r="A68" s="22">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B68" s="23" t="s">
         <v>168</v>
@@ -3989,19 +3982,17 @@
       <c r="D68" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E68" s="22" t="s">
-        <v>134</v>
-      </c>
+      <c r="E68" s="22"/>
       <c r="F68" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="G68" s="25" t="s">
+      <c r="G68" s="54" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="69" ht="15.75" spans="1:7">
+    <row r="69" ht="15.75" hidden="1" spans="1:7">
       <c r="A69" s="22">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B69" s="23" t="s">
         <v>171</v>
@@ -4016,13 +4007,13 @@
       <c r="F69" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="55" t="s">
+      <c r="G69" s="54" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="70" ht="15.75" spans="1:7">
+    <row r="70" ht="31.5" hidden="1" spans="1:7">
       <c r="A70" s="22">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B70" s="23" t="s">
         <v>174</v>
@@ -4030,20 +4021,20 @@
       <c r="C70" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D70" s="22" t="s">
+      <c r="D70" s="28" t="s">
         <v>125</v>
       </c>
       <c r="E70" s="22"/>
-      <c r="F70" s="32" t="s">
+      <c r="F70" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="55" t="s">
+      <c r="G70" s="54" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="71" ht="31.5" spans="1:7">
+    <row r="71" ht="15.75" hidden="1" spans="1:7">
       <c r="A71" s="22">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B71" s="23" t="s">
         <v>177</v>
@@ -4051,20 +4042,20 @@
       <c r="C71" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D71" s="22" t="s">
         <v>125</v>
       </c>
       <c r="E71" s="22"/>
-      <c r="F71" s="39" t="s">
+      <c r="F71" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="55" t="s">
+      <c r="G71" s="54" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="72" ht="15.75" spans="1:7">
+    <row r="72" ht="15.75" hidden="1" spans="1:7">
       <c r="A72" s="22">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B72" s="23" t="s">
         <v>180</v>
@@ -4075,17 +4066,19 @@
       <c r="D72" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E72" s="22"/>
+      <c r="E72" s="22" t="s">
+        <v>134</v>
+      </c>
       <c r="F72" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="55" t="s">
+      <c r="G72" s="54" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="73" ht="15.75" spans="1:7">
+    <row r="73" ht="15.75" hidden="1" spans="1:7">
       <c r="A73" s="22">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B73" s="23" t="s">
         <v>183</v>
@@ -4096,19 +4089,17 @@
       <c r="D73" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E73" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F73" s="26" t="s">
+      <c r="E73" s="22"/>
+      <c r="F73" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="G73" s="55" t="s">
+      <c r="G73" s="25" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="74" ht="15.75" spans="1:7">
+    <row r="74" ht="15.75" hidden="1" spans="1:7">
       <c r="A74" s="22">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B74" s="23" t="s">
         <v>186</v>
@@ -4119,7 +4110,9 @@
       <c r="D74" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E74" s="22"/>
+      <c r="E74" s="22" t="s">
+        <v>134</v>
+      </c>
       <c r="F74" s="32" t="s">
         <v>187</v>
       </c>
@@ -4127,9 +4120,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="75" ht="15.75" spans="1:7">
+    <row r="75" ht="15.75" hidden="1" spans="1:7">
       <c r="A75" s="22">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B75" s="23" t="s">
         <v>189</v>
@@ -4140,19 +4133,17 @@
       <c r="D75" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E75" s="22" t="s">
-        <v>134</v>
-      </c>
+      <c r="E75" s="22"/>
       <c r="F75" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="G75" s="25" t="s">
+      <c r="G75" s="54" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="76" ht="15.75" spans="1:7">
+    <row r="76" ht="31.5" hidden="1" spans="1:7">
       <c r="A76" s="22">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B76" s="23" t="s">
         <v>192</v>
@@ -4163,17 +4154,19 @@
       <c r="D76" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E76" s="22"/>
+      <c r="E76" s="22" t="s">
+        <v>126</v>
+      </c>
       <c r="F76" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="G76" s="55" t="s">
+      <c r="G76" s="25" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="77" ht="31.5" spans="1:7">
+    <row r="77" ht="15.75" hidden="1" spans="1:7">
       <c r="A77" s="22">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B77" s="23" t="s">
         <v>195</v>
@@ -4184,22 +4177,18 @@
       <c r="D77" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E77" s="22" t="s">
-        <v>126</v>
-      </c>
+      <c r="E77" s="22"/>
       <c r="F77" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="G77" s="25" t="s">
+      <c r="G77" s="25"/>
+    </row>
+    <row r="78" ht="15.75" hidden="1" spans="1:7">
+      <c r="A78" s="22">
+        <v>79</v>
+      </c>
+      <c r="B78" s="23" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" spans="1:7">
-      <c r="A78" s="22">
-        <v>78</v>
-      </c>
-      <c r="B78" s="23" t="s">
-        <v>198</v>
       </c>
       <c r="C78" s="23" t="s">
         <v>8</v>
@@ -4207,15 +4196,19 @@
       <c r="D78" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E78" s="22"/>
+      <c r="E78" s="22" t="s">
+        <v>126</v>
+      </c>
       <c r="F78" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="G78" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="G78" s="25"/>
-    </row>
-    <row r="79" ht="15.75" spans="1:7">
+    </row>
+    <row r="79" ht="15.75" hidden="1" spans="1:7">
       <c r="A79" s="22">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B79" s="23" t="s">
         <v>200</v>
@@ -4227,18 +4220,18 @@
         <v>125</v>
       </c>
       <c r="E79" s="22" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="F79" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="G79" s="55" t="s">
+      <c r="G79" s="25" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="80" ht="15.75" spans="1:7">
+    <row r="80" ht="15.75" hidden="1" spans="1:7">
       <c r="A80" s="22">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B80" s="23" t="s">
         <v>203</v>
@@ -4250,21 +4243,19 @@
         <v>125</v>
       </c>
       <c r="E80" s="22" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F80" s="32" t="s">
         <v>204</v>
       </c>
-      <c r="G80" s="25" t="s">
+      <c r="G80" s="25"/>
+    </row>
+    <row r="81" ht="15.75" hidden="1" spans="1:7">
+      <c r="A81" s="22">
+        <v>82</v>
+      </c>
+      <c r="B81" s="23" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" spans="1:7">
-      <c r="A81" s="22">
-        <v>81</v>
-      </c>
-      <c r="B81" s="23" t="s">
-        <v>206</v>
       </c>
       <c r="C81" s="23" t="s">
         <v>8</v>
@@ -4272,17 +4263,17 @@
       <c r="D81" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E81" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="F81" s="32" t="s">
+      <c r="E81" s="22"/>
+      <c r="F81" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="G81" s="25" t="s">
         <v>207</v>
       </c>
-      <c r="G81" s="25"/>
-    </row>
-    <row r="82" ht="15.75" spans="1:7">
+    </row>
+    <row r="82" ht="15.75" hidden="1" spans="1:7">
       <c r="A82" s="22">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B82" s="23" t="s">
         <v>208</v>
@@ -4293,17 +4284,19 @@
       <c r="D82" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E82" s="22"/>
-      <c r="F82" s="24" t="s">
+      <c r="E82" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F82" s="32" t="s">
         <v>209</v>
       </c>
       <c r="G82" s="25" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="83" ht="15.75" spans="1:7">
+    <row r="83" ht="15.75" hidden="1" spans="1:7">
       <c r="A83" s="22">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B83" s="23" t="s">
         <v>211</v>
@@ -4314,22 +4307,18 @@
       <c r="D83" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E83" s="22" t="s">
-        <v>126</v>
-      </c>
+      <c r="E83" s="31"/>
       <c r="F83" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="G83" s="25" t="s">
+      <c r="G83" s="25"/>
+    </row>
+    <row r="84" ht="15.75" hidden="1" spans="1:7">
+      <c r="A84" s="22">
+        <v>85</v>
+      </c>
+      <c r="B84" s="23" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" spans="1:7">
-      <c r="A84" s="22">
-        <v>84</v>
-      </c>
-      <c r="B84" s="23" t="s">
-        <v>214</v>
       </c>
       <c r="C84" s="23" t="s">
         <v>8</v>
@@ -4337,15 +4326,19 @@
       <c r="D84" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E84" s="31"/>
-      <c r="F84" s="32" t="s">
+      <c r="E84" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F84" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="G84" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="G84" s="25"/>
-    </row>
-    <row r="85" ht="15.75" spans="1:7">
+    </row>
+    <row r="85" ht="15.75" hidden="1" spans="1:7">
       <c r="A85" s="22">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B85" s="23" t="s">
         <v>216</v>
@@ -4353,41 +4346,39 @@
       <c r="C85" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D85" s="22" t="s">
+      <c r="D85" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="E85" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="F85" s="43" t="s">
+      <c r="E85" s="31"/>
+      <c r="F85" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="G85" s="25" t="s">
+      <c r="G85" s="25"/>
+    </row>
+    <row r="86" ht="15.75" hidden="1" spans="1:7">
+      <c r="A86" s="22">
+        <v>87</v>
+      </c>
+      <c r="B86" s="23" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="86" ht="15.75" spans="1:7">
-      <c r="A86" s="22">
-        <v>86</v>
-      </c>
-      <c r="B86" s="23" t="s">
-        <v>219</v>
-      </c>
       <c r="C86" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D86" s="28" t="s">
+      <c r="D86" s="22" t="s">
         <v>125</v>
       </c>
       <c r="E86" s="31"/>
       <c r="F86" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="G86" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="G86" s="25"/>
-    </row>
-    <row r="87" ht="15.75" spans="1:7">
+    </row>
+    <row r="87" ht="15.75" hidden="1" spans="1:7">
       <c r="A87" s="22">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B87" s="23" t="s">
         <v>221</v>
@@ -4398,7 +4389,7 @@
       <c r="D87" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E87" s="31"/>
+      <c r="E87" s="35"/>
       <c r="F87" s="32" t="s">
         <v>222</v>
       </c>
@@ -4406,9 +4397,9 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" ht="15.75" spans="1:7">
+    <row r="88" ht="15.75" hidden="1" spans="1:7">
       <c r="A88" s="22">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B88" s="23" t="s">
         <v>224</v>
@@ -4419,17 +4410,17 @@
       <c r="D88" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E88" s="35"/>
+      <c r="E88" s="22"/>
       <c r="F88" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="G88" s="25" t="s">
+      <c r="G88" s="54" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="89" ht="15.75" spans="1:7">
+    <row r="89" ht="15.75" hidden="1" spans="1:7">
       <c r="A89" s="22">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B89" s="23" t="s">
         <v>227</v>
@@ -4440,17 +4431,19 @@
       <c r="D89" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E89" s="22"/>
+      <c r="E89" s="22" t="s">
+        <v>138</v>
+      </c>
       <c r="F89" s="32" t="s">
         <v>228</v>
       </c>
-      <c r="G89" s="55" t="s">
+      <c r="G89" s="25" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="90" ht="15.75" spans="1:7">
+    <row r="90" ht="15.75" hidden="1" spans="1:7">
       <c r="A90" s="22">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B90" s="23" t="s">
         <v>230</v>
@@ -4461,19 +4454,17 @@
       <c r="D90" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E90" s="22" t="s">
-        <v>138</v>
-      </c>
+      <c r="E90" s="22"/>
       <c r="F90" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="G90" s="25" t="s">
+      <c r="G90" s="54" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="91" ht="15.75" spans="1:7">
+    <row r="91" ht="15.75" hidden="1" spans="1:7">
       <c r="A91" s="22">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B91" s="23" t="s">
         <v>233</v>
@@ -4484,20 +4475,22 @@
       <c r="D91" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E91" s="22"/>
+      <c r="E91" s="22" t="s">
+        <v>234</v>
+      </c>
       <c r="F91" s="32" t="s">
-        <v>234</v>
-      </c>
-      <c r="G91" s="55" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="92" ht="15.75" spans="1:7">
+      <c r="G91" s="54" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" hidden="1" spans="1:7">
       <c r="A92" s="22">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B92" s="23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C92" s="23" t="s">
         <v>8</v>
@@ -4505,19 +4498,17 @@
       <c r="D92" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E92" s="22" t="s">
-        <v>237</v>
-      </c>
+      <c r="E92" s="22"/>
       <c r="F92" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="G92" s="55" t="s">
+      <c r="G92" s="25" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="93" ht="15.75" spans="1:7">
+    <row r="93" ht="15.75" hidden="1" spans="1:7">
       <c r="A93" s="22">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B93" s="23" t="s">
         <v>240</v>
@@ -4528,17 +4519,19 @@
       <c r="D93" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E93" s="22"/>
-      <c r="F93" s="32" t="s">
+      <c r="E93" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F93" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="G93" s="25" t="s">
+      <c r="G93" s="54" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="94" ht="15.75" spans="1:7">
+    <row r="94" ht="15.75" hidden="1" spans="1:7">
       <c r="A94" s="22">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B94" s="23" t="s">
         <v>243</v>
@@ -4549,19 +4542,17 @@
       <c r="D94" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E94" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F94" s="43" t="s">
+      <c r="E94" s="22"/>
+      <c r="F94" s="32" t="s">
         <v>244</v>
       </c>
-      <c r="G94" s="55" t="s">
+      <c r="G94" s="25" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="95" ht="15.75" spans="1:7">
+    <row r="95" ht="31.5" hidden="1" spans="1:7">
       <c r="A95" s="22">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B95" s="23" t="s">
         <v>246</v>
@@ -4569,32 +4560,34 @@
       <c r="C95" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D95" s="22" t="s">
+      <c r="D95" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="E95" s="22"/>
+      <c r="E95" s="22" t="s">
+        <v>247</v>
+      </c>
       <c r="F95" s="32" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="96" ht="31.5" spans="1:7">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" hidden="1" spans="1:7">
       <c r="A96" s="22">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B96" s="23" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C96" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D96" s="28" t="s">
+      <c r="D96" s="22" t="s">
         <v>125</v>
       </c>
       <c r="E96" s="22" t="s">
-        <v>250</v>
+        <v>138</v>
       </c>
       <c r="F96" s="32" t="s">
         <v>251</v>
@@ -4603,9 +4596,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="97" ht="15.75" spans="1:7">
+    <row r="97" ht="15.75" hidden="1" spans="1:7">
       <c r="A97" s="22">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B97" s="23" t="s">
         <v>253</v>
@@ -4617,7 +4610,7 @@
         <v>125</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F97" s="32" t="s">
         <v>254</v>
@@ -4626,9 +4619,9 @@
         <v>255</v>
       </c>
     </row>
-    <row r="98" ht="15.75" spans="1:7">
+    <row r="98" ht="15.75" hidden="1" spans="1:7">
       <c r="A98" s="22">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B98" s="23" t="s">
         <v>256</v>
@@ -4639,22 +4632,16 @@
       <c r="D98" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E98" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="F98" s="32" t="s">
+      <c r="E98" s="22"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="25"/>
+    </row>
+    <row r="99" ht="15.75" hidden="1" spans="1:7">
+      <c r="A99" s="22">
+        <v>100</v>
+      </c>
+      <c r="B99" s="23" t="s">
         <v>257</v>
-      </c>
-      <c r="G98" s="25" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" spans="1:7">
-      <c r="A99" s="22">
-        <v>99</v>
-      </c>
-      <c r="B99" s="23" t="s">
-        <v>259</v>
       </c>
       <c r="C99" s="23" t="s">
         <v>8</v>
@@ -4662,13 +4649,17 @@
       <c r="D99" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E99" s="22"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="25"/>
-    </row>
-    <row r="100" ht="15.75" spans="1:7">
+      <c r="E99" s="35"/>
+      <c r="F99" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="G99" s="25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" hidden="1" spans="1:7">
       <c r="A100" s="22">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B100" s="23" t="s">
         <v>260</v>
@@ -4679,20 +4670,18 @@
       <c r="D100" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E100" s="35"/>
+      <c r="E100" s="31"/>
       <c r="F100" s="26" t="s">
         <v>261</v>
       </c>
-      <c r="G100" s="25" t="s">
+      <c r="G100" s="25"/>
+    </row>
+    <row r="101" ht="15.75" hidden="1" spans="1:7">
+      <c r="A101" s="22">
+        <v>102</v>
+      </c>
+      <c r="B101" s="23" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="101" ht="15.75" spans="1:7">
-      <c r="A101" s="22">
-        <v>101</v>
-      </c>
-      <c r="B101" s="23" t="s">
-        <v>263</v>
       </c>
       <c r="C101" s="23" t="s">
         <v>8</v>
@@ -4700,15 +4689,17 @@
       <c r="D101" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E101" s="31"/>
-      <c r="F101" s="26" t="s">
+      <c r="E101" s="35"/>
+      <c r="F101" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="G101" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="G101" s="25"/>
-    </row>
-    <row r="102" ht="15.75" spans="1:7">
+    </row>
+    <row r="102" ht="15.75" hidden="1" spans="1:7">
       <c r="A102" s="22">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B102" s="23" t="s">
         <v>265</v>
@@ -4719,7 +4710,9 @@
       <c r="D102" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E102" s="35"/>
+      <c r="E102" s="22" t="s">
+        <v>134</v>
+      </c>
       <c r="F102" s="32" t="s">
         <v>266</v>
       </c>
@@ -4727,9 +4720,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="103" ht="15.75" spans="1:7">
+    <row r="103" ht="15.75" hidden="1" spans="1:7">
       <c r="A103" s="22">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B103" s="23" t="s">
         <v>268</v>
@@ -4740,9 +4733,7 @@
       <c r="D103" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E103" s="22" t="s">
-        <v>134</v>
-      </c>
+      <c r="E103" s="35"/>
       <c r="F103" s="32" t="s">
         <v>269</v>
       </c>
@@ -4750,9 +4741,9 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" ht="15.75" spans="1:7">
+    <row r="104" ht="15.75" hidden="1" spans="1:7">
       <c r="A104" s="22">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B104" s="23" t="s">
         <v>271</v>
@@ -4763,17 +4754,19 @@
       <c r="D104" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E104" s="35"/>
+      <c r="E104" s="22" t="s">
+        <v>138</v>
+      </c>
       <c r="F104" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="G104" s="25" t="s">
+      <c r="G104" s="55" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="105" ht="15.75" spans="1:7">
+    <row r="105" ht="15.75" hidden="1" spans="1:7">
       <c r="A105" s="22">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B105" s="23" t="s">
         <v>274</v>
@@ -4785,18 +4778,16 @@
         <v>125</v>
       </c>
       <c r="E105" s="22" t="s">
-        <v>138</v>
+        <v>275</v>
       </c>
       <c r="F105" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="G105" s="56" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="106" ht="15.75" spans="1:7">
+      <c r="G105" s="25"/>
+    </row>
+    <row r="106" ht="15.75" hidden="1" spans="1:7">
       <c r="A106" s="22">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B106" s="23" t="s">
         <v>277</v>
@@ -4804,366 +4795,366 @@
       <c r="C106" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D106" s="22" t="s">
+      <c r="D106" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E106" s="22" t="s">
+      <c r="E106" s="46"/>
+      <c r="F106" s="47" t="s">
         <v>278</v>
       </c>
-      <c r="F106" s="32" t="s">
+      <c r="G106" s="27"/>
+    </row>
+    <row r="107" ht="15.75" hidden="1" spans="1:7">
+      <c r="A107" s="22">
+        <v>108</v>
+      </c>
+      <c r="B107" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="G106" s="25"/>
-    </row>
-    <row r="107" ht="15.75" spans="1:7">
-      <c r="A107" s="22">
-        <v>107</v>
-      </c>
-      <c r="B107" s="23" t="s">
+      <c r="C107" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E107" s="46"/>
+      <c r="F107" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C107" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="44" t="s">
+      <c r="G107" s="27"/>
+    </row>
+    <row r="108" ht="31.5" hidden="1" spans="1:7">
+      <c r="A108" s="22">
+        <v>109</v>
+      </c>
+      <c r="B108" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="C108" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E107" s="45"/>
-      <c r="F107" s="46" t="s">
-        <v>281</v>
-      </c>
-      <c r="G107" s="27"/>
-    </row>
-    <row r="108" ht="15.75" spans="1:7">
-      <c r="A108" s="22">
-        <v>108</v>
-      </c>
-      <c r="B108" s="23" t="s">
+      <c r="E108" s="46"/>
+      <c r="F108" s="47" t="s">
         <v>282</v>
       </c>
-      <c r="C108" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D108" s="44" t="s">
+      <c r="G108" s="27"/>
+    </row>
+    <row r="109" ht="15.75" hidden="1" spans="1:7">
+      <c r="A109" s="22">
+        <v>110</v>
+      </c>
+      <c r="B109" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="C109" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E108" s="45"/>
-      <c r="F108" s="46" t="s">
-        <v>283</v>
-      </c>
-      <c r="G108" s="27"/>
-    </row>
-    <row r="109" ht="31.5" spans="1:7">
-      <c r="A109" s="22">
-        <v>109</v>
-      </c>
-      <c r="B109" s="23" t="s">
+      <c r="E109" s="46"/>
+      <c r="F109" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C109" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="44" t="s">
+      <c r="G109" s="27"/>
+    </row>
+    <row r="110" ht="31.5" hidden="1" spans="1:7">
+      <c r="A110" s="22">
+        <v>111</v>
+      </c>
+      <c r="B110" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="C110" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E109" s="45"/>
-      <c r="F109" s="46" t="s">
-        <v>285</v>
-      </c>
-      <c r="G109" s="27"/>
-    </row>
-    <row r="110" ht="15.75" spans="1:7">
-      <c r="A110" s="22">
-        <v>110</v>
-      </c>
-      <c r="B110" s="23" t="s">
+      <c r="E110" s="46"/>
+      <c r="F110" s="47" t="s">
         <v>286</v>
       </c>
-      <c r="C110" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="44" t="s">
+      <c r="G110" s="27"/>
+    </row>
+    <row r="111" ht="15.75" hidden="1" spans="1:7">
+      <c r="A111" s="22">
+        <v>112</v>
+      </c>
+      <c r="B111" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="C111" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E110" s="45"/>
-      <c r="F110" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="G110" s="27"/>
-    </row>
-    <row r="111" ht="31.5" spans="1:7">
-      <c r="A111" s="22">
-        <v>111</v>
-      </c>
-      <c r="B111" s="23" t="s">
+      <c r="E111" s="46"/>
+      <c r="F111" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="C111" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="44" t="s">
+      <c r="G111" s="27"/>
+    </row>
+    <row r="112" ht="15.75" hidden="1" spans="1:7">
+      <c r="A112" s="22">
+        <v>113</v>
+      </c>
+      <c r="B112" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="C112" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E111" s="45"/>
-      <c r="F111" s="46" t="s">
-        <v>289</v>
-      </c>
-      <c r="G111" s="27"/>
-    </row>
-    <row r="112" ht="15.75" spans="1:7">
-      <c r="A112" s="22">
-        <v>112</v>
-      </c>
-      <c r="B112" s="23" t="s">
+      <c r="E112" s="46"/>
+      <c r="F112" s="47" t="s">
+        <v>272</v>
+      </c>
+      <c r="G112" s="27"/>
+    </row>
+    <row r="113" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
+      <c r="A113" s="22">
+        <v>114</v>
+      </c>
+      <c r="B113" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="C112" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="44" t="s">
+      <c r="C113" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E112" s="45"/>
-      <c r="F112" s="46" t="s">
+      <c r="E113" s="46"/>
+      <c r="F113" s="48" t="s">
         <v>291</v>
       </c>
-      <c r="G112" s="27"/>
-    </row>
-    <row r="113" ht="15.75" spans="1:7">
-      <c r="A113" s="22">
-        <v>113</v>
-      </c>
-      <c r="B113" s="23" t="s">
+      <c r="G113" s="27"/>
+    </row>
+    <row r="114" ht="15.75" hidden="1" spans="1:7">
+      <c r="A114" s="22">
+        <v>115</v>
+      </c>
+      <c r="B114" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="C113" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D113" s="44" t="s">
+      <c r="C114" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E113" s="45"/>
-      <c r="F113" s="46" t="s">
-        <v>275</v>
-      </c>
-      <c r="G113" s="27"/>
-    </row>
-    <row r="114" s="15" customFormat="1" ht="15.75" spans="1:7">
-      <c r="A114" s="22">
-        <v>114</v>
-      </c>
-      <c r="B114" s="23" t="s">
+      <c r="E114" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="F114" s="47" t="s">
         <v>293</v>
       </c>
-      <c r="C114" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="44" t="s">
+      <c r="G114" s="27"/>
+    </row>
+    <row r="115" ht="15.75" hidden="1" spans="1:7">
+      <c r="A115" s="22">
+        <v>116</v>
+      </c>
+      <c r="B115" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E114" s="45"/>
-      <c r="F114" s="47" t="s">
-        <v>294</v>
-      </c>
-      <c r="G114" s="27"/>
-    </row>
-    <row r="115" ht="15.75" spans="1:7">
-      <c r="A115" s="22">
-        <v>115</v>
-      </c>
-      <c r="B115" s="23" t="s">
+      <c r="E115" s="46"/>
+      <c r="F115" s="47" t="s">
         <v>295</v>
       </c>
-      <c r="C115" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="44" t="s">
+      <c r="G115" s="27"/>
+    </row>
+    <row r="116" ht="15.75" hidden="1" spans="1:7">
+      <c r="A116" s="22">
+        <v>117</v>
+      </c>
+      <c r="B116" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E115" s="44" t="s">
-        <v>138</v>
-      </c>
-      <c r="F115" s="46" t="s">
-        <v>296</v>
-      </c>
-      <c r="G115" s="27"/>
-    </row>
-    <row r="116" ht="15.75" spans="1:7">
-      <c r="A116" s="22">
-        <v>116</v>
-      </c>
-      <c r="B116" s="23" t="s">
+      <c r="E116" s="46"/>
+      <c r="F116" s="47" t="s">
         <v>297</v>
       </c>
-      <c r="C116" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="44" t="s">
+      <c r="G116" s="27"/>
+    </row>
+    <row r="117" ht="15.75" hidden="1" spans="1:7">
+      <c r="A117" s="22">
+        <v>118</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E116" s="45"/>
-      <c r="F116" s="46" t="s">
-        <v>298</v>
-      </c>
-      <c r="G116" s="27"/>
-    </row>
-    <row r="117" ht="15.75" spans="1:7">
-      <c r="A117" s="22">
-        <v>117</v>
-      </c>
-      <c r="B117" s="23" t="s">
+      <c r="E117" s="46"/>
+      <c r="F117" s="47" t="s">
         <v>299</v>
       </c>
-      <c r="C117" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D117" s="44" t="s">
+      <c r="G117" s="27"/>
+    </row>
+    <row r="118" ht="15.75" hidden="1" spans="1:7">
+      <c r="A118" s="22">
+        <v>119</v>
+      </c>
+      <c r="B118" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E117" s="45"/>
-      <c r="F117" s="46" t="s">
-        <v>300</v>
-      </c>
-      <c r="G117" s="27"/>
-    </row>
-    <row r="118" ht="15.75" spans="1:7">
-      <c r="A118" s="22">
-        <v>118</v>
-      </c>
-      <c r="B118" s="23" t="s">
+      <c r="E118" s="46"/>
+      <c r="F118" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="C118" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="44" t="s">
+      <c r="G118" s="27"/>
+    </row>
+    <row r="119" ht="15.75" hidden="1" spans="1:7">
+      <c r="A119" s="22">
+        <v>120</v>
+      </c>
+      <c r="B119" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="C119" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E118" s="45"/>
-      <c r="F118" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="G118" s="27"/>
-    </row>
-    <row r="119" ht="15.75" spans="1:7">
-      <c r="A119" s="22">
-        <v>119</v>
-      </c>
-      <c r="B119" s="23" t="s">
+      <c r="E119" s="46"/>
+      <c r="F119" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="C119" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="44" t="s">
+      <c r="G119" s="27"/>
+    </row>
+    <row r="120" ht="15.75" hidden="1" spans="1:7">
+      <c r="A120" s="22">
+        <v>121</v>
+      </c>
+      <c r="B120" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="C120" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E119" s="45"/>
-      <c r="F119" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="G119" s="27"/>
-    </row>
-    <row r="120" ht="15.75" spans="1:7">
-      <c r="A120" s="22">
-        <v>120</v>
-      </c>
-      <c r="B120" s="23" t="s">
+      <c r="E120" s="46"/>
+      <c r="F120" s="47" t="s">
         <v>305</v>
       </c>
-      <c r="C120" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" s="44" t="s">
+      <c r="G120" s="27"/>
+    </row>
+    <row r="121" ht="15.75" hidden="1" spans="1:7">
+      <c r="A121" s="22">
+        <v>122</v>
+      </c>
+      <c r="B121" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="C121" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E120" s="45"/>
-      <c r="F120" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="G120" s="27"/>
-    </row>
-    <row r="121" ht="15.75" spans="1:7">
-      <c r="A121" s="22">
-        <v>121</v>
-      </c>
-      <c r="B121" s="23" t="s">
+      <c r="E121" s="46"/>
+      <c r="F121" s="47" t="s">
         <v>307</v>
       </c>
-      <c r="C121" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="44" t="s">
+      <c r="G121" s="49"/>
+    </row>
+    <row r="122" ht="15.75" hidden="1" spans="1:7">
+      <c r="A122" s="22">
+        <v>123</v>
+      </c>
+      <c r="B122" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="C122" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E121" s="45"/>
-      <c r="F121" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="G121" s="27"/>
-    </row>
-    <row r="122" ht="15.75" spans="1:7">
-      <c r="A122" s="22">
-        <v>122</v>
-      </c>
-      <c r="B122" s="23" t="s">
+      <c r="E122" s="46"/>
+      <c r="F122" s="47" t="s">
         <v>309</v>
       </c>
-      <c r="C122" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D122" s="44" t="s">
+      <c r="G122" s="27"/>
+    </row>
+    <row r="123" ht="15.75" hidden="1" spans="1:7">
+      <c r="A123" s="22">
+        <v>124</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="C123" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="E122" s="45"/>
-      <c r="F122" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="G122" s="48"/>
-    </row>
-    <row r="123" ht="15.75" spans="1:7">
-      <c r="A123" s="22">
-        <v>123</v>
-      </c>
-      <c r="B123" s="23" t="s">
+      <c r="E123" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="47" t="s">
         <v>311</v>
       </c>
-      <c r="C123" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="44" t="s">
+      <c r="G123" s="27"/>
+    </row>
+    <row r="124" ht="31.5" hidden="1" spans="1:7">
+      <c r="A124" s="22">
         <v>125</v>
       </c>
-      <c r="E123" s="45"/>
-      <c r="F123" s="46" t="s">
+      <c r="B124" s="23" t="s">
         <v>312</v>
       </c>
-      <c r="G123" s="27"/>
-    </row>
-    <row r="124" ht="15.75" spans="1:7">
-      <c r="A124" s="22">
-        <v>124</v>
-      </c>
-      <c r="B124" s="23" t="s">
+      <c r="C124" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C124" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D124" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="E124" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F124" s="46" t="s">
+      <c r="E124" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F124" s="47" t="s">
         <v>314</v>
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" ht="31.5" spans="1:7">
+    <row r="125" ht="15.75" hidden="1" spans="1:7">
       <c r="A125" s="22">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B125" s="23" t="s">
         <v>315</v>
@@ -5171,81 +5162,83 @@
       <c r="C125" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="44" t="s">
+      <c r="D125" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E125" s="46"/>
+      <c r="F125" s="47" t="s">
         <v>316</v>
       </c>
-      <c r="E125" s="44" t="s">
+      <c r="G125" s="27"/>
+    </row>
+    <row r="126" ht="15.75" hidden="1" spans="1:7">
+      <c r="A126" s="22">
+        <v>127</v>
+      </c>
+      <c r="B126" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="F125" s="46" t="s">
-        <v>317</v>
-      </c>
-      <c r="G125" s="27"/>
-    </row>
-    <row r="126" ht="15.75" spans="1:7">
-      <c r="A126" s="22">
-        <v>126</v>
-      </c>
-      <c r="B126" s="23" t="s">
+      <c r="F126" s="47" t="s">
         <v>318</v>
       </c>
-      <c r="C126" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="E126" s="45"/>
-      <c r="F126" s="46" t="s">
+      <c r="G126" s="27"/>
+    </row>
+    <row r="127" ht="15.75" hidden="1" spans="1:7">
+      <c r="A127" s="22">
+        <v>128</v>
+      </c>
+      <c r="B127" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="G126" s="27"/>
-    </row>
-    <row r="127" ht="15.75" spans="1:7">
-      <c r="A127" s="22">
-        <v>127</v>
-      </c>
-      <c r="B127" s="23" t="s">
+      <c r="C127" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F127" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="C127" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" s="44" t="s">
+      <c r="G127" s="27"/>
+    </row>
+    <row r="128" ht="15.75" hidden="1" spans="1:7">
+      <c r="A128" s="22">
+        <v>129</v>
+      </c>
+      <c r="B128" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="C128" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E127" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="F127" s="46" t="s">
-        <v>321</v>
-      </c>
-      <c r="G127" s="27"/>
-    </row>
-    <row r="128" ht="15.75" spans="1:7">
-      <c r="A128" s="22">
-        <v>128</v>
-      </c>
-      <c r="B128" s="23" t="s">
+      <c r="E128" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" s="50" t="s">
         <v>322</v>
       </c>
-      <c r="C128" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="F128" s="46" t="s">
+      <c r="G128" s="54" t="s">
         <v>323</v>
       </c>
-      <c r="G128" s="27"/>
-    </row>
-    <row r="129" ht="15.75" spans="1:7">
+    </row>
+    <row r="129" ht="15.75" hidden="1" spans="1:7">
       <c r="A129" s="22">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B129" s="23" t="s">
         <v>324</v>
@@ -5253,45 +5246,45 @@
       <c r="C129" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D129" s="44" t="s">
+      <c r="D129" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E129" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F129" s="51" t="s">
+        <v>325</v>
+      </c>
+      <c r="G129" s="56" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" hidden="1" spans="1:7">
+      <c r="A130" s="22">
+        <v>131</v>
+      </c>
+      <c r="B130" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="C130" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E129" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F129" s="49" t="s">
-        <v>325</v>
-      </c>
-      <c r="G129" s="55" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" spans="1:7">
-      <c r="A130" s="22">
-        <v>130</v>
-      </c>
-      <c r="B130" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="C130" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D130" s="16" t="s">
-        <v>125</v>
-      </c>
       <c r="E130" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F130" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F130" s="43" t="s">
         <v>328</v>
       </c>
-      <c r="G130" s="57" t="s">
+      <c r="G130" s="56" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="131" ht="15.75" spans="1:7">
+    <row r="131" ht="15.75" hidden="1" spans="1:7">
       <c r="A131" s="22">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B131" s="17" t="s">
         <v>330</v>
@@ -5300,24 +5293,24 @@
         <v>8</v>
       </c>
       <c r="D131" s="16" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="E131" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F131" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="F131" s="51" t="s">
         <v>331</v>
       </c>
-      <c r="G131" s="57" t="s">
+      <c r="G131" s="56" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="132" ht="15.75" spans="1:7">
+    <row r="132" ht="15.75" hidden="1" spans="1:7">
       <c r="A132" s="22">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>8</v>
@@ -5328,59 +5321,59 @@
       <c r="E132" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F132" s="50" t="s">
+      <c r="F132" s="51" t="s">
+        <v>309</v>
+      </c>
+      <c r="G132" s="56" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" hidden="1" spans="1:7">
+      <c r="A133" s="22">
+        <v>134</v>
+      </c>
+      <c r="B133" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="G132" s="57" t="s">
+      <c r="C133" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E133" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F133" s="17" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="133" ht="15.75" spans="1:7">
-      <c r="A133" s="22">
-        <v>133</v>
-      </c>
-      <c r="B133" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="C133" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D133" s="16" t="s">
+    <row r="134" ht="15.75" hidden="1" spans="1:7">
+      <c r="A134" s="22">
+        <v>135</v>
+      </c>
+      <c r="B134" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="C134" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="E133" s="16" t="s">
+      <c r="E134" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F133" s="50" t="s">
-        <v>312</v>
-      </c>
-      <c r="G133" s="57" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" spans="1:7">
-      <c r="A134" s="22">
-        <v>134</v>
-      </c>
-      <c r="B134" s="17" t="s">
+      <c r="F134" s="51" t="s">
         <v>337</v>
       </c>
-      <c r="C134" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D134" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E134" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F134" s="17" t="s">
+      <c r="G134" s="51" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="135" ht="15.75" spans="1:7">
+    <row r="135" ht="15.75" hidden="1" spans="1:7">
       <c r="A135" s="22">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B135" s="17" t="s">
         <v>339</v>
@@ -5394,16 +5387,16 @@
       <c r="E135" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F135" s="50" t="s">
+      <c r="F135" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="G135" s="50" t="s">
+      <c r="G135" s="56" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="136" ht="15.75" spans="1:7">
+    <row r="136" ht="15.75" hidden="1" spans="1:7">
       <c r="A136" s="22">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B136" s="17" t="s">
         <v>342</v>
@@ -5417,18 +5410,18 @@
       <c r="E136" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F136" s="50" t="s">
+      <c r="F136" s="51" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="57" t="s">
+      <c r="G136" s="56" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="137" ht="15.75" spans="1:7">
+    <row r="137" ht="15.75" hidden="1" spans="1:7">
       <c r="A137" s="22">
-        <v>137</v>
-      </c>
-      <c r="B137" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="B137" s="23" t="s">
         <v>345</v>
       </c>
       <c r="C137" s="23" t="s">
@@ -5440,39 +5433,36 @@
       <c r="E137" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F137" s="50" t="s">
+      <c r="F137" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="G137" s="57" t="s">
+      <c r="G137" s="56" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="138" ht="15.75" spans="1:7">
+    <row r="138" ht="15.75" hidden="1" spans="1:7">
       <c r="A138" s="22">
-        <v>138</v>
-      </c>
-      <c r="B138" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B138" s="17" t="s">
         <v>348</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="16" t="s">
-        <v>125</v>
+        <v>9</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F138" s="50" t="s">
         <v>349</v>
       </c>
-      <c r="G138" s="57" t="s">
+      <c r="F138" s="51" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="139" ht="15.75" spans="1:7">
+    <row r="139" ht="15.75" hidden="1" spans="1:7">
       <c r="A139" s="22">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B139" s="17" t="s">
         <v>351</v>
@@ -5481,18 +5471,21 @@
         <v>8</v>
       </c>
       <c r="D139" s="16" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="E139" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F139" s="52" t="s">
         <v>352</v>
       </c>
-      <c r="F139" s="50" t="s">
+      <c r="G139" s="57" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="140" ht="15.75" spans="1:7">
+    <row r="140" ht="15.75" hidden="1" spans="1:7">
       <c r="A140" s="22">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B140" s="17" t="s">
         <v>354</v>
@@ -5504,97 +5497,77 @@
         <v>125</v>
       </c>
       <c r="E140" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="F140" s="51" t="s">
+        <v>234</v>
+      </c>
+      <c r="F140" s="53" t="s">
         <v>355</v>
       </c>
-      <c r="G140" s="58" t="s">
+    </row>
+    <row r="141" ht="15.75" hidden="1" spans="1:7">
+      <c r="A141" s="22">
+        <v>142</v>
+      </c>
+      <c r="B141" s="17" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="141" ht="15.75" spans="1:7">
-      <c r="A141" s="22">
-        <v>141</v>
-      </c>
-      <c r="B141" s="17" t="s">
+      <c r="C141" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F141" s="53" t="s">
         <v>357</v>
       </c>
-      <c r="C141" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D141" s="16" t="s">
+    </row>
+    <row r="142" ht="31.5" hidden="1" spans="1:7">
+      <c r="A142" s="22">
+        <v>143</v>
+      </c>
+      <c r="B142" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="C142" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="22" t="s">
         <v>125</v>
       </c>
-      <c r="E141" s="16" t="s">
-        <v>237</v>
-      </c>
-      <c r="F141" s="52" t="s">
+      <c r="E142" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F142" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="G142" s="25" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" hidden="1" spans="1:7">
+      <c r="A143" s="22">
+        <v>144</v>
+      </c>
+      <c r="B143" s="23" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="142" ht="15.75" spans="1:7">
-      <c r="A142" s="22">
-        <v>142</v>
-      </c>
-      <c r="B142" s="17" t="s">
+      <c r="C143" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E143" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F143" s="53" t="s">
         <v>359</v>
       </c>
-      <c r="C142" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E142" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F142" s="52" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="143" ht="31.5" spans="1:7">
-      <c r="A143" s="22">
-        <v>143</v>
-      </c>
-      <c r="B143" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="C143" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E143" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="F143" s="32" t="s">
-        <v>196</v>
-      </c>
-      <c r="G143" s="25" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="144" ht="15.75" spans="1:7">
-      <c r="A144" s="22">
-        <v>144</v>
-      </c>
-      <c r="B144" s="53" t="s">
-        <v>361</v>
-      </c>
-      <c r="C144" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D144" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E144" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F144" s="54" t="s">
-        <v>362</v>
-      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="D144" s="17"/>
     </row>
     <row r="145" spans="4:4">
       <c r="D145" s="17"/>
@@ -8656,64 +8629,66 @@
     <row r="1164" spans="4:4">
       <c r="D1164" s="17"/>
     </row>
-    <row r="1165" spans="4:4">
-      <c r="D1165" s="17"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G144" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G143" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="BENSALEM RITEDJ INES"/>
+        <filter val="BENSALEM ABDELHAMID"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
     <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
     <hyperlink ref="F54" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
-    <hyperlink ref="F107" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
-    <hyperlink ref="F108" r:id="rId5" display="aliaissani97@gmail.com"/>
-    <hyperlink ref="F126" r:id="rId6" display="medzerdani@gmail.com"/>
-    <hyperlink ref="F123" r:id="rId7" display="turkibilal22@gmail.com"/>
-    <hyperlink ref="F122" r:id="rId8" display="sacihamza40@gmail.com"/>
-    <hyperlink ref="F121" r:id="rId9" display="Boba1620@hotmail.com"/>
-    <hyperlink ref="F97" r:id="rId10" display="khelifa-mir@outlook.fr"/>
-    <hyperlink ref="F78" r:id="rId11" display="fethi22miloua@gmail.com"/>
-    <hyperlink ref="F76" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
-    <hyperlink ref="F95" r:id="rId13" display="mehadjiameslem@gmail.com"/>
-    <hyperlink ref="F93" r:id="rId14" display="mekhalefleila@gmail.com"/>
-    <hyperlink ref="F92" r:id="rId15" display="khalidamet4@gmail.com"/>
-    <hyperlink ref="F120" r:id="rId16" display="layatimedi@gmail.com"/>
-    <hyperlink ref="F87" r:id="rId17" display="m_latreche@yahoo.com"/>
-    <hyperlink ref="F119" r:id="rId18" display="kadrirania51@gmail.com"/>
-    <hyperlink ref="F83" r:id="rId19" display="protoboy9999@gmail.com"/>
-    <hyperlink ref="F117" r:id="rId20" display="khadidjafezazi90@gmail"/>
-    <hyperlink ref="F77" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F74" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
-    <hyperlink ref="F69" r:id="rId23" display="douaaboularaf@gmail.com"/>
-    <hyperlink ref="F113" r:id="rId24" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F63" r:id="rId25" display="rawnakritedj@gmail.com" tooltip="mailto:rawnakritedj@gmail.com"/>
-    <hyperlink ref="F111" r:id="rId26" display="bkbhbb22@gmail.com"/>
-    <hyperlink ref="F60" r:id="rId27" display="bendida65@gmail.com"/>
-    <hyperlink ref="F59" r:id="rId28" display="sarrabencella@gmail.com"/>
-    <hyperlink ref="F61" r:id="rId29" display="ri123hab@gmail.com"/>
-    <hyperlink ref="F110" r:id="rId30" display="meriembelabed5@gmail.com"/>
-    <hyperlink ref="F45" r:id="rId31" display="rezoug.med@gmail.com"/>
-    <hyperlink ref="F86" r:id="rId32" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
-    <hyperlink ref="F58" r:id="rId33" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
-    <hyperlink ref="F102" r:id="rId34" display="zarebmohammedamine@gmail.com"/>
-    <hyperlink ref="F103" r:id="rId35" display="djamel71ziani@gmail.com"/>
-    <hyperlink ref="F67" r:id="rId36" display="ahmedboudali32@gmail.com"/>
-    <hyperlink ref="F71" r:id="rId37" display="chaouche.abdallah@gmail.com"/>
-    <hyperlink ref="F62" r:id="rId38" display="lakhdar_belhallouche@hotmail.fr"/>
-    <hyperlink ref="F82" r:id="rId39" display="ahmed.hadji22@yahoo.com"/>
-    <hyperlink ref="F105" r:id="rId40" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F32" r:id="rId41" display="khatir.mohamed1977@gmail.com"/>
-    <hyperlink ref="F2" r:id="rId42" display="irecom_abid@yahoo.fr"/>
-    <hyperlink ref="F7" r:id="rId43" display="karis483@hotmail.fr"/>
-    <hyperlink ref="F8" r:id="rId44" display="bahlilmounir@yahoo.fr"/>
-    <hyperlink ref="F10" r:id="rId45" display="beddadboucif@gmail.com"/>
-    <hyperlink ref="F9" r:id="rId46" display="seyfeddine.electrotechnique@gmail.com"/>
-    <hyperlink ref="F129" r:id="rId47" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
-    <hyperlink ref="F114" r:id="rId48" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
-    <hyperlink ref="F143" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F144" r:id="rId49" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
+    <hyperlink ref="F106" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
+    <hyperlink ref="F107" r:id="rId5" display="aliaissani97@gmail.com"/>
+    <hyperlink ref="F125" r:id="rId6" display="medzerdani@gmail.com"/>
+    <hyperlink ref="F122" r:id="rId7" display="turkibilal22@gmail.com"/>
+    <hyperlink ref="F121" r:id="rId8" display="sacihamza40@gmail.com"/>
+    <hyperlink ref="F120" r:id="rId9" display="Boba1620@hotmail.com"/>
+    <hyperlink ref="F96" r:id="rId10" display="khelifa-mir@outlook.fr"/>
+    <hyperlink ref="F77" r:id="rId11" display="fethi22miloua@gmail.com"/>
+    <hyperlink ref="F75" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
+    <hyperlink ref="F94" r:id="rId13" display="mehadjiameslem@gmail.com"/>
+    <hyperlink ref="F92" r:id="rId14" display="mekhalefleila@gmail.com"/>
+    <hyperlink ref="F91" r:id="rId15" display="khalidamet4@gmail.com"/>
+    <hyperlink ref="F119" r:id="rId16" display="layatimedi@gmail.com"/>
+    <hyperlink ref="F86" r:id="rId17" display="m_latreche@yahoo.com"/>
+    <hyperlink ref="F118" r:id="rId18" display="kadrirania51@gmail.com"/>
+    <hyperlink ref="F82" r:id="rId19" display="protoboy9999@gmail.com"/>
+    <hyperlink ref="F116" r:id="rId20" display="khadidjafezazi90@gmail"/>
+    <hyperlink ref="F76" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F73" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F68" r:id="rId23" display="douaaboularaf@gmail.com"/>
+    <hyperlink ref="F112" r:id="rId24" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F110" r:id="rId25" display="bkbhbb22@gmail.com"/>
+    <hyperlink ref="F60" r:id="rId26" display="bendida65@gmail.com"/>
+    <hyperlink ref="F59" r:id="rId27" display="sarrabencella@gmail.com"/>
+    <hyperlink ref="F61" r:id="rId28" display="ri123hab@gmail.com"/>
+    <hyperlink ref="F109" r:id="rId29" display="meriembelabed5@gmail.com"/>
+    <hyperlink ref="F45" r:id="rId30" display="rezoug.med@gmail.com"/>
+    <hyperlink ref="F85" r:id="rId31" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
+    <hyperlink ref="F58" r:id="rId32" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
+    <hyperlink ref="F101" r:id="rId33" display="zarebmohammedamine@gmail.com"/>
+    <hyperlink ref="F102" r:id="rId34" display="djamel71ziani@gmail.com"/>
+    <hyperlink ref="F66" r:id="rId35" display="ahmedboudali32@gmail.com"/>
+    <hyperlink ref="F70" r:id="rId36" display="chaouche.abdallah@gmail.com"/>
+    <hyperlink ref="F62" r:id="rId37" display="lakhdar_belhallouche@hotmail.fr"/>
+    <hyperlink ref="F81" r:id="rId38" display="ahmed.hadji22@yahoo.com"/>
+    <hyperlink ref="F104" r:id="rId39" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F32" r:id="rId40" display="khatir.mohamed1977@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId41" display="irecom_abid@yahoo.fr"/>
+    <hyperlink ref="F7" r:id="rId42" display="karis483@hotmail.fr"/>
+    <hyperlink ref="F8" r:id="rId43" display="bahlilmounir@yahoo.fr"/>
+    <hyperlink ref="F10" r:id="rId44" display="beddadboucif@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId45" display="seyfeddine.electrotechnique@gmail.com"/>
+    <hyperlink ref="F128" r:id="rId46" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F113" r:id="rId47" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F142" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F143" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8736,202 +8711,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>367</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>375</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="400">
   <si>
     <t>N°</t>
   </si>
@@ -1112,6 +1112,12 @@
   </si>
   <si>
     <t>n_benseddik@yahoo.fr</t>
+  </si>
+  <si>
+    <t>YAMANI MASSIM</t>
+  </si>
+  <si>
+    <t>yamanimassim@yahoo.fr</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2524,7 +2530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G1164"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
@@ -2561,7 +2567,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" spans="1:7">
+    <row r="2" ht="15.75" spans="1:7">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -2582,7 +2588,7 @@
       </c>
       <c r="G2" s="25"/>
     </row>
-    <row r="3" ht="15.75" hidden="1" spans="1:7">
+    <row r="3" ht="15.75" spans="1:7">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -2603,7 +2609,7 @@
       </c>
       <c r="G3" s="25"/>
     </row>
-    <row r="4" ht="15.75" hidden="1" spans="1:7">
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -2624,7 +2630,7 @@
       </c>
       <c r="G4" s="25"/>
     </row>
-    <row r="5" ht="15.75" hidden="1" spans="1:7">
+    <row r="5" ht="15.75" spans="1:7">
       <c r="A5" s="22">
         <v>4</v>
       </c>
@@ -2645,7 +2651,7 @@
       </c>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" ht="15.75" hidden="1" spans="1:7">
+    <row r="6" ht="15.75" spans="1:7">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -2666,7 +2672,7 @@
       </c>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" ht="15.75" hidden="1" spans="1:7">
+    <row r="7" ht="15.75" spans="1:7">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -2689,7 +2695,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" hidden="1" spans="1:7">
+    <row r="8" ht="15.75" spans="1:7">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -2712,7 +2718,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" hidden="1" spans="1:7">
+    <row r="9" ht="15.75" spans="1:7">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -2733,7 +2739,7 @@
       </c>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" ht="15.75" hidden="1" spans="1:7">
+    <row r="10" ht="15.75" spans="1:7">
       <c r="A10" s="22">
         <v>9</v>
       </c>
@@ -2756,7 +2762,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" hidden="1" spans="1:7">
+    <row r="11" ht="15.75" spans="1:7">
       <c r="A11" s="22">
         <v>10</v>
       </c>
@@ -2777,7 +2783,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" ht="15.75" hidden="1" spans="1:7">
+    <row r="12" ht="15.75" spans="1:7">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -2798,7 +2804,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" ht="15.75" hidden="1" spans="1:7">
+    <row r="13" ht="15.75" spans="1:7">
       <c r="A13" s="22">
         <v>12</v>
       </c>
@@ -2819,7 +2825,7 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" ht="15.75" hidden="1" spans="1:7">
+    <row r="14" ht="15.75" spans="1:7">
       <c r="A14" s="22">
         <v>13</v>
       </c>
@@ -2840,7 +2846,7 @@
       </c>
       <c r="G14" s="25"/>
     </row>
-    <row r="15" ht="15.75" hidden="1" spans="1:7">
+    <row r="15" ht="15.75" spans="1:7">
       <c r="A15" s="22">
         <v>14</v>
       </c>
@@ -2861,7 +2867,7 @@
       </c>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" ht="31.5" hidden="1" spans="1:7">
+    <row r="16" ht="31.5" spans="1:7">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -2882,7 +2888,7 @@
       </c>
       <c r="G16" s="25"/>
     </row>
-    <row r="17" ht="15.75" hidden="1" spans="1:7">
+    <row r="17" ht="15.75" spans="1:7">
       <c r="A17" s="22">
         <v>16</v>
       </c>
@@ -2903,7 +2909,7 @@
       </c>
       <c r="G17" s="25"/>
     </row>
-    <row r="18" ht="15.75" hidden="1" spans="1:7">
+    <row r="18" ht="15.75" spans="1:7">
       <c r="A18" s="22">
         <v>17</v>
       </c>
@@ -2924,7 +2930,7 @@
       </c>
       <c r="G18" s="25"/>
     </row>
-    <row r="19" ht="15.75" hidden="1" spans="1:7">
+    <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="22">
         <v>18</v>
       </c>
@@ -2945,7 +2951,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" ht="31.5" hidden="1" spans="1:7">
+    <row r="20" ht="31.5" spans="1:7">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -2966,7 +2972,7 @@
       </c>
       <c r="G20" s="25"/>
     </row>
-    <row r="21" ht="15.75" hidden="1" spans="1:7">
+    <row r="21" ht="15.75" spans="1:7">
       <c r="A21" s="22">
         <v>20</v>
       </c>
@@ -2987,7 +2993,7 @@
       </c>
       <c r="G21" s="25"/>
     </row>
-    <row r="22" ht="15.75" hidden="1" spans="1:7">
+    <row r="22" ht="15.75" spans="1:7">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -3008,7 +3014,7 @@
       </c>
       <c r="G22" s="25"/>
     </row>
-    <row r="23" ht="15.75" hidden="1" spans="1:7">
+    <row r="23" ht="15.75" spans="1:7">
       <c r="A23" s="22">
         <v>22</v>
       </c>
@@ -3029,7 +3035,7 @@
       </c>
       <c r="G23" s="25"/>
     </row>
-    <row r="24" ht="15.75" hidden="1" spans="1:7">
+    <row r="24" ht="15.75" spans="1:7">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -3050,7 +3056,7 @@
       </c>
       <c r="G24" s="25"/>
     </row>
-    <row r="25" ht="15.75" hidden="1" spans="1:7">
+    <row r="25" ht="15.75" spans="1:7">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -3071,7 +3077,7 @@
       </c>
       <c r="G25" s="25"/>
     </row>
-    <row r="26" ht="31.5" hidden="1" spans="1:7">
+    <row r="26" ht="31.5" spans="1:7">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -3092,7 +3098,7 @@
       </c>
       <c r="G26" s="25"/>
     </row>
-    <row r="27" ht="15.75" hidden="1" spans="1:7">
+    <row r="27" ht="15.75" spans="1:7">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -3113,7 +3119,7 @@
       </c>
       <c r="G27" s="25"/>
     </row>
-    <row r="28" ht="15.75" hidden="1" spans="1:7">
+    <row r="28" ht="15.75" spans="1:7">
       <c r="A28" s="22">
         <v>27</v>
       </c>
@@ -3134,7 +3140,7 @@
       </c>
       <c r="G28" s="25"/>
     </row>
-    <row r="29" ht="15.75" hidden="1" spans="1:7">
+    <row r="29" ht="15.75" spans="1:7">
       <c r="A29" s="22">
         <v>28</v>
       </c>
@@ -3155,7 +3161,7 @@
       </c>
       <c r="G29" s="25"/>
     </row>
-    <row r="30" ht="15.75" hidden="1" spans="1:7">
+    <row r="30" ht="15.75" spans="1:7">
       <c r="A30" s="22">
         <v>29</v>
       </c>
@@ -3176,7 +3182,7 @@
       </c>
       <c r="G30" s="25"/>
     </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
+    <row r="31" ht="15.75" spans="1:7">
       <c r="A31" s="22">
         <v>30</v>
       </c>
@@ -3197,7 +3203,7 @@
       </c>
       <c r="G31" s="25"/>
     </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
+    <row r="32" ht="15.75" spans="1:7">
       <c r="A32" s="22">
         <v>31</v>
       </c>
@@ -3218,7 +3224,7 @@
       </c>
       <c r="G32" s="25"/>
     </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
+    <row r="33" ht="15.75" spans="1:7">
       <c r="A33" s="22">
         <v>32</v>
       </c>
@@ -3239,7 +3245,7 @@
       </c>
       <c r="G33" s="25"/>
     </row>
-    <row r="34" ht="15.75" hidden="1" spans="1:7">
+    <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="22">
         <v>34</v>
       </c>
@@ -3260,7 +3266,7 @@
       </c>
       <c r="G34" s="25"/>
     </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
+    <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="22">
         <v>35</v>
       </c>
@@ -3281,7 +3287,7 @@
       </c>
       <c r="G35" s="25"/>
     </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
+    <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="22">
         <v>36</v>
       </c>
@@ -3304,7 +3310,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="22">
         <v>37</v>
       </c>
@@ -3325,7 +3331,7 @@
       </c>
       <c r="G37" s="25"/>
     </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
+    <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="22">
         <v>38</v>
       </c>
@@ -3348,7 +3354,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="31.5" hidden="1" spans="1:7">
+    <row r="39" ht="31.5" spans="1:7">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -3369,7 +3375,7 @@
       </c>
       <c r="G39" s="25"/>
     </row>
-    <row r="40" ht="15.75" hidden="1" spans="1:7">
+    <row r="40" ht="15.75" spans="1:7">
       <c r="A40" s="22">
         <v>40</v>
       </c>
@@ -3390,7 +3396,7 @@
       </c>
       <c r="G40" s="25"/>
     </row>
-    <row r="41" ht="15.75" hidden="1" spans="1:7">
+    <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="22">
         <v>41</v>
       </c>
@@ -3411,7 +3417,7 @@
       </c>
       <c r="G41" s="25"/>
     </row>
-    <row r="42" ht="15.75" hidden="1" spans="1:7">
+    <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="22">
         <v>42</v>
       </c>
@@ -3432,7 +3438,7 @@
       </c>
       <c r="G42" s="25"/>
     </row>
-    <row r="43" ht="15.75" hidden="1" spans="1:7">
+    <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="22">
         <v>43</v>
       </c>
@@ -3453,7 +3459,7 @@
       </c>
       <c r="G43" s="25"/>
     </row>
-    <row r="44" ht="15.75" hidden="1" spans="1:7">
+    <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="22">
         <v>44</v>
       </c>
@@ -3474,7 +3480,7 @@
       </c>
       <c r="G44" s="25"/>
     </row>
-    <row r="45" ht="15.75" hidden="1" spans="1:7">
+    <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="22">
         <v>45</v>
       </c>
@@ -3495,7 +3501,7 @@
       </c>
       <c r="G45" s="25"/>
     </row>
-    <row r="46" ht="15.75" hidden="1" spans="1:7">
+    <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="22">
         <v>46</v>
       </c>
@@ -3516,7 +3522,7 @@
       </c>
       <c r="G46" s="25"/>
     </row>
-    <row r="47" ht="15.75" hidden="1" spans="1:7">
+    <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="22">
         <v>47</v>
       </c>
@@ -3537,7 +3543,7 @@
       </c>
       <c r="G47" s="25"/>
     </row>
-    <row r="48" ht="15.75" hidden="1" spans="1:7">
+    <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="22">
         <v>48</v>
       </c>
@@ -3558,7 +3564,7 @@
       </c>
       <c r="G48" s="25"/>
     </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
+    <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="22">
         <v>49</v>
       </c>
@@ -3579,7 +3585,7 @@
       </c>
       <c r="G49" s="25"/>
     </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
+    <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="22">
         <v>50</v>
       </c>
@@ -3600,7 +3606,7 @@
       </c>
       <c r="G50" s="25"/>
     </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
+    <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="22">
         <v>51</v>
       </c>
@@ -3621,7 +3627,7 @@
       </c>
       <c r="G51" s="25"/>
     </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
+    <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="22">
         <v>52</v>
       </c>
@@ -3644,7 +3650,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
+    <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="22">
         <v>53</v>
       </c>
@@ -3665,7 +3671,7 @@
       </c>
       <c r="G53" s="25"/>
     </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
+    <row r="54" ht="15.75" spans="1:7">
       <c r="A54" s="22">
         <v>54</v>
       </c>
@@ -3688,7 +3694,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
+    <row r="55" ht="15.75" spans="1:7">
       <c r="A55" s="22">
         <v>55</v>
       </c>
@@ -3709,7 +3715,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
+    <row r="56" ht="15.75" spans="1:7">
       <c r="A56" s="22">
         <v>56</v>
       </c>
@@ -3726,7 +3732,7 @@
       <c r="F56" s="34"/>
       <c r="G56" s="25"/>
     </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
+    <row r="57" ht="15.75" spans="1:7">
       <c r="A57" s="22">
         <v>57</v>
       </c>
@@ -3749,7 +3755,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
+    <row r="58" ht="15.75" spans="1:7">
       <c r="A58" s="22">
         <v>58</v>
       </c>
@@ -3772,7 +3778,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" ht="15.75" hidden="1" spans="1:7">
+    <row r="59" ht="15.75" spans="1:7">
       <c r="A59" s="22">
         <v>59</v>
       </c>
@@ -3795,7 +3801,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" ht="15.75" hidden="1" spans="1:7">
+    <row r="60" ht="15.75" spans="1:7">
       <c r="A60" s="22">
         <v>60</v>
       </c>
@@ -3818,7 +3824,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="61" ht="15.75" hidden="1" spans="1:7">
+    <row r="61" ht="15.75" spans="1:7">
       <c r="A61" s="22">
         <v>61</v>
       </c>
@@ -3839,7 +3845,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" ht="31.5" hidden="1" spans="1:7">
+    <row r="62" ht="31.5" spans="1:7">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -3883,7 +3889,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="64" ht="31.5" hidden="1" spans="1:7">
+    <row r="64" ht="31.5" spans="1:7">
       <c r="A64" s="22">
         <v>65</v>
       </c>
@@ -3904,7 +3910,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="65" ht="15.75" hidden="1" spans="1:7">
+    <row r="65" ht="15.75" spans="1:7">
       <c r="A65" s="22">
         <v>66</v>
       </c>
@@ -3925,7 +3931,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" ht="15.75" hidden="1" spans="1:7">
+    <row r="66" ht="15.75" spans="1:7">
       <c r="A66" s="22">
         <v>67</v>
       </c>
@@ -3946,7 +3952,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="67" ht="15.75" hidden="1" spans="1:7">
+    <row r="67" ht="15.75" spans="1:7">
       <c r="A67" s="22">
         <v>68</v>
       </c>
@@ -3969,7 +3975,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="68" ht="15.75" hidden="1" spans="1:7">
+    <row r="68" ht="15.75" spans="1:7">
       <c r="A68" s="22">
         <v>69</v>
       </c>
@@ -3990,7 +3996,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="69" ht="15.75" hidden="1" spans="1:7">
+    <row r="69" ht="15.75" spans="1:7">
       <c r="A69" s="22">
         <v>70</v>
       </c>
@@ -4011,7 +4017,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="70" ht="31.5" hidden="1" spans="1:7">
+    <row r="70" ht="31.5" spans="1:7">
       <c r="A70" s="22">
         <v>71</v>
       </c>
@@ -4032,7 +4038,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="71" ht="15.75" hidden="1" spans="1:7">
+    <row r="71" ht="15.75" spans="1:7">
       <c r="A71" s="22">
         <v>72</v>
       </c>
@@ -4053,7 +4059,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="72" ht="15.75" hidden="1" spans="1:7">
+    <row r="72" ht="15.75" spans="1:7">
       <c r="A72" s="22">
         <v>73</v>
       </c>
@@ -4076,7 +4082,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="73" ht="15.75" hidden="1" spans="1:7">
+    <row r="73" ht="15.75" spans="1:7">
       <c r="A73" s="22">
         <v>74</v>
       </c>
@@ -4097,7 +4103,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="74" ht="15.75" hidden="1" spans="1:7">
+    <row r="74" ht="15.75" spans="1:7">
       <c r="A74" s="22">
         <v>75</v>
       </c>
@@ -4120,7 +4126,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="75" ht="15.75" hidden="1" spans="1:7">
+    <row r="75" ht="15.75" spans="1:7">
       <c r="A75" s="22">
         <v>76</v>
       </c>
@@ -4141,7 +4147,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" ht="31.5" hidden="1" spans="1:7">
+    <row r="76" ht="31.5" spans="1:7">
       <c r="A76" s="22">
         <v>77</v>
       </c>
@@ -4164,7 +4170,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="77" ht="15.75" hidden="1" spans="1:7">
+    <row r="77" ht="15.75" spans="1:7">
       <c r="A77" s="22">
         <v>78</v>
       </c>
@@ -4183,7 +4189,7 @@
       </c>
       <c r="G77" s="25"/>
     </row>
-    <row r="78" ht="15.75" hidden="1" spans="1:7">
+    <row r="78" ht="15.75" spans="1:7">
       <c r="A78" s="22">
         <v>79</v>
       </c>
@@ -4206,7 +4212,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="79" ht="15.75" hidden="1" spans="1:7">
+    <row r="79" ht="15.75" spans="1:7">
       <c r="A79" s="22">
         <v>80</v>
       </c>
@@ -4229,7 +4235,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="80" ht="15.75" hidden="1" spans="1:7">
+    <row r="80" ht="15.75" spans="1:7">
       <c r="A80" s="22">
         <v>81</v>
       </c>
@@ -4250,7 +4256,7 @@
       </c>
       <c r="G80" s="25"/>
     </row>
-    <row r="81" ht="15.75" hidden="1" spans="1:7">
+    <row r="81" ht="15.75" spans="1:7">
       <c r="A81" s="22">
         <v>82</v>
       </c>
@@ -4271,7 +4277,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="82" ht="15.75" hidden="1" spans="1:7">
+    <row r="82" ht="15.75" spans="1:7">
       <c r="A82" s="22">
         <v>83</v>
       </c>
@@ -4294,7 +4300,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="83" ht="15.75" hidden="1" spans="1:7">
+    <row r="83" ht="15.75" spans="1:7">
       <c r="A83" s="22">
         <v>84</v>
       </c>
@@ -4313,7 +4319,7 @@
       </c>
       <c r="G83" s="25"/>
     </row>
-    <row r="84" ht="15.75" hidden="1" spans="1:7">
+    <row r="84" ht="15.75" spans="1:7">
       <c r="A84" s="22">
         <v>85</v>
       </c>
@@ -4336,7 +4342,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="85" ht="15.75" hidden="1" spans="1:7">
+    <row r="85" ht="15.75" spans="1:7">
       <c r="A85" s="22">
         <v>86</v>
       </c>
@@ -4355,7 +4361,7 @@
       </c>
       <c r="G85" s="25"/>
     </row>
-    <row r="86" ht="15.75" hidden="1" spans="1:7">
+    <row r="86" ht="15.75" spans="1:7">
       <c r="A86" s="22">
         <v>87</v>
       </c>
@@ -4376,7 +4382,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="87" ht="15.75" hidden="1" spans="1:7">
+    <row r="87" ht="15.75" spans="1:7">
       <c r="A87" s="22">
         <v>88</v>
       </c>
@@ -4397,7 +4403,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="88" ht="15.75" hidden="1" spans="1:7">
+    <row r="88" ht="15.75" spans="1:7">
       <c r="A88" s="22">
         <v>89</v>
       </c>
@@ -4418,7 +4424,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="89" ht="15.75" hidden="1" spans="1:7">
+    <row r="89" ht="15.75" spans="1:7">
       <c r="A89" s="22">
         <v>90</v>
       </c>
@@ -4441,7 +4447,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="90" ht="15.75" hidden="1" spans="1:7">
+    <row r="90" ht="15.75" spans="1:7">
       <c r="A90" s="22">
         <v>91</v>
       </c>
@@ -4462,7 +4468,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="91" ht="15.75" hidden="1" spans="1:7">
+    <row r="91" ht="15.75" spans="1:7">
       <c r="A91" s="22">
         <v>92</v>
       </c>
@@ -4485,7 +4491,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="92" ht="15.75" hidden="1" spans="1:7">
+    <row r="92" ht="15.75" spans="1:7">
       <c r="A92" s="22">
         <v>93</v>
       </c>
@@ -4506,7 +4512,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="93" ht="15.75" hidden="1" spans="1:7">
+    <row r="93" ht="15.75" spans="1:7">
       <c r="A93" s="22">
         <v>94</v>
       </c>
@@ -4529,7 +4535,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="94" ht="15.75" hidden="1" spans="1:7">
+    <row r="94" ht="15.75" spans="1:7">
       <c r="A94" s="22">
         <v>95</v>
       </c>
@@ -4550,7 +4556,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="95" ht="31.5" hidden="1" spans="1:7">
+    <row r="95" ht="31.5" spans="1:7">
       <c r="A95" s="22">
         <v>96</v>
       </c>
@@ -4573,7 +4579,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="96" ht="15.75" hidden="1" spans="1:7">
+    <row r="96" ht="15.75" spans="1:7">
       <c r="A96" s="22">
         <v>97</v>
       </c>
@@ -4596,7 +4602,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="97" ht="15.75" hidden="1" spans="1:7">
+    <row r="97" ht="15.75" spans="1:7">
       <c r="A97" s="22">
         <v>98</v>
       </c>
@@ -4619,7 +4625,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="98" ht="15.75" hidden="1" spans="1:7">
+    <row r="98" ht="15.75" spans="1:7">
       <c r="A98" s="22">
         <v>99</v>
       </c>
@@ -4636,7 +4642,7 @@
       <c r="F98" s="32"/>
       <c r="G98" s="25"/>
     </row>
-    <row r="99" ht="15.75" hidden="1" spans="1:7">
+    <row r="99" ht="15.75" spans="1:7">
       <c r="A99" s="22">
         <v>100</v>
       </c>
@@ -4657,7 +4663,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="100" ht="15.75" hidden="1" spans="1:7">
+    <row r="100" ht="15.75" spans="1:7">
       <c r="A100" s="22">
         <v>101</v>
       </c>
@@ -4676,7 +4682,7 @@
       </c>
       <c r="G100" s="25"/>
     </row>
-    <row r="101" ht="15.75" hidden="1" spans="1:7">
+    <row r="101" ht="15.75" spans="1:7">
       <c r="A101" s="22">
         <v>102</v>
       </c>
@@ -4697,7 +4703,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="102" ht="15.75" hidden="1" spans="1:7">
+    <row r="102" ht="15.75" spans="1:7">
       <c r="A102" s="22">
         <v>103</v>
       </c>
@@ -4720,7 +4726,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="103" ht="15.75" hidden="1" spans="1:7">
+    <row r="103" ht="15.75" spans="1:7">
       <c r="A103" s="22">
         <v>104</v>
       </c>
@@ -4741,7 +4747,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" ht="15.75" hidden="1" spans="1:7">
+    <row r="104" ht="15.75" spans="1:7">
       <c r="A104" s="22">
         <v>105</v>
       </c>
@@ -4764,7 +4770,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="105" ht="15.75" hidden="1" spans="1:7">
+    <row r="105" ht="15.75" spans="1:7">
       <c r="A105" s="22">
         <v>106</v>
       </c>
@@ -4785,7 +4791,7 @@
       </c>
       <c r="G105" s="25"/>
     </row>
-    <row r="106" ht="15.75" hidden="1" spans="1:7">
+    <row r="106" ht="15.75" spans="1:7">
       <c r="A106" s="22">
         <v>107</v>
       </c>
@@ -4804,7 +4810,7 @@
       </c>
       <c r="G106" s="27"/>
     </row>
-    <row r="107" ht="15.75" hidden="1" spans="1:7">
+    <row r="107" ht="15.75" spans="1:7">
       <c r="A107" s="22">
         <v>108</v>
       </c>
@@ -4823,7 +4829,7 @@
       </c>
       <c r="G107" s="27"/>
     </row>
-    <row r="108" ht="31.5" hidden="1" spans="1:7">
+    <row r="108" ht="31.5" spans="1:7">
       <c r="A108" s="22">
         <v>109</v>
       </c>
@@ -4842,7 +4848,7 @@
       </c>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" ht="15.75" hidden="1" spans="1:7">
+    <row r="109" ht="15.75" spans="1:7">
       <c r="A109" s="22">
         <v>110</v>
       </c>
@@ -4861,7 +4867,7 @@
       </c>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" ht="31.5" hidden="1" spans="1:7">
+    <row r="110" ht="31.5" spans="1:7">
       <c r="A110" s="22">
         <v>111</v>
       </c>
@@ -4880,7 +4886,7 @@
       </c>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" ht="15.75" hidden="1" spans="1:7">
+    <row r="111" ht="15.75" spans="1:7">
       <c r="A111" s="22">
         <v>112</v>
       </c>
@@ -4899,7 +4905,7 @@
       </c>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" ht="15.75" hidden="1" spans="1:7">
+    <row r="112" ht="15.75" spans="1:7">
       <c r="A112" s="22">
         <v>113</v>
       </c>
@@ -4918,7 +4924,7 @@
       </c>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
+    <row r="113" s="15" customFormat="1" ht="15.75" spans="1:7">
       <c r="A113" s="22">
         <v>114</v>
       </c>
@@ -4937,7 +4943,7 @@
       </c>
       <c r="G113" s="27"/>
     </row>
-    <row r="114" ht="15.75" hidden="1" spans="1:7">
+    <row r="114" ht="15.75" spans="1:7">
       <c r="A114" s="22">
         <v>115</v>
       </c>
@@ -4958,7 +4964,7 @@
       </c>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" ht="15.75" hidden="1" spans="1:7">
+    <row r="115" ht="15.75" spans="1:7">
       <c r="A115" s="22">
         <v>116</v>
       </c>
@@ -4977,7 +4983,7 @@
       </c>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" ht="15.75" hidden="1" spans="1:7">
+    <row r="116" ht="15.75" spans="1:7">
       <c r="A116" s="22">
         <v>117</v>
       </c>
@@ -4996,7 +5002,7 @@
       </c>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" ht="15.75" hidden="1" spans="1:7">
+    <row r="117" ht="15.75" spans="1:7">
       <c r="A117" s="22">
         <v>118</v>
       </c>
@@ -5015,7 +5021,7 @@
       </c>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" ht="15.75" hidden="1" spans="1:7">
+    <row r="118" ht="15.75" spans="1:7">
       <c r="A118" s="22">
         <v>119</v>
       </c>
@@ -5034,7 +5040,7 @@
       </c>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" ht="15.75" hidden="1" spans="1:7">
+    <row r="119" ht="15.75" spans="1:7">
       <c r="A119" s="22">
         <v>120</v>
       </c>
@@ -5053,7 +5059,7 @@
       </c>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" ht="15.75" hidden="1" spans="1:7">
+    <row r="120" ht="15.75" spans="1:7">
       <c r="A120" s="22">
         <v>121</v>
       </c>
@@ -5072,7 +5078,7 @@
       </c>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" ht="15.75" hidden="1" spans="1:7">
+    <row r="121" ht="15.75" spans="1:7">
       <c r="A121" s="22">
         <v>122</v>
       </c>
@@ -5091,7 +5097,7 @@
       </c>
       <c r="G121" s="49"/>
     </row>
-    <row r="122" ht="15.75" hidden="1" spans="1:7">
+    <row r="122" ht="15.75" spans="1:7">
       <c r="A122" s="22">
         <v>123</v>
       </c>
@@ -5110,7 +5116,7 @@
       </c>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" ht="15.75" hidden="1" spans="1:7">
+    <row r="123" ht="15.75" spans="1:7">
       <c r="A123" s="22">
         <v>124</v>
       </c>
@@ -5131,7 +5137,7 @@
       </c>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" ht="31.5" hidden="1" spans="1:7">
+    <row r="124" ht="31.5" spans="1:7">
       <c r="A124" s="22">
         <v>125</v>
       </c>
@@ -5152,7 +5158,7 @@
       </c>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" ht="15.75" hidden="1" spans="1:7">
+    <row r="125" ht="15.75" spans="1:7">
       <c r="A125" s="22">
         <v>126</v>
       </c>
@@ -5171,7 +5177,7 @@
       </c>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" ht="15.75" hidden="1" spans="1:7">
+    <row r="126" ht="15.75" spans="1:7">
       <c r="A126" s="22">
         <v>127</v>
       </c>
@@ -5192,7 +5198,7 @@
       </c>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" ht="15.75" hidden="1" spans="1:7">
+    <row r="127" ht="15.75" spans="1:7">
       <c r="A127" s="22">
         <v>128</v>
       </c>
@@ -5213,7 +5219,7 @@
       </c>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" ht="15.75" hidden="1" spans="1:7">
+    <row r="128" ht="15.75" spans="1:7">
       <c r="A128" s="22">
         <v>129</v>
       </c>
@@ -5236,7 +5242,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="129" ht="15.75" hidden="1" spans="1:7">
+    <row r="129" ht="15.75" spans="1:7">
       <c r="A129" s="22">
         <v>130</v>
       </c>
@@ -5259,7 +5265,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="130" ht="15.75" hidden="1" spans="1:7">
+    <row r="130" ht="15.75" spans="1:7">
       <c r="A130" s="22">
         <v>131</v>
       </c>
@@ -5282,7 +5288,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="131" ht="15.75" hidden="1" spans="1:7">
+    <row r="131" ht="15.75" spans="1:7">
       <c r="A131" s="22">
         <v>132</v>
       </c>
@@ -5305,7 +5311,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" ht="15.75" hidden="1" spans="1:7">
+    <row r="132" ht="15.75" spans="1:7">
       <c r="A132" s="22">
         <v>133</v>
       </c>
@@ -5328,7 +5334,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="133" ht="15.75" hidden="1" spans="1:7">
+    <row r="133" ht="15.75" spans="1:7">
       <c r="A133" s="22">
         <v>134</v>
       </c>
@@ -5348,7 +5354,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="134" ht="15.75" hidden="1" spans="1:7">
+    <row r="134" ht="15.75" spans="1:7">
       <c r="A134" s="22">
         <v>135</v>
       </c>
@@ -5371,7 +5377,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="135" ht="15.75" hidden="1" spans="1:7">
+    <row r="135" ht="15.75" spans="1:7">
       <c r="A135" s="22">
         <v>136</v>
       </c>
@@ -5394,7 +5400,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="136" ht="15.75" hidden="1" spans="1:7">
+    <row r="136" ht="15.75" spans="1:7">
       <c r="A136" s="22">
         <v>137</v>
       </c>
@@ -5417,7 +5423,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="137" ht="15.75" hidden="1" spans="1:7">
+    <row r="137" ht="15.75" spans="1:7">
       <c r="A137" s="22">
         <v>138</v>
       </c>
@@ -5440,7 +5446,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" ht="15.75" hidden="1" spans="1:7">
+    <row r="138" ht="15.75" spans="1:7">
       <c r="A138" s="22">
         <v>139</v>
       </c>
@@ -5460,7 +5466,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="139" ht="15.75" hidden="1" spans="1:7">
+    <row r="139" ht="15.75" spans="1:7">
       <c r="A139" s="22">
         <v>140</v>
       </c>
@@ -5483,7 +5489,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="140" ht="15.75" hidden="1" spans="1:7">
+    <row r="140" ht="15.75" spans="1:7">
       <c r="A140" s="22">
         <v>141</v>
       </c>
@@ -5503,7 +5509,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="141" ht="15.75" hidden="1" spans="1:7">
+    <row r="141" ht="15.75" spans="1:7">
       <c r="A141" s="22">
         <v>142</v>
       </c>
@@ -5523,7 +5529,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="142" ht="31.5" hidden="1" spans="1:7">
+    <row r="142" ht="31.5" spans="1:7">
       <c r="A142" s="22">
         <v>143</v>
       </c>
@@ -5546,7 +5552,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="143" ht="15.75" hidden="1" spans="1:7">
+    <row r="143" ht="15.75" spans="1:7">
       <c r="A143" s="22">
         <v>144</v>
       </c>
@@ -5566,8 +5572,25 @@
         <v>359</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
-      <c r="D144" s="17"/>
+    <row r="144" ht="15.75" spans="1:7">
+      <c r="A144" s="22">
+        <v>145</v>
+      </c>
+      <c r="B144" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="C144" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144" s="53" t="s">
+        <v>361</v>
+      </c>
     </row>
     <row r="145" spans="4:4">
       <c r="D145" s="17"/>
@@ -8630,13 +8653,7 @@
       <c r="D1164" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G143" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="BENSALEM RITEDJ INES"/>
-        <filter val="BENSALEM ABDELHAMID"/>
-      </filters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G144" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8689,6 +8706,7 @@
     <hyperlink ref="F113" r:id="rId47" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
     <hyperlink ref="F142" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
     <hyperlink ref="F143" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
+    <hyperlink ref="F144" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8711,202 +8729,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>372</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>372</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="403">
   <si>
     <t>N°</t>
   </si>
@@ -1118,6 +1118,15 @@
   </si>
   <si>
     <t>yamanimassim@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BERREKHCHI BERRAHMA NEILA</t>
+  </si>
+  <si>
+    <t>neilabekhchiberrahma@gmail.com</t>
+  </si>
+  <si>
+    <t>0656 88 71 07</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2535,7 +2544,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="16" customWidth="1"/>
-    <col min="2" max="2" width="27.2857142857143" style="17" customWidth="1"/>
+    <col min="2" max="2" width="33.5714285714286" style="17" customWidth="1"/>
     <col min="3" max="3" width="29.7142857142857" style="17" customWidth="1"/>
     <col min="4" max="4" width="19.1428571428571" style="16" customWidth="1"/>
     <col min="5" max="5" width="21.552380952381" style="16" customWidth="1"/>
@@ -5592,52 +5601,72 @@
         <v>361</v>
       </c>
     </row>
-    <row r="145" spans="4:4">
-      <c r="D145" s="17"/>
-    </row>
-    <row r="146" spans="4:4">
+    <row r="145" ht="19" customHeight="1" spans="1:7">
+      <c r="A145" s="22">
+        <v>145</v>
+      </c>
+      <c r="B145" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="C145" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E145" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="F145" s="53" t="s">
+        <v>363</v>
+      </c>
+      <c r="G145" s="25" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
       <c r="D146" s="17"/>
     </row>
-    <row r="147" spans="4:4">
+    <row r="147" spans="1:7">
       <c r="D147" s="17"/>
     </row>
-    <row r="148" spans="4:4">
+    <row r="148" spans="1:7">
       <c r="D148" s="17"/>
     </row>
-    <row r="149" spans="4:4">
+    <row r="149" spans="1:7">
       <c r="D149" s="17"/>
     </row>
-    <row r="150" spans="4:4">
+    <row r="150" spans="1:7">
       <c r="D150" s="17"/>
     </row>
-    <row r="151" spans="4:4">
+    <row r="151" spans="1:7">
       <c r="D151" s="17"/>
     </row>
-    <row r="152" spans="4:4">
+    <row r="152" spans="1:7">
       <c r="D152" s="17"/>
     </row>
-    <row r="153" spans="4:4">
+    <row r="153" spans="1:7">
       <c r="D153" s="17"/>
     </row>
-    <row r="154" spans="4:4">
+    <row r="154" spans="1:7">
       <c r="D154" s="17"/>
     </row>
-    <row r="155" spans="4:4">
+    <row r="155" spans="1:7">
       <c r="D155" s="17"/>
     </row>
-    <row r="156" spans="4:4">
+    <row r="156" spans="1:7">
       <c r="D156" s="17"/>
     </row>
-    <row r="157" spans="4:4">
+    <row r="157" spans="1:7">
       <c r="D157" s="17"/>
     </row>
-    <row r="158" spans="4:4">
+    <row r="158" spans="1:7">
       <c r="D158" s="17"/>
     </row>
-    <row r="159" spans="4:4">
+    <row r="159" spans="1:7">
       <c r="D159" s="17"/>
     </row>
-    <row r="160" spans="4:4">
+    <row r="160" spans="1:7">
       <c r="D160" s="17"/>
     </row>
     <row r="161" spans="4:4">
@@ -8707,6 +8736,7 @@
     <hyperlink ref="F142" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
     <hyperlink ref="F143" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
     <hyperlink ref="F144" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
+    <hyperlink ref="F145" r:id="rId50" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8729,202 +8759,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="405">
   <si>
     <t>N°</t>
   </si>
@@ -1127,6 +1127,12 @@
   </si>
   <si>
     <t>0656 88 71 07</t>
+  </si>
+  <si>
+    <t>FILALI INES</t>
+  </si>
+  <si>
+    <t>nesfilali2003@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2039,7 +2045,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2186,6 +2192,7 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2700,7 +2707,7 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="54" t="s">
+      <c r="G7" s="55" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2723,7 +2730,7 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="55" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2767,7 +2774,7 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="55" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2876,7 +2883,7 @@
       </c>
       <c r="G15" s="25"/>
     </row>
-    <row r="16" ht="31.5" spans="1:7">
+    <row r="16" ht="15.75" spans="1:7">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -2960,7 +2967,7 @@
       </c>
       <c r="G19" s="25"/>
     </row>
-    <row r="20" ht="31.5" spans="1:7">
+    <row r="20" ht="15.75" spans="1:7">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -3086,7 +3093,7 @@
       </c>
       <c r="G25" s="25"/>
     </row>
-    <row r="26" ht="31.5" spans="1:7">
+    <row r="26" ht="15.75" spans="1:7">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -3315,7 +3322,7 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="55" t="s">
+      <c r="G36" s="56" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3359,11 +3366,11 @@
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="54" t="s">
+      <c r="G38" s="55" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="31.5" spans="1:7">
+    <row r="39" ht="15.75" spans="1:7">
       <c r="A39" s="22">
         <v>39</v>
       </c>
@@ -3655,7 +3662,7 @@
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="54" t="s">
+      <c r="G52" s="55" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3699,7 +3706,7 @@
       <c r="F54" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="54" t="s">
+      <c r="G54" s="55" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3854,7 +3861,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="62" ht="31.5" spans="1:7">
+    <row r="62" ht="15.75" spans="1:7">
       <c r="A62" s="22">
         <v>62</v>
       </c>
@@ -3875,7 +3882,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="63" ht="30" spans="1:7">
+    <row r="63" ht="15.75" spans="1:7">
       <c r="A63" s="22">
         <v>64</v>
       </c>
@@ -3894,11 +3901,11 @@
       <c r="F63" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="G63" s="54" t="s">
+      <c r="G63" s="55" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="64" ht="31.5" spans="1:7">
+    <row r="64" ht="15.75" spans="1:7">
       <c r="A64" s="22">
         <v>65</v>
       </c>
@@ -3957,7 +3964,7 @@
       <c r="F66" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="G66" s="55" t="s">
+      <c r="G66" s="56" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4001,7 +4008,7 @@
       <c r="F68" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="G68" s="54" t="s">
+      <c r="G68" s="55" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4022,7 +4029,7 @@
       <c r="F69" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="54" t="s">
+      <c r="G69" s="55" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4043,7 +4050,7 @@
       <c r="F70" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="54" t="s">
+      <c r="G70" s="55" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4064,7 +4071,7 @@
       <c r="F71" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="54" t="s">
+      <c r="G71" s="55" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4087,7 +4094,7 @@
       <c r="F72" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="54" t="s">
+      <c r="G72" s="55" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4152,11 +4159,11 @@
       <c r="F75" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="G75" s="54" t="s">
+      <c r="G75" s="55" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="76" ht="31.5" spans="1:7">
+    <row r="76" ht="15.75" spans="1:7">
       <c r="A76" s="22">
         <v>77</v>
       </c>
@@ -4217,7 +4224,7 @@
       <c r="F78" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="G78" s="54" t="s">
+      <c r="G78" s="55" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4429,7 +4436,7 @@
       <c r="F88" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="G88" s="54" t="s">
+      <c r="G88" s="55" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4473,7 +4480,7 @@
       <c r="F90" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="G90" s="54" t="s">
+      <c r="G90" s="55" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4496,7 +4503,7 @@
       <c r="F91" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="G91" s="54" t="s">
+      <c r="G91" s="55" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4540,7 +4547,7 @@
       <c r="F93" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="G93" s="54" t="s">
+      <c r="G93" s="55" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4775,7 +4782,7 @@
       <c r="F104" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="G104" s="55" t="s">
+      <c r="G104" s="56" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4838,7 +4845,7 @@
       </c>
       <c r="G107" s="27"/>
     </row>
-    <row r="108" ht="31.5" spans="1:7">
+    <row r="108" ht="15.75" spans="1:7">
       <c r="A108" s="22">
         <v>109</v>
       </c>
@@ -5247,7 +5254,7 @@
       <c r="F128" s="50" t="s">
         <v>322</v>
       </c>
-      <c r="G128" s="54" t="s">
+      <c r="G128" s="55" t="s">
         <v>323</v>
       </c>
     </row>
@@ -5270,7 +5277,7 @@
       <c r="F129" s="51" t="s">
         <v>325</v>
       </c>
-      <c r="G129" s="56" t="s">
+      <c r="G129" s="57" t="s">
         <v>326</v>
       </c>
     </row>
@@ -5293,7 +5300,7 @@
       <c r="F130" s="43" t="s">
         <v>328</v>
       </c>
-      <c r="G130" s="56" t="s">
+      <c r="G130" s="57" t="s">
         <v>329</v>
       </c>
     </row>
@@ -5316,7 +5323,7 @@
       <c r="F131" s="51" t="s">
         <v>331</v>
       </c>
-      <c r="G131" s="56" t="s">
+      <c r="G131" s="57" t="s">
         <v>332</v>
       </c>
     </row>
@@ -5339,7 +5346,7 @@
       <c r="F132" s="51" t="s">
         <v>309</v>
       </c>
-      <c r="G132" s="56" t="s">
+      <c r="G132" s="57" t="s">
         <v>333</v>
       </c>
     </row>
@@ -5405,7 +5412,7 @@
       <c r="F135" s="51" t="s">
         <v>340</v>
       </c>
-      <c r="G135" s="56" t="s">
+      <c r="G135" s="57" t="s">
         <v>341</v>
       </c>
     </row>
@@ -5428,7 +5435,7 @@
       <c r="F136" s="51" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="56" t="s">
+      <c r="G136" s="57" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5451,7 +5458,7 @@
       <c r="F137" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="G137" s="56" t="s">
+      <c r="G137" s="57" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5494,7 +5501,7 @@
       <c r="F139" s="52" t="s">
         <v>352</v>
       </c>
-      <c r="G139" s="57" t="s">
+      <c r="G139" s="58" t="s">
         <v>353</v>
       </c>
     </row>
@@ -5538,7 +5545,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="142" ht="31.5" spans="1:7">
+    <row r="142" ht="15.75" spans="1:7">
       <c r="A142" s="22">
         <v>143</v>
       </c>
@@ -5624,8 +5631,22 @@
         <v>364</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
-      <c r="D146" s="17"/>
+    <row r="146" ht="15.75" spans="1:7">
+      <c r="B146" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="C146" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D146" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E146" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F146" s="54" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="147" spans="1:7">
       <c r="D147" s="17"/>
@@ -8682,7 +8703,7 @@
       <c r="D1164" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G144" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G145" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8759,202 +8780,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>377</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>377</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="421">
   <si>
     <t>N°</t>
   </si>
@@ -1133,6 +1133,54 @@
   </si>
   <si>
     <t>nesfilali2003@gmail.com</t>
+  </si>
+  <si>
+    <t>0794297709</t>
+  </si>
+  <si>
+    <t>KADARI BELKACEM</t>
+  </si>
+  <si>
+    <t>belkacemKadari@gmail.com</t>
+  </si>
+  <si>
+    <t>0553282842</t>
+  </si>
+  <si>
+    <t>DOUIAICI MOHAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mdouiaici@hotmail.com </t>
+  </si>
+  <si>
+    <t>MOKEDDES AMINA</t>
+  </si>
+  <si>
+    <t>Mokaddesamina@gmail.com</t>
+  </si>
+  <si>
+    <t>TAIBI SOUMIA</t>
+  </si>
+  <si>
+    <t>soumiaaiboudi27@gmail.com</t>
+  </si>
+  <si>
+    <t>KHIAT WALID</t>
+  </si>
+  <si>
+    <t>walid.sebastien@gmail.com</t>
+  </si>
+  <si>
+    <t>BENSNADA NADIA</t>
+  </si>
+  <si>
+    <t>bensenadanadia3@gmail.com</t>
+  </si>
+  <si>
+    <t>MEDLES IMED</t>
+  </si>
+  <si>
+    <t>Iimedmedles@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1259,7 +1307,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1341,12 +1389,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Cambria"/>
@@ -1361,9 +1403,10 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF434343"/>
-      <name val="Cambria"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1918,10 +1961,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1930,122 +1976,119 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2177,30 +2220,49 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2707,7 +2769,7 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G7" s="58" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2730,7 +2792,7 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="55" t="s">
+      <c r="G8" s="58" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2774,7 +2836,7 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="58" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3322,7 +3384,7 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="56" t="s">
+      <c r="G36" s="59" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3366,7 +3428,7 @@
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="55" t="s">
+      <c r="G38" s="58" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3662,7 +3724,7 @@
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="55" t="s">
+      <c r="G52" s="58" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3706,7 +3768,7 @@
       <c r="F54" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="55" t="s">
+      <c r="G54" s="58" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3901,7 +3963,7 @@
       <c r="F63" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="G63" s="55" t="s">
+      <c r="G63" s="58" t="s">
         <v>155</v>
       </c>
     </row>
@@ -3964,7 +4026,7 @@
       <c r="F66" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="G66" s="56" t="s">
+      <c r="G66" s="59" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4008,7 +4070,7 @@
       <c r="F68" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="G68" s="55" t="s">
+      <c r="G68" s="58" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4029,7 +4091,7 @@
       <c r="F69" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="55" t="s">
+      <c r="G69" s="58" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4050,7 +4112,7 @@
       <c r="F70" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="55" t="s">
+      <c r="G70" s="58" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4071,7 +4133,7 @@
       <c r="F71" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="55" t="s">
+      <c r="G71" s="58" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4094,7 +4156,7 @@
       <c r="F72" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="55" t="s">
+      <c r="G72" s="58" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4159,7 +4221,7 @@
       <c r="F75" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="G75" s="55" t="s">
+      <c r="G75" s="58" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4224,7 +4286,7 @@
       <c r="F78" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="G78" s="55" t="s">
+      <c r="G78" s="58" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4436,7 +4498,7 @@
       <c r="F88" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="G88" s="55" t="s">
+      <c r="G88" s="58" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4480,7 +4542,7 @@
       <c r="F90" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="G90" s="55" t="s">
+      <c r="G90" s="58" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4503,7 +4565,7 @@
       <c r="F91" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="G91" s="55" t="s">
+      <c r="G91" s="58" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4547,7 +4609,7 @@
       <c r="F93" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="G93" s="55" t="s">
+      <c r="G93" s="58" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4782,7 +4844,7 @@
       <c r="F104" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="G104" s="56" t="s">
+      <c r="G104" s="59" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4821,7 +4883,7 @@
         <v>125</v>
       </c>
       <c r="E106" s="46"/>
-      <c r="F106" s="47" t="s">
+      <c r="F106" s="32" t="s">
         <v>278</v>
       </c>
       <c r="G106" s="27"/>
@@ -4840,7 +4902,7 @@
         <v>125</v>
       </c>
       <c r="E107" s="46"/>
-      <c r="F107" s="47" t="s">
+      <c r="F107" s="32" t="s">
         <v>280</v>
       </c>
       <c r="G107" s="27"/>
@@ -4859,7 +4921,7 @@
         <v>125</v>
       </c>
       <c r="E108" s="46"/>
-      <c r="F108" s="47" t="s">
+      <c r="F108" s="32" t="s">
         <v>282</v>
       </c>
       <c r="G108" s="27"/>
@@ -4878,7 +4940,7 @@
         <v>125</v>
       </c>
       <c r="E109" s="46"/>
-      <c r="F109" s="47" t="s">
+      <c r="F109" s="32" t="s">
         <v>284</v>
       </c>
       <c r="G109" s="27"/>
@@ -4897,7 +4959,7 @@
         <v>125</v>
       </c>
       <c r="E110" s="46"/>
-      <c r="F110" s="47" t="s">
+      <c r="F110" s="32" t="s">
         <v>286</v>
       </c>
       <c r="G110" s="27"/>
@@ -4916,7 +4978,7 @@
         <v>125</v>
       </c>
       <c r="E111" s="46"/>
-      <c r="F111" s="47" t="s">
+      <c r="F111" s="32" t="s">
         <v>288</v>
       </c>
       <c r="G111" s="27"/>
@@ -4935,7 +4997,7 @@
         <v>125</v>
       </c>
       <c r="E112" s="46"/>
-      <c r="F112" s="47" t="s">
+      <c r="F112" s="32" t="s">
         <v>272</v>
       </c>
       <c r="G112" s="27"/>
@@ -4954,7 +5016,7 @@
         <v>125</v>
       </c>
       <c r="E113" s="46"/>
-      <c r="F113" s="48" t="s">
+      <c r="F113" s="32" t="s">
         <v>291</v>
       </c>
       <c r="G113" s="27"/>
@@ -4975,7 +5037,7 @@
       <c r="E114" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="F114" s="47" t="s">
+      <c r="F114" s="32" t="s">
         <v>293</v>
       </c>
       <c r="G114" s="27"/>
@@ -4994,7 +5056,7 @@
         <v>125</v>
       </c>
       <c r="E115" s="46"/>
-      <c r="F115" s="47" t="s">
+      <c r="F115" s="32" t="s">
         <v>295</v>
       </c>
       <c r="G115" s="27"/>
@@ -5013,7 +5075,7 @@
         <v>125</v>
       </c>
       <c r="E116" s="46"/>
-      <c r="F116" s="47" t="s">
+      <c r="F116" s="32" t="s">
         <v>297</v>
       </c>
       <c r="G116" s="27"/>
@@ -5032,7 +5094,7 @@
         <v>125</v>
       </c>
       <c r="E117" s="46"/>
-      <c r="F117" s="47" t="s">
+      <c r="F117" s="32" t="s">
         <v>299</v>
       </c>
       <c r="G117" s="27"/>
@@ -5051,7 +5113,7 @@
         <v>125</v>
       </c>
       <c r="E118" s="46"/>
-      <c r="F118" s="47" t="s">
+      <c r="F118" s="32" t="s">
         <v>301</v>
       </c>
       <c r="G118" s="27"/>
@@ -5070,7 +5132,7 @@
         <v>125</v>
       </c>
       <c r="E119" s="46"/>
-      <c r="F119" s="47" t="s">
+      <c r="F119" s="32" t="s">
         <v>303</v>
       </c>
       <c r="G119" s="27"/>
@@ -5089,7 +5151,7 @@
         <v>125</v>
       </c>
       <c r="E120" s="46"/>
-      <c r="F120" s="47" t="s">
+      <c r="F120" s="32" t="s">
         <v>305</v>
       </c>
       <c r="G120" s="27"/>
@@ -5108,10 +5170,10 @@
         <v>125</v>
       </c>
       <c r="E121" s="46"/>
-      <c r="F121" s="47" t="s">
+      <c r="F121" s="32" t="s">
         <v>307</v>
       </c>
-      <c r="G121" s="49"/>
+      <c r="G121" s="47"/>
     </row>
     <row r="122" ht="15.75" spans="1:7">
       <c r="A122" s="22">
@@ -5127,7 +5189,7 @@
         <v>125</v>
       </c>
       <c r="E122" s="46"/>
-      <c r="F122" s="47" t="s">
+      <c r="F122" s="32" t="s">
         <v>309</v>
       </c>
       <c r="G122" s="27"/>
@@ -5148,7 +5210,7 @@
       <c r="E123" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="F123" s="47" t="s">
+      <c r="F123" s="32" t="s">
         <v>311</v>
       </c>
       <c r="G123" s="27"/>
@@ -5169,7 +5231,7 @@
       <c r="E124" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="F124" s="47" t="s">
+      <c r="F124" s="32" t="s">
         <v>314</v>
       </c>
       <c r="G124" s="27"/>
@@ -5188,7 +5250,7 @@
         <v>125</v>
       </c>
       <c r="E125" s="46"/>
-      <c r="F125" s="47" t="s">
+      <c r="F125" s="32" t="s">
         <v>316</v>
       </c>
       <c r="G125" s="27"/>
@@ -5209,7 +5271,7 @@
       <c r="E126" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="F126" s="47" t="s">
+      <c r="F126" s="32" t="s">
         <v>318</v>
       </c>
       <c r="G126" s="27"/>
@@ -5230,7 +5292,7 @@
       <c r="E127" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="F127" s="47" t="s">
+      <c r="F127" s="32" t="s">
         <v>320</v>
       </c>
       <c r="G127" s="27"/>
@@ -5251,10 +5313,10 @@
       <c r="E128" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="F128" s="50" t="s">
+      <c r="F128" s="32" t="s">
         <v>322</v>
       </c>
-      <c r="G128" s="55" t="s">
+      <c r="G128" s="58" t="s">
         <v>323</v>
       </c>
     </row>
@@ -5274,10 +5336,10 @@
       <c r="E129" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F129" s="51" t="s">
+      <c r="F129" s="32" t="s">
         <v>325</v>
       </c>
-      <c r="G129" s="57" t="s">
+      <c r="G129" s="60" t="s">
         <v>326</v>
       </c>
     </row>
@@ -5297,10 +5359,10 @@
       <c r="E130" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F130" s="43" t="s">
+      <c r="F130" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="G130" s="57" t="s">
+      <c r="G130" s="60" t="s">
         <v>329</v>
       </c>
     </row>
@@ -5320,10 +5382,10 @@
       <c r="E131" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F131" s="51" t="s">
+      <c r="F131" s="32" t="s">
         <v>331</v>
       </c>
-      <c r="G131" s="57" t="s">
+      <c r="G131" s="60" t="s">
         <v>332</v>
       </c>
     </row>
@@ -5343,10 +5405,10 @@
       <c r="E132" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F132" s="51" t="s">
+      <c r="F132" s="32" t="s">
         <v>309</v>
       </c>
-      <c r="G132" s="57" t="s">
+      <c r="G132" s="60" t="s">
         <v>333</v>
       </c>
     </row>
@@ -5366,7 +5428,7 @@
       <c r="E133" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F133" s="17" t="s">
+      <c r="F133" s="32" t="s">
         <v>335</v>
       </c>
     </row>
@@ -5386,10 +5448,10 @@
       <c r="E134" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F134" s="51" t="s">
+      <c r="F134" s="32" t="s">
         <v>337</v>
       </c>
-      <c r="G134" s="51" t="s">
+      <c r="G134" s="48" t="s">
         <v>338</v>
       </c>
     </row>
@@ -5409,10 +5471,10 @@
       <c r="E135" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F135" s="51" t="s">
+      <c r="F135" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="G135" s="57" t="s">
+      <c r="G135" s="60" t="s">
         <v>341</v>
       </c>
     </row>
@@ -5432,10 +5494,10 @@
       <c r="E136" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F136" s="51" t="s">
+      <c r="F136" s="32" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="57" t="s">
+      <c r="G136" s="60" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5455,10 +5517,10 @@
       <c r="E137" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F137" s="51" t="s">
+      <c r="F137" s="32" t="s">
         <v>346</v>
       </c>
-      <c r="G137" s="57" t="s">
+      <c r="G137" s="60" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5478,7 +5540,7 @@
       <c r="E138" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="F138" s="51" t="s">
+      <c r="F138" s="32" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5498,10 +5560,10 @@
       <c r="E139" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F139" s="52" t="s">
+      <c r="F139" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="G139" s="58" t="s">
+      <c r="G139" s="61" t="s">
         <v>353</v>
       </c>
     </row>
@@ -5521,7 +5583,7 @@
       <c r="E140" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="F140" s="53" t="s">
+      <c r="F140" s="32" t="s">
         <v>355</v>
       </c>
     </row>
@@ -5541,7 +5603,7 @@
       <c r="E141" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F141" s="53" t="s">
+      <c r="F141" s="32" t="s">
         <v>357</v>
       </c>
     </row>
@@ -5561,7 +5623,7 @@
       <c r="E142" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="F142" s="53" t="s">
+      <c r="F142" s="32" t="s">
         <v>193</v>
       </c>
       <c r="G142" s="25" t="s">
@@ -5578,13 +5640,13 @@
       <c r="C143" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D143" s="16" t="s">
+      <c r="D143" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E143" s="16" t="s">
+      <c r="E143" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F143" s="53" t="s">
+      <c r="F143" s="32" t="s">
         <v>359</v>
       </c>
     </row>
@@ -5598,13 +5660,13 @@
       <c r="C144" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D144" s="16" t="s">
+      <c r="D144" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="E144" s="16" t="s">
+      <c r="E144" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F144" s="53" t="s">
+      <c r="F144" s="32" t="s">
         <v>361</v>
       </c>
     </row>
@@ -5618,13 +5680,13 @@
       <c r="C145" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D145" s="16" t="s">
+      <c r="D145" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="E145" s="16" t="s">
+      <c r="E145" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="F145" s="53" t="s">
+      <c r="F145" s="32" t="s">
         <v>363</v>
       </c>
       <c r="G145" s="25" t="s">
@@ -5632,45 +5694,191 @@
       </c>
     </row>
     <row r="146" ht="15.75" spans="1:7">
+      <c r="A146" s="22">
+        <v>146</v>
+      </c>
       <c r="B146" s="23" t="s">
         <v>365</v>
       </c>
       <c r="C146" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D146" s="16" t="s">
+      <c r="D146" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="E146" s="16" t="s">
+      <c r="E146" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="F146" s="54" t="s">
+      <c r="F146" s="32" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="147" spans="1:7">
-      <c r="D147" s="17"/>
-    </row>
-    <row r="148" spans="1:7">
-      <c r="D148" s="17"/>
-    </row>
-    <row r="149" spans="1:7">
-      <c r="D149" s="17"/>
-    </row>
-    <row r="150" spans="1:7">
-      <c r="D150" s="17"/>
-    </row>
-    <row r="151" spans="1:7">
-      <c r="D151" s="17"/>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="D152" s="17"/>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="D153" s="17"/>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="D154" s="17"/>
+      <c r="G146" s="51"/>
+    </row>
+    <row r="147" ht="15.75" spans="1:7">
+      <c r="A147" s="22">
+        <v>147</v>
+      </c>
+      <c r="B147" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C147" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E147" s="50"/>
+      <c r="F147" s="32" t="s">
+        <v>301</v>
+      </c>
+      <c r="G147" s="62" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" spans="1:7">
+      <c r="A148" s="22">
+        <v>148</v>
+      </c>
+      <c r="B148" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E148" s="50" t="s">
+        <v>134</v>
+      </c>
+      <c r="F148" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="G148" s="63" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" spans="1:7">
+      <c r="A149" s="22">
+        <v>149</v>
+      </c>
+      <c r="B149" s="53" t="s">
+        <v>371</v>
+      </c>
+      <c r="C149" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="G149" s="51"/>
+    </row>
+    <row r="150" ht="15.75" spans="1:7">
+      <c r="A150" s="22">
+        <v>150</v>
+      </c>
+      <c r="B150" s="54" t="s">
+        <v>373</v>
+      </c>
+      <c r="C150" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E150" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="F150" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="G150" s="55"/>
+    </row>
+    <row r="151" ht="15.75" spans="1:7">
+      <c r="A151" s="50">
+        <v>151</v>
+      </c>
+      <c r="B151" s="53" t="s">
+        <v>375</v>
+      </c>
+      <c r="C151" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E151" s="50"/>
+      <c r="F151" s="56" t="s">
+        <v>376</v>
+      </c>
+      <c r="G151" s="55"/>
+    </row>
+    <row r="152" ht="15.75" spans="1:7">
+      <c r="A152" s="50">
+        <v>152</v>
+      </c>
+      <c r="B152" s="53" t="s">
+        <v>377</v>
+      </c>
+      <c r="C152" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E152" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="F152" s="56" t="s">
+        <v>378</v>
+      </c>
+      <c r="G152" s="55"/>
+    </row>
+    <row r="153" ht="15.75" spans="1:7">
+      <c r="A153" s="50">
+        <v>153</v>
+      </c>
+      <c r="B153" s="51" t="s">
+        <v>379</v>
+      </c>
+      <c r="C153" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E153" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="F153" s="56" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" spans="1:7">
+      <c r="A154" s="50">
+        <v>153</v>
+      </c>
+      <c r="B154" s="57" t="s">
+        <v>381</v>
+      </c>
+      <c r="C154" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E154" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="F154" s="56" t="s">
+        <v>382</v>
+      </c>
     </row>
     <row r="155" spans="1:7">
       <c r="D155" s="17"/>
@@ -8703,7 +8911,7 @@
       <c r="D1164" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G145" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G147" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8758,6 +8966,10 @@
     <hyperlink ref="F143" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
     <hyperlink ref="F144" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
     <hyperlink ref="F145" r:id="rId50" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
+    <hyperlink ref="F148" r:id="rId51" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
+    <hyperlink ref="F151" r:id="rId52" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
+    <hyperlink ref="F152" r:id="rId53" display="walid.sebastien@gmail.com"/>
+    <hyperlink ref="F153" r:id="rId54" display="bensenadanadia3@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8780,202 +8992,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>390</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>373</v>
-      </c>
       <c r="D9" s="7" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>376</v>
-      </c>
       <c r="D10" s="7" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$156</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="423">
   <si>
     <t>N°</t>
   </si>
@@ -922,9 +922,6 @@
     <t>fantazibelkisse.13@gmail.com</t>
   </si>
   <si>
-    <t>FEZAZI KHADIDJA</t>
-  </si>
-  <si>
     <t>khadidjafezazi90@gmail</t>
   </si>
   <si>
@@ -1069,9 +1066,6 @@
     <t>0697113466</t>
   </si>
   <si>
-    <t>Fezazi ISMAHENE</t>
-  </si>
-  <si>
     <t>ismahene.fezazi@gmail.com</t>
   </si>
   <si>
@@ -1102,7 +1096,7 @@
     <t>mekhfikhalida87@gmail.com</t>
   </si>
   <si>
-    <t>ZATLA HICHEM</t>
+    <t>ZATLA HICHAM</t>
   </si>
   <si>
     <t>hicham.zatla@gmail.com</t>
@@ -1180,7 +1174,19 @@
     <t>MEDLES IMED</t>
   </si>
   <si>
-    <t>Iimedmedles@gmail.com</t>
+    <t>imedmedles@gmail.com</t>
+  </si>
+  <si>
+    <t>ANANI MACHO</t>
+  </si>
+  <si>
+    <t>anani66@yahoo.fr</t>
+  </si>
+  <si>
+    <t>FEZAZI OMAR</t>
+  </si>
+  <si>
+    <t>fezaziomarfz@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2088,7 +2094,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2225,12 +2231,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2243,12 +2243,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2258,9 +2252,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2769,7 +2760,7 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="54" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2792,7 +2783,7 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="54" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2836,7 +2827,7 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="54" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3384,7 +3375,7 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="59" t="s">
+      <c r="G36" s="55" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3428,7 +3419,7 @@
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="58" t="s">
+      <c r="G38" s="54" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3724,7 +3715,7 @@
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="58" t="s">
+      <c r="G52" s="54" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3768,7 +3759,7 @@
       <c r="F54" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="58" t="s">
+      <c r="G54" s="54" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3963,7 +3954,7 @@
       <c r="F63" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="G63" s="58" t="s">
+      <c r="G63" s="54" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4026,7 +4017,7 @@
       <c r="F66" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="G66" s="59" t="s">
+      <c r="G66" s="55" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4070,7 +4061,7 @@
       <c r="F68" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="G68" s="58" t="s">
+      <c r="G68" s="54" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4091,7 +4082,7 @@
       <c r="F69" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="58" t="s">
+      <c r="G69" s="54" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4112,7 +4103,7 @@
       <c r="F70" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="58" t="s">
+      <c r="G70" s="54" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4133,7 +4124,7 @@
       <c r="F71" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="58" t="s">
+      <c r="G71" s="54" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4156,7 +4147,7 @@
       <c r="F72" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="58" t="s">
+      <c r="G72" s="54" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4221,7 +4212,7 @@
       <c r="F75" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="G75" s="58" t="s">
+      <c r="G75" s="54" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4286,7 +4277,7 @@
       <c r="F78" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="G78" s="58" t="s">
+      <c r="G78" s="54" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4498,7 +4489,7 @@
       <c r="F88" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="G88" s="58" t="s">
+      <c r="G88" s="54" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4542,7 +4533,7 @@
       <c r="F90" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="G90" s="58" t="s">
+      <c r="G90" s="54" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4565,7 +4556,7 @@
       <c r="F91" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="G91" s="58" t="s">
+      <c r="G91" s="54" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4609,7 +4600,7 @@
       <c r="F93" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="G93" s="58" t="s">
+      <c r="G93" s="54" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4844,7 +4835,7 @@
       <c r="F104" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="G104" s="59" t="s">
+      <c r="G104" s="55" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5065,9 +5056,7 @@
       <c r="A116" s="22">
         <v>117</v>
       </c>
-      <c r="B116" s="23" t="s">
-        <v>296</v>
-      </c>
+      <c r="B116" s="23"/>
       <c r="C116" s="23" t="s">
         <v>8</v>
       </c>
@@ -5076,7 +5065,7 @@
       </c>
       <c r="E116" s="46"/>
       <c r="F116" s="32" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G116" s="27"/>
     </row>
@@ -5085,7 +5074,7 @@
         <v>118</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C117" s="23" t="s">
         <v>8</v>
@@ -5095,7 +5084,7 @@
       </c>
       <c r="E117" s="46"/>
       <c r="F117" s="32" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G117" s="27"/>
     </row>
@@ -5104,7 +5093,7 @@
         <v>119</v>
       </c>
       <c r="B118" s="23" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C118" s="23" t="s">
         <v>8</v>
@@ -5114,7 +5103,7 @@
       </c>
       <c r="E118" s="46"/>
       <c r="F118" s="32" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G118" s="27"/>
     </row>
@@ -5123,7 +5112,7 @@
         <v>120</v>
       </c>
       <c r="B119" s="23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C119" s="23" t="s">
         <v>8</v>
@@ -5133,7 +5122,7 @@
       </c>
       <c r="E119" s="46"/>
       <c r="F119" s="32" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G119" s="27"/>
     </row>
@@ -5142,7 +5131,7 @@
         <v>121</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C120" s="23" t="s">
         <v>8</v>
@@ -5152,7 +5141,7 @@
       </c>
       <c r="E120" s="46"/>
       <c r="F120" s="32" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G120" s="27"/>
     </row>
@@ -5161,7 +5150,7 @@
         <v>122</v>
       </c>
       <c r="B121" s="23" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C121" s="23" t="s">
         <v>8</v>
@@ -5171,7 +5160,7 @@
       </c>
       <c r="E121" s="46"/>
       <c r="F121" s="32" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G121" s="47"/>
     </row>
@@ -5180,7 +5169,7 @@
         <v>123</v>
       </c>
       <c r="B122" s="23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C122" s="23" t="s">
         <v>8</v>
@@ -5190,7 +5179,7 @@
       </c>
       <c r="E122" s="46"/>
       <c r="F122" s="32" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G122" s="27"/>
     </row>
@@ -5199,7 +5188,7 @@
         <v>124</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C123" s="23" t="s">
         <v>8</v>
@@ -5211,7 +5200,7 @@
         <v>10</v>
       </c>
       <c r="F123" s="32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G123" s="27"/>
     </row>
@@ -5220,19 +5209,19 @@
         <v>125</v>
       </c>
       <c r="B124" s="23" t="s">
+        <v>311</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="45" t="s">
         <v>312</v>
-      </c>
-      <c r="C124" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D124" s="45" t="s">
-        <v>313</v>
       </c>
       <c r="E124" s="45" t="s">
         <v>29</v>
       </c>
       <c r="F124" s="32" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G124" s="27"/>
     </row>
@@ -5241,7 +5230,7 @@
         <v>126</v>
       </c>
       <c r="B125" s="23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C125" s="23" t="s">
         <v>8</v>
@@ -5251,7 +5240,7 @@
       </c>
       <c r="E125" s="46"/>
       <c r="F125" s="32" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G125" s="27"/>
     </row>
@@ -5260,7 +5249,7 @@
         <v>127</v>
       </c>
       <c r="B126" s="23" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C126" s="23" t="s">
         <v>8</v>
@@ -5272,7 +5261,7 @@
         <v>29</v>
       </c>
       <c r="F126" s="32" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G126" s="27"/>
     </row>
@@ -5281,7 +5270,7 @@
         <v>128</v>
       </c>
       <c r="B127" s="23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C127" s="23" t="s">
         <v>8</v>
@@ -5293,7 +5282,7 @@
         <v>29</v>
       </c>
       <c r="F127" s="32" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G127" s="27"/>
     </row>
@@ -5302,7 +5291,7 @@
         <v>129</v>
       </c>
       <c r="B128" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C128" s="23" t="s">
         <v>8</v>
@@ -5314,10 +5303,10 @@
         <v>10</v>
       </c>
       <c r="F128" s="32" t="s">
+        <v>321</v>
+      </c>
+      <c r="G128" s="54" t="s">
         <v>322</v>
-      </c>
-      <c r="G128" s="58" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="129" ht="15.75" spans="1:7">
@@ -5325,7 +5314,7 @@
         <v>130</v>
       </c>
       <c r="B129" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C129" s="23" t="s">
         <v>8</v>
@@ -5337,10 +5326,10 @@
         <v>134</v>
       </c>
       <c r="F129" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="G129" s="56" t="s">
         <v>325</v>
-      </c>
-      <c r="G129" s="60" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="130" ht="15.75" spans="1:7">
@@ -5348,7 +5337,7 @@
         <v>131</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C130" s="23" t="s">
         <v>8</v>
@@ -5360,10 +5349,10 @@
         <v>29</v>
       </c>
       <c r="F130" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="G130" s="56" t="s">
         <v>328</v>
-      </c>
-      <c r="G130" s="60" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="131" ht="15.75" spans="1:7">
@@ -5371,7 +5360,7 @@
         <v>132</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C131" s="23" t="s">
         <v>8</v>
@@ -5383,10 +5372,10 @@
         <v>134</v>
       </c>
       <c r="F131" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="G131" s="56" t="s">
         <v>331</v>
-      </c>
-      <c r="G131" s="60" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="132" ht="15.75" spans="1:7">
@@ -5394,7 +5383,7 @@
         <v>133</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C132" s="23" t="s">
         <v>8</v>
@@ -5406,10 +5395,10 @@
         <v>134</v>
       </c>
       <c r="F132" s="32" t="s">
-        <v>309</v>
-      </c>
-      <c r="G132" s="60" t="s">
-        <v>333</v>
+        <v>308</v>
+      </c>
+      <c r="G132" s="56" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="133" ht="15.75" spans="1:7">
@@ -5417,7 +5406,7 @@
         <v>134</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C133" s="23" t="s">
         <v>8</v>
@@ -5429,7 +5418,7 @@
         <v>29</v>
       </c>
       <c r="F133" s="32" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:7">
@@ -5437,7 +5426,7 @@
         <v>135</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C134" s="23" t="s">
         <v>8</v>
@@ -5449,10 +5438,10 @@
         <v>134</v>
       </c>
       <c r="F134" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="G134" s="48" t="s">
         <v>337</v>
-      </c>
-      <c r="G134" s="48" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="135" ht="15.75" spans="1:7">
@@ -5460,7 +5449,7 @@
         <v>136</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C135" s="23" t="s">
         <v>8</v>
@@ -5472,10 +5461,10 @@
         <v>134</v>
       </c>
       <c r="F135" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="G135" s="56" t="s">
         <v>340</v>
-      </c>
-      <c r="G135" s="60" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="136" ht="15.75" spans="1:7">
@@ -5483,7 +5472,7 @@
         <v>137</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C136" s="23" t="s">
         <v>8</v>
@@ -5495,19 +5484,17 @@
         <v>134</v>
       </c>
       <c r="F136" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="G136" s="56" t="s">
         <v>343</v>
-      </c>
-      <c r="G136" s="60" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="137" ht="15.75" spans="1:7">
       <c r="A137" s="22">
         <v>138</v>
       </c>
-      <c r="B137" s="23" t="s">
-        <v>345</v>
-      </c>
+      <c r="B137" s="23"/>
       <c r="C137" s="23" t="s">
         <v>8</v>
       </c>
@@ -5518,10 +5505,10 @@
         <v>134</v>
       </c>
       <c r="F137" s="32" t="s">
-        <v>346</v>
-      </c>
-      <c r="G137" s="60" t="s">
-        <v>347</v>
+        <v>344</v>
+      </c>
+      <c r="G137" s="56" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="138" ht="15.75" spans="1:7">
@@ -5529,7 +5516,7 @@
         <v>139</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C138" s="23" t="s">
         <v>8</v>
@@ -5538,10 +5525,10 @@
         <v>9</v>
       </c>
       <c r="E138" s="16" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F138" s="32" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="139" ht="15.75" spans="1:7">
@@ -5549,7 +5536,7 @@
         <v>140</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C139" s="23" t="s">
         <v>8</v>
@@ -5561,10 +5548,10 @@
         <v>134</v>
       </c>
       <c r="F139" s="32" t="s">
-        <v>352</v>
-      </c>
-      <c r="G139" s="61" t="s">
-        <v>353</v>
+        <v>350</v>
+      </c>
+      <c r="G139" s="57" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="140" ht="15.75" spans="1:7">
@@ -5572,7 +5559,7 @@
         <v>141</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C140" s="23" t="s">
         <v>8</v>
@@ -5584,7 +5571,7 @@
         <v>234</v>
       </c>
       <c r="F140" s="32" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="141" ht="15.75" spans="1:7">
@@ -5592,7 +5579,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C141" s="23" t="s">
         <v>8</v>
@@ -5604,7 +5591,7 @@
         <v>29</v>
       </c>
       <c r="F141" s="32" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="142" ht="15.75" spans="1:7">
@@ -5635,19 +5622,19 @@
         <v>144</v>
       </c>
       <c r="B143" s="23" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C143" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D143" s="50" t="s">
+      <c r="D143" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="E143" s="50" t="s">
+      <c r="E143" s="31" t="s">
         <v>10</v>
       </c>
       <c r="F143" s="32" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="144" ht="15.75" spans="1:7">
@@ -5655,19 +5642,19 @@
         <v>145</v>
       </c>
       <c r="B144" s="23" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C144" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D144" s="50" t="s">
+      <c r="D144" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E144" s="50" t="s">
+      <c r="E144" s="31" t="s">
         <v>10</v>
       </c>
       <c r="F144" s="32" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="145" ht="19" customHeight="1" spans="1:7">
@@ -5675,22 +5662,22 @@
         <v>145</v>
       </c>
       <c r="B145" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="C145" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E145" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="F145" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="G145" s="25" t="s">
         <v>362</v>
-      </c>
-      <c r="C145" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D145" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E145" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F145" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="G145" s="25" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="146" ht="15.75" spans="1:7">
@@ -5698,41 +5685,41 @@
         <v>146</v>
       </c>
       <c r="B146" s="23" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C146" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D146" s="50" t="s">
+      <c r="D146" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="E146" s="50" t="s">
+      <c r="E146" s="31" t="s">
         <v>138</v>
       </c>
       <c r="F146" s="32" t="s">
-        <v>366</v>
-      </c>
-      <c r="G146" s="51"/>
+        <v>364</v>
+      </c>
+      <c r="G146" s="25"/>
     </row>
     <row r="147" ht="15.75" spans="1:7">
       <c r="A147" s="22">
         <v>147</v>
       </c>
       <c r="B147" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C147" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E147" s="31"/>
+      <c r="F147" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="C147" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D147" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E147" s="50"/>
-      <c r="F147" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="G147" s="62" t="s">
-        <v>367</v>
+      <c r="G147" s="58" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="148" ht="15.75" spans="1:7">
@@ -5740,151 +5727,185 @@
         <v>148</v>
       </c>
       <c r="B148" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="C148" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E148" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="F148" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="G148" s="55" t="s">
         <v>368</v>
-      </c>
-      <c r="C148" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D148" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E148" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F148" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="G148" s="63" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="149" ht="15.75" spans="1:7">
       <c r="A149" s="22">
         <v>149</v>
       </c>
-      <c r="B149" s="53" t="s">
-        <v>371</v>
+      <c r="B149" s="51" t="s">
+        <v>369</v>
       </c>
       <c r="C149" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D149" s="50" t="s">
+      <c r="D149" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="E149" s="50" t="s">
+      <c r="E149" s="31" t="s">
         <v>10</v>
       </c>
       <c r="F149" s="30" t="s">
-        <v>372</v>
-      </c>
-      <c r="G149" s="51"/>
+        <v>370</v>
+      </c>
+      <c r="G149" s="25"/>
     </row>
     <row r="150" ht="15.75" spans="1:7">
       <c r="A150" s="22">
         <v>150</v>
       </c>
-      <c r="B150" s="54" t="s">
+      <c r="B150" s="52" t="s">
+        <v>371</v>
+      </c>
+      <c r="C150" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E150" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F150" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="G150" s="53"/>
+    </row>
+    <row r="151" ht="15.75" spans="1:7">
+      <c r="A151" s="31">
+        <v>151</v>
+      </c>
+      <c r="B151" s="51" t="s">
         <v>373</v>
       </c>
-      <c r="C150" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="50" t="s">
+      <c r="C151" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="E150" s="50" t="s">
+      <c r="E151" s="31"/>
+      <c r="F151" s="24" t="s">
+        <v>374</v>
+      </c>
+      <c r="G151" s="53"/>
+    </row>
+    <row r="152" ht="15.75" spans="1:7">
+      <c r="A152" s="31">
+        <v>152</v>
+      </c>
+      <c r="B152" s="51" t="s">
+        <v>375</v>
+      </c>
+      <c r="C152" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E152" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="F150" s="30" t="s">
-        <v>374</v>
-      </c>
-      <c r="G150" s="55"/>
-    </row>
-    <row r="151" ht="15.75" spans="1:7">
-      <c r="A151" s="50">
-        <v>151</v>
-      </c>
-      <c r="B151" s="53" t="s">
-        <v>375</v>
-      </c>
-      <c r="C151" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="50" t="s">
+      <c r="F152" s="24" t="s">
+        <v>376</v>
+      </c>
+      <c r="G152" s="53"/>
+    </row>
+    <row r="153" ht="15.75" spans="1:7">
+      <c r="A153" s="31">
+        <v>153</v>
+      </c>
+      <c r="B153" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="C153" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="E151" s="50"/>
-      <c r="F151" s="56" t="s">
-        <v>376</v>
-      </c>
-      <c r="G151" s="55"/>
-    </row>
-    <row r="152" ht="15.75" spans="1:7">
-      <c r="A152" s="50">
-        <v>152</v>
-      </c>
-      <c r="B152" s="53" t="s">
-        <v>377</v>
-      </c>
-      <c r="C152" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D152" s="50" t="s">
+      <c r="E153" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F153" s="24" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" spans="1:7">
+      <c r="A154" s="31">
+        <v>153</v>
+      </c>
+      <c r="B154" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="C154" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="E152" s="50" t="s">
+      <c r="E154" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="F152" s="56" t="s">
-        <v>378</v>
-      </c>
-      <c r="G152" s="55"/>
-    </row>
-    <row r="153" ht="15.75" spans="1:7">
-      <c r="A153" s="50">
-        <v>153</v>
-      </c>
-      <c r="B153" s="51" t="s">
-        <v>379</v>
-      </c>
-      <c r="C153" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E153" s="50" t="s">
+      <c r="F154" s="24" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" spans="1:7">
+      <c r="A155" s="31">
+        <v>154</v>
+      </c>
+      <c r="B155" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="C155" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="F153" s="56" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="154" ht="15.75" spans="1:7">
-      <c r="A154" s="50">
-        <v>153</v>
-      </c>
-      <c r="B154" s="57" t="s">
-        <v>381</v>
-      </c>
-      <c r="C154" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D154" s="50" t="s">
-        <v>125</v>
-      </c>
-      <c r="E154" s="50" t="s">
+      <c r="F155" s="24" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" spans="1:7">
+      <c r="A156" s="31">
+        <v>155</v>
+      </c>
+      <c r="B156" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="C156" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="F154" s="56" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="D155" s="17"/>
-    </row>
-    <row r="156" spans="1:7">
-      <c r="D156" s="17"/>
+      <c r="F156" s="24" t="s">
+        <v>384</v>
+      </c>
     </row>
     <row r="157" spans="1:7">
       <c r="D157" s="17"/>
@@ -8911,7 +8932,7 @@
       <c r="D1164" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G147" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G156" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8970,6 +8991,7 @@
     <hyperlink ref="F151" r:id="rId52" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
     <hyperlink ref="F152" r:id="rId53" display="walid.sebastien@gmail.com"/>
     <hyperlink ref="F153" r:id="rId54" display="bensenadanadia3@gmail.com"/>
+    <hyperlink ref="F154" r:id="rId55" display="imedmedles@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -8992,202 +9014,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>395</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>395</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="425">
   <si>
     <t>N°</t>
   </si>
@@ -1187,6 +1187,12 @@
   </si>
   <si>
     <t>fezaziomarfz@gmail.com</t>
+  </si>
+  <si>
+    <t>LAID ABDELALI</t>
+  </si>
+  <si>
+    <t>aidabdelali@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2094,7 +2100,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2242,6 +2248,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2760,7 +2769,7 @@
       <c r="F7" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="54" t="s">
+      <c r="G7" s="55" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2783,7 +2792,7 @@
       <c r="F8" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="54" t="s">
+      <c r="G8" s="55" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2827,7 +2836,7 @@
       <c r="F10" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="54" t="s">
+      <c r="G10" s="55" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3375,7 +3384,7 @@
       <c r="F36" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="55" t="s">
+      <c r="G36" s="56" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3419,7 +3428,7 @@
       <c r="F38" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="54" t="s">
+      <c r="G38" s="55" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3715,7 +3724,7 @@
       <c r="F52" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="54" t="s">
+      <c r="G52" s="55" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3759,7 +3768,7 @@
       <c r="F54" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="54" t="s">
+      <c r="G54" s="55" t="s">
         <v>128</v>
       </c>
     </row>
@@ -3954,7 +3963,7 @@
       <c r="F63" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="G63" s="54" t="s">
+      <c r="G63" s="55" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4017,7 +4026,7 @@
       <c r="F66" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="G66" s="55" t="s">
+      <c r="G66" s="56" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4061,7 +4070,7 @@
       <c r="F68" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="G68" s="54" t="s">
+      <c r="G68" s="55" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4082,7 +4091,7 @@
       <c r="F69" s="32" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="54" t="s">
+      <c r="G69" s="55" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4103,7 +4112,7 @@
       <c r="F70" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="G70" s="54" t="s">
+      <c r="G70" s="55" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4124,7 +4133,7 @@
       <c r="F71" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="G71" s="54" t="s">
+      <c r="G71" s="55" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4147,7 +4156,7 @@
       <c r="F72" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="G72" s="54" t="s">
+      <c r="G72" s="55" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4212,7 +4221,7 @@
       <c r="F75" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="G75" s="54" t="s">
+      <c r="G75" s="55" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4277,7 +4286,7 @@
       <c r="F78" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="G78" s="54" t="s">
+      <c r="G78" s="55" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4489,7 +4498,7 @@
       <c r="F88" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="G88" s="54" t="s">
+      <c r="G88" s="55" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4533,7 +4542,7 @@
       <c r="F90" s="32" t="s">
         <v>231</v>
       </c>
-      <c r="G90" s="54" t="s">
+      <c r="G90" s="55" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4556,7 +4565,7 @@
       <c r="F91" s="32" t="s">
         <v>235</v>
       </c>
-      <c r="G91" s="54" t="s">
+      <c r="G91" s="55" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4600,7 +4609,7 @@
       <c r="F93" s="44" t="s">
         <v>241</v>
       </c>
-      <c r="G93" s="54" t="s">
+      <c r="G93" s="55" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4835,7 +4844,7 @@
       <c r="F104" s="32" t="s">
         <v>272</v>
       </c>
-      <c r="G104" s="55" t="s">
+      <c r="G104" s="56" t="s">
         <v>273</v>
       </c>
     </row>
@@ -5305,7 +5314,7 @@
       <c r="F128" s="32" t="s">
         <v>321</v>
       </c>
-      <c r="G128" s="54" t="s">
+      <c r="G128" s="55" t="s">
         <v>322</v>
       </c>
     </row>
@@ -5328,7 +5337,7 @@
       <c r="F129" s="32" t="s">
         <v>324</v>
       </c>
-      <c r="G129" s="56" t="s">
+      <c r="G129" s="57" t="s">
         <v>325</v>
       </c>
     </row>
@@ -5351,7 +5360,7 @@
       <c r="F130" s="32" t="s">
         <v>327</v>
       </c>
-      <c r="G130" s="56" t="s">
+      <c r="G130" s="57" t="s">
         <v>328</v>
       </c>
     </row>
@@ -5374,7 +5383,7 @@
       <c r="F131" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="G131" s="56" t="s">
+      <c r="G131" s="57" t="s">
         <v>331</v>
       </c>
     </row>
@@ -5397,7 +5406,7 @@
       <c r="F132" s="32" t="s">
         <v>308</v>
       </c>
-      <c r="G132" s="56" t="s">
+      <c r="G132" s="57" t="s">
         <v>332</v>
       </c>
     </row>
@@ -5463,7 +5472,7 @@
       <c r="F135" s="32" t="s">
         <v>339</v>
       </c>
-      <c r="G135" s="56" t="s">
+      <c r="G135" s="57" t="s">
         <v>340</v>
       </c>
     </row>
@@ -5486,7 +5495,7 @@
       <c r="F136" s="32" t="s">
         <v>342</v>
       </c>
-      <c r="G136" s="56" t="s">
+      <c r="G136" s="57" t="s">
         <v>343</v>
       </c>
     </row>
@@ -5507,7 +5516,7 @@
       <c r="F137" s="32" t="s">
         <v>344</v>
       </c>
-      <c r="G137" s="56" t="s">
+      <c r="G137" s="57" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5550,7 +5559,7 @@
       <c r="F139" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="G139" s="57" t="s">
+      <c r="G139" s="58" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5718,7 +5727,7 @@
       <c r="F147" s="32" t="s">
         <v>300</v>
       </c>
-      <c r="G147" s="58" t="s">
+      <c r="G147" s="59" t="s">
         <v>365</v>
       </c>
     </row>
@@ -5741,7 +5750,7 @@
       <c r="F148" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="G148" s="55" t="s">
+      <c r="G148" s="56" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5907,11 +5916,45 @@
         <v>384</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
-      <c r="D157" s="17"/>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="D158" s="17"/>
+    <row r="157" ht="15.75" spans="1:7">
+      <c r="A157" s="31">
+        <v>155</v>
+      </c>
+      <c r="B157" s="27" t="s">
+        <v>383</v>
+      </c>
+      <c r="C157" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F157" s="24" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" spans="1:7">
+      <c r="A158" s="31">
+        <v>156</v>
+      </c>
+      <c r="B158" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="C158" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="E158" s="54" t="s">
+        <v>134</v>
+      </c>
+      <c r="F158" s="24" t="s">
+        <v>386</v>
+      </c>
     </row>
     <row r="159" spans="1:7">
       <c r="D159" s="17"/>
@@ -8992,6 +9035,7 @@
     <hyperlink ref="F152" r:id="rId53" display="walid.sebastien@gmail.com"/>
     <hyperlink ref="F153" r:id="rId54" display="bensenadanadia3@gmail.com"/>
     <hyperlink ref="F154" r:id="rId55" display="imedmedles@gmail.com"/>
+    <hyperlink ref="F158" r:id="rId56" display="aidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -9014,202 +9058,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>397</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>397</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$158</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="427">
   <si>
     <t>N°</t>
   </si>
@@ -1193,6 +1193,12 @@
   </si>
   <si>
     <t>aidabdelali@gmail.com</t>
+  </si>
+  <si>
+    <t>LAZERGUI SIHEM</t>
+  </si>
+  <si>
+    <t>sihemlazergui@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2249,9 +2255,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -5946,18 +5950,32 @@
       <c r="C158" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="54" t="s">
+      <c r="D158" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="E158" s="54" t="s">
+      <c r="E158" s="31" t="s">
         <v>134</v>
       </c>
       <c r="F158" s="24" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
-      <c r="D159" s="17"/>
+    <row r="159" ht="15.75" spans="1:7">
+      <c r="B159" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="C159" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E159" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="F159" s="54" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="160" spans="1:7">
       <c r="D160" s="17"/>
@@ -8975,7 +8993,7 @@
       <c r="D1164" s="17"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G156" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G158" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -9058,202 +9076,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>399</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>399</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -211,7 +211,7 @@
     <t>boukhoulda.fodil@yahoo.fr</t>
   </si>
   <si>
-    <t>BOUNOUA HOURIA</t>
+    <t>SEMMACHE HOURIA</t>
   </si>
   <si>
     <t>hsemmach@yahoo.fr</t>
@@ -985,7 +985,7 @@
     <t>klomar05@yahoo.fr</t>
   </si>
   <si>
-    <t>SAIDI KHEIREDDINE</t>
+    <t>SAIDI KHEYREDDINE</t>
   </si>
   <si>
     <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
@@ -2182,7 +2182,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2336,16 +2336,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2359,9 +2350,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2709,7 +2697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:G1163"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
@@ -2746,7 +2734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" spans="1:7">
+    <row r="2" ht="15.75" spans="1:7">
       <c r="A2" s="23">
         <v>1</v>
       </c>
@@ -2767,7 +2755,7 @@
       </c>
       <c r="G2" s="26"/>
     </row>
-    <row r="3" ht="15.75" hidden="1" spans="1:7">
+    <row r="3" ht="15.75" spans="1:7">
       <c r="A3" s="23">
         <v>2</v>
       </c>
@@ -2788,7 +2776,7 @@
       </c>
       <c r="G3" s="26"/>
     </row>
-    <row r="4" ht="15.75" hidden="1" spans="1:7">
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="23">
         <v>3</v>
       </c>
@@ -2809,7 +2797,7 @@
       </c>
       <c r="G4" s="26"/>
     </row>
-    <row r="5" ht="15.75" hidden="1" spans="1:7">
+    <row r="5" ht="15.75" spans="1:7">
       <c r="A5" s="23">
         <v>4</v>
       </c>
@@ -2830,7 +2818,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" ht="15.75" hidden="1" spans="1:7">
+    <row r="6" ht="15.75" spans="1:7">
       <c r="A6" s="23">
         <v>5</v>
       </c>
@@ -2851,7 +2839,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" ht="15.75" hidden="1" spans="1:7">
+    <row r="7" ht="15.75" spans="1:7">
       <c r="A7" s="23">
         <v>6</v>
       </c>
@@ -2870,11 +2858,11 @@
       <c r="F7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="58" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" hidden="1" spans="1:7">
+    <row r="8" ht="15.75" spans="1:7">
       <c r="A8" s="23">
         <v>7</v>
       </c>
@@ -2893,11 +2881,11 @@
       <c r="F8" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="61" t="s">
+      <c r="G8" s="58" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" hidden="1" spans="1:7">
+    <row r="9" ht="15.75" spans="1:7">
       <c r="A9" s="23">
         <v>8</v>
       </c>
@@ -2918,7 +2906,7 @@
       </c>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" ht="15.75" hidden="1" spans="1:7">
+    <row r="10" ht="15.75" spans="1:7">
       <c r="A10" s="23">
         <v>9</v>
       </c>
@@ -2937,11 +2925,11 @@
       <c r="F10" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="61" t="s">
+      <c r="G10" s="58" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" hidden="1" spans="1:7">
+    <row r="11" ht="15.75" spans="1:7">
       <c r="A11" s="23">
         <v>10</v>
       </c>
@@ -2962,7 +2950,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" ht="15.75" hidden="1" spans="1:7">
+    <row r="12" ht="15.75" spans="1:7">
       <c r="A12" s="23">
         <v>11</v>
       </c>
@@ -2983,7 +2971,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" ht="15.75" hidden="1" spans="1:7">
+    <row r="13" ht="15.75" spans="1:7">
       <c r="A13" s="23">
         <v>12</v>
       </c>
@@ -3004,7 +2992,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" ht="15.75" hidden="1" spans="1:7">
+    <row r="14" ht="15.75" spans="1:7">
       <c r="A14" s="23">
         <v>13</v>
       </c>
@@ -3025,7 +3013,7 @@
       </c>
       <c r="G14" s="26"/>
     </row>
-    <row r="15" ht="15.75" hidden="1" spans="1:7">
+    <row r="15" ht="15.75" spans="1:7">
       <c r="A15" s="23">
         <v>14</v>
       </c>
@@ -3046,7 +3034,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" ht="15.75" hidden="1" spans="1:7">
+    <row r="16" ht="15.75" spans="1:7">
       <c r="A16" s="23">
         <v>15</v>
       </c>
@@ -3067,7 +3055,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" ht="15.75" hidden="1" spans="1:7">
+    <row r="17" ht="15.75" spans="1:7">
       <c r="A17" s="23">
         <v>16</v>
       </c>
@@ -3088,7 +3076,7 @@
       </c>
       <c r="G17" s="26"/>
     </row>
-    <row r="18" ht="15.75" hidden="1" spans="1:7">
+    <row r="18" ht="15.75" spans="1:7">
       <c r="A18" s="23">
         <v>17</v>
       </c>
@@ -3109,7 +3097,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" ht="15.75" hidden="1" spans="1:7">
+    <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="23">
         <v>18</v>
       </c>
@@ -3130,7 +3118,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" ht="15.75" hidden="1" spans="1:7">
+    <row r="20" ht="15.75" spans="1:7">
       <c r="A20" s="23">
         <v>19</v>
       </c>
@@ -3151,7 +3139,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" ht="15.75" hidden="1" spans="1:7">
+    <row r="21" ht="15.75" spans="1:7">
       <c r="A21" s="23">
         <v>20</v>
       </c>
@@ -3172,7 +3160,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" ht="15.75" hidden="1" spans="1:7">
+    <row r="22" ht="15.75" spans="1:7">
       <c r="A22" s="23">
         <v>21</v>
       </c>
@@ -3193,7 +3181,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" ht="15.75" hidden="1" spans="1:7">
+    <row r="23" ht="15.75" spans="1:7">
       <c r="A23" s="23">
         <v>22</v>
       </c>
@@ -3214,7 +3202,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" ht="15.75" hidden="1" spans="1:7">
+    <row r="24" ht="15.75" spans="1:7">
       <c r="A24" s="23">
         <v>23</v>
       </c>
@@ -3235,7 +3223,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" ht="15.75" hidden="1" spans="1:7">
+    <row r="25" ht="15.75" spans="1:7">
       <c r="A25" s="23">
         <v>24</v>
       </c>
@@ -3256,7 +3244,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" ht="15.75" hidden="1" spans="1:7">
+    <row r="26" ht="15.75" spans="1:7">
       <c r="A26" s="23">
         <v>25</v>
       </c>
@@ -3277,7 +3265,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" ht="15.75" hidden="1" spans="1:7">
+    <row r="27" ht="15.75" spans="1:7">
       <c r="A27" s="23">
         <v>26</v>
       </c>
@@ -3298,7 +3286,7 @@
       </c>
       <c r="G27" s="26"/>
     </row>
-    <row r="28" ht="15.75" hidden="1" spans="1:7">
+    <row r="28" ht="15.75" spans="1:7">
       <c r="A28" s="23">
         <v>27</v>
       </c>
@@ -3319,7 +3307,7 @@
       </c>
       <c r="G28" s="26"/>
     </row>
-    <row r="29" ht="15.75" hidden="1" spans="1:7">
+    <row r="29" ht="15.75" spans="1:7">
       <c r="A29" s="23">
         <v>28</v>
       </c>
@@ -3340,7 +3328,7 @@
       </c>
       <c r="G29" s="26"/>
     </row>
-    <row r="30" ht="15.75" hidden="1" spans="1:7">
+    <row r="30" ht="15.75" spans="1:7">
       <c r="A30" s="23">
         <v>29</v>
       </c>
@@ -3361,7 +3349,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
+    <row r="31" ht="15.75" spans="1:7">
       <c r="A31" s="23">
         <v>30</v>
       </c>
@@ -3382,7 +3370,7 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
+    <row r="32" ht="15.75" spans="1:7">
       <c r="A32" s="23">
         <v>31</v>
       </c>
@@ -3403,7 +3391,7 @@
       </c>
       <c r="G32" s="26"/>
     </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
+    <row r="33" ht="15.75" spans="1:7">
       <c r="A33" s="23">
         <v>32</v>
       </c>
@@ -3424,7 +3412,7 @@
       </c>
       <c r="G33" s="26"/>
     </row>
-    <row r="34" ht="15.75" hidden="1" spans="1:7">
+    <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="23">
         <v>34</v>
       </c>
@@ -3445,7 +3433,7 @@
       </c>
       <c r="G34" s="26"/>
     </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
+    <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="23">
         <v>35</v>
       </c>
@@ -3466,7 +3454,7 @@
       </c>
       <c r="G35" s="26"/>
     </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
+    <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="23">
         <v>36</v>
       </c>
@@ -3485,11 +3473,11 @@
       <c r="F36" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="62" t="s">
+      <c r="G36" s="59" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="23">
         <v>37</v>
       </c>
@@ -3510,7 +3498,7 @@
       </c>
       <c r="G37" s="26"/>
     </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
+    <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="23">
         <v>38</v>
       </c>
@@ -3529,11 +3517,11 @@
       <c r="F38" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="61" t="s">
+      <c r="G38" s="58" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="15.75" hidden="1" spans="1:7">
+    <row r="39" ht="15.75" spans="1:7">
       <c r="A39" s="23">
         <v>39</v>
       </c>
@@ -3554,7 +3542,7 @@
       </c>
       <c r="G39" s="26"/>
     </row>
-    <row r="40" ht="15.75" hidden="1" spans="1:7">
+    <row r="40" ht="15.75" spans="1:7">
       <c r="A40" s="23">
         <v>40</v>
       </c>
@@ -3575,7 +3563,7 @@
       </c>
       <c r="G40" s="26"/>
     </row>
-    <row r="41" ht="15.75" hidden="1" spans="1:7">
+    <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="23">
         <v>41</v>
       </c>
@@ -3596,7 +3584,7 @@
       </c>
       <c r="G41" s="26"/>
     </row>
-    <row r="42" ht="15.75" hidden="1" spans="1:7">
+    <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="23">
         <v>42</v>
       </c>
@@ -3617,7 +3605,7 @@
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" ht="15.75" hidden="1" spans="1:7">
+    <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="23">
         <v>43</v>
       </c>
@@ -3638,7 +3626,7 @@
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" ht="15.75" hidden="1" spans="1:7">
+    <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="23">
         <v>44</v>
       </c>
@@ -3659,7 +3647,7 @@
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" ht="15.75" hidden="1" spans="1:7">
+    <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="23">
         <v>45</v>
       </c>
@@ -3680,7 +3668,7 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" ht="15.75" hidden="1" spans="1:7">
+    <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="23">
         <v>46</v>
       </c>
@@ -3701,7 +3689,7 @@
       </c>
       <c r="G46" s="26"/>
     </row>
-    <row r="47" ht="15.75" hidden="1" spans="1:7">
+    <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="23">
         <v>47</v>
       </c>
@@ -3722,7 +3710,7 @@
       </c>
       <c r="G47" s="26"/>
     </row>
-    <row r="48" ht="15.75" hidden="1" spans="1:7">
+    <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="23">
         <v>48</v>
       </c>
@@ -3743,7 +3731,7 @@
       </c>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
+    <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="23">
         <v>49</v>
       </c>
@@ -3764,7 +3752,7 @@
       </c>
       <c r="G49" s="26"/>
     </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
+    <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="23">
         <v>50</v>
       </c>
@@ -3785,7 +3773,7 @@
       </c>
       <c r="G50" s="26"/>
     </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
+    <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="23">
         <v>51</v>
       </c>
@@ -3806,7 +3794,7 @@
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
+    <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="23">
         <v>52</v>
       </c>
@@ -3825,11 +3813,11 @@
       <c r="F52" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="61" t="s">
+      <c r="G52" s="58" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
+    <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="23">
         <v>53</v>
       </c>
@@ -3869,7 +3857,7 @@
       <c r="F54" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="61" t="s">
+      <c r="G54" s="58" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4047,7 +4035,7 @@
       <c r="F62" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="G62" s="61" t="s">
+      <c r="G62" s="58" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4110,7 +4098,7 @@
       <c r="F65" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G65" s="62" t="s">
+      <c r="G65" s="59" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4154,7 +4142,7 @@
       <c r="F67" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="G67" s="61" t="s">
+      <c r="G67" s="58" t="s">
         <v>169</v>
       </c>
     </row>
@@ -4175,7 +4163,7 @@
       <c r="F68" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="G68" s="61" t="s">
+      <c r="G68" s="58" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4196,7 +4184,7 @@
       <c r="F69" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="G69" s="61" t="s">
+      <c r="G69" s="58" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4217,7 +4205,7 @@
       <c r="F70" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="G70" s="61" t="s">
+      <c r="G70" s="58" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4240,7 +4228,7 @@
       <c r="F71" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="61" t="s">
+      <c r="G71" s="58" t="s">
         <v>181</v>
       </c>
     </row>
@@ -4305,7 +4293,7 @@
       <c r="F74" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="G74" s="61" t="s">
+      <c r="G74" s="58" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4370,7 +4358,7 @@
       <c r="F77" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="G77" s="61" t="s">
+      <c r="G77" s="58" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4582,7 +4570,7 @@
       <c r="F87" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="G87" s="61" t="s">
+      <c r="G87" s="58" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4626,7 +4614,7 @@
       <c r="F89" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="G89" s="61" t="s">
+      <c r="G89" s="58" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4649,7 +4637,7 @@
       <c r="F90" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="G90" s="61" t="s">
+      <c r="G90" s="58" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4693,7 +4681,7 @@
       <c r="F92" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="G92" s="61" t="s">
+      <c r="G92" s="58" t="s">
         <v>241</v>
       </c>
     </row>
@@ -4928,7 +4916,7 @@
       <c r="F103" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="G103" s="62" t="s">
+      <c r="G103" s="59" t="s">
         <v>272</v>
       </c>
     </row>
@@ -5297,7 +5285,7 @@
       </c>
       <c r="G122" s="28"/>
     </row>
-    <row r="123" ht="31.5" hidden="1" spans="1:7">
+    <row r="123" ht="31.5" spans="1:7">
       <c r="A123" s="23">
         <v>125</v>
       </c>
@@ -5337,7 +5325,7 @@
       </c>
       <c r="G124" s="28"/>
     </row>
-    <row r="125" ht="15.75" hidden="1" spans="1:7">
+    <row r="125" ht="15.75" spans="1:7">
       <c r="A125" s="23">
         <v>127</v>
       </c>
@@ -5358,7 +5346,7 @@
       </c>
       <c r="G125" s="28"/>
     </row>
-    <row r="126" ht="15.75" hidden="1" spans="1:7">
+    <row r="126" ht="15.75" spans="1:7">
       <c r="A126" s="23">
         <v>128</v>
       </c>
@@ -5379,7 +5367,7 @@
       </c>
       <c r="G126" s="28"/>
     </row>
-    <row r="127" ht="15.75" hidden="1" spans="1:7">
+    <row r="127" ht="15.75" spans="1:7">
       <c r="A127" s="23">
         <v>129</v>
       </c>
@@ -5398,7 +5386,7 @@
       <c r="F127" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="G127" s="61" t="s">
+      <c r="G127" s="58" t="s">
         <v>321</v>
       </c>
     </row>
@@ -5421,11 +5409,11 @@
       <c r="F128" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="G128" s="63" t="s">
+      <c r="G128" s="60" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="129" ht="15.75" hidden="1" spans="1:7">
+    <row r="129" ht="15.75" spans="1:7">
       <c r="A129" s="23">
         <v>131</v>
       </c>
@@ -5444,7 +5432,7 @@
       <c r="F129" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="G129" s="63" t="s">
+      <c r="G129" s="60" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5467,7 +5455,7 @@
       <c r="F130" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="G130" s="63" t="s">
+      <c r="G130" s="60" t="s">
         <v>330</v>
       </c>
     </row>
@@ -5490,11 +5478,11 @@
       <c r="F131" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="G131" s="63" t="s">
+      <c r="G131" s="60" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="132" ht="15.75" hidden="1" spans="1:7">
+    <row r="132" ht="15.75" spans="1:7">
       <c r="A132" s="23">
         <v>134</v>
       </c>
@@ -5556,7 +5544,7 @@
       <c r="F134" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="G134" s="63" t="s">
+      <c r="G134" s="60" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5579,7 +5567,7 @@
       <c r="F135" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="G135" s="63" t="s">
+      <c r="G135" s="60" t="s">
         <v>342</v>
       </c>
     </row>
@@ -5600,11 +5588,11 @@
       <c r="F136" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="63" t="s">
+      <c r="G136" s="60" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="137" ht="15.75" hidden="1" spans="1:7">
+    <row r="137" ht="15.75" spans="1:7">
       <c r="A137" s="23">
         <v>139</v>
       </c>
@@ -5643,7 +5631,7 @@
       <c r="F138" s="33" t="s">
         <v>349</v>
       </c>
-      <c r="G138" s="64" t="s">
+      <c r="G138" s="61" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5667,7 +5655,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="140" ht="15.75" hidden="1" spans="1:7">
+    <row r="140" ht="15.75" spans="1:7">
       <c r="A140" s="23">
         <v>142</v>
       </c>
@@ -5710,7 +5698,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="142" ht="15.75" hidden="1" spans="1:7">
+    <row r="142" ht="15.75" spans="1:7">
       <c r="A142" s="23">
         <v>144</v>
       </c>
@@ -5730,7 +5718,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="143" ht="15.75" hidden="1" spans="1:7">
+    <row r="143" ht="15.75" spans="1:7">
       <c r="A143" s="23">
         <v>145</v>
       </c>
@@ -5811,7 +5799,7 @@
       <c r="F146" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="G146" s="65" t="s">
+      <c r="G146" s="62" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5834,11 +5822,11 @@
       <c r="F147" s="31" t="s">
         <v>366</v>
       </c>
-      <c r="G147" s="62" t="s">
+      <c r="G147" s="59" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="148" ht="15.75" hidden="1" spans="1:7">
+    <row r="148" ht="15.75" spans="1:7">
       <c r="A148" s="23">
         <v>149</v>
       </c>
@@ -5962,7 +5950,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" ht="15.75" hidden="1" spans="1:7">
+    <row r="154" ht="15.75" spans="1:7">
       <c r="A154" s="32">
         <v>154</v>
       </c>
@@ -5983,7 +5971,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" ht="15.75" hidden="1" spans="1:7">
+    <row r="155" ht="15.75" spans="1:7">
       <c r="A155" s="32">
         <v>155</v>
       </c>
@@ -6004,7 +5992,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" ht="15.75" hidden="1" spans="1:7">
+    <row r="156" ht="15.75" spans="1:7">
       <c r="A156" s="32">
         <v>155</v>
       </c>
@@ -6086,7 +6074,7 @@
       <c r="F159" s="55" t="s">
         <v>389</v>
       </c>
-      <c r="G159" s="62" t="s">
+      <c r="G159" s="59" t="s">
         <v>390</v>
       </c>
     </row>
@@ -6115,7 +6103,7 @@
       <c r="A161" s="32">
         <v>160</v>
       </c>
-      <c r="B161" s="56" t="s">
+      <c r="B161" s="51" t="s">
         <v>393</v>
       </c>
       <c r="C161" s="24" t="s">
@@ -6130,7 +6118,7 @@
       <c r="F161" s="25" t="s">
         <v>394</v>
       </c>
-      <c r="G161" s="62" t="s">
+      <c r="G161" s="59" t="s">
         <v>395</v>
       </c>
     </row>
@@ -6151,7 +6139,7 @@
         <v>137</v>
       </c>
       <c r="F162" s="26"/>
-      <c r="G162" s="66" t="s">
+      <c r="G162" s="59" t="s">
         <v>397</v>
       </c>
     </row>
@@ -6174,7 +6162,7 @@
       <c r="F163" s="25" t="s">
         <v>399</v>
       </c>
-      <c r="G163" s="66" t="s">
+      <c r="G163" s="59" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6197,7 +6185,7 @@
       <c r="F164" s="25" t="s">
         <v>402</v>
       </c>
-      <c r="G164" s="66" t="s">
+      <c r="G164" s="59" t="s">
         <v>403</v>
       </c>
     </row>
@@ -6205,22 +6193,22 @@
       <c r="A165" s="32">
         <v>164</v>
       </c>
-      <c r="B165" s="58" t="s">
+      <c r="B165" s="56" t="s">
         <v>404</v>
       </c>
       <c r="C165" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D165" s="59" t="s">
+      <c r="D165" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="E165" s="59" t="s">
+      <c r="E165" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="F165" s="60" t="s">
+      <c r="F165" s="57" t="s">
         <v>405</v>
       </c>
-      <c r="G165" s="66" t="s">
+      <c r="G165" s="59" t="s">
         <v>406</v>
       </c>
     </row>
@@ -6228,22 +6216,22 @@
       <c r="A166" s="32">
         <v>165</v>
       </c>
-      <c r="B166" s="57" t="s">
+      <c r="B166" s="26" t="s">
         <v>407</v>
       </c>
       <c r="C166" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D166" s="59" t="s">
+      <c r="D166" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E166" s="59" t="s">
+      <c r="E166" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="F166" s="60" t="s">
+      <c r="F166" s="57" t="s">
         <v>408</v>
       </c>
-      <c r="G166" s="66" t="s">
+      <c r="G166" s="59" t="s">
         <v>409</v>
       </c>
     </row>
@@ -9239,12 +9227,7 @@
       <c r="D1163" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G165" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="3">
-      <customFilters>
-        <customFilter operator="equal" val="Vacataire"/>
-      </customFilters>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G166" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -985,7 +985,7 @@
     <t>klomar05@yahoo.fr</t>
   </si>
   <si>
-    <t>SAIDI KHEYREDDINE</t>
+    <t>SAIDI KHAYREDDINE</t>
   </si>
   <si>
     <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
@@ -2697,7 +2697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr filterMode="1" codeName="Sheet1"/>
   <dimension ref="A1:G1163"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
@@ -2734,7 +2734,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" spans="1:7">
+    <row r="2" ht="15.75" hidden="1" spans="1:7">
       <c r="A2" s="23">
         <v>1</v>
       </c>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G2" s="26"/>
     </row>
-    <row r="3" ht="15.75" spans="1:7">
+    <row r="3" ht="15.75" hidden="1" spans="1:7">
       <c r="A3" s="23">
         <v>2</v>
       </c>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="G3" s="26"/>
     </row>
-    <row r="4" ht="15.75" spans="1:7">
+    <row r="4" ht="15.75" hidden="1" spans="1:7">
       <c r="A4" s="23">
         <v>3</v>
       </c>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="G4" s="26"/>
     </row>
-    <row r="5" ht="15.75" spans="1:7">
+    <row r="5" ht="15.75" hidden="1" spans="1:7">
       <c r="A5" s="23">
         <v>4</v>
       </c>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" ht="15.75" spans="1:7">
+    <row r="6" ht="15.75" hidden="1" spans="1:7">
       <c r="A6" s="23">
         <v>5</v>
       </c>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" ht="15.75" spans="1:7">
+    <row r="7" ht="15.75" hidden="1" spans="1:7">
       <c r="A7" s="23">
         <v>6</v>
       </c>
@@ -2862,7 +2862,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" spans="1:7">
+    <row r="8" ht="15.75" hidden="1" spans="1:7">
       <c r="A8" s="23">
         <v>7</v>
       </c>
@@ -2885,7 +2885,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" spans="1:7">
+    <row r="9" ht="15.75" hidden="1" spans="1:7">
       <c r="A9" s="23">
         <v>8</v>
       </c>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" ht="15.75" spans="1:7">
+    <row r="10" ht="15.75" hidden="1" spans="1:7">
       <c r="A10" s="23">
         <v>9</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" spans="1:7">
+    <row r="11" ht="15.75" hidden="1" spans="1:7">
       <c r="A11" s="23">
         <v>10</v>
       </c>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" ht="15.75" spans="1:7">
+    <row r="12" ht="15.75" hidden="1" spans="1:7">
       <c r="A12" s="23">
         <v>11</v>
       </c>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" ht="15.75" spans="1:7">
+    <row r="13" ht="15.75" hidden="1" spans="1:7">
       <c r="A13" s="23">
         <v>12</v>
       </c>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" ht="15.75" spans="1:7">
+    <row r="14" ht="15.75" hidden="1" spans="1:7">
       <c r="A14" s="23">
         <v>13</v>
       </c>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="G14" s="26"/>
     </row>
-    <row r="15" ht="15.75" spans="1:7">
+    <row r="15" ht="15.75" hidden="1" spans="1:7">
       <c r="A15" s="23">
         <v>14</v>
       </c>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" ht="15.75" spans="1:7">
+    <row r="16" ht="15.75" hidden="1" spans="1:7">
       <c r="A16" s="23">
         <v>15</v>
       </c>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" ht="15.75" spans="1:7">
+    <row r="17" ht="15.75" hidden="1" spans="1:7">
       <c r="A17" s="23">
         <v>16</v>
       </c>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G17" s="26"/>
     </row>
-    <row r="18" ht="15.75" spans="1:7">
+    <row r="18" ht="15.75" hidden="1" spans="1:7">
       <c r="A18" s="23">
         <v>17</v>
       </c>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" ht="15.75" spans="1:7">
+    <row r="19" ht="15.75" hidden="1" spans="1:7">
       <c r="A19" s="23">
         <v>18</v>
       </c>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" ht="15.75" spans="1:7">
+    <row r="20" ht="15.75" hidden="1" spans="1:7">
       <c r="A20" s="23">
         <v>19</v>
       </c>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" ht="15.75" spans="1:7">
+    <row r="21" ht="15.75" hidden="1" spans="1:7">
       <c r="A21" s="23">
         <v>20</v>
       </c>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" ht="15.75" spans="1:7">
+    <row r="22" ht="15.75" hidden="1" spans="1:7">
       <c r="A22" s="23">
         <v>21</v>
       </c>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" ht="15.75" spans="1:7">
+    <row r="23" ht="15.75" hidden="1" spans="1:7">
       <c r="A23" s="23">
         <v>22</v>
       </c>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" ht="15.75" spans="1:7">
+    <row r="24" ht="15.75" hidden="1" spans="1:7">
       <c r="A24" s="23">
         <v>23</v>
       </c>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" ht="15.75" spans="1:7">
+    <row r="25" ht="15.75" hidden="1" spans="1:7">
       <c r="A25" s="23">
         <v>24</v>
       </c>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" ht="15.75" spans="1:7">
+    <row r="26" ht="15.75" hidden="1" spans="1:7">
       <c r="A26" s="23">
         <v>25</v>
       </c>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" ht="15.75" spans="1:7">
+    <row r="27" ht="15.75" hidden="1" spans="1:7">
       <c r="A27" s="23">
         <v>26</v>
       </c>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G27" s="26"/>
     </row>
-    <row r="28" ht="15.75" spans="1:7">
+    <row r="28" ht="15.75" hidden="1" spans="1:7">
       <c r="A28" s="23">
         <v>27</v>
       </c>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="G28" s="26"/>
     </row>
-    <row r="29" ht="15.75" spans="1:7">
+    <row r="29" ht="15.75" hidden="1" spans="1:7">
       <c r="A29" s="23">
         <v>28</v>
       </c>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="G29" s="26"/>
     </row>
-    <row r="30" ht="15.75" spans="1:7">
+    <row r="30" ht="15.75" hidden="1" spans="1:7">
       <c r="A30" s="23">
         <v>29</v>
       </c>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" ht="15.75" spans="1:7">
+    <row r="31" ht="15.75" hidden="1" spans="1:7">
       <c r="A31" s="23">
         <v>30</v>
       </c>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" ht="15.75" spans="1:7">
+    <row r="32" ht="15.75" hidden="1" spans="1:7">
       <c r="A32" s="23">
         <v>31</v>
       </c>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="G32" s="26"/>
     </row>
-    <row r="33" ht="15.75" spans="1:7">
+    <row r="33" ht="15.75" hidden="1" spans="1:7">
       <c r="A33" s="23">
         <v>32</v>
       </c>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G33" s="26"/>
     </row>
-    <row r="34" ht="15.75" spans="1:7">
+    <row r="34" ht="15.75" hidden="1" spans="1:7">
       <c r="A34" s="23">
         <v>34</v>
       </c>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="G34" s="26"/>
     </row>
-    <row r="35" ht="15.75" spans="1:7">
+    <row r="35" ht="15.75" hidden="1" spans="1:7">
       <c r="A35" s="23">
         <v>35</v>
       </c>
@@ -3454,7 +3454,7 @@
       </c>
       <c r="G35" s="26"/>
     </row>
-    <row r="36" ht="15.75" spans="1:7">
+    <row r="36" ht="15.75" hidden="1" spans="1:7">
       <c r="A36" s="23">
         <v>36</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" ht="15.75" spans="1:7">
+    <row r="37" ht="15.75" hidden="1" spans="1:7">
       <c r="A37" s="23">
         <v>37</v>
       </c>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="G37" s="26"/>
     </row>
-    <row r="38" ht="15.75" spans="1:7">
+    <row r="38" ht="15.75" hidden="1" spans="1:7">
       <c r="A38" s="23">
         <v>38</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="15.75" spans="1:7">
+    <row r="39" ht="15.75" hidden="1" spans="1:7">
       <c r="A39" s="23">
         <v>39</v>
       </c>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="G39" s="26"/>
     </row>
-    <row r="40" ht="15.75" spans="1:7">
+    <row r="40" ht="15.75" hidden="1" spans="1:7">
       <c r="A40" s="23">
         <v>40</v>
       </c>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G40" s="26"/>
     </row>
-    <row r="41" ht="15.75" spans="1:7">
+    <row r="41" ht="15.75" hidden="1" spans="1:7">
       <c r="A41" s="23">
         <v>41</v>
       </c>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="G41" s="26"/>
     </row>
-    <row r="42" ht="15.75" spans="1:7">
+    <row r="42" ht="15.75" hidden="1" spans="1:7">
       <c r="A42" s="23">
         <v>42</v>
       </c>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" ht="15.75" spans="1:7">
+    <row r="43" ht="15.75" hidden="1" spans="1:7">
       <c r="A43" s="23">
         <v>43</v>
       </c>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" ht="15.75" spans="1:7">
+    <row r="44" ht="15.75" hidden="1" spans="1:7">
       <c r="A44" s="23">
         <v>44</v>
       </c>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" ht="15.75" spans="1:7">
+    <row r="45" ht="15.75" hidden="1" spans="1:7">
       <c r="A45" s="23">
         <v>45</v>
       </c>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" ht="15.75" spans="1:7">
+    <row r="46" ht="15.75" hidden="1" spans="1:7">
       <c r="A46" s="23">
         <v>46</v>
       </c>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="G46" s="26"/>
     </row>
-    <row r="47" ht="15.75" spans="1:7">
+    <row r="47" ht="15.75" hidden="1" spans="1:7">
       <c r="A47" s="23">
         <v>47</v>
       </c>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="G47" s="26"/>
     </row>
-    <row r="48" ht="15.75" spans="1:7">
+    <row r="48" ht="15.75" hidden="1" spans="1:7">
       <c r="A48" s="23">
         <v>48</v>
       </c>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" ht="15.75" spans="1:7">
+    <row r="49" ht="15.75" hidden="1" spans="1:7">
       <c r="A49" s="23">
         <v>49</v>
       </c>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="G49" s="26"/>
     </row>
-    <row r="50" ht="15.75" spans="1:7">
+    <row r="50" ht="15.75" hidden="1" spans="1:7">
       <c r="A50" s="23">
         <v>50</v>
       </c>
@@ -3773,7 +3773,7 @@
       </c>
       <c r="G50" s="26"/>
     </row>
-    <row r="51" ht="15.75" spans="1:7">
+    <row r="51" ht="15.75" hidden="1" spans="1:7">
       <c r="A51" s="23">
         <v>51</v>
       </c>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" ht="15.75" spans="1:7">
+    <row r="52" ht="15.75" hidden="1" spans="1:7">
       <c r="A52" s="23">
         <v>52</v>
       </c>
@@ -3817,7 +3817,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="53" ht="15.75" spans="1:7">
+    <row r="53" ht="15.75" hidden="1" spans="1:7">
       <c r="A53" s="23">
         <v>53</v>
       </c>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G53" s="26"/>
     </row>
-    <row r="54" ht="15.75" spans="1:7">
+    <row r="54" ht="15.75" hidden="1" spans="1:7">
       <c r="A54" s="23">
         <v>54</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="55" ht="15.75" spans="1:7">
+    <row r="55" ht="15.75" hidden="1" spans="1:7">
       <c r="A55" s="23">
         <v>55</v>
       </c>
@@ -3882,7 +3882,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="56" ht="15.75" spans="1:7">
+    <row r="56" ht="15.75" hidden="1" spans="1:7">
       <c r="A56" s="23">
         <v>57</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="57" ht="15.75" spans="1:7">
+    <row r="57" ht="15.75" hidden="1" spans="1:7">
       <c r="A57" s="23">
         <v>58</v>
       </c>
@@ -3928,7 +3928,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="58" ht="15.75" spans="1:7">
+    <row r="58" ht="15.75" hidden="1" spans="1:7">
       <c r="A58" s="23">
         <v>59</v>
       </c>
@@ -3951,7 +3951,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="59" ht="15.75" spans="1:7">
+    <row r="59" ht="15.75" hidden="1" spans="1:7">
       <c r="A59" s="23">
         <v>60</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="60" ht="15.75" spans="1:7">
+    <row r="60" ht="15.75" hidden="1" spans="1:7">
       <c r="A60" s="23">
         <v>61</v>
       </c>
@@ -3995,7 +3995,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="61" ht="15.75" spans="1:7">
+    <row r="61" ht="15.75" hidden="1" spans="1:7">
       <c r="A61" s="23">
         <v>62</v>
       </c>
@@ -4016,7 +4016,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="62" ht="15.75" spans="1:7">
+    <row r="62" ht="15.75" hidden="1" spans="1:7">
       <c r="A62" s="23">
         <v>64</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="63" ht="15.75" spans="1:7">
+    <row r="63" ht="15.75" hidden="1" spans="1:7">
       <c r="A63" s="23">
         <v>65</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="64" ht="15.75" spans="1:7">
+    <row r="64" ht="15.75" hidden="1" spans="1:7">
       <c r="A64" s="23">
         <v>66</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="65" ht="15.75" spans="1:7">
+    <row r="65" ht="15.75" hidden="1" spans="1:7">
       <c r="A65" s="23">
         <v>67</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="66" ht="15.75" spans="1:7">
+    <row r="66" ht="15.75" hidden="1" spans="1:7">
       <c r="A66" s="23">
         <v>68</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="67" ht="15.75" spans="1:7">
+    <row r="67" ht="15.75" hidden="1" spans="1:7">
       <c r="A67" s="23">
         <v>69</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="68" ht="15.75" spans="1:7">
+    <row r="68" ht="15.75" hidden="1" spans="1:7">
       <c r="A68" s="23">
         <v>70</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="69" ht="31.5" spans="1:7">
+    <row r="69" ht="31.5" hidden="1" spans="1:7">
       <c r="A69" s="23">
         <v>71</v>
       </c>
@@ -4188,7 +4188,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="70" ht="15.75" spans="1:7">
+    <row r="70" ht="15.75" hidden="1" spans="1:7">
       <c r="A70" s="23">
         <v>72</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="71" ht="15.75" spans="1:7">
+    <row r="71" ht="15.75" hidden="1" spans="1:7">
       <c r="A71" s="23">
         <v>73</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="72" ht="15.75" spans="1:7">
+    <row r="72" ht="15.75" hidden="1" spans="1:7">
       <c r="A72" s="23">
         <v>74</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="73" ht="15.75" spans="1:7">
+    <row r="73" ht="15.75" hidden="1" spans="1:7">
       <c r="A73" s="23">
         <v>75</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="74" ht="15.75" spans="1:7">
+    <row r="74" ht="15.75" hidden="1" spans="1:7">
       <c r="A74" s="23">
         <v>76</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="75" ht="15.75" spans="1:7">
+    <row r="75" ht="15.75" hidden="1" spans="1:7">
       <c r="A75" s="23">
         <v>77</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="76" ht="15.75" spans="1:7">
+    <row r="76" ht="15.75" hidden="1" spans="1:7">
       <c r="A76" s="23">
         <v>78</v>
       </c>
@@ -4339,7 +4339,7 @@
       </c>
       <c r="G76" s="26"/>
     </row>
-    <row r="77" ht="15.75" spans="1:7">
+    <row r="77" ht="15.75" hidden="1" spans="1:7">
       <c r="A77" s="23">
         <v>79</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="78" ht="15.75" spans="1:7">
+    <row r="78" ht="15.75" hidden="1" spans="1:7">
       <c r="A78" s="23">
         <v>80</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="79" ht="15.75" spans="1:7">
+    <row r="79" ht="15.75" hidden="1" spans="1:7">
       <c r="A79" s="23">
         <v>81</v>
       </c>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G79" s="26"/>
     </row>
-    <row r="80" ht="15.75" spans="1:7">
+    <row r="80" ht="15.75" hidden="1" spans="1:7">
       <c r="A80" s="23">
         <v>82</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" ht="15.75" spans="1:7">
+    <row r="81" ht="15.75" hidden="1" spans="1:7">
       <c r="A81" s="23">
         <v>83</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="82" ht="15.75" spans="1:7">
+    <row r="82" ht="15.75" hidden="1" spans="1:7">
       <c r="A82" s="23">
         <v>84</v>
       </c>
@@ -4469,7 +4469,7 @@
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" ht="15.75" spans="1:7">
+    <row r="83" ht="15.75" hidden="1" spans="1:7">
       <c r="A83" s="23">
         <v>85</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="84" ht="15.75" spans="1:7">
+    <row r="84" ht="15.75" hidden="1" spans="1:7">
       <c r="A84" s="23">
         <v>86</v>
       </c>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" ht="15.75" spans="1:7">
+    <row r="85" ht="15.75" hidden="1" spans="1:7">
       <c r="A85" s="23">
         <v>87</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="86" ht="15.75" spans="1:7">
+    <row r="86" ht="15.75" hidden="1" spans="1:7">
       <c r="A86" s="23">
         <v>88</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="87" ht="15.75" spans="1:7">
+    <row r="87" ht="15.75" hidden="1" spans="1:7">
       <c r="A87" s="23">
         <v>89</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="88" ht="15.75" spans="1:7">
+    <row r="88" ht="15.75" hidden="1" spans="1:7">
       <c r="A88" s="23">
         <v>90</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="89" ht="15.75" spans="1:7">
+    <row r="89" ht="15.75" hidden="1" spans="1:7">
       <c r="A89" s="23">
         <v>91</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="90" ht="15.75" spans="1:7">
+    <row r="90" ht="15.75" hidden="1" spans="1:7">
       <c r="A90" s="23">
         <v>92</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="91" ht="15.75" spans="1:7">
+    <row r="91" ht="15.75" hidden="1" spans="1:7">
       <c r="A91" s="23">
         <v>93</v>
       </c>
@@ -4662,7 +4662,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="92" ht="15.75" spans="1:7">
+    <row r="92" ht="15.75" hidden="1" spans="1:7">
       <c r="A92" s="23">
         <v>94</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="93" ht="15.75" spans="1:7">
+    <row r="93" ht="15.75" hidden="1" spans="1:7">
       <c r="A93" s="23">
         <v>95</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="94" ht="31.5" spans="1:7">
+    <row r="94" ht="31.5" hidden="1" spans="1:7">
       <c r="A94" s="23">
         <v>96</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="95" ht="15.75" spans="1:7">
+    <row r="95" ht="15.75" hidden="1" spans="1:7">
       <c r="A95" s="23">
         <v>97</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="96" ht="15.75" spans="1:7">
+    <row r="96" ht="15.75" hidden="1" spans="1:7">
       <c r="A96" s="23">
         <v>98</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="97" ht="15.75" spans="1:7">
+    <row r="97" ht="15.75" hidden="1" spans="1:7">
       <c r="A97" s="23">
         <v>99</v>
       </c>
@@ -4792,7 +4792,7 @@
       <c r="F97" s="33"/>
       <c r="G97" s="26"/>
     </row>
-    <row r="98" ht="15.75" spans="1:7">
+    <row r="98" ht="15.75" hidden="1" spans="1:7">
       <c r="A98" s="23">
         <v>100</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="99" ht="15.75" spans="1:7">
+    <row r="99" ht="15.75" hidden="1" spans="1:7">
       <c r="A99" s="23">
         <v>101</v>
       </c>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" ht="15.75" spans="1:7">
+    <row r="100" ht="15.75" hidden="1" spans="1:7">
       <c r="A100" s="23">
         <v>102</v>
       </c>
@@ -4853,7 +4853,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="101" ht="15.75" spans="1:7">
+    <row r="101" ht="15.75" hidden="1" spans="1:7">
       <c r="A101" s="23">
         <v>103</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="102" ht="15.75" spans="1:7">
+    <row r="102" ht="15.75" hidden="1" spans="1:7">
       <c r="A102" s="23">
         <v>104</v>
       </c>
@@ -4897,7 +4897,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="103" ht="15.75" spans="1:7">
+    <row r="103" ht="15.75" hidden="1" spans="1:7">
       <c r="A103" s="23">
         <v>105</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="104" ht="15.75" spans="1:7">
+    <row r="104" ht="15.75" hidden="1" spans="1:7">
       <c r="A104" s="23">
         <v>106</v>
       </c>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" ht="15.75" spans="1:7">
+    <row r="105" ht="15.75" hidden="1" spans="1:7">
       <c r="A105" s="23">
         <v>107</v>
       </c>
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G105" s="28"/>
     </row>
-    <row r="106" ht="15.75" spans="1:7">
+    <row r="106" ht="15.75" hidden="1" spans="1:7">
       <c r="A106" s="23">
         <v>108</v>
       </c>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G106" s="28"/>
     </row>
-    <row r="107" ht="15.75" spans="1:7">
+    <row r="107" ht="15.75" hidden="1" spans="1:7">
       <c r="A107" s="23">
         <v>109</v>
       </c>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="G107" s="28"/>
     </row>
-    <row r="108" ht="15.75" spans="1:7">
+    <row r="108" ht="15.75" hidden="1" spans="1:7">
       <c r="A108" s="23">
         <v>110</v>
       </c>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="G108" s="28"/>
     </row>
-    <row r="109" ht="31.5" spans="1:7">
+    <row r="109" ht="31.5" hidden="1" spans="1:7">
       <c r="A109" s="23">
         <v>111</v>
       </c>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G109" s="28"/>
     </row>
-    <row r="110" ht="15.75" spans="1:7">
+    <row r="110" ht="15.75" hidden="1" spans="1:7">
       <c r="A110" s="23">
         <v>112</v>
       </c>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="G110" s="28"/>
     </row>
-    <row r="111" ht="15.75" spans="1:7">
+    <row r="111" ht="15.75" hidden="1" spans="1:7">
       <c r="A111" s="23">
         <v>113</v>
       </c>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G111" s="28"/>
     </row>
-    <row r="112" s="15" customFormat="1" ht="15.75" spans="1:7">
+    <row r="112" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
       <c r="A112" s="23">
         <v>114</v>
       </c>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="G112" s="28"/>
     </row>
-    <row r="113" ht="15.75" spans="1:7">
+    <row r="113" ht="15.75" hidden="1" spans="1:7">
       <c r="A113" s="23">
         <v>115</v>
       </c>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G113" s="28"/>
     </row>
-    <row r="114" ht="15.75" spans="1:7">
+    <row r="114" ht="15.75" hidden="1" spans="1:7">
       <c r="A114" s="23">
         <v>116</v>
       </c>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="G114" s="28"/>
     </row>
-    <row r="115" ht="15.75" spans="1:7">
+    <row r="115" ht="15.75" hidden="1" spans="1:7">
       <c r="A115" s="23">
         <v>117</v>
       </c>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="G115" s="28"/>
     </row>
-    <row r="116" ht="15.75" spans="1:7">
+    <row r="116" ht="15.75" hidden="1" spans="1:7">
       <c r="A116" s="23">
         <v>118</v>
       </c>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="G116" s="28"/>
     </row>
-    <row r="117" ht="15.75" spans="1:7">
+    <row r="117" ht="15.75" hidden="1" spans="1:7">
       <c r="A117" s="23">
         <v>119</v>
       </c>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G117" s="28"/>
     </row>
-    <row r="118" ht="15.75" spans="1:7">
+    <row r="118" ht="15.75" hidden="1" spans="1:7">
       <c r="A118" s="23">
         <v>120</v>
       </c>
@@ -5207,7 +5207,7 @@
       </c>
       <c r="G118" s="28"/>
     </row>
-    <row r="119" ht="15.75" spans="1:7">
+    <row r="119" ht="15.75" hidden="1" spans="1:7">
       <c r="A119" s="23">
         <v>121</v>
       </c>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="G119" s="28"/>
     </row>
-    <row r="120" ht="15.75" spans="1:7">
+    <row r="120" ht="15.75" hidden="1" spans="1:7">
       <c r="A120" s="23">
         <v>122</v>
       </c>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="G120" s="47"/>
     </row>
-    <row r="121" ht="15.75" spans="1:7">
+    <row r="121" ht="15.75" hidden="1" spans="1:7">
       <c r="A121" s="23">
         <v>123</v>
       </c>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="G121" s="28"/>
     </row>
-    <row r="122" ht="15.75" spans="1:7">
+    <row r="122" ht="15.75" hidden="1" spans="1:7">
       <c r="A122" s="23">
         <v>124</v>
       </c>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="G122" s="28"/>
     </row>
-    <row r="123" ht="31.5" spans="1:7">
+    <row r="123" ht="31.5" hidden="1" spans="1:7">
       <c r="A123" s="23">
         <v>125</v>
       </c>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="G123" s="28"/>
     </row>
-    <row r="124" ht="15.75" spans="1:7">
+    <row r="124" ht="15.75" hidden="1" spans="1:7">
       <c r="A124" s="23">
         <v>126</v>
       </c>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="G124" s="28"/>
     </row>
-    <row r="125" ht="15.75" spans="1:7">
+    <row r="125" ht="15.75" hidden="1" spans="1:7">
       <c r="A125" s="23">
         <v>127</v>
       </c>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="G126" s="28"/>
     </row>
-    <row r="127" ht="15.75" spans="1:7">
+    <row r="127" ht="15.75" hidden="1" spans="1:7">
       <c r="A127" s="23">
         <v>129</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="128" ht="15.75" spans="1:7">
+    <row r="128" ht="15.75" hidden="1" spans="1:7">
       <c r="A128" s="23">
         <v>130</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="129" ht="15.75" spans="1:7">
+    <row r="129" ht="15.75" hidden="1" spans="1:7">
       <c r="A129" s="23">
         <v>131</v>
       </c>
@@ -5436,7 +5436,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="130" ht="15.75" spans="1:7">
+    <row r="130" ht="15.75" hidden="1" spans="1:7">
       <c r="A130" s="23">
         <v>132</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="131" ht="15.75" spans="1:7">
+    <row r="131" ht="15.75" hidden="1" spans="1:7">
       <c r="A131" s="23">
         <v>133</v>
       </c>
@@ -5482,7 +5482,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="132" ht="15.75" spans="1:7">
+    <row r="132" ht="15.75" hidden="1" spans="1:7">
       <c r="A132" s="23">
         <v>134</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="133" ht="15.75" spans="1:7">
+    <row r="133" ht="15.75" hidden="1" spans="1:7">
       <c r="A133" s="23">
         <v>135</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="134" ht="15.75" spans="1:7">
+    <row r="134" ht="15.75" hidden="1" spans="1:7">
       <c r="A134" s="23">
         <v>136</v>
       </c>
@@ -5548,7 +5548,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="135" ht="15.75" spans="1:7">
+    <row r="135" ht="15.75" hidden="1" spans="1:7">
       <c r="A135" s="23">
         <v>137</v>
       </c>
@@ -5571,7 +5571,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="136" ht="15.75" spans="1:7">
+    <row r="136" ht="15.75" hidden="1" spans="1:7">
       <c r="A136" s="23">
         <v>138</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="137" ht="15.75" spans="1:7">
+    <row r="137" ht="15.75" hidden="1" spans="1:7">
       <c r="A137" s="23">
         <v>139</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="138" ht="15.75" spans="1:7">
+    <row r="138" ht="15.75" hidden="1" spans="1:7">
       <c r="A138" s="23">
         <v>140</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="139" ht="15.75" spans="1:7">
+    <row r="139" ht="15.75" hidden="1" spans="1:7">
       <c r="A139" s="23">
         <v>141</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="140" ht="15.75" spans="1:7">
+    <row r="140" ht="15.75" hidden="1" spans="1:7">
       <c r="A140" s="23">
         <v>142</v>
       </c>
@@ -5675,7 +5675,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="141" ht="15.75" spans="1:7">
+    <row r="141" ht="15.75" hidden="1" spans="1:7">
       <c r="A141" s="23">
         <v>143</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="142" ht="15.75" spans="1:7">
+    <row r="142" ht="15.75" hidden="1" spans="1:7">
       <c r="A142" s="23">
         <v>144</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="143" ht="15.75" spans="1:7">
+    <row r="143" ht="15.75" hidden="1" spans="1:7">
       <c r="A143" s="23">
         <v>145</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="144" ht="19" customHeight="1" spans="1:7">
+    <row r="144" ht="19" hidden="1" customHeight="1" spans="1:7">
       <c r="A144" s="23">
         <v>145</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="145" ht="15.75" spans="1:7">
+    <row r="145" ht="15.75" hidden="1" spans="1:7">
       <c r="A145" s="23">
         <v>146</v>
       </c>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" ht="15.75" spans="1:7">
+    <row r="146" ht="15.75" hidden="1" spans="1:7">
       <c r="A146" s="23">
         <v>147</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="147" ht="15.75" spans="1:7">
+    <row r="147" ht="15.75" hidden="1" spans="1:7">
       <c r="A147" s="23">
         <v>148</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="148" ht="15.75" spans="1:7">
+    <row r="148" ht="15.75" hidden="1" spans="1:7">
       <c r="A148" s="23">
         <v>149</v>
       </c>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="G148" s="26"/>
     </row>
-    <row r="149" ht="15.75" spans="1:7">
+    <row r="149" ht="15.75" hidden="1" spans="1:7">
       <c r="A149" s="23">
         <v>150</v>
       </c>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="G149" s="53"/>
     </row>
-    <row r="150" ht="15.75" spans="1:7">
+    <row r="150" ht="15.75" hidden="1" spans="1:7">
       <c r="A150" s="32">
         <v>151</v>
       </c>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="G150" s="53"/>
     </row>
-    <row r="151" ht="15.75" spans="1:7">
+    <row r="151" ht="15.75" hidden="1" spans="1:7">
       <c r="A151" s="32">
         <v>152</v>
       </c>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G151" s="26"/>
     </row>
-    <row r="152" ht="15.75" spans="1:7">
+    <row r="152" ht="15.75" hidden="1" spans="1:7">
       <c r="A152" s="32">
         <v>153</v>
       </c>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="G152" s="26"/>
     </row>
-    <row r="153" ht="15.75" spans="1:7">
+    <row r="153" ht="15.75" hidden="1" spans="1:7">
       <c r="A153" s="32">
         <v>153</v>
       </c>
@@ -5950,7 +5950,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" ht="15.75" spans="1:7">
+    <row r="154" ht="15.75" hidden="1" spans="1:7">
       <c r="A154" s="32">
         <v>154</v>
       </c>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" ht="15.75" spans="1:7">
+    <row r="155" ht="15.75" hidden="1" spans="1:7">
       <c r="A155" s="32">
         <v>155</v>
       </c>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" ht="15.75" spans="1:7">
+    <row r="156" ht="15.75" hidden="1" spans="1:7">
       <c r="A156" s="32">
         <v>155</v>
       </c>
@@ -6013,7 +6013,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" ht="15.75" spans="1:7">
+    <row r="157" ht="15.75" hidden="1" spans="1:7">
       <c r="A157" s="32">
         <v>156</v>
       </c>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G157" s="26"/>
     </row>
-    <row r="158" ht="15.75" spans="1:7">
+    <row r="158" ht="15.75" hidden="1" spans="1:7">
       <c r="A158" s="32">
         <v>157</v>
       </c>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="G158" s="26"/>
     </row>
-    <row r="159" ht="15.75" spans="1:7">
+    <row r="159" ht="15.75" hidden="1" spans="1:7">
       <c r="A159" s="32">
         <v>158</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="160" ht="15.75" spans="1:7">
+    <row r="160" ht="15.75" hidden="1" spans="1:7">
       <c r="A160" s="32">
         <v>159</v>
       </c>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="G160" s="26"/>
     </row>
-    <row r="161" ht="15.75" spans="1:7">
+    <row r="161" ht="15.75" hidden="1" spans="1:7">
       <c r="A161" s="32">
         <v>160</v>
       </c>
@@ -6122,7 +6122,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="162" ht="15.75" spans="1:7">
+    <row r="162" ht="15.75" hidden="1" spans="1:7">
       <c r="A162" s="32">
         <v>161</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="163" ht="15.75" spans="1:7">
+    <row r="163" ht="15.75" hidden="1" spans="1:7">
       <c r="A163" s="32">
         <v>162</v>
       </c>
@@ -6166,7 +6166,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="164" ht="15.75" spans="1:7">
+    <row r="164" ht="15.75" hidden="1" spans="1:7">
       <c r="A164" s="32">
         <v>163</v>
       </c>
@@ -6189,7 +6189,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="165" s="16" customFormat="1" ht="15.75" spans="1:7">
+    <row r="165" s="16" customFormat="1" ht="15.75" hidden="1" spans="1:7">
       <c r="A165" s="32">
         <v>164</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="166" ht="15.75" spans="1:7">
+    <row r="166" ht="15.75" hidden="1" spans="1:7">
       <c r="A166" s="32">
         <v>165</v>
       </c>
@@ -9228,6 +9228,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G166" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="SAIDI KHEYREDDINE"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <hyperlinks>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="450">
   <si>
     <t>N°</t>
   </si>
@@ -1189,7 +1189,7 @@
     <t>LAID ABDELALI</t>
   </si>
   <si>
-    <t>aidabdelali@gmail.com</t>
+    <t>laidabdelali@gmail.com</t>
   </si>
   <si>
     <t>LAZERGUI SIHEM</t>
@@ -1262,6 +1262,12 @@
   </si>
   <si>
     <t>0556565254</t>
+  </si>
+  <si>
+    <t>BENSEMICHA MOHAMED</t>
+  </si>
+  <si>
+    <t>mhamedbensmicha00@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -5346,7 +5352,7 @@
       </c>
       <c r="G125" s="28"/>
     </row>
-    <row r="126" ht="15.75" spans="1:7">
+    <row r="126" ht="15.75" hidden="1" spans="1:7">
       <c r="A126" s="23">
         <v>128</v>
       </c>
@@ -6013,7 +6019,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" ht="15.75" hidden="1" spans="1:7">
+    <row r="157" ht="15.75" spans="1:7">
       <c r="A157" s="32">
         <v>156</v>
       </c>
@@ -6235,8 +6241,25 @@
         <v>409</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
-      <c r="D167" s="18"/>
+    <row r="167" ht="15.75" spans="1:7">
+      <c r="A167" s="32">
+        <v>156</v>
+      </c>
+      <c r="B167" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="C167" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E167" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F167" s="25" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="168" spans="1:7">
       <c r="D168" s="18"/>
@@ -9230,7 +9253,7 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G166" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
       <filters>
-        <filter val="SAIDI KHEYREDDINE"/>
+        <filter val="LAID ABDELALI"/>
       </filters>
     </filterColumn>
     <extLst/>
@@ -9292,7 +9315,7 @@
     <hyperlink ref="F151" r:id="rId53" display="walid.sebastien@gmail.com"/>
     <hyperlink ref="F152" r:id="rId54" display="bensenadanadia3@gmail.com"/>
     <hyperlink ref="F153" r:id="rId55" display="imedmedles@gmail.com"/>
-    <hyperlink ref="F157" r:id="rId56" display="aidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
+    <hyperlink ref="F157" r:id="rId56" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
     <hyperlink ref="F159" r:id="rId57" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
     <hyperlink ref="F160" r:id="rId58" display="rachid.hadjboulenouar@gamil.com"/>
     <hyperlink ref="F161" r:id="rId59" display="moh@medbnr.com"/>
@@ -9321,202 +9344,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>422</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$167</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="452">
   <si>
     <t>N°</t>
   </si>
@@ -55,15 +55,651 @@
     <t>N°/TEL</t>
   </si>
   <si>
+    <t>MOULAY MILOUD</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Vacataire</t>
+  </si>
+  <si>
+    <t>Doctorant (Magister)</t>
+  </si>
+  <si>
+    <t>mmiloud@yahoo.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 42 85 61 91 </t>
+  </si>
+  <si>
+    <t>ABBAS MOHAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctorant (Master) </t>
+  </si>
+  <si>
+    <t>abbasmohammed.com@gmail.com</t>
+  </si>
+  <si>
+    <t>0696562379</t>
+  </si>
+  <si>
+    <t>ELGHODASSE ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>elghodasseabdelmadjid@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 77 21 68</t>
+  </si>
+  <si>
+    <t>GHALEM ABDELHAK</t>
+  </si>
+  <si>
+    <t>ghalem.abdelhak@yahoo.com</t>
+  </si>
+  <si>
+    <t>0675437370</t>
+  </si>
+  <si>
+    <t>HAMMAR MEHDI</t>
+  </si>
+  <si>
+    <t>protoboy9999@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 33 46 70 </t>
+  </si>
+  <si>
+    <t>MEGUEDAD ABOUBAKR</t>
+  </si>
+  <si>
+    <t>megdz100@gmail.com</t>
+  </si>
+  <si>
+    <t>0799491736</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>Doctorante (Master)</t>
+  </si>
+  <si>
+    <t>khalidamet4@gmail.com</t>
+  </si>
+  <si>
+    <t>0550651046</t>
+  </si>
+  <si>
+    <t>MEKHFI KHALIDA</t>
+  </si>
+  <si>
+    <t>mekhfikhalida87@gmail.com</t>
+  </si>
+  <si>
+    <t>ARAB ABDELMADJID</t>
+  </si>
+  <si>
+    <t>Doctorat</t>
+  </si>
+  <si>
+    <t>arab4abdelmadjid@gmail.com</t>
+  </si>
+  <si>
+    <t>06 57 28 84 81</t>
+  </si>
+  <si>
+    <t>BENDIDA MOHAMED</t>
+  </si>
+  <si>
+    <t>bendida65@gmail.com</t>
+  </si>
+  <si>
+    <t>05 50 59 52 24</t>
+  </si>
+  <si>
+    <t>BENSALEM Mohammed Mustapha</t>
+  </si>
+  <si>
+    <t>bensalem.moh.mus@gmail.com</t>
+  </si>
+  <si>
+    <t>0550114832</t>
+  </si>
+  <si>
+    <t>BOUKHARI SOUMIA</t>
+  </si>
+  <si>
+    <t>boukharisoumiafarah@gmail.com</t>
+  </si>
+  <si>
+    <t>06 96 05 82 37</t>
+  </si>
+  <si>
+    <t>DJEZIRI SOUMIA</t>
+  </si>
+  <si>
+    <t>somiadjeziri22@gmail.com</t>
+  </si>
+  <si>
+    <t>0540920164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROUNI Wassila Abir </t>
+  </si>
+  <si>
+    <t>Wassila.drouni@gmail.com</t>
+  </si>
+  <si>
+    <t>05 51 24 38 19</t>
+  </si>
+  <si>
+    <t>HADER ABDERRAHMANE</t>
+  </si>
+  <si>
+    <t>aer.hader91@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 00 44 75</t>
+  </si>
+  <si>
+    <t>MERADJAH IBRAHIM</t>
+  </si>
+  <si>
+    <t>ibrahimmeradjah72@gmail.com</t>
+  </si>
+  <si>
+    <t>0663114536</t>
+  </si>
+  <si>
+    <t>MOKEDDEM AMINA</t>
+  </si>
+  <si>
+    <t>mokeddem.amina2222@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 56 42 87 15 </t>
+  </si>
+  <si>
+    <t>ZIANI DJAMEL</t>
+  </si>
+  <si>
+    <t>djamel71ziani@gmail.com</t>
+  </si>
+  <si>
+    <t>05 61 11 10 02</t>
+  </si>
+  <si>
+    <t>REGUIEG ZAKARIA</t>
+  </si>
+  <si>
+    <t>reguiegzakaria10@gmail.com</t>
+  </si>
+  <si>
+    <t>0792070651</t>
+  </si>
+  <si>
+    <t>BENMESSAOUD LEYLA</t>
+  </si>
+  <si>
+    <t>l_benmessaoud@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0553714385</t>
+  </si>
+  <si>
+    <t>TURKI BILAL MEROUANE</t>
+  </si>
+  <si>
+    <t>turkibilal22@gmail.com</t>
+  </si>
+  <si>
+    <t>0655206865</t>
+  </si>
+  <si>
+    <t>SABOUNDJI Asmaa Hadjer</t>
+  </si>
+  <si>
+    <t>saboundjiasmaa@gmail.com</t>
+  </si>
+  <si>
+    <t>0655459306 /  0556562385</t>
+  </si>
+  <si>
+    <t>HACENE IMENE</t>
+  </si>
+  <si>
+    <t>hacene_imene12@yahoo.com</t>
+  </si>
+  <si>
+    <t>0542471563</t>
+  </si>
+  <si>
+    <t>BENKATLANE Aissa</t>
+  </si>
+  <si>
+    <t>a.benkatlane@gmail.com</t>
+  </si>
+  <si>
+    <t>0697113466</t>
+  </si>
+  <si>
+    <t>ismahene.fezazi@gmail.com</t>
+  </si>
+  <si>
+    <t>0652652866</t>
+  </si>
+  <si>
+    <t>BELAIDI OUAFIA</t>
+  </si>
+  <si>
+    <t>belaidi.ouafia@outlook.fr</t>
+  </si>
+  <si>
+    <t>0668834015</t>
+  </si>
+  <si>
+    <t>BERREKHCHI BERRAHMA NEILA</t>
+  </si>
+  <si>
+    <t>neilabekhchiberrahma@gmail.com</t>
+  </si>
+  <si>
+    <t>0656 88 71 07</t>
+  </si>
+  <si>
+    <t>KADARI BELKACEM</t>
+  </si>
+  <si>
+    <t>belkacemKadari@gmail.com</t>
+  </si>
+  <si>
+    <t>0553282842</t>
+  </si>
+  <si>
+    <t>LAID ABDELALI</t>
+  </si>
+  <si>
+    <t>laidabdelali@gmail.com</t>
+  </si>
+  <si>
+    <t>HADJ BOULANOUAR RACHID</t>
+  </si>
+  <si>
+    <t>rachid.hadjboulenouar@gmail.com</t>
+  </si>
+  <si>
+    <t>BENSEMICHA MOHAMED</t>
+  </si>
+  <si>
+    <t>mhamedbensmicha00@gmail.com</t>
+  </si>
+  <si>
+    <t>MOUILAH  KHEIRA</t>
+  </si>
+  <si>
+    <t>Ingénieur</t>
+  </si>
+  <si>
+    <t>mouilahka4614@gmail.com</t>
+  </si>
+  <si>
+    <t>BENGRIT MALIKA</t>
+  </si>
+  <si>
+    <t>Permanente</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>malikabengrit@gmail.com</t>
+  </si>
+  <si>
+    <t>BENKHALLOUK KADDOUR</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>benkh_ka@yahoo.fr</t>
+  </si>
+  <si>
+    <t>GHAZEL FATIHA</t>
+  </si>
+  <si>
+    <t>nour73_fac@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SAHALI YAMINA</t>
+  </si>
+  <si>
+    <t>ya_sahali@yahoo.fr</t>
+  </si>
+  <si>
+    <t>AREZKI MOUFOK</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>Mouffok.arezki22@gmail.com </t>
+  </si>
+  <si>
+    <t>06 97 05 81 64</t>
+  </si>
+  <si>
+    <t>BENCELLA SARRA</t>
+  </si>
+  <si>
+    <t>sarrabencella@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 94 25 37 34 </t>
+  </si>
+  <si>
+    <t>BENHARAT ABDELHADI</t>
+  </si>
+  <si>
+    <t>Hadi.bnh00@gmail.com</t>
+  </si>
+  <si>
+    <t>KHELLAF KADDA</t>
+  </si>
+  <si>
+    <t>khellafkadda1234@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 65 72 17 23 </t>
+  </si>
+  <si>
+    <t>MAHKOUKA ZAZA</t>
+  </si>
+  <si>
+    <t>mahkouka.zaza@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0778 36 07 76 </t>
+  </si>
+  <si>
+    <t>MIR KHELIFA</t>
+  </si>
+  <si>
+    <t>khelifa-mir@outlook.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 59 78 39 </t>
+  </si>
+  <si>
+    <t>BERROUNA HENEN</t>
+  </si>
+  <si>
+    <t>berhenen@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0671745806</t>
+  </si>
+  <si>
+    <t>DELLOUM AMIRA</t>
+  </si>
+  <si>
+    <t>amiradelloum28@gmail.com</t>
+  </si>
+  <si>
+    <t>FILALI INES</t>
+  </si>
+  <si>
+    <t>nesfilali2003@gmail.com</t>
+  </si>
+  <si>
+    <t>MOKEDDES AMINA</t>
+  </si>
+  <si>
+    <t>Mokaddesamina@gmail.com</t>
+  </si>
+  <si>
+    <t>KHIAT WALID</t>
+  </si>
+  <si>
+    <t>walid.sebastien@gmail.com</t>
+  </si>
+  <si>
+    <t>BENSNADA NADIA</t>
+  </si>
+  <si>
+    <t>bensenadanadia3@gmail.com</t>
+  </si>
+  <si>
+    <t>MEDLES IMED</t>
+  </si>
+  <si>
+    <t>imedmedles@gmail.com</t>
+  </si>
+  <si>
+    <t>LAZERGUI SIHEM</t>
+  </si>
+  <si>
+    <t>sihemlazergui@gmail.com</t>
+  </si>
+  <si>
+    <t>ATTAR IMAD</t>
+  </si>
+  <si>
+    <t>attarimad3@gmail.com</t>
+  </si>
+  <si>
+    <t>0656697602</t>
+  </si>
+  <si>
+    <t>BENOUAR MOHAMED</t>
+  </si>
+  <si>
+    <t>moh@medbnr.com</t>
+  </si>
+  <si>
+    <t>0774814578</t>
+  </si>
+  <si>
+    <t>MELIANI ABDELHAK</t>
+  </si>
+  <si>
+    <t>0541306332</t>
+  </si>
+  <si>
+    <t>YAMOUNE FATIMA ZOHRA HADIL</t>
+  </si>
+  <si>
+    <t>hadilyamoune@gmail.com</t>
+  </si>
+  <si>
+    <t>0697176260</t>
+  </si>
+  <si>
+    <t>DIDAOUI KAWTHAR</t>
+  </si>
+  <si>
+    <t>didaouikawthar331@gmail.com</t>
+  </si>
+  <si>
+    <t>0699099272</t>
+  </si>
+  <si>
+    <t>IKKACHE NARIMEN</t>
+  </si>
+  <si>
+    <t>ikkachenarimen.2017@gmail.com</t>
+  </si>
+  <si>
+    <t>BECHEKIR SEYFEDDINE</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>seyfeddine.electrotechnique@gmail.com</t>
+  </si>
+  <si>
+    <t>BEDDAD BOUCIF</t>
+  </si>
+  <si>
+    <t>beddadboucif@gmail.com</t>
+  </si>
+  <si>
+    <t>0665458282</t>
+  </si>
+  <si>
+    <t>BENBELLIL NADJAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nn.nn.phy.chi@gmail.com </t>
+  </si>
+  <si>
+    <t>BENDIMERAD SALAH EDDINE</t>
+  </si>
+  <si>
+    <t>s_bendimerad@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BERMAKI HAMZA</t>
+  </si>
+  <si>
+    <t>bermaki.hamza@gmail.com</t>
+  </si>
+  <si>
+    <t>DRIEF FAIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drieff4@gmail.com </t>
+  </si>
+  <si>
+    <t>HANAFI SALAH</t>
+  </si>
+  <si>
+    <t>udl.fge.vdpg@gmail.com</t>
+  </si>
+  <si>
+    <t>HASSANI NAIMA</t>
+  </si>
+  <si>
+    <t>naimahassani69@yahoo.fr</t>
+  </si>
+  <si>
+    <t>JBILOU MOKHTARIA</t>
+  </si>
+  <si>
+    <t>harmel71@yahoo.fr</t>
+  </si>
+  <si>
+    <t>LALEDJ NADJET</t>
+  </si>
+  <si>
+    <t>nadjet_69@hotmail.fr</t>
+  </si>
+  <si>
+    <t>MAAMMAR MOHAMED</t>
+  </si>
+  <si>
+    <t>mohamed.maammar@gmail.com</t>
+  </si>
+  <si>
+    <t>MIMOUNI CHAHINEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mimounichahinez@gmail.com </t>
+  </si>
+  <si>
+    <t>0558193860</t>
+  </si>
+  <si>
+    <t>BRAHAMI MOHAMED NADJIB</t>
+  </si>
+  <si>
+    <t>nadjbrahami@gmail.com</t>
+  </si>
+  <si>
+    <t>ZENASNI MERIEM</t>
+  </si>
+  <si>
+    <t>zenasnimeriem29@gmail.com</t>
+  </si>
+  <si>
+    <t>0552037098</t>
+  </si>
+  <si>
+    <t>REGUIG ABDELDJALIL</t>
+  </si>
+  <si>
+    <t>Mise en disponibilité</t>
+  </si>
+  <si>
+    <t>abdeldjalil.reguig@outlook.com</t>
+  </si>
+  <si>
+    <t>KADA KLOUCHA OMAR</t>
+  </si>
+  <si>
+    <t>klomar05@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SAIDI KHAYREDDINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
+  </si>
+  <si>
+    <t>SEMMAK ABDELKADER</t>
+  </si>
+  <si>
+    <t>semmak.abdelkader@outlook.com</t>
+  </si>
+  <si>
+    <t>0772111809</t>
+  </si>
+  <si>
+    <t>OUARI KHEIRA</t>
+  </si>
+  <si>
+    <t>ouari_k@yahoo.fr</t>
+  </si>
+  <si>
+    <t>ZATLA HICHAM</t>
+  </si>
+  <si>
+    <t>hicham.zatla@gmail.com</t>
+  </si>
+  <si>
+    <t>FEZAZI OMAR</t>
+  </si>
+  <si>
+    <t>fezaziomarfz@gmail.com</t>
+  </si>
+  <si>
+    <t>YAHI HICHEM</t>
+  </si>
+  <si>
+    <t>hichem-y33@hotmail.com</t>
+  </si>
+  <si>
+    <t>0556565254</t>
+  </si>
+  <si>
+    <t>BADIS KARIMA</t>
+  </si>
+  <si>
+    <t>MCB</t>
+  </si>
+  <si>
+    <t>karis483@hotmail.fr</t>
+  </si>
+  <si>
+    <t>0560337902</t>
+  </si>
+  <si>
     <t>ABID MOHAMED</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
     <t>Pr</t>
   </si>
   <si>
@@ -94,21 +730,6 @@
     <t>ahazaiz2011@yahoo.fr</t>
   </si>
   <si>
-    <t>BADIS KARIMA</t>
-  </si>
-  <si>
-    <t>Permanente</t>
-  </si>
-  <si>
-    <t>MCB</t>
-  </si>
-  <si>
-    <t>karis483@hotmail.fr</t>
-  </si>
-  <si>
-    <t>0560337902</t>
-  </si>
-  <si>
     <t>BAHLIL MOUNIR</t>
   </si>
   <si>
@@ -118,24 +739,6 @@
     <t>0672447184</t>
   </si>
   <si>
-    <t>BECHEKIR SEYFEDDINE</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
-    <t>seyfeddine.electrotechnique@gmail.com</t>
-  </si>
-  <si>
-    <t>BEDDAD BOUCIF</t>
-  </si>
-  <si>
-    <t>beddadboucif@gmail.com</t>
-  </si>
-  <si>
-    <t>0665458282</t>
-  </si>
-  <si>
     <t>BELLEBNA YASSINE</t>
   </si>
   <si>
@@ -154,57 +757,24 @@
     <t>dept.eln@gmail.com</t>
   </si>
   <si>
-    <t>BENBELLIL NADJAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nn.nn.phy.chi@gmail.com </t>
-  </si>
-  <si>
     <t>BENDAOUD ABDELBER</t>
   </si>
   <si>
     <t>babdelber22@yahoo.fr</t>
   </si>
   <si>
-    <t>BENDIMERAD SALAH EDDINE</t>
-  </si>
-  <si>
-    <t>s_bendimerad@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BENGRIT MALIKA</t>
-  </si>
-  <si>
-    <t>MAA</t>
-  </si>
-  <si>
-    <t>malikabengrit@gmail.com</t>
-  </si>
-  <si>
     <t>BENHAMIDA FARID</t>
   </si>
   <si>
     <t>farid.benhamida@yahoo.fr</t>
   </si>
   <si>
-    <t>BENKHALLOUK KADDOUR</t>
-  </si>
-  <si>
-    <t>benkh_ka@yahoo.fr</t>
-  </si>
-  <si>
     <t>BENTAALLAH ABDERRAHIM</t>
   </si>
   <si>
     <t>bentaallah65@yahoo.fr</t>
   </si>
   <si>
-    <t>BERMAKI HAMZA</t>
-  </si>
-  <si>
-    <t>bermaki.hamza@gmail.com</t>
-  </si>
-  <si>
     <t>BOUKHOULDA FODIL</t>
   </si>
   <si>
@@ -223,66 +793,24 @@
     <t>djeriri_youcef@yahoo.fr</t>
   </si>
   <si>
-    <t>DRIEF FAIZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drieff4@gmail.com </t>
-  </si>
-  <si>
     <t>FELLAH MOHAMMED KARIM</t>
   </si>
   <si>
     <t>mkfellah@gmail.com</t>
   </si>
   <si>
-    <t>GHAZEL FATIHA</t>
-  </si>
-  <si>
-    <t>nour73_fac@yahoo.fr</t>
-  </si>
-  <si>
     <t>HADJERI SAMIR</t>
   </si>
   <si>
     <t>shadjeri2@yahoo.fr</t>
   </si>
   <si>
-    <t>HANAFI SALAH</t>
-  </si>
-  <si>
-    <t>udl.fge.vdpg@gmail.com</t>
-  </si>
-  <si>
-    <t>HASSANI NAIMA</t>
-  </si>
-  <si>
-    <t>naimahassani69@yahoo.fr</t>
-  </si>
-  <si>
-    <t>JBILOU MOKHTARIA</t>
-  </si>
-  <si>
-    <t>harmel71@yahoo.fr</t>
-  </si>
-  <si>
     <t>KHATIR MOHAMED</t>
   </si>
   <si>
     <t>khatir.mohamed1977@gmail.com</t>
   </si>
   <si>
-    <t>LALEDJ NADJET</t>
-  </si>
-  <si>
-    <t>nadjet_69@hotmail.fr</t>
-  </si>
-  <si>
-    <t>MAAMMAR MOHAMED</t>
-  </si>
-  <si>
-    <t>mohamed.maammar@gmail.com</t>
-  </si>
-  <si>
     <t>MASSOUM AHMED</t>
   </si>
   <si>
@@ -304,21 +832,6 @@
     <t>el.houcine@yahoo.fr</t>
   </si>
   <si>
-    <t>MIMOUNI CHAHINEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mimounichahinez@gmail.com </t>
-  </si>
-  <si>
-    <t>0558193860</t>
-  </si>
-  <si>
-    <t>BRAHAMI MOHAMED NADJIB</t>
-  </si>
-  <si>
-    <t>nadjbrahami@gmail.com</t>
-  </si>
-  <si>
     <t>NACERI ABDELLATIF</t>
   </si>
   <si>
@@ -355,12 +868,6 @@
     <t>rezoug.med@gmail.com</t>
   </si>
   <si>
-    <t>SAHALI YAMINA</t>
-  </si>
-  <si>
-    <t>ya_sahali@yahoo.fr</t>
-  </si>
-  <si>
     <t>SEMMAH ABDELHAFID</t>
   </si>
   <si>
@@ -391,34 +898,58 @@
     <t>azeblah@yahoo.fr</t>
   </si>
   <si>
-    <t>ZENASNI MERIEM</t>
-  </si>
-  <si>
-    <t>zenasnimeriem29@gmail.com</t>
-  </si>
-  <si>
-    <t>0552037098</t>
-  </si>
-  <si>
     <t>ZIDI SID AHMED</t>
   </si>
   <si>
     <t>sbzidi@yahoo.fr</t>
   </si>
   <si>
-    <t>ABBAS MOHAMED</t>
-  </si>
-  <si>
-    <t>Vacataire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctorant (Master) </t>
-  </si>
-  <si>
-    <t>abbasmohammed.com@gmail.com</t>
-  </si>
-  <si>
-    <t>0696562379</t>
+    <t>RAIS ABDELMAJID</t>
+  </si>
+  <si>
+    <t>amrais@yahoo.com</t>
+  </si>
+  <si>
+    <t>ABBOU MAJDA</t>
+  </si>
+  <si>
+    <t>milouaf@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0556831346</t>
+  </si>
+  <si>
+    <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>n_benseddik@yahoo.fr</t>
+  </si>
+  <si>
+    <t>YAMANI MASSIM</t>
+  </si>
+  <si>
+    <t>yamanimassim@yahoo.fr</t>
+  </si>
+  <si>
+    <t>DOUIAICI MOHAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mdouiaici@hotmail.com </t>
+  </si>
+  <si>
+    <t>ANANI MACHO</t>
+  </si>
+  <si>
+    <t>anani66@yahoo.fr</t>
+  </si>
+  <si>
+    <t>ABID HAMZA</t>
+  </si>
+  <si>
+    <t>PrE</t>
+  </si>
+  <si>
+    <t>abid_hamza@yahoo.fr</t>
   </si>
   <si>
     <t>ABDELI MAMA</t>
@@ -430,48 +961,6 @@
     <t xml:space="preserve">05 52 96 89 21 </t>
   </si>
   <si>
-    <t>ARAB ABDELMADJID</t>
-  </si>
-  <si>
-    <t>Doctorat</t>
-  </si>
-  <si>
-    <t>arab4abdelmadjid@gmail.com</t>
-  </si>
-  <si>
-    <t>06 57 28 84 81</t>
-  </si>
-  <si>
-    <t>AREZKI MOUFOK</t>
-  </si>
-  <si>
-    <t>Master</t>
-  </si>
-  <si>
-    <t>Mouffok.arezki22@gmail.com </t>
-  </si>
-  <si>
-    <t>06 97 05 81 64</t>
-  </si>
-  <si>
-    <t>BENCELLA SARRA</t>
-  </si>
-  <si>
-    <t>sarrabencella@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 94 25 37 34 </t>
-  </si>
-  <si>
-    <t>BENDIDA MOHAMED</t>
-  </si>
-  <si>
-    <t>bendida65@gmail.com</t>
-  </si>
-  <si>
-    <t>05 50 59 52 24</t>
-  </si>
-  <si>
     <t>BELHABRI RIHAB</t>
   </si>
   <si>
@@ -490,15 +979,6 @@
     <t>06 96 0582 37</t>
   </si>
   <si>
-    <t>BENSALEM Mohammed Mustapha</t>
-  </si>
-  <si>
-    <t>bensalem.moh.mus@gmail.com</t>
-  </si>
-  <si>
-    <t>0550114832</t>
-  </si>
-  <si>
     <t>BETTACHE ABDERRAHMANE</t>
   </si>
   <si>
@@ -526,15 +1006,6 @@
     <t>0656855101</t>
   </si>
   <si>
-    <t>BOUKHARI SOUMIA</t>
-  </si>
-  <si>
-    <t>boukharisoumiafarah@gmail.com</t>
-  </si>
-  <si>
-    <t>06 96 05 82 37</t>
-  </si>
-  <si>
     <t>BOULARAF AICHA</t>
   </si>
   <si>
@@ -571,15 +1042,6 @@
     <t>0673948096</t>
   </si>
   <si>
-    <t>DJEZIRI SOUMIA</t>
-  </si>
-  <si>
-    <t>somiadjeziri22@gmail.com</t>
-  </si>
-  <si>
-    <t>0540920164</t>
-  </si>
-  <si>
     <t>DRICI LAMIA</t>
   </si>
   <si>
@@ -589,15 +1051,6 @@
     <t xml:space="preserve">06 97 35 08 88 </t>
   </si>
   <si>
-    <t xml:space="preserve">DROUNI Wassila Abir </t>
-  </si>
-  <si>
-    <t>Wassila.drouni@gmail.com</t>
-  </si>
-  <si>
-    <t>05 51 24 38 19</t>
-  </si>
-  <si>
     <t>El MESTARI WAHIBA</t>
   </si>
   <si>
@@ -607,45 +1060,12 @@
     <t>0556130770</t>
   </si>
   <si>
-    <t>ELGHODASSE ABDEL MADJID</t>
-  </si>
-  <si>
-    <t>elghodasseabdelmadjid@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 77 21 68</t>
-  </si>
-  <si>
     <t>MILOUA FETHI</t>
   </si>
   <si>
     <t>fethi22miloua@gmail.com</t>
   </si>
   <si>
-    <t>GHALEM ABDELHAK</t>
-  </si>
-  <si>
-    <t>ghalem.abdelhak@yahoo.com</t>
-  </si>
-  <si>
-    <t>0675437370</t>
-  </si>
-  <si>
-    <t>HADER ABDERRAHMANE</t>
-  </si>
-  <si>
-    <t>aer.hader91@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 00 44 75</t>
-  </si>
-  <si>
-    <t>BENHARAT ABDELHADI</t>
-  </si>
-  <si>
-    <t>Hadi.bnh00@gmail.com</t>
-  </si>
-  <si>
     <t>HADJI AHMED</t>
   </si>
   <si>
@@ -655,30 +1075,12 @@
     <t xml:space="preserve">06 98 14 23 47 </t>
   </si>
   <si>
-    <t>HAMMAR MEHDI</t>
-  </si>
-  <si>
-    <t>protoboy9999@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 33 46 70 </t>
-  </si>
-  <si>
     <t>HARMEL MOHAMED</t>
   </si>
   <si>
     <t xml:space="preserve">Harmel.mohamed22@hotmail.com </t>
   </si>
   <si>
-    <t>KHELLAF KADDA</t>
-  </si>
-  <si>
-    <t>khellafkadda1234@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 65 72 17 23 </t>
-  </si>
-  <si>
     <t>LAHCEN AZDDINE</t>
   </si>
   <si>
@@ -712,15 +1114,6 @@
     <t>0657058282</t>
   </si>
   <si>
-    <t>MAHKOUKA ZAZA</t>
-  </si>
-  <si>
-    <t>mahkouka.zaza@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0778 36 07 76 </t>
-  </si>
-  <si>
     <t>MANSOURI ABDERRAZAK</t>
   </si>
   <si>
@@ -730,18 +1123,6 @@
     <t>0696417435</t>
   </si>
   <si>
-    <t>MECHETTEM KHALIDA</t>
-  </si>
-  <si>
-    <t>Doctorante (Master)</t>
-  </si>
-  <si>
-    <t>khalidamet4@gmail.com</t>
-  </si>
-  <si>
-    <t>0550651046</t>
-  </si>
-  <si>
     <t>MEKHALEF SOUMIA</t>
   </si>
   <si>
@@ -751,15 +1132,6 @@
     <t xml:space="preserve">05 59 03 18 24 </t>
   </si>
   <si>
-    <t>MERADJAH IBRAHIM</t>
-  </si>
-  <si>
-    <t>ibrahimmeradjah72@gmail.com</t>
-  </si>
-  <si>
-    <t>0663114536</t>
-  </si>
-  <si>
     <t>MESLEM MEHADJIA</t>
   </si>
   <si>
@@ -769,36 +1141,6 @@
     <t xml:space="preserve">06 97 01 34 39 </t>
   </si>
   <si>
-    <t>MOULAY MILOUD</t>
-  </si>
-  <si>
-    <t>Doctorant (Magister)</t>
-  </si>
-  <si>
-    <t>mmiloud@yahoo.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 42 85 61 91 </t>
-  </si>
-  <si>
-    <t>MIR KHELIFA</t>
-  </si>
-  <si>
-    <t>khelifa-mir@outlook.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 59 78 39 </t>
-  </si>
-  <si>
-    <t>MOKEDDEM AMINA</t>
-  </si>
-  <si>
-    <t>mokeddem.amina2222@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 56 42 87 15 </t>
-  </si>
-  <si>
     <t xml:space="preserve">Non Défini </t>
   </si>
   <si>
@@ -826,15 +1168,6 @@
     <t xml:space="preserve">0674 68 05 35 </t>
   </si>
   <si>
-    <t>ZIANI DJAMEL</t>
-  </si>
-  <si>
-    <t>djamel71ziani@gmail.com</t>
-  </si>
-  <si>
-    <t>05 61 11 10 02</t>
-  </si>
-  <si>
     <t>LARBI ZIDI</t>
   </si>
   <si>
@@ -844,24 +1177,6 @@
     <t>07 92 12 03 38</t>
   </si>
   <si>
-    <t>BERROUNA HENEN</t>
-  </si>
-  <si>
-    <t>berhenen@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0671745806</t>
-  </si>
-  <si>
-    <t>MOUILAH  KHEIRA</t>
-  </si>
-  <si>
-    <t>Ingénieur</t>
-  </si>
-  <si>
-    <t>mouilahka4614@gmail.com</t>
-  </si>
-  <si>
     <t>ABED ZOULIKHA</t>
   </si>
   <si>
@@ -907,12 +1222,6 @@
     <t>chikhi_nawel75@yahoo.fr</t>
   </si>
   <si>
-    <t>DELLOUM AMIRA</t>
-  </si>
-  <si>
-    <t>amiradelloum28@gmail.com</t>
-  </si>
-  <si>
     <t>FENTAZY BELKISSE</t>
   </si>
   <si>
@@ -952,322 +1261,19 @@
     <t>sacihamza40@gmail.com</t>
   </si>
   <si>
-    <t>TURKI BILAL MEROUANE</t>
-  </si>
-  <si>
-    <t>turkibilal22@gmail.com</t>
-  </si>
-  <si>
-    <t>RAIS ABDELMAJID</t>
-  </si>
-  <si>
-    <t>amrais@yahoo.com</t>
-  </si>
-  <si>
-    <t>REGUIG ABDELDJALIL</t>
-  </si>
-  <si>
-    <t>Mise en disponibilité</t>
-  </si>
-  <si>
-    <t>abdeldjalil.reguig@outlook.com</t>
-  </si>
-  <si>
     <t>ZERDANI MOHAMMED</t>
   </si>
   <si>
     <t>medzerdani@gmail.com</t>
   </si>
   <si>
-    <t>KADA KLOUCHA OMAR</t>
-  </si>
-  <si>
-    <t>klomar05@yahoo.fr</t>
-  </si>
-  <si>
-    <t>SAIDI KHAYREDDINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
-  </si>
-  <si>
-    <t>ABBOU MAJDA</t>
-  </si>
-  <si>
-    <t>milouaf@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0556831346</t>
-  </si>
-  <si>
-    <t>REGUIEG ZAKARIA</t>
-  </si>
-  <si>
-    <t>reguiegzakaria10@gmail.com</t>
-  </si>
-  <si>
-    <t>0792070651</t>
-  </si>
-  <si>
-    <t>SEMMAK ABDELKADER</t>
-  </si>
-  <si>
-    <t>semmak.abdelkader@outlook.com</t>
-  </si>
-  <si>
-    <t>0772111809</t>
-  </si>
-  <si>
-    <t>BENMESSAOUD LEYLA</t>
-  </si>
-  <si>
-    <t>l_benmessaoud@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0553714385</t>
-  </si>
-  <si>
-    <t>0655206865</t>
-  </si>
-  <si>
-    <t>OUARI KHEIRA</t>
-  </si>
-  <si>
-    <t>ouari_k@yahoo.fr</t>
-  </si>
-  <si>
-    <t>SABOUNDJI Asmaa Hadjer</t>
-  </si>
-  <si>
-    <t>saboundjiasmaa@gmail.com</t>
-  </si>
-  <si>
-    <t>0655459306 /  0556562385</t>
-  </si>
-  <si>
-    <t>HACENE IMENE</t>
-  </si>
-  <si>
-    <t>hacene_imene12@yahoo.com</t>
-  </si>
-  <si>
-    <t>0542471563</t>
-  </si>
-  <si>
-    <t>BENKATLANE Aissa</t>
-  </si>
-  <si>
-    <t>a.benkatlane@gmail.com</t>
-  </si>
-  <si>
-    <t>0697113466</t>
-  </si>
-  <si>
-    <t>ismahene.fezazi@gmail.com</t>
-  </si>
-  <si>
-    <t>0652652866</t>
-  </si>
-  <si>
-    <t>ABID HAMZA</t>
-  </si>
-  <si>
-    <t>PrE</t>
-  </si>
-  <si>
-    <t>abid_hamza@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BELAIDI OUAFIA</t>
-  </si>
-  <si>
-    <t>belaidi.ouafia@outlook.fr</t>
-  </si>
-  <si>
-    <t>0668834015</t>
-  </si>
-  <si>
-    <t>MEKHFI KHALIDA</t>
-  </si>
-  <si>
-    <t>mekhfikhalida87@gmail.com</t>
-  </si>
-  <si>
-    <t>ZATLA HICHAM</t>
-  </si>
-  <si>
-    <t>hicham.zatla@gmail.com</t>
-  </si>
-  <si>
-    <t>BENSEDDIK NADIA</t>
-  </si>
-  <si>
-    <t>n_benseddik@yahoo.fr</t>
-  </si>
-  <si>
-    <t>YAMANI MASSIM</t>
-  </si>
-  <si>
-    <t>yamanimassim@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BERREKHCHI BERRAHMA NEILA</t>
-  </si>
-  <si>
-    <t>neilabekhchiberrahma@gmail.com</t>
-  </si>
-  <si>
-    <t>0656 88 71 07</t>
-  </si>
-  <si>
-    <t>FILALI INES</t>
-  </si>
-  <si>
-    <t>nesfilali2003@gmail.com</t>
-  </si>
-  <si>
     <t>0794297709</t>
   </si>
   <si>
-    <t>KADARI BELKACEM</t>
-  </si>
-  <si>
-    <t>belkacemKadari@gmail.com</t>
-  </si>
-  <si>
-    <t>0553282842</t>
-  </si>
-  <si>
-    <t>DOUIAICI MOHAMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mdouiaici@hotmail.com </t>
-  </si>
-  <si>
-    <t>MOKEDDES AMINA</t>
-  </si>
-  <si>
-    <t>Mokaddesamina@gmail.com</t>
-  </si>
-  <si>
     <t>TAIBI SOUMIA</t>
   </si>
   <si>
     <t>soumiaaiboudi27@gmail.com</t>
-  </si>
-  <si>
-    <t>KHIAT WALID</t>
-  </si>
-  <si>
-    <t>walid.sebastien@gmail.com</t>
-  </si>
-  <si>
-    <t>BENSNADA NADIA</t>
-  </si>
-  <si>
-    <t>bensenadanadia3@gmail.com</t>
-  </si>
-  <si>
-    <t>MEDLES IMED</t>
-  </si>
-  <si>
-    <t>imedmedles@gmail.com</t>
-  </si>
-  <si>
-    <t>ANANI MACHO</t>
-  </si>
-  <si>
-    <t>anani66@yahoo.fr</t>
-  </si>
-  <si>
-    <t>FEZAZI OMAR</t>
-  </si>
-  <si>
-    <t>fezaziomarfz@gmail.com</t>
-  </si>
-  <si>
-    <t>LAID ABDELALI</t>
-  </si>
-  <si>
-    <t>laidabdelali@gmail.com</t>
-  </si>
-  <si>
-    <t>LAZERGUI SIHEM</t>
-  </si>
-  <si>
-    <t>sihemlazergui@gmail.com</t>
-  </si>
-  <si>
-    <t>ATTAR IMAD</t>
-  </si>
-  <si>
-    <t>attarimad3@gmail.com</t>
-  </si>
-  <si>
-    <t>0656697602</t>
-  </si>
-  <si>
-    <t>HADJ BOULANOUAR RACHID</t>
-  </si>
-  <si>
-    <t>rachid.hadjboulenouar@gamil.com</t>
-  </si>
-  <si>
-    <t>BENOUAR MOHAMED</t>
-  </si>
-  <si>
-    <t>moh@medbnr.com</t>
-  </si>
-  <si>
-    <t>0774814578</t>
-  </si>
-  <si>
-    <t>MELIANI ABDELHAK</t>
-  </si>
-  <si>
-    <t>0541306332</t>
-  </si>
-  <si>
-    <t>YAMOUNE FATIMA ZOHRA HADIL</t>
-  </si>
-  <si>
-    <t>hadilyamoune@gmail.com</t>
-  </si>
-  <si>
-    <t>0697176260</t>
-  </si>
-  <si>
-    <t>MEGUEDAD ABOUBAKR</t>
-  </si>
-  <si>
-    <t>megdz100@gmail.com</t>
-  </si>
-  <si>
-    <t>0799491736</t>
-  </si>
-  <si>
-    <t>DIDAOUI KAWTHAR</t>
-  </si>
-  <si>
-    <t>didaouikaouthar331@gmail.com</t>
-  </si>
-  <si>
-    <t>0699099272</t>
-  </si>
-  <si>
-    <t>YAHI HICHEM</t>
-  </si>
-  <si>
-    <t>hichem-y33@hotmail.com</t>
-  </si>
-  <si>
-    <t>0556565254</t>
-  </si>
-  <si>
-    <t>BENSEMICHA MOHAMED</t>
-  </si>
-  <si>
-    <t>mhamedbensmicha00@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1394,7 +1400,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1446,16 +1452,16 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Cambria"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1470,6 +1476,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF1155CC"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color rgb="FF5E5E5E"/>
       <name val="Helvetica"/>
@@ -1480,13 +1505,6 @@
       <color rgb="FFFF0000"/>
       <name val="Cambria"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2060,135 +2078,135 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2256,37 +2274,84 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2298,54 +2363,42 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2353,9 +2406,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2704,7 +2760,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1" codeName="Sheet1"/>
-  <dimension ref="A1:G1163"/>
+  <dimension ref="A1:G1161"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="17" customWidth="1"/>
@@ -2740,9 +2796,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" spans="1:7">
+    <row r="2" ht="31.5" hidden="1" spans="1:7">
       <c r="A2" s="23">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>7</v>
@@ -2750,44 +2806,48 @@
       <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="25" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="26"/>
+      <c r="G2" s="27" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" ht="15.75" hidden="1" spans="1:7">
       <c r="A3" s="23">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="25" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="71" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" ht="15.75" hidden="1" spans="1:7">
       <c r="A4" s="23">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>8</v>
@@ -2796,19 +2856,21 @@
         <v>9</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="F4" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="27" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" ht="15.75" hidden="1" spans="1:7">
       <c r="A5" s="23">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>8</v>
@@ -2817,19 +2879,21 @@
         <v>9</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="71" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="6" ht="15.75" hidden="1" spans="1:7">
       <c r="A6" s="23">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>8</v>
@@ -2838,65 +2902,67 @@
         <v>9</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" ht="15.75" hidden="1" spans="1:7">
       <c r="A7" s="23">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C7" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>24</v>
+        <v>14</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="15.75" hidden="1" spans="1:7">
-      <c r="A8" s="23">
-        <v>7</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>25</v>
+      <c r="A8" s="29">
+        <v>163</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>26</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="58" t="s">
+      <c r="E8" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="31" t="s">
         <v>27</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" ht="15.75" hidden="1" spans="1:7">
       <c r="A9" s="23">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="24" t="s">
         <v>8</v>
@@ -2905,19 +2971,21 @@
         <v>9</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="F9" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G9" s="71" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="10" ht="15.75" hidden="1" spans="1:7">
       <c r="A10" s="23">
-        <v>9</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>31</v>
+        <v>141</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>33</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>8</v>
@@ -2925,43 +2993,43 @@
       <c r="D10" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="58" t="s">
-        <v>33</v>
-      </c>
+      <c r="E10" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="27"/>
     </row>
     <row r="11" ht="15.75" hidden="1" spans="1:7">
       <c r="A11" s="23">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="26"/>
+      <c r="E11" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="12" ht="15.75" hidden="1" spans="1:7">
       <c r="A12" s="23">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>8</v>
@@ -2969,41 +3037,45 @@
       <c r="D12" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="26"/>
+      <c r="E12" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="13" ht="15.75" hidden="1" spans="1:7">
       <c r="A13" s="23">
-        <v>12</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>38</v>
+        <v>64</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D13" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="26"/>
+      <c r="E13" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="71" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="14" ht="15.75" hidden="1" spans="1:7">
       <c r="A14" s="23">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>8</v>
@@ -3012,19 +3084,21 @@
         <v>9</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="15" ht="15.75" hidden="1" spans="1:7">
       <c r="A15" s="23">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>8</v>
@@ -3033,19 +3107,21 @@
         <v>9</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="71" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="16" ht="15.75" hidden="1" spans="1:7">
       <c r="A16" s="23">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>8</v>
@@ -3054,40 +3130,44 @@
         <v>9</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="F16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="17" ht="15.75" hidden="1" spans="1:7">
       <c r="A17" s="23">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="G17" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" ht="15.75" hidden="1" spans="1:7">
       <c r="A18" s="23">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>8</v>
@@ -3096,19 +3176,21 @@
         <v>9</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="71" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="19" ht="15.75" hidden="1" spans="1:7">
       <c r="A19" s="23">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>8</v>
@@ -3116,20 +3198,22 @@
       <c r="D19" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="26"/>
+      <c r="E19" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" ht="15.75" hidden="1" spans="1:7">
       <c r="A20" s="23">
-        <v>19</v>
+        <v>103</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>8</v>
@@ -3138,292 +3222,312 @@
         <v>9</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="26"/>
+        <v>36</v>
+      </c>
+      <c r="F20" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="21" ht="15.75" hidden="1" spans="1:7">
       <c r="A21" s="23">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" s="26"/>
+      <c r="E21" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G21" s="73" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="22" ht="15.75" hidden="1" spans="1:7">
       <c r="A22" s="23">
-        <v>21</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>57</v>
+        <v>132</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>69</v>
       </c>
       <c r="C22" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="26"/>
+      <c r="E22" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="G22" s="73" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="23" ht="15.75" hidden="1" spans="1:7">
       <c r="A23" s="23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>59</v>
+        <v>133</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>72</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="26"/>
+      <c r="D23" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="G23" s="73" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="24" ht="15.75" hidden="1" spans="1:7">
       <c r="A24" s="23">
-        <v>23</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>61</v>
+        <v>135</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>75</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="26"/>
+      <c r="E24" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="25" ht="15.75" hidden="1" spans="1:7">
       <c r="A25" s="23">
-        <v>24</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>63</v>
+        <v>136</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>78</v>
       </c>
       <c r="C25" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="26"/>
+      <c r="D25" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="G25" s="73" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="26" ht="15.75" hidden="1" spans="1:7">
       <c r="A26" s="23">
-        <v>25</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>65</v>
+        <v>137</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>81</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="26"/>
+      <c r="E26" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="73" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="27" ht="15.75" hidden="1" spans="1:7">
       <c r="A27" s="23">
-        <v>26</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>67</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B27" s="24"/>
       <c r="C27" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="26"/>
+      <c r="D27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="G27" s="73" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="28" ht="15.75" hidden="1" spans="1:7">
       <c r="A28" s="23">
-        <v>27</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>69</v>
+        <v>140</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>86</v>
       </c>
       <c r="C28" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="26"/>
+      <c r="E28" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="74" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="29" ht="15.75" hidden="1" spans="1:7">
       <c r="A29" s="23">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F29" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="26"/>
+      <c r="E29" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="G29" s="27" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="30" ht="15.75" hidden="1" spans="1:7">
       <c r="A30" s="23">
-        <v>29</v>
+        <v>148</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="26"/>
+      <c r="D30" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="G30" s="72" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="31" ht="15.75" hidden="1" spans="1:7">
-      <c r="A31" s="23">
-        <v>30</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>75</v>
+      <c r="A31" s="29">
+        <v>156</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>95</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="26"/>
+      <c r="D31" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" s="27"/>
     </row>
     <row r="32" ht="15.75" hidden="1" spans="1:7">
-      <c r="A32" s="23">
-        <v>31</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>77</v>
+      <c r="A32" s="29">
+        <v>159</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>97</v>
       </c>
       <c r="C32" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" s="26"/>
+      <c r="E32" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="27"/>
     </row>
     <row r="33" ht="15.75" hidden="1" spans="1:7">
-      <c r="A33" s="23">
-        <v>32</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>79</v>
+      <c r="A33" s="29">
+        <v>156</v>
+      </c>
+      <c r="B33" s="41" t="s">
+        <v>99</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="G33" s="26"/>
+      <c r="E33" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="G33" s="27"/>
     </row>
     <row r="34" ht="15.75" hidden="1" spans="1:7">
       <c r="A34" s="23">
-        <v>34</v>
+        <v>106</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>8</v>
@@ -3432,128 +3536,126 @@
         <v>9</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="26"/>
-    </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
+        <v>102</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" s="27"/>
+    </row>
+    <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="23">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" s="26"/>
-    </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
+        <v>106</v>
+      </c>
+      <c r="F35" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="G35" s="27"/>
+    </row>
+    <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="23">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" s="59" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+        <v>109</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="F36" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="G36" s="27"/>
+    </row>
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="23">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="G37" s="26"/>
-    </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
+        <v>106</v>
+      </c>
+      <c r="F37" s="35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="27"/>
+    </row>
+    <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="23">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="G38" s="58" t="s">
-        <v>92</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F38" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="G38" s="27"/>
     </row>
     <row r="39" ht="15.75" hidden="1" spans="1:7">
       <c r="A39" s="23">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C39" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="23" t="s">
+      <c r="D39" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" s="26"/>
+      <c r="E39" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="G39" s="27" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="40" ht="15.75" hidden="1" spans="1:7">
       <c r="A40" s="23">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>8</v>
@@ -3562,19 +3664,21 @@
         <v>9</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" s="26"/>
+        <v>116</v>
+      </c>
+      <c r="F40" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="G40" s="27" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="41" ht="15.75" hidden="1" spans="1:7">
       <c r="A41" s="23">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>8</v>
@@ -3583,19 +3687,19 @@
         <v>9</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G41" s="26"/>
+        <v>116</v>
+      </c>
+      <c r="F41" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="G41" s="27"/>
     </row>
     <row r="42" ht="15.75" hidden="1" spans="1:7">
       <c r="A42" s="23">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C42" s="24" t="s">
         <v>8</v>
@@ -3603,41 +3707,45 @@
       <c r="D42" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="G42" s="26"/>
+      <c r="E42" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="G42" s="27" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="43" ht="15.75" hidden="1" spans="1:7">
       <c r="A43" s="23">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C43" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="G43" s="26"/>
+        <v>116</v>
+      </c>
+      <c r="F43" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" s="27" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="44" ht="15.75" hidden="1" spans="1:7">
       <c r="A44" s="23">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>8</v>
@@ -3646,19 +3754,21 @@
         <v>9</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44" s="26"/>
+        <v>116</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="G44" s="27" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="45" ht="15.75" hidden="1" spans="1:7">
       <c r="A45" s="23">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C45" s="24" t="s">
         <v>8</v>
@@ -3667,1077 +3777,1069 @@
         <v>9</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="G45" s="26"/>
+        <v>116</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="G45" s="72" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="46" ht="15.75" hidden="1" spans="1:7">
       <c r="A46" s="23">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="C46" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F46" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G46" s="26"/>
+      <c r="D46" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="42" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="G46" s="28"/>
     </row>
     <row r="47" ht="15.75" hidden="1" spans="1:7">
       <c r="A47" s="23">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="C47" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="23" t="s">
+      <c r="D47" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="G47" s="26"/>
+      <c r="E47" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F47" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="G47" s="27"/>
     </row>
     <row r="48" ht="15.75" hidden="1" spans="1:7">
       <c r="A48" s="23">
-        <v>48</v>
-      </c>
-      <c r="B48" s="24" t="s">
-        <v>111</v>
+        <v>150</v>
+      </c>
+      <c r="B48" s="30" t="s">
+        <v>140</v>
       </c>
       <c r="C48" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D48" s="23" t="s">
+      <c r="D48" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F48" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="G48" s="27"/>
+    </row>
+    <row r="49" ht="15.75" hidden="1" spans="1:7">
+      <c r="A49" s="29">
+        <v>152</v>
+      </c>
+      <c r="B49" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F49" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="G49" s="27"/>
+    </row>
+    <row r="50" ht="15.75" hidden="1" spans="1:7">
+      <c r="A50" s="29">
+        <v>153</v>
+      </c>
+      <c r="B50" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F50" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="G50" s="27"/>
+    </row>
+    <row r="51" ht="15.75" hidden="1" spans="1:7">
+      <c r="A51" s="29">
+        <v>153</v>
+      </c>
+      <c r="B51" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="G51" s="27"/>
+    </row>
+    <row r="52" ht="15.75" hidden="1" spans="1:7">
+      <c r="A52" s="29">
+        <v>157</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="G52" s="27"/>
+    </row>
+    <row r="53" ht="15.75" hidden="1" spans="1:7">
+      <c r="A53" s="29">
+        <v>158</v>
+      </c>
+      <c r="B53" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="G53" s="72" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" hidden="1" spans="1:7">
+      <c r="A54" s="29">
+        <v>160</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="G54" s="72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" hidden="1" spans="1:7">
+      <c r="A55" s="29">
+        <v>161</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E55" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F55" s="27"/>
+      <c r="G55" s="72" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" hidden="1" spans="1:7">
+      <c r="A56" s="29">
+        <v>162</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F56" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="G56" s="72" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" hidden="1" spans="1:7">
+      <c r="A57" s="29">
+        <v>164</v>
+      </c>
+      <c r="B57" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" s="45" t="s">
+        <v>162</v>
+      </c>
+      <c r="G57" s="72" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" hidden="1" spans="1:7">
+      <c r="A58" s="29">
+        <v>157</v>
+      </c>
+      <c r="B58" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="46" t="s">
+        <v>116</v>
+      </c>
+      <c r="F58" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="G58" s="27"/>
+    </row>
+    <row r="59" ht="15.75" spans="1:7">
+      <c r="A59" s="23">
+        <v>8</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F59" s="31" t="s">
+        <v>168</v>
+      </c>
+      <c r="G59" s="27"/>
+    </row>
+    <row r="60" ht="15.75" spans="1:7">
+      <c r="A60" s="23">
+        <v>9</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E60" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="F60" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="G60" s="71" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" spans="1:7">
+      <c r="A61" s="23">
+        <v>13</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F61" s="35" t="s">
+        <v>173</v>
+      </c>
+      <c r="G61" s="27"/>
+    </row>
+    <row r="62" ht="15.75" spans="1:7">
+      <c r="A62" s="23">
+        <v>15</v>
+      </c>
+      <c r="B62" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F62" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="G62" s="27"/>
+    </row>
+    <row r="63" ht="15.75" spans="1:7">
+      <c r="A63" s="23">
+        <v>20</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F63" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="G63" s="27"/>
+    </row>
+    <row r="64" ht="15.75" spans="1:7">
+      <c r="A64" s="23">
+        <v>24</v>
+      </c>
+      <c r="B64" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F64" s="51" t="s">
+        <v>179</v>
+      </c>
+      <c r="G64" s="27"/>
+    </row>
+    <row r="65" ht="15.75" spans="1:7">
+      <c r="A65" s="23">
+        <v>28</v>
+      </c>
+      <c r="B65" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C65" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F65" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="G65" s="27"/>
+    </row>
+    <row r="66" ht="15.75" spans="1:7">
+      <c r="A66" s="23">
+        <v>29</v>
+      </c>
+      <c r="B66" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F66" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G66" s="27"/>
+    </row>
+    <row r="67" ht="15.75" spans="1:7">
+      <c r="A67" s="23">
+        <v>30</v>
+      </c>
+      <c r="B67" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="C67" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F67" s="35" t="s">
+        <v>185</v>
+      </c>
+      <c r="G67" s="27"/>
+    </row>
+    <row r="68" ht="15.75" spans="1:7">
+      <c r="A68" s="23">
+        <v>32</v>
+      </c>
+      <c r="B68" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C68" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F68" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="G68" s="27"/>
+    </row>
+    <row r="69" ht="15.75" spans="1:7">
+      <c r="A69" s="23">
+        <v>34</v>
+      </c>
+      <c r="B69" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E69" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F69" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="G69" s="27"/>
+    </row>
+    <row r="70" ht="15.75" spans="1:7">
+      <c r="A70" s="23">
+        <v>38</v>
+      </c>
+      <c r="B70" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="C70" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F70" s="35" t="s">
+        <v>191</v>
+      </c>
+      <c r="G70" s="71" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" spans="1:7">
+      <c r="A71" s="23">
+        <v>39</v>
+      </c>
+      <c r="B71" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E71" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F71" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="G71" s="27"/>
+    </row>
+    <row r="72" ht="15.75" spans="1:7">
+      <c r="A72" s="23">
+        <v>52</v>
+      </c>
+      <c r="B72" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E72" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="F72" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="G72" s="71" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="73" ht="31.5" hidden="1" spans="1:7">
+      <c r="A73" s="23">
+        <v>125</v>
+      </c>
+      <c r="B73" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="C73" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="E73" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="F73" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="G73" s="28"/>
+    </row>
+    <row r="74" ht="15.75" spans="1:7">
+      <c r="A74" s="23">
+        <v>127</v>
+      </c>
+      <c r="B74" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E74" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="F74" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="G74" s="28"/>
+    </row>
+    <row r="75" ht="15.75" spans="1:7">
+      <c r="A75" s="23">
+        <v>128</v>
+      </c>
+      <c r="B75" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C75" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E75" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="F75" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="G75" s="28"/>
+    </row>
+    <row r="76" ht="15.75" spans="1:7">
+      <c r="A76" s="23">
+        <v>131</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E76" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F76" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="G76" s="73" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" spans="1:7">
+      <c r="A77" s="23">
+        <v>134</v>
+      </c>
+      <c r="B77" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E77" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="G77" s="27"/>
+    </row>
+    <row r="78" ht="15.75" spans="1:7">
+      <c r="A78" s="23">
+        <v>142</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E78" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="G78" s="27"/>
+    </row>
+    <row r="79" ht="15.75" spans="1:7">
+      <c r="A79" s="29">
+        <v>155</v>
+      </c>
+      <c r="B79" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E79" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="G79" s="27"/>
+    </row>
+    <row r="80" ht="15.75" spans="1:7">
+      <c r="A80" s="29">
+        <v>165</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E80" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F80" s="53" t="s">
+        <v>215</v>
+      </c>
+      <c r="G80" s="72" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" spans="1:7">
+      <c r="A81" s="23">
+        <v>6</v>
+      </c>
+      <c r="B81" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C81" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E81" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="F81" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="G81" s="71" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" spans="1:7">
+      <c r="A82" s="23">
+        <v>1</v>
+      </c>
+      <c r="B82" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E82" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F82" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="G82" s="27"/>
+    </row>
+    <row r="83" ht="15.75" spans="1:7">
+      <c r="A83" s="23">
+        <v>2</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F83" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="G83" s="27"/>
+    </row>
+    <row r="84" ht="15.75" spans="1:7">
+      <c r="A84" s="23">
+        <v>3</v>
+      </c>
+      <c r="B84" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E84" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F84" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="G84" s="27"/>
+    </row>
+    <row r="85" ht="15.75" spans="1:7">
+      <c r="A85" s="23">
+        <v>4</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E85" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F85" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="G85" s="27"/>
+    </row>
+    <row r="86" ht="15.75" spans="1:7">
+      <c r="A86" s="23">
+        <v>5</v>
+      </c>
+      <c r="B86" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E86" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F86" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="G86" s="27"/>
+    </row>
+    <row r="87" ht="15.75" spans="1:7">
+      <c r="A87" s="23">
+        <v>7</v>
+      </c>
+      <c r="B87" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F87" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="G87" s="71" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" spans="1:7">
+      <c r="A88" s="23">
+        <v>10</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="C88" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E88" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F88" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="G88" s="27"/>
+    </row>
+    <row r="89" ht="15.75" spans="1:7">
+      <c r="A89" s="23">
+        <v>11</v>
+      </c>
+      <c r="B89" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="C89" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F89" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="G89" s="27"/>
+    </row>
+    <row r="90" ht="15.75" spans="1:7">
+      <c r="A90" s="23">
+        <v>12</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="C90" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E90" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F90" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="G90" s="27"/>
+    </row>
+    <row r="91" ht="15.75" spans="1:7">
+      <c r="A91" s="23">
+        <v>14</v>
+      </c>
+      <c r="B91" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="C91" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E91" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F91" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="G91" s="27"/>
+    </row>
+    <row r="92" ht="15.75" spans="1:7">
+      <c r="A92" s="23">
+        <v>17</v>
+      </c>
+      <c r="B92" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="C92" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F92" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="G92" s="27"/>
+    </row>
+    <row r="93" ht="15.75" spans="1:7">
+      <c r="A93" s="23">
+        <v>19</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="C93" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E93" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F93" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="G93" s="27"/>
+    </row>
+    <row r="94" ht="15.75" spans="1:7">
+      <c r="A94" s="23">
         <v>21</v>
       </c>
-      <c r="E48" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="26"/>
-    </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
-      <c r="A49" s="23">
-        <v>49</v>
-      </c>
-      <c r="B49" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G49" s="26"/>
-    </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
-      <c r="A50" s="23">
-        <v>50</v>
-      </c>
-      <c r="B50" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="G50" s="26"/>
-    </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
-      <c r="A51" s="23">
-        <v>51</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="G51" s="26"/>
-    </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
-      <c r="A52" s="23">
-        <v>52</v>
-      </c>
-      <c r="B52" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="G52" s="58" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
-      <c r="A53" s="23">
-        <v>53</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="G53" s="26"/>
-    </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
-      <c r="A54" s="23">
-        <v>54</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F54" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="G54" s="58" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
-      <c r="A55" s="23">
-        <v>55</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55" s="34"/>
-      <c r="F55" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="G55" s="26" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
-      <c r="A56" s="23">
-        <v>57</v>
-      </c>
-      <c r="B56" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E56" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="F56" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="G56" s="26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
-      <c r="A57" s="23">
-        <v>58</v>
-      </c>
-      <c r="B57" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="F57" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="G57" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
-      <c r="A58" s="23">
-        <v>59</v>
-      </c>
-      <c r="B58" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="G58" s="26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" hidden="1" spans="1:7">
-      <c r="A59" s="23">
-        <v>60</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E59" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="F59" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="G59" s="26" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" hidden="1" spans="1:7">
-      <c r="A60" s="23">
-        <v>61</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C60" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="E60" s="37"/>
-      <c r="F60" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="G60" s="38" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" hidden="1" spans="1:7">
-      <c r="A61" s="23">
-        <v>62</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E61" s="30"/>
-      <c r="F61" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="G61" s="26" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" hidden="1" spans="1:7">
-      <c r="A62" s="23">
-        <v>64</v>
-      </c>
-      <c r="B62" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E62" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="F62" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="G62" s="58" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" hidden="1" spans="1:7">
-      <c r="A63" s="23">
-        <v>65</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E63" s="32"/>
-      <c r="F63" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" hidden="1" spans="1:7">
-      <c r="A64" s="23">
-        <v>66</v>
-      </c>
-      <c r="B64" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E64" s="35"/>
-      <c r="F64" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" hidden="1" spans="1:7">
-      <c r="A65" s="23">
-        <v>67</v>
-      </c>
-      <c r="B65" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="C65" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E65" s="32"/>
-      <c r="F65" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="G65" s="59" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" hidden="1" spans="1:7">
-      <c r="A66" s="23">
-        <v>68</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F66" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="G66" s="26" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" hidden="1" spans="1:7">
-      <c r="A67" s="23">
-        <v>69</v>
-      </c>
-      <c r="B67" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="C67" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" s="23"/>
-      <c r="F67" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="G67" s="58" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" hidden="1" spans="1:7">
-      <c r="A68" s="23">
-        <v>70</v>
-      </c>
-      <c r="B68" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="C68" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E68" s="23"/>
-      <c r="F68" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="G68" s="58" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="69" ht="31.5" hidden="1" spans="1:7">
-      <c r="A69" s="23">
-        <v>71</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="C69" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E69" s="23"/>
-      <c r="F69" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="G69" s="58" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" hidden="1" spans="1:7">
-      <c r="A70" s="23">
-        <v>72</v>
-      </c>
-      <c r="B70" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E70" s="23"/>
-      <c r="F70" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="G70" s="58" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" hidden="1" spans="1:7">
-      <c r="A71" s="23">
-        <v>73</v>
-      </c>
-      <c r="B71" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="C71" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F71" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="G71" s="58" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" hidden="1" spans="1:7">
-      <c r="A72" s="23">
-        <v>74</v>
-      </c>
-      <c r="B72" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E72" s="23"/>
-      <c r="F72" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="G72" s="26" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" hidden="1" spans="1:7">
-      <c r="A73" s="23">
-        <v>75</v>
-      </c>
-      <c r="B73" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="C73" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E73" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F73" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="G73" s="26" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" hidden="1" spans="1:7">
-      <c r="A74" s="23">
-        <v>76</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E74" s="23"/>
-      <c r="F74" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="G74" s="58" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" hidden="1" spans="1:7">
-      <c r="A75" s="23">
-        <v>77</v>
-      </c>
-      <c r="B75" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E75" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F75" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="G75" s="26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" hidden="1" spans="1:7">
-      <c r="A76" s="23">
-        <v>78</v>
-      </c>
-      <c r="B76" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E76" s="23"/>
-      <c r="F76" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="G76" s="26"/>
-    </row>
-    <row r="77" ht="15.75" hidden="1" spans="1:7">
-      <c r="A77" s="23">
-        <v>79</v>
-      </c>
-      <c r="B77" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="C77" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E77" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F77" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="G77" s="58" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" hidden="1" spans="1:7">
-      <c r="A78" s="23">
-        <v>80</v>
-      </c>
-      <c r="B78" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E78" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F78" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="G78" s="26" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" hidden="1" spans="1:7">
-      <c r="A79" s="23">
-        <v>81</v>
-      </c>
-      <c r="B79" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="C79" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E79" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F79" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="G79" s="26"/>
-    </row>
-    <row r="80" ht="15.75" hidden="1" spans="1:7">
-      <c r="A80" s="23">
-        <v>82</v>
-      </c>
-      <c r="B80" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="C80" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E80" s="23"/>
-      <c r="F80" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="G80" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" hidden="1" spans="1:7">
-      <c r="A81" s="23">
-        <v>83</v>
-      </c>
-      <c r="B81" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E81" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F81" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="G81" s="26" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" hidden="1" spans="1:7">
-      <c r="A82" s="23">
-        <v>84</v>
-      </c>
-      <c r="B82" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E82" s="32"/>
-      <c r="F82" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="G82" s="26"/>
-    </row>
-    <row r="83" ht="15.75" hidden="1" spans="1:7">
-      <c r="A83" s="23">
-        <v>85</v>
-      </c>
-      <c r="B83" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="C83" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E83" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F83" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="G83" s="26" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" hidden="1" spans="1:7">
-      <c r="A84" s="23">
-        <v>86</v>
-      </c>
-      <c r="B84" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C84" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E84" s="32"/>
-      <c r="F84" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="G84" s="26"/>
-    </row>
-    <row r="85" ht="15.75" hidden="1" spans="1:7">
-      <c r="A85" s="23">
-        <v>87</v>
-      </c>
-      <c r="B85" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="C85" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E85" s="32"/>
-      <c r="F85" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="G85" s="26" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" hidden="1" spans="1:7">
-      <c r="A86" s="23">
-        <v>88</v>
-      </c>
-      <c r="B86" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="C86" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E86" s="35"/>
-      <c r="F86" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="G86" s="26" t="s">
+      <c r="B94" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="C94" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E94" s="23" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="87" ht="15.75" hidden="1" spans="1:7">
-      <c r="A87" s="23">
-        <v>89</v>
-      </c>
-      <c r="B87" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C87" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E87" s="23"/>
-      <c r="F87" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="G87" s="58" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" hidden="1" spans="1:7">
-      <c r="A88" s="23">
-        <v>90</v>
-      </c>
-      <c r="B88" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C88" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E88" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F88" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="G88" s="26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" hidden="1" spans="1:7">
-      <c r="A89" s="23">
-        <v>91</v>
-      </c>
-      <c r="B89" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="C89" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E89" s="23"/>
-      <c r="F89" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="G89" s="58" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" hidden="1" spans="1:7">
-      <c r="A90" s="23">
-        <v>92</v>
-      </c>
-      <c r="B90" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="C90" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="F90" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="G90" s="58" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" hidden="1" spans="1:7">
-      <c r="A91" s="23">
-        <v>93</v>
-      </c>
-      <c r="B91" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C91" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E91" s="23"/>
-      <c r="F91" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="G91" s="26" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" hidden="1" spans="1:7">
-      <c r="A92" s="23">
-        <v>94</v>
-      </c>
-      <c r="B92" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="C92" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E92" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F92" s="44" t="s">
-        <v>240</v>
-      </c>
-      <c r="G92" s="58" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" hidden="1" spans="1:7">
-      <c r="A93" s="23">
-        <v>95</v>
-      </c>
-      <c r="B93" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="C93" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E93" s="23"/>
-      <c r="F93" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="G93" s="26" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="94" ht="31.5" hidden="1" spans="1:7">
-      <c r="A94" s="23">
-        <v>96</v>
-      </c>
-      <c r="B94" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="C94" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E94" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="F94" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="G94" s="26" t="s">
+      <c r="F94" s="35" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="95" ht="15.75" hidden="1" spans="1:7">
+      <c r="G94" s="27"/>
+    </row>
+    <row r="95" ht="15.75" spans="1:7">
       <c r="A95" s="23">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="B95" s="24" t="s">
         <v>249</v>
@@ -4746,594 +4848,632 @@
         <v>8</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F95" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="F95" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="G95" s="26" t="s">
+      <c r="G95" s="27"/>
+    </row>
+    <row r="96" ht="15.75" spans="1:7">
+      <c r="A96" s="23">
+        <v>23</v>
+      </c>
+      <c r="B96" s="24" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="96" ht="15.75" hidden="1" spans="1:7">
-      <c r="A96" s="23">
-        <v>98</v>
-      </c>
-      <c r="B96" s="24" t="s">
+      <c r="C96" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E96" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F96" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="C96" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E96" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F96" s="33" t="s">
+      <c r="G96" s="27"/>
+    </row>
+    <row r="97" ht="15.75" spans="1:7">
+      <c r="A97" s="23">
+        <v>25</v>
+      </c>
+      <c r="B97" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="G96" s="26" t="s">
+      <c r="C97" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E97" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F97" s="35" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="97" ht="15.75" hidden="1" spans="1:7">
-      <c r="A97" s="23">
-        <v>99</v>
-      </c>
-      <c r="B97" s="24" t="s">
+      <c r="G97" s="27"/>
+    </row>
+    <row r="98" ht="15.75" spans="1:7">
+      <c r="A98" s="23">
+        <v>27</v>
+      </c>
+      <c r="B98" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="C97" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E97" s="23"/>
-      <c r="F97" s="33"/>
-      <c r="G97" s="26"/>
-    </row>
-    <row r="98" ht="15.75" hidden="1" spans="1:7">
-      <c r="A98" s="23">
-        <v>100</v>
-      </c>
-      <c r="B98" s="24" t="s">
+      <c r="C98" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E98" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F98" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="C98" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E98" s="35"/>
-      <c r="F98" s="27" t="s">
+      <c r="G98" s="27"/>
+    </row>
+    <row r="99" ht="15.75" spans="1:7">
+      <c r="A99" s="23">
+        <v>31</v>
+      </c>
+      <c r="B99" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="G98" s="26" t="s">
+      <c r="C99" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E99" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F99" s="31" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="99" ht="15.75" hidden="1" spans="1:7">
-      <c r="A99" s="23">
-        <v>101</v>
-      </c>
-      <c r="B99" s="24" t="s">
+      <c r="G99" s="27"/>
+    </row>
+    <row r="100" ht="15.75" spans="1:7">
+      <c r="A100" s="23">
+        <v>35</v>
+      </c>
+      <c r="B100" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="C99" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E99" s="32"/>
-      <c r="F99" s="27" t="s">
+      <c r="C100" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E100" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F100" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="G99" s="26"/>
-    </row>
-    <row r="100" ht="15.75" hidden="1" spans="1:7">
-      <c r="A100" s="23">
-        <v>102</v>
-      </c>
-      <c r="B100" s="24" t="s">
+      <c r="G100" s="27"/>
+    </row>
+    <row r="101" ht="15.75" spans="1:7">
+      <c r="A101" s="23">
+        <v>36</v>
+      </c>
+      <c r="B101" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="C100" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E100" s="35"/>
-      <c r="F100" s="33" t="s">
+      <c r="C101" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E101" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F101" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="G100" s="26" t="s">
+      <c r="G101" s="72" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="101" ht="15.75" hidden="1" spans="1:7">
-      <c r="A101" s="23">
-        <v>103</v>
-      </c>
-      <c r="B101" s="24" t="s">
+    <row r="102" ht="15.75" spans="1:7">
+      <c r="A102" s="23">
+        <v>37</v>
+      </c>
+      <c r="B102" s="24" t="s">
         <v>264</v>
       </c>
-      <c r="C101" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D101" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E101" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F101" s="33" t="s">
+      <c r="C102" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E102" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F102" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="G101" s="26" t="s">
+      <c r="G102" s="27"/>
+    </row>
+    <row r="103" ht="15.75" spans="1:7">
+      <c r="A103" s="23">
+        <v>40</v>
+      </c>
+      <c r="B103" s="24" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="102" ht="15.75" hidden="1" spans="1:7">
-      <c r="A102" s="23">
-        <v>104</v>
-      </c>
-      <c r="B102" s="24" t="s">
+      <c r="C103" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E103" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F103" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="C102" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D102" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E102" s="35"/>
-      <c r="F102" s="33" t="s">
+      <c r="G103" s="27"/>
+    </row>
+    <row r="104" ht="15.75" spans="1:7">
+      <c r="A104" s="23">
+        <v>41</v>
+      </c>
+      <c r="B104" s="24" t="s">
         <v>268</v>
       </c>
-      <c r="G102" s="26" t="s">
+      <c r="C104" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E104" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F104" s="35" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="103" ht="15.75" hidden="1" spans="1:7">
-      <c r="A103" s="23">
+      <c r="G104" s="27"/>
+    </row>
+    <row r="105" ht="15.75" spans="1:7">
+      <c r="A105" s="23">
+        <v>42</v>
+      </c>
+      <c r="B105" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E105" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F105" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="G105" s="27"/>
+    </row>
+    <row r="106" ht="15.75" spans="1:7">
+      <c r="A106" s="23">
+        <v>43</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="B103" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="C103" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E103" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F103" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="G103" s="59" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" hidden="1" spans="1:7">
-      <c r="A104" s="23">
-        <v>106</v>
-      </c>
-      <c r="B104" s="24" t="s">
+      <c r="E106" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F106" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C104" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E104" s="23" t="s">
+      <c r="G106" s="27"/>
+    </row>
+    <row r="107" ht="15.75" spans="1:7">
+      <c r="A107" s="23">
+        <v>44</v>
+      </c>
+      <c r="B107" s="24" t="s">
         <v>274</v>
       </c>
-      <c r="F104" s="33" t="s">
+      <c r="C107" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E107" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F107" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="G104" s="26"/>
-    </row>
-    <row r="105" ht="15.75" hidden="1" spans="1:7">
-      <c r="A105" s="23">
-        <v>107</v>
-      </c>
-      <c r="B105" s="24" t="s">
+      <c r="G107" s="27"/>
+    </row>
+    <row r="108" ht="15.75" spans="1:7">
+      <c r="A108" s="23">
+        <v>45</v>
+      </c>
+      <c r="B108" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="C105" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E105" s="46"/>
-      <c r="F105" s="33" t="s">
+      <c r="C108" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E108" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F108" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="G105" s="28"/>
-    </row>
-    <row r="106" ht="15.75" hidden="1" spans="1:7">
-      <c r="A106" s="23">
-        <v>108</v>
-      </c>
-      <c r="B106" s="24" t="s">
+      <c r="G108" s="27"/>
+    </row>
+    <row r="109" ht="15.75" spans="1:7">
+      <c r="A109" s="23">
+        <v>47</v>
+      </c>
+      <c r="B109" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="C106" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E106" s="46"/>
-      <c r="F106" s="33" t="s">
+      <c r="C109" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E109" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F109" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="G106" s="28"/>
-    </row>
-    <row r="107" ht="15.75" hidden="1" spans="1:7">
-      <c r="A107" s="23">
+      <c r="G109" s="27"/>
+    </row>
+    <row r="110" ht="15.75" spans="1:7">
+      <c r="A110" s="23">
+        <v>48</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="E110" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F110" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="G110" s="27"/>
+    </row>
+    <row r="111" ht="15.75" spans="1:7">
+      <c r="A111" s="23">
+        <v>49</v>
+      </c>
+      <c r="B111" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="B107" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="C107" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E107" s="46"/>
-      <c r="F107" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="G107" s="28"/>
-    </row>
-    <row r="108" ht="15.75" hidden="1" spans="1:7">
-      <c r="A108" s="23">
-        <v>110</v>
-      </c>
-      <c r="B108" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D108" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E108" s="46"/>
-      <c r="F108" s="33" t="s">
+      <c r="E111" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F111" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="G108" s="28"/>
-    </row>
-    <row r="109" ht="31.5" hidden="1" spans="1:7">
-      <c r="A109" s="23">
-        <v>111</v>
-      </c>
-      <c r="B109" s="24" t="s">
+      <c r="G111" s="27"/>
+    </row>
+    <row r="112" s="15" customFormat="1" ht="15.75" spans="1:7">
+      <c r="A112" s="23">
+        <v>50</v>
+      </c>
+      <c r="B112" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="C109" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E109" s="46"/>
-      <c r="F109" s="33" t="s">
+      <c r="C112" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E112" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F112" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="G109" s="28"/>
-    </row>
-    <row r="110" ht="15.75" hidden="1" spans="1:7">
-      <c r="A110" s="23">
-        <v>112</v>
-      </c>
-      <c r="B110" s="24" t="s">
+      <c r="G112" s="27"/>
+    </row>
+    <row r="113" ht="15.75" spans="1:7">
+      <c r="A113" s="23">
+        <v>51</v>
+      </c>
+      <c r="B113" s="24" t="s">
         <v>286</v>
       </c>
-      <c r="C110" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E110" s="46"/>
-      <c r="F110" s="33" t="s">
+      <c r="C113" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E113" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F113" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="G110" s="28"/>
-    </row>
-    <row r="111" ht="15.75" hidden="1" spans="1:7">
-      <c r="A111" s="23">
-        <v>113</v>
-      </c>
-      <c r="B111" s="24" t="s">
+      <c r="G113" s="27"/>
+    </row>
+    <row r="114" ht="15.75" spans="1:7">
+      <c r="A114" s="23">
+        <v>53</v>
+      </c>
+      <c r="B114" s="24" t="s">
         <v>288</v>
       </c>
-      <c r="C111" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E111" s="46"/>
-      <c r="F111" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="G111" s="28"/>
-    </row>
-    <row r="112" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
-      <c r="A112" s="23">
-        <v>114</v>
-      </c>
-      <c r="B112" s="24" t="s">
+      <c r="C114" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="E114" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="F114" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="C112" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E112" s="46"/>
-      <c r="F112" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="G112" s="28"/>
-    </row>
-    <row r="113" ht="15.75" hidden="1" spans="1:7">
-      <c r="A113" s="23">
-        <v>115</v>
-      </c>
-      <c r="B113" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="C113" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D113" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E113" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F113" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="G113" s="28"/>
-    </row>
-    <row r="114" ht="15.75" hidden="1" spans="1:7">
-      <c r="A114" s="23">
-        <v>116</v>
-      </c>
-      <c r="B114" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="C114" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E114" s="46"/>
-      <c r="F114" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="G114" s="28"/>
+      <c r="G114" s="27"/>
     </row>
     <row r="115" ht="15.75" hidden="1" spans="1:7">
       <c r="A115" s="23">
-        <v>117</v>
-      </c>
-      <c r="B115" s="24"/>
+        <v>124</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>290</v>
+      </c>
       <c r="C115" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D115" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E115" s="46"/>
-      <c r="F115" s="33" t="s">
+      <c r="D115" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="F115" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="G115" s="28"/>
+    </row>
+    <row r="116" ht="15.75" spans="1:7">
+      <c r="A116" s="23">
+        <v>129</v>
+      </c>
+      <c r="B116" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="C116" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="E116" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="F116" s="26" t="s">
+        <v>293</v>
+      </c>
+      <c r="G116" s="71" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" spans="1:7">
+      <c r="A117" s="23">
+        <v>144</v>
+      </c>
+      <c r="B117" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="G115" s="28"/>
-    </row>
-    <row r="116" ht="15.75" hidden="1" spans="1:7">
-      <c r="A116" s="23">
-        <v>118</v>
-      </c>
-      <c r="B116" s="24" t="s">
+      <c r="C117" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="E117" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="F117" s="26" t="s">
         <v>296</v>
       </c>
-      <c r="C116" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E116" s="46"/>
-      <c r="F116" s="33" t="s">
+      <c r="G117" s="27"/>
+    </row>
+    <row r="118" ht="15.75" spans="1:7">
+      <c r="A118" s="23">
+        <v>145</v>
+      </c>
+      <c r="B118" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="G116" s="28"/>
-    </row>
-    <row r="117" ht="15.75" hidden="1" spans="1:7">
-      <c r="A117" s="23">
-        <v>119</v>
-      </c>
-      <c r="B117" s="24" t="s">
+      <c r="C118" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E118" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="F118" s="26" t="s">
         <v>298</v>
       </c>
-      <c r="C117" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D117" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E117" s="46"/>
-      <c r="F117" s="33" t="s">
+      <c r="G118" s="27"/>
+    </row>
+    <row r="119" ht="15.75" spans="1:7">
+      <c r="A119" s="23">
+        <v>149</v>
+      </c>
+      <c r="B119" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="G117" s="28"/>
-    </row>
-    <row r="118" ht="15.75" hidden="1" spans="1:7">
-      <c r="A118" s="23">
-        <v>120</v>
-      </c>
-      <c r="B118" s="24" t="s">
+      <c r="C119" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E119" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="F119" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="C118" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E118" s="46"/>
-      <c r="F118" s="33" t="s">
+      <c r="G119" s="27"/>
+    </row>
+    <row r="120" ht="15.75" spans="1:7">
+      <c r="A120" s="29">
+        <v>154</v>
+      </c>
+      <c r="B120" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="G118" s="28"/>
-    </row>
-    <row r="119" ht="15.75" hidden="1" spans="1:7">
-      <c r="A119" s="23">
-        <v>121</v>
-      </c>
-      <c r="B119" s="24" t="s">
+      <c r="C120" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E120" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="F120" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="C119" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E119" s="46"/>
-      <c r="F119" s="33" t="s">
+      <c r="G120" s="27"/>
+    </row>
+    <row r="121" ht="15.75" spans="1:7">
+      <c r="A121" s="23">
+        <v>139</v>
+      </c>
+      <c r="B121" s="27" t="s">
         <v>303</v>
       </c>
-      <c r="G119" s="28"/>
-    </row>
-    <row r="120" ht="15.75" hidden="1" spans="1:7">
-      <c r="A120" s="23">
-        <v>122</v>
-      </c>
-      <c r="B120" s="24" t="s">
+      <c r="C121" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E121" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="C120" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E120" s="46"/>
-      <c r="F120" s="33" t="s">
+      <c r="F121" s="26" t="s">
         <v>305</v>
       </c>
-      <c r="G120" s="47"/>
-    </row>
-    <row r="121" ht="15.75" hidden="1" spans="1:7">
-      <c r="A121" s="23">
-        <v>123</v>
-      </c>
-      <c r="B121" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C121" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E121" s="46"/>
-      <c r="F121" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="G121" s="28"/>
+      <c r="G121" s="27"/>
     </row>
     <row r="122" ht="15.75" hidden="1" spans="1:7">
       <c r="A122" s="23">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="B122" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="C122" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="54"/>
+      <c r="F122" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="G122" s="27" t="s">
         <v>308</v>
       </c>
-      <c r="C122" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D122" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E122" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="33" t="s">
+    </row>
+    <row r="123" ht="15.75" hidden="1" spans="1:7">
+      <c r="A123" s="23">
+        <v>61</v>
+      </c>
+      <c r="B123" s="24" t="s">
         <v>309</v>
       </c>
-      <c r="G122" s="28"/>
-    </row>
-    <row r="123" ht="31.5" hidden="1" spans="1:7">
-      <c r="A123" s="23">
-        <v>125</v>
-      </c>
-      <c r="B123" s="24" t="s">
+      <c r="C123" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="56"/>
+      <c r="F123" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="C123" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="45" t="s">
+      <c r="G123" s="57" t="s">
         <v>311</v>
       </c>
-      <c r="E123" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="F123" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="G123" s="28"/>
     </row>
     <row r="124" ht="15.75" hidden="1" spans="1:7">
       <c r="A124" s="23">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="B124" s="24" t="s">
+        <v>312</v>
+      </c>
+      <c r="C124" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="48"/>
+      <c r="F124" s="58" t="s">
         <v>313</v>
       </c>
-      <c r="C124" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D124" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E124" s="46"/>
-      <c r="F124" s="33" t="s">
+      <c r="G124" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="G124" s="28"/>
     </row>
     <row r="125" ht="15.75" hidden="1" spans="1:7">
       <c r="A125" s="23">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="B125" s="24" t="s">
         <v>315</v>
@@ -5341,925 +5481,848 @@
       <c r="C125" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="45" t="s">
+      <c r="D125" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E125" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="F125" s="33" t="s">
+      <c r="E125" s="29"/>
+      <c r="F125" s="26" t="s">
         <v>316</v>
       </c>
-      <c r="G125" s="28"/>
+      <c r="G125" s="27" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="126" ht="15.75" hidden="1" spans="1:7">
       <c r="A126" s="23">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="B126" s="24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C126" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D126" s="45" t="s">
+      <c r="D126" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E126" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="F126" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="G126" s="28"/>
+      <c r="E126" s="32"/>
+      <c r="F126" s="59" t="s">
+        <v>319</v>
+      </c>
+      <c r="G126" s="27" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="127" ht="15.75" hidden="1" spans="1:7">
       <c r="A127" s="23">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="B127" s="24" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C127" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D127" s="45" t="s">
+      <c r="D127" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E127" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F127" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="G127" s="58" t="s">
-        <v>321</v>
+      <c r="E127" s="29"/>
+      <c r="F127" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="G127" s="72" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="128" ht="15.75" hidden="1" spans="1:7">
       <c r="A128" s="23">
-        <v>130</v>
+        <v>69</v>
       </c>
       <c r="B128" s="24" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C128" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D128" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E128" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F128" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="G128" s="60" t="s">
-        <v>324</v>
+      <c r="D128" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="60"/>
+      <c r="F128" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="G128" s="75" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="129" ht="15.75" hidden="1" spans="1:7">
       <c r="A129" s="23">
-        <v>131</v>
-      </c>
-      <c r="B129" s="18" t="s">
-        <v>325</v>
+        <v>70</v>
+      </c>
+      <c r="B129" s="49" t="s">
+        <v>327</v>
       </c>
       <c r="C129" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D129" s="17" t="s">
+      <c r="D129" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="E129" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F129" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="G129" s="60" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" hidden="1" spans="1:7">
+      <c r="E129" s="60"/>
+      <c r="F129" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="G129" s="75" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="130" ht="31.5" hidden="1" spans="1:7">
       <c r="A130" s="23">
-        <v>132</v>
-      </c>
-      <c r="B130" s="18" t="s">
-        <v>328</v>
+        <v>71</v>
+      </c>
+      <c r="B130" s="49" t="s">
+        <v>330</v>
       </c>
       <c r="C130" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D130" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E130" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F130" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G130" s="60" t="s">
-        <v>330</v>
+      <c r="D130" s="62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" s="60"/>
+      <c r="F130" s="58" t="s">
+        <v>331</v>
+      </c>
+      <c r="G130" s="75" t="s">
+        <v>332</v>
       </c>
     </row>
     <row r="131" ht="15.75" hidden="1" spans="1:7">
       <c r="A131" s="23">
-        <v>133</v>
-      </c>
-      <c r="B131" s="18" t="s">
-        <v>306</v>
+        <v>72</v>
+      </c>
+      <c r="B131" s="49" t="s">
+        <v>333</v>
       </c>
       <c r="C131" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D131" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E131" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F131" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="G131" s="60" t="s">
-        <v>331</v>
+      <c r="D131" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="60"/>
+      <c r="F131" s="35" t="s">
+        <v>334</v>
+      </c>
+      <c r="G131" s="75" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="132" ht="15.75" hidden="1" spans="1:7">
       <c r="A132" s="23">
-        <v>134</v>
-      </c>
-      <c r="B132" s="18" t="s">
-        <v>332</v>
+        <v>74</v>
+      </c>
+      <c r="B132" s="49" t="s">
+        <v>336</v>
       </c>
       <c r="C132" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D132" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="E132" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F132" s="33" t="s">
-        <v>333</v>
+      <c r="D132" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="60"/>
+      <c r="F132" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="G132" s="63" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="133" ht="15.75" hidden="1" spans="1:7">
       <c r="A133" s="23">
-        <v>135</v>
-      </c>
-      <c r="B133" s="18" t="s">
-        <v>334</v>
+        <v>76</v>
+      </c>
+      <c r="B133" s="49" t="s">
+        <v>339</v>
       </c>
       <c r="C133" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D133" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E133" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F133" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="G133" s="48" t="s">
-        <v>336</v>
+      <c r="D133" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="60"/>
+      <c r="F133" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="G133" s="75" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="134" ht="15.75" hidden="1" spans="1:7">
       <c r="A134" s="23">
-        <v>136</v>
-      </c>
-      <c r="B134" s="18" t="s">
-        <v>337</v>
+        <v>78</v>
+      </c>
+      <c r="B134" s="49" t="s">
+        <v>342</v>
       </c>
       <c r="C134" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D134" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E134" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F134" s="33" t="s">
-        <v>338</v>
-      </c>
-      <c r="G134" s="60" t="s">
-        <v>339</v>
-      </c>
+      <c r="D134" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="60"/>
+      <c r="F134" s="26" t="s">
+        <v>343</v>
+      </c>
+      <c r="G134" s="63"/>
     </row>
     <row r="135" ht="15.75" hidden="1" spans="1:7">
       <c r="A135" s="23">
-        <v>137</v>
-      </c>
-      <c r="B135" s="18" t="s">
-        <v>340</v>
+        <v>82</v>
+      </c>
+      <c r="B135" s="49" t="s">
+        <v>344</v>
       </c>
       <c r="C135" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D135" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E135" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F135" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="G135" s="60" t="s">
-        <v>342</v>
+      <c r="D135" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="60"/>
+      <c r="F135" s="31" t="s">
+        <v>345</v>
+      </c>
+      <c r="G135" s="63" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="136" ht="15.75" hidden="1" spans="1:7">
       <c r="A136" s="23">
-        <v>138</v>
-      </c>
-      <c r="B136" s="24"/>
+        <v>84</v>
+      </c>
+      <c r="B136" s="24" t="s">
+        <v>347</v>
+      </c>
       <c r="C136" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D136" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E136" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F136" s="33" t="s">
-        <v>343</v>
-      </c>
-      <c r="G136" s="60" t="s">
-        <v>344</v>
-      </c>
+      <c r="D136" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="64"/>
+      <c r="F136" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="G136" s="63"/>
     </row>
     <row r="137" ht="15.75" hidden="1" spans="1:7">
       <c r="A137" s="23">
-        <v>139</v>
-      </c>
-      <c r="B137" s="18" t="s">
-        <v>345</v>
+        <v>86</v>
+      </c>
+      <c r="B137" s="49" t="s">
+        <v>349</v>
       </c>
       <c r="C137" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D137" s="17" t="s">
+      <c r="D137" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="E137" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="F137" s="33" t="s">
-        <v>347</v>
-      </c>
+      <c r="E137" s="64"/>
+      <c r="F137" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="G137" s="63"/>
     </row>
     <row r="138" ht="15.75" hidden="1" spans="1:7">
       <c r="A138" s="23">
-        <v>140</v>
-      </c>
-      <c r="B138" s="18" t="s">
-        <v>348</v>
+        <v>87</v>
+      </c>
+      <c r="B138" s="49" t="s">
+        <v>351</v>
       </c>
       <c r="C138" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D138" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E138" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F138" s="33" t="s">
-        <v>349</v>
-      </c>
-      <c r="G138" s="61" t="s">
-        <v>350</v>
+      <c r="D138" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="64"/>
+      <c r="F138" s="26" t="s">
+        <v>352</v>
+      </c>
+      <c r="G138" s="63" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="139" ht="15.75" hidden="1" spans="1:7">
       <c r="A139" s="23">
-        <v>141</v>
-      </c>
-      <c r="B139" s="18" t="s">
-        <v>351</v>
+        <v>88</v>
+      </c>
+      <c r="B139" s="49" t="s">
+        <v>354</v>
       </c>
       <c r="C139" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D139" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="E139" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="F139" s="33" t="s">
-        <v>352</v>
+      <c r="D139" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="65"/>
+      <c r="F139" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="G139" s="63" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="140" ht="15.75" hidden="1" spans="1:7">
       <c r="A140" s="23">
-        <v>142</v>
-      </c>
-      <c r="B140" s="18" t="s">
-        <v>353</v>
+        <v>89</v>
+      </c>
+      <c r="B140" s="49" t="s">
+        <v>357</v>
       </c>
       <c r="C140" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D140" s="17" t="s">
+      <c r="D140" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="E140" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="F140" s="33" t="s">
-        <v>354</v>
+      <c r="E140" s="60"/>
+      <c r="F140" s="26" t="s">
+        <v>358</v>
+      </c>
+      <c r="G140" s="75" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="141" ht="15.75" hidden="1" spans="1:7">
       <c r="A141" s="23">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="B141" s="24" t="s">
-        <v>191</v>
+        <v>360</v>
       </c>
       <c r="C141" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E141" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F141" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="G141" s="26" t="s">
-        <v>193</v>
+        <v>9</v>
+      </c>
+      <c r="E141" s="23"/>
+      <c r="F141" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="G141" s="71" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="142" ht="15.75" hidden="1" spans="1:7">
       <c r="A142" s="23">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="B142" s="24" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C142" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D142" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E142" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F142" s="33" t="s">
-        <v>356</v>
+      <c r="D142" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" s="23"/>
+      <c r="F142" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="G142" s="63" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="143" ht="15.75" hidden="1" spans="1:7">
       <c r="A143" s="23">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="B143" s="24" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C143" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D143" s="32" t="s">
+      <c r="D143" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E143" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F143" s="33" t="s">
-        <v>358</v>
+      <c r="E143" s="23"/>
+      <c r="F143" s="26" t="s">
+        <v>367</v>
+      </c>
+      <c r="G143" s="63" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="144" ht="19" hidden="1" customHeight="1" spans="1:7">
       <c r="A144" s="23">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="B144" s="24" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C144" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D144" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E144" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F144" s="33" t="s">
-        <v>360</v>
-      </c>
-      <c r="G144" s="26" t="s">
-        <v>361</v>
-      </c>
+      <c r="D144" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" s="23"/>
+      <c r="F144" s="26"/>
+      <c r="G144" s="27"/>
     </row>
     <row r="145" ht="15.75" hidden="1" spans="1:7">
       <c r="A145" s="23">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="B145" s="24" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C145" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D145" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E145" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F145" s="33" t="s">
-        <v>363</v>
-      </c>
-      <c r="G145" s="26"/>
+      <c r="D145" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145" s="32"/>
+      <c r="F145" s="35" t="s">
+        <v>371</v>
+      </c>
+      <c r="G145" s="27" t="s">
+        <v>372</v>
+      </c>
     </row>
     <row r="146" ht="15.75" hidden="1" spans="1:7">
       <c r="A146" s="23">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="B146" s="24" t="s">
-        <v>298</v>
+        <v>373</v>
       </c>
       <c r="C146" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D146" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E146" s="32"/>
-      <c r="F146" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="G146" s="62" t="s">
-        <v>364</v>
-      </c>
+      <c r="D146" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" s="29"/>
+      <c r="F146" s="35" t="s">
+        <v>374</v>
+      </c>
+      <c r="G146" s="63"/>
     </row>
     <row r="147" ht="15.75" hidden="1" spans="1:7">
       <c r="A147" s="23">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="B147" s="24" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C147" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D147" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E147" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F147" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="G147" s="59" t="s">
-        <v>367</v>
+      <c r="D147" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="32"/>
+      <c r="F147" s="26" t="s">
+        <v>376</v>
+      </c>
+      <c r="G147" s="27" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="148" ht="15.75" hidden="1" spans="1:7">
       <c r="A148" s="23">
-        <v>149</v>
-      </c>
-      <c r="B148" s="51" t="s">
-        <v>368</v>
+        <v>104</v>
+      </c>
+      <c r="B148" s="24" t="s">
+        <v>378</v>
       </c>
       <c r="C148" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D148" s="32" t="s">
+      <c r="D148" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E148" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F148" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="G148" s="26"/>
+      <c r="E148" s="32"/>
+      <c r="F148" s="26" t="s">
+        <v>379</v>
+      </c>
+      <c r="G148" s="27" t="s">
+        <v>380</v>
+      </c>
     </row>
     <row r="149" ht="15.75" hidden="1" spans="1:7">
       <c r="A149" s="23">
-        <v>150</v>
-      </c>
-      <c r="B149" s="52" t="s">
-        <v>370</v>
+        <v>107</v>
+      </c>
+      <c r="B149" s="66" t="s">
+        <v>381</v>
       </c>
       <c r="C149" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D149" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E149" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F149" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="G149" s="53"/>
+      <c r="D149" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" s="52"/>
+      <c r="F149" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="G149" s="67"/>
     </row>
     <row r="150" ht="15.75" hidden="1" spans="1:7">
-      <c r="A150" s="32">
+      <c r="A150" s="23">
+        <v>108</v>
+      </c>
+      <c r="B150" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="C150" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="52"/>
+      <c r="F150" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="G150" s="67"/>
+    </row>
+    <row r="151" ht="15.75" hidden="1" spans="1:7">
+      <c r="A151" s="23">
+        <v>109</v>
+      </c>
+      <c r="B151" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="C151" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="52"/>
+      <c r="F151" s="68" t="s">
+        <v>386</v>
+      </c>
+      <c r="G151" s="28"/>
+    </row>
+    <row r="152" ht="15.75" hidden="1" spans="1:7">
+      <c r="A152" s="23">
+        <v>110</v>
+      </c>
+      <c r="B152" s="24" t="s">
+        <v>387</v>
+      </c>
+      <c r="C152" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="52"/>
+      <c r="F152" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="G152" s="28"/>
+    </row>
+    <row r="153" ht="31.5" hidden="1" spans="1:7">
+      <c r="A153" s="23">
+        <v>111</v>
+      </c>
+      <c r="B153" s="24" t="s">
+        <v>389</v>
+      </c>
+      <c r="C153" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="52"/>
+      <c r="F153" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="G153" s="28"/>
+    </row>
+    <row r="154" ht="15.75" hidden="1" spans="1:7">
+      <c r="A154" s="23">
+        <v>112</v>
+      </c>
+      <c r="B154" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="C154" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="52"/>
+      <c r="F154" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="G154" s="28"/>
+    </row>
+    <row r="155" ht="15.75" hidden="1" spans="1:7">
+      <c r="A155" s="23">
+        <v>113</v>
+      </c>
+      <c r="B155" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="C155" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" s="52"/>
+      <c r="F155" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="G155" s="28"/>
+    </row>
+    <row r="156" ht="15.75" hidden="1" spans="1:7">
+      <c r="A156" s="23">
+        <v>114</v>
+      </c>
+      <c r="B156" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="C156" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="52"/>
+      <c r="F156" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="G156" s="28"/>
+    </row>
+    <row r="157" ht="15.75" hidden="1" spans="1:7">
+      <c r="A157" s="23">
+        <v>116</v>
+      </c>
+      <c r="B157" s="24" t="s">
+        <v>396</v>
+      </c>
+      <c r="C157" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="52"/>
+      <c r="F157" s="26" t="s">
+        <v>397</v>
+      </c>
+      <c r="G157" s="28"/>
+    </row>
+    <row r="158" ht="15.75" hidden="1" spans="1:7">
+      <c r="A158" s="23">
+        <v>117</v>
+      </c>
+      <c r="B158" s="24"/>
+      <c r="C158" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="52"/>
+      <c r="F158" s="26" t="s">
+        <v>398</v>
+      </c>
+      <c r="G158" s="28"/>
+    </row>
+    <row r="159" ht="15.75" hidden="1" spans="1:7">
+      <c r="A159" s="23">
+        <v>118</v>
+      </c>
+      <c r="B159" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="C159" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" s="52"/>
+      <c r="F159" s="51" t="s">
+        <v>400</v>
+      </c>
+      <c r="G159" s="28"/>
+    </row>
+    <row r="160" ht="15.75" hidden="1" spans="1:7">
+      <c r="A160" s="23">
+        <v>119</v>
+      </c>
+      <c r="B160" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="C160" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" s="52"/>
+      <c r="F160" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="G160" s="28"/>
+    </row>
+    <row r="161" ht="15.75" hidden="1" spans="1:7">
+      <c r="A161" s="23">
+        <v>120</v>
+      </c>
+      <c r="B161" s="24" t="s">
+        <v>403</v>
+      </c>
+      <c r="C161" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" s="52"/>
+      <c r="F161" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="G161" s="28"/>
+    </row>
+    <row r="162" ht="15.75" hidden="1" spans="1:7">
+      <c r="A162" s="23">
+        <v>121</v>
+      </c>
+      <c r="B162" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="C162" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" s="52"/>
+      <c r="F162" s="26" t="s">
+        <v>406</v>
+      </c>
+      <c r="G162" s="28"/>
+    </row>
+    <row r="163" ht="15.75" hidden="1" spans="1:7">
+      <c r="A163" s="23">
+        <v>122</v>
+      </c>
+      <c r="B163" s="24" t="s">
+        <v>407</v>
+      </c>
+      <c r="C163" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" s="52"/>
+      <c r="F163" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="G163" s="69"/>
+    </row>
+    <row r="164" s="16" customFormat="1" ht="15.75" hidden="1" spans="1:7">
+      <c r="A164" s="23">
+        <v>123</v>
+      </c>
+      <c r="B164" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C164" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" s="52"/>
+      <c r="F164" s="51" t="s">
+        <v>73</v>
+      </c>
+      <c r="G164" s="28"/>
+    </row>
+    <row r="165" ht="15.75" hidden="1" spans="1:7">
+      <c r="A165" s="23">
+        <v>126</v>
+      </c>
+      <c r="B165" s="24" t="s">
+        <v>409</v>
+      </c>
+      <c r="C165" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" s="52"/>
+      <c r="F165" s="26" t="s">
+        <v>410</v>
+      </c>
+      <c r="G165" s="28"/>
+    </row>
+    <row r="166" ht="15.75" hidden="1" spans="1:7">
+      <c r="A166" s="23">
+        <v>147</v>
+      </c>
+      <c r="B166" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="C166" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E166" s="29"/>
+      <c r="F166" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="G166" s="76" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" hidden="1" spans="1:7">
+      <c r="A167" s="29">
         <v>151</v>
       </c>
-      <c r="B150" s="51" t="s">
-        <v>372</v>
-      </c>
-      <c r="C150" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E150" s="32"/>
-      <c r="F150" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="G150" s="53"/>
-    </row>
-    <row r="151" ht="15.75" hidden="1" spans="1:7">
-      <c r="A151" s="32">
-        <v>152</v>
-      </c>
-      <c r="B151" s="51" t="s">
-        <v>374</v>
-      </c>
-      <c r="C151" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E151" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F151" s="54" t="s">
-        <v>375</v>
-      </c>
-      <c r="G151" s="26"/>
-    </row>
-    <row r="152" ht="15.75" hidden="1" spans="1:7">
-      <c r="A152" s="32">
-        <v>153</v>
-      </c>
-      <c r="B152" s="26" t="s">
-        <v>376</v>
-      </c>
-      <c r="C152" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D152" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E152" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F152" s="25" t="s">
-        <v>377</v>
-      </c>
-      <c r="G152" s="26"/>
-    </row>
-    <row r="153" ht="15.75" hidden="1" spans="1:7">
-      <c r="A153" s="32">
-        <v>153</v>
-      </c>
-      <c r="B153" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="C153" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E153" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F153" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="G153" s="26"/>
-    </row>
-    <row r="154" ht="15.75" hidden="1" spans="1:7">
-      <c r="A154" s="32">
-        <v>154</v>
-      </c>
-      <c r="B154" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="C154" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D154" s="32" t="s">
+      <c r="B167" s="30" t="s">
+        <v>412</v>
+      </c>
+      <c r="C167" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E154" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F154" s="25" t="s">
-        <v>381</v>
-      </c>
-      <c r="G154" s="26"/>
-    </row>
-    <row r="155" ht="15.75" hidden="1" spans="1:7">
-      <c r="A155" s="32">
-        <v>155</v>
-      </c>
-      <c r="B155" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="C155" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D155" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F155" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="G155" s="26"/>
-    </row>
-    <row r="156" ht="15.75" hidden="1" spans="1:7">
-      <c r="A156" s="32">
-        <v>155</v>
-      </c>
-      <c r="B156" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="C156" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D156" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F156" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="G156" s="26"/>
-    </row>
-    <row r="157" ht="15.75" spans="1:7">
-      <c r="A157" s="32">
-        <v>156</v>
-      </c>
-      <c r="B157" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="C157" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D157" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E157" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F157" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="G157" s="26"/>
-    </row>
-    <row r="158" ht="15.75" hidden="1" spans="1:7">
-      <c r="A158" s="32">
-        <v>157</v>
-      </c>
-      <c r="B158" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="C158" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D158" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E158" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F158" s="25" t="s">
-        <v>387</v>
-      </c>
-      <c r="G158" s="26"/>
-    </row>
-    <row r="159" ht="15.75" hidden="1" spans="1:7">
-      <c r="A159" s="32">
-        <v>158</v>
-      </c>
-      <c r="B159" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="C159" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D159" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E159" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F159" s="55" t="s">
-        <v>389</v>
-      </c>
-      <c r="G159" s="59" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="160" ht="15.75" hidden="1" spans="1:7">
-      <c r="A160" s="32">
-        <v>159</v>
-      </c>
-      <c r="B160" s="28" t="s">
-        <v>391</v>
-      </c>
-      <c r="C160" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D160" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E160" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F160" s="55" t="s">
-        <v>392</v>
-      </c>
-      <c r="G160" s="26"/>
-    </row>
-    <row r="161" ht="15.75" hidden="1" spans="1:7">
-      <c r="A161" s="32">
-        <v>160</v>
-      </c>
-      <c r="B161" s="51" t="s">
-        <v>393</v>
-      </c>
-      <c r="C161" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E161" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F161" s="25" t="s">
-        <v>394</v>
-      </c>
-      <c r="G161" s="59" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="162" ht="15.75" hidden="1" spans="1:7">
-      <c r="A162" s="32">
-        <v>161</v>
-      </c>
-      <c r="B162" s="51" t="s">
-        <v>396</v>
-      </c>
-      <c r="C162" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D162" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E162" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F162" s="26"/>
-      <c r="G162" s="59" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="163" ht="15.75" hidden="1" spans="1:7">
-      <c r="A163" s="32">
-        <v>162</v>
-      </c>
-      <c r="B163" s="51" t="s">
-        <v>398</v>
-      </c>
-      <c r="C163" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D163" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E163" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F163" s="25" t="s">
-        <v>399</v>
-      </c>
-      <c r="G163" s="59" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="164" ht="15.75" hidden="1" spans="1:7">
-      <c r="A164" s="32">
-        <v>163</v>
-      </c>
-      <c r="B164" s="51" t="s">
-        <v>401</v>
-      </c>
-      <c r="C164" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D164" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E164" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="F164" s="25" t="s">
-        <v>402</v>
-      </c>
-      <c r="G164" s="59" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="165" s="16" customFormat="1" ht="15.75" hidden="1" spans="1:7">
-      <c r="A165" s="32">
-        <v>164</v>
-      </c>
-      <c r="B165" s="56" t="s">
-        <v>404</v>
-      </c>
-      <c r="C165" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D165" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E165" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F165" s="57" t="s">
-        <v>405</v>
-      </c>
-      <c r="G165" s="59" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="166" ht="15.75" hidden="1" spans="1:7">
-      <c r="A166" s="32">
-        <v>165</v>
-      </c>
-      <c r="B166" s="26" t="s">
-        <v>407</v>
-      </c>
-      <c r="C166" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D166" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F166" s="57" t="s">
-        <v>408</v>
-      </c>
-      <c r="G166" s="59" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="167" ht="15.75" spans="1:7">
-      <c r="A167" s="32">
-        <v>156</v>
-      </c>
-      <c r="B167" s="18" t="s">
-        <v>410</v>
-      </c>
-      <c r="C167" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D167" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E167" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F167" s="25" t="s">
-        <v>411</v>
-      </c>
+      <c r="E167" s="29"/>
+      <c r="F167" s="31" t="s">
+        <v>413</v>
+      </c>
+      <c r="G167" s="63"/>
     </row>
     <row r="168" spans="1:7">
       <c r="D168" s="18"/>
@@ -9243,85 +9306,84 @@
     <row r="1161" spans="4:4">
       <c r="D1161" s="18"/>
     </row>
-    <row r="1162" spans="4:4">
-      <c r="D1162" s="18"/>
-    </row>
-    <row r="1163" spans="4:4">
-      <c r="D1163" s="18"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G166" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G167" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
       <filters>
-        <filter val="LAID ABDELALI"/>
+        <filter val="Permanent"/>
+        <filter val="Permanente"/>
       </filters>
     </filterColumn>
+    <sortState ref="A2:G167">
+      <sortCondition ref="E1"/>
+    </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
-    <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
-    <hyperlink ref="F54" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
-    <hyperlink ref="F105" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
-    <hyperlink ref="F106" r:id="rId5" display="aliaissani97@gmail.com"/>
-    <hyperlink ref="F124" r:id="rId6" display="medzerdani@gmail.com"/>
-    <hyperlink ref="F121" r:id="rId7" display="turkibilal22@gmail.com"/>
-    <hyperlink ref="F120" r:id="rId8" display="sacihamza40@gmail.com"/>
-    <hyperlink ref="F119" r:id="rId9" display="Boba1620@hotmail.com"/>
-    <hyperlink ref="F95" r:id="rId10" display="khelifa-mir@outlook.fr"/>
-    <hyperlink ref="F76" r:id="rId11" display="fethi22miloua@gmail.com"/>
-    <hyperlink ref="F74" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
-    <hyperlink ref="F93" r:id="rId13" display="mehadjiameslem@gmail.com"/>
-    <hyperlink ref="F91" r:id="rId14" display="mekhalefleila@gmail.com"/>
-    <hyperlink ref="F90" r:id="rId15" display="khalidamet4@gmail.com"/>
-    <hyperlink ref="F118" r:id="rId16" display="layatimedi@gmail.com"/>
-    <hyperlink ref="F85" r:id="rId17" display="m_latreche@yahoo.com"/>
-    <hyperlink ref="F117" r:id="rId18" display="kadrirania51@gmail.com"/>
-    <hyperlink ref="F81" r:id="rId19" display="protoboy9999@gmail.com"/>
-    <hyperlink ref="F115" r:id="rId20" display="khadidjafezazi90@gmail"/>
-    <hyperlink ref="F75" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F72" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
-    <hyperlink ref="F67" r:id="rId23" display="douaaboularaf@gmail.com"/>
-    <hyperlink ref="F111" r:id="rId24" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F109" r:id="rId25" display="bkbhbb22@gmail.com"/>
-    <hyperlink ref="F59" r:id="rId26" display="bendida65@gmail.com"/>
-    <hyperlink ref="F58" r:id="rId27" display="sarrabencella@gmail.com"/>
-    <hyperlink ref="F60" r:id="rId28" display="ri123hab@gmail.com"/>
-    <hyperlink ref="F108" r:id="rId29" display="meriembelabed5@gmail.com"/>
-    <hyperlink ref="F45" r:id="rId30" display="rezoug.med@gmail.com"/>
-    <hyperlink ref="F84" r:id="rId31" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
-    <hyperlink ref="F57" r:id="rId32" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
-    <hyperlink ref="F100" r:id="rId33" display="zarebmohammedamine@gmail.com"/>
-    <hyperlink ref="F101" r:id="rId34" display="djamel71ziani@gmail.com"/>
-    <hyperlink ref="F65" r:id="rId35" display="ahmedboudali32@gmail.com"/>
-    <hyperlink ref="F69" r:id="rId36" display="chaouche.abdallah@gmail.com"/>
-    <hyperlink ref="F61" r:id="rId37" display="lakhdar_belhallouche@hotmail.fr"/>
-    <hyperlink ref="F80" r:id="rId38" display="ahmed.hadji22@yahoo.com"/>
-    <hyperlink ref="F103" r:id="rId39" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F32" r:id="rId40" display="khatir.mohamed1977@gmail.com"/>
-    <hyperlink ref="F2" r:id="rId41" display="irecom_abid@yahoo.fr"/>
-    <hyperlink ref="F7" r:id="rId42" display="karis483@hotmail.fr"/>
-    <hyperlink ref="F8" r:id="rId43" display="bahlilmounir@yahoo.fr"/>
-    <hyperlink ref="F10" r:id="rId44" display="beddadboucif@gmail.com"/>
-    <hyperlink ref="F9" r:id="rId45" display="seyfeddine.electrotechnique@gmail.com"/>
-    <hyperlink ref="F127" r:id="rId46" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
-    <hyperlink ref="F112" r:id="rId47" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
-    <hyperlink ref="F141" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F142" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
-    <hyperlink ref="F143" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
-    <hyperlink ref="F144" r:id="rId50" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
-    <hyperlink ref="F147" r:id="rId51" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
-    <hyperlink ref="F150" r:id="rId52" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
-    <hyperlink ref="F151" r:id="rId53" display="walid.sebastien@gmail.com"/>
-    <hyperlink ref="F152" r:id="rId54" display="bensenadanadia3@gmail.com"/>
-    <hyperlink ref="F153" r:id="rId55" display="imedmedles@gmail.com"/>
-    <hyperlink ref="F157" r:id="rId56" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
-    <hyperlink ref="F159" r:id="rId57" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
-    <hyperlink ref="F160" r:id="rId58" display="rachid.hadjboulenouar@gamil.com"/>
-    <hyperlink ref="F161" r:id="rId59" display="moh@medbnr.com"/>
-    <hyperlink ref="F163" r:id="rId60" display="hadilyamoune@gmail.com"/>
-    <hyperlink ref="F164" r:id="rId61" display="megdz100@gmail.com"/>
-    <hyperlink ref="F165" r:id="rId62" display="didaouikaouthar331@gmail.com"/>
+    <hyperlink ref="F93" r:id="rId1" display="bentaallah65@yahoo.fr"/>
+    <hyperlink ref="F96" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
+    <hyperlink ref="F3" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
+    <hyperlink ref="F149" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
+    <hyperlink ref="F150" r:id="rId5" display="aliaissani97@gmail.com"/>
+    <hyperlink ref="F165" r:id="rId6" display="medzerdani@gmail.com"/>
+    <hyperlink ref="F164" r:id="rId7" display="turkibilal22@gmail.com"/>
+    <hyperlink ref="F163" r:id="rId8" display="sacihamza40@gmail.com"/>
+    <hyperlink ref="F162" r:id="rId9" display="Boba1620@hotmail.com"/>
+    <hyperlink ref="F44" r:id="rId10" display="khelifa-mir@outlook.fr"/>
+    <hyperlink ref="F134" r:id="rId11" display="fethi22miloua@gmail.com"/>
+    <hyperlink ref="F133" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
+    <hyperlink ref="F143" r:id="rId13" display="mehadjiameslem@gmail.com"/>
+    <hyperlink ref="F142" r:id="rId14" display="mekhalefleila@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId15" display="khalidamet4@gmail.com"/>
+    <hyperlink ref="F161" r:id="rId16" display="layatimedi@gmail.com"/>
+    <hyperlink ref="F138" r:id="rId17" display="m_latreche@yahoo.com"/>
+    <hyperlink ref="F160" r:id="rId18" display="kadrirania51@gmail.com"/>
+    <hyperlink ref="F6" r:id="rId19" display="protoboy9999@gmail.com"/>
+    <hyperlink ref="F158" r:id="rId20" display="khadidjafezazi90@gmail"/>
+    <hyperlink ref="F4" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F132" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F128" r:id="rId23" display="douaaboularaf@gmail.com"/>
+    <hyperlink ref="F155" r:id="rId24" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F153" r:id="rId25" display="bkbhbb22@gmail.com"/>
+    <hyperlink ref="F12" r:id="rId26" display="bendida65@gmail.com"/>
+    <hyperlink ref="F40" r:id="rId27" display="sarrabencella@gmail.com"/>
+    <hyperlink ref="F123" r:id="rId28" display="ri123hab@gmail.com"/>
+    <hyperlink ref="F152" r:id="rId29" display="meriembelabed5@gmail.com"/>
+    <hyperlink ref="F108" r:id="rId30" display="rezoug.med@gmail.com"/>
+    <hyperlink ref="F137" r:id="rId31" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
+    <hyperlink ref="F39" r:id="rId32" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
+    <hyperlink ref="F147" r:id="rId33" display="zarebmohammedamine@gmail.com"/>
+    <hyperlink ref="F20" r:id="rId34" display="djamel71ziani@gmail.com"/>
+    <hyperlink ref="F127" r:id="rId35" display="ahmedboudali32@gmail.com"/>
+    <hyperlink ref="F130" r:id="rId36" display="chaouche.abdallah@gmail.com"/>
+    <hyperlink ref="F124" r:id="rId37" display="lakhdar_belhallouche@hotmail.fr"/>
+    <hyperlink ref="F135" r:id="rId38" display="ahmed.hadji22@yahoo.com"/>
+    <hyperlink ref="F45" r:id="rId39" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F99" r:id="rId40" display="khatir.mohamed1977@gmail.com"/>
+    <hyperlink ref="F82" r:id="rId41" display="irecom_abid@yahoo.fr"/>
+    <hyperlink ref="F81" r:id="rId42" display="karis483@hotmail.fr"/>
+    <hyperlink ref="F87" r:id="rId43" display="bahlilmounir@yahoo.fr"/>
+    <hyperlink ref="F60" r:id="rId44" display="beddadboucif@gmail.com"/>
+    <hyperlink ref="F59" r:id="rId45" display="seyfeddine.electrotechnique@gmail.com"/>
+    <hyperlink ref="F116" r:id="rId46" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F156" r:id="rId47" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F7" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F117" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
+    <hyperlink ref="F118" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
+    <hyperlink ref="F29" r:id="rId50" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
+    <hyperlink ref="F30" r:id="rId51" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
+    <hyperlink ref="F167" r:id="rId52" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
+    <hyperlink ref="F49" r:id="rId53" display="walid.sebastien@gmail.com"/>
+    <hyperlink ref="F50" r:id="rId54" display="bensenadanadia3@gmail.com"/>
+    <hyperlink ref="F51" r:id="rId55" display="imedmedles@gmail.com"/>
+    <hyperlink ref="F31" r:id="rId56" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
+    <hyperlink ref="F53" r:id="rId57" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
+    <hyperlink ref="F54" r:id="rId58" display="moh@medbnr.com"/>
+    <hyperlink ref="F56" r:id="rId59" display="hadilyamoune@gmail.com"/>
+    <hyperlink ref="F8" r:id="rId60" display="megdz100@gmail.com"/>
+    <hyperlink ref="F58" r:id="rId61" display="ikkachenarimen.2017@gmail.com"/>
+    <hyperlink ref="F32" r:id="rId62" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
+    <hyperlink ref="F57" r:id="rId63" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -9344,202 +9406,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>424</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>424</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -55,15 +55,723 @@
     <t>N°/TEL</t>
   </si>
   <si>
+    <t>ABID MOHAMED</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>Pr</t>
+  </si>
+  <si>
+    <t>irecom_abid@yahoo.fr</t>
+  </si>
+  <si>
+    <t>AKSA WESSIM</t>
+  </si>
+  <si>
+    <t>aksa86wessim@gmail.com</t>
+  </si>
+  <si>
+    <t>ARDJOUN SID AHMED</t>
+  </si>
+  <si>
+    <t>ardjoun.s.e.m@gmail.com</t>
+  </si>
+  <si>
+    <t>AYAD ABDELGHANI</t>
+  </si>
+  <si>
+    <t>ayad_abdelghani@yahoo.fr</t>
+  </si>
+  <si>
+    <t>AZAIZ AHMED</t>
+  </si>
+  <si>
+    <t>ahazaiz2011@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BADIS KARIMA</t>
+  </si>
+  <si>
+    <t>Permanente</t>
+  </si>
+  <si>
+    <t>MCB</t>
+  </si>
+  <si>
+    <t>karis483@hotmail.fr</t>
+  </si>
+  <si>
+    <t>0560337902</t>
+  </si>
+  <si>
+    <t>BAHLIL MOUNIR</t>
+  </si>
+  <si>
+    <t>bahlilmounir@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0672447184</t>
+  </si>
+  <si>
+    <t>BECHEKIR SEYFEDDINE</t>
+  </si>
+  <si>
+    <t>MCA</t>
+  </si>
+  <si>
+    <t>seyfeddine.electrotechnique@gmail.com</t>
+  </si>
+  <si>
+    <t>BEDDAD BOUCIF</t>
+  </si>
+  <si>
+    <t>beddadboucif@gmail.com</t>
+  </si>
+  <si>
+    <t>0665458282</t>
+  </si>
+  <si>
+    <t>BELLEBNA YASSINE</t>
+  </si>
+  <si>
+    <t>fgevdpg@gmail.com</t>
+  </si>
+  <si>
+    <t>BENAISSA ABDELKADER</t>
+  </si>
+  <si>
+    <t>aek_benaissa@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BERRAHAL BEL ABBES</t>
+  </si>
+  <si>
+    <t>dept.eln@gmail.com</t>
+  </si>
+  <si>
+    <t>BENBELLIL NADJAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nn.nn.phy.chi@gmail.com </t>
+  </si>
+  <si>
+    <t>BENDAOUD ABDELBER</t>
+  </si>
+  <si>
+    <t>babdelber22@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BENDIMERAD SALAH EDDINE</t>
+  </si>
+  <si>
+    <t>s_bendimerad@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BENGRIT MALIKA</t>
+  </si>
+  <si>
+    <t>MAA</t>
+  </si>
+  <si>
+    <t>malikabengrit@gmail.com</t>
+  </si>
+  <si>
+    <t>BENHAMIDA FARID</t>
+  </si>
+  <si>
+    <t>farid.benhamida@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BENKHALOUK KADDOUR</t>
+  </si>
+  <si>
+    <t>benkh_ka@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BENTAALLAH ABDERRAHIM</t>
+  </si>
+  <si>
+    <t>bentaallah65@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BERMAKI HAMZA</t>
+  </si>
+  <si>
+    <t>bermaki.hamza@gmail.com</t>
+  </si>
+  <si>
+    <t>BOUKHOULDA FODIL</t>
+  </si>
+  <si>
+    <t>boukhoulda.fodil@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SEMMACHE HOURIA</t>
+  </si>
+  <si>
+    <t>hsemmach@yahoo.fr</t>
+  </si>
+  <si>
+    <t>DJERIRI YOUCEF</t>
+  </si>
+  <si>
+    <t>djeriri_youcef@yahoo.fr</t>
+  </si>
+  <si>
+    <t>DRIEF FAIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drieff4@gmail.com </t>
+  </si>
+  <si>
+    <t>FELLAH MOHAMMED KARIM</t>
+  </si>
+  <si>
+    <t>mkfellah@gmail.com</t>
+  </si>
+  <si>
+    <t>GHAZEL FATIHA</t>
+  </si>
+  <si>
+    <t>nour73_fac@yahoo.fr</t>
+  </si>
+  <si>
+    <t>HADJERI SAMIR</t>
+  </si>
+  <si>
+    <t>shadjeri2@yahoo.fr</t>
+  </si>
+  <si>
+    <t>HANAFI SALAH</t>
+  </si>
+  <si>
+    <t>udl.fge.vdpg@gmail.com</t>
+  </si>
+  <si>
+    <t>HASSANI NAIMA</t>
+  </si>
+  <si>
+    <t>naimahassani69@yahoo.fr</t>
+  </si>
+  <si>
+    <t>JBILOU MOKHTARIA</t>
+  </si>
+  <si>
+    <t>harmel71@yahoo.fr</t>
+  </si>
+  <si>
+    <t>KHATIR MOHAMED</t>
+  </si>
+  <si>
+    <t>khatir.mohamed1977@gmail.com</t>
+  </si>
+  <si>
+    <t>LALEDJ NADJET</t>
+  </si>
+  <si>
+    <t>nadjet_69@hotmail.fr</t>
+  </si>
+  <si>
+    <t>MAAMMAR MOHAMED</t>
+  </si>
+  <si>
+    <t>mohamed.maammar@gmail.com</t>
+  </si>
+  <si>
+    <t>MASSOUM AHMED</t>
+  </si>
+  <si>
+    <t>ahmassoum@yahoo.fr</t>
+  </si>
+  <si>
+    <t>MILOUA FARID</t>
+  </si>
+  <si>
+    <t>milouafarid@gmail.com</t>
+  </si>
+  <si>
+    <t>0657011874</t>
+  </si>
+  <si>
+    <t>MILOUDI HOUCINE</t>
+  </si>
+  <si>
+    <t>el.houcine@yahoo.fr</t>
+  </si>
+  <si>
+    <t>MIMOUNI CHAHINEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mimounichahinez@gmail.com </t>
+  </si>
+  <si>
+    <t>0558193860</t>
+  </si>
+  <si>
+    <t>BRAHAMI MOHAMED NADJIB</t>
+  </si>
+  <si>
+    <t>nadjbrahami@gmail.com</t>
+  </si>
+  <si>
+    <t>NACERI ABDELLATIF</t>
+  </si>
+  <si>
+    <t>abdnaceri@yahoo.fr</t>
+  </si>
+  <si>
+    <t>NASSOUR KAMEL</t>
+  </si>
+  <si>
+    <t>nass_ka@yahoo.fr</t>
+  </si>
+  <si>
+    <t>NEMMICH SAID</t>
+  </si>
+  <si>
+    <t>nemmichsaid@gmail.com</t>
+  </si>
+  <si>
+    <t>OUKLI MIMOUNA</t>
+  </si>
+  <si>
+    <t>mounaoukli@yahoo.fr</t>
+  </si>
+  <si>
+    <t>RAMI ABDELKADER</t>
+  </si>
+  <si>
+    <t>abc_rim20052003@yahoo.fr</t>
+  </si>
+  <si>
+    <t>REZOUG MOHAMMED</t>
+  </si>
+  <si>
+    <t>rezoug.med@gmail.com</t>
+  </si>
+  <si>
+    <t>SAHALI YAMINA</t>
+  </si>
+  <si>
+    <t>ya_sahali@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SEMMAH ABDELHAFID</t>
+  </si>
+  <si>
+    <t>hafid.semmah@yahoo.fr</t>
+  </si>
+  <si>
+    <t>TABET DERRAZ HIND</t>
+  </si>
+  <si>
+    <t>htabet05@yahoo.fr</t>
+  </si>
+  <si>
+    <t>TILMATINE AMAR</t>
+  </si>
+  <si>
+    <t>atilmatine@gmail.com</t>
+  </si>
+  <si>
+    <t>TOUHAMI SEDDIK</t>
+  </si>
+  <si>
+    <t>seddik.touhami@gmail.com</t>
+  </si>
+  <si>
+    <t>ZEBLAH ABDELKADER</t>
+  </si>
+  <si>
+    <t>azeblah@yahoo.fr</t>
+  </si>
+  <si>
+    <t>ZENASNI MERIEM</t>
+  </si>
+  <si>
+    <t>zenasnimeriem29@gmail.com</t>
+  </si>
+  <si>
+    <t>0552037098</t>
+  </si>
+  <si>
+    <t>ZIDI SID AHMED</t>
+  </si>
+  <si>
+    <t>sbzidi@yahoo.fr</t>
+  </si>
+  <si>
+    <t>ABBAS MOHAMED</t>
+  </si>
+  <si>
+    <t>Vacataire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctorant (Master) </t>
+  </si>
+  <si>
+    <t>abbasmohammed.com@gmail.com</t>
+  </si>
+  <si>
+    <t>0696562379</t>
+  </si>
+  <si>
+    <t>ABDELI MAMA</t>
+  </si>
+  <si>
+    <t>abdelli.mama@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 52 96 89 21 </t>
+  </si>
+  <si>
+    <t>ARAB ABDELMADJID</t>
+  </si>
+  <si>
+    <t>Doctorat</t>
+  </si>
+  <si>
+    <t>arab4abdelmadjid@gmail.com</t>
+  </si>
+  <si>
+    <t>06 57 28 84 81</t>
+  </si>
+  <si>
+    <t>AREZKI MOUFOK</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>Mouffok.arezki22@gmail.com </t>
+  </si>
+  <si>
+    <t>06 97 05 81 64</t>
+  </si>
+  <si>
+    <t>BENCELLA SARRA</t>
+  </si>
+  <si>
+    <t>sarrabencella@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 94 25 37 34 </t>
+  </si>
+  <si>
+    <t>BENDIDA MOHAMED</t>
+  </si>
+  <si>
+    <t>bendida65@gmail.com</t>
+  </si>
+  <si>
+    <t>05 50 59 52 24</t>
+  </si>
+  <si>
+    <t>BELHABRI RIHAB</t>
+  </si>
+  <si>
+    <t>ri123hab@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 54 40 75 58 </t>
+  </si>
+  <si>
+    <t>BELHALLOUCHE LAKHDAR</t>
+  </si>
+  <si>
+    <t>lakhdar_belhallouche@hotmail.fr</t>
+  </si>
+  <si>
+    <t>06 96 0582 37</t>
+  </si>
+  <si>
+    <t>BENSALEM Mohammed Mustapha</t>
+  </si>
+  <si>
+    <t>bensalem.moh.mus@gmail.com</t>
+  </si>
+  <si>
+    <t>0550114832</t>
+  </si>
+  <si>
+    <t>BETTACHE ABDERRAHMANE</t>
+  </si>
+  <si>
+    <t>abderrahmanbettache@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">066939 21 49 </t>
+  </si>
+  <si>
+    <t>BOUBEKEUR HALIMA</t>
+  </si>
+  <si>
+    <t>boubekeur97sba@gmail.com</t>
+  </si>
+  <si>
+    <t>06 74 50 65 01</t>
+  </si>
+  <si>
+    <t>BOUDALI AHMED</t>
+  </si>
+  <si>
+    <t>ahmedboudali32@gmail.com</t>
+  </si>
+  <si>
+    <t>0656855101</t>
+  </si>
+  <si>
+    <t>BOUKHARI SOUMIA</t>
+  </si>
+  <si>
+    <t>boukharisoumiafarah@gmail.com</t>
+  </si>
+  <si>
+    <t>06 96 05 82 37</t>
+  </si>
+  <si>
+    <t>BOULARAF AICHA</t>
+  </si>
+  <si>
+    <t>douaaboularaf@gmail.com</t>
+  </si>
+  <si>
+    <t>0799747080</t>
+  </si>
+  <si>
+    <t>BOURAHLA CHAHRAZED</t>
+  </si>
+  <si>
+    <t>bourahla.phys@gmail.com</t>
+  </si>
+  <si>
+    <t>0781893264</t>
+  </si>
+  <si>
+    <t>CHABANE CHAOUCHE ABDALLAH</t>
+  </si>
+  <si>
+    <t>chaouche.abdallah@gmail.com</t>
+  </si>
+  <si>
+    <t>0664457108</t>
+  </si>
+  <si>
+    <t>DJELLOULI YOUNES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">djellouli08younes08@gmail.com </t>
+  </si>
+  <si>
+    <t>0673948096</t>
+  </si>
+  <si>
+    <t>DJEZIRI SOUMIA</t>
+  </si>
+  <si>
+    <t>somiadjeziri22@gmail.com</t>
+  </si>
+  <si>
+    <t>0540920164</t>
+  </si>
+  <si>
+    <t>DRICI LAMIA</t>
+  </si>
+  <si>
+    <t>Lamia_du22@hotmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 97 35 08 88 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DROUNI Wassila Abir </t>
+  </si>
+  <si>
+    <t>Wassila.drouni@gmail.com</t>
+  </si>
+  <si>
+    <t>05 51 24 38 19</t>
+  </si>
+  <si>
+    <t>El MESTARI WAHIBA</t>
+  </si>
+  <si>
+    <t>wahibaelmestarii@gmail.com</t>
+  </si>
+  <si>
+    <t>0556130770</t>
+  </si>
+  <si>
+    <t>ELGHODASSE ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>elghodasseabdelmadjid@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 77 21 68</t>
+  </si>
+  <si>
+    <t>MILOUA FETHI</t>
+  </si>
+  <si>
+    <t>fethi22miloua@gmail.com</t>
+  </si>
+  <si>
+    <t>GHALEM ABDELHAK</t>
+  </si>
+  <si>
+    <t>ghalem.abdelhak@yahoo.com</t>
+  </si>
+  <si>
+    <t>0675437370</t>
+  </si>
+  <si>
+    <t>HADER ABDERRAHMANE</t>
+  </si>
+  <si>
+    <t>aer.hader91@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 00 44 75</t>
+  </si>
+  <si>
+    <t>BENHARAT ABDELHADI</t>
+  </si>
+  <si>
+    <t>Hadi.bnh00@gmail.com</t>
+  </si>
+  <si>
+    <t>HADJI AHMED</t>
+  </si>
+  <si>
+    <t>ahmed.hadji22@yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 98 14 23 47 </t>
+  </si>
+  <si>
+    <t>HAMMAR MEHDI</t>
+  </si>
+  <si>
+    <t>protoboy9999@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 33 46 70 </t>
+  </si>
+  <si>
+    <t>HARMEL MOHAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmel.mohamed22@hotmail.com </t>
+  </si>
+  <si>
+    <t>KHELLAF KADDA</t>
+  </si>
+  <si>
+    <t>khellafkadda1234@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 65 72 17 23 </t>
+  </si>
+  <si>
+    <t>LAHCEN AZDDINE</t>
+  </si>
+  <si>
+    <t>azddinelahcene@gmail.com</t>
+  </si>
+  <si>
+    <t>LATRECHE MOKHTAR</t>
+  </si>
+  <si>
+    <t>m_latreche@yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 75 89 45 05 </t>
+  </si>
+  <si>
+    <t>LOUSDAD AYMEN</t>
+  </si>
+  <si>
+    <t>lousdadaymen.aziz@gmail.com</t>
+  </si>
+  <si>
+    <t>07 94 94 48 94</t>
+  </si>
+  <si>
+    <t>MAHIDDINE Abderrahim</t>
+  </si>
+  <si>
+    <t>ma2006ne_86@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0657058282</t>
+  </si>
+  <si>
+    <t>MAHKOUKA ZAZA</t>
+  </si>
+  <si>
+    <t>mahkouka.zaza@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0778 36 07 76 </t>
+  </si>
+  <si>
+    <t>MANSOURI ABDERRAZAK</t>
+  </si>
+  <si>
+    <t>abderazakmahdi22@gmail.com</t>
+  </si>
+  <si>
+    <t>0696417435</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>Doctorante (Master)</t>
+  </si>
+  <si>
+    <t>khalidamet4@gmail.com</t>
+  </si>
+  <si>
+    <t>0550651046</t>
+  </si>
+  <si>
+    <t>MEKHALEF SOUMIA</t>
+  </si>
+  <si>
+    <t>mekhalefleila@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 59 03 18 24 </t>
+  </si>
+  <si>
+    <t>MERADJAH IBRAHIM</t>
+  </si>
+  <si>
+    <t>ibrahimmeradjah72@gmail.com</t>
+  </si>
+  <si>
+    <t>0663114536</t>
+  </si>
+  <si>
+    <t>MESLEM MEHADJIA</t>
+  </si>
+  <si>
+    <t>mehadjiameslem@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 97 01 34 39 </t>
+  </si>
+  <si>
     <t>MOULAY MILOUD</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Vacataire</t>
-  </si>
-  <si>
     <t>Doctorant (Magister)</t>
   </si>
   <si>
@@ -73,43 +781,472 @@
     <t xml:space="preserve">05 42 85 61 91 </t>
   </si>
   <si>
-    <t>ABBAS MOHAMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doctorant (Master) </t>
-  </si>
-  <si>
-    <t>abbasmohammed.com@gmail.com</t>
-  </si>
-  <si>
-    <t>0696562379</t>
-  </si>
-  <si>
-    <t>ELGHODASSE ABDEL MADJID</t>
-  </si>
-  <si>
-    <t>elghodasseabdelmadjid@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 77 21 68</t>
-  </si>
-  <si>
-    <t>GHALEM ABDELHAK</t>
-  </si>
-  <si>
-    <t>ghalem.abdelhak@yahoo.com</t>
-  </si>
-  <si>
-    <t>0675437370</t>
-  </si>
-  <si>
-    <t>HAMMAR MEHDI</t>
-  </si>
-  <si>
-    <t>protoboy9999@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 33 46 70 </t>
+    <t>MIR KHELIFA</t>
+  </si>
+  <si>
+    <t>khelifa-mir@outlook.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 59 78 39 </t>
+  </si>
+  <si>
+    <t>MOKEDDEM AMINA</t>
+  </si>
+  <si>
+    <t>mokeddem.amina2222@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 56 42 87 15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non Défini </t>
+  </si>
+  <si>
+    <t>REDJALA MAJDA</t>
+  </si>
+  <si>
+    <t>majdaredjala1492@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 53 64 47 91 </t>
+  </si>
+  <si>
+    <t>SENOUCI HAYAT</t>
+  </si>
+  <si>
+    <t>senoucihayat11@gmail.com</t>
+  </si>
+  <si>
+    <t>ZAREB Mohammed Amine</t>
+  </si>
+  <si>
+    <t>zarebmohammedamine@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0674 68 05 35 </t>
+  </si>
+  <si>
+    <t>ZIANI DJAMEL</t>
+  </si>
+  <si>
+    <t>djamel71ziani@gmail.com</t>
+  </si>
+  <si>
+    <t>05 61 11 10 02</t>
+  </si>
+  <si>
+    <t>LARBI ZIDI</t>
+  </si>
+  <si>
+    <t>larbi.zidi6@gmail.com</t>
+  </si>
+  <si>
+    <t>07 92 12 03 38</t>
+  </si>
+  <si>
+    <t>BERROUNA HENEN</t>
+  </si>
+  <si>
+    <t>berhenen@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0671745806</t>
+  </si>
+  <si>
+    <t>MOUILAH  KHEIRA</t>
+  </si>
+  <si>
+    <t>Ingénieur</t>
+  </si>
+  <si>
+    <t>mouilahka4614@gmail.com</t>
+  </si>
+  <si>
+    <t>ABED ZOULIKHA</t>
+  </si>
+  <si>
+    <t>zoulikhaabed3@gmail.com</t>
+  </si>
+  <si>
+    <t>AISSANI ALI</t>
+  </si>
+  <si>
+    <t>aliaissani97@gmail.com</t>
+  </si>
+  <si>
+    <t>AZZA ROMAISSA FATIMA ZOHRA</t>
+  </si>
+  <si>
+    <t>azzafatimazohraromaissa.l3@gmail.com</t>
+  </si>
+  <si>
+    <t>BELABED MERIEM</t>
+  </si>
+  <si>
+    <t>meriembelabed5@gmail.com</t>
+  </si>
+  <si>
+    <t>BENKABOU MOHAMED EL HABIB</t>
+  </si>
+  <si>
+    <t>bkbhbb22@gmail.com</t>
+  </si>
+  <si>
+    <t>BENMASOUD LEILA</t>
+  </si>
+  <si>
+    <t>l.benmessaoud@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BERROUNA HANANE</t>
+  </si>
+  <si>
+    <t>CHIKHI NAWEL</t>
+  </si>
+  <si>
+    <t>chikhi_nawel75@yahoo.fr</t>
+  </si>
+  <si>
+    <t>DELLOUM AMIRA</t>
+  </si>
+  <si>
+    <t>amiradelloum28@gmail.com</t>
+  </si>
+  <si>
+    <t>FENTAZY BELKISSE</t>
+  </si>
+  <si>
+    <t>fantazibelkisse.13@gmail.com</t>
+  </si>
+  <si>
+    <t>khadidjafezazi90@gmail</t>
+  </si>
+  <si>
+    <t>KADA ZAIR IKRAM</t>
+  </si>
+  <si>
+    <t>ikram.kadazair@gmail.com</t>
+  </si>
+  <si>
+    <t>KADRI RANIA</t>
+  </si>
+  <si>
+    <t>kadrirania51@gmail.com</t>
+  </si>
+  <si>
+    <t>LAYATI TAYEB MEHDI</t>
+  </si>
+  <si>
+    <t>layatimedi@gmail.com</t>
+  </si>
+  <si>
+    <t>NEFAHA ABOUBAKR</t>
+  </si>
+  <si>
+    <t>Boba1620@hotmail.com</t>
+  </si>
+  <si>
+    <t>SACI HAMZA</t>
+  </si>
+  <si>
+    <t>sacihamza40@gmail.com</t>
+  </si>
+  <si>
+    <t>TURKI BILAL MEROUANE</t>
+  </si>
+  <si>
+    <t>turkibilal22@gmail.com</t>
+  </si>
+  <si>
+    <t>RAIS ABDELMAJID</t>
+  </si>
+  <si>
+    <t>amrais@yahoo.com</t>
+  </si>
+  <si>
+    <t>REGUIG ABDELDJALIL</t>
+  </si>
+  <si>
+    <t>Mise en disponibilité</t>
+  </si>
+  <si>
+    <t>abdeldjalil.reguig@outlook.com</t>
+  </si>
+  <si>
+    <t>ZERDANI MOHAMMED</t>
+  </si>
+  <si>
+    <t>medzerdani@gmail.com</t>
+  </si>
+  <si>
+    <t>KADA KLOUCHA OMAR</t>
+  </si>
+  <si>
+    <t>klomar05@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SAIDI KHAYREDDINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
+  </si>
+  <si>
+    <t>ABBOU MAJDA</t>
+  </si>
+  <si>
+    <t>milouaf@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0556831346</t>
+  </si>
+  <si>
+    <t>REGUIEG ZAKARIA</t>
+  </si>
+  <si>
+    <t>reguiegzakaria10@gmail.com</t>
+  </si>
+  <si>
+    <t>0792070651</t>
+  </si>
+  <si>
+    <t>SEMMAK ABDELKADER</t>
+  </si>
+  <si>
+    <t>semmak.abdelkader@outlook.com</t>
+  </si>
+  <si>
+    <t>0772111809</t>
+  </si>
+  <si>
+    <t>BENMESSAOUD LEYLA</t>
+  </si>
+  <si>
+    <t>l_benmessaoud@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0553714385</t>
+  </si>
+  <si>
+    <t>0655206865</t>
+  </si>
+  <si>
+    <t>OUARI KHEIRA</t>
+  </si>
+  <si>
+    <t>ouari_k@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SABOUNDJI Asmaa Hadjer</t>
+  </si>
+  <si>
+    <t>saboundjiasmaa@gmail.com</t>
+  </si>
+  <si>
+    <t>0655459306 /  0556562385</t>
+  </si>
+  <si>
+    <t>HACENE IMENE</t>
+  </si>
+  <si>
+    <t>hacene_imene12@yahoo.com</t>
+  </si>
+  <si>
+    <t>0542471563</t>
+  </si>
+  <si>
+    <t>BENKATLANE Aissa</t>
+  </si>
+  <si>
+    <t>a.benkatlane@gmail.com</t>
+  </si>
+  <si>
+    <t>0697113466</t>
+  </si>
+  <si>
+    <t>ismahene.fezazi@gmail.com</t>
+  </si>
+  <si>
+    <t>0652652866</t>
+  </si>
+  <si>
+    <t>ABID HAMZA</t>
+  </si>
+  <si>
+    <t>PrE</t>
+  </si>
+  <si>
+    <t>abid_hamza@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BELAIDI OUAFIA</t>
+  </si>
+  <si>
+    <t>belaidi.ouafia@outlook.fr</t>
+  </si>
+  <si>
+    <t>0668834015</t>
+  </si>
+  <si>
+    <t>MEKHFI KHALIDA</t>
+  </si>
+  <si>
+    <t>mekhfikhalida87@gmail.com</t>
+  </si>
+  <si>
+    <t>ZATLA HICHAM</t>
+  </si>
+  <si>
+    <t>hicham.zatla@gmail.com</t>
+  </si>
+  <si>
+    <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>n_benseddik@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BERREKHCHI BERRAHMA NEILA</t>
+  </si>
+  <si>
+    <t>neilabekhchiberrahma@gmail.com</t>
+  </si>
+  <si>
+    <t>0656 88 71 07</t>
+  </si>
+  <si>
+    <t>YAMANI MASSIM</t>
+  </si>
+  <si>
+    <t>yamanimassim@yahoo.fr</t>
+  </si>
+  <si>
+    <t>FILALI INES</t>
+  </si>
+  <si>
+    <t>nesfilali2003@gmail.com</t>
+  </si>
+  <si>
+    <t>0794297709</t>
+  </si>
+  <si>
+    <t>KADARI BELKACEM</t>
+  </si>
+  <si>
+    <t>belkacemKadari@gmail.com</t>
+  </si>
+  <si>
+    <t>0553282842</t>
+  </si>
+  <si>
+    <t>DOUIAICI MOHAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mdouiaici@hotmail.com </t>
+  </si>
+  <si>
+    <t>MOKEDDES AMINA</t>
+  </si>
+  <si>
+    <t>Mokaddesamina@gmail.com</t>
+  </si>
+  <si>
+    <t>TAIBI SOUMIA</t>
+  </si>
+  <si>
+    <t>soumiaaiboudi27@gmail.com</t>
+  </si>
+  <si>
+    <t>KHIAT WALID</t>
+  </si>
+  <si>
+    <t>walid.sebastien@gmail.com</t>
+  </si>
+  <si>
+    <t>BENSNADA NADIA</t>
+  </si>
+  <si>
+    <t>bensenadanadia3@gmail.com</t>
+  </si>
+  <si>
+    <t>MEDLES IMED</t>
+  </si>
+  <si>
+    <t>imedmedles@gmail.com</t>
+  </si>
+  <si>
+    <t>ANANI MACHO</t>
+  </si>
+  <si>
+    <t>anani66@yahoo.fr</t>
+  </si>
+  <si>
+    <t>FEZAZI OMAR</t>
+  </si>
+  <si>
+    <t>fezaziomarfz@gmail.com</t>
+  </si>
+  <si>
+    <t>LAID ABDELALI</t>
+  </si>
+  <si>
+    <t>laidabdelali@gmail.com</t>
+  </si>
+  <si>
+    <t>BENSEMICHA MOHAMED</t>
+  </si>
+  <si>
+    <t>mhamedbensmicha00@gmail.com</t>
+  </si>
+  <si>
+    <t>LAZERGUI SIHEM</t>
+  </si>
+  <si>
+    <t>sihemlazergui@gmail.com</t>
+  </si>
+  <si>
+    <t>IKKACHE NARIMEN</t>
+  </si>
+  <si>
+    <t>ikkachenarimen.2017@gmail.com</t>
+  </si>
+  <si>
+    <t>ATTAR IMAD</t>
+  </si>
+  <si>
+    <t>attarimad3@gmail.com</t>
+  </si>
+  <si>
+    <t>0656697602</t>
+  </si>
+  <si>
+    <t>HADJ BOULANOUAR RACHID</t>
+  </si>
+  <si>
+    <t>rachid.hadjboulenouar@gmail.com</t>
+  </si>
+  <si>
+    <t>BENOUAR MOHAMED</t>
+  </si>
+  <si>
+    <t>moh@medbnr.com</t>
+  </si>
+  <si>
+    <t>0774814578</t>
+  </si>
+  <si>
+    <t>MELIANI ABDELHAK</t>
+  </si>
+  <si>
+    <t>0541306332</t>
+  </si>
+  <si>
+    <t>YAMOUNE FATIMA ZOHRA HADIL</t>
+  </si>
+  <si>
+    <t>hadilyamoune@gmail.com</t>
+  </si>
+  <si>
+    <t>0697176260</t>
   </si>
   <si>
     <t>MEGUEDAD ABOUBAKR</t>
@@ -121,402 +1258,6 @@
     <t>0799491736</t>
   </si>
   <si>
-    <t>MECHETTEM KHALIDA</t>
-  </si>
-  <si>
-    <t>Doctorante (Master)</t>
-  </si>
-  <si>
-    <t>khalidamet4@gmail.com</t>
-  </si>
-  <si>
-    <t>0550651046</t>
-  </si>
-  <si>
-    <t>MEKHFI KHALIDA</t>
-  </si>
-  <si>
-    <t>mekhfikhalida87@gmail.com</t>
-  </si>
-  <si>
-    <t>ARAB ABDELMADJID</t>
-  </si>
-  <si>
-    <t>Doctorat</t>
-  </si>
-  <si>
-    <t>arab4abdelmadjid@gmail.com</t>
-  </si>
-  <si>
-    <t>06 57 28 84 81</t>
-  </si>
-  <si>
-    <t>BENDIDA MOHAMED</t>
-  </si>
-  <si>
-    <t>bendida65@gmail.com</t>
-  </si>
-  <si>
-    <t>05 50 59 52 24</t>
-  </si>
-  <si>
-    <t>BENSALEM Mohammed Mustapha</t>
-  </si>
-  <si>
-    <t>bensalem.moh.mus@gmail.com</t>
-  </si>
-  <si>
-    <t>0550114832</t>
-  </si>
-  <si>
-    <t>BOUKHARI SOUMIA</t>
-  </si>
-  <si>
-    <t>boukharisoumiafarah@gmail.com</t>
-  </si>
-  <si>
-    <t>06 96 05 82 37</t>
-  </si>
-  <si>
-    <t>DJEZIRI SOUMIA</t>
-  </si>
-  <si>
-    <t>somiadjeziri22@gmail.com</t>
-  </si>
-  <si>
-    <t>0540920164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DROUNI Wassila Abir </t>
-  </si>
-  <si>
-    <t>Wassila.drouni@gmail.com</t>
-  </si>
-  <si>
-    <t>05 51 24 38 19</t>
-  </si>
-  <si>
-    <t>HADER ABDERRAHMANE</t>
-  </si>
-  <si>
-    <t>aer.hader91@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 00 44 75</t>
-  </si>
-  <si>
-    <t>MERADJAH IBRAHIM</t>
-  </si>
-  <si>
-    <t>ibrahimmeradjah72@gmail.com</t>
-  </si>
-  <si>
-    <t>0663114536</t>
-  </si>
-  <si>
-    <t>MOKEDDEM AMINA</t>
-  </si>
-  <si>
-    <t>mokeddem.amina2222@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 56 42 87 15 </t>
-  </si>
-  <si>
-    <t>ZIANI DJAMEL</t>
-  </si>
-  <si>
-    <t>djamel71ziani@gmail.com</t>
-  </si>
-  <si>
-    <t>05 61 11 10 02</t>
-  </si>
-  <si>
-    <t>REGUIEG ZAKARIA</t>
-  </si>
-  <si>
-    <t>reguiegzakaria10@gmail.com</t>
-  </si>
-  <si>
-    <t>0792070651</t>
-  </si>
-  <si>
-    <t>BENMESSAOUD LEYLA</t>
-  </si>
-  <si>
-    <t>l_benmessaoud@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0553714385</t>
-  </si>
-  <si>
-    <t>TURKI BILAL MEROUANE</t>
-  </si>
-  <si>
-    <t>turkibilal22@gmail.com</t>
-  </si>
-  <si>
-    <t>0655206865</t>
-  </si>
-  <si>
-    <t>SABOUNDJI Asmaa Hadjer</t>
-  </si>
-  <si>
-    <t>saboundjiasmaa@gmail.com</t>
-  </si>
-  <si>
-    <t>0655459306 /  0556562385</t>
-  </si>
-  <si>
-    <t>HACENE IMENE</t>
-  </si>
-  <si>
-    <t>hacene_imene12@yahoo.com</t>
-  </si>
-  <si>
-    <t>0542471563</t>
-  </si>
-  <si>
-    <t>BENKATLANE Aissa</t>
-  </si>
-  <si>
-    <t>a.benkatlane@gmail.com</t>
-  </si>
-  <si>
-    <t>0697113466</t>
-  </si>
-  <si>
-    <t>ismahene.fezazi@gmail.com</t>
-  </si>
-  <si>
-    <t>0652652866</t>
-  </si>
-  <si>
-    <t>BELAIDI OUAFIA</t>
-  </si>
-  <si>
-    <t>belaidi.ouafia@outlook.fr</t>
-  </si>
-  <si>
-    <t>0668834015</t>
-  </si>
-  <si>
-    <t>BERREKHCHI BERRAHMA NEILA</t>
-  </si>
-  <si>
-    <t>neilabekhchiberrahma@gmail.com</t>
-  </si>
-  <si>
-    <t>0656 88 71 07</t>
-  </si>
-  <si>
-    <t>KADARI BELKACEM</t>
-  </si>
-  <si>
-    <t>belkacemKadari@gmail.com</t>
-  </si>
-  <si>
-    <t>0553282842</t>
-  </si>
-  <si>
-    <t>LAID ABDELALI</t>
-  </si>
-  <si>
-    <t>laidabdelali@gmail.com</t>
-  </si>
-  <si>
-    <t>HADJ BOULANOUAR RACHID</t>
-  </si>
-  <si>
-    <t>rachid.hadjboulenouar@gmail.com</t>
-  </si>
-  <si>
-    <t>BENSEMICHA MOHAMED</t>
-  </si>
-  <si>
-    <t>mhamedbensmicha00@gmail.com</t>
-  </si>
-  <si>
-    <t>MOUILAH  KHEIRA</t>
-  </si>
-  <si>
-    <t>Ingénieur</t>
-  </si>
-  <si>
-    <t>mouilahka4614@gmail.com</t>
-  </si>
-  <si>
-    <t>BENGRIT MALIKA</t>
-  </si>
-  <si>
-    <t>Permanente</t>
-  </si>
-  <si>
-    <t>MAA</t>
-  </si>
-  <si>
-    <t>malikabengrit@gmail.com</t>
-  </si>
-  <si>
-    <t>BENKHALLOUK KADDOUR</t>
-  </si>
-  <si>
-    <t>Permanent</t>
-  </si>
-  <si>
-    <t>benkh_ka@yahoo.fr</t>
-  </si>
-  <si>
-    <t>GHAZEL FATIHA</t>
-  </si>
-  <si>
-    <t>nour73_fac@yahoo.fr</t>
-  </si>
-  <si>
-    <t>SAHALI YAMINA</t>
-  </si>
-  <si>
-    <t>ya_sahali@yahoo.fr</t>
-  </si>
-  <si>
-    <t>AREZKI MOUFOK</t>
-  </si>
-  <si>
-    <t>Master</t>
-  </si>
-  <si>
-    <t>Mouffok.arezki22@gmail.com </t>
-  </si>
-  <si>
-    <t>06 97 05 81 64</t>
-  </si>
-  <si>
-    <t>BENCELLA SARRA</t>
-  </si>
-  <si>
-    <t>sarrabencella@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 94 25 37 34 </t>
-  </si>
-  <si>
-    <t>BENHARAT ABDELHADI</t>
-  </si>
-  <si>
-    <t>Hadi.bnh00@gmail.com</t>
-  </si>
-  <si>
-    <t>KHELLAF KADDA</t>
-  </si>
-  <si>
-    <t>khellafkadda1234@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 65 72 17 23 </t>
-  </si>
-  <si>
-    <t>MAHKOUKA ZAZA</t>
-  </si>
-  <si>
-    <t>mahkouka.zaza@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0778 36 07 76 </t>
-  </si>
-  <si>
-    <t>MIR KHELIFA</t>
-  </si>
-  <si>
-    <t>khelifa-mir@outlook.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 59 78 39 </t>
-  </si>
-  <si>
-    <t>BERROUNA HENEN</t>
-  </si>
-  <si>
-    <t>berhenen@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0671745806</t>
-  </si>
-  <si>
-    <t>DELLOUM AMIRA</t>
-  </si>
-  <si>
-    <t>amiradelloum28@gmail.com</t>
-  </si>
-  <si>
-    <t>FILALI INES</t>
-  </si>
-  <si>
-    <t>nesfilali2003@gmail.com</t>
-  </si>
-  <si>
-    <t>MOKEDDES AMINA</t>
-  </si>
-  <si>
-    <t>Mokaddesamina@gmail.com</t>
-  </si>
-  <si>
-    <t>KHIAT WALID</t>
-  </si>
-  <si>
-    <t>walid.sebastien@gmail.com</t>
-  </si>
-  <si>
-    <t>BENSNADA NADIA</t>
-  </si>
-  <si>
-    <t>bensenadanadia3@gmail.com</t>
-  </si>
-  <si>
-    <t>MEDLES IMED</t>
-  </si>
-  <si>
-    <t>imedmedles@gmail.com</t>
-  </si>
-  <si>
-    <t>LAZERGUI SIHEM</t>
-  </si>
-  <si>
-    <t>sihemlazergui@gmail.com</t>
-  </si>
-  <si>
-    <t>ATTAR IMAD</t>
-  </si>
-  <si>
-    <t>attarimad3@gmail.com</t>
-  </si>
-  <si>
-    <t>0656697602</t>
-  </si>
-  <si>
-    <t>BENOUAR MOHAMED</t>
-  </si>
-  <si>
-    <t>moh@medbnr.com</t>
-  </si>
-  <si>
-    <t>0774814578</t>
-  </si>
-  <si>
-    <t>MELIANI ABDELHAK</t>
-  </si>
-  <si>
-    <t>0541306332</t>
-  </si>
-  <si>
-    <t>YAMOUNE FATIMA ZOHRA HADIL</t>
-  </si>
-  <si>
-    <t>hadilyamoune@gmail.com</t>
-  </si>
-  <si>
-    <t>0697176260</t>
-  </si>
-  <si>
     <t>DIDAOUI KAWTHAR</t>
   </si>
   <si>
@@ -526,156 +1267,6 @@
     <t>0699099272</t>
   </si>
   <si>
-    <t>IKKACHE NARIMEN</t>
-  </si>
-  <si>
-    <t>ikkachenarimen.2017@gmail.com</t>
-  </si>
-  <si>
-    <t>BECHEKIR SEYFEDDINE</t>
-  </si>
-  <si>
-    <t>MCA</t>
-  </si>
-  <si>
-    <t>seyfeddine.electrotechnique@gmail.com</t>
-  </si>
-  <si>
-    <t>BEDDAD BOUCIF</t>
-  </si>
-  <si>
-    <t>beddadboucif@gmail.com</t>
-  </si>
-  <si>
-    <t>0665458282</t>
-  </si>
-  <si>
-    <t>BENBELLIL NADJAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nn.nn.phy.chi@gmail.com </t>
-  </si>
-  <si>
-    <t>BENDIMERAD SALAH EDDINE</t>
-  </si>
-  <si>
-    <t>s_bendimerad@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BERMAKI HAMZA</t>
-  </si>
-  <si>
-    <t>bermaki.hamza@gmail.com</t>
-  </si>
-  <si>
-    <t>DRIEF FAIZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">drieff4@gmail.com </t>
-  </si>
-  <si>
-    <t>HANAFI SALAH</t>
-  </si>
-  <si>
-    <t>udl.fge.vdpg@gmail.com</t>
-  </si>
-  <si>
-    <t>HASSANI NAIMA</t>
-  </si>
-  <si>
-    <t>naimahassani69@yahoo.fr</t>
-  </si>
-  <si>
-    <t>JBILOU MOKHTARIA</t>
-  </si>
-  <si>
-    <t>harmel71@yahoo.fr</t>
-  </si>
-  <si>
-    <t>LALEDJ NADJET</t>
-  </si>
-  <si>
-    <t>nadjet_69@hotmail.fr</t>
-  </si>
-  <si>
-    <t>MAAMMAR MOHAMED</t>
-  </si>
-  <si>
-    <t>mohamed.maammar@gmail.com</t>
-  </si>
-  <si>
-    <t>MIMOUNI CHAHINEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mimounichahinez@gmail.com </t>
-  </si>
-  <si>
-    <t>0558193860</t>
-  </si>
-  <si>
-    <t>BRAHAMI MOHAMED NADJIB</t>
-  </si>
-  <si>
-    <t>nadjbrahami@gmail.com</t>
-  </si>
-  <si>
-    <t>ZENASNI MERIEM</t>
-  </si>
-  <si>
-    <t>zenasnimeriem29@gmail.com</t>
-  </si>
-  <si>
-    <t>0552037098</t>
-  </si>
-  <si>
-    <t>REGUIG ABDELDJALIL</t>
-  </si>
-  <si>
-    <t>Mise en disponibilité</t>
-  </si>
-  <si>
-    <t>abdeldjalil.reguig@outlook.com</t>
-  </si>
-  <si>
-    <t>KADA KLOUCHA OMAR</t>
-  </si>
-  <si>
-    <t>klomar05@yahoo.fr</t>
-  </si>
-  <si>
-    <t>SAIDI KHAYREDDINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
-  </si>
-  <si>
-    <t>SEMMAK ABDELKADER</t>
-  </si>
-  <si>
-    <t>semmak.abdelkader@outlook.com</t>
-  </si>
-  <si>
-    <t>0772111809</t>
-  </si>
-  <si>
-    <t>OUARI KHEIRA</t>
-  </si>
-  <si>
-    <t>ouari_k@yahoo.fr</t>
-  </si>
-  <si>
-    <t>ZATLA HICHAM</t>
-  </si>
-  <si>
-    <t>hicham.zatla@gmail.com</t>
-  </si>
-  <si>
-    <t>FEZAZI OMAR</t>
-  </si>
-  <si>
-    <t>fezaziomarfz@gmail.com</t>
-  </si>
-  <si>
     <t>YAHI HICHEM</t>
   </si>
   <si>
@@ -683,597 +1274,6 @@
   </si>
   <si>
     <t>0556565254</t>
-  </si>
-  <si>
-    <t>BADIS KARIMA</t>
-  </si>
-  <si>
-    <t>MCB</t>
-  </si>
-  <si>
-    <t>karis483@hotmail.fr</t>
-  </si>
-  <si>
-    <t>0560337902</t>
-  </si>
-  <si>
-    <t>ABID MOHAMED</t>
-  </si>
-  <si>
-    <t>Pr</t>
-  </si>
-  <si>
-    <t>irecom_abid@yahoo.fr</t>
-  </si>
-  <si>
-    <t>AKSA WESSIM</t>
-  </si>
-  <si>
-    <t>aksa86wessim@gmail.com</t>
-  </si>
-  <si>
-    <t>ARDJOUN SID AHMED</t>
-  </si>
-  <si>
-    <t>ardjoun.s.e.m@gmail.com</t>
-  </si>
-  <si>
-    <t>AYAD ABDELGHANI</t>
-  </si>
-  <si>
-    <t>ayad_abdelghani@yahoo.fr</t>
-  </si>
-  <si>
-    <t>AZAIZ AHMED</t>
-  </si>
-  <si>
-    <t>ahazaiz2011@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BAHLIL MOUNIR</t>
-  </si>
-  <si>
-    <t>bahlilmounir@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0672447184</t>
-  </si>
-  <si>
-    <t>BELLEBNA YASSINE</t>
-  </si>
-  <si>
-    <t>fgevdpg@gmail.com</t>
-  </si>
-  <si>
-    <t>BENAISSA ABDELKADER</t>
-  </si>
-  <si>
-    <t>aek_benaissa@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BERRAHAL BEL ABBES</t>
-  </si>
-  <si>
-    <t>dept.eln@gmail.com</t>
-  </si>
-  <si>
-    <t>BENDAOUD ABDELBER</t>
-  </si>
-  <si>
-    <t>babdelber22@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BENHAMIDA FARID</t>
-  </si>
-  <si>
-    <t>farid.benhamida@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BENTAALLAH ABDERRAHIM</t>
-  </si>
-  <si>
-    <t>bentaallah65@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BOUKHOULDA FODIL</t>
-  </si>
-  <si>
-    <t>boukhoulda.fodil@yahoo.fr</t>
-  </si>
-  <si>
-    <t>SEMMACHE HOURIA</t>
-  </si>
-  <si>
-    <t>hsemmach@yahoo.fr</t>
-  </si>
-  <si>
-    <t>DJERIRI YOUCEF</t>
-  </si>
-  <si>
-    <t>djeriri_youcef@yahoo.fr</t>
-  </si>
-  <si>
-    <t>FELLAH MOHAMMED KARIM</t>
-  </si>
-  <si>
-    <t>mkfellah@gmail.com</t>
-  </si>
-  <si>
-    <t>HADJERI SAMIR</t>
-  </si>
-  <si>
-    <t>shadjeri2@yahoo.fr</t>
-  </si>
-  <si>
-    <t>KHATIR MOHAMED</t>
-  </si>
-  <si>
-    <t>khatir.mohamed1977@gmail.com</t>
-  </si>
-  <si>
-    <t>MASSOUM AHMED</t>
-  </si>
-  <si>
-    <t>ahmassoum@yahoo.fr</t>
-  </si>
-  <si>
-    <t>MILOUA FARID</t>
-  </si>
-  <si>
-    <t>milouafarid@gmail.com</t>
-  </si>
-  <si>
-    <t>0657011874</t>
-  </si>
-  <si>
-    <t>MILOUDI HOUCINE</t>
-  </si>
-  <si>
-    <t>el.houcine@yahoo.fr</t>
-  </si>
-  <si>
-    <t>NACERI ABDELLATIF</t>
-  </si>
-  <si>
-    <t>abdnaceri@yahoo.fr</t>
-  </si>
-  <si>
-    <t>NASSOUR KAMEL</t>
-  </si>
-  <si>
-    <t>nass_ka@yahoo.fr</t>
-  </si>
-  <si>
-    <t>NEMMICH SAID</t>
-  </si>
-  <si>
-    <t>nemmichsaid@gmail.com</t>
-  </si>
-  <si>
-    <t>OUKLI MIMOUNA</t>
-  </si>
-  <si>
-    <t>mounaoukli@yahoo.fr</t>
-  </si>
-  <si>
-    <t>RAMI ABDELKADER</t>
-  </si>
-  <si>
-    <t>abc_rim20052003@yahoo.fr</t>
-  </si>
-  <si>
-    <t>REZOUG MOHAMMED</t>
-  </si>
-  <si>
-    <t>rezoug.med@gmail.com</t>
-  </si>
-  <si>
-    <t>SEMMAH ABDELHAFID</t>
-  </si>
-  <si>
-    <t>hafid.semmah@yahoo.fr</t>
-  </si>
-  <si>
-    <t>TABET DERRAZ HIND</t>
-  </si>
-  <si>
-    <t>htabet05@yahoo.fr</t>
-  </si>
-  <si>
-    <t>TILMATINE AMAR</t>
-  </si>
-  <si>
-    <t>atilmatine@gmail.com</t>
-  </si>
-  <si>
-    <t>TOUHAMI SEDDIK</t>
-  </si>
-  <si>
-    <t>seddik.touhami@gmail.com</t>
-  </si>
-  <si>
-    <t>ZEBLAH ABDELKADER</t>
-  </si>
-  <si>
-    <t>azeblah@yahoo.fr</t>
-  </si>
-  <si>
-    <t>ZIDI SID AHMED</t>
-  </si>
-  <si>
-    <t>sbzidi@yahoo.fr</t>
-  </si>
-  <si>
-    <t>RAIS ABDELMAJID</t>
-  </si>
-  <si>
-    <t>amrais@yahoo.com</t>
-  </si>
-  <si>
-    <t>ABBOU MAJDA</t>
-  </si>
-  <si>
-    <t>milouaf@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0556831346</t>
-  </si>
-  <si>
-    <t>BENSEDDIK NADIA</t>
-  </si>
-  <si>
-    <t>n_benseddik@yahoo.fr</t>
-  </si>
-  <si>
-    <t>YAMANI MASSIM</t>
-  </si>
-  <si>
-    <t>yamanimassim@yahoo.fr</t>
-  </si>
-  <si>
-    <t>DOUIAICI MOHAMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mdouiaici@hotmail.com </t>
-  </si>
-  <si>
-    <t>ANANI MACHO</t>
-  </si>
-  <si>
-    <t>anani66@yahoo.fr</t>
-  </si>
-  <si>
-    <t>ABID HAMZA</t>
-  </si>
-  <si>
-    <t>PrE</t>
-  </si>
-  <si>
-    <t>abid_hamza@yahoo.fr</t>
-  </si>
-  <si>
-    <t>ABDELI MAMA</t>
-  </si>
-  <si>
-    <t>abdelli.mama@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 52 96 89 21 </t>
-  </si>
-  <si>
-    <t>BELHABRI RIHAB</t>
-  </si>
-  <si>
-    <t>ri123hab@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 54 40 75 58 </t>
-  </si>
-  <si>
-    <t>BELHALLOUCHE LAKHDAR</t>
-  </si>
-  <si>
-    <t>lakhdar_belhallouche@hotmail.fr</t>
-  </si>
-  <si>
-    <t>06 96 0582 37</t>
-  </si>
-  <si>
-    <t>BETTACHE ABDERRAHMANE</t>
-  </si>
-  <si>
-    <t>abderrahmanbettache@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">066939 21 49 </t>
-  </si>
-  <si>
-    <t>BOUBEKEUR HALIMA</t>
-  </si>
-  <si>
-    <t>boubekeur97sba@gmail.com</t>
-  </si>
-  <si>
-    <t>06 74 50 65 01</t>
-  </si>
-  <si>
-    <t>BOUDALI AHMED</t>
-  </si>
-  <si>
-    <t>ahmedboudali32@gmail.com</t>
-  </si>
-  <si>
-    <t>0656855101</t>
-  </si>
-  <si>
-    <t>BOULARAF AICHA</t>
-  </si>
-  <si>
-    <t>douaaboularaf@gmail.com</t>
-  </si>
-  <si>
-    <t>0799747080</t>
-  </si>
-  <si>
-    <t>BOURAHLA CHAHRAZED</t>
-  </si>
-  <si>
-    <t>bourahla.phys@gmail.com</t>
-  </si>
-  <si>
-    <t>0781893264</t>
-  </si>
-  <si>
-    <t>CHABANE CHAOUCHE ABDALLAH</t>
-  </si>
-  <si>
-    <t>chaouche.abdallah@gmail.com</t>
-  </si>
-  <si>
-    <t>0664457108</t>
-  </si>
-  <si>
-    <t>DJELLOULI YOUNES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">djellouli08younes08@gmail.com </t>
-  </si>
-  <si>
-    <t>0673948096</t>
-  </si>
-  <si>
-    <t>DRICI LAMIA</t>
-  </si>
-  <si>
-    <t>Lamia_du22@hotmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 97 35 08 88 </t>
-  </si>
-  <si>
-    <t>El MESTARI WAHIBA</t>
-  </si>
-  <si>
-    <t>wahibaelmestarii@gmail.com</t>
-  </si>
-  <si>
-    <t>0556130770</t>
-  </si>
-  <si>
-    <t>MILOUA FETHI</t>
-  </si>
-  <si>
-    <t>fethi22miloua@gmail.com</t>
-  </si>
-  <si>
-    <t>HADJI AHMED</t>
-  </si>
-  <si>
-    <t>ahmed.hadji22@yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 98 14 23 47 </t>
-  </si>
-  <si>
-    <t>HARMEL MOHAMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmel.mohamed22@hotmail.com </t>
-  </si>
-  <si>
-    <t>LAHCEN AZDDINE</t>
-  </si>
-  <si>
-    <t>azddinelahcene@gmail.com</t>
-  </si>
-  <si>
-    <t>LATRECHE MOKHTAR</t>
-  </si>
-  <si>
-    <t>m_latreche@yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 75 89 45 05 </t>
-  </si>
-  <si>
-    <t>LOUSDAD AYMEN</t>
-  </si>
-  <si>
-    <t>lousdadaymen.aziz@gmail.com</t>
-  </si>
-  <si>
-    <t>07 94 94 48 94</t>
-  </si>
-  <si>
-    <t>MAHIDDINE Abderrahim</t>
-  </si>
-  <si>
-    <t>ma2006ne_86@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0657058282</t>
-  </si>
-  <si>
-    <t>MANSOURI ABDERRAZAK</t>
-  </si>
-  <si>
-    <t>abderazakmahdi22@gmail.com</t>
-  </si>
-  <si>
-    <t>0696417435</t>
-  </si>
-  <si>
-    <t>MEKHALEF SOUMIA</t>
-  </si>
-  <si>
-    <t>mekhalefleila@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 59 03 18 24 </t>
-  </si>
-  <si>
-    <t>MESLEM MEHADJIA</t>
-  </si>
-  <si>
-    <t>mehadjiameslem@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 97 01 34 39 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non Défini </t>
-  </si>
-  <si>
-    <t>REDJALA MAJDA</t>
-  </si>
-  <si>
-    <t>majdaredjala1492@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 53 64 47 91 </t>
-  </si>
-  <si>
-    <t>SENOUCI HAYAT</t>
-  </si>
-  <si>
-    <t>senoucihayat11@gmail.com</t>
-  </si>
-  <si>
-    <t>ZAREB Mohammed Amine</t>
-  </si>
-  <si>
-    <t>zarebmohammedamine@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0674 68 05 35 </t>
-  </si>
-  <si>
-    <t>LARBI ZIDI</t>
-  </si>
-  <si>
-    <t>larbi.zidi6@gmail.com</t>
-  </si>
-  <si>
-    <t>07 92 12 03 38</t>
-  </si>
-  <si>
-    <t>ABED ZOULIKHA</t>
-  </si>
-  <si>
-    <t>zoulikhaabed3@gmail.com</t>
-  </si>
-  <si>
-    <t>AISSANI ALI</t>
-  </si>
-  <si>
-    <t>aliaissani97@gmail.com</t>
-  </si>
-  <si>
-    <t>AZZA ROMAISSA FATIMA ZOHRA</t>
-  </si>
-  <si>
-    <t>azzafatimazohraromaissa.l3@gmail.com</t>
-  </si>
-  <si>
-    <t>BELABED MERIEM</t>
-  </si>
-  <si>
-    <t>meriembelabed5@gmail.com</t>
-  </si>
-  <si>
-    <t>BENKABOU MOHAMED EL HABIB</t>
-  </si>
-  <si>
-    <t>bkbhbb22@gmail.com</t>
-  </si>
-  <si>
-    <t>BENMASOUD LEILA</t>
-  </si>
-  <si>
-    <t>l.benmessaoud@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BERROUNA HANANE</t>
-  </si>
-  <si>
-    <t>CHIKHI NAWEL</t>
-  </si>
-  <si>
-    <t>chikhi_nawel75@yahoo.fr</t>
-  </si>
-  <si>
-    <t>FENTAZY BELKISSE</t>
-  </si>
-  <si>
-    <t>fantazibelkisse.13@gmail.com</t>
-  </si>
-  <si>
-    <t>khadidjafezazi90@gmail</t>
-  </si>
-  <si>
-    <t>KADA ZAIR IKRAM</t>
-  </si>
-  <si>
-    <t>ikram.kadazair@gmail.com</t>
-  </si>
-  <si>
-    <t>KADRI RANIA</t>
-  </si>
-  <si>
-    <t>kadrirania51@gmail.com</t>
-  </si>
-  <si>
-    <t>LAYATI TAYEB MEHDI</t>
-  </si>
-  <si>
-    <t>layatimedi@gmail.com</t>
-  </si>
-  <si>
-    <t>NEFAHA ABOUBAKR</t>
-  </si>
-  <si>
-    <t>Boba1620@hotmail.com</t>
-  </si>
-  <si>
-    <t>SACI HAMZA</t>
-  </si>
-  <si>
-    <t>sacihamza40@gmail.com</t>
-  </si>
-  <si>
-    <t>ZERDANI MOHAMMED</t>
-  </si>
-  <si>
-    <t>medzerdani@gmail.com</t>
-  </si>
-  <si>
-    <t>0794297709</t>
-  </si>
-  <si>
-    <t>TAIBI SOUMIA</t>
-  </si>
-  <si>
-    <t>soumiaaiboudi27@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1452,16 +1452,16 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Cambria"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="Cambria"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1473,25 +1473,6 @@
       <sz val="10.5"/>
       <color rgb="FF222222"/>
       <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF1155CC"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1508,10 +1489,29 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF1155CC"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -2078,7 +2078,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -2206,7 +2206,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2274,84 +2274,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2363,42 +2316,71 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
@@ -2406,12 +2388,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2796,9 +2778,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="31.5" hidden="1" spans="1:7">
+    <row r="2" ht="15.75" hidden="1" spans="1:7">
       <c r="A2" s="23">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>7</v>
@@ -2806,48 +2788,44 @@
       <c r="C2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="23" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="27" t="s">
-        <v>12</v>
-      </c>
+      <c r="G2" s="26"/>
     </row>
     <row r="3" ht="15.75" hidden="1" spans="1:7">
       <c r="A3" s="23">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="B3" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="71" t="s">
-        <v>16</v>
-      </c>
+      <c r="G3" s="26"/>
     </row>
     <row r="4" ht="15.75" hidden="1" spans="1:7">
       <c r="A4" s="23">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>8</v>
@@ -2856,21 +2834,19 @@
         <v>9</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>19</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="26"/>
     </row>
     <row r="5" ht="15.75" hidden="1" spans="1:7">
       <c r="A5" s="23">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>8</v>
@@ -2879,21 +2855,19 @@
         <v>9</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="71" t="s">
-        <v>22</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F5" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="26"/>
     </row>
     <row r="6" ht="15.75" hidden="1" spans="1:7">
       <c r="A6" s="23">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>8</v>
@@ -2902,67 +2876,65 @@
         <v>9</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>25</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="26"/>
     </row>
     <row r="7" ht="15.75" hidden="1" spans="1:7">
       <c r="A7" s="23">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" hidden="1" spans="1:7">
+      <c r="A8" s="23">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" hidden="1" spans="1:7">
-      <c r="A8" s="29">
-        <v>163</v>
-      </c>
-      <c r="B8" s="30" t="s">
+      <c r="E8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="31" t="s">
+      <c r="G8" s="65" t="s">
         <v>27</v>
-      </c>
-      <c r="G8" s="72" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" ht="15.75" hidden="1" spans="1:7">
       <c r="A9" s="23">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="24" t="s">
         <v>8</v>
@@ -2971,21 +2943,19 @@
         <v>9</v>
       </c>
       <c r="E9" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="71" t="s">
-        <v>32</v>
-      </c>
+      <c r="G9" s="26"/>
     </row>
     <row r="10" ht="15.75" hidden="1" spans="1:7">
       <c r="A10" s="23">
-        <v>141</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>33</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>31</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>8</v>
@@ -2993,43 +2963,43 @@
       <c r="D10" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="G10" s="27"/>
+      <c r="E10" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="65" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" ht="15.75" hidden="1" spans="1:7">
       <c r="A11" s="23">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="B11" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>38</v>
-      </c>
+      <c r="G11" s="26"/>
     </row>
     <row r="12" ht="15.75" hidden="1" spans="1:7">
       <c r="A12" s="23">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>8</v>
@@ -3037,45 +3007,41 @@
       <c r="D12" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>41</v>
-      </c>
+      <c r="E12" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" s="26"/>
     </row>
     <row r="13" ht="15.75" hidden="1" spans="1:7">
       <c r="A13" s="23">
-        <v>64</v>
-      </c>
-      <c r="B13" s="30" t="s">
-        <v>42</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>38</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="71" t="s">
-        <v>44</v>
-      </c>
+      <c r="E13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="26"/>
     </row>
     <row r="14" ht="15.75" hidden="1" spans="1:7">
       <c r="A14" s="23">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>8</v>
@@ -3084,21 +3050,19 @@
         <v>9</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>47</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="26"/>
     </row>
     <row r="15" ht="15.75" hidden="1" spans="1:7">
       <c r="A15" s="23">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>8</v>
@@ -3107,21 +3071,19 @@
         <v>9</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="71" t="s">
-        <v>50</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F15" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="26"/>
     </row>
     <row r="16" ht="15.75" hidden="1" spans="1:7">
       <c r="A16" s="23">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>8</v>
@@ -3130,44 +3092,40 @@
         <v>9</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>53</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="F16" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="26"/>
     </row>
     <row r="17" ht="15.75" hidden="1" spans="1:7">
       <c r="A17" s="23">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>56</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="F17" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" s="26"/>
     </row>
     <row r="18" ht="15.75" hidden="1" spans="1:7">
       <c r="A18" s="23">
-        <v>94</v>
+        <v>17</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>8</v>
@@ -3176,21 +3134,19 @@
         <v>9</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="71" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" ht="15.75" hidden="1" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="23">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C19" s="24" t="s">
         <v>8</v>
@@ -3198,22 +3154,20 @@
       <c r="D19" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>62</v>
-      </c>
+      <c r="E19" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="26"/>
     </row>
     <row r="20" ht="15.75" hidden="1" spans="1:7">
       <c r="A20" s="23">
-        <v>103</v>
+        <v>19</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="C20" s="24" t="s">
         <v>8</v>
@@ -3222,312 +3176,292 @@
         <v>9</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>65</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="G20" s="26"/>
     </row>
     <row r="21" ht="15.75" hidden="1" spans="1:7">
       <c r="A21" s="23">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="29" t="s">
+      <c r="D21" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" s="26" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" s="73" t="s">
-        <v>68</v>
-      </c>
+      <c r="E21" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G21" s="26"/>
     </row>
     <row r="22" ht="15.75" hidden="1" spans="1:7">
       <c r="A22" s="23">
-        <v>132</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>69</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>57</v>
       </c>
       <c r="C22" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="73" t="s">
-        <v>71</v>
-      </c>
+      <c r="E22" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="26"/>
     </row>
     <row r="23" ht="15.75" hidden="1" spans="1:7">
       <c r="A23" s="23">
-        <v>133</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>72</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>59</v>
       </c>
       <c r="C23" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="G23" s="73" t="s">
-        <v>74</v>
-      </c>
+      <c r="D23" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G23" s="26"/>
     </row>
     <row r="24" ht="15.75" hidden="1" spans="1:7">
       <c r="A24" s="23">
-        <v>135</v>
-      </c>
-      <c r="B24" s="27" t="s">
-        <v>75</v>
+        <v>23</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>61</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="29" t="s">
+      <c r="D24" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>77</v>
-      </c>
+      <c r="E24" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="26"/>
     </row>
     <row r="25" ht="15.75" hidden="1" spans="1:7">
       <c r="A25" s="23">
-        <v>136</v>
-      </c>
-      <c r="B25" s="27" t="s">
-        <v>78</v>
+        <v>24</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>63</v>
       </c>
       <c r="C25" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F25" s="26" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="73" t="s">
-        <v>80</v>
-      </c>
+      <c r="D25" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="26"/>
     </row>
     <row r="26" ht="15.75" hidden="1" spans="1:7">
       <c r="A26" s="23">
-        <v>137</v>
-      </c>
-      <c r="B26" s="27" t="s">
-        <v>81</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="G26" s="73" t="s">
-        <v>83</v>
-      </c>
+      <c r="E26" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="26"/>
     </row>
     <row r="27" ht="15.75" hidden="1" spans="1:7">
       <c r="A27" s="23">
-        <v>138</v>
-      </c>
-      <c r="B27" s="24"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>67</v>
+      </c>
       <c r="C27" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G27" s="73" t="s">
-        <v>85</v>
-      </c>
+      <c r="D27" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="26"/>
     </row>
     <row r="28" ht="15.75" hidden="1" spans="1:7">
       <c r="A28" s="23">
-        <v>140</v>
-      </c>
-      <c r="B28" s="27" t="s">
-        <v>86</v>
+        <v>27</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>69</v>
       </c>
       <c r="C28" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28" s="74" t="s">
-        <v>88</v>
-      </c>
+      <c r="E28" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="26"/>
     </row>
     <row r="29" ht="15.75" hidden="1" spans="1:7">
       <c r="A29" s="23">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="29" t="s">
+      <c r="D29" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F29" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>91</v>
-      </c>
+      <c r="E29" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G29" s="26"/>
     </row>
     <row r="30" ht="15.75" hidden="1" spans="1:7">
       <c r="A30" s="23">
-        <v>148</v>
+        <v>29</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G30" s="26"/>
+    </row>
+    <row r="31" ht="15.75" hidden="1" spans="1:7">
+      <c r="A31" s="23">
+        <v>30</v>
+      </c>
+      <c r="B31" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="26"/>
+    </row>
+    <row r="32" ht="15.75" hidden="1" spans="1:7">
+      <c r="A32" s="23">
+        <v>31</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="G30" s="72" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
-      <c r="A31" s="29">
-        <v>156</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="29" t="s">
+      <c r="E32" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="G32" s="26"/>
+    </row>
+    <row r="33" ht="15.75" hidden="1" spans="1:7">
+      <c r="A33" s="23">
+        <v>32</v>
+      </c>
+      <c r="B33" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F31" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="G31" s="27"/>
-    </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
-      <c r="A32" s="29">
-        <v>159</v>
-      </c>
-      <c r="B32" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F32" s="40" t="s">
-        <v>98</v>
-      </c>
-      <c r="G32" s="27"/>
-    </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
-      <c r="A33" s="29">
-        <v>156</v>
-      </c>
-      <c r="B33" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="27"/>
+      <c r="E33" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" ht="15.75" hidden="1" spans="1:7">
       <c r="A34" s="23">
-        <v>106</v>
+        <v>34</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>8</v>
@@ -3536,126 +3470,128 @@
         <v>9</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="F34" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" s="27"/>
-    </row>
-    <row r="35" ht="15.75" spans="1:7">
+        <v>29</v>
+      </c>
+      <c r="F34" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="G34" s="26"/>
+    </row>
+    <row r="35" ht="15.75" hidden="1" spans="1:7">
       <c r="A35" s="23">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="F35" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="G35" s="27"/>
-    </row>
-    <row r="36" ht="15.75" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F35" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G35" s="26"/>
+    </row>
+    <row r="36" ht="15.75" hidden="1" spans="1:7">
       <c r="A36" s="23">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E36" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="F36" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="G36" s="27"/>
-    </row>
-    <row r="37" ht="15.75" spans="1:7">
+        <v>9</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="G36" s="66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" hidden="1" spans="1:7">
       <c r="A37" s="23">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="F37" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="G37" s="27"/>
-    </row>
-    <row r="38" ht="15.75" spans="1:7">
+        <v>10</v>
+      </c>
+      <c r="F37" s="27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" s="26"/>
+    </row>
+    <row r="38" ht="15.75" hidden="1" spans="1:7">
       <c r="A38" s="23">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="F38" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="G38" s="27"/>
+        <v>29</v>
+      </c>
+      <c r="F38" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="G38" s="65" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="39" ht="15.75" hidden="1" spans="1:7">
       <c r="A39" s="23">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="C39" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="25" t="s">
+      <c r="D39" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="F39" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>118</v>
-      </c>
+      <c r="E39" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="26"/>
     </row>
     <row r="40" ht="15.75" hidden="1" spans="1:7">
       <c r="A40" s="23">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>8</v>
@@ -3664,21 +3600,19 @@
         <v>9</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="F40" s="26" t="s">
-        <v>120</v>
-      </c>
-      <c r="G40" s="27" t="s">
-        <v>121</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F40" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" s="26"/>
     </row>
     <row r="41" ht="15.75" hidden="1" spans="1:7">
       <c r="A41" s="23">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>8</v>
@@ -3687,19 +3621,19 @@
         <v>9</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="G41" s="27"/>
+        <v>10</v>
+      </c>
+      <c r="F41" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="G41" s="26"/>
     </row>
     <row r="42" ht="15.75" hidden="1" spans="1:7">
       <c r="A42" s="23">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C42" s="24" t="s">
         <v>8</v>
@@ -3707,45 +3641,41 @@
       <c r="D42" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="G42" s="27" t="s">
-        <v>126</v>
-      </c>
+      <c r="E42" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="G42" s="26"/>
     </row>
     <row r="43" ht="15.75" hidden="1" spans="1:7">
       <c r="A43" s="23">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="C43" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="F43" s="26" t="s">
-        <v>128</v>
-      </c>
-      <c r="G43" s="27" t="s">
-        <v>129</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F43" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="G43" s="26"/>
     </row>
     <row r="44" ht="15.75" hidden="1" spans="1:7">
       <c r="A44" s="23">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>8</v>
@@ -3754,21 +3684,19 @@
         <v>9</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>131</v>
-      </c>
-      <c r="G44" s="27" t="s">
-        <v>132</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F44" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="G44" s="26"/>
     </row>
     <row r="45" ht="15.75" hidden="1" spans="1:7">
       <c r="A45" s="23">
+        <v>45</v>
+      </c>
+      <c r="B45" s="24" t="s">
         <v>105</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>133</v>
       </c>
       <c r="C45" s="24" t="s">
         <v>8</v>
@@ -3777,1069 +3705,1077 @@
         <v>9</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="F45" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G45" s="72" t="s">
-        <v>135</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F45" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="G45" s="26"/>
     </row>
     <row r="46" ht="15.75" hidden="1" spans="1:7">
       <c r="A46" s="23">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="C46" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D46" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="F46" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="G46" s="28"/>
+      <c r="D46" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F46" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="G46" s="26"/>
     </row>
     <row r="47" ht="15.75" hidden="1" spans="1:7">
       <c r="A47" s="23">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="B47" s="24" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="C47" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="29" t="s">
+      <c r="D47" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="G47" s="27"/>
+      <c r="E47" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="G47" s="26"/>
     </row>
     <row r="48" ht="15.75" hidden="1" spans="1:7">
       <c r="A48" s="23">
+        <v>48</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="G48" s="26"/>
+    </row>
+    <row r="49" ht="15.75" hidden="1" spans="1:7">
+      <c r="A49" s="23">
+        <v>49</v>
+      </c>
+      <c r="B49" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G49" s="26"/>
+    </row>
+    <row r="50" ht="15.75" hidden="1" spans="1:7">
+      <c r="A50" s="23">
+        <v>50</v>
+      </c>
+      <c r="B50" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G50" s="26"/>
+    </row>
+    <row r="51" ht="15.75" hidden="1" spans="1:7">
+      <c r="A51" s="23">
+        <v>51</v>
+      </c>
+      <c r="B51" s="24" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51" s="26"/>
+    </row>
+    <row r="52" ht="15.75" hidden="1" spans="1:7">
+      <c r="A52" s="23">
+        <v>52</v>
+      </c>
+      <c r="B52" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="G52" s="65" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" hidden="1" spans="1:7">
+      <c r="A53" s="23">
+        <v>53</v>
+      </c>
+      <c r="B53" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G53" s="26"/>
+    </row>
+    <row r="54" ht="15.75" hidden="1" spans="1:7">
+      <c r="A54" s="23">
+        <v>54</v>
+      </c>
+      <c r="B54" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G54" s="65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" hidden="1" spans="1:7">
+      <c r="A55" s="23">
+        <v>55</v>
+      </c>
+      <c r="B55" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="34"/>
+      <c r="F55" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="G55" s="26" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" hidden="1" spans="1:7">
+      <c r="A56" s="23">
+        <v>57</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E56" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="G56" s="26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" hidden="1" spans="1:7">
+      <c r="A57" s="23">
+        <v>58</v>
+      </c>
+      <c r="B57" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="G57" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" hidden="1" spans="1:7">
+      <c r="A58" s="23">
+        <v>59</v>
+      </c>
+      <c r="B58" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E58" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="G58" s="26" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" hidden="1" spans="1:7">
+      <c r="A59" s="23">
+        <v>60</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E59" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="G59" s="26" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" hidden="1" spans="1:7">
+      <c r="A60" s="23">
+        <v>61</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="E60" s="37"/>
+      <c r="F60" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="G60" s="38" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" hidden="1" spans="1:7">
+      <c r="A61" s="23">
+        <v>62</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E61" s="30"/>
+      <c r="F61" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="B48" s="30" t="s">
-        <v>140</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F48" s="39" t="s">
-        <v>141</v>
-      </c>
-      <c r="G48" s="27"/>
-    </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
-      <c r="A49" s="29">
+      <c r="G61" s="26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" hidden="1" spans="1:7">
+      <c r="A62" s="23">
+        <v>64</v>
+      </c>
+      <c r="B62" s="40" t="s">
         <v>152</v>
       </c>
-      <c r="B49" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F49" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="G49" s="27"/>
-    </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
-      <c r="A50" s="29">
+      <c r="C62" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="E62" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F62" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="B50" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F50" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="G50" s="27"/>
-    </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
-      <c r="A51" s="29">
-        <v>153</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F51" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="G51" s="27"/>
-    </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
-      <c r="A52" s="29">
+      <c r="G62" s="65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" hidden="1" spans="1:7">
+      <c r="A63" s="23">
+        <v>65</v>
+      </c>
+      <c r="B63" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="C63" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E63" s="32"/>
+      <c r="F63" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="G63" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="B52" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E52" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F52" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="G52" s="27"/>
-    </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
-      <c r="A53" s="29">
+    </row>
+    <row r="64" ht="15.75" hidden="1" spans="1:7">
+      <c r="A64" s="23">
+        <v>66</v>
+      </c>
+      <c r="B64" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="B53" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F53" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="G53" s="72" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
-      <c r="A54" s="29">
+      <c r="C64" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E64" s="35"/>
+      <c r="F64" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="G64" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="B54" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F54" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="G54" s="72" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
-      <c r="A55" s="29">
+    </row>
+    <row r="65" ht="15.75" hidden="1" spans="1:7">
+      <c r="A65" s="23">
+        <v>67</v>
+      </c>
+      <c r="B65" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="B55" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E55" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F55" s="27"/>
-      <c r="G55" s="72" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
-      <c r="A56" s="29">
+      <c r="C65" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E65" s="32"/>
+      <c r="F65" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="B56" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F56" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="G56" s="72" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
-      <c r="A57" s="29">
+      <c r="G65" s="66" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" hidden="1" spans="1:7">
+      <c r="A66" s="23">
+        <v>68</v>
+      </c>
+      <c r="B66" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B57" s="44" t="s">
-        <v>161</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="29" t="s">
-        <v>116</v>
-      </c>
-      <c r="F57" s="45" t="s">
-        <v>162</v>
-      </c>
-      <c r="G57" s="72" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
-      <c r="A58" s="29">
-        <v>157</v>
-      </c>
-      <c r="B58" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="46" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="46" t="s">
-        <v>116</v>
-      </c>
-      <c r="F58" s="47" t="s">
+      <c r="C66" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F66" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="G58" s="27"/>
-    </row>
-    <row r="59" ht="15.75" spans="1:7">
-      <c r="A59" s="23">
-        <v>8</v>
-      </c>
-      <c r="B59" s="24" t="s">
+      <c r="G66" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="C59" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E59" s="23" t="s">
+    </row>
+    <row r="67" ht="15.75" hidden="1" spans="1:7">
+      <c r="A67" s="23">
+        <v>69</v>
+      </c>
+      <c r="B67" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="F59" s="31" t="s">
+      <c r="C67" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E67" s="23"/>
+      <c r="F67" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="G59" s="27"/>
-    </row>
-    <row r="60" ht="15.75" spans="1:7">
-      <c r="A60" s="23">
-        <v>9</v>
-      </c>
-      <c r="B60" s="24" t="s">
+      <c r="G67" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="C60" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="E60" s="48" t="s">
-        <v>167</v>
-      </c>
-      <c r="F60" s="39" t="s">
+    </row>
+    <row r="68" ht="15.75" hidden="1" spans="1:7">
+      <c r="A68" s="23">
+        <v>70</v>
+      </c>
+      <c r="B68" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="G60" s="71" t="s">
+      <c r="C68" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E68" s="23"/>
+      <c r="F68" s="33" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" spans="1:7">
-      <c r="A61" s="23">
-        <v>13</v>
-      </c>
-      <c r="B61" s="24" t="s">
+      <c r="G68" s="65" t="s">
         <v>172</v>
       </c>
-      <c r="C61" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F61" s="35" t="s">
+    </row>
+    <row r="69" ht="31.5" hidden="1" spans="1:7">
+      <c r="A69" s="23">
+        <v>71</v>
+      </c>
+      <c r="B69" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="G61" s="27"/>
-    </row>
-    <row r="62" ht="15.75" spans="1:7">
-      <c r="A62" s="23">
-        <v>15</v>
-      </c>
-      <c r="B62" s="49" t="s">
+      <c r="C69" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E69" s="23"/>
+      <c r="F69" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C62" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E62" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F62" s="50" t="s">
+      <c r="G69" s="65" t="s">
         <v>175</v>
       </c>
-      <c r="G62" s="27"/>
-    </row>
-    <row r="63" ht="15.75" spans="1:7">
-      <c r="A63" s="23">
-        <v>20</v>
-      </c>
-      <c r="B63" s="24" t="s">
+    </row>
+    <row r="70" ht="15.75" hidden="1" spans="1:7">
+      <c r="A70" s="23">
+        <v>72</v>
+      </c>
+      <c r="B70" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="C63" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E63" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F63" s="35" t="s">
+      <c r="C70" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E70" s="23"/>
+      <c r="F70" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="G63" s="27"/>
-    </row>
-    <row r="64" ht="15.75" spans="1:7">
-      <c r="A64" s="23">
-        <v>24</v>
-      </c>
-      <c r="B64" s="24" t="s">
+      <c r="G70" s="65" t="s">
         <v>178</v>
       </c>
-      <c r="C64" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E64" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F64" s="51" t="s">
+    </row>
+    <row r="71" ht="15.75" hidden="1" spans="1:7">
+      <c r="A71" s="23">
+        <v>73</v>
+      </c>
+      <c r="B71" s="24" t="s">
         <v>179</v>
       </c>
-      <c r="G64" s="27"/>
-    </row>
-    <row r="65" ht="15.75" spans="1:7">
-      <c r="A65" s="23">
-        <v>28</v>
-      </c>
-      <c r="B65" s="24" t="s">
+      <c r="C71" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E71" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F71" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="C65" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E65" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F65" s="35" t="s">
+      <c r="G71" s="65" t="s">
         <v>181</v>
       </c>
-      <c r="G65" s="27"/>
-    </row>
-    <row r="66" ht="15.75" spans="1:7">
-      <c r="A66" s="23">
-        <v>29</v>
-      </c>
-      <c r="B66" s="24" t="s">
+    </row>
+    <row r="72" ht="15.75" hidden="1" spans="1:7">
+      <c r="A72" s="23">
+        <v>74</v>
+      </c>
+      <c r="B72" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F66" s="35" t="s">
+      <c r="C72" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E72" s="23"/>
+      <c r="F72" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="G66" s="27"/>
-    </row>
-    <row r="67" ht="15.75" spans="1:7">
-      <c r="A67" s="23">
-        <v>30</v>
-      </c>
-      <c r="B67" s="24" t="s">
+      <c r="G72" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="C67" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E67" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F67" s="35" t="s">
+    </row>
+    <row r="73" ht="15.75" hidden="1" spans="1:7">
+      <c r="A73" s="23">
+        <v>75</v>
+      </c>
+      <c r="B73" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="G67" s="27"/>
-    </row>
-    <row r="68" ht="15.75" spans="1:7">
-      <c r="A68" s="23">
-        <v>32</v>
-      </c>
-      <c r="B68" s="24" t="s">
+      <c r="C73" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F73" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C68" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E68" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F68" s="35" t="s">
+      <c r="G73" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="G68" s="27"/>
-    </row>
-    <row r="69" ht="15.75" spans="1:7">
-      <c r="A69" s="23">
-        <v>34</v>
-      </c>
-      <c r="B69" s="24" t="s">
+    </row>
+    <row r="74" ht="15.75" hidden="1" spans="1:7">
+      <c r="A74" s="23">
+        <v>76</v>
+      </c>
+      <c r="B74" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="C69" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E69" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F69" s="35" t="s">
+      <c r="C74" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E74" s="23"/>
+      <c r="F74" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="G69" s="27"/>
-    </row>
-    <row r="70" ht="15.75" spans="1:7">
-      <c r="A70" s="23">
-        <v>38</v>
-      </c>
-      <c r="B70" s="24" t="s">
+      <c r="G74" s="65" t="s">
         <v>190</v>
       </c>
-      <c r="C70" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F70" s="35" t="s">
+    </row>
+    <row r="75" ht="15.75" hidden="1" spans="1:7">
+      <c r="A75" s="23">
+        <v>77</v>
+      </c>
+      <c r="B75" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="G70" s="71" t="s">
+      <c r="C75" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E75" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F75" s="33" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="71" ht="15.75" spans="1:7">
-      <c r="A71" s="23">
-        <v>39</v>
-      </c>
-      <c r="B71" s="24" t="s">
+      <c r="G75" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="C71" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F71" s="35" t="s">
+    </row>
+    <row r="76" ht="15.75" hidden="1" spans="1:7">
+      <c r="A76" s="23">
+        <v>78</v>
+      </c>
+      <c r="B76" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="G71" s="27"/>
-    </row>
-    <row r="72" ht="15.75" spans="1:7">
-      <c r="A72" s="23">
-        <v>52</v>
-      </c>
-      <c r="B72" s="24" t="s">
+      <c r="C76" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E76" s="23"/>
+      <c r="F76" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="C72" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E72" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="F72" s="35" t="s">
+      <c r="G76" s="26"/>
+    </row>
+    <row r="77" ht="15.75" hidden="1" spans="1:7">
+      <c r="A77" s="23">
+        <v>79</v>
+      </c>
+      <c r="B77" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="G72" s="71" t="s">
+      <c r="C77" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E77" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F77" s="33" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="73" ht="31.5" hidden="1" spans="1:7">
-      <c r="A73" s="23">
+      <c r="G77" s="65" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" hidden="1" spans="1:7">
+      <c r="A78" s="23">
+        <v>80</v>
+      </c>
+      <c r="B78" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="B73" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="C73" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="42" t="s">
-        <v>199</v>
-      </c>
-      <c r="E73" s="42" t="s">
-        <v>167</v>
-      </c>
-      <c r="F73" s="26" t="s">
+      <c r="E78" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F78" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="G73" s="28"/>
-    </row>
-    <row r="74" ht="15.75" spans="1:7">
-      <c r="A74" s="23">
-        <v>127</v>
-      </c>
-      <c r="B74" s="24" t="s">
+      <c r="G78" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="C74" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="E74" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="F74" s="26" t="s">
+    </row>
+    <row r="79" ht="15.75" hidden="1" spans="1:7">
+      <c r="A79" s="23">
+        <v>81</v>
+      </c>
+      <c r="B79" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="G74" s="28"/>
-    </row>
-    <row r="75" ht="15.75" spans="1:7">
-      <c r="A75" s="23">
-        <v>128</v>
-      </c>
-      <c r="B75" s="24" t="s">
+      <c r="C79" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E79" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="F79" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="C75" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="E75" s="52" t="s">
-        <v>167</v>
-      </c>
-      <c r="F75" s="26" t="s">
+      <c r="G79" s="26"/>
+    </row>
+    <row r="80" ht="15.75" hidden="1" spans="1:7">
+      <c r="A80" s="23">
+        <v>82</v>
+      </c>
+      <c r="B80" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="G75" s="28"/>
-    </row>
-    <row r="76" ht="15.75" spans="1:7">
-      <c r="A76" s="23">
-        <v>131</v>
-      </c>
-      <c r="B76" s="27" t="s">
+      <c r="C80" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E80" s="23"/>
+      <c r="F80" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="C76" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E76" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F76" s="26" t="s">
+      <c r="G80" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="G76" s="73" t="s">
+    </row>
+    <row r="81" ht="15.75" hidden="1" spans="1:7">
+      <c r="A81" s="23">
+        <v>83</v>
+      </c>
+      <c r="B81" s="24" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="77" ht="15.75" spans="1:7">
-      <c r="A77" s="23">
-        <v>134</v>
-      </c>
-      <c r="B77" s="27" t="s">
+      <c r="C81" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E81" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F81" s="33" t="s">
         <v>208</v>
       </c>
-      <c r="C77" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E77" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F77" s="26" t="s">
+      <c r="G81" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="G77" s="27"/>
-    </row>
-    <row r="78" ht="15.75" spans="1:7">
-      <c r="A78" s="23">
-        <v>142</v>
-      </c>
-      <c r="B78" s="27" t="s">
+    </row>
+    <row r="82" ht="15.75" hidden="1" spans="1:7">
+      <c r="A82" s="23">
+        <v>84</v>
+      </c>
+      <c r="B82" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="C78" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E78" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F78" s="26" t="s">
+      <c r="C82" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E82" s="32"/>
+      <c r="F82" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="G78" s="27"/>
-    </row>
-    <row r="79" ht="15.75" spans="1:7">
-      <c r="A79" s="29">
-        <v>155</v>
-      </c>
-      <c r="B79" s="28" t="s">
+      <c r="G82" s="26"/>
+    </row>
+    <row r="83" ht="15.75" hidden="1" spans="1:7">
+      <c r="A83" s="23">
+        <v>85</v>
+      </c>
+      <c r="B83" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="C79" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E79" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F79" s="31" t="s">
+      <c r="C83" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E83" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F83" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="G79" s="27"/>
-    </row>
-    <row r="80" ht="15.75" spans="1:7">
-      <c r="A80" s="29">
-        <v>165</v>
-      </c>
-      <c r="B80" s="27" t="s">
+      <c r="G83" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="C80" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E80" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="F80" s="53" t="s">
+    </row>
+    <row r="84" ht="15.75" hidden="1" spans="1:7">
+      <c r="A84" s="23">
+        <v>86</v>
+      </c>
+      <c r="B84" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="G80" s="72" t="s">
+      <c r="C84" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E84" s="32"/>
+      <c r="F84" s="33" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="81" ht="15.75" spans="1:7">
-      <c r="A81" s="23">
-        <v>6</v>
-      </c>
-      <c r="B81" s="24" t="s">
+      <c r="G84" s="26"/>
+    </row>
+    <row r="85" ht="15.75" hidden="1" spans="1:7">
+      <c r="A85" s="23">
+        <v>87</v>
+      </c>
+      <c r="B85" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="C81" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E81" s="23" t="s">
+      <c r="C85" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E85" s="32"/>
+      <c r="F85" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="F81" s="31" t="s">
+      <c r="G85" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="G81" s="71" t="s">
+    </row>
+    <row r="86" ht="15.75" hidden="1" spans="1:7">
+      <c r="A86" s="23">
+        <v>88</v>
+      </c>
+      <c r="B86" s="24" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="82" ht="15.75" spans="1:7">
-      <c r="A82" s="23">
-        <v>1</v>
-      </c>
-      <c r="B82" s="24" t="s">
+      <c r="C86" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" s="35"/>
+      <c r="F86" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="C82" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E82" s="23" t="s">
+      <c r="G86" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="F82" s="31" t="s">
+    </row>
+    <row r="87" ht="15.75" hidden="1" spans="1:7">
+      <c r="A87" s="23">
+        <v>89</v>
+      </c>
+      <c r="B87" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="G82" s="27"/>
-    </row>
-    <row r="83" ht="15.75" spans="1:7">
-      <c r="A83" s="23">
-        <v>2</v>
-      </c>
-      <c r="B83" s="24" t="s">
+      <c r="C87" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E87" s="23"/>
+      <c r="F87" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="C83" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E83" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F83" s="35" t="s">
+      <c r="G87" s="65" t="s">
         <v>225</v>
       </c>
-      <c r="G83" s="27"/>
-    </row>
-    <row r="84" ht="15.75" spans="1:7">
-      <c r="A84" s="23">
-        <v>3</v>
-      </c>
-      <c r="B84" s="24" t="s">
+    </row>
+    <row r="88" ht="15.75" hidden="1" spans="1:7">
+      <c r="A88" s="23">
+        <v>90</v>
+      </c>
+      <c r="B88" s="24" t="s">
         <v>226</v>
       </c>
-      <c r="C84" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E84" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F84" s="35" t="s">
+      <c r="C88" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E88" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="F88" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="G84" s="27"/>
-    </row>
-    <row r="85" ht="15.75" spans="1:7">
-      <c r="A85" s="23">
-        <v>4</v>
-      </c>
-      <c r="B85" s="24" t="s">
+      <c r="G88" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="C85" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E85" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F85" s="35" t="s">
+    </row>
+    <row r="89" ht="15.75" hidden="1" spans="1:7">
+      <c r="A89" s="23">
+        <v>91</v>
+      </c>
+      <c r="B89" s="24" t="s">
         <v>229</v>
       </c>
-      <c r="G85" s="27"/>
-    </row>
-    <row r="86" ht="15.75" spans="1:7">
-      <c r="A86" s="23">
-        <v>5</v>
-      </c>
-      <c r="B86" s="24" t="s">
+      <c r="C89" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E89" s="23"/>
+      <c r="F89" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="C86" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E86" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F86" s="35" t="s">
+      <c r="G89" s="65" t="s">
         <v>231</v>
       </c>
-      <c r="G86" s="27"/>
-    </row>
-    <row r="87" ht="15.75" spans="1:7">
-      <c r="A87" s="23">
-        <v>7</v>
-      </c>
-      <c r="B87" s="24" t="s">
+    </row>
+    <row r="90" ht="15.75" hidden="1" spans="1:7">
+      <c r="A90" s="23">
+        <v>92</v>
+      </c>
+      <c r="B90" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="C87" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E87" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F87" s="31" t="s">
+      <c r="C90" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E90" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="G87" s="71" t="s">
+      <c r="F90" s="33" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="88" ht="15.75" spans="1:7">
-      <c r="A88" s="23">
-        <v>10</v>
-      </c>
-      <c r="B88" s="24" t="s">
+      <c r="G90" s="65" t="s">
         <v>235</v>
       </c>
-      <c r="C88" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E88" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F88" s="31" t="s">
+    </row>
+    <row r="91" ht="15.75" hidden="1" spans="1:7">
+      <c r="A91" s="23">
+        <v>93</v>
+      </c>
+      <c r="B91" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="G88" s="27"/>
-    </row>
-    <row r="89" ht="15.75" spans="1:7">
-      <c r="A89" s="23">
-        <v>11</v>
-      </c>
-      <c r="B89" s="24" t="s">
+      <c r="C91" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E91" s="23"/>
+      <c r="F91" s="33" t="s">
         <v>237</v>
       </c>
-      <c r="C89" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E89" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F89" s="35" t="s">
+      <c r="G91" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="G89" s="27"/>
-    </row>
-    <row r="90" ht="15.75" spans="1:7">
-      <c r="A90" s="23">
-        <v>12</v>
-      </c>
-      <c r="B90" s="24" t="s">
+    </row>
+    <row r="92" ht="15.75" hidden="1" spans="1:7">
+      <c r="A92" s="23">
+        <v>94</v>
+      </c>
+      <c r="B92" s="24" t="s">
         <v>239</v>
       </c>
-      <c r="C90" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F90" s="35" t="s">
+      <c r="C92" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E92" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F92" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="G90" s="27"/>
-    </row>
-    <row r="91" ht="15.75" spans="1:7">
-      <c r="A91" s="23">
-        <v>14</v>
-      </c>
-      <c r="B91" s="24" t="s">
+      <c r="G92" s="65" t="s">
         <v>241</v>
       </c>
-      <c r="C91" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E91" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F91" s="35" t="s">
+    </row>
+    <row r="93" ht="15.75" hidden="1" spans="1:7">
+      <c r="A93" s="23">
+        <v>95</v>
+      </c>
+      <c r="B93" s="24" t="s">
         <v>242</v>
       </c>
-      <c r="G91" s="27"/>
-    </row>
-    <row r="92" ht="15.75" spans="1:7">
-      <c r="A92" s="23">
-        <v>17</v>
-      </c>
-      <c r="B92" s="24" t="s">
+      <c r="C93" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E93" s="23"/>
+      <c r="F93" s="33" t="s">
         <v>243</v>
       </c>
-      <c r="C92" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E92" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F92" s="35" t="s">
+      <c r="G93" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="G92" s="27"/>
-    </row>
-    <row r="93" ht="15.75" spans="1:7">
-      <c r="A93" s="23">
-        <v>19</v>
-      </c>
-      <c r="B93" s="24" t="s">
+    </row>
+    <row r="94" ht="31.5" hidden="1" spans="1:7">
+      <c r="A94" s="23">
+        <v>96</v>
+      </c>
+      <c r="B94" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="C93" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E93" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F93" s="35" t="s">
+      <c r="C94" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E94" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="G93" s="27"/>
-    </row>
-    <row r="94" ht="15.75" spans="1:7">
-      <c r="A94" s="23">
-        <v>21</v>
-      </c>
-      <c r="B94" s="24" t="s">
+      <c r="F94" s="33" t="s">
         <v>247</v>
       </c>
-      <c r="C94" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E94" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F94" s="35" t="s">
+      <c r="G94" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="G94" s="27"/>
-    </row>
-    <row r="95" ht="15.75" spans="1:7">
+    </row>
+    <row r="95" ht="15.75" hidden="1" spans="1:7">
       <c r="A95" s="23">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="B95" s="24" t="s">
         <v>249</v>
@@ -4848,632 +4784,594 @@
         <v>8</v>
       </c>
       <c r="D95" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E95" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="F95" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="G95" s="26" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" hidden="1" spans="1:7">
+      <c r="A96" s="23">
+        <v>98</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E96" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F96" s="33" t="s">
+        <v>253</v>
+      </c>
+      <c r="G96" s="26" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" hidden="1" spans="1:7">
+      <c r="A97" s="23">
+        <v>99</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="C97" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E97" s="23"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="26"/>
+    </row>
+    <row r="98" ht="15.75" hidden="1" spans="1:7">
+      <c r="A98" s="23">
+        <v>100</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="C98" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E98" s="35"/>
+      <c r="F98" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="G98" s="26" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" hidden="1" spans="1:7">
+      <c r="A99" s="23">
+        <v>101</v>
+      </c>
+      <c r="B99" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C99" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E99" s="32"/>
+      <c r="F99" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="G99" s="26"/>
+    </row>
+    <row r="100" ht="15.75" hidden="1" spans="1:7">
+      <c r="A100" s="23">
+        <v>102</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="C100" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E100" s="35"/>
+      <c r="F100" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="G100" s="26" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" hidden="1" spans="1:7">
+      <c r="A101" s="23">
+        <v>103</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="C101" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E101" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="F101" s="33" t="s">
+        <v>265</v>
+      </c>
+      <c r="G101" s="26" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" hidden="1" spans="1:7">
+      <c r="A102" s="23">
+        <v>104</v>
+      </c>
+      <c r="B102" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="C102" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E102" s="35"/>
+      <c r="F102" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="G102" s="26" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" hidden="1" spans="1:7">
+      <c r="A103" s="23">
         <v>105</v>
       </c>
-      <c r="E95" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F95" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="G95" s="27"/>
-    </row>
-    <row r="96" ht="15.75" spans="1:7">
-      <c r="A96" s="23">
-        <v>23</v>
-      </c>
-      <c r="B96" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C96" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="23" t="s">
+      <c r="B103" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="C103" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E103" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="F103" s="33" t="s">
+        <v>271</v>
+      </c>
+      <c r="G103" s="66" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" hidden="1" spans="1:7">
+      <c r="A104" s="23">
+        <v>106</v>
+      </c>
+      <c r="B104" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="C104" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="E104" s="23" t="s">
+        <v>274</v>
+      </c>
+      <c r="F104" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="G104" s="26"/>
+    </row>
+    <row r="105" ht="15.75" hidden="1" spans="1:7">
+      <c r="A105" s="23">
+        <v>107</v>
+      </c>
+      <c r="B105" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E105" s="46"/>
+      <c r="F105" s="33" t="s">
+        <v>277</v>
+      </c>
+      <c r="G105" s="28"/>
+    </row>
+    <row r="106" ht="15.75" hidden="1" spans="1:7">
+      <c r="A106" s="23">
+        <v>108</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E106" s="46"/>
+      <c r="F106" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="G106" s="28"/>
+    </row>
+    <row r="107" ht="15.75" hidden="1" spans="1:7">
+      <c r="A107" s="23">
         <v>109</v>
       </c>
-      <c r="E96" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F96" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="G96" s="27"/>
-    </row>
-    <row r="97" ht="15.75" spans="1:7">
-      <c r="A97" s="23">
-        <v>25</v>
-      </c>
-      <c r="B97" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="C97" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E97" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F97" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="G97" s="27"/>
-    </row>
-    <row r="98" ht="15.75" spans="1:7">
-      <c r="A98" s="23">
-        <v>27</v>
-      </c>
-      <c r="B98" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="C98" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E98" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F98" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="G98" s="27"/>
-    </row>
-    <row r="99" ht="15.75" spans="1:7">
-      <c r="A99" s="23">
-        <v>31</v>
-      </c>
-      <c r="B99" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="C99" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E99" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F99" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="G99" s="27"/>
-    </row>
-    <row r="100" ht="15.75" spans="1:7">
-      <c r="A100" s="23">
-        <v>35</v>
-      </c>
-      <c r="B100" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C100" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E100" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F100" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="G100" s="27"/>
-    </row>
-    <row r="101" ht="15.75" spans="1:7">
-      <c r="A101" s="23">
-        <v>36</v>
-      </c>
-      <c r="B101" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="C101" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D101" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E101" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F101" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="G101" s="72" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" spans="1:7">
-      <c r="A102" s="23">
-        <v>37</v>
-      </c>
-      <c r="B102" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="C102" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D102" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E102" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F102" s="35" t="s">
-        <v>265</v>
-      </c>
-      <c r="G102" s="27"/>
-    </row>
-    <row r="103" ht="15.75" spans="1:7">
-      <c r="A103" s="23">
-        <v>40</v>
-      </c>
-      <c r="B103" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="C103" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E103" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F103" s="35" t="s">
-        <v>267</v>
-      </c>
-      <c r="G103" s="27"/>
-    </row>
-    <row r="104" ht="15.75" spans="1:7">
-      <c r="A104" s="23">
-        <v>41</v>
-      </c>
-      <c r="B104" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="C104" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E104" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F104" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="G104" s="27"/>
-    </row>
-    <row r="105" ht="15.75" spans="1:7">
-      <c r="A105" s="23">
-        <v>42</v>
-      </c>
-      <c r="B105" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="C105" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E105" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F105" s="35" t="s">
+      <c r="B107" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E107" s="46"/>
+      <c r="F107" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="G107" s="28"/>
+    </row>
+    <row r="108" ht="15.75" hidden="1" spans="1:7">
+      <c r="A108" s="23">
+        <v>110</v>
+      </c>
+      <c r="B108" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E108" s="46"/>
+      <c r="F108" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="G108" s="28"/>
+    </row>
+    <row r="109" ht="31.5" hidden="1" spans="1:7">
+      <c r="A109" s="23">
+        <v>111</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E109" s="46"/>
+      <c r="F109" s="33" t="s">
+        <v>285</v>
+      </c>
+      <c r="G109" s="28"/>
+    </row>
+    <row r="110" ht="15.75" hidden="1" spans="1:7">
+      <c r="A110" s="23">
+        <v>112</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E110" s="46"/>
+      <c r="F110" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="G110" s="28"/>
+    </row>
+    <row r="111" ht="15.75" hidden="1" spans="1:7">
+      <c r="A111" s="23">
+        <v>113</v>
+      </c>
+      <c r="B111" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E111" s="46"/>
+      <c r="F111" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="G105" s="27"/>
-    </row>
-    <row r="106" ht="15.75" spans="1:7">
-      <c r="A106" s="23">
-        <v>43</v>
-      </c>
-      <c r="B106" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="C106" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E106" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F106" s="35" t="s">
-        <v>273</v>
-      </c>
-      <c r="G106" s="27"/>
-    </row>
-    <row r="107" ht="15.75" spans="1:7">
-      <c r="A107" s="23">
-        <v>44</v>
-      </c>
-      <c r="B107" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="C107" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E107" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F107" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="G107" s="27"/>
-    </row>
-    <row r="108" ht="15.75" spans="1:7">
-      <c r="A108" s="23">
-        <v>45</v>
-      </c>
-      <c r="B108" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D108" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E108" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F108" s="35" t="s">
-        <v>277</v>
-      </c>
-      <c r="G108" s="27"/>
-    </row>
-    <row r="109" ht="15.75" spans="1:7">
-      <c r="A109" s="23">
-        <v>47</v>
-      </c>
-      <c r="B109" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="C109" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E109" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F109" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="G109" s="27"/>
-    </row>
-    <row r="110" ht="15.75" spans="1:7">
-      <c r="A110" s="23">
-        <v>48</v>
-      </c>
-      <c r="B110" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="C110" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E110" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F110" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="G110" s="27"/>
-    </row>
-    <row r="111" ht="15.75" spans="1:7">
-      <c r="A111" s="23">
-        <v>49</v>
-      </c>
-      <c r="B111" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C111" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E111" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F111" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="G111" s="27"/>
-    </row>
-    <row r="112" s="15" customFormat="1" ht="15.75" spans="1:7">
+      <c r="G111" s="28"/>
+    </row>
+    <row r="112" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
       <c r="A112" s="23">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="B112" s="24" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C112" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D112" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E112" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F112" s="35" t="s">
-        <v>285</v>
-      </c>
-      <c r="G112" s="27"/>
-    </row>
-    <row r="113" ht="15.75" spans="1:7">
+      <c r="D112" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E112" s="46"/>
+      <c r="F112" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="G112" s="28"/>
+    </row>
+    <row r="113" ht="15.75" hidden="1" spans="1:7">
       <c r="A113" s="23">
-        <v>51</v>
+        <v>115</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C113" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D113" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E113" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F113" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="G113" s="27"/>
-    </row>
-    <row r="114" ht="15.75" spans="1:7">
+      <c r="D113" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E113" s="45" t="s">
+        <v>137</v>
+      </c>
+      <c r="F113" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="G113" s="28"/>
+    </row>
+    <row r="114" ht="15.75" hidden="1" spans="1:7">
       <c r="A114" s="23">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C114" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D114" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E114" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F114" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="G114" s="27"/>
+      <c r="D114" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E114" s="46"/>
+      <c r="F114" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="G114" s="28"/>
     </row>
     <row r="115" ht="15.75" hidden="1" spans="1:7">
       <c r="A115" s="23">
-        <v>124</v>
-      </c>
-      <c r="B115" s="24" t="s">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="B115" s="24"/>
       <c r="C115" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D115" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E115" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="F115" s="26" t="s">
-        <v>291</v>
+      <c r="D115" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E115" s="46"/>
+      <c r="F115" s="33" t="s">
+        <v>295</v>
       </c>
       <c r="G115" s="28"/>
     </row>
-    <row r="116" ht="15.75" spans="1:7">
+    <row r="116" ht="15.75" hidden="1" spans="1:7">
       <c r="A116" s="23">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B116" s="24" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C116" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D116" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="E116" s="52" t="s">
-        <v>222</v>
-      </c>
-      <c r="F116" s="26" t="s">
-        <v>293</v>
-      </c>
-      <c r="G116" s="71" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" spans="1:7">
+      <c r="D116" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E116" s="46"/>
+      <c r="F116" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="G116" s="28"/>
+    </row>
+    <row r="117" ht="15.75" hidden="1" spans="1:7">
       <c r="A117" s="23">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="B117" s="24" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C117" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D117" s="29" t="s">
-        <v>105</v>
-      </c>
-      <c r="E117" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="F117" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="G117" s="27"/>
-    </row>
-    <row r="118" ht="15.75" spans="1:7">
+      <c r="D117" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E117" s="46"/>
+      <c r="F117" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="G117" s="28"/>
+    </row>
+    <row r="118" ht="15.75" hidden="1" spans="1:7">
       <c r="A118" s="23">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="B118" s="24" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C118" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D118" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E118" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>298</v>
-      </c>
-      <c r="G118" s="27"/>
-    </row>
-    <row r="119" ht="15.75" spans="1:7">
+      <c r="D118" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E118" s="46"/>
+      <c r="F118" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="G118" s="28"/>
+    </row>
+    <row r="119" ht="15.75" hidden="1" spans="1:7">
       <c r="A119" s="23">
-        <v>149</v>
-      </c>
-      <c r="B119" s="30" t="s">
-        <v>299</v>
+        <v>121</v>
+      </c>
+      <c r="B119" s="24" t="s">
+        <v>302</v>
       </c>
       <c r="C119" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D119" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E119" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="F119" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="G119" s="27"/>
-    </row>
-    <row r="120" ht="15.75" spans="1:7">
-      <c r="A120" s="29">
-        <v>154</v>
-      </c>
-      <c r="B120" s="28" t="s">
-        <v>301</v>
+      <c r="D119" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E119" s="46"/>
+      <c r="F119" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="G119" s="28"/>
+    </row>
+    <row r="120" ht="15.75" hidden="1" spans="1:7">
+      <c r="A120" s="23">
+        <v>122</v>
+      </c>
+      <c r="B120" s="24" t="s">
+        <v>304</v>
       </c>
       <c r="C120" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D120" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E120" s="29" t="s">
-        <v>222</v>
-      </c>
-      <c r="F120" s="31" t="s">
-        <v>302</v>
-      </c>
-      <c r="G120" s="27"/>
-    </row>
-    <row r="121" ht="15.75" spans="1:7">
+      <c r="D120" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E120" s="46"/>
+      <c r="F120" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="G120" s="47"/>
+    </row>
+    <row r="121" ht="15.75" hidden="1" spans="1:7">
       <c r="A121" s="23">
-        <v>139</v>
-      </c>
-      <c r="B121" s="27" t="s">
-        <v>303</v>
+        <v>123</v>
+      </c>
+      <c r="B121" s="24" t="s">
+        <v>306</v>
       </c>
       <c r="C121" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D121" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E121" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="F121" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="G121" s="27"/>
+      <c r="D121" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E121" s="46"/>
+      <c r="F121" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="G121" s="28"/>
     </row>
     <row r="122" ht="15.75" hidden="1" spans="1:7">
       <c r="A122" s="23">
-        <v>55</v>
+        <v>124</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C122" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D122" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="54"/>
-      <c r="F122" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="G122" s="27" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="123" ht="15.75" hidden="1" spans="1:7">
+      <c r="D122" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E122" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="G122" s="28"/>
+    </row>
+    <row r="123" ht="31.5" hidden="1" spans="1:7">
       <c r="A123" s="23">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="B123" s="24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C123" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D123" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="56"/>
-      <c r="F123" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="G123" s="57" t="s">
+      <c r="D123" s="45" t="s">
         <v>311</v>
       </c>
+      <c r="E123" s="45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F123" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="G123" s="28"/>
     </row>
     <row r="124" ht="15.75" hidden="1" spans="1:7">
       <c r="A124" s="23">
-        <v>62</v>
+        <v>126</v>
       </c>
       <c r="B124" s="24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C124" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D124" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="48"/>
-      <c r="F124" s="58" t="s">
-        <v>313</v>
-      </c>
-      <c r="G124" s="27" t="s">
+      <c r="D124" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="E124" s="46"/>
+      <c r="F124" s="33" t="s">
         <v>314</v>
       </c>
+      <c r="G124" s="28"/>
     </row>
     <row r="125" ht="15.75" hidden="1" spans="1:7">
       <c r="A125" s="23">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="B125" s="24" t="s">
         <v>315</v>
@@ -5481,848 +5379,932 @@
       <c r="C125" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="23" t="s">
+      <c r="D125" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E125" s="29"/>
-      <c r="F125" s="26" t="s">
+      <c r="E125" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="G125" s="27" t="s">
-        <v>317</v>
-      </c>
+      <c r="G125" s="28"/>
     </row>
     <row r="126" ht="15.75" hidden="1" spans="1:7">
       <c r="A126" s="23">
-        <v>66</v>
+        <v>128</v>
       </c>
       <c r="B126" s="24" t="s">
+        <v>317</v>
+      </c>
+      <c r="C126" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F126" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="C126" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="32"/>
-      <c r="F126" s="59" t="s">
-        <v>319</v>
-      </c>
-      <c r="G126" s="27" t="s">
-        <v>320</v>
-      </c>
+      <c r="G126" s="28"/>
     </row>
     <row r="127" ht="15.75" hidden="1" spans="1:7">
       <c r="A127" s="23">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="B127" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="C127" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="45" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F127" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="G127" s="65" t="s">
         <v>321</v>
-      </c>
-      <c r="C127" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="29"/>
-      <c r="F127" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="G127" s="72" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="128" ht="15.75" hidden="1" spans="1:7">
       <c r="A128" s="23">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="B128" s="24" t="s">
+        <v>322</v>
+      </c>
+      <c r="C128" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E128" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F128" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="G128" s="67" t="s">
         <v>324</v>
-      </c>
-      <c r="C128" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="60"/>
-      <c r="F128" s="26" t="s">
-        <v>325</v>
-      </c>
-      <c r="G128" s="75" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="129" ht="15.75" hidden="1" spans="1:7">
       <c r="A129" s="23">
-        <v>70</v>
-      </c>
-      <c r="B129" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="B129" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="C129" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F129" s="33" t="s">
+        <v>326</v>
+      </c>
+      <c r="G129" s="67" t="s">
         <v>327</v>
       </c>
-      <c r="C129" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" s="60"/>
-      <c r="F129" s="26" t="s">
+    </row>
+    <row r="130" ht="15.75" hidden="1" spans="1:7">
+      <c r="A130" s="23">
+        <v>132</v>
+      </c>
+      <c r="B130" s="50" t="s">
         <v>328</v>
       </c>
-      <c r="G129" s="75" t="s">
+      <c r="C130" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E130" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F130" s="33" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="130" ht="31.5" hidden="1" spans="1:7">
-      <c r="A130" s="23">
-        <v>71</v>
-      </c>
-      <c r="B130" s="49" t="s">
+      <c r="G130" s="67" t="s">
         <v>330</v>
-      </c>
-      <c r="C130" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D130" s="62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" s="60"/>
-      <c r="F130" s="58" t="s">
-        <v>331</v>
-      </c>
-      <c r="G130" s="75" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="131" ht="15.75" hidden="1" spans="1:7">
       <c r="A131" s="23">
-        <v>72</v>
-      </c>
-      <c r="B131" s="49" t="s">
-        <v>333</v>
+        <v>133</v>
+      </c>
+      <c r="B131" s="50" t="s">
+        <v>306</v>
       </c>
       <c r="C131" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D131" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" s="60"/>
-      <c r="F131" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="G131" s="75" t="s">
-        <v>335</v>
+      <c r="D131" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E131" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F131" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="G131" s="67" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="132" ht="15.75" hidden="1" spans="1:7">
       <c r="A132" s="23">
-        <v>74</v>
-      </c>
-      <c r="B132" s="49" t="s">
-        <v>336</v>
+        <v>134</v>
+      </c>
+      <c r="B132" s="50" t="s">
+        <v>332</v>
       </c>
       <c r="C132" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D132" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="60"/>
-      <c r="F132" s="26" t="s">
-        <v>337</v>
-      </c>
-      <c r="G132" s="63" t="s">
-        <v>338</v>
-      </c>
+      <c r="D132" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="E132" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F132" s="33" t="s">
+        <v>333</v>
+      </c>
+      <c r="G132" s="50"/>
     </row>
     <row r="133" ht="15.75" hidden="1" spans="1:7">
       <c r="A133" s="23">
-        <v>76</v>
-      </c>
-      <c r="B133" s="49" t="s">
-        <v>339</v>
+        <v>135</v>
+      </c>
+      <c r="B133" s="50" t="s">
+        <v>334</v>
       </c>
       <c r="C133" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D133" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="60"/>
-      <c r="F133" s="26" t="s">
-        <v>340</v>
-      </c>
-      <c r="G133" s="75" t="s">
-        <v>341</v>
+      <c r="D133" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E133" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F133" s="33" t="s">
+        <v>335</v>
+      </c>
+      <c r="G133" s="49" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="134" ht="15.75" hidden="1" spans="1:7">
       <c r="A134" s="23">
-        <v>78</v>
-      </c>
-      <c r="B134" s="49" t="s">
-        <v>342</v>
+        <v>136</v>
+      </c>
+      <c r="B134" s="50" t="s">
+        <v>337</v>
       </c>
       <c r="C134" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D134" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="60"/>
-      <c r="F134" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="G134" s="63"/>
+      <c r="D134" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E134" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F134" s="33" t="s">
+        <v>338</v>
+      </c>
+      <c r="G134" s="67" t="s">
+        <v>339</v>
+      </c>
     </row>
     <row r="135" ht="15.75" hidden="1" spans="1:7">
       <c r="A135" s="23">
-        <v>82</v>
-      </c>
-      <c r="B135" s="49" t="s">
-        <v>344</v>
+        <v>137</v>
+      </c>
+      <c r="B135" s="50" t="s">
+        <v>340</v>
       </c>
       <c r="C135" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D135" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="60"/>
-      <c r="F135" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="G135" s="63" t="s">
-        <v>346</v>
+      <c r="D135" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E135" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F135" s="33" t="s">
+        <v>341</v>
+      </c>
+      <c r="G135" s="67" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="136" ht="15.75" hidden="1" spans="1:7">
       <c r="A136" s="23">
-        <v>84</v>
-      </c>
-      <c r="B136" s="24" t="s">
-        <v>347</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="B136" s="24"/>
       <c r="C136" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D136" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E136" s="64"/>
-      <c r="F136" s="26" t="s">
-        <v>348</v>
-      </c>
-      <c r="G136" s="63"/>
+      <c r="D136" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E136" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F136" s="33" t="s">
+        <v>343</v>
+      </c>
+      <c r="G136" s="67" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="137" ht="15.75" hidden="1" spans="1:7">
       <c r="A137" s="23">
-        <v>86</v>
-      </c>
-      <c r="B137" s="49" t="s">
-        <v>349</v>
+        <v>139</v>
+      </c>
+      <c r="B137" s="50" t="s">
+        <v>345</v>
       </c>
       <c r="C137" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D137" s="62" t="s">
+      <c r="D137" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="E137" s="64"/>
-      <c r="F137" s="26" t="s">
-        <v>350</v>
-      </c>
-      <c r="G137" s="63"/>
+      <c r="E137" s="48" t="s">
+        <v>346</v>
+      </c>
+      <c r="F137" s="33" t="s">
+        <v>347</v>
+      </c>
+      <c r="G137" s="50"/>
     </row>
     <row r="138" ht="15.75" hidden="1" spans="1:7">
       <c r="A138" s="23">
-        <v>87</v>
-      </c>
-      <c r="B138" s="49" t="s">
-        <v>351</v>
+        <v>140</v>
+      </c>
+      <c r="B138" s="50" t="s">
+        <v>348</v>
       </c>
       <c r="C138" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D138" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E138" s="64"/>
-      <c r="F138" s="26" t="s">
-        <v>352</v>
-      </c>
-      <c r="G138" s="63" t="s">
-        <v>353</v>
+      <c r="D138" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E138" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="F138" s="33" t="s">
+        <v>349</v>
+      </c>
+      <c r="G138" s="68" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="139" ht="15.75" hidden="1" spans="1:7">
       <c r="A139" s="23">
-        <v>88</v>
-      </c>
-      <c r="B139" s="49" t="s">
-        <v>354</v>
+        <v>141</v>
+      </c>
+      <c r="B139" s="50" t="s">
+        <v>351</v>
       </c>
       <c r="C139" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D139" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" s="65"/>
-      <c r="F139" s="26" t="s">
-        <v>355</v>
-      </c>
-      <c r="G139" s="63" t="s">
-        <v>356</v>
-      </c>
+      <c r="D139" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="E139" s="48" t="s">
+        <v>233</v>
+      </c>
+      <c r="F139" s="33" t="s">
+        <v>352</v>
+      </c>
+      <c r="G139" s="50"/>
     </row>
     <row r="140" ht="15.75" hidden="1" spans="1:7">
       <c r="A140" s="23">
-        <v>89</v>
-      </c>
-      <c r="B140" s="49" t="s">
-        <v>357</v>
+        <v>142</v>
+      </c>
+      <c r="B140" s="50" t="s">
+        <v>353</v>
       </c>
       <c r="C140" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D140" s="60" t="s">
+      <c r="D140" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="E140" s="60"/>
-      <c r="F140" s="26" t="s">
-        <v>358</v>
-      </c>
-      <c r="G140" s="75" t="s">
-        <v>359</v>
-      </c>
+      <c r="E140" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F140" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="G140" s="50"/>
     </row>
     <row r="141" ht="15.75" hidden="1" spans="1:7">
       <c r="A141" s="23">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="B141" s="24" t="s">
-        <v>360</v>
+        <v>191</v>
       </c>
       <c r="C141" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E141" s="23"/>
-      <c r="F141" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="G141" s="71" t="s">
-        <v>362</v>
+        <v>125</v>
+      </c>
+      <c r="E141" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F141" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="G141" s="26" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="142" ht="15.75" hidden="1" spans="1:7">
       <c r="A142" s="23">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="B142" s="24" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="C142" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D142" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E142" s="23"/>
-      <c r="F142" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="G142" s="63" t="s">
-        <v>365</v>
-      </c>
+      <c r="D142" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E142" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F142" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="G142" s="50"/>
     </row>
     <row r="143" ht="15.75" hidden="1" spans="1:7">
       <c r="A143" s="23">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="B143" s="24" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C143" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D143" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E143" s="23"/>
-      <c r="F143" s="26" t="s">
-        <v>367</v>
-      </c>
-      <c r="G143" s="63" t="s">
-        <v>368</v>
+      <c r="D143" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E143" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F143" s="33" t="s">
+        <v>358</v>
+      </c>
+      <c r="G143" s="50" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="144" ht="19" hidden="1" customHeight="1" spans="1:7">
       <c r="A144" s="23">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="B144" s="24" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="C144" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D144" s="23" t="s">
+      <c r="D144" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E144" s="23"/>
-      <c r="F144" s="26"/>
-      <c r="G144" s="27"/>
+      <c r="E144" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="G144" s="26"/>
     </row>
     <row r="145" ht="15.75" hidden="1" spans="1:7">
       <c r="A145" s="23">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="B145" s="24" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="C145" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D145" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E145" s="32"/>
-      <c r="F145" s="35" t="s">
-        <v>371</v>
-      </c>
-      <c r="G145" s="27" t="s">
-        <v>372</v>
-      </c>
+      <c r="D145" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E145" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F145" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="G145" s="26"/>
     </row>
     <row r="146" ht="15.75" hidden="1" spans="1:7">
       <c r="A146" s="23">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="B146" s="24" t="s">
-        <v>373</v>
+        <v>298</v>
       </c>
       <c r="C146" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D146" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E146" s="29"/>
-      <c r="F146" s="35" t="s">
-        <v>374</v>
-      </c>
-      <c r="G146" s="63"/>
+      <c r="D146" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E146" s="32"/>
+      <c r="F146" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="G146" s="69" t="s">
+        <v>364</v>
+      </c>
     </row>
     <row r="147" ht="15.75" hidden="1" spans="1:7">
       <c r="A147" s="23">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="B147" s="24" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="C147" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D147" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="32"/>
-      <c r="F147" s="26" t="s">
-        <v>376</v>
-      </c>
-      <c r="G147" s="27" t="s">
-        <v>377</v>
+      <c r="D147" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E147" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F147" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="G147" s="66" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="148" ht="15.75" hidden="1" spans="1:7">
       <c r="A148" s="23">
-        <v>104</v>
-      </c>
-      <c r="B148" s="24" t="s">
-        <v>378</v>
+        <v>149</v>
+      </c>
+      <c r="B148" s="53" t="s">
+        <v>368</v>
       </c>
       <c r="C148" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D148" s="23" t="s">
+      <c r="D148" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E148" s="32"/>
-      <c r="F148" s="26" t="s">
-        <v>379</v>
-      </c>
-      <c r="G148" s="27" t="s">
-        <v>380</v>
-      </c>
+      <c r="E148" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="G148" s="26"/>
     </row>
     <row r="149" ht="15.75" hidden="1" spans="1:7">
       <c r="A149" s="23">
-        <v>107</v>
-      </c>
-      <c r="B149" s="66" t="s">
+        <v>150</v>
+      </c>
+      <c r="B149" s="54" t="s">
+        <v>370</v>
+      </c>
+      <c r="C149" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E149" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F149" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="G149" s="55"/>
+    </row>
+    <row r="150" ht="15.75" hidden="1" spans="1:7">
+      <c r="A150" s="32">
+        <v>151</v>
+      </c>
+      <c r="B150" s="53" t="s">
+        <v>372</v>
+      </c>
+      <c r="C150" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E150" s="32"/>
+      <c r="F150" s="25" t="s">
+        <v>373</v>
+      </c>
+      <c r="G150" s="55"/>
+    </row>
+    <row r="151" ht="15.75" hidden="1" spans="1:7">
+      <c r="A151" s="32">
+        <v>152</v>
+      </c>
+      <c r="B151" s="53" t="s">
+        <v>374</v>
+      </c>
+      <c r="C151" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E151" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F151" s="56" t="s">
+        <v>375</v>
+      </c>
+      <c r="G151" s="26"/>
+    </row>
+    <row r="152" ht="15.75" hidden="1" spans="1:7">
+      <c r="A152" s="32">
+        <v>153</v>
+      </c>
+      <c r="B152" s="26" t="s">
+        <v>376</v>
+      </c>
+      <c r="C152" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E152" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F152" s="25" t="s">
+        <v>377</v>
+      </c>
+      <c r="G152" s="26"/>
+    </row>
+    <row r="153" ht="15.75" hidden="1" spans="1:7">
+      <c r="A153" s="32">
+        <v>153</v>
+      </c>
+      <c r="B153" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="C153" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E153" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F153" s="25" t="s">
+        <v>379</v>
+      </c>
+      <c r="G153" s="26"/>
+    </row>
+    <row r="154" ht="15.75" hidden="1" spans="1:7">
+      <c r="A154" s="32">
+        <v>154</v>
+      </c>
+      <c r="B154" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="C154" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" s="25" t="s">
         <v>381</v>
       </c>
-      <c r="C149" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D149" s="42" t="s">
+      <c r="G154" s="26"/>
+    </row>
+    <row r="155" ht="15.75" hidden="1" spans="1:7">
+      <c r="A155" s="32">
+        <v>155</v>
+      </c>
+      <c r="B155" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="C155" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E149" s="52"/>
-      <c r="F149" s="26" t="s">
-        <v>382</v>
-      </c>
-      <c r="G149" s="67"/>
-    </row>
-    <row r="150" ht="15.75" hidden="1" spans="1:7">
-      <c r="A150" s="23">
-        <v>108</v>
-      </c>
-      <c r="B150" s="24" t="s">
+      <c r="E155" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F155" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="C150" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="42" t="s">
+      <c r="G155" s="26"/>
+    </row>
+    <row r="156" ht="15.75" hidden="1" spans="1:7">
+      <c r="A156" s="32">
+        <v>156</v>
+      </c>
+      <c r="B156" s="28" t="s">
+        <v>384</v>
+      </c>
+      <c r="C156" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E156" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F156" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="G156" s="26"/>
+    </row>
+    <row r="157" ht="15.75" hidden="1" spans="1:7">
+      <c r="A157" s="32">
+        <v>156</v>
+      </c>
+      <c r="B157" s="57" t="s">
+        <v>386</v>
+      </c>
+      <c r="C157" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E157" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F157" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="G157" s="26"/>
+    </row>
+    <row r="158" ht="15.75" hidden="1" spans="1:7">
+      <c r="A158" s="32">
+        <v>157</v>
+      </c>
+      <c r="B158" s="28" t="s">
+        <v>388</v>
+      </c>
+      <c r="C158" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E158" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F158" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="G158" s="26"/>
+    </row>
+    <row r="159" ht="15.75" hidden="1" spans="1:7">
+      <c r="A159" s="32">
+        <v>157</v>
+      </c>
+      <c r="B159" s="57" t="s">
+        <v>390</v>
+      </c>
+      <c r="C159" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="58" t="s">
+        <v>125</v>
+      </c>
+      <c r="E159" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="F159" s="59" t="s">
+        <v>391</v>
+      </c>
+      <c r="G159" s="26"/>
+    </row>
+    <row r="160" ht="15.75" hidden="1" spans="1:7">
+      <c r="A160" s="32">
+        <v>158</v>
+      </c>
+      <c r="B160" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="C160" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E160" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F160" s="60" t="s">
+        <v>393</v>
+      </c>
+      <c r="G160" s="66" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" hidden="1" spans="1:7">
+      <c r="A161" s="32">
+        <v>159</v>
+      </c>
+      <c r="B161" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="C161" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E161" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="F161" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="G161" s="26"/>
+    </row>
+    <row r="162" ht="15.75" hidden="1" spans="1:7">
+      <c r="A162" s="32">
+        <v>160</v>
+      </c>
+      <c r="B162" s="53" t="s">
+        <v>397</v>
+      </c>
+      <c r="C162" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E162" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F162" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="G162" s="66" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" hidden="1" spans="1:7">
+      <c r="A163" s="32">
+        <v>161</v>
+      </c>
+      <c r="B163" s="53" t="s">
+        <v>400</v>
+      </c>
+      <c r="C163" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E163" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F163" s="26"/>
+      <c r="G163" s="66" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="164" s="16" customFormat="1" ht="15.75" hidden="1" spans="1:7">
+      <c r="A164" s="32">
+        <v>162</v>
+      </c>
+      <c r="B164" s="53" t="s">
+        <v>402</v>
+      </c>
+      <c r="C164" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E164" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F164" s="59" t="s">
+        <v>403</v>
+      </c>
+      <c r="G164" s="66" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" hidden="1" spans="1:7">
+      <c r="A165" s="32">
+        <v>163</v>
+      </c>
+      <c r="B165" s="53" t="s">
+        <v>405</v>
+      </c>
+      <c r="C165" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E165" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="F165" s="25" t="s">
+        <v>406</v>
+      </c>
+      <c r="G165" s="66" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" hidden="1" spans="1:7">
+      <c r="A166" s="32">
+        <v>164</v>
+      </c>
+      <c r="B166" s="62" t="s">
+        <v>408</v>
+      </c>
+      <c r="C166" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E166" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="F166" s="63" t="s">
+        <v>409</v>
+      </c>
+      <c r="G166" s="70" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" hidden="1" spans="1:7">
+      <c r="A167" s="32">
+        <v>165</v>
+      </c>
+      <c r="B167" s="26" t="s">
+        <v>411</v>
+      </c>
+      <c r="C167" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="E150" s="52"/>
-      <c r="F150" s="26" t="s">
-        <v>384</v>
-      </c>
-      <c r="G150" s="67"/>
-    </row>
-    <row r="151" ht="15.75" hidden="1" spans="1:7">
-      <c r="A151" s="23">
-        <v>109</v>
-      </c>
-      <c r="B151" s="24" t="s">
-        <v>385</v>
-      </c>
-      <c r="C151" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" s="52"/>
-      <c r="F151" s="68" t="s">
-        <v>386</v>
-      </c>
-      <c r="G151" s="28"/>
-    </row>
-    <row r="152" ht="15.75" hidden="1" spans="1:7">
-      <c r="A152" s="23">
-        <v>110</v>
-      </c>
-      <c r="B152" s="24" t="s">
-        <v>387</v>
-      </c>
-      <c r="C152" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D152" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E152" s="52"/>
-      <c r="F152" s="26" t="s">
-        <v>388</v>
-      </c>
-      <c r="G152" s="28"/>
-    </row>
-    <row r="153" ht="31.5" hidden="1" spans="1:7">
-      <c r="A153" s="23">
-        <v>111</v>
-      </c>
-      <c r="B153" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="C153" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="52"/>
-      <c r="F153" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="G153" s="28"/>
-    </row>
-    <row r="154" ht="15.75" hidden="1" spans="1:7">
-      <c r="A154" s="23">
-        <v>112</v>
-      </c>
-      <c r="B154" s="24" t="s">
-        <v>391</v>
-      </c>
-      <c r="C154" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D154" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="52"/>
-      <c r="F154" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="G154" s="28"/>
-    </row>
-    <row r="155" ht="15.75" hidden="1" spans="1:7">
-      <c r="A155" s="23">
-        <v>113</v>
-      </c>
-      <c r="B155" s="24" t="s">
-        <v>393</v>
-      </c>
-      <c r="C155" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D155" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="52"/>
-      <c r="F155" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G155" s="28"/>
-    </row>
-    <row r="156" ht="15.75" hidden="1" spans="1:7">
-      <c r="A156" s="23">
-        <v>114</v>
-      </c>
-      <c r="B156" s="24" t="s">
-        <v>394</v>
-      </c>
-      <c r="C156" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D156" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" s="52"/>
-      <c r="F156" s="26" t="s">
-        <v>395</v>
-      </c>
-      <c r="G156" s="28"/>
-    </row>
-    <row r="157" ht="15.75" hidden="1" spans="1:7">
-      <c r="A157" s="23">
-        <v>116</v>
-      </c>
-      <c r="B157" s="24" t="s">
-        <v>396</v>
-      </c>
-      <c r="C157" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D157" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" s="52"/>
-      <c r="F157" s="26" t="s">
-        <v>397</v>
-      </c>
-      <c r="G157" s="28"/>
-    </row>
-    <row r="158" ht="15.75" hidden="1" spans="1:7">
-      <c r="A158" s="23">
-        <v>117</v>
-      </c>
-      <c r="B158" s="24"/>
-      <c r="C158" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D158" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" s="52"/>
-      <c r="F158" s="26" t="s">
-        <v>398</v>
-      </c>
-      <c r="G158" s="28"/>
-    </row>
-    <row r="159" ht="15.75" hidden="1" spans="1:7">
-      <c r="A159" s="23">
-        <v>118</v>
-      </c>
-      <c r="B159" s="24" t="s">
-        <v>399</v>
-      </c>
-      <c r="C159" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D159" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E159" s="52"/>
-      <c r="F159" s="51" t="s">
-        <v>400</v>
-      </c>
-      <c r="G159" s="28"/>
-    </row>
-    <row r="160" ht="15.75" hidden="1" spans="1:7">
-      <c r="A160" s="23">
-        <v>119</v>
-      </c>
-      <c r="B160" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="C160" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D160" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E160" s="52"/>
-      <c r="F160" s="26" t="s">
-        <v>402</v>
-      </c>
-      <c r="G160" s="28"/>
-    </row>
-    <row r="161" ht="15.75" hidden="1" spans="1:7">
-      <c r="A161" s="23">
-        <v>120</v>
-      </c>
-      <c r="B161" s="24" t="s">
-        <v>403</v>
-      </c>
-      <c r="C161" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E161" s="52"/>
-      <c r="F161" s="26" t="s">
-        <v>404</v>
-      </c>
-      <c r="G161" s="28"/>
-    </row>
-    <row r="162" ht="15.75" hidden="1" spans="1:7">
-      <c r="A162" s="23">
-        <v>121</v>
-      </c>
-      <c r="B162" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="C162" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D162" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E162" s="52"/>
-      <c r="F162" s="26" t="s">
-        <v>406</v>
-      </c>
-      <c r="G162" s="28"/>
-    </row>
-    <row r="163" ht="15.75" hidden="1" spans="1:7">
-      <c r="A163" s="23">
-        <v>122</v>
-      </c>
-      <c r="B163" s="24" t="s">
-        <v>407</v>
-      </c>
-      <c r="C163" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D163" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E163" s="52"/>
-      <c r="F163" s="26" t="s">
-        <v>408</v>
-      </c>
-      <c r="G163" s="69"/>
-    </row>
-    <row r="164" s="16" customFormat="1" ht="15.75" hidden="1" spans="1:7">
-      <c r="A164" s="23">
-        <v>123</v>
-      </c>
-      <c r="B164" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="C164" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D164" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E164" s="52"/>
-      <c r="F164" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="G164" s="28"/>
-    </row>
-    <row r="165" ht="15.75" hidden="1" spans="1:7">
-      <c r="A165" s="23">
-        <v>126</v>
-      </c>
-      <c r="B165" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="C165" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D165" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="E165" s="52"/>
-      <c r="F165" s="26" t="s">
-        <v>410</v>
-      </c>
-      <c r="G165" s="28"/>
-    </row>
-    <row r="166" ht="15.75" hidden="1" spans="1:7">
-      <c r="A166" s="23">
-        <v>147</v>
-      </c>
-      <c r="B166" s="24" t="s">
-        <v>401</v>
-      </c>
-      <c r="C166" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D166" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" s="29"/>
-      <c r="F166" s="26" t="s">
-        <v>402</v>
-      </c>
-      <c r="G166" s="76" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="167" ht="15.75" hidden="1" spans="1:7">
-      <c r="A167" s="29">
-        <v>151</v>
-      </c>
-      <c r="B167" s="30" t="s">
+      <c r="E167" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F167" s="64" t="s">
         <v>412</v>
       </c>
-      <c r="C167" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D167" s="29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" s="29"/>
-      <c r="F167" s="31" t="s">
+      <c r="G167" s="70" t="s">
         <v>413</v>
       </c>
-      <c r="G167" s="63"/>
     </row>
     <row r="168" spans="1:7">
       <c r="D168" s="18"/>
@@ -9308,82 +9290,81 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G167" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="3">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Permanent"/>
-        <filter val="Permanente"/>
+        <filter val="BENKHALLOUK KADDOUR"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:G167">
-      <sortCondition ref="E1"/>
+      <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="F93" r:id="rId1" display="bentaallah65@yahoo.fr"/>
-    <hyperlink ref="F96" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
-    <hyperlink ref="F3" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
-    <hyperlink ref="F149" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
-    <hyperlink ref="F150" r:id="rId5" display="aliaissani97@gmail.com"/>
-    <hyperlink ref="F165" r:id="rId6" display="medzerdani@gmail.com"/>
-    <hyperlink ref="F164" r:id="rId7" display="turkibilal22@gmail.com"/>
-    <hyperlink ref="F163" r:id="rId8" display="sacihamza40@gmail.com"/>
-    <hyperlink ref="F162" r:id="rId9" display="Boba1620@hotmail.com"/>
-    <hyperlink ref="F44" r:id="rId10" display="khelifa-mir@outlook.fr"/>
-    <hyperlink ref="F134" r:id="rId11" display="fethi22miloua@gmail.com"/>
-    <hyperlink ref="F133" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
-    <hyperlink ref="F143" r:id="rId13" display="mehadjiameslem@gmail.com"/>
-    <hyperlink ref="F142" r:id="rId14" display="mekhalefleila@gmail.com"/>
-    <hyperlink ref="F9" r:id="rId15" display="khalidamet4@gmail.com"/>
-    <hyperlink ref="F161" r:id="rId16" display="layatimedi@gmail.com"/>
-    <hyperlink ref="F138" r:id="rId17" display="m_latreche@yahoo.com"/>
-    <hyperlink ref="F160" r:id="rId18" display="kadrirania51@gmail.com"/>
-    <hyperlink ref="F6" r:id="rId19" display="protoboy9999@gmail.com"/>
-    <hyperlink ref="F158" r:id="rId20" display="khadidjafezazi90@gmail"/>
-    <hyperlink ref="F4" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F132" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
-    <hyperlink ref="F128" r:id="rId23" display="douaaboularaf@gmail.com"/>
-    <hyperlink ref="F155" r:id="rId24" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F153" r:id="rId25" display="bkbhbb22@gmail.com"/>
-    <hyperlink ref="F12" r:id="rId26" display="bendida65@gmail.com"/>
-    <hyperlink ref="F40" r:id="rId27" display="sarrabencella@gmail.com"/>
-    <hyperlink ref="F123" r:id="rId28" display="ri123hab@gmail.com"/>
-    <hyperlink ref="F152" r:id="rId29" display="meriembelabed5@gmail.com"/>
-    <hyperlink ref="F108" r:id="rId30" display="rezoug.med@gmail.com"/>
-    <hyperlink ref="F137" r:id="rId31" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
-    <hyperlink ref="F39" r:id="rId32" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
-    <hyperlink ref="F147" r:id="rId33" display="zarebmohammedamine@gmail.com"/>
-    <hyperlink ref="F20" r:id="rId34" display="djamel71ziani@gmail.com"/>
-    <hyperlink ref="F127" r:id="rId35" display="ahmedboudali32@gmail.com"/>
-    <hyperlink ref="F130" r:id="rId36" display="chaouche.abdallah@gmail.com"/>
-    <hyperlink ref="F124" r:id="rId37" display="lakhdar_belhallouche@hotmail.fr"/>
-    <hyperlink ref="F135" r:id="rId38" display="ahmed.hadji22@yahoo.com"/>
-    <hyperlink ref="F45" r:id="rId39" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F99" r:id="rId40" display="khatir.mohamed1977@gmail.com"/>
-    <hyperlink ref="F82" r:id="rId41" display="irecom_abid@yahoo.fr"/>
-    <hyperlink ref="F81" r:id="rId42" display="karis483@hotmail.fr"/>
-    <hyperlink ref="F87" r:id="rId43" display="bahlilmounir@yahoo.fr"/>
-    <hyperlink ref="F60" r:id="rId44" display="beddadboucif@gmail.com"/>
-    <hyperlink ref="F59" r:id="rId45" display="seyfeddine.electrotechnique@gmail.com"/>
-    <hyperlink ref="F116" r:id="rId46" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
-    <hyperlink ref="F156" r:id="rId47" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
-    <hyperlink ref="F7" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F117" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
-    <hyperlink ref="F118" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
-    <hyperlink ref="F29" r:id="rId50" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
-    <hyperlink ref="F30" r:id="rId51" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
-    <hyperlink ref="F167" r:id="rId52" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
-    <hyperlink ref="F49" r:id="rId53" display="walid.sebastien@gmail.com"/>
-    <hyperlink ref="F50" r:id="rId54" display="bensenadanadia3@gmail.com"/>
-    <hyperlink ref="F51" r:id="rId55" display="imedmedles@gmail.com"/>
-    <hyperlink ref="F31" r:id="rId56" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
-    <hyperlink ref="F53" r:id="rId57" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
-    <hyperlink ref="F54" r:id="rId58" display="moh@medbnr.com"/>
-    <hyperlink ref="F56" r:id="rId59" display="hadilyamoune@gmail.com"/>
-    <hyperlink ref="F8" r:id="rId60" display="megdz100@gmail.com"/>
-    <hyperlink ref="F58" r:id="rId61" display="ikkachenarimen.2017@gmail.com"/>
-    <hyperlink ref="F32" r:id="rId62" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
-    <hyperlink ref="F57" r:id="rId63" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
+    <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
+    <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
+    <hyperlink ref="F54" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
+    <hyperlink ref="F105" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
+    <hyperlink ref="F106" r:id="rId5" display="aliaissani97@gmail.com"/>
+    <hyperlink ref="F124" r:id="rId6" display="medzerdani@gmail.com"/>
+    <hyperlink ref="F121" r:id="rId7" display="turkibilal22@gmail.com"/>
+    <hyperlink ref="F120" r:id="rId8" display="sacihamza40@gmail.com"/>
+    <hyperlink ref="F119" r:id="rId9" display="Boba1620@hotmail.com"/>
+    <hyperlink ref="F95" r:id="rId10" display="khelifa-mir@outlook.fr"/>
+    <hyperlink ref="F76" r:id="rId11" display="fethi22miloua@gmail.com"/>
+    <hyperlink ref="F74" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
+    <hyperlink ref="F93" r:id="rId13" display="mehadjiameslem@gmail.com"/>
+    <hyperlink ref="F91" r:id="rId14" display="mekhalefleila@gmail.com"/>
+    <hyperlink ref="F90" r:id="rId15" display="khalidamet4@gmail.com"/>
+    <hyperlink ref="F118" r:id="rId16" display="layatimedi@gmail.com"/>
+    <hyperlink ref="F85" r:id="rId17" display="m_latreche@yahoo.com"/>
+    <hyperlink ref="F117" r:id="rId18" display="kadrirania51@gmail.com"/>
+    <hyperlink ref="F81" r:id="rId19" display="protoboy9999@gmail.com"/>
+    <hyperlink ref="F115" r:id="rId20" display="khadidjafezazi90@gmail"/>
+    <hyperlink ref="F75" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F72" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F67" r:id="rId23" display="douaaboularaf@gmail.com"/>
+    <hyperlink ref="F111" r:id="rId24" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F109" r:id="rId25" display="bkbhbb22@gmail.com"/>
+    <hyperlink ref="F59" r:id="rId26" display="bendida65@gmail.com"/>
+    <hyperlink ref="F58" r:id="rId27" display="sarrabencella@gmail.com"/>
+    <hyperlink ref="F60" r:id="rId28" display="ri123hab@gmail.com"/>
+    <hyperlink ref="F108" r:id="rId29" display="meriembelabed5@gmail.com"/>
+    <hyperlink ref="F45" r:id="rId30" display="rezoug.med@gmail.com"/>
+    <hyperlink ref="F84" r:id="rId31" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
+    <hyperlink ref="F57" r:id="rId32" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
+    <hyperlink ref="F100" r:id="rId33" display="zarebmohammedamine@gmail.com"/>
+    <hyperlink ref="F101" r:id="rId34" display="djamel71ziani@gmail.com"/>
+    <hyperlink ref="F65" r:id="rId35" display="ahmedboudali32@gmail.com"/>
+    <hyperlink ref="F69" r:id="rId36" display="chaouche.abdallah@gmail.com"/>
+    <hyperlink ref="F61" r:id="rId37" display="lakhdar_belhallouche@hotmail.fr"/>
+    <hyperlink ref="F80" r:id="rId38" display="ahmed.hadji22@yahoo.com"/>
+    <hyperlink ref="F103" r:id="rId39" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F32" r:id="rId40" display="khatir.mohamed1977@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId41" display="irecom_abid@yahoo.fr"/>
+    <hyperlink ref="F7" r:id="rId42" display="karis483@hotmail.fr"/>
+    <hyperlink ref="F8" r:id="rId43" display="bahlilmounir@yahoo.fr"/>
+    <hyperlink ref="F10" r:id="rId44" display="beddadboucif@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId45" display="seyfeddine.electrotechnique@gmail.com"/>
+    <hyperlink ref="F127" r:id="rId46" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F112" r:id="rId47" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F141" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F142" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
+    <hyperlink ref="F144" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
+    <hyperlink ref="F143" r:id="rId50" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
+    <hyperlink ref="F147" r:id="rId51" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
+    <hyperlink ref="F150" r:id="rId52" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
+    <hyperlink ref="F151" r:id="rId53" display="walid.sebastien@gmail.com"/>
+    <hyperlink ref="F152" r:id="rId54" display="bensenadanadia3@gmail.com"/>
+    <hyperlink ref="F153" r:id="rId55" display="imedmedles@gmail.com"/>
+    <hyperlink ref="F156" r:id="rId56" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
+    <hyperlink ref="F160" r:id="rId57" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
+    <hyperlink ref="F162" r:id="rId58" display="moh@medbnr.com"/>
+    <hyperlink ref="F164" r:id="rId59" display="hadilyamoune@gmail.com"/>
+    <hyperlink ref="F165" r:id="rId60" display="megdz100@gmail.com"/>
+    <hyperlink ref="F159" r:id="rId61" display="ikkachenarimen.2017@gmail.com"/>
+    <hyperlink ref="F161" r:id="rId62" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
+    <hyperlink ref="F166" r:id="rId63" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -1123,7 +1123,7 @@
     <t>FILALI INES</t>
   </si>
   <si>
-    <t>nesfilali2003@gmail.com</t>
+    <t>inesfilali2003@gmail.com</t>
   </si>
   <si>
     <t>0794297709</t>
@@ -2206,7 +2206,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2363,12 +2363,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2902,7 +2896,7 @@
       <c r="F7" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="65" t="s">
+      <c r="G7" s="63" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2925,7 +2919,7 @@
       <c r="F8" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="65" t="s">
+      <c r="G8" s="63" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2969,7 +2963,7 @@
       <c r="F10" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="65" t="s">
+      <c r="G10" s="63" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3141,7 +3135,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" ht="15.75" spans="1:7">
+    <row r="19" ht="15.75" hidden="1" spans="1:7">
       <c r="A19" s="23">
         <v>18</v>
       </c>
@@ -3517,7 +3511,7 @@
       <c r="F36" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="G36" s="66" t="s">
+      <c r="G36" s="64" t="s">
         <v>87</v>
       </c>
     </row>
@@ -3561,7 +3555,7 @@
       <c r="F38" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="65" t="s">
+      <c r="G38" s="63" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3857,7 +3851,7 @@
       <c r="F52" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="G52" s="65" t="s">
+      <c r="G52" s="63" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3901,7 +3895,7 @@
       <c r="F54" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="G54" s="65" t="s">
+      <c r="G54" s="63" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4079,7 +4073,7 @@
       <c r="F62" s="42" t="s">
         <v>153</v>
       </c>
-      <c r="G62" s="65" t="s">
+      <c r="G62" s="63" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4142,7 +4136,7 @@
       <c r="F65" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G65" s="66" t="s">
+      <c r="G65" s="64" t="s">
         <v>163</v>
       </c>
     </row>
@@ -4186,7 +4180,7 @@
       <c r="F67" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="G67" s="65" t="s">
+      <c r="G67" s="63" t="s">
         <v>169</v>
       </c>
     </row>
@@ -4207,7 +4201,7 @@
       <c r="F68" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="G68" s="65" t="s">
+      <c r="G68" s="63" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4228,7 +4222,7 @@
       <c r="F69" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="G69" s="65" t="s">
+      <c r="G69" s="63" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4249,7 +4243,7 @@
       <c r="F70" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="G70" s="65" t="s">
+      <c r="G70" s="63" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4272,7 +4266,7 @@
       <c r="F71" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="G71" s="65" t="s">
+      <c r="G71" s="63" t="s">
         <v>181</v>
       </c>
     </row>
@@ -4337,7 +4331,7 @@
       <c r="F74" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="G74" s="65" t="s">
+      <c r="G74" s="63" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4402,7 +4396,7 @@
       <c r="F77" s="33" t="s">
         <v>197</v>
       </c>
-      <c r="G77" s="65" t="s">
+      <c r="G77" s="63" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4614,7 +4608,7 @@
       <c r="F87" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="G87" s="65" t="s">
+      <c r="G87" s="63" t="s">
         <v>225</v>
       </c>
     </row>
@@ -4658,7 +4652,7 @@
       <c r="F89" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="G89" s="65" t="s">
+      <c r="G89" s="63" t="s">
         <v>231</v>
       </c>
     </row>
@@ -4681,7 +4675,7 @@
       <c r="F90" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="G90" s="65" t="s">
+      <c r="G90" s="63" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4725,7 +4719,7 @@
       <c r="F92" s="44" t="s">
         <v>240</v>
       </c>
-      <c r="G92" s="65" t="s">
+      <c r="G92" s="63" t="s">
         <v>241</v>
       </c>
     </row>
@@ -4960,7 +4954,7 @@
       <c r="F103" s="33" t="s">
         <v>271</v>
       </c>
-      <c r="G103" s="66" t="s">
+      <c r="G103" s="64" t="s">
         <v>272</v>
       </c>
     </row>
@@ -5430,7 +5424,7 @@
       <c r="F127" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="G127" s="65" t="s">
+      <c r="G127" s="63" t="s">
         <v>321</v>
       </c>
     </row>
@@ -5453,7 +5447,7 @@
       <c r="F128" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="G128" s="67" t="s">
+      <c r="G128" s="65" t="s">
         <v>324</v>
       </c>
     </row>
@@ -5476,7 +5470,7 @@
       <c r="F129" s="33" t="s">
         <v>326</v>
       </c>
-      <c r="G129" s="67" t="s">
+      <c r="G129" s="65" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5499,7 +5493,7 @@
       <c r="F130" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="G130" s="67" t="s">
+      <c r="G130" s="65" t="s">
         <v>330</v>
       </c>
     </row>
@@ -5522,7 +5516,7 @@
       <c r="F131" s="33" t="s">
         <v>307</v>
       </c>
-      <c r="G131" s="67" t="s">
+      <c r="G131" s="65" t="s">
         <v>331</v>
       </c>
     </row>
@@ -5589,7 +5583,7 @@
       <c r="F134" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="G134" s="67" t="s">
+      <c r="G134" s="65" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5612,7 +5606,7 @@
       <c r="F135" s="33" t="s">
         <v>341</v>
       </c>
-      <c r="G135" s="67" t="s">
+      <c r="G135" s="65" t="s">
         <v>342</v>
       </c>
     </row>
@@ -5633,7 +5627,7 @@
       <c r="F136" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="G136" s="67" t="s">
+      <c r="G136" s="65" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5677,7 +5671,7 @@
       <c r="F138" s="33" t="s">
         <v>349</v>
       </c>
-      <c r="G138" s="68" t="s">
+      <c r="G138" s="66" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5811,7 +5805,7 @@
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" ht="15.75" hidden="1" spans="1:7">
+    <row r="145" ht="15.75" spans="1:7">
       <c r="A145" s="23">
         <v>146</v>
       </c>
@@ -5827,7 +5821,7 @@
       <c r="E145" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="F145" s="33" t="s">
+      <c r="F145" s="31" t="s">
         <v>363</v>
       </c>
       <c r="G145" s="26"/>
@@ -5849,7 +5843,7 @@
       <c r="F146" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="G146" s="69" t="s">
+      <c r="G146" s="67" t="s">
         <v>364</v>
       </c>
     </row>
@@ -5872,7 +5866,7 @@
       <c r="F147" s="31" t="s">
         <v>366</v>
       </c>
-      <c r="G147" s="66" t="s">
+      <c r="G147" s="64" t="s">
         <v>367</v>
       </c>
     </row>
@@ -6067,7 +6061,7 @@
       <c r="A157" s="32">
         <v>156</v>
       </c>
-      <c r="B157" s="57" t="s">
+      <c r="B157" s="26" t="s">
         <v>386</v>
       </c>
       <c r="C157" s="24" t="s">
@@ -6109,19 +6103,19 @@
       <c r="A159" s="32">
         <v>157</v>
       </c>
-      <c r="B159" s="57" t="s">
+      <c r="B159" s="26" t="s">
         <v>390</v>
       </c>
       <c r="C159" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D159" s="58" t="s">
+      <c r="D159" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="E159" s="58" t="s">
+      <c r="E159" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="F159" s="59" t="s">
+      <c r="F159" s="57" t="s">
         <v>391</v>
       </c>
       <c r="G159" s="26"/>
@@ -6142,10 +6136,10 @@
       <c r="E160" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="F160" s="60" t="s">
+      <c r="F160" s="58" t="s">
         <v>393</v>
       </c>
-      <c r="G160" s="66" t="s">
+      <c r="G160" s="64" t="s">
         <v>394</v>
       </c>
     </row>
@@ -6165,7 +6159,7 @@
       <c r="E161" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="F161" s="61" t="s">
+      <c r="F161" s="59" t="s">
         <v>396</v>
       </c>
       <c r="G161" s="26"/>
@@ -6189,7 +6183,7 @@
       <c r="F162" s="25" t="s">
         <v>398</v>
       </c>
-      <c r="G162" s="66" t="s">
+      <c r="G162" s="64" t="s">
         <v>399</v>
       </c>
     </row>
@@ -6210,7 +6204,7 @@
         <v>137</v>
       </c>
       <c r="F163" s="26"/>
-      <c r="G163" s="66" t="s">
+      <c r="G163" s="64" t="s">
         <v>401</v>
       </c>
     </row>
@@ -6230,10 +6224,10 @@
       <c r="E164" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="F164" s="59" t="s">
+      <c r="F164" s="57" t="s">
         <v>403</v>
       </c>
-      <c r="G164" s="66" t="s">
+      <c r="G164" s="64" t="s">
         <v>404</v>
       </c>
     </row>
@@ -6256,7 +6250,7 @@
       <c r="F165" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="G165" s="66" t="s">
+      <c r="G165" s="64" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6264,7 +6258,7 @@
       <c r="A166" s="32">
         <v>164</v>
       </c>
-      <c r="B166" s="62" t="s">
+      <c r="B166" s="60" t="s">
         <v>408</v>
       </c>
       <c r="C166" s="23" t="s">
@@ -6276,10 +6270,10 @@
       <c r="E166" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="F166" s="63" t="s">
+      <c r="F166" s="61" t="s">
         <v>409</v>
       </c>
-      <c r="G166" s="70" t="s">
+      <c r="G166" s="68" t="s">
         <v>410</v>
       </c>
     </row>
@@ -6299,10 +6293,10 @@
       <c r="E167" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="F167" s="64" t="s">
+      <c r="F167" s="62" t="s">
         <v>412</v>
       </c>
-      <c r="G167" s="70" t="s">
+      <c r="G167" s="68" t="s">
         <v>413</v>
       </c>
     </row>
@@ -9292,10 +9286,10 @@
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G167" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
       <filters>
-        <filter val="BENKHALLOUK KADDOUR"/>
+        <filter val="FILALI INES"/>
       </filters>
     </filterColumn>
-    <sortState ref="A2:G167">
+    <sortState ref="A1:G167">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9365,6 +9359,7 @@
     <hyperlink ref="F159" r:id="rId61" display="ikkachenarimen.2017@gmail.com"/>
     <hyperlink ref="F161" r:id="rId62" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
     <hyperlink ref="F166" r:id="rId63" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
+    <hyperlink ref="F145" r:id="rId64" display="inesfilali2003@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$173</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="910" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="473">
   <si>
     <t>N°</t>
   </si>
@@ -187,12 +187,15 @@
     <t>farid.benhamida@yahoo.fr</t>
   </si>
   <si>
-    <t>BENKHALOUK KADDOUR</t>
+    <t>BENKHALLOUK KADDOUR</t>
   </si>
   <si>
     <t>benkh_ka@yahoo.fr</t>
   </si>
   <si>
+    <t>0560327888</t>
+  </si>
+  <si>
     <t>BENTAALLAH ABDERRAHIM</t>
   </si>
   <si>
@@ -868,6 +871,9 @@
     <t>zoulikhaabed3@gmail.com</t>
   </si>
   <si>
+    <t>0665697925</t>
+  </si>
+  <si>
     <t>AISSANI ALI</t>
   </si>
   <si>
@@ -898,6 +904,9 @@
     <t>l.benmessaoud@yahoo.fr</t>
   </si>
   <si>
+    <t>0553714385/0669056569</t>
+  </si>
+  <si>
     <t>BERROUNA HANANE</t>
   </si>
   <si>
@@ -919,9 +928,6 @@
     <t>fantazibelkisse.13@gmail.com</t>
   </si>
   <si>
-    <t>khadidjafezazi90@gmail</t>
-  </si>
-  <si>
     <t>KADA ZAIR IKRAM</t>
   </si>
   <si>
@@ -964,6 +970,9 @@
     <t>amrais@yahoo.com</t>
   </si>
   <si>
+    <t>0657 28 66 17</t>
+  </si>
+  <si>
     <t>REGUIG ABDELDJALIL</t>
   </si>
   <si>
@@ -1093,6 +1102,9 @@
     <t>mekhfikhalida87@gmail.com</t>
   </si>
   <si>
+    <t>0663594477</t>
+  </si>
+  <si>
     <t>ZATLA HICHAM</t>
   </si>
   <si>
@@ -1162,7 +1174,7 @@
     <t>walid.sebastien@gmail.com</t>
   </si>
   <si>
-    <t>BENSNADA NADIA</t>
+    <t>BENSENADA NADIA</t>
   </si>
   <si>
     <t>bensenadanadia3@gmail.com</t>
@@ -1174,6 +1186,9 @@
     <t>imedmedles@gmail.com</t>
   </si>
   <si>
+    <t>0557949511</t>
+  </si>
+  <si>
     <t>ANANI MACHO</t>
   </si>
   <si>
@@ -1198,18 +1213,27 @@
     <t>mhamedbensmicha00@gmail.com</t>
   </si>
   <si>
+    <t>0776460041</t>
+  </si>
+  <si>
     <t>LAZERGUI SIHEM</t>
   </si>
   <si>
     <t>sihemlazergui@gmail.com</t>
   </si>
   <si>
+    <t>0659768499</t>
+  </si>
+  <si>
     <t>IKKACHE NARIMEN</t>
   </si>
   <si>
     <t>ikkachenarimen.2017@gmail.com</t>
   </si>
   <si>
+    <t>0652282221</t>
+  </si>
+  <si>
     <t>ATTAR IMAD</t>
   </si>
   <si>
@@ -1237,6 +1261,9 @@
     <t>MELIANI ABDELHAK</t>
   </si>
   <si>
+    <t>abdelhaklafane@gmail.com</t>
+  </si>
+  <si>
     <t>0541306332</t>
   </si>
   <si>
@@ -1267,13 +1294,49 @@
     <t>0699099272</t>
   </si>
   <si>
-    <t>YAHI HICHEM</t>
+    <t>YAHI AHMED HICHEM</t>
   </si>
   <si>
     <t>hichem-y33@hotmail.com</t>
   </si>
   <si>
     <t>0556565254</t>
+  </si>
+  <si>
+    <t>CHAFI MERIEM</t>
+  </si>
+  <si>
+    <t>chafi.meriem@yahoo.fr</t>
+  </si>
+  <si>
+    <t>CHIRANI SOUMIA</t>
+  </si>
+  <si>
+    <t>chirani soumiaaiboudi27@gmail.com</t>
+  </si>
+  <si>
+    <t>DERKAOUI ZOUAOUIA</t>
+  </si>
+  <si>
+    <t>EL-FIAD MOHAMED DJILLALI</t>
+  </si>
+  <si>
+    <t>HADJOUNI AMINE</t>
+  </si>
+  <si>
+    <t>hadjouni-amine@hotmail.com</t>
+  </si>
+  <si>
+    <t>SAHRAOUI HADIL</t>
+  </si>
+  <si>
+    <t>sahraouihadil2001@gmail.com</t>
+  </si>
+  <si>
+    <t>0549 57 13 09</t>
+  </si>
+  <si>
+    <t>TALEB SOUMIA</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -1400,7 +1463,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1436,6 +1499,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
@@ -1449,68 +1520,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Cambria"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF222222"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF5E5E5E"/>
-      <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Cambria"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9.75"/>
       <color rgb="FF1155CC"/>
       <name val="Helvetica"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF1155CC"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1874,7 +1892,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1935,30 +1953,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2078,135 +2072,135 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2258,136 +2252,60 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2736,3587 +2654,3611 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr filterMode="1" codeName="Sheet1"/>
-  <dimension ref="A1:G1161"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <dimension ref="A1:G1160"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="17" customWidth="1"/>
     <col min="2" max="2" width="33.5714285714286" style="18" customWidth="1"/>
     <col min="3" max="3" width="29.7142857142857" style="18" customWidth="1"/>
     <col min="4" max="4" width="19.1428571428571" style="17" customWidth="1"/>
     <col min="5" max="5" width="21.552380952381" style="17" customWidth="1"/>
-    <col min="6" max="6" width="38.8571428571429" style="18" customWidth="1"/>
-    <col min="7" max="7" width="24.2857142857143" style="18" customWidth="1"/>
-    <col min="8" max="16384" width="11" style="19"/>
+    <col min="6" max="6" width="38.8571428571429" style="19" customWidth="1"/>
+    <col min="7" max="7" width="24.2857142857143" style="20" customWidth="1"/>
+    <col min="8" max="16384" width="11" style="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" spans="1:7">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="23" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="15.75" hidden="1" spans="1:7">
-      <c r="A2" s="23">
+      <c r="A2" s="24">
         <v>1</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="25" t="s">
+      <c r="F2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="26"/>
     </row>
     <row r="3" ht="15.75" hidden="1" spans="1:7">
-      <c r="A3" s="23">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="23" t="s">
+      <c r="C3" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="26"/>
     </row>
     <row r="4" ht="15.75" hidden="1" spans="1:7">
-      <c r="A4" s="23">
+      <c r="A4" s="24">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="23" t="s">
+      <c r="C4" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="26"/>
     </row>
     <row r="5" ht="15.75" hidden="1" spans="1:7">
-      <c r="A5" s="23">
+      <c r="A5" s="24">
         <v>4</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="23" t="s">
+      <c r="C5" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="26"/>
     </row>
     <row r="6" ht="15.75" hidden="1" spans="1:7">
-      <c r="A6" s="23">
+      <c r="A6" s="24">
         <v>5</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="23" t="s">
+      <c r="C6" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="26"/>
     </row>
     <row r="7" ht="15.75" hidden="1" spans="1:7">
-      <c r="A7" s="23">
+      <c r="A7" s="24">
         <v>6</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="23" t="s">
+      <c r="C7" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="38" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" ht="15.75" hidden="1" spans="1:7">
-      <c r="A8" s="23">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="23" t="s">
+      <c r="C8" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="63" t="s">
+      <c r="G8" s="38" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" ht="15.75" hidden="1" spans="1:7">
-      <c r="A9" s="23">
-        <v>8</v>
-      </c>
-      <c r="B9" s="24" t="s">
+      <c r="A9" s="24">
+        <v>8</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="23" t="s">
+      <c r="C9" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="26"/>
     </row>
     <row r="10" ht="15.75" hidden="1" spans="1:7">
-      <c r="A10" s="23">
+      <c r="A10" s="24">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="29" t="s">
+      <c r="C10" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="E10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="38" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" ht="15.75" hidden="1" spans="1:7">
-      <c r="A11" s="23">
+      <c r="A11" s="24">
         <v>10</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="23" t="s">
+      <c r="C11" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="26"/>
     </row>
     <row r="12" ht="15.75" hidden="1" spans="1:7">
-      <c r="A12" s="23">
+      <c r="A12" s="24">
         <v>11</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="23" t="s">
+      <c r="C12" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="26"/>
     </row>
     <row r="13" ht="15.75" hidden="1" spans="1:7">
-      <c r="A13" s="23">
+      <c r="A13" s="24">
         <v>12</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="23" t="s">
+      <c r="C13" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="26"/>
     </row>
     <row r="14" ht="15.75" hidden="1" spans="1:7">
-      <c r="A14" s="23">
+      <c r="A14" s="24">
         <v>13</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="23" t="s">
+      <c r="C14" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="26"/>
     </row>
     <row r="15" ht="15.75" hidden="1" spans="1:7">
-      <c r="A15" s="23">
+      <c r="A15" s="24">
         <v>14</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="23" t="s">
+      <c r="C15" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F15" s="27" t="s">
+      <c r="F15" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="26"/>
     </row>
     <row r="16" ht="15.75" hidden="1" spans="1:7">
-      <c r="A16" s="23">
+      <c r="A16" s="24">
         <v>15</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="23" t="s">
+      <c r="C16" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G16" s="26"/>
     </row>
     <row r="17" ht="15.75" hidden="1" spans="1:7">
-      <c r="A17" s="23">
+      <c r="A17" s="24">
         <v>16</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="23" t="s">
+      <c r="C17" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="F17" s="27" t="s">
+      <c r="F17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G17" s="26"/>
     </row>
     <row r="18" ht="15.75" hidden="1" spans="1:7">
-      <c r="A18" s="23">
+      <c r="A18" s="24">
         <v>17</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="23" t="s">
+      <c r="C18" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="27" t="s">
+      <c r="F18" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="G18" s="26"/>
     </row>
     <row r="19" ht="15.75" hidden="1" spans="1:7">
-      <c r="A19" s="23">
+      <c r="A19" s="24">
         <v>18</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="23" t="s">
+      <c r="C19" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="26"/>
+      <c r="G19" s="38" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="20" ht="15.75" hidden="1" spans="1:7">
-      <c r="A20" s="23">
+      <c r="A20" s="24">
         <v>19</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" hidden="1" spans="1:7">
+      <c r="A21" s="24">
+        <v>20</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" hidden="1" spans="1:7">
+      <c r="A22" s="24">
+        <v>21</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" hidden="1" spans="1:7">
+      <c r="A23" s="24">
+        <v>22</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" hidden="1" spans="1:7">
+      <c r="A24" s="24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" hidden="1" spans="1:7">
+      <c r="A25" s="24">
+        <v>24</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" hidden="1" spans="1:7">
+      <c r="A26" s="24">
+        <v>25</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" hidden="1" spans="1:7">
+      <c r="A27" s="24">
+        <v>26</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" hidden="1" spans="1:7">
+      <c r="A28" s="24">
+        <v>27</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" hidden="1" spans="1:7">
+      <c r="A29" s="24">
+        <v>28</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" hidden="1" spans="1:7">
+      <c r="A30" s="24">
+        <v>29</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" hidden="1" spans="1:7">
+      <c r="A31" s="24">
+        <v>30</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" hidden="1" spans="1:7">
+      <c r="A32" s="24">
+        <v>31</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" hidden="1" spans="1:7">
+      <c r="A33" s="24">
+        <v>32</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" hidden="1" spans="1:7">
+      <c r="A34" s="24">
+        <v>34</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" hidden="1" spans="1:7">
+      <c r="A35" s="24">
+        <v>35</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" hidden="1" spans="1:7">
+      <c r="A36" s="24">
+        <v>36</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" hidden="1" spans="1:7">
+      <c r="A37" s="24">
+        <v>37</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" hidden="1" spans="1:7">
+      <c r="A38" s="24">
+        <v>38</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="G38" s="38" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" hidden="1" spans="1:7">
+      <c r="A39" s="24">
+        <v>39</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" hidden="1" spans="1:7">
+      <c r="A40" s="24">
+        <v>40</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" hidden="1" spans="1:7">
+      <c r="A41" s="24">
+        <v>41</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" hidden="1" spans="1:7">
+      <c r="A42" s="24">
+        <v>42</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" hidden="1" spans="1:7">
+      <c r="A43" s="24">
+        <v>43</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" hidden="1" spans="1:7">
+      <c r="A44" s="24">
+        <v>44</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" hidden="1" spans="1:7">
+      <c r="A45" s="24">
+        <v>45</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" hidden="1" spans="1:7">
+      <c r="A46" s="24">
+        <v>46</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E46" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" hidden="1" spans="1:7">
+      <c r="A47" s="24">
+        <v>47</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" hidden="1" spans="1:7">
+      <c r="A48" s="24">
+        <v>48</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E48" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" hidden="1" spans="1:7">
+      <c r="A49" s="24">
+        <v>49</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" hidden="1" spans="1:7">
+      <c r="A50" s="24">
+        <v>50</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" hidden="1" spans="1:7">
+      <c r="A51" s="24">
+        <v>51</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" hidden="1" spans="1:7">
+      <c r="A52" s="24">
+        <v>52</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G52" s="38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" hidden="1" spans="1:7">
+      <c r="A53" s="24">
         <v>53</v>
       </c>
-      <c r="C20" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="23" t="s">
+      <c r="B53" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E53" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="27" t="s">
+      <c r="F53" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" spans="1:7">
+      <c r="A54" s="24">
         <v>54</v>
       </c>
-      <c r="G20" s="26"/>
-    </row>
-    <row r="21" ht="15.75" hidden="1" spans="1:7">
-      <c r="A21" s="23">
-        <v>20</v>
-      </c>
-      <c r="B21" s="24" t="s">
+      <c r="B54" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G54" s="38" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" spans="1:7">
+      <c r="A55" s="24">
         <v>55</v>
       </c>
-      <c r="C21" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="23" t="s">
+      <c r="B55" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E55" s="29"/>
+      <c r="F55" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="G55" s="20" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" spans="1:7">
+      <c r="A56" s="24">
+        <v>57</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="G56" s="20" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" spans="1:7">
+      <c r="A57" s="24">
+        <v>58</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="G57" s="20" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" spans="1:7">
+      <c r="A58" s="24">
+        <v>59</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C58" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E58" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="G58" s="20" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" spans="1:7">
+      <c r="A59" s="24">
+        <v>60</v>
+      </c>
+      <c r="B59" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="G59" s="20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" spans="1:7">
+      <c r="A60" s="24">
+        <v>61</v>
+      </c>
+      <c r="B60" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="E60" s="32"/>
+      <c r="F60" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="G60" s="20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" spans="1:7">
+      <c r="A61" s="24">
+        <v>62</v>
+      </c>
+      <c r="B61" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E61" s="27"/>
+      <c r="F61" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="G61" s="20" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" ht="31.5" spans="1:7">
+      <c r="A62" s="24">
+        <v>64</v>
+      </c>
+      <c r="B62" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C62" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>134</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="G62" s="38" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" spans="1:7">
+      <c r="A63" s="24">
+        <v>65</v>
+      </c>
+      <c r="B63" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E63" s="28"/>
+      <c r="F63" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="G63" s="20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" spans="1:7">
+      <c r="A64" s="24">
+        <v>66</v>
+      </c>
+      <c r="B64" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E64" s="30"/>
+      <c r="F64" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G64" s="20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" spans="1:7">
+      <c r="A65" s="24">
+        <v>67</v>
+      </c>
+      <c r="B65" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E65" s="28"/>
+      <c r="F65" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G65" s="38" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" spans="1:7">
+      <c r="A66" s="24">
+        <v>68</v>
+      </c>
+      <c r="B66" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C66" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E66" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F66" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G66" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" spans="1:7">
+      <c r="A67" s="24">
+        <v>69</v>
+      </c>
+      <c r="B67" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E67" s="24"/>
+      <c r="F67" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="G67" s="38" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" spans="1:7">
+      <c r="A68" s="24">
+        <v>70</v>
+      </c>
+      <c r="B68" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E68" s="24"/>
+      <c r="F68" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G68" s="38" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="69" ht="31.5" spans="1:7">
+      <c r="A69" s="24">
+        <v>71</v>
+      </c>
+      <c r="B69" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="C69" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E69" s="24"/>
+      <c r="F69" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="G69" s="38" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" spans="1:7">
+      <c r="A70" s="24">
+        <v>72</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E70" s="24"/>
+      <c r="F70" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G70" s="38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" spans="1:7">
+      <c r="A71" s="24">
+        <v>73</v>
+      </c>
+      <c r="B71" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E71" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G71" s="38" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" spans="1:7">
+      <c r="A72" s="24">
+        <v>74</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E72" s="24"/>
+      <c r="F72" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="G72" s="20" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" spans="1:7">
+      <c r="A73" s="24">
+        <v>75</v>
+      </c>
+      <c r="B73" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E73" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="G73" s="20" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" spans="1:7">
+      <c r="A74" s="24">
+        <v>76</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E74" s="24"/>
+      <c r="F74" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G74" s="38" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" spans="1:7">
+      <c r="A75" s="24">
+        <v>77</v>
+      </c>
+      <c r="B75" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E75" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" spans="1:7">
+      <c r="A76" s="24">
+        <v>78</v>
+      </c>
+      <c r="B76" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E76" s="24"/>
+      <c r="F76" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" spans="1:7">
+      <c r="A77" s="24">
+        <v>79</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E77" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="G77" s="38" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" spans="1:7">
+      <c r="A78" s="24">
+        <v>80</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E78" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" spans="1:7">
+      <c r="A79" s="24">
+        <v>81</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E79" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" spans="1:7">
+      <c r="A80" s="24">
+        <v>82</v>
+      </c>
+      <c r="B80" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="C80" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E80" s="24"/>
+      <c r="F80" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="G80" s="20" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" spans="1:7">
+      <c r="A81" s="24">
+        <v>83</v>
+      </c>
+      <c r="B81" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C81" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E81" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" spans="1:7">
+      <c r="A82" s="24">
+        <v>84</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E82" s="28"/>
+      <c r="F82" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" spans="1:7">
+      <c r="A83" s="24">
+        <v>85</v>
+      </c>
+      <c r="B83" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="C83" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E83" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" spans="1:7">
+      <c r="A84" s="24">
+        <v>86</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="C84" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E84" s="28"/>
+      <c r="F84" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" spans="1:7">
+      <c r="A85" s="24">
+        <v>87</v>
+      </c>
+      <c r="B85" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C85" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E85" s="28"/>
+      <c r="F85" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="G85" s="20" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" spans="1:7">
+      <c r="A86" s="24">
+        <v>88</v>
+      </c>
+      <c r="B86" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="C86" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E86" s="30"/>
+      <c r="F86" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G86" s="20" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" spans="1:7">
+      <c r="A87" s="24">
+        <v>89</v>
+      </c>
+      <c r="B87" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="C87" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E87" s="24"/>
+      <c r="F87" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="G87" s="38" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" spans="1:7">
+      <c r="A88" s="24">
+        <v>90</v>
+      </c>
+      <c r="B88" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E88" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="G88" s="20" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" spans="1:7">
+      <c r="A89" s="24">
+        <v>91</v>
+      </c>
+      <c r="B89" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C89" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E89" s="24"/>
+      <c r="F89" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="G89" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" spans="1:7">
+      <c r="A90" s="24">
+        <v>92</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="C90" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E90" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="G90" s="38" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" spans="1:7">
+      <c r="A91" s="24">
+        <v>93</v>
+      </c>
+      <c r="B91" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="C91" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E91" s="24"/>
+      <c r="F91" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="G91" s="20" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" spans="1:7">
+      <c r="A92" s="24">
+        <v>94</v>
+      </c>
+      <c r="B92" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="C92" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E92" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F92" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="G92" s="38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" spans="1:7">
+      <c r="A93" s="24">
+        <v>95</v>
+      </c>
+      <c r="B93" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E93" s="24"/>
+      <c r="F93" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="G93" s="20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" ht="31.5" spans="1:7">
+      <c r="A94" s="24">
+        <v>96</v>
+      </c>
+      <c r="B94" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E94" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="F94" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="G94" s="20" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="95" ht="15.75" spans="1:7">
+      <c r="A95" s="24">
+        <v>97</v>
+      </c>
+      <c r="B95" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="C95" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E95" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F95" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="G95" s="20" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="96" ht="15.75" spans="1:7">
+      <c r="A96" s="24">
+        <v>98</v>
+      </c>
+      <c r="B96" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="C96" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E96" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G96" s="20" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="97" ht="15.75" spans="1:7">
+      <c r="A97" s="24">
+        <v>99</v>
+      </c>
+      <c r="B97" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C97" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E97" s="24"/>
+    </row>
+    <row r="98" ht="15.75" spans="1:7">
+      <c r="A98" s="24">
+        <v>100</v>
+      </c>
+      <c r="B98" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E98" s="30"/>
+      <c r="F98" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="G98" s="20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" spans="1:7">
+      <c r="A99" s="24">
+        <v>101</v>
+      </c>
+      <c r="B99" s="25" t="s">
+        <v>260</v>
+      </c>
+      <c r="C99" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E99" s="28"/>
+      <c r="F99" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" spans="1:7">
+      <c r="A100" s="24">
+        <v>102</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C100" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E100" s="30"/>
+      <c r="F100" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="G100" s="20" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" spans="1:7">
+      <c r="A101" s="24">
+        <v>103</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="C101" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E101" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F101" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="G101" s="20" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" spans="1:7">
+      <c r="A102" s="24">
+        <v>104</v>
+      </c>
+      <c r="B102" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="C102" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E102" s="30"/>
+      <c r="F102" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="G102" s="20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" spans="1:7">
+      <c r="A103" s="24">
+        <v>105</v>
+      </c>
+      <c r="B103" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="C103" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E103" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F103" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G103" s="38" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" spans="1:7">
+      <c r="A104" s="24">
+        <v>106</v>
+      </c>
+      <c r="B104" s="25" t="s">
+        <v>274</v>
+      </c>
+      <c r="C104" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E104" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="F104" s="19" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" spans="1:7">
+      <c r="A105" s="24">
+        <v>107</v>
+      </c>
+      <c r="B105" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="C105" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E105" s="35"/>
+      <c r="F105" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="G105" s="38" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" spans="1:7">
+      <c r="A106" s="24">
+        <v>108</v>
+      </c>
+      <c r="B106" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="C106" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E106" s="35"/>
+      <c r="F106" s="19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" spans="1:7">
+      <c r="A107" s="24">
+        <v>109</v>
+      </c>
+      <c r="B107" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="C107" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E107" s="35"/>
+      <c r="F107" s="19" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" spans="1:7">
+      <c r="A108" s="24">
+        <v>110</v>
+      </c>
+      <c r="B108" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="C108" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E108" s="35"/>
+      <c r="F108" s="19" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="109" ht="31.5" spans="1:7">
+      <c r="A109" s="24">
+        <v>111</v>
+      </c>
+      <c r="B109" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E109" s="35"/>
+      <c r="F109" s="19" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" spans="1:7">
+      <c r="A110" s="24">
+        <v>112</v>
+      </c>
+      <c r="B110" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E110" s="35"/>
+      <c r="F110" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="G110" s="20" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" spans="1:7">
+      <c r="A111" s="24">
+        <v>113</v>
+      </c>
+      <c r="B111" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="C111" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E111" s="35"/>
+      <c r="F111" s="19" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="112" s="15" customFormat="1" ht="15.75" spans="1:7">
+      <c r="A112" s="24">
+        <v>114</v>
+      </c>
+      <c r="B112" s="25" t="s">
+        <v>292</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E112" s="35"/>
+      <c r="F112" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G112" s="20"/>
+    </row>
+    <row r="113" ht="15.75" spans="1:7">
+      <c r="A113" s="24">
+        <v>115</v>
+      </c>
+      <c r="B113" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="C113" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E113" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="F113" s="19" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" spans="1:7">
+      <c r="A114" s="24">
+        <v>116</v>
+      </c>
+      <c r="B114" s="25" t="s">
+        <v>296</v>
+      </c>
+      <c r="C114" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E114" s="35"/>
+      <c r="F114" s="19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" spans="1:7">
+      <c r="A115" s="24">
+        <v>118</v>
+      </c>
+      <c r="B115" s="25" t="s">
+        <v>298</v>
+      </c>
+      <c r="C115" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E115" s="35"/>
+      <c r="F115" s="19" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" spans="1:7">
+      <c r="A116" s="24">
+        <v>119</v>
+      </c>
+      <c r="B116" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="C116" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E116" s="35"/>
+      <c r="F116" s="19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" spans="1:7">
+      <c r="A117" s="24">
+        <v>120</v>
+      </c>
+      <c r="B117" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="C117" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E117" s="35"/>
+      <c r="F117" s="19" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" spans="1:7">
+      <c r="A118" s="24">
+        <v>121</v>
+      </c>
+      <c r="B118" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="C118" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E118" s="35"/>
+      <c r="F118" s="19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" spans="1:7">
+      <c r="A119" s="24">
+        <v>122</v>
+      </c>
+      <c r="B119" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="C119" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E119" s="35"/>
+      <c r="F119" s="19" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" spans="1:7">
+      <c r="A120" s="24">
+        <v>123</v>
+      </c>
+      <c r="B120" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C120" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E120" s="35"/>
+      <c r="F120" s="19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" spans="1:7">
+      <c r="A121" s="24">
+        <v>124</v>
+      </c>
+      <c r="B121" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E121" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="G121" s="20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="122" ht="31.5" hidden="1" spans="1:7">
+      <c r="A122" s="24">
+        <v>125</v>
+      </c>
+      <c r="B122" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="C122" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="E122" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F122" s="19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" spans="1:7">
+      <c r="A123" s="24">
+        <v>126</v>
+      </c>
+      <c r="B123" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E123" s="35"/>
+      <c r="F123" s="19" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="124" ht="15.75" hidden="1" spans="1:7">
+      <c r="A124" s="24">
+        <v>127</v>
+      </c>
+      <c r="B124" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="C124" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E124" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21" s="26"/>
-    </row>
-    <row r="22" ht="15.75" hidden="1" spans="1:7">
-      <c r="A22" s="23">
+      <c r="F124" s="19" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" hidden="1" spans="1:7">
+      <c r="A125" s="24">
+        <v>128</v>
+      </c>
+      <c r="B125" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="C125" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" s="19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" hidden="1" spans="1:7">
+      <c r="A126" s="24">
+        <v>129</v>
+      </c>
+      <c r="B126" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="C126" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="G126" s="38" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" spans="1:7">
+      <c r="A127" s="24">
+        <v>130</v>
+      </c>
+      <c r="B127" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="C127" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E127" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F127" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G127" s="38" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" hidden="1" spans="1:7">
+      <c r="A128" s="24">
+        <v>131</v>
+      </c>
+      <c r="B128" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="C128" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F128" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="G128" s="38" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" spans="1:7">
+      <c r="A129" s="24">
+        <v>132</v>
+      </c>
+      <c r="B129" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="C129" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E129" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F129" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="G129" s="38" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" spans="1:7">
+      <c r="A130" s="24">
+        <v>133</v>
+      </c>
+      <c r="B130" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C130" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E130" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F130" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="G130" s="38" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" hidden="1" spans="1:7">
+      <c r="A131" s="24">
+        <v>134</v>
+      </c>
+      <c r="B131" s="25" t="s">
+        <v>335</v>
+      </c>
+      <c r="C131" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="23" t="s">
+      <c r="E131" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131" s="19" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" spans="1:7">
+      <c r="A132" s="24">
+        <v>135</v>
+      </c>
+      <c r="B132" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="C132" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E132" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F132" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="G132" s="20" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" spans="1:7">
+      <c r="A133" s="24">
+        <v>136</v>
+      </c>
+      <c r="B133" s="25" t="s">
+        <v>340</v>
+      </c>
+      <c r="C133" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E133" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F133" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="G133" s="38" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" spans="1:7">
+      <c r="A134" s="24">
+        <v>137</v>
+      </c>
+      <c r="B134" s="25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C134" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E134" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F134" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="G134" s="38" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" spans="1:7">
+      <c r="A135" s="24">
+        <v>138</v>
+      </c>
+      <c r="B135" s="25"/>
+      <c r="C135" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D135" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E135" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F135" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="G135" s="38" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" hidden="1" spans="1:7">
+      <c r="A136" s="24">
+        <v>139</v>
+      </c>
+      <c r="B136" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="C136" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E136" s="36" t="s">
+        <v>349</v>
+      </c>
+      <c r="F136" s="19" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" spans="1:7">
+      <c r="A137" s="24">
+        <v>140</v>
+      </c>
+      <c r="B137" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="C137" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E137" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="F137" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="G137" s="38" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" spans="1:7">
+      <c r="A138" s="24">
+        <v>141</v>
+      </c>
+      <c r="B138" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="C138" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E138" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="F138" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="G138" s="38" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" hidden="1" spans="1:7">
+      <c r="A139" s="24">
+        <v>142</v>
+      </c>
+      <c r="B139" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="C139" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F139" s="19" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" spans="1:7">
+      <c r="A140" s="24">
+        <v>143</v>
+      </c>
+      <c r="B140" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="C140" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E140" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F140" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G140" s="20" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" hidden="1" spans="1:7">
+      <c r="A141" s="24">
+        <v>144</v>
+      </c>
+      <c r="B141" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C141" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E141" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="27" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="26"/>
-    </row>
-    <row r="23" ht="15.75" hidden="1" spans="1:7">
-      <c r="A23" s="23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E23" s="23" t="s">
+      <c r="F141" s="19" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" spans="1:7">
+      <c r="A142" s="24">
+        <v>145</v>
+      </c>
+      <c r="B142" s="25" t="s">
+        <v>361</v>
+      </c>
+      <c r="C142" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F142" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="G142" s="20" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="143" ht="19" hidden="1" customHeight="1" spans="1:7">
+      <c r="A143" s="24">
+        <v>145</v>
+      </c>
+      <c r="B143" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="C143" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G23" s="26"/>
-    </row>
-    <row r="24" ht="15.75" hidden="1" spans="1:7">
-      <c r="A24" s="23">
-        <v>23</v>
-      </c>
-      <c r="B24" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="23" t="s">
+      <c r="F143" s="19" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" spans="1:7">
+      <c r="A144" s="24">
+        <v>146</v>
+      </c>
+      <c r="B144" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="C144" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E144" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F144" s="19" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" spans="1:7">
+      <c r="A145" s="24">
+        <v>147</v>
+      </c>
+      <c r="B145" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="C145" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D145" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E145" s="28"/>
+      <c r="F145" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="G145" s="38" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" spans="1:7">
+      <c r="A146" s="24">
+        <v>148</v>
+      </c>
+      <c r="B146" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="C146" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D146" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E146" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F146" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="G146" s="38" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" hidden="1" spans="1:7">
+      <c r="A147" s="24">
+        <v>149</v>
+      </c>
+      <c r="B147" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="C147" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E147" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F24" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="26"/>
-    </row>
-    <row r="25" ht="15.75" hidden="1" spans="1:7">
-      <c r="A25" s="23">
-        <v>24</v>
-      </c>
-      <c r="B25" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="23" t="s">
+      <c r="F147" s="19" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" spans="1:7">
+      <c r="A148" s="24">
+        <v>150</v>
+      </c>
+      <c r="B148" s="25" t="s">
+        <v>374</v>
+      </c>
+      <c r="C148" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E148" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F148" s="19" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" spans="1:7">
+      <c r="A149" s="24">
+        <v>151</v>
+      </c>
+      <c r="B149" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="C149" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E149" s="28"/>
+      <c r="F149" s="19" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" spans="1:7">
+      <c r="A150" s="24">
+        <v>152</v>
+      </c>
+      <c r="B150" s="25" t="s">
+        <v>378</v>
+      </c>
+      <c r="C150" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E150" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F150" s="19" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" spans="1:7">
+      <c r="A151" s="24">
+        <v>153</v>
+      </c>
+      <c r="B151" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="C151" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E151" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F151" s="19" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" spans="1:7">
+      <c r="A152" s="24">
+        <v>153</v>
+      </c>
+      <c r="B152" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="C152" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D152" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E152" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F152" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="G152" s="38" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" hidden="1" spans="1:7">
+      <c r="A153" s="24">
+        <v>154</v>
+      </c>
+      <c r="B153" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="C153" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F153" s="19" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" hidden="1" spans="1:7">
+      <c r="A154" s="24">
+        <v>155</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="C154" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25" s="26"/>
-    </row>
-    <row r="26" ht="15.75" hidden="1" spans="1:7">
-      <c r="A26" s="23">
-        <v>25</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="23" t="s">
+      <c r="F154" s="19" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" spans="1:7">
+      <c r="A155" s="24">
+        <v>156</v>
+      </c>
+      <c r="B155" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="C155" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E155" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F155" s="19" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" spans="1:7">
+      <c r="A156" s="24">
+        <v>156</v>
+      </c>
+      <c r="B156" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="C156" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E156" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F156" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="G156" s="38" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" spans="1:7">
+      <c r="A157" s="24">
+        <v>157</v>
+      </c>
+      <c r="B157" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="C157" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E157" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F157" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="G157" s="38" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" spans="1:7">
+      <c r="A158" s="24">
+        <v>157</v>
+      </c>
+      <c r="B158" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="C158" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E158" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F158" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="G158" s="38" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" spans="1:7">
+      <c r="A159" s="24">
+        <v>158</v>
+      </c>
+      <c r="B159" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="C159" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E159" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F159" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="G159" s="38" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" spans="1:7">
+      <c r="A160" s="24">
+        <v>159</v>
+      </c>
+      <c r="B160" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="C160" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E160" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F160" s="19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" spans="1:7">
+      <c r="A161" s="24">
+        <v>160</v>
+      </c>
+      <c r="B161" s="25" t="s">
+        <v>405</v>
+      </c>
+      <c r="C161" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E161" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F161" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="G161" s="38" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" spans="1:7">
+      <c r="A162" s="24">
+        <v>161</v>
+      </c>
+      <c r="B162" s="25" t="s">
+        <v>408</v>
+      </c>
+      <c r="C162" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E162" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F162" s="37" t="s">
+        <v>409</v>
+      </c>
+      <c r="G162" s="38" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="163" s="16" customFormat="1" ht="31.5" spans="1:7">
+      <c r="A163" s="24">
+        <v>162</v>
+      </c>
+      <c r="B163" s="25" t="s">
+        <v>411</v>
+      </c>
+      <c r="C163" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E163" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F163" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="G163" s="38" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" spans="1:7">
+      <c r="A164" s="24">
+        <v>163</v>
+      </c>
+      <c r="B164" s="25" t="s">
+        <v>414</v>
+      </c>
+      <c r="C164" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E164" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="F164" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="G164" s="38" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" spans="1:7">
+      <c r="A165" s="24">
+        <v>164</v>
+      </c>
+      <c r="B165" s="25" t="s">
+        <v>417</v>
+      </c>
+      <c r="C165" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E165" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F165" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="G165" s="38" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" hidden="1" spans="1:7">
+      <c r="A166" s="24">
+        <v>165</v>
+      </c>
+      <c r="B166" s="25" t="s">
+        <v>420</v>
+      </c>
+      <c r="C166" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="26"/>
-    </row>
-    <row r="27" ht="15.75" hidden="1" spans="1:7">
-      <c r="A27" s="23">
-        <v>26</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="26"/>
-    </row>
-    <row r="28" ht="15.75" hidden="1" spans="1:7">
-      <c r="A28" s="23">
-        <v>27</v>
-      </c>
-      <c r="B28" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="26"/>
-    </row>
-    <row r="29" ht="15.75" hidden="1" spans="1:7">
-      <c r="A29" s="23">
-        <v>28</v>
-      </c>
-      <c r="B29" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29" s="23" t="s">
+      <c r="E166" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="F29" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="26"/>
-    </row>
-    <row r="30" ht="15.75" hidden="1" spans="1:7">
-      <c r="A30" s="23">
-        <v>29</v>
-      </c>
-      <c r="B30" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>74</v>
-      </c>
-      <c r="G30" s="26"/>
-    </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
-      <c r="A31" s="23">
-        <v>30</v>
-      </c>
-      <c r="B31" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="26"/>
-    </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
-      <c r="A32" s="23">
-        <v>31</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" s="26"/>
-    </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
-      <c r="A33" s="23">
-        <v>32</v>
-      </c>
-      <c r="B33" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="G33" s="26"/>
-    </row>
-    <row r="34" ht="15.75" hidden="1" spans="1:7">
-      <c r="A34" s="23">
-        <v>34</v>
-      </c>
-      <c r="B34" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="G34" s="26"/>
-    </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
-      <c r="A35" s="23">
-        <v>35</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G35" s="26"/>
-    </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
-      <c r="A36" s="23">
-        <v>36</v>
-      </c>
-      <c r="B36" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F36" s="27" t="s">
-        <v>86</v>
-      </c>
-      <c r="G36" s="64" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
-      <c r="A37" s="23">
-        <v>37</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="G37" s="26"/>
-    </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
-      <c r="A38" s="23">
-        <v>38</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F38" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="G38" s="63" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" hidden="1" spans="1:7">
-      <c r="A39" s="23">
-        <v>39</v>
-      </c>
-      <c r="B39" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F39" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="G39" s="26"/>
-    </row>
-    <row r="40" ht="15.75" hidden="1" spans="1:7">
-      <c r="A40" s="23">
-        <v>40</v>
-      </c>
-      <c r="B40" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="G40" s="26"/>
-    </row>
-    <row r="41" ht="15.75" hidden="1" spans="1:7">
-      <c r="A41" s="23">
-        <v>41</v>
-      </c>
-      <c r="B41" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="G41" s="26"/>
-    </row>
-    <row r="42" ht="15.75" hidden="1" spans="1:7">
-      <c r="A42" s="23">
-        <v>42</v>
-      </c>
-      <c r="B42" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>100</v>
-      </c>
-      <c r="G42" s="26"/>
-    </row>
-    <row r="43" ht="15.75" hidden="1" spans="1:7">
-      <c r="A43" s="23">
-        <v>43</v>
-      </c>
-      <c r="B43" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="G43" s="26"/>
-    </row>
-    <row r="44" ht="15.75" hidden="1" spans="1:7">
-      <c r="A44" s="23">
-        <v>44</v>
-      </c>
-      <c r="B44" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="G44" s="26"/>
-    </row>
-    <row r="45" ht="15.75" hidden="1" spans="1:7">
-      <c r="A45" s="23">
-        <v>45</v>
-      </c>
-      <c r="B45" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="G45" s="26"/>
-    </row>
-    <row r="46" ht="15.75" hidden="1" spans="1:7">
-      <c r="A46" s="23">
-        <v>46</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="F46" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G46" s="26"/>
-    </row>
-    <row r="47" ht="15.75" hidden="1" spans="1:7">
-      <c r="A47" s="23">
-        <v>47</v>
-      </c>
-      <c r="B47" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F47" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="G47" s="26"/>
-    </row>
-    <row r="48" ht="15.75" hidden="1" spans="1:7">
-      <c r="A48" s="23">
-        <v>48</v>
-      </c>
-      <c r="B48" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="26"/>
-    </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
-      <c r="A49" s="23">
-        <v>49</v>
-      </c>
-      <c r="B49" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G49" s="26"/>
-    </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
-      <c r="A50" s="23">
-        <v>50</v>
-      </c>
-      <c r="B50" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="G50" s="26"/>
-    </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
-      <c r="A51" s="23">
-        <v>51</v>
-      </c>
-      <c r="B51" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F51" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="G51" s="26"/>
-    </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
-      <c r="A52" s="23">
-        <v>52</v>
-      </c>
-      <c r="B52" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F52" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="G52" s="63" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
-      <c r="A53" s="23">
-        <v>53</v>
-      </c>
-      <c r="B53" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F53" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="G53" s="26"/>
-    </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
-      <c r="A54" s="23">
-        <v>54</v>
-      </c>
-      <c r="B54" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" s="23" t="s">
+      <c r="F166" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G166" s="38" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="167" ht="15.75" spans="1:7">
+      <c r="A167" s="24">
+        <v>166</v>
+      </c>
+      <c r="B167" s="25" t="s">
+        <v>423</v>
+      </c>
+      <c r="C167" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="F54" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="G54" s="63" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
-      <c r="A55" s="23">
-        <v>55</v>
-      </c>
-      <c r="B55" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55" s="34"/>
-      <c r="F55" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="G55" s="26" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
-      <c r="A56" s="23">
-        <v>57</v>
-      </c>
-      <c r="B56" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E56" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="F56" s="33" t="s">
-        <v>134</v>
-      </c>
-      <c r="G56" s="26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
-      <c r="A57" s="23">
-        <v>58</v>
-      </c>
-      <c r="B57" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C57" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="F57" s="33" t="s">
+      <c r="E167" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="G57" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
-      <c r="A58" s="23">
-        <v>59</v>
-      </c>
-      <c r="B58" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C58" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F58" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="G58" s="26" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" hidden="1" spans="1:7">
-      <c r="A59" s="23">
-        <v>60</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>143</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E59" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="F59" s="33" t="s">
-        <v>144</v>
-      </c>
-      <c r="G59" s="26" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" hidden="1" spans="1:7">
-      <c r="A60" s="23">
-        <v>61</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C60" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="36" t="s">
-        <v>125</v>
-      </c>
-      <c r="E60" s="37"/>
-      <c r="F60" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="G60" s="38" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" hidden="1" spans="1:7">
-      <c r="A61" s="23">
-        <v>62</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E61" s="30"/>
-      <c r="F61" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="G61" s="26" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" hidden="1" spans="1:7">
-      <c r="A62" s="23">
-        <v>64</v>
-      </c>
-      <c r="B62" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="41" t="s">
-        <v>125</v>
-      </c>
-      <c r="E62" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="F62" s="42" t="s">
-        <v>153</v>
-      </c>
-      <c r="G62" s="63" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" hidden="1" spans="1:7">
-      <c r="A63" s="23">
-        <v>65</v>
-      </c>
-      <c r="B63" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="C63" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E63" s="32"/>
-      <c r="F63" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" hidden="1" spans="1:7">
-      <c r="A64" s="23">
-        <v>66</v>
-      </c>
-      <c r="B64" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="C64" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E64" s="35"/>
-      <c r="F64" s="43" t="s">
-        <v>159</v>
-      </c>
-      <c r="G64" s="26" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" hidden="1" spans="1:7">
-      <c r="A65" s="23">
-        <v>67</v>
-      </c>
-      <c r="B65" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="C65" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E65" s="32"/>
-      <c r="F65" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="G65" s="64" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" hidden="1" spans="1:7">
-      <c r="A66" s="23">
-        <v>68</v>
-      </c>
-      <c r="B66" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="C66" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F66" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="G66" s="26" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" hidden="1" spans="1:7">
-      <c r="A67" s="23">
-        <v>69</v>
-      </c>
-      <c r="B67" s="24" t="s">
+      <c r="F167" s="19" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" spans="1:7">
+      <c r="A168" s="24">
         <v>167</v>
       </c>
-      <c r="C67" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" s="23"/>
-      <c r="F67" s="33" t="s">
+      <c r="B168" s="25" t="s">
+        <v>425</v>
+      </c>
+      <c r="C168" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E168" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F168" s="19" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" spans="1:7">
+      <c r="A169" s="24">
         <v>168</v>
       </c>
-      <c r="G67" s="63" t="s">
+      <c r="B169" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="C169" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E169" s="28"/>
+    </row>
+    <row r="170" ht="15.75" spans="1:7">
+      <c r="A170" s="24">
         <v>169</v>
       </c>
-    </row>
-    <row r="68" ht="15.75" hidden="1" spans="1:7">
-      <c r="A68" s="23">
-        <v>70</v>
-      </c>
-      <c r="B68" s="24" t="s">
+      <c r="B170" s="25" t="s">
+        <v>428</v>
+      </c>
+      <c r="C170" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E170" s="28"/>
+    </row>
+    <row r="171" ht="15.75" spans="1:7">
+      <c r="A171" s="24">
         <v>170</v>
       </c>
-      <c r="C68" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E68" s="23"/>
-      <c r="F68" s="33" t="s">
+      <c r="B171" s="25" t="s">
+        <v>429</v>
+      </c>
+      <c r="C171" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E171" s="28"/>
+      <c r="F171" s="19" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" spans="1:7">
+      <c r="A172" s="24">
         <v>171</v>
       </c>
-      <c r="G68" s="63" t="s">
+      <c r="B172" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="C172" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E172" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F172" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="G172" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" spans="1:7">
+      <c r="A173" s="24">
         <v>172</v>
       </c>
-    </row>
-    <row r="69" ht="31.5" hidden="1" spans="1:7">
-      <c r="A69" s="23">
-        <v>71</v>
-      </c>
-      <c r="B69" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="C69" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E69" s="23"/>
-      <c r="F69" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="G69" s="63" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" hidden="1" spans="1:7">
-      <c r="A70" s="23">
-        <v>72</v>
-      </c>
-      <c r="B70" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="C70" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E70" s="23"/>
-      <c r="F70" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="G70" s="63" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" hidden="1" spans="1:7">
-      <c r="A71" s="23">
-        <v>73</v>
-      </c>
-      <c r="B71" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="C71" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F71" s="27" t="s">
-        <v>180</v>
-      </c>
-      <c r="G71" s="63" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" hidden="1" spans="1:7">
-      <c r="A72" s="23">
-        <v>74</v>
-      </c>
-      <c r="B72" s="24" t="s">
-        <v>182</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E72" s="23"/>
-      <c r="F72" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="G72" s="26" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" hidden="1" spans="1:7">
-      <c r="A73" s="23">
-        <v>75</v>
-      </c>
-      <c r="B73" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="C73" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E73" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F73" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="G73" s="26" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" hidden="1" spans="1:7">
-      <c r="A74" s="23">
-        <v>76</v>
-      </c>
-      <c r="B74" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E74" s="23"/>
-      <c r="F74" s="33" t="s">
-        <v>189</v>
-      </c>
-      <c r="G74" s="63" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" hidden="1" spans="1:7">
-      <c r="A75" s="23">
-        <v>77</v>
-      </c>
-      <c r="B75" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C75" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E75" s="23" t="s">
+      <c r="B173" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="C173" s="25"/>
+      <c r="D173" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="F75" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="G75" s="26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" hidden="1" spans="1:7">
-      <c r="A76" s="23">
-        <v>78</v>
-      </c>
-      <c r="B76" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="C76" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E76" s="23"/>
-      <c r="F76" s="33" t="s">
-        <v>195</v>
-      </c>
-      <c r="G76" s="26"/>
-    </row>
-    <row r="77" ht="15.75" hidden="1" spans="1:7">
-      <c r="A77" s="23">
-        <v>79</v>
-      </c>
-      <c r="B77" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="C77" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E77" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F77" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="G77" s="63" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" hidden="1" spans="1:7">
-      <c r="A78" s="23">
-        <v>80</v>
-      </c>
-      <c r="B78" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E78" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F78" s="33" t="s">
-        <v>200</v>
-      </c>
-      <c r="G78" s="26" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" hidden="1" spans="1:7">
-      <c r="A79" s="23">
-        <v>81</v>
-      </c>
-      <c r="B79" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="C79" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E79" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F79" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="G79" s="26"/>
-    </row>
-    <row r="80" ht="15.75" hidden="1" spans="1:7">
-      <c r="A80" s="23">
-        <v>82</v>
-      </c>
-      <c r="B80" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="C80" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E80" s="23"/>
-      <c r="F80" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="G80" s="26" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" hidden="1" spans="1:7">
-      <c r="A81" s="23">
-        <v>83</v>
-      </c>
-      <c r="B81" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E81" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F81" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="G81" s="26" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" hidden="1" spans="1:7">
-      <c r="A82" s="23">
-        <v>84</v>
-      </c>
-      <c r="B82" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E82" s="32"/>
-      <c r="F82" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="G82" s="26"/>
-    </row>
-    <row r="83" ht="15.75" hidden="1" spans="1:7">
-      <c r="A83" s="23">
-        <v>85</v>
-      </c>
-      <c r="B83" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="C83" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E83" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F83" s="44" t="s">
-        <v>213</v>
-      </c>
-      <c r="G83" s="26" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" hidden="1" spans="1:7">
-      <c r="A84" s="23">
-        <v>86</v>
-      </c>
-      <c r="B84" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="C84" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E84" s="32"/>
-      <c r="F84" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="G84" s="26"/>
-    </row>
-    <row r="85" ht="15.75" hidden="1" spans="1:7">
-      <c r="A85" s="23">
-        <v>87</v>
-      </c>
-      <c r="B85" s="24" t="s">
-        <v>217</v>
-      </c>
-      <c r="C85" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E85" s="32"/>
-      <c r="F85" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="G85" s="26" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" hidden="1" spans="1:7">
-      <c r="A86" s="23">
-        <v>88</v>
-      </c>
-      <c r="B86" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="C86" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E86" s="35"/>
-      <c r="F86" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="G86" s="26" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" hidden="1" spans="1:7">
-      <c r="A87" s="23">
-        <v>89</v>
-      </c>
-      <c r="B87" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C87" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E87" s="23"/>
-      <c r="F87" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="G87" s="63" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" hidden="1" spans="1:7">
-      <c r="A88" s="23">
-        <v>90</v>
-      </c>
-      <c r="B88" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C88" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E88" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F88" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="G88" s="26" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" hidden="1" spans="1:7">
-      <c r="A89" s="23">
-        <v>91</v>
-      </c>
-      <c r="B89" s="24" t="s">
-        <v>229</v>
-      </c>
-      <c r="C89" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E89" s="23"/>
-      <c r="F89" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="G89" s="63" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" hidden="1" spans="1:7">
-      <c r="A90" s="23">
-        <v>92</v>
-      </c>
-      <c r="B90" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="C90" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>233</v>
-      </c>
-      <c r="F90" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="G90" s="63" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" hidden="1" spans="1:7">
-      <c r="A91" s="23">
-        <v>93</v>
-      </c>
-      <c r="B91" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C91" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E91" s="23"/>
-      <c r="F91" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="G91" s="26" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" hidden="1" spans="1:7">
-      <c r="A92" s="23">
-        <v>94</v>
-      </c>
-      <c r="B92" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="C92" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E92" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F92" s="44" t="s">
-        <v>240</v>
-      </c>
-      <c r="G92" s="63" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" hidden="1" spans="1:7">
-      <c r="A93" s="23">
-        <v>95</v>
-      </c>
-      <c r="B93" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="C93" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E93" s="23"/>
-      <c r="F93" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="G93" s="26" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="94" ht="31.5" hidden="1" spans="1:7">
-      <c r="A94" s="23">
-        <v>96</v>
-      </c>
-      <c r="B94" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="C94" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="E94" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="F94" s="33" t="s">
-        <v>247</v>
-      </c>
-      <c r="G94" s="26" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="95" ht="15.75" hidden="1" spans="1:7">
-      <c r="A95" s="23">
-        <v>97</v>
-      </c>
-      <c r="B95" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C95" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E95" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F95" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="G95" s="26" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="96" ht="15.75" hidden="1" spans="1:7">
-      <c r="A96" s="23">
-        <v>98</v>
-      </c>
-      <c r="B96" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="C96" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E96" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F96" s="33" t="s">
-        <v>253</v>
-      </c>
-      <c r="G96" s="26" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="97" ht="15.75" hidden="1" spans="1:7">
-      <c r="A97" s="23">
-        <v>99</v>
-      </c>
-      <c r="B97" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="C97" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E97" s="23"/>
-      <c r="F97" s="33"/>
-      <c r="G97" s="26"/>
-    </row>
-    <row r="98" ht="15.75" hidden="1" spans="1:7">
-      <c r="A98" s="23">
-        <v>100</v>
-      </c>
-      <c r="B98" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="C98" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D98" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E98" s="35"/>
-      <c r="F98" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="G98" s="26" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" hidden="1" spans="1:7">
-      <c r="A99" s="23">
-        <v>101</v>
-      </c>
-      <c r="B99" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="C99" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E99" s="32"/>
-      <c r="F99" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="G99" s="26"/>
-    </row>
-    <row r="100" ht="15.75" hidden="1" spans="1:7">
-      <c r="A100" s="23">
-        <v>102</v>
-      </c>
-      <c r="B100" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="C100" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D100" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E100" s="35"/>
-      <c r="F100" s="33" t="s">
-        <v>262</v>
-      </c>
-      <c r="G100" s="26" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="101" ht="15.75" hidden="1" spans="1:7">
-      <c r="A101" s="23">
-        <v>103</v>
-      </c>
-      <c r="B101" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="C101" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D101" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E101" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="F101" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="G101" s="26" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="102" ht="15.75" hidden="1" spans="1:7">
-      <c r="A102" s="23">
-        <v>104</v>
-      </c>
-      <c r="B102" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="C102" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D102" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E102" s="35"/>
-      <c r="F102" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="G102" s="26" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="103" ht="15.75" hidden="1" spans="1:7">
-      <c r="A103" s="23">
-        <v>105</v>
-      </c>
-      <c r="B103" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="C103" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D103" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E103" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="F103" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="G103" s="64" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" hidden="1" spans="1:7">
-      <c r="A104" s="23">
-        <v>106</v>
-      </c>
-      <c r="B104" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="C104" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E104" s="23" t="s">
-        <v>274</v>
-      </c>
-      <c r="F104" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="G104" s="26"/>
-    </row>
-    <row r="105" ht="15.75" hidden="1" spans="1:7">
-      <c r="A105" s="23">
-        <v>107</v>
-      </c>
-      <c r="B105" s="24" t="s">
-        <v>276</v>
-      </c>
-      <c r="C105" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D105" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E105" s="46"/>
-      <c r="F105" s="33" t="s">
-        <v>277</v>
-      </c>
-      <c r="G105" s="28"/>
-    </row>
-    <row r="106" ht="15.75" hidden="1" spans="1:7">
-      <c r="A106" s="23">
-        <v>108</v>
-      </c>
-      <c r="B106" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="C106" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D106" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E106" s="46"/>
-      <c r="F106" s="33" t="s">
-        <v>279</v>
-      </c>
-      <c r="G106" s="28"/>
-    </row>
-    <row r="107" ht="15.75" hidden="1" spans="1:7">
-      <c r="A107" s="23">
-        <v>109</v>
-      </c>
-      <c r="B107" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="C107" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D107" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E107" s="46"/>
-      <c r="F107" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="G107" s="28"/>
-    </row>
-    <row r="108" ht="15.75" hidden="1" spans="1:7">
-      <c r="A108" s="23">
-        <v>110</v>
-      </c>
-      <c r="B108" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D108" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E108" s="46"/>
-      <c r="F108" s="33" t="s">
-        <v>283</v>
-      </c>
-      <c r="G108" s="28"/>
-    </row>
-    <row r="109" ht="31.5" hidden="1" spans="1:7">
-      <c r="A109" s="23">
-        <v>111</v>
-      </c>
-      <c r="B109" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="C109" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E109" s="46"/>
-      <c r="F109" s="33" t="s">
-        <v>285</v>
-      </c>
-      <c r="G109" s="28"/>
-    </row>
-    <row r="110" ht="15.75" hidden="1" spans="1:7">
-      <c r="A110" s="23">
-        <v>112</v>
-      </c>
-      <c r="B110" s="24" t="s">
-        <v>286</v>
-      </c>
-      <c r="C110" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D110" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E110" s="46"/>
-      <c r="F110" s="33" t="s">
-        <v>287</v>
-      </c>
-      <c r="G110" s="28"/>
-    </row>
-    <row r="111" ht="15.75" hidden="1" spans="1:7">
-      <c r="A111" s="23">
-        <v>113</v>
-      </c>
-      <c r="B111" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="C111" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E111" s="46"/>
-      <c r="F111" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="G111" s="28"/>
-    </row>
-    <row r="112" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
-      <c r="A112" s="23">
-        <v>114</v>
-      </c>
-      <c r="B112" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="C112" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D112" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E112" s="46"/>
-      <c r="F112" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="G112" s="28"/>
-    </row>
-    <row r="113" ht="15.75" hidden="1" spans="1:7">
-      <c r="A113" s="23">
-        <v>115</v>
-      </c>
-      <c r="B113" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="C113" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D113" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E113" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="F113" s="33" t="s">
-        <v>292</v>
-      </c>
-      <c r="G113" s="28"/>
-    </row>
-    <row r="114" ht="15.75" hidden="1" spans="1:7">
-      <c r="A114" s="23">
-        <v>116</v>
-      </c>
-      <c r="B114" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="C114" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D114" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E114" s="46"/>
-      <c r="F114" s="33" t="s">
-        <v>294</v>
-      </c>
-      <c r="G114" s="28"/>
-    </row>
-    <row r="115" ht="15.75" hidden="1" spans="1:7">
-      <c r="A115" s="23">
-        <v>117</v>
-      </c>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E115" s="46"/>
-      <c r="F115" s="33" t="s">
-        <v>295</v>
-      </c>
-      <c r="G115" s="28"/>
-    </row>
-    <row r="116" ht="15.75" hidden="1" spans="1:7">
-      <c r="A116" s="23">
-        <v>118</v>
-      </c>
-      <c r="B116" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="C116" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D116" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E116" s="46"/>
-      <c r="F116" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="G116" s="28"/>
-    </row>
-    <row r="117" ht="15.75" hidden="1" spans="1:7">
-      <c r="A117" s="23">
-        <v>119</v>
-      </c>
-      <c r="B117" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="C117" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D117" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E117" s="46"/>
-      <c r="F117" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="G117" s="28"/>
-    </row>
-    <row r="118" ht="15.75" hidden="1" spans="1:7">
-      <c r="A118" s="23">
-        <v>120</v>
-      </c>
-      <c r="B118" s="24" t="s">
-        <v>300</v>
-      </c>
-      <c r="C118" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D118" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E118" s="46"/>
-      <c r="F118" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="G118" s="28"/>
-    </row>
-    <row r="119" ht="15.75" hidden="1" spans="1:7">
-      <c r="A119" s="23">
-        <v>121</v>
-      </c>
-      <c r="B119" s="24" t="s">
-        <v>302</v>
-      </c>
-      <c r="C119" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D119" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E119" s="46"/>
-      <c r="F119" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="G119" s="28"/>
-    </row>
-    <row r="120" ht="15.75" hidden="1" spans="1:7">
-      <c r="A120" s="23">
-        <v>122</v>
-      </c>
-      <c r="B120" s="24" t="s">
-        <v>304</v>
-      </c>
-      <c r="C120" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D120" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E120" s="46"/>
-      <c r="F120" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="G120" s="47"/>
-    </row>
-    <row r="121" ht="15.75" hidden="1" spans="1:7">
-      <c r="A121" s="23">
-        <v>123</v>
-      </c>
-      <c r="B121" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C121" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E121" s="46"/>
-      <c r="F121" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="G121" s="28"/>
-    </row>
-    <row r="122" ht="15.75" hidden="1" spans="1:7">
-      <c r="A122" s="23">
-        <v>124</v>
-      </c>
-      <c r="B122" s="24" t="s">
-        <v>308</v>
-      </c>
-      <c r="C122" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D122" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E122" s="45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="G122" s="28"/>
-    </row>
-    <row r="123" ht="31.5" hidden="1" spans="1:7">
-      <c r="A123" s="23">
-        <v>125</v>
-      </c>
-      <c r="B123" s="24" t="s">
-        <v>310</v>
-      </c>
-      <c r="C123" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="45" t="s">
-        <v>311</v>
-      </c>
-      <c r="E123" s="45" t="s">
-        <v>29</v>
-      </c>
-      <c r="F123" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="G123" s="28"/>
-    </row>
-    <row r="124" ht="15.75" hidden="1" spans="1:7">
-      <c r="A124" s="23">
-        <v>126</v>
-      </c>
-      <c r="B124" s="24" t="s">
-        <v>313</v>
-      </c>
-      <c r="C124" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D124" s="45" t="s">
-        <v>125</v>
-      </c>
-      <c r="E124" s="46"/>
-      <c r="F124" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="G124" s="28"/>
-    </row>
-    <row r="125" ht="15.75" hidden="1" spans="1:7">
-      <c r="A125" s="23">
-        <v>127</v>
-      </c>
-      <c r="B125" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="C125" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="F125" s="33" t="s">
-        <v>316</v>
-      </c>
-      <c r="G125" s="28"/>
-    </row>
-    <row r="126" ht="15.75" hidden="1" spans="1:7">
-      <c r="A126" s="23">
-        <v>128</v>
-      </c>
-      <c r="B126" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="C126" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="F126" s="33" t="s">
-        <v>318</v>
-      </c>
-      <c r="G126" s="28"/>
-    </row>
-    <row r="127" ht="15.75" hidden="1" spans="1:7">
-      <c r="A127" s="23">
-        <v>129</v>
-      </c>
-      <c r="B127" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="C127" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D127" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="F127" s="33" t="s">
-        <v>320</v>
-      </c>
-      <c r="G127" s="63" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="128" ht="15.75" hidden="1" spans="1:7">
-      <c r="A128" s="23">
-        <v>130</v>
-      </c>
-      <c r="B128" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="C128" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E128" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F128" s="33" t="s">
-        <v>323</v>
-      </c>
-      <c r="G128" s="65" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" hidden="1" spans="1:7">
-      <c r="A129" s="23">
-        <v>131</v>
-      </c>
-      <c r="B129" s="50" t="s">
-        <v>325</v>
-      </c>
-      <c r="C129" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="F129" s="33" t="s">
-        <v>326</v>
-      </c>
-      <c r="G129" s="65" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" hidden="1" spans="1:7">
-      <c r="A130" s="23">
-        <v>132</v>
-      </c>
-      <c r="B130" s="50" t="s">
-        <v>328</v>
-      </c>
-      <c r="C130" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D130" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E130" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F130" s="33" t="s">
-        <v>329</v>
-      </c>
-      <c r="G130" s="65" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="131" ht="15.75" hidden="1" spans="1:7">
-      <c r="A131" s="23">
-        <v>133</v>
-      </c>
-      <c r="B131" s="50" t="s">
-        <v>306</v>
-      </c>
-      <c r="C131" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D131" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E131" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F131" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="G131" s="65" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="132" ht="15.75" hidden="1" spans="1:7">
-      <c r="A132" s="23">
-        <v>134</v>
-      </c>
-      <c r="B132" s="50" t="s">
-        <v>332</v>
-      </c>
-      <c r="C132" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D132" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="E132" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="F132" s="33" t="s">
-        <v>333</v>
-      </c>
-      <c r="G132" s="50"/>
-    </row>
-    <row r="133" ht="15.75" hidden="1" spans="1:7">
-      <c r="A133" s="23">
-        <v>135</v>
-      </c>
-      <c r="B133" s="50" t="s">
-        <v>334</v>
-      </c>
-      <c r="C133" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D133" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E133" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F133" s="33" t="s">
-        <v>335</v>
-      </c>
-      <c r="G133" s="49" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" hidden="1" spans="1:7">
-      <c r="A134" s="23">
-        <v>136</v>
-      </c>
-      <c r="B134" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="C134" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D134" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E134" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F134" s="33" t="s">
-        <v>338</v>
-      </c>
-      <c r="G134" s="65" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="135" ht="15.75" hidden="1" spans="1:7">
-      <c r="A135" s="23">
-        <v>137</v>
-      </c>
-      <c r="B135" s="50" t="s">
-        <v>340</v>
-      </c>
-      <c r="C135" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D135" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E135" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F135" s="33" t="s">
-        <v>341</v>
-      </c>
-      <c r="G135" s="65" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="136" ht="15.75" hidden="1" spans="1:7">
-      <c r="A136" s="23">
-        <v>138</v>
-      </c>
-      <c r="B136" s="24"/>
-      <c r="C136" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D136" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E136" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F136" s="33" t="s">
-        <v>343</v>
-      </c>
-      <c r="G136" s="65" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="137" ht="15.75" hidden="1" spans="1:7">
-      <c r="A137" s="23">
-        <v>139</v>
-      </c>
-      <c r="B137" s="50" t="s">
-        <v>345</v>
-      </c>
-      <c r="C137" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D137" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" s="48" t="s">
-        <v>346</v>
-      </c>
-      <c r="F137" s="33" t="s">
-        <v>347</v>
-      </c>
-      <c r="G137" s="50"/>
-    </row>
-    <row r="138" ht="15.75" hidden="1" spans="1:7">
-      <c r="A138" s="23">
-        <v>140</v>
-      </c>
-      <c r="B138" s="50" t="s">
-        <v>348</v>
-      </c>
-      <c r="C138" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D138" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E138" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="F138" s="33" t="s">
-        <v>349</v>
-      </c>
-      <c r="G138" s="66" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="139" ht="15.75" hidden="1" spans="1:7">
-      <c r="A139" s="23">
-        <v>141</v>
-      </c>
-      <c r="B139" s="50" t="s">
-        <v>351</v>
-      </c>
-      <c r="C139" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="48" t="s">
-        <v>125</v>
-      </c>
-      <c r="E139" s="48" t="s">
-        <v>233</v>
-      </c>
-      <c r="F139" s="33" t="s">
-        <v>352</v>
-      </c>
-      <c r="G139" s="50"/>
-    </row>
-    <row r="140" ht="15.75" hidden="1" spans="1:7">
-      <c r="A140" s="23">
-        <v>142</v>
-      </c>
-      <c r="B140" s="50" t="s">
-        <v>353</v>
-      </c>
-      <c r="C140" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="F140" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="G140" s="50"/>
-    </row>
-    <row r="141" ht="15.75" hidden="1" spans="1:7">
-      <c r="A141" s="23">
-        <v>143</v>
-      </c>
-      <c r="B141" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="C141" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D141" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E141" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F141" s="33" t="s">
-        <v>192</v>
-      </c>
-      <c r="G141" s="26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="142" ht="15.75" hidden="1" spans="1:7">
-      <c r="A142" s="23">
-        <v>144</v>
-      </c>
-      <c r="B142" s="24" t="s">
-        <v>355</v>
-      </c>
-      <c r="C142" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E142" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F142" s="33" t="s">
-        <v>356</v>
-      </c>
-      <c r="G142" s="50"/>
-    </row>
-    <row r="143" ht="15.75" hidden="1" spans="1:7">
-      <c r="A143" s="23">
-        <v>145</v>
-      </c>
-      <c r="B143" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="C143" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E143" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F143" s="33" t="s">
-        <v>358</v>
-      </c>
-      <c r="G143" s="50" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="144" ht="19" hidden="1" customHeight="1" spans="1:7">
-      <c r="A144" s="23">
-        <v>145</v>
-      </c>
-      <c r="B144" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="C144" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D144" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E144" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F144" s="33" t="s">
-        <v>361</v>
-      </c>
-      <c r="G144" s="26"/>
-    </row>
-    <row r="145" ht="15.75" spans="1:7">
-      <c r="A145" s="23">
-        <v>146</v>
-      </c>
-      <c r="B145" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="C145" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D145" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E145" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F145" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="G145" s="26"/>
-    </row>
-    <row r="146" ht="15.75" hidden="1" spans="1:7">
-      <c r="A146" s="23">
-        <v>147</v>
-      </c>
-      <c r="B146" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="C146" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D146" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E146" s="32"/>
-      <c r="F146" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="G146" s="67" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="147" ht="15.75" hidden="1" spans="1:7">
-      <c r="A147" s="23">
-        <v>148</v>
-      </c>
-      <c r="B147" s="24" t="s">
-        <v>365</v>
-      </c>
-      <c r="C147" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D147" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E147" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F147" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="G147" s="64" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="148" ht="15.75" hidden="1" spans="1:7">
-      <c r="A148" s="23">
-        <v>149</v>
-      </c>
-      <c r="B148" s="53" t="s">
-        <v>368</v>
-      </c>
-      <c r="C148" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D148" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F148" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="G148" s="26"/>
-    </row>
-    <row r="149" ht="15.75" hidden="1" spans="1:7">
-      <c r="A149" s="23">
-        <v>150</v>
-      </c>
-      <c r="B149" s="54" t="s">
-        <v>370</v>
-      </c>
-      <c r="C149" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D149" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E149" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F149" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="G149" s="55"/>
-    </row>
-    <row r="150" ht="15.75" hidden="1" spans="1:7">
-      <c r="A150" s="32">
-        <v>151</v>
-      </c>
-      <c r="B150" s="53" t="s">
-        <v>372</v>
-      </c>
-      <c r="C150" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E150" s="32"/>
-      <c r="F150" s="25" t="s">
-        <v>373</v>
-      </c>
-      <c r="G150" s="55"/>
-    </row>
-    <row r="151" ht="15.75" hidden="1" spans="1:7">
-      <c r="A151" s="32">
-        <v>152</v>
-      </c>
-      <c r="B151" s="53" t="s">
-        <v>374</v>
-      </c>
-      <c r="C151" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E151" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F151" s="56" t="s">
-        <v>375</v>
-      </c>
-      <c r="G151" s="26"/>
-    </row>
-    <row r="152" ht="15.75" hidden="1" spans="1:7">
-      <c r="A152" s="32">
-        <v>153</v>
-      </c>
-      <c r="B152" s="26" t="s">
-        <v>376</v>
-      </c>
-      <c r="C152" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D152" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E152" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F152" s="25" t="s">
-        <v>377</v>
-      </c>
-      <c r="G152" s="26"/>
-    </row>
-    <row r="153" ht="15.75" hidden="1" spans="1:7">
-      <c r="A153" s="32">
-        <v>153</v>
-      </c>
-      <c r="B153" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="C153" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E153" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F153" s="25" t="s">
-        <v>379</v>
-      </c>
-      <c r="G153" s="26"/>
-    </row>
-    <row r="154" ht="15.75" hidden="1" spans="1:7">
-      <c r="A154" s="32">
-        <v>154</v>
-      </c>
-      <c r="B154" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="C154" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D154" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F154" s="25" t="s">
-        <v>381</v>
-      </c>
-      <c r="G154" s="26"/>
-    </row>
-    <row r="155" ht="15.75" hidden="1" spans="1:7">
-      <c r="A155" s="32">
-        <v>155</v>
-      </c>
-      <c r="B155" s="28" t="s">
-        <v>382</v>
-      </c>
-      <c r="C155" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D155" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F155" s="25" t="s">
-        <v>383</v>
-      </c>
-      <c r="G155" s="26"/>
-    </row>
-    <row r="156" ht="15.75" hidden="1" spans="1:7">
-      <c r="A156" s="32">
-        <v>156</v>
-      </c>
-      <c r="B156" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="C156" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D156" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E156" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F156" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="G156" s="26"/>
-    </row>
-    <row r="157" ht="15.75" hidden="1" spans="1:7">
-      <c r="A157" s="32">
-        <v>156</v>
-      </c>
-      <c r="B157" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="C157" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D157" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E157" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F157" s="25" t="s">
-        <v>387</v>
-      </c>
-      <c r="G157" s="26"/>
-    </row>
-    <row r="158" ht="15.75" hidden="1" spans="1:7">
-      <c r="A158" s="32">
-        <v>157</v>
-      </c>
-      <c r="B158" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="C158" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D158" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E158" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F158" s="25" t="s">
-        <v>389</v>
-      </c>
-      <c r="G158" s="26"/>
-    </row>
-    <row r="159" ht="15.75" hidden="1" spans="1:7">
-      <c r="A159" s="32">
-        <v>157</v>
-      </c>
-      <c r="B159" s="26" t="s">
-        <v>390</v>
-      </c>
-      <c r="C159" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D159" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E159" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F159" s="57" t="s">
-        <v>391</v>
-      </c>
-      <c r="G159" s="26"/>
-    </row>
-    <row r="160" ht="15.75" hidden="1" spans="1:7">
-      <c r="A160" s="32">
-        <v>158</v>
-      </c>
-      <c r="B160" s="28" t="s">
-        <v>392</v>
-      </c>
-      <c r="C160" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D160" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E160" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F160" s="58" t="s">
-        <v>393</v>
-      </c>
-      <c r="G160" s="64" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="161" ht="15.75" hidden="1" spans="1:7">
-      <c r="A161" s="32">
-        <v>159</v>
-      </c>
-      <c r="B161" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="C161" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E161" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="F161" s="59" t="s">
-        <v>396</v>
-      </c>
-      <c r="G161" s="26"/>
-    </row>
-    <row r="162" ht="15.75" hidden="1" spans="1:7">
-      <c r="A162" s="32">
-        <v>160</v>
-      </c>
-      <c r="B162" s="53" t="s">
-        <v>397</v>
-      </c>
-      <c r="C162" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D162" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E162" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F162" s="25" t="s">
-        <v>398</v>
-      </c>
-      <c r="G162" s="64" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="163" ht="15.75" hidden="1" spans="1:7">
-      <c r="A163" s="32">
-        <v>161</v>
-      </c>
-      <c r="B163" s="53" t="s">
-        <v>400</v>
-      </c>
-      <c r="C163" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D163" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E163" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F163" s="26"/>
-      <c r="G163" s="64" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="164" s="16" customFormat="1" ht="15.75" hidden="1" spans="1:7">
-      <c r="A164" s="32">
-        <v>162</v>
-      </c>
-      <c r="B164" s="53" t="s">
-        <v>402</v>
-      </c>
-      <c r="C164" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D164" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E164" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F164" s="57" t="s">
-        <v>403</v>
-      </c>
-      <c r="G164" s="64" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="165" ht="15.75" hidden="1" spans="1:7">
-      <c r="A165" s="32">
-        <v>163</v>
-      </c>
-      <c r="B165" s="53" t="s">
-        <v>405</v>
-      </c>
-      <c r="C165" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D165" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E165" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="F165" s="25" t="s">
-        <v>406</v>
-      </c>
-      <c r="G165" s="64" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="166" ht="15.75" hidden="1" spans="1:7">
-      <c r="A166" s="32">
-        <v>164</v>
-      </c>
-      <c r="B166" s="60" t="s">
-        <v>408</v>
-      </c>
-      <c r="C166" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D166" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="E166" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="F166" s="61" t="s">
-        <v>409</v>
-      </c>
-      <c r="G166" s="68" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="167" ht="15.75" hidden="1" spans="1:7">
-      <c r="A167" s="32">
-        <v>165</v>
-      </c>
-      <c r="B167" s="26" t="s">
-        <v>411</v>
-      </c>
-      <c r="C167" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D167" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="E167" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="F167" s="62" t="s">
-        <v>412</v>
-      </c>
-      <c r="G167" s="68" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7">
-      <c r="D168" s="18"/>
-    </row>
-    <row r="169" spans="1:7">
-      <c r="D169" s="18"/>
-    </row>
-    <row r="170" spans="1:7">
-      <c r="D170" s="18"/>
-    </row>
-    <row r="171" spans="1:7">
-      <c r="D171" s="18"/>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="D172" s="18"/>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="D173" s="18"/>
+      <c r="E173" s="28"/>
     </row>
     <row r="174" spans="1:7">
       <c r="D174" s="18"/>
@@ -9279,17 +9221,14 @@
     <row r="1160" spans="4:4">
       <c r="D1160" s="18"/>
     </row>
-    <row r="1161" spans="4:4">
-      <c r="D1161" s="18"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G167" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G173" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
       <filters>
-        <filter val="FILALI INES"/>
+        <filter val="Vacataire"/>
       </filters>
     </filterColumn>
-    <sortState ref="A1:G167">
+    <sortState ref="A1:G173">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9300,66 +9239,65 @@
     <hyperlink ref="F54" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
     <hyperlink ref="F105" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
     <hyperlink ref="F106" r:id="rId5" display="aliaissani97@gmail.com"/>
-    <hyperlink ref="F124" r:id="rId6" display="medzerdani@gmail.com"/>
-    <hyperlink ref="F121" r:id="rId7" display="turkibilal22@gmail.com"/>
-    <hyperlink ref="F120" r:id="rId8" display="sacihamza40@gmail.com"/>
-    <hyperlink ref="F119" r:id="rId9" display="Boba1620@hotmail.com"/>
+    <hyperlink ref="F123" r:id="rId6" display="medzerdani@gmail.com"/>
+    <hyperlink ref="F120" r:id="rId7" display="turkibilal22@gmail.com"/>
+    <hyperlink ref="F119" r:id="rId8" display="sacihamza40@gmail.com"/>
+    <hyperlink ref="F118" r:id="rId9" display="Boba1620@hotmail.com"/>
     <hyperlink ref="F95" r:id="rId10" display="khelifa-mir@outlook.fr"/>
     <hyperlink ref="F76" r:id="rId11" display="fethi22miloua@gmail.com"/>
     <hyperlink ref="F74" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
     <hyperlink ref="F93" r:id="rId13" display="mehadjiameslem@gmail.com"/>
     <hyperlink ref="F91" r:id="rId14" display="mekhalefleila@gmail.com"/>
     <hyperlink ref="F90" r:id="rId15" display="khalidamet4@gmail.com"/>
-    <hyperlink ref="F118" r:id="rId16" display="layatimedi@gmail.com"/>
+    <hyperlink ref="F117" r:id="rId16" display="layatimedi@gmail.com"/>
     <hyperlink ref="F85" r:id="rId17" display="m_latreche@yahoo.com"/>
-    <hyperlink ref="F117" r:id="rId18" display="kadrirania51@gmail.com"/>
+    <hyperlink ref="F116" r:id="rId18" display="kadrirania51@gmail.com"/>
     <hyperlink ref="F81" r:id="rId19" display="protoboy9999@gmail.com"/>
-    <hyperlink ref="F115" r:id="rId20" display="khadidjafezazi90@gmail"/>
-    <hyperlink ref="F75" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F72" r:id="rId22" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
-    <hyperlink ref="F67" r:id="rId23" display="douaaboularaf@gmail.com"/>
-    <hyperlink ref="F111" r:id="rId24" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F109" r:id="rId25" display="bkbhbb22@gmail.com"/>
-    <hyperlink ref="F59" r:id="rId26" display="bendida65@gmail.com"/>
-    <hyperlink ref="F58" r:id="rId27" display="sarrabencella@gmail.com"/>
-    <hyperlink ref="F60" r:id="rId28" display="ri123hab@gmail.com"/>
-    <hyperlink ref="F108" r:id="rId29" display="meriembelabed5@gmail.com"/>
-    <hyperlink ref="F45" r:id="rId30" display="rezoug.med@gmail.com"/>
-    <hyperlink ref="F84" r:id="rId31" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
-    <hyperlink ref="F57" r:id="rId32" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
-    <hyperlink ref="F100" r:id="rId33" display="zarebmohammedamine@gmail.com"/>
-    <hyperlink ref="F101" r:id="rId34" display="djamel71ziani@gmail.com"/>
-    <hyperlink ref="F65" r:id="rId35" display="ahmedboudali32@gmail.com"/>
-    <hyperlink ref="F69" r:id="rId36" display="chaouche.abdallah@gmail.com"/>
-    <hyperlink ref="F61" r:id="rId37" display="lakhdar_belhallouche@hotmail.fr"/>
-    <hyperlink ref="F80" r:id="rId38" display="ahmed.hadji22@yahoo.com"/>
-    <hyperlink ref="F103" r:id="rId39" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F32" r:id="rId40" display="khatir.mohamed1977@gmail.com"/>
-    <hyperlink ref="F2" r:id="rId41" display="irecom_abid@yahoo.fr"/>
-    <hyperlink ref="F7" r:id="rId42" display="karis483@hotmail.fr"/>
-    <hyperlink ref="F8" r:id="rId43" display="bahlilmounir@yahoo.fr"/>
-    <hyperlink ref="F10" r:id="rId44" display="beddadboucif@gmail.com"/>
-    <hyperlink ref="F9" r:id="rId45" display="seyfeddine.electrotechnique@gmail.com"/>
-    <hyperlink ref="F127" r:id="rId46" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
-    <hyperlink ref="F112" r:id="rId47" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
-    <hyperlink ref="F141" r:id="rId21" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F142" r:id="rId48" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
-    <hyperlink ref="F144" r:id="rId49" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
-    <hyperlink ref="F143" r:id="rId50" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
-    <hyperlink ref="F147" r:id="rId51" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
-    <hyperlink ref="F150" r:id="rId52" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
-    <hyperlink ref="F151" r:id="rId53" display="walid.sebastien@gmail.com"/>
-    <hyperlink ref="F152" r:id="rId54" display="bensenadanadia3@gmail.com"/>
-    <hyperlink ref="F153" r:id="rId55" display="imedmedles@gmail.com"/>
-    <hyperlink ref="F156" r:id="rId56" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
-    <hyperlink ref="F160" r:id="rId57" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
-    <hyperlink ref="F162" r:id="rId58" display="moh@medbnr.com"/>
-    <hyperlink ref="F164" r:id="rId59" display="hadilyamoune@gmail.com"/>
-    <hyperlink ref="F165" r:id="rId60" display="megdz100@gmail.com"/>
-    <hyperlink ref="F159" r:id="rId61" display="ikkachenarimen.2017@gmail.com"/>
-    <hyperlink ref="F161" r:id="rId62" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
-    <hyperlink ref="F166" r:id="rId63" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
-    <hyperlink ref="F145" r:id="rId64" display="inesfilali2003@gmail.com"/>
+    <hyperlink ref="F75" r:id="rId20" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F72" r:id="rId21" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F67" r:id="rId22" display="douaaboularaf@gmail.com"/>
+    <hyperlink ref="F111" r:id="rId23" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F109" r:id="rId24" display="bkbhbb22@gmail.com"/>
+    <hyperlink ref="F59" r:id="rId25" display="bendida65@gmail.com"/>
+    <hyperlink ref="F58" r:id="rId26" display="sarrabencella@gmail.com"/>
+    <hyperlink ref="F60" r:id="rId27" display="ri123hab@gmail.com"/>
+    <hyperlink ref="F108" r:id="rId28" display="meriembelabed5@gmail.com"/>
+    <hyperlink ref="F45" r:id="rId29" display="rezoug.med@gmail.com"/>
+    <hyperlink ref="F84" r:id="rId30" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
+    <hyperlink ref="F57" r:id="rId31" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
+    <hyperlink ref="F100" r:id="rId32" display="zarebmohammedamine@gmail.com"/>
+    <hyperlink ref="F101" r:id="rId33" display="djamel71ziani@gmail.com"/>
+    <hyperlink ref="F65" r:id="rId34" display="ahmedboudali32@gmail.com"/>
+    <hyperlink ref="F69" r:id="rId35" display="chaouche.abdallah@gmail.com"/>
+    <hyperlink ref="F61" r:id="rId36" display="lakhdar_belhallouche@hotmail.fr"/>
+    <hyperlink ref="F80" r:id="rId37" display="ahmed.hadji22@yahoo.com"/>
+    <hyperlink ref="F103" r:id="rId38" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F32" r:id="rId39" display="khatir.mohamed1977@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId40" display="irecom_abid@yahoo.fr"/>
+    <hyperlink ref="F7" r:id="rId41" display="karis483@hotmail.fr"/>
+    <hyperlink ref="F8" r:id="rId42" display="bahlilmounir@yahoo.fr"/>
+    <hyperlink ref="F10" r:id="rId43" display="beddadboucif@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId44" display="seyfeddine.electrotechnique@gmail.com"/>
+    <hyperlink ref="F126" r:id="rId45" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F112" r:id="rId46" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F140" r:id="rId20" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F141" r:id="rId47" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
+    <hyperlink ref="F143" r:id="rId48" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
+    <hyperlink ref="F142" r:id="rId49" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
+    <hyperlink ref="F146" r:id="rId50" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
+    <hyperlink ref="F149" r:id="rId51" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
+    <hyperlink ref="F150" r:id="rId52" display="walid.sebastien@gmail.com"/>
+    <hyperlink ref="F151" r:id="rId53" display="bensenadanadia3@gmail.com"/>
+    <hyperlink ref="F152" r:id="rId54" display="imedmedles@gmail.com"/>
+    <hyperlink ref="F155" r:id="rId55" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
+    <hyperlink ref="F159" r:id="rId56" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
+    <hyperlink ref="F161" r:id="rId57" display="moh@medbnr.com"/>
+    <hyperlink ref="F163" r:id="rId58" display="hadilyamoune@gmail.com"/>
+    <hyperlink ref="F164" r:id="rId59" display="megdz100@gmail.com"/>
+    <hyperlink ref="F158" r:id="rId60" display="ikkachenarimen.2017@gmail.com"/>
+    <hyperlink ref="F160" r:id="rId61" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
+    <hyperlink ref="F165" r:id="rId62" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
+    <hyperlink ref="F144" r:id="rId63" display="inesfilali2003@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -9382,202 +9320,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -316,7 +316,7 @@
     <t>0558193860</t>
   </si>
   <si>
-    <t>BRAHAMI MOHAMED NADJIB</t>
+    <t>BRAHAMI MOHAMMED NADJIB</t>
   </si>
   <si>
     <t>nadjbrahami@gmail.com</t>
@@ -3182,7 +3182,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" ht="15.75" hidden="1" spans="1:7">
+    <row r="26" ht="15.75" spans="1:7">
       <c r="A26" s="24">
         <v>25</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" ht="15.75" hidden="1" spans="1:7">
+    <row r="39" ht="15.75" spans="1:7">
       <c r="A39" s="24">
         <v>39</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="45" ht="15.75" hidden="1" spans="1:7">
+    <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="24">
         <v>45</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="54" ht="15.75" spans="1:7">
+    <row r="54" ht="15.75" hidden="1" spans="1:7">
       <c r="A54" s="24">
         <v>54</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" ht="15.75" spans="1:7">
+    <row r="55" ht="15.75" hidden="1" spans="1:7">
       <c r="A55" s="24">
         <v>55</v>
       </c>
@@ -3795,7 +3795,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" ht="15.75" spans="1:7">
+    <row r="56" ht="15.75" hidden="1" spans="1:7">
       <c r="A56" s="24">
         <v>57</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="57" ht="15.75" spans="1:7">
+    <row r="57" ht="15.75" hidden="1" spans="1:7">
       <c r="A57" s="24">
         <v>58</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="58" ht="15.75" spans="1:7">
+    <row r="58" ht="15.75" hidden="1" spans="1:7">
       <c r="A58" s="24">
         <v>59</v>
       </c>
@@ -3864,7 +3864,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="59" ht="15.75" spans="1:7">
+    <row r="59" ht="15.75" hidden="1" spans="1:7">
       <c r="A59" s="24">
         <v>60</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" ht="15.75" spans="1:7">
+    <row r="60" ht="15.75" hidden="1" spans="1:7">
       <c r="A60" s="24">
         <v>61</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" ht="15.75" spans="1:7">
+    <row r="61" ht="15.75" hidden="1" spans="1:7">
       <c r="A61" s="24">
         <v>62</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" ht="15.75" spans="1:7">
+    <row r="63" ht="15.75" hidden="1" spans="1:7">
       <c r="A63" s="24">
         <v>65</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" ht="15.75" spans="1:7">
+    <row r="64" ht="15.75" hidden="1" spans="1:7">
       <c r="A64" s="24">
         <v>66</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="65" ht="15.75" spans="1:7">
+    <row r="65" ht="15.75" hidden="1" spans="1:7">
       <c r="A65" s="24">
         <v>67</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" ht="15.75" spans="1:7">
+    <row r="66" ht="15.75" hidden="1" spans="1:7">
       <c r="A66" s="24">
         <v>68</v>
       </c>
@@ -4038,7 +4038,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" ht="15.75" spans="1:7">
+    <row r="67" ht="15.75" hidden="1" spans="1:7">
       <c r="A67" s="24">
         <v>69</v>
       </c>
@@ -4059,7 +4059,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="68" ht="15.75" spans="1:7">
+    <row r="68" ht="15.75" hidden="1" spans="1:7">
       <c r="A68" s="24">
         <v>70</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" ht="31.5" spans="1:7">
+    <row r="69" ht="31.5" hidden="1" spans="1:7">
       <c r="A69" s="24">
         <v>71</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="70" ht="15.75" spans="1:7">
+    <row r="70" ht="15.75" hidden="1" spans="1:7">
       <c r="A70" s="24">
         <v>72</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="71" ht="15.75" spans="1:7">
+    <row r="71" ht="15.75" hidden="1" spans="1:7">
       <c r="A71" s="24">
         <v>73</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="72" ht="15.75" spans="1:7">
+    <row r="72" ht="15.75" hidden="1" spans="1:7">
       <c r="A72" s="24">
         <v>74</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="73" ht="15.75" spans="1:7">
+    <row r="73" ht="15.75" hidden="1" spans="1:7">
       <c r="A73" s="24">
         <v>75</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="74" ht="15.75" spans="1:7">
+    <row r="74" ht="15.75" hidden="1" spans="1:7">
       <c r="A74" s="24">
         <v>76</v>
       </c>
@@ -4210,7 +4210,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="75" ht="15.75" spans="1:7">
+    <row r="75" ht="15.75" hidden="1" spans="1:7">
       <c r="A75" s="24">
         <v>77</v>
       </c>
@@ -4233,7 +4233,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="76" ht="15.75" spans="1:7">
+    <row r="76" ht="15.75" hidden="1" spans="1:7">
       <c r="A76" s="24">
         <v>78</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="77" ht="15.75" spans="1:7">
+    <row r="77" ht="15.75" hidden="1" spans="1:7">
       <c r="A77" s="24">
         <v>79</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="78" ht="15.75" spans="1:7">
+    <row r="78" ht="15.75" hidden="1" spans="1:7">
       <c r="A78" s="24">
         <v>80</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="79" ht="15.75" spans="1:7">
+    <row r="79" ht="15.75" hidden="1" spans="1:7">
       <c r="A79" s="24">
         <v>81</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="80" ht="15.75" spans="1:7">
+    <row r="80" ht="15.75" hidden="1" spans="1:7">
       <c r="A80" s="24">
         <v>82</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" ht="15.75" spans="1:7">
+    <row r="81" ht="15.75" hidden="1" spans="1:7">
       <c r="A81" s="24">
         <v>83</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="82" ht="15.75" spans="1:7">
+    <row r="82" ht="15.75" hidden="1" spans="1:7">
       <c r="A82" s="24">
         <v>84</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="83" ht="15.75" spans="1:7">
+    <row r="83" ht="15.75" hidden="1" spans="1:7">
       <c r="A83" s="24">
         <v>85</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="84" ht="15.75" spans="1:7">
+    <row r="84" ht="15.75" hidden="1" spans="1:7">
       <c r="A84" s="24">
         <v>86</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="85" ht="15.75" spans="1:7">
+    <row r="85" ht="15.75" hidden="1" spans="1:7">
       <c r="A85" s="24">
         <v>87</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="86" ht="15.75" spans="1:7">
+    <row r="86" ht="15.75" hidden="1" spans="1:7">
       <c r="A86" s="24">
         <v>88</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="87" ht="15.75" spans="1:7">
+    <row r="87" ht="15.75" hidden="1" spans="1:7">
       <c r="A87" s="24">
         <v>89</v>
       </c>
@@ -4483,7 +4483,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="88" ht="15.75" spans="1:7">
+    <row r="88" ht="15.75" hidden="1" spans="1:7">
       <c r="A88" s="24">
         <v>90</v>
       </c>
@@ -4506,7 +4506,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="89" ht="15.75" spans="1:7">
+    <row r="89" ht="15.75" hidden="1" spans="1:7">
       <c r="A89" s="24">
         <v>91</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="90" ht="15.75" spans="1:7">
+    <row r="90" ht="15.75" hidden="1" spans="1:7">
       <c r="A90" s="24">
         <v>92</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="91" ht="15.75" spans="1:7">
+    <row r="91" ht="15.75" hidden="1" spans="1:7">
       <c r="A91" s="24">
         <v>93</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="92" ht="15.75" spans="1:7">
+    <row r="92" ht="15.75" hidden="1" spans="1:7">
       <c r="A92" s="24">
         <v>94</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="93" ht="15.75" spans="1:7">
+    <row r="93" ht="15.75" hidden="1" spans="1:7">
       <c r="A93" s="24">
         <v>95</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="94" ht="31.5" spans="1:7">
+    <row r="94" ht="31.5" hidden="1" spans="1:7">
       <c r="A94" s="24">
         <v>96</v>
       </c>
@@ -4638,7 +4638,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="95" ht="15.75" spans="1:7">
+    <row r="95" ht="15.75" hidden="1" spans="1:7">
       <c r="A95" s="24">
         <v>97</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="96" ht="15.75" spans="1:7">
+    <row r="96" ht="15.75" hidden="1" spans="1:7">
       <c r="A96" s="24">
         <v>98</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="97" ht="15.75" spans="1:7">
+    <row r="97" ht="15.75" hidden="1" spans="1:7">
       <c r="A97" s="24">
         <v>99</v>
       </c>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="E97" s="24"/>
     </row>
-    <row r="98" ht="15.75" spans="1:7">
+    <row r="98" ht="15.75" hidden="1" spans="1:7">
       <c r="A98" s="24">
         <v>100</v>
       </c>
@@ -4720,7 +4720,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="99" ht="15.75" spans="1:7">
+    <row r="99" ht="15.75" hidden="1" spans="1:7">
       <c r="A99" s="24">
         <v>101</v>
       </c>
@@ -4759,7 +4759,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="101" ht="15.75" spans="1:7">
+    <row r="101" ht="15.75" hidden="1" spans="1:7">
       <c r="A101" s="24">
         <v>103</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="102" ht="15.75" spans="1:7">
+    <row r="102" ht="15.75" hidden="1" spans="1:7">
       <c r="A102" s="24">
         <v>104</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="103" ht="15.75" spans="1:7">
+    <row r="103" ht="15.75" hidden="1" spans="1:7">
       <c r="A103" s="24">
         <v>105</v>
       </c>
@@ -4826,7 +4826,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="104" ht="15.75" spans="1:7">
+    <row r="104" ht="15.75" hidden="1" spans="1:7">
       <c r="A104" s="24">
         <v>106</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="105" ht="15.75" spans="1:7">
+    <row r="105" ht="15.75" hidden="1" spans="1:7">
       <c r="A105" s="24">
         <v>107</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="106" ht="15.75" spans="1:7">
+    <row r="106" ht="15.75" hidden="1" spans="1:7">
       <c r="A106" s="24">
         <v>108</v>
       </c>
@@ -4885,7 +4885,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="107" ht="15.75" spans="1:7">
+    <row r="107" ht="15.75" hidden="1" spans="1:7">
       <c r="A107" s="24">
         <v>109</v>
       </c>
@@ -4903,7 +4903,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="108" ht="15.75" spans="1:7">
+    <row r="108" ht="15.75" hidden="1" spans="1:7">
       <c r="A108" s="24">
         <v>110</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="109" ht="31.5" spans="1:7">
+    <row r="109" ht="31.5" hidden="1" spans="1:7">
       <c r="A109" s="24">
         <v>111</v>
       </c>
@@ -4939,7 +4939,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="110" ht="15.75" spans="1:7">
+    <row r="110" ht="15.75" hidden="1" spans="1:7">
       <c r="A110" s="24">
         <v>112</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="111" ht="15.75" spans="1:7">
+    <row r="111" ht="15.75" hidden="1" spans="1:7">
       <c r="A111" s="24">
         <v>113</v>
       </c>
@@ -4978,7 +4978,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="112" s="15" customFormat="1" ht="15.75" spans="1:7">
+    <row r="112" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
       <c r="A112" s="24">
         <v>114</v>
       </c>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="G112" s="20"/>
     </row>
-    <row r="113" ht="15.75" spans="1:7">
+    <row r="113" ht="15.75" hidden="1" spans="1:7">
       <c r="A113" s="24">
         <v>115</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" ht="15.75" spans="1:7">
+    <row r="114" ht="15.75" hidden="1" spans="1:7">
       <c r="A114" s="24">
         <v>116</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="115" ht="15.75" spans="1:7">
+    <row r="115" ht="15.75" hidden="1" spans="1:7">
       <c r="A115" s="24">
         <v>118</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="116" ht="15.75" spans="1:7">
+    <row r="116" ht="15.75" hidden="1" spans="1:7">
       <c r="A116" s="24">
         <v>119</v>
       </c>
@@ -5071,7 +5071,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="117" ht="15.75" spans="1:7">
+    <row r="117" ht="15.75" hidden="1" spans="1:7">
       <c r="A117" s="24">
         <v>120</v>
       </c>
@@ -5089,7 +5089,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="118" ht="15.75" spans="1:7">
+    <row r="118" ht="15.75" hidden="1" spans="1:7">
       <c r="A118" s="24">
         <v>121</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="119" ht="15.75" spans="1:7">
+    <row r="119" ht="15.75" hidden="1" spans="1:7">
       <c r="A119" s="24">
         <v>122</v>
       </c>
@@ -5125,7 +5125,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="120" ht="15.75" spans="1:7">
+    <row r="120" ht="15.75" hidden="1" spans="1:7">
       <c r="A120" s="24">
         <v>123</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="121" ht="15.75" spans="1:7">
+    <row r="121" ht="15.75" hidden="1" spans="1:7">
       <c r="A121" s="24">
         <v>124</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="127" ht="15.75" spans="1:7">
+    <row r="127" ht="15.75" hidden="1" spans="1:7">
       <c r="A127" s="24">
         <v>130</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="129" ht="15.75" spans="1:7">
+    <row r="129" ht="15.75" hidden="1" spans="1:7">
       <c r="A129" s="24">
         <v>132</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="130" ht="15.75" spans="1:7">
+    <row r="130" ht="15.75" hidden="1" spans="1:7">
       <c r="A130" s="24">
         <v>133</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="132" ht="15.75" spans="1:7">
+    <row r="132" ht="15.75" hidden="1" spans="1:7">
       <c r="A132" s="24">
         <v>135</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="133" ht="15.75" spans="1:7">
+    <row r="133" ht="15.75" hidden="1" spans="1:7">
       <c r="A133" s="24">
         <v>136</v>
       </c>
@@ -5425,7 +5425,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="134" ht="15.75" spans="1:7">
+    <row r="134" ht="15.75" hidden="1" spans="1:7">
       <c r="A134" s="24">
         <v>137</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="135" ht="15.75" spans="1:7">
+    <row r="135" ht="15.75" hidden="1" spans="1:7">
       <c r="A135" s="24">
         <v>138</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="137" ht="15.75" spans="1:7">
+    <row r="137" ht="15.75" hidden="1" spans="1:7">
       <c r="A137" s="24">
         <v>140</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="138" ht="15.75" spans="1:7">
+    <row r="138" ht="15.75" hidden="1" spans="1:7">
       <c r="A138" s="24">
         <v>141</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="140" ht="15.75" spans="1:7">
+    <row r="140" ht="15.75" hidden="1" spans="1:7">
       <c r="A140" s="24">
         <v>143</v>
       </c>
@@ -5598,7 +5598,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="142" ht="15.75" spans="1:7">
+    <row r="142" ht="15.75" hidden="1" spans="1:7">
       <c r="A142" s="24">
         <v>145</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="144" ht="15.75" spans="1:7">
+    <row r="144" ht="15.75" hidden="1" spans="1:7">
       <c r="A144" s="24">
         <v>146</v>
       </c>
@@ -5661,7 +5661,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="145" ht="15.75" spans="1:7">
+    <row r="145" ht="15.75" hidden="1" spans="1:7">
       <c r="A145" s="24">
         <v>147</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="146" ht="15.75" spans="1:7">
+    <row r="146" ht="15.75" hidden="1" spans="1:7">
       <c r="A146" s="24">
         <v>148</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="148" ht="15.75" spans="1:7">
+    <row r="148" ht="15.75" hidden="1" spans="1:7">
       <c r="A148" s="24">
         <v>150</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="149" ht="15.75" spans="1:7">
+    <row r="149" ht="15.75" hidden="1" spans="1:7">
       <c r="A149" s="24">
         <v>151</v>
       </c>
@@ -5763,7 +5763,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="150" ht="15.75" spans="1:7">
+    <row r="150" ht="15.75" hidden="1" spans="1:7">
       <c r="A150" s="24">
         <v>152</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="151" ht="15.75" spans="1:7">
+    <row r="151" ht="15.75" hidden="1" spans="1:7">
       <c r="A151" s="24">
         <v>153</v>
       </c>
@@ -5803,7 +5803,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="152" ht="15.75" spans="1:7">
+    <row r="152" ht="15.75" hidden="1" spans="1:7">
       <c r="A152" s="24">
         <v>153</v>
       </c>
@@ -5866,7 +5866,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="155" ht="15.75" spans="1:7">
+    <row r="155" ht="15.75" hidden="1" spans="1:7">
       <c r="A155" s="24">
         <v>156</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="156" ht="15.75" spans="1:7">
+    <row r="156" ht="15.75" hidden="1" spans="1:7">
       <c r="A156" s="24">
         <v>156</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="157" ht="15.75" spans="1:7">
+    <row r="157" ht="15.75" hidden="1" spans="1:7">
       <c r="A157" s="24">
         <v>157</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="158" ht="15.75" spans="1:7">
+    <row r="158" ht="15.75" hidden="1" spans="1:7">
       <c r="A158" s="24">
         <v>157</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="159" ht="15.75" spans="1:7">
+    <row r="159" ht="15.75" hidden="1" spans="1:7">
       <c r="A159" s="24">
         <v>158</v>
       </c>
@@ -5978,7 +5978,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="160" ht="15.75" spans="1:7">
+    <row r="160" ht="15.75" hidden="1" spans="1:7">
       <c r="A160" s="24">
         <v>159</v>
       </c>
@@ -5998,7 +5998,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="161" ht="15.75" spans="1:7">
+    <row r="161" ht="15.75" hidden="1" spans="1:7">
       <c r="A161" s="24">
         <v>160</v>
       </c>
@@ -6021,7 +6021,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="162" ht="15.75" spans="1:7">
+    <row r="162" ht="15.75" hidden="1" spans="1:7">
       <c r="A162" s="24">
         <v>161</v>
       </c>
@@ -6044,7 +6044,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="163" s="16" customFormat="1" ht="31.5" spans="1:7">
+    <row r="163" s="16" customFormat="1" ht="31.5" hidden="1" spans="1:7">
       <c r="A163" s="24">
         <v>162</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="164" ht="15.75" spans="1:7">
+    <row r="164" ht="15.75" hidden="1" spans="1:7">
       <c r="A164" s="24">
         <v>163</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="165" ht="15.75" spans="1:7">
+    <row r="165" ht="15.75" hidden="1" spans="1:7">
       <c r="A165" s="24">
         <v>164</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="167" ht="15.75" spans="1:7">
+    <row r="167" ht="15.75" hidden="1" spans="1:7">
       <c r="A167" s="24">
         <v>166</v>
       </c>
@@ -6156,7 +6156,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="168" ht="15.75" spans="1:7">
+    <row r="168" ht="15.75" hidden="1" spans="1:7">
       <c r="A168" s="24">
         <v>167</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="169" ht="15.75" spans="1:7">
+    <row r="169" ht="15.75" hidden="1" spans="1:7">
       <c r="A169" s="24">
         <v>168</v>
       </c>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E169" s="28"/>
     </row>
-    <row r="170" ht="15.75" spans="1:7">
+    <row r="170" ht="15.75" hidden="1" spans="1:7">
       <c r="A170" s="24">
         <v>169</v>
       </c>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="E170" s="28"/>
     </row>
-    <row r="171" ht="15.75" spans="1:7">
+    <row r="171" ht="15.75" hidden="1" spans="1:7">
       <c r="A171" s="24">
         <v>170</v>
       </c>
@@ -6224,7 +6224,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="172" ht="15.75" spans="1:7">
+    <row r="172" ht="15.75" hidden="1" spans="1:7">
       <c r="A172" s="24">
         <v>171</v>
       </c>
@@ -6247,7 +6247,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="173" ht="15.75" spans="1:7">
+    <row r="173" ht="15.75" hidden="1" spans="1:7">
       <c r="A173" s="24">
         <v>172</v>
       </c>
@@ -9223,9 +9223,14 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G173" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="3">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Vacataire"/>
+        <filter val="BENSALEM Mohammed Mustapha"/>
+        <filter val="BRAHAMI MOHAMED NADJIB"/>
+        <filter val="ZERDANI MOHAMMED"/>
+        <filter val="REZOUG MOHAMMED"/>
+        <filter val="ZAREB Mohammed Amine"/>
+        <filter val="FELLAH MOHAMMED KARIM"/>
       </filters>
     </filterColumn>
     <sortState ref="A1:G173">

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$170</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="473">
   <si>
     <t>N°</t>
   </si>
@@ -610,6 +610,492 @@
     <t>0556130770</t>
   </si>
   <si>
+    <t>MILOUA FETHI</t>
+  </si>
+  <si>
+    <t>fethi22miloua@gmail.com</t>
+  </si>
+  <si>
+    <t>GHALEM ABDELHAK</t>
+  </si>
+  <si>
+    <t>ghalem.abdelhak@yahoo.com</t>
+  </si>
+  <si>
+    <t>0675437370</t>
+  </si>
+  <si>
+    <t>HADER ABDERRAHMANE</t>
+  </si>
+  <si>
+    <t>aer.hader91@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 00 44 75</t>
+  </si>
+  <si>
+    <t>BENHARAT ABDELHADI</t>
+  </si>
+  <si>
+    <t>Hadi.bnh00@gmail.com</t>
+  </si>
+  <si>
+    <t>HADJI AHMED</t>
+  </si>
+  <si>
+    <t>ahmed.hadji22@yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 98 14 23 47 </t>
+  </si>
+  <si>
+    <t>HAMMAR MEHDI</t>
+  </si>
+  <si>
+    <t>protoboy9999@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 33 46 70 </t>
+  </si>
+  <si>
+    <t>HARMEL MOHAMED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmel.mohamed22@hotmail.com </t>
+  </si>
+  <si>
+    <t>KHELLAF KADDA</t>
+  </si>
+  <si>
+    <t>khellafkadda1234@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 65 72 17 23 </t>
+  </si>
+  <si>
+    <t>LAHCEN AZDDINE</t>
+  </si>
+  <si>
+    <t>azddinelahcene@gmail.com</t>
+  </si>
+  <si>
+    <t>LATRECHE MOKHTAR</t>
+  </si>
+  <si>
+    <t>m_latreche@yahoo.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 75 89 45 05 </t>
+  </si>
+  <si>
+    <t>LOUSDAD AYMEN</t>
+  </si>
+  <si>
+    <t>lousdadaymen.aziz@gmail.com</t>
+  </si>
+  <si>
+    <t>07 94 94 48 94</t>
+  </si>
+  <si>
+    <t>MAHIDDINE Abderrahim</t>
+  </si>
+  <si>
+    <t>ma2006ne_86@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0657058282</t>
+  </si>
+  <si>
+    <t>MAHKOUKA ZAZA</t>
+  </si>
+  <si>
+    <t>mahkouka.zaza@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0778 36 07 76 </t>
+  </si>
+  <si>
+    <t>MANSOURI ABDERRAZAK</t>
+  </si>
+  <si>
+    <t>abderazakmahdi22@gmail.com</t>
+  </si>
+  <si>
+    <t>0696417435</t>
+  </si>
+  <si>
+    <t>MECHETTEM KHALIDA</t>
+  </si>
+  <si>
+    <t>Doctorante (Master)</t>
+  </si>
+  <si>
+    <t>khalidamet4@gmail.com</t>
+  </si>
+  <si>
+    <t>0550651046</t>
+  </si>
+  <si>
+    <t>MEKHALEF SOUMIA</t>
+  </si>
+  <si>
+    <t>mekhalefleila@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 59 03 18 24 </t>
+  </si>
+  <si>
+    <t>MERADJAH IBRAHIM</t>
+  </si>
+  <si>
+    <t>ibrahimmeradjah72@gmail.com</t>
+  </si>
+  <si>
+    <t>0663114536</t>
+  </si>
+  <si>
+    <t>MESLEM MEHADJIA</t>
+  </si>
+  <si>
+    <t>mehadjiameslem@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 97 01 34 39 </t>
+  </si>
+  <si>
+    <t>MOULAY MILOUD</t>
+  </si>
+  <si>
+    <t>Doctorant (Magister)</t>
+  </si>
+  <si>
+    <t>mmiloud@yahoo.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 42 85 61 91 </t>
+  </si>
+  <si>
+    <t>MIR KHELIFA</t>
+  </si>
+  <si>
+    <t>khelifa-mir@outlook.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 69 59 78 39 </t>
+  </si>
+  <si>
+    <t>MOKEDDEM AMINA</t>
+  </si>
+  <si>
+    <t>mokeddem.amina2222@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 56 42 87 15 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non Défini </t>
+  </si>
+  <si>
+    <t>REDJALA MAJDA</t>
+  </si>
+  <si>
+    <t>majdaredjala1492@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05 53 64 47 91 </t>
+  </si>
+  <si>
+    <t>SENOUCI HAYAT</t>
+  </si>
+  <si>
+    <t>senoucihayat11@gmail.com</t>
+  </si>
+  <si>
+    <t>ZAREB Mohammed Amine</t>
+  </si>
+  <si>
+    <t>zarebmohammedamine@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0674 68 05 35 </t>
+  </si>
+  <si>
+    <t>ZIANI DJAMEL</t>
+  </si>
+  <si>
+    <t>djamel71ziani@gmail.com</t>
+  </si>
+  <si>
+    <t>05 61 11 10 02</t>
+  </si>
+  <si>
+    <t>LARBI ZIDI</t>
+  </si>
+  <si>
+    <t>larbi.zidi6@gmail.com</t>
+  </si>
+  <si>
+    <t>07 92 12 03 38</t>
+  </si>
+  <si>
+    <t>BERROUNA HENEN</t>
+  </si>
+  <si>
+    <t>berhenen@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0671745806</t>
+  </si>
+  <si>
+    <t>MOUILAH  KHEIRA</t>
+  </si>
+  <si>
+    <t>Ingénieur</t>
+  </si>
+  <si>
+    <t>mouilahka4614@gmail.com</t>
+  </si>
+  <si>
+    <t>ABED ZOULIKHA</t>
+  </si>
+  <si>
+    <t>zoulikhaabed3@gmail.com</t>
+  </si>
+  <si>
+    <t>0665697925</t>
+  </si>
+  <si>
+    <t>AISSANI ALI</t>
+  </si>
+  <si>
+    <t>aliaissani97@gmail.com</t>
+  </si>
+  <si>
+    <t>AZZA ROMAISSA FATIMA ZOHRA</t>
+  </si>
+  <si>
+    <t>azzafatimazohraromaissa.l3@gmail.com</t>
+  </si>
+  <si>
+    <t>BELABED MERIEM</t>
+  </si>
+  <si>
+    <t>meriembelabed5@gmail.com</t>
+  </si>
+  <si>
+    <t>BENKABOU MOHAMED EL HABIB</t>
+  </si>
+  <si>
+    <t>bkbhbb22@gmail.com</t>
+  </si>
+  <si>
+    <t>BENMASOUD LEILA</t>
+  </si>
+  <si>
+    <t>l.benmessaoud@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0553714385/0669056569</t>
+  </si>
+  <si>
+    <t>BERROUNA HANANE</t>
+  </si>
+  <si>
+    <t>CHIKHI NAWEL</t>
+  </si>
+  <si>
+    <t>chikhi_nawel75@yahoo.fr</t>
+  </si>
+  <si>
+    <t>DELLOUM AMIRA</t>
+  </si>
+  <si>
+    <t>amiradelloum28@gmail.com</t>
+  </si>
+  <si>
+    <t>FENTAZY BELKISSE</t>
+  </si>
+  <si>
+    <t>fantazibelkisse.13@gmail.com</t>
+  </si>
+  <si>
+    <t>KADA ZAIR IKRAM</t>
+  </si>
+  <si>
+    <t>ikram.kadazair@gmail.com</t>
+  </si>
+  <si>
+    <t>LAYATI TAYEB MEHDI</t>
+  </si>
+  <si>
+    <t>layatimedi@gmail.com</t>
+  </si>
+  <si>
+    <t>NEFAHA ABOUBAKR</t>
+  </si>
+  <si>
+    <t>Boba1620@hotmail.com</t>
+  </si>
+  <si>
+    <t>SACI HAMZA</t>
+  </si>
+  <si>
+    <t>sacihamza40@gmail.com</t>
+  </si>
+  <si>
+    <t>RAIS ABDELMAJID</t>
+  </si>
+  <si>
+    <t>amrais@yahoo.com</t>
+  </si>
+  <si>
+    <t>0657 28 66 17</t>
+  </si>
+  <si>
+    <t>REGUIG ABDELDJALIL</t>
+  </si>
+  <si>
+    <t>Mise en disponibilité</t>
+  </si>
+  <si>
+    <t>abdeldjalil.reguig@outlook.com</t>
+  </si>
+  <si>
+    <t>ZERDANI MOHAMMED</t>
+  </si>
+  <si>
+    <t>medzerdani@gmail.com</t>
+  </si>
+  <si>
+    <t>KADA KLOUCHA OMAR</t>
+  </si>
+  <si>
+    <t>klomar05@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SAIDI KHAYREDDINE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
+  </si>
+  <si>
+    <t>ABBOU MAJDA</t>
+  </si>
+  <si>
+    <t>milouaf@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0556831346</t>
+  </si>
+  <si>
+    <t>REGUIEG ZAKARIA</t>
+  </si>
+  <si>
+    <t>reguiegzakaria10@gmail.com</t>
+  </si>
+  <si>
+    <t>0792070651</t>
+  </si>
+  <si>
+    <t>SEMMAK ABDELKADER</t>
+  </si>
+  <si>
+    <t>semmak.abdelkader@outlook.com</t>
+  </si>
+  <si>
+    <t>0772111809</t>
+  </si>
+  <si>
+    <t>BENMESSAOUD LEYLA</t>
+  </si>
+  <si>
+    <t>l_benmessaoud@yahoo.fr</t>
+  </si>
+  <si>
+    <t>0553714385</t>
+  </si>
+  <si>
+    <t>TURKI BILAL MEROUANE</t>
+  </si>
+  <si>
+    <t>turkibilal22@gmail.com</t>
+  </si>
+  <si>
+    <t>0655206865</t>
+  </si>
+  <si>
+    <t>OUARI KHEIRA</t>
+  </si>
+  <si>
+    <t>ouari_k@yahoo.fr</t>
+  </si>
+  <si>
+    <t>SABOUNDJI Asmaa Hadjer</t>
+  </si>
+  <si>
+    <t>saboundjiasmaa@gmail.com</t>
+  </si>
+  <si>
+    <t>0655459306 /  0556562385</t>
+  </si>
+  <si>
+    <t>HACENE IMENE</t>
+  </si>
+  <si>
+    <t>hacene_imene12@yahoo.com</t>
+  </si>
+  <si>
+    <t>0542471563</t>
+  </si>
+  <si>
+    <t>BENKATLANE Aissa</t>
+  </si>
+  <si>
+    <t>a.benkatlane@gmail.com</t>
+  </si>
+  <si>
+    <t>0697113466</t>
+  </si>
+  <si>
+    <t>ismahene.fezazi@gmail.com</t>
+  </si>
+  <si>
+    <t>0652652866</t>
+  </si>
+  <si>
+    <t>ABID HAMZA</t>
+  </si>
+  <si>
+    <t>PrE</t>
+  </si>
+  <si>
+    <t>abid_hamza@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BELAIDI OUAFIA</t>
+  </si>
+  <si>
+    <t>belaidi.ouafia@outlook.fr</t>
+  </si>
+  <si>
+    <t>0668834015</t>
+  </si>
+  <si>
+    <t>MEKHFI KHALIDA</t>
+  </si>
+  <si>
+    <t>mekhfikhalida87@gmail.com</t>
+  </si>
+  <si>
+    <t>0663594477</t>
+  </si>
+  <si>
+    <t>ZATLA HICHAM</t>
+  </si>
+  <si>
+    <t>hicham.zatla@gmail.com</t>
+  </si>
+  <si>
     <t>ELGHODASSE ABDEL MADJID</t>
   </si>
   <si>
@@ -619,523 +1105,37 @@
     <t>05 41 77 21 68</t>
   </si>
   <si>
-    <t>MILOUA FETHI</t>
-  </si>
-  <si>
-    <t>fethi22miloua@gmail.com</t>
-  </si>
-  <si>
-    <t>GHALEM ABDELHAK</t>
-  </si>
-  <si>
-    <t>ghalem.abdelhak@yahoo.com</t>
-  </si>
-  <si>
-    <t>0675437370</t>
-  </si>
-  <si>
-    <t>HADER ABDERRAHMANE</t>
-  </si>
-  <si>
-    <t>aer.hader91@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 00 44 75</t>
-  </si>
-  <si>
-    <t>BENHARAT ABDELHADI</t>
-  </si>
-  <si>
-    <t>Hadi.bnh00@gmail.com</t>
-  </si>
-  <si>
-    <t>HADJI AHMED</t>
-  </si>
-  <si>
-    <t>ahmed.hadji22@yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 98 14 23 47 </t>
-  </si>
-  <si>
-    <t>HAMMAR MEHDI</t>
-  </si>
-  <si>
-    <t>protoboy9999@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 33 46 70 </t>
-  </si>
-  <si>
-    <t>HARMEL MOHAMED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmel.mohamed22@hotmail.com </t>
-  </si>
-  <si>
-    <t>KHELLAF KADDA</t>
-  </si>
-  <si>
-    <t>khellafkadda1234@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 65 72 17 23 </t>
-  </si>
-  <si>
-    <t>LAHCEN AZDDINE</t>
-  </si>
-  <si>
-    <t>azddinelahcene@gmail.com</t>
-  </si>
-  <si>
-    <t>LATRECHE MOKHTAR</t>
-  </si>
-  <si>
-    <t>m_latreche@yahoo.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07 75 89 45 05 </t>
-  </si>
-  <si>
-    <t>LOUSDAD AYMEN</t>
-  </si>
-  <si>
-    <t>lousdadaymen.aziz@gmail.com</t>
-  </si>
-  <si>
-    <t>07 94 94 48 94</t>
-  </si>
-  <si>
-    <t>MAHIDDINE Abderrahim</t>
-  </si>
-  <si>
-    <t>ma2006ne_86@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0657058282</t>
-  </si>
-  <si>
-    <t>MAHKOUKA ZAZA</t>
-  </si>
-  <si>
-    <t>mahkouka.zaza@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0778 36 07 76 </t>
-  </si>
-  <si>
-    <t>MANSOURI ABDERRAZAK</t>
-  </si>
-  <si>
-    <t>abderazakmahdi22@gmail.com</t>
-  </si>
-  <si>
-    <t>0696417435</t>
-  </si>
-  <si>
-    <t>MECHETTEM KHALIDA</t>
-  </si>
-  <si>
-    <t>Doctorante (Master)</t>
-  </si>
-  <si>
-    <t>khalidamet4@gmail.com</t>
-  </si>
-  <si>
-    <t>0550651046</t>
-  </si>
-  <si>
-    <t>MEKHALEF SOUMIA</t>
-  </si>
-  <si>
-    <t>mekhalefleila@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 59 03 18 24 </t>
-  </si>
-  <si>
-    <t>MERADJAH IBRAHIM</t>
-  </si>
-  <si>
-    <t>ibrahimmeradjah72@gmail.com</t>
-  </si>
-  <si>
-    <t>0663114536</t>
-  </si>
-  <si>
-    <t>MESLEM MEHADJIA</t>
-  </si>
-  <si>
-    <t>mehadjiameslem@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 97 01 34 39 </t>
-  </si>
-  <si>
-    <t>MOULAY MILOUD</t>
-  </si>
-  <si>
-    <t>Doctorant (Magister)</t>
-  </si>
-  <si>
-    <t>mmiloud@yahoo.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 42 85 61 91 </t>
-  </si>
-  <si>
-    <t>MIR KHELIFA</t>
-  </si>
-  <si>
-    <t>khelifa-mir@outlook.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 69 59 78 39 </t>
-  </si>
-  <si>
-    <t>MOKEDDEM AMINA</t>
-  </si>
-  <si>
-    <t>mokeddem.amina2222@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06 56 42 87 15 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non Défini </t>
-  </si>
-  <si>
-    <t>REDJALA MAJDA</t>
-  </si>
-  <si>
-    <t>majdaredjala1492@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05 53 64 47 91 </t>
-  </si>
-  <si>
-    <t>SENOUCI HAYAT</t>
-  </si>
-  <si>
-    <t>senoucihayat11@gmail.com</t>
-  </si>
-  <si>
-    <t>ZAREB Mohammed Amine</t>
-  </si>
-  <si>
-    <t>zarebmohammedamine@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0674 68 05 35 </t>
-  </si>
-  <si>
-    <t>ZIANI DJAMEL</t>
-  </si>
-  <si>
-    <t>djamel71ziani@gmail.com</t>
-  </si>
-  <si>
-    <t>05 61 11 10 02</t>
-  </si>
-  <si>
-    <t>LARBI ZIDI</t>
-  </si>
-  <si>
-    <t>larbi.zidi6@gmail.com</t>
-  </si>
-  <si>
-    <t>07 92 12 03 38</t>
-  </si>
-  <si>
-    <t>BERROUNA HENEN</t>
-  </si>
-  <si>
-    <t>berhenen@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0671745806</t>
-  </si>
-  <si>
-    <t>MOUILAH  KHEIRA</t>
-  </si>
-  <si>
-    <t>Ingénieur</t>
-  </si>
-  <si>
-    <t>mouilahka4614@gmail.com</t>
-  </si>
-  <si>
-    <t>ABED ZOULIKHA</t>
-  </si>
-  <si>
-    <t>zoulikhaabed3@gmail.com</t>
-  </si>
-  <si>
-    <t>0665697925</t>
-  </si>
-  <si>
-    <t>AISSANI ALI</t>
-  </si>
-  <si>
-    <t>aliaissani97@gmail.com</t>
-  </si>
-  <si>
-    <t>AZZA ROMAISSA FATIMA ZOHRA</t>
-  </si>
-  <si>
-    <t>azzafatimazohraromaissa.l3@gmail.com</t>
-  </si>
-  <si>
-    <t>BELABED MERIEM</t>
-  </si>
-  <si>
-    <t>meriembelabed5@gmail.com</t>
-  </si>
-  <si>
-    <t>BENKABOU MOHAMED EL HABIB</t>
-  </si>
-  <si>
-    <t>bkbhbb22@gmail.com</t>
-  </si>
-  <si>
-    <t>BENMASOUD LEILA</t>
-  </si>
-  <si>
-    <t>l.benmessaoud@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0553714385/0669056569</t>
-  </si>
-  <si>
-    <t>BERROUNA HANANE</t>
-  </si>
-  <si>
-    <t>CHIKHI NAWEL</t>
-  </si>
-  <si>
-    <t>chikhi_nawel75@yahoo.fr</t>
-  </si>
-  <si>
-    <t>DELLOUM AMIRA</t>
-  </si>
-  <si>
-    <t>amiradelloum28@gmail.com</t>
-  </si>
-  <si>
-    <t>FENTAZY BELKISSE</t>
-  </si>
-  <si>
-    <t>fantazibelkisse.13@gmail.com</t>
-  </si>
-  <si>
-    <t>KADA ZAIR IKRAM</t>
-  </si>
-  <si>
-    <t>ikram.kadazair@gmail.com</t>
+    <t>BENSEDDIK NADIA</t>
+  </si>
+  <si>
+    <t>n_benseddik@yahoo.fr</t>
+  </si>
+  <si>
+    <t>BERREKHCHI BERRAHMA NEILA</t>
+  </si>
+  <si>
+    <t>neilabekhchiberrahma@gmail.com</t>
+  </si>
+  <si>
+    <t>0656 88 71 07</t>
+  </si>
+  <si>
+    <t>YAMANI MASSIM</t>
+  </si>
+  <si>
+    <t>yamanimassim@yahoo.fr</t>
+  </si>
+  <si>
+    <t>FILALI INES</t>
+  </si>
+  <si>
+    <t>inesfilali2003@gmail.com</t>
   </si>
   <si>
     <t>KADRI RANIA</t>
   </si>
   <si>
     <t>kadrirania51@gmail.com</t>
-  </si>
-  <si>
-    <t>LAYATI TAYEB MEHDI</t>
-  </si>
-  <si>
-    <t>layatimedi@gmail.com</t>
-  </si>
-  <si>
-    <t>NEFAHA ABOUBAKR</t>
-  </si>
-  <si>
-    <t>Boba1620@hotmail.com</t>
-  </si>
-  <si>
-    <t>SACI HAMZA</t>
-  </si>
-  <si>
-    <t>sacihamza40@gmail.com</t>
-  </si>
-  <si>
-    <t>TURKI BILAL MEROUANE</t>
-  </si>
-  <si>
-    <t>turkibilal22@gmail.com</t>
-  </si>
-  <si>
-    <t>RAIS ABDELMAJID</t>
-  </si>
-  <si>
-    <t>amrais@yahoo.com</t>
-  </si>
-  <si>
-    <t>0657 28 66 17</t>
-  </si>
-  <si>
-    <t>REGUIG ABDELDJALIL</t>
-  </si>
-  <si>
-    <t>Mise en disponibilité</t>
-  </si>
-  <si>
-    <t>abdeldjalil.reguig@outlook.com</t>
-  </si>
-  <si>
-    <t>ZERDANI MOHAMMED</t>
-  </si>
-  <si>
-    <t>medzerdani@gmail.com</t>
-  </si>
-  <si>
-    <t>KADA KLOUCHA OMAR</t>
-  </si>
-  <si>
-    <t>klomar05@yahoo.fr</t>
-  </si>
-  <si>
-    <t>SAIDI KHAYREDDINE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">saidi_kheiro@yahoo.fr </t>
-  </si>
-  <si>
-    <t>ABBOU MAJDA</t>
-  </si>
-  <si>
-    <t>milouaf@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0556831346</t>
-  </si>
-  <si>
-    <t>REGUIEG ZAKARIA</t>
-  </si>
-  <si>
-    <t>reguiegzakaria10@gmail.com</t>
-  </si>
-  <si>
-    <t>0792070651</t>
-  </si>
-  <si>
-    <t>SEMMAK ABDELKADER</t>
-  </si>
-  <si>
-    <t>semmak.abdelkader@outlook.com</t>
-  </si>
-  <si>
-    <t>0772111809</t>
-  </si>
-  <si>
-    <t>BENMESSAOUD LEYLA</t>
-  </si>
-  <si>
-    <t>l_benmessaoud@yahoo.fr</t>
-  </si>
-  <si>
-    <t>0553714385</t>
-  </si>
-  <si>
-    <t>0655206865</t>
-  </si>
-  <si>
-    <t>OUARI KHEIRA</t>
-  </si>
-  <si>
-    <t>ouari_k@yahoo.fr</t>
-  </si>
-  <si>
-    <t>SABOUNDJI Asmaa Hadjer</t>
-  </si>
-  <si>
-    <t>saboundjiasmaa@gmail.com</t>
-  </si>
-  <si>
-    <t>0655459306 /  0556562385</t>
-  </si>
-  <si>
-    <t>HACENE IMENE</t>
-  </si>
-  <si>
-    <t>hacene_imene12@yahoo.com</t>
-  </si>
-  <si>
-    <t>0542471563</t>
-  </si>
-  <si>
-    <t>BENKATLANE Aissa</t>
-  </si>
-  <si>
-    <t>a.benkatlane@gmail.com</t>
-  </si>
-  <si>
-    <t>0697113466</t>
-  </si>
-  <si>
-    <t>ismahene.fezazi@gmail.com</t>
-  </si>
-  <si>
-    <t>0652652866</t>
-  </si>
-  <si>
-    <t>ABID HAMZA</t>
-  </si>
-  <si>
-    <t>PrE</t>
-  </si>
-  <si>
-    <t>abid_hamza@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BELAIDI OUAFIA</t>
-  </si>
-  <si>
-    <t>belaidi.ouafia@outlook.fr</t>
-  </si>
-  <si>
-    <t>0668834015</t>
-  </si>
-  <si>
-    <t>MEKHFI KHALIDA</t>
-  </si>
-  <si>
-    <t>mekhfikhalida87@gmail.com</t>
-  </si>
-  <si>
-    <t>0663594477</t>
-  </si>
-  <si>
-    <t>ZATLA HICHAM</t>
-  </si>
-  <si>
-    <t>hicham.zatla@gmail.com</t>
-  </si>
-  <si>
-    <t>BENSEDDIK NADIA</t>
-  </si>
-  <si>
-    <t>n_benseddik@yahoo.fr</t>
-  </si>
-  <si>
-    <t>BERREKHCHI BERRAHMA NEILA</t>
-  </si>
-  <si>
-    <t>neilabekhchiberrahma@gmail.com</t>
-  </si>
-  <si>
-    <t>0656 88 71 07</t>
-  </si>
-  <si>
-    <t>YAMANI MASSIM</t>
-  </si>
-  <si>
-    <t>yamanimassim@yahoo.fr</t>
-  </si>
-  <si>
-    <t>FILALI INES</t>
-  </si>
-  <si>
-    <t>inesfilali2003@gmail.com</t>
   </si>
   <si>
     <t>0794297709</t>
@@ -2653,8 +2653,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1" codeName="Sheet1"/>
-  <dimension ref="A1:G1160"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:G1157"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="17" customWidth="1"/>
@@ -2690,7 +2690,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="15.75" hidden="1" spans="1:7">
+    <row r="2" ht="15.75" spans="1:7">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="15.75" hidden="1" spans="1:7">
+    <row r="3" ht="15.75" spans="1:7">
       <c r="A3" s="24">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" ht="15.75" hidden="1" spans="1:7">
+    <row r="4" ht="15.75" spans="1:7">
       <c r="A4" s="24">
         <v>3</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="15.75" hidden="1" spans="1:7">
+    <row r="5" ht="15.75" spans="1:7">
       <c r="A5" s="24">
         <v>4</v>
       </c>
@@ -2770,7 +2770,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" ht="15.75" hidden="1" spans="1:7">
+    <row r="6" ht="15.75" spans="1:7">
       <c r="A6" s="24">
         <v>5</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="15.75" hidden="1" spans="1:7">
+    <row r="7" ht="15.75" spans="1:7">
       <c r="A7" s="24">
         <v>6</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" ht="15.75" hidden="1" spans="1:7">
+    <row r="8" ht="15.75" spans="1:7">
       <c r="A8" s="24">
         <v>7</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" ht="15.75" hidden="1" spans="1:7">
+    <row r="9" ht="15.75" spans="1:7">
       <c r="A9" s="24">
         <v>8</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" ht="15.75" hidden="1" spans="1:7">
+    <row r="10" ht="15.75" spans="1:7">
       <c r="A10" s="24">
         <v>9</v>
       </c>
@@ -2879,7 +2879,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="15.75" hidden="1" spans="1:7">
+    <row r="11" ht="15.75" spans="1:7">
       <c r="A11" s="24">
         <v>10</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" ht="15.75" hidden="1" spans="1:7">
+    <row r="12" ht="15.75" spans="1:7">
       <c r="A12" s="24">
         <v>11</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" ht="15.75" hidden="1" spans="1:7">
+    <row r="13" ht="15.75" spans="1:7">
       <c r="A13" s="24">
         <v>12</v>
       </c>
@@ -2939,7 +2939,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" ht="15.75" hidden="1" spans="1:7">
+    <row r="14" ht="15.75" spans="1:7">
       <c r="A14" s="24">
         <v>13</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="15.75" hidden="1" spans="1:7">
+    <row r="15" ht="15.75" spans="1:7">
       <c r="A15" s="24">
         <v>14</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" ht="15.75" hidden="1" spans="1:7">
+    <row r="16" ht="15.75" spans="1:7">
       <c r="A16" s="24">
         <v>15</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" ht="15.75" hidden="1" spans="1:7">
+    <row r="17" ht="15.75" spans="1:7">
       <c r="A17" s="24">
         <v>16</v>
       </c>
@@ -3019,7 +3019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" ht="15.75" hidden="1" spans="1:7">
+    <row r="18" ht="15.75" spans="1:7">
       <c r="A18" s="24">
         <v>17</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" ht="15.75" hidden="1" spans="1:7">
+    <row r="19" ht="15.75" spans="1:7">
       <c r="A19" s="24">
         <v>18</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="20" ht="15.75" hidden="1" spans="1:7">
+    <row r="20" ht="15.75" spans="1:7">
       <c r="A20" s="24">
         <v>19</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="21" ht="15.75" hidden="1" spans="1:7">
+    <row r="21" ht="15.75" spans="1:7">
       <c r="A21" s="24">
         <v>20</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" ht="15.75" hidden="1" spans="1:7">
+    <row r="22" ht="15.75" spans="1:7">
       <c r="A22" s="24">
         <v>21</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" ht="15.75" hidden="1" spans="1:7">
+    <row r="23" ht="15.75" spans="1:7">
       <c r="A23" s="24">
         <v>22</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="24" ht="15.75" hidden="1" spans="1:7">
+    <row r="24" ht="15.75" spans="1:7">
       <c r="A24" s="24">
         <v>23</v>
       </c>
@@ -3162,7 +3162,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" ht="15.75" hidden="1" spans="1:7">
+    <row r="25" ht="15.75" spans="1:7">
       <c r="A25" s="24">
         <v>24</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" ht="15.75" hidden="1" spans="1:7">
+    <row r="27" ht="15.75" spans="1:7">
       <c r="A27" s="24">
         <v>26</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" ht="15.75" hidden="1" spans="1:7">
+    <row r="28" ht="15.75" spans="1:7">
       <c r="A28" s="24">
         <v>27</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" ht="15.75" hidden="1" spans="1:7">
+    <row r="29" ht="15.75" spans="1:7">
       <c r="A29" s="24">
         <v>28</v>
       </c>
@@ -3262,7 +3262,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" ht="15.75" hidden="1" spans="1:7">
+    <row r="30" ht="15.75" spans="1:7">
       <c r="A30" s="24">
         <v>29</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" ht="15.75" hidden="1" spans="1:7">
+    <row r="31" ht="15.75" spans="1:7">
       <c r="A31" s="24">
         <v>30</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" ht="15.75" hidden="1" spans="1:7">
+    <row r="32" ht="15.75" spans="1:7">
       <c r="A32" s="24">
         <v>31</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" ht="15.75" hidden="1" spans="1:7">
+    <row r="33" ht="15.75" spans="1:7">
       <c r="A33" s="24">
         <v>32</v>
       </c>
@@ -3342,9 +3342,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" ht="15.75" hidden="1" spans="1:7">
+    <row r="34" ht="15.75" spans="1:7">
       <c r="A34" s="24">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="25" t="s">
         <v>82</v>
@@ -3362,9 +3362,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" ht="15.75" hidden="1" spans="1:7">
+    <row r="35" ht="15.75" spans="1:7">
       <c r="A35" s="24">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="25" t="s">
         <v>84</v>
@@ -3382,9 +3382,9 @@
         <v>85</v>
       </c>
     </row>
-    <row r="36" ht="15.75" hidden="1" spans="1:7">
+    <row r="36" ht="15.75" spans="1:7">
       <c r="A36" s="24">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>86</v>
@@ -3405,9 +3405,9 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" ht="15.75" hidden="1" spans="1:7">
+    <row r="37" ht="15.75" spans="1:7">
       <c r="A37" s="24">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37" s="25" t="s">
         <v>89</v>
@@ -3425,9 +3425,9 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" ht="15.75" hidden="1" spans="1:7">
+    <row r="38" ht="15.75" spans="1:7">
       <c r="A38" s="24">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="25" t="s">
         <v>91</v>
@@ -3450,7 +3450,7 @@
     </row>
     <row r="39" ht="15.75" spans="1:7">
       <c r="A39" s="24">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>94</v>
@@ -3468,9 +3468,9 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" ht="15.75" hidden="1" spans="1:7">
+    <row r="40" ht="15.75" spans="1:7">
       <c r="A40" s="24">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="25" t="s">
         <v>96</v>
@@ -3488,9 +3488,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="41" ht="15.75" hidden="1" spans="1:7">
+    <row r="41" ht="15.75" spans="1:7">
       <c r="A41" s="24">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="25" t="s">
         <v>98</v>
@@ -3508,9 +3508,9 @@
         <v>99</v>
       </c>
     </row>
-    <row r="42" ht="15.75" hidden="1" spans="1:7">
+    <row r="42" ht="15.75" spans="1:7">
       <c r="A42" s="24">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42" s="25" t="s">
         <v>100</v>
@@ -3528,9 +3528,9 @@
         <v>101</v>
       </c>
     </row>
-    <row r="43" ht="15.75" hidden="1" spans="1:7">
+    <row r="43" ht="15.75" spans="1:7">
       <c r="A43" s="24">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="25" t="s">
         <v>102</v>
@@ -3548,9 +3548,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="44" ht="15.75" hidden="1" spans="1:7">
+    <row r="44" ht="15.75" spans="1:7">
       <c r="A44" s="24">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44" s="25" t="s">
         <v>104</v>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="45" ht="15.75" spans="1:7">
       <c r="A45" s="24">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45" s="25" t="s">
         <v>106</v>
@@ -3588,9 +3588,9 @@
         <v>107</v>
       </c>
     </row>
-    <row r="46" ht="15.75" hidden="1" spans="1:7">
+    <row r="46" ht="15.75" spans="1:7">
       <c r="A46" s="24">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" s="25" t="s">
         <v>108</v>
@@ -3608,9 +3608,9 @@
         <v>109</v>
       </c>
     </row>
-    <row r="47" ht="15.75" hidden="1" spans="1:7">
+    <row r="47" ht="15.75" spans="1:7">
       <c r="A47" s="24">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="25" t="s">
         <v>110</v>
@@ -3628,9 +3628,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="48" ht="15.75" hidden="1" spans="1:7">
+    <row r="48" ht="15.75" spans="1:7">
       <c r="A48" s="24">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="25" t="s">
         <v>112</v>
@@ -3648,9 +3648,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" ht="15.75" hidden="1" spans="1:7">
+    <row r="49" ht="15.75" spans="1:7">
       <c r="A49" s="24">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="25" t="s">
         <v>114</v>
@@ -3668,9 +3668,9 @@
         <v>115</v>
       </c>
     </row>
-    <row r="50" ht="15.75" hidden="1" spans="1:7">
+    <row r="50" ht="15.75" spans="1:7">
       <c r="A50" s="24">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="25" t="s">
         <v>116</v>
@@ -3688,9 +3688,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="51" ht="15.75" hidden="1" spans="1:7">
+    <row r="51" ht="15.75" spans="1:7">
       <c r="A51" s="24">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="25" t="s">
         <v>118</v>
@@ -3708,9 +3708,9 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" ht="15.75" hidden="1" spans="1:7">
+    <row r="52" ht="15.75" spans="1:7">
       <c r="A52" s="24">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="25" t="s">
         <v>120</v>
@@ -3731,9 +3731,9 @@
         <v>122</v>
       </c>
     </row>
-    <row r="53" ht="15.75" hidden="1" spans="1:7">
+    <row r="53" ht="15.75" spans="1:7">
       <c r="A53" s="24">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="25" t="s">
         <v>123</v>
@@ -3751,9 +3751,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="54" ht="15.75" hidden="1" spans="1:7">
+    <row r="54" ht="15.75" spans="1:7">
       <c r="A54" s="24">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="25" t="s">
         <v>125</v>
@@ -3774,9 +3774,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="55" ht="15.75" hidden="1" spans="1:7">
+    <row r="55" ht="15.75" spans="1:7">
       <c r="A55" s="24">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="25" t="s">
         <v>130</v>
@@ -3795,9 +3795,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56" ht="15.75" hidden="1" spans="1:7">
+    <row r="56" ht="15.75" spans="1:7">
       <c r="A56" s="24">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B56" s="25" t="s">
         <v>133</v>
@@ -3818,9 +3818,9 @@
         <v>136</v>
       </c>
     </row>
-    <row r="57" ht="15.75" hidden="1" spans="1:7">
+    <row r="57" ht="15.75" spans="1:7">
       <c r="A57" s="24">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B57" s="25" t="s">
         <v>137</v>
@@ -3841,9 +3841,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="58" ht="15.75" hidden="1" spans="1:7">
+    <row r="58" ht="15.75" spans="1:7">
       <c r="A58" s="24">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B58" s="25" t="s">
         <v>141</v>
@@ -3864,9 +3864,9 @@
         <v>143</v>
       </c>
     </row>
-    <row r="59" ht="15.75" hidden="1" spans="1:7">
+    <row r="59" ht="15.75" spans="1:7">
       <c r="A59" s="24">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B59" s="25" t="s">
         <v>144</v>
@@ -3887,9 +3887,9 @@
         <v>146</v>
       </c>
     </row>
-    <row r="60" ht="15.75" hidden="1" spans="1:7">
+    <row r="60" ht="15.75" spans="1:7">
       <c r="A60" s="24">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B60" s="25" t="s">
         <v>147</v>
@@ -3908,9 +3908,9 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" ht="15.75" hidden="1" spans="1:7">
+    <row r="61" ht="15.75" spans="1:7">
       <c r="A61" s="24">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B61" s="25" t="s">
         <v>150</v>
@@ -3931,7 +3931,7 @@
     </row>
     <row r="62" ht="31.5" spans="1:7">
       <c r="A62" s="24">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B62" s="25" t="s">
         <v>153</v>
@@ -3952,9 +3952,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="63" ht="15.75" hidden="1" spans="1:7">
+    <row r="63" ht="15.75" spans="1:7">
       <c r="A63" s="24">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B63" s="25" t="s">
         <v>156</v>
@@ -3973,9 +3973,9 @@
         <v>158</v>
       </c>
     </row>
-    <row r="64" ht="15.75" hidden="1" spans="1:7">
+    <row r="64" ht="15.75" spans="1:7">
       <c r="A64" s="24">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B64" s="25" t="s">
         <v>159</v>
@@ -3994,9 +3994,9 @@
         <v>161</v>
       </c>
     </row>
-    <row r="65" ht="15.75" hidden="1" spans="1:7">
+    <row r="65" ht="15.75" spans="1:7">
       <c r="A65" s="24">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B65" s="25" t="s">
         <v>162</v>
@@ -4015,9 +4015,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="66" ht="15.75" hidden="1" spans="1:7">
+    <row r="66" ht="15.75" spans="1:7">
       <c r="A66" s="24">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B66" s="25" t="s">
         <v>165</v>
@@ -4038,9 +4038,9 @@
         <v>167</v>
       </c>
     </row>
-    <row r="67" ht="15.75" hidden="1" spans="1:7">
+    <row r="67" ht="15.75" spans="1:7">
       <c r="A67" s="24">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>168</v>
@@ -4059,9 +4059,9 @@
         <v>170</v>
       </c>
     </row>
-    <row r="68" ht="15.75" hidden="1" spans="1:7">
+    <row r="68" ht="15.75" spans="1:7">
       <c r="A68" s="24">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B68" s="25" t="s">
         <v>171</v>
@@ -4080,9 +4080,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="69" ht="31.5" hidden="1" spans="1:7">
+    <row r="69" ht="31.5" spans="1:7">
       <c r="A69" s="24">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B69" s="25" t="s">
         <v>174</v>
@@ -4101,9 +4101,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="70" ht="15.75" hidden="1" spans="1:7">
+    <row r="70" ht="15.75" spans="1:7">
       <c r="A70" s="24">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B70" s="25" t="s">
         <v>177</v>
@@ -4122,9 +4122,9 @@
         <v>179</v>
       </c>
     </row>
-    <row r="71" ht="15.75" hidden="1" spans="1:7">
+    <row r="71" ht="15.75" spans="1:7">
       <c r="A71" s="24">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B71" s="25" t="s">
         <v>180</v>
@@ -4145,9 +4145,9 @@
         <v>182</v>
       </c>
     </row>
-    <row r="72" ht="15.75" hidden="1" spans="1:7">
+    <row r="72" ht="15.75" spans="1:7">
       <c r="A72" s="24">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B72" s="25" t="s">
         <v>183</v>
@@ -4166,9 +4166,9 @@
         <v>185</v>
       </c>
     </row>
-    <row r="73" ht="15.75" hidden="1" spans="1:7">
+    <row r="73" ht="15.75" spans="1:7">
       <c r="A73" s="24">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B73" s="25" t="s">
         <v>186</v>
@@ -4189,9 +4189,9 @@
         <v>188</v>
       </c>
     </row>
-    <row r="74" ht="15.75" hidden="1" spans="1:7">
+    <row r="74" ht="15.75" spans="1:7">
       <c r="A74" s="24">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B74" s="25" t="s">
         <v>189</v>
@@ -4210,9 +4210,9 @@
         <v>191</v>
       </c>
     </row>
-    <row r="75" ht="15.75" hidden="1" spans="1:7">
+    <row r="75" ht="15.75" spans="1:7">
       <c r="A75" s="24">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B75" s="25" t="s">
         <v>192</v>
@@ -4223,22 +4223,17 @@
       <c r="D75" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E75" s="24" t="s">
-        <v>127</v>
-      </c>
+      <c r="E75" s="24"/>
       <c r="F75" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="G75" s="20" t="s">
+    </row>
+    <row r="76" ht="15.75" spans="1:7">
+      <c r="A76" s="24">
+        <v>75</v>
+      </c>
+      <c r="B76" s="25" t="s">
         <v>194</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" hidden="1" spans="1:7">
-      <c r="A76" s="24">
-        <v>78</v>
-      </c>
-      <c r="B76" s="25" t="s">
-        <v>195</v>
       </c>
       <c r="C76" s="25" t="s">
         <v>8</v>
@@ -4246,14 +4241,19 @@
       <c r="D76" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E76" s="24"/>
+      <c r="E76" s="24" t="s">
+        <v>127</v>
+      </c>
       <c r="F76" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="G76" s="38" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="77" ht="15.75" hidden="1" spans="1:7">
+    <row r="77" ht="15.75" spans="1:7">
       <c r="A77" s="24">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B77" s="25" t="s">
         <v>197</v>
@@ -4265,18 +4265,18 @@
         <v>126</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F77" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="G77" s="38" t="s">
+      <c r="G77" s="20" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="78" ht="15.75" hidden="1" spans="1:7">
+    <row r="78" ht="15.75" spans="1:7">
       <c r="A78" s="24">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B78" s="25" t="s">
         <v>200</v>
@@ -4288,21 +4288,18 @@
         <v>126</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F78" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="G78" s="20" t="s">
+    </row>
+    <row r="79" ht="15.75" spans="1:7">
+      <c r="A79" s="24">
+        <v>78</v>
+      </c>
+      <c r="B79" s="25" t="s">
         <v>202</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" hidden="1" spans="1:7">
-      <c r="A79" s="24">
-        <v>81</v>
-      </c>
-      <c r="B79" s="25" t="s">
-        <v>203</v>
       </c>
       <c r="C79" s="25" t="s">
         <v>8</v>
@@ -4310,16 +4307,17 @@
       <c r="D79" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E79" s="24" t="s">
-        <v>138</v>
-      </c>
+      <c r="E79" s="24"/>
       <c r="F79" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G79" s="20" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="80" ht="15.75" hidden="1" spans="1:7">
+    <row r="80" ht="15.75" spans="1:7">
       <c r="A80" s="24">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B80" s="25" t="s">
         <v>205</v>
@@ -4330,7 +4328,9 @@
       <c r="D80" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E80" s="24"/>
+      <c r="E80" s="24" t="s">
+        <v>127</v>
+      </c>
       <c r="F80" s="19" t="s">
         <v>206</v>
       </c>
@@ -4338,9 +4338,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="81" ht="15.75" hidden="1" spans="1:7">
+    <row r="81" ht="15.75" spans="1:7">
       <c r="A81" s="24">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B81" s="25" t="s">
         <v>208</v>
@@ -4351,22 +4351,17 @@
       <c r="D81" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E81" s="24" t="s">
-        <v>127</v>
-      </c>
+      <c r="E81" s="28"/>
       <c r="F81" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="G81" s="20" t="s">
+    </row>
+    <row r="82" ht="15.75" spans="1:7">
+      <c r="A82" s="24">
+        <v>81</v>
+      </c>
+      <c r="B82" s="25" t="s">
         <v>210</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" hidden="1" spans="1:7">
-      <c r="A82" s="24">
-        <v>84</v>
-      </c>
-      <c r="B82" s="25" t="s">
-        <v>211</v>
       </c>
       <c r="C82" s="25" t="s">
         <v>8</v>
@@ -4374,14 +4369,19 @@
       <c r="D82" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E82" s="28"/>
+      <c r="E82" s="28" t="s">
+        <v>138</v>
+      </c>
       <c r="F82" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="G82" s="20" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="83" ht="15.75" hidden="1" spans="1:7">
+    <row r="83" ht="15.75" spans="1:7">
       <c r="A83" s="24">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B83" s="25" t="s">
         <v>213</v>
@@ -4389,40 +4389,38 @@
       <c r="C83" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D83" s="24" t="s">
+      <c r="D83" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="E83" s="28" t="s">
-        <v>138</v>
-      </c>
+      <c r="E83" s="28"/>
       <c r="F83" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="G83" s="20" t="s">
+    </row>
+    <row r="84" ht="15.75" spans="1:7">
+      <c r="A84" s="24">
+        <v>83</v>
+      </c>
+      <c r="B84" s="25" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="84" ht="15.75" hidden="1" spans="1:7">
-      <c r="A84" s="24">
-        <v>86</v>
-      </c>
-      <c r="B84" s="25" t="s">
-        <v>216</v>
-      </c>
       <c r="C84" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D84" s="26" t="s">
+      <c r="D84" s="24" t="s">
         <v>126</v>
       </c>
       <c r="E84" s="28"/>
       <c r="F84" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G84" s="20" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="85" ht="15.75" hidden="1" spans="1:7">
+    <row r="85" ht="15.75" spans="1:7">
       <c r="A85" s="24">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B85" s="25" t="s">
         <v>218</v>
@@ -4433,7 +4431,7 @@
       <c r="D85" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E85" s="28"/>
+      <c r="E85" s="30"/>
       <c r="F85" s="19" t="s">
         <v>219</v>
       </c>
@@ -4441,9 +4439,9 @@
         <v>220</v>
       </c>
     </row>
-    <row r="86" ht="15.75" hidden="1" spans="1:7">
+    <row r="86" ht="15.75" spans="1:7">
       <c r="A86" s="24">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B86" s="25" t="s">
         <v>221</v>
@@ -4454,17 +4452,17 @@
       <c r="D86" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E86" s="30"/>
+      <c r="E86" s="24"/>
       <c r="F86" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="G86" s="20" t="s">
+      <c r="G86" s="38" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="87" ht="15.75" hidden="1" spans="1:7">
+    <row r="87" ht="15.75" spans="1:7">
       <c r="A87" s="24">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B87" s="25" t="s">
         <v>224</v>
@@ -4475,17 +4473,19 @@
       <c r="D87" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E87" s="24"/>
+      <c r="E87" s="24" t="s">
+        <v>138</v>
+      </c>
       <c r="F87" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="G87" s="38" t="s">
+      <c r="G87" s="20" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="88" ht="15.75" hidden="1" spans="1:7">
+    <row r="88" ht="15.75" spans="1:7">
       <c r="A88" s="24">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B88" s="25" t="s">
         <v>227</v>
@@ -4496,19 +4496,17 @@
       <c r="D88" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E88" s="24" t="s">
-        <v>138</v>
-      </c>
+      <c r="E88" s="24"/>
       <c r="F88" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="G88" s="20" t="s">
+      <c r="G88" s="38" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="89" ht="15.75" hidden="1" spans="1:7">
+    <row r="89" ht="15.75" spans="1:7">
       <c r="A89" s="24">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B89" s="25" t="s">
         <v>230</v>
@@ -4519,20 +4517,22 @@
       <c r="D89" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E89" s="24"/>
+      <c r="E89" s="24" t="s">
+        <v>231</v>
+      </c>
       <c r="F89" s="19" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G89" s="38" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" hidden="1" spans="1:7">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" spans="1:7">
       <c r="A90" s="24">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C90" s="25" t="s">
         <v>8</v>
@@ -4540,19 +4540,17 @@
       <c r="D90" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E90" s="24" t="s">
-        <v>234</v>
-      </c>
+      <c r="E90" s="24"/>
       <c r="F90" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="G90" s="38" t="s">
+      <c r="G90" s="20" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="91" ht="15.75" hidden="1" spans="1:7">
+    <row r="91" ht="15.75" spans="1:7">
       <c r="A91" s="24">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B91" s="25" t="s">
         <v>237</v>
@@ -4563,17 +4561,19 @@
       <c r="D91" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E91" s="24"/>
+      <c r="E91" s="24" t="s">
+        <v>134</v>
+      </c>
       <c r="F91" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="G91" s="20" t="s">
+      <c r="G91" s="38" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="92" ht="15.75" hidden="1" spans="1:7">
+    <row r="92" ht="15.75" spans="1:7">
       <c r="A92" s="24">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B92" s="25" t="s">
         <v>240</v>
@@ -4584,19 +4584,17 @@
       <c r="D92" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E92" s="24" t="s">
-        <v>134</v>
-      </c>
+      <c r="E92" s="24"/>
       <c r="F92" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="G92" s="38" t="s">
+      <c r="G92" s="20" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="93" ht="15.75" hidden="1" spans="1:7">
+    <row r="93" ht="31.5" spans="1:7">
       <c r="A93" s="24">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B93" s="25" t="s">
         <v>243</v>
@@ -4604,32 +4602,34 @@
       <c r="C93" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D93" s="24" t="s">
+      <c r="D93" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="E93" s="24"/>
+      <c r="E93" s="24" t="s">
+        <v>244</v>
+      </c>
       <c r="F93" s="19" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G93" s="20" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="94" ht="31.5" hidden="1" spans="1:7">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" spans="1:7">
       <c r="A94" s="24">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C94" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D94" s="26" t="s">
+      <c r="D94" s="24" t="s">
         <v>126</v>
       </c>
       <c r="E94" s="24" t="s">
-        <v>247</v>
+        <v>138</v>
       </c>
       <c r="F94" s="19" t="s">
         <v>248</v>
@@ -4638,9 +4638,9 @@
         <v>249</v>
       </c>
     </row>
-    <row r="95" ht="15.75" hidden="1" spans="1:7">
+    <row r="95" ht="15.75" spans="1:7">
       <c r="A95" s="24">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B95" s="25" t="s">
         <v>250</v>
@@ -4652,7 +4652,7 @@
         <v>126</v>
       </c>
       <c r="E95" s="24" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F95" s="19" t="s">
         <v>251</v>
@@ -4661,9 +4661,9 @@
         <v>252</v>
       </c>
     </row>
-    <row r="96" ht="15.75" hidden="1" spans="1:7">
+    <row r="96" ht="15.75" spans="1:7">
       <c r="A96" s="24">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B96" s="25" t="s">
         <v>253</v>
@@ -4674,22 +4674,14 @@
       <c r="D96" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E96" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="F96" s="19" t="s">
+      <c r="E96" s="24"/>
+    </row>
+    <row r="97" ht="15.75" spans="1:7">
+      <c r="A97" s="24">
+        <v>96</v>
+      </c>
+      <c r="B97" s="25" t="s">
         <v>254</v>
-      </c>
-      <c r="G96" s="20" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="97" ht="15.75" hidden="1" spans="1:7">
-      <c r="A97" s="24">
-        <v>99</v>
-      </c>
-      <c r="B97" s="25" t="s">
-        <v>256</v>
       </c>
       <c r="C97" s="25" t="s">
         <v>8</v>
@@ -4697,11 +4689,17 @@
       <c r="D97" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E97" s="24"/>
-    </row>
-    <row r="98" ht="15.75" hidden="1" spans="1:7">
+      <c r="E97" s="30"/>
+      <c r="F97" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="G97" s="20" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" spans="1:7">
       <c r="A98" s="24">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B98" s="25" t="s">
         <v>257</v>
@@ -4712,20 +4710,17 @@
       <c r="D98" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E98" s="30"/>
+      <c r="E98" s="28"/>
       <c r="F98" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="G98" s="20" t="s">
+    </row>
+    <row r="99" ht="15.75" spans="1:7">
+      <c r="A99" s="24">
+        <v>98</v>
+      </c>
+      <c r="B99" s="25" t="s">
         <v>259</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" hidden="1" spans="1:7">
-      <c r="A99" s="24">
-        <v>101</v>
-      </c>
-      <c r="B99" s="25" t="s">
-        <v>260</v>
       </c>
       <c r="C99" s="25" t="s">
         <v>8</v>
@@ -4733,14 +4728,17 @@
       <c r="D99" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E99" s="28"/>
+      <c r="E99" s="30"/>
       <c r="F99" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="G99" s="20" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="100" ht="15.75" spans="1:7">
       <c r="A100" s="24">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B100" s="25" t="s">
         <v>262</v>
@@ -4751,7 +4749,9 @@
       <c r="D100" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E100" s="30"/>
+      <c r="E100" s="24" t="s">
+        <v>134</v>
+      </c>
       <c r="F100" s="19" t="s">
         <v>263</v>
       </c>
@@ -4759,9 +4759,9 @@
         <v>264</v>
       </c>
     </row>
-    <row r="101" ht="15.75" hidden="1" spans="1:7">
+    <row r="101" ht="15.75" spans="1:7">
       <c r="A101" s="24">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B101" s="25" t="s">
         <v>265</v>
@@ -4772,9 +4772,7 @@
       <c r="D101" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E101" s="24" t="s">
-        <v>134</v>
-      </c>
+      <c r="E101" s="30"/>
       <c r="F101" s="19" t="s">
         <v>266</v>
       </c>
@@ -4782,9 +4780,9 @@
         <v>267</v>
       </c>
     </row>
-    <row r="102" ht="15.75" hidden="1" spans="1:7">
+    <row r="102" ht="15.75" spans="1:7">
       <c r="A102" s="24">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B102" s="25" t="s">
         <v>268</v>
@@ -4795,17 +4793,19 @@
       <c r="D102" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E102" s="30"/>
+      <c r="E102" s="24" t="s">
+        <v>138</v>
+      </c>
       <c r="F102" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="G102" s="20" t="s">
+      <c r="G102" s="38" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="103" ht="15.75" hidden="1" spans="1:7">
+    <row r="103" ht="15.75" spans="1:7">
       <c r="A103" s="24">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B103" s="25" t="s">
         <v>271</v>
@@ -4817,18 +4817,15 @@
         <v>126</v>
       </c>
       <c r="E103" s="24" t="s">
-        <v>138</v>
+        <v>272</v>
       </c>
       <c r="F103" s="19" t="s">
-        <v>272</v>
-      </c>
-      <c r="G103" s="38" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="104" ht="15.75" hidden="1" spans="1:7">
+    <row r="104" ht="15.75" spans="1:7">
       <c r="A104" s="24">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B104" s="25" t="s">
         <v>274</v>
@@ -4836,19 +4833,20 @@
       <c r="C104" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D104" s="24" t="s">
+      <c r="D104" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="E104" s="24" t="s">
+      <c r="E104" s="35"/>
+      <c r="F104" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="F104" s="19" t="s">
+      <c r="G104" s="38" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="105" ht="15.75" hidden="1" spans="1:7">
+    <row r="105" ht="15.75" spans="1:7">
       <c r="A105" s="24">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B105" s="25" t="s">
         <v>277</v>
@@ -4863,16 +4861,13 @@
       <c r="F105" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="G105" s="38" t="s">
+    </row>
+    <row r="106" ht="15.75" spans="1:7">
+      <c r="A106" s="24">
+        <v>105</v>
+      </c>
+      <c r="B106" s="25" t="s">
         <v>279</v>
-      </c>
-    </row>
-    <row r="106" ht="15.75" hidden="1" spans="1:7">
-      <c r="A106" s="24">
-        <v>108</v>
-      </c>
-      <c r="B106" s="25" t="s">
-        <v>280</v>
       </c>
       <c r="C106" s="25" t="s">
         <v>8</v>
@@ -4882,15 +4877,15 @@
       </c>
       <c r="E106" s="35"/>
       <c r="F106" s="19" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" spans="1:7">
+      <c r="A107" s="24">
+        <v>106</v>
+      </c>
+      <c r="B107" s="25" t="s">
         <v>281</v>
-      </c>
-    </row>
-    <row r="107" ht="15.75" hidden="1" spans="1:7">
-      <c r="A107" s="24">
-        <v>109</v>
-      </c>
-      <c r="B107" s="25" t="s">
-        <v>282</v>
       </c>
       <c r="C107" s="25" t="s">
         <v>8</v>
@@ -4900,15 +4895,15 @@
       </c>
       <c r="E107" s="35"/>
       <c r="F107" s="19" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="108" ht="31.5" spans="1:7">
+      <c r="A108" s="24">
+        <v>107</v>
+      </c>
+      <c r="B108" s="25" t="s">
         <v>283</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" hidden="1" spans="1:7">
-      <c r="A108" s="24">
-        <v>110</v>
-      </c>
-      <c r="B108" s="25" t="s">
-        <v>284</v>
       </c>
       <c r="C108" s="25" t="s">
         <v>8</v>
@@ -4918,15 +4913,15 @@
       </c>
       <c r="E108" s="35"/>
       <c r="F108" s="19" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" spans="1:7">
+      <c r="A109" s="24">
+        <v>108</v>
+      </c>
+      <c r="B109" s="25" t="s">
         <v>285</v>
-      </c>
-    </row>
-    <row r="109" ht="31.5" hidden="1" spans="1:7">
-      <c r="A109" s="24">
-        <v>111</v>
-      </c>
-      <c r="B109" s="25" t="s">
-        <v>286</v>
       </c>
       <c r="C109" s="25" t="s">
         <v>8</v>
@@ -4936,12 +4931,15 @@
       </c>
       <c r="E109" s="35"/>
       <c r="F109" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G109" s="20" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="110" ht="15.75" hidden="1" spans="1:7">
+    <row r="110" ht="15.75" spans="1:7">
       <c r="A110" s="24">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B110" s="25" t="s">
         <v>288</v>
@@ -4954,18 +4952,15 @@
       </c>
       <c r="E110" s="35"/>
       <c r="F110" s="19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="111" s="15" customFormat="1" ht="15.75" spans="1:7">
+      <c r="A111" s="24">
+        <v>110</v>
+      </c>
+      <c r="B111" s="25" t="s">
         <v>289</v>
-      </c>
-      <c r="G110" s="20" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" hidden="1" spans="1:7">
-      <c r="A111" s="24">
-        <v>113</v>
-      </c>
-      <c r="B111" s="25" t="s">
-        <v>291</v>
       </c>
       <c r="C111" s="25" t="s">
         <v>8</v>
@@ -4975,15 +4970,16 @@
       </c>
       <c r="E111" s="35"/>
       <c r="F111" s="19" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="112" s="15" customFormat="1" ht="15.75" hidden="1" spans="1:7">
+        <v>290</v>
+      </c>
+      <c r="G111" s="20"/>
+    </row>
+    <row r="112" ht="15.75" spans="1:7">
       <c r="A112" s="24">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C112" s="25" t="s">
         <v>8</v>
@@ -4991,18 +4987,19 @@
       <c r="D112" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="E112" s="35"/>
+      <c r="E112" s="34" t="s">
+        <v>138</v>
+      </c>
       <c r="F112" s="19" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" spans="1:7">
+      <c r="A113" s="24">
+        <v>112</v>
+      </c>
+      <c r="B113" s="25" t="s">
         <v>293</v>
-      </c>
-      <c r="G112" s="20"/>
-    </row>
-    <row r="113" ht="15.75" hidden="1" spans="1:7">
-      <c r="A113" s="24">
-        <v>115</v>
-      </c>
-      <c r="B113" s="25" t="s">
-        <v>294</v>
       </c>
       <c r="C113" s="25" t="s">
         <v>8</v>
@@ -5010,19 +5007,17 @@
       <c r="D113" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="34" t="s">
-        <v>138</v>
-      </c>
+      <c r="E113" s="35"/>
       <c r="F113" s="19" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" spans="1:7">
+      <c r="A114" s="24">
+        <v>113</v>
+      </c>
+      <c r="B114" s="25" t="s">
         <v>295</v>
-      </c>
-    </row>
-    <row r="114" ht="15.75" hidden="1" spans="1:7">
-      <c r="A114" s="24">
-        <v>116</v>
-      </c>
-      <c r="B114" s="25" t="s">
-        <v>296</v>
       </c>
       <c r="C114" s="25" t="s">
         <v>8</v>
@@ -5032,15 +5027,15 @@
       </c>
       <c r="E114" s="35"/>
       <c r="F114" s="19" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="115" ht="15.75" spans="1:7">
+      <c r="A115" s="24">
+        <v>114</v>
+      </c>
+      <c r="B115" s="25" t="s">
         <v>297</v>
-      </c>
-    </row>
-    <row r="115" ht="15.75" hidden="1" spans="1:7">
-      <c r="A115" s="24">
-        <v>118</v>
-      </c>
-      <c r="B115" s="25" t="s">
-        <v>298</v>
       </c>
       <c r="C115" s="25" t="s">
         <v>8</v>
@@ -5050,15 +5045,15 @@
       </c>
       <c r="E115" s="35"/>
       <c r="F115" s="19" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="116" ht="15.75" spans="1:7">
+      <c r="A116" s="24">
+        <v>115</v>
+      </c>
+      <c r="B116" s="25" t="s">
         <v>299</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" hidden="1" spans="1:7">
-      <c r="A116" s="24">
-        <v>119</v>
-      </c>
-      <c r="B116" s="25" t="s">
-        <v>300</v>
       </c>
       <c r="C116" s="25" t="s">
         <v>8</v>
@@ -5068,15 +5063,15 @@
       </c>
       <c r="E116" s="35"/>
       <c r="F116" s="19" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" spans="1:7">
+      <c r="A117" s="24">
+        <v>116</v>
+      </c>
+      <c r="B117" s="25" t="s">
         <v>301</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" hidden="1" spans="1:7">
-      <c r="A117" s="24">
-        <v>120</v>
-      </c>
-      <c r="B117" s="25" t="s">
-        <v>302</v>
       </c>
       <c r="C117" s="25" t="s">
         <v>8</v>
@@ -5086,15 +5081,15 @@
       </c>
       <c r="E117" s="35"/>
       <c r="F117" s="19" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" spans="1:7">
+      <c r="A118" s="24">
+        <v>117</v>
+      </c>
+      <c r="B118" s="25" t="s">
         <v>303</v>
-      </c>
-    </row>
-    <row r="118" ht="15.75" hidden="1" spans="1:7">
-      <c r="A118" s="24">
-        <v>121</v>
-      </c>
-      <c r="B118" s="25" t="s">
-        <v>304</v>
       </c>
       <c r="C118" s="25" t="s">
         <v>8</v>
@@ -5102,14 +5097,19 @@
       <c r="D118" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="E118" s="35"/>
+      <c r="E118" s="34" t="s">
+        <v>10</v>
+      </c>
       <c r="F118" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="G118" s="20" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="119" ht="15.75" hidden="1" spans="1:7">
+    <row r="119" ht="31.5" spans="1:7">
       <c r="A119" s="24">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B119" s="25" t="s">
         <v>306</v>
@@ -5118,19 +5118,21 @@
         <v>8</v>
       </c>
       <c r="D119" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E119" s="35"/>
+        <v>307</v>
+      </c>
+      <c r="E119" s="34" t="s">
+        <v>29</v>
+      </c>
       <c r="F119" s="19" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="120" ht="15.75" hidden="1" spans="1:7">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="120" ht="15.75" spans="1:7">
       <c r="A120" s="24">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B120" s="25" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C120" s="25" t="s">
         <v>8</v>
@@ -5140,35 +5142,32 @@
       </c>
       <c r="E120" s="35"/>
       <c r="F120" s="19" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="121" ht="15.75" hidden="1" spans="1:7">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="121" ht="15.75" spans="1:7">
       <c r="A121" s="24">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B121" s="25" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C121" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E121" s="34" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="E121" s="35" t="s">
+        <v>29</v>
       </c>
       <c r="F121" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="G121" s="20" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="122" ht="31.5" hidden="1" spans="1:7">
+    <row r="122" ht="15.75" spans="1:7">
       <c r="A122" s="24">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B122" s="25" t="s">
         <v>313</v>
@@ -5177,36 +5176,41 @@
         <v>8</v>
       </c>
       <c r="D122" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F122" s="19" t="s">
         <v>314</v>
-      </c>
-      <c r="E122" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="F122" s="19" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="123" ht="15.75" spans="1:7">
       <c r="A123" s="24">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B123" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="C123" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="C123" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D123" s="34" t="s">
-        <v>126</v>
-      </c>
-      <c r="E123" s="35"/>
-      <c r="F123" s="19" t="s">
+      <c r="G123" s="38" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="124" ht="15.75" hidden="1" spans="1:7">
+    <row r="124" ht="15.75" spans="1:7">
       <c r="A124" s="24">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B124" s="25" t="s">
         <v>318</v>
@@ -5214,65 +5218,71 @@
       <c r="C124" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D124" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="35" t="s">
-        <v>29</v>
+      <c r="D124" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E124" s="36" t="s">
+        <v>134</v>
       </c>
       <c r="F124" s="19" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="125" ht="15.75" hidden="1" spans="1:7">
+      <c r="G124" s="38" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" spans="1:7">
       <c r="A125" s="24">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B125" s="25" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C125" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D125" s="34" t="s">
+      <c r="D125" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="E125" s="35" t="s">
+      <c r="E125" s="36" t="s">
         <v>29</v>
       </c>
       <c r="F125" s="19" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="126" ht="15.75" hidden="1" spans="1:7">
+        <v>322</v>
+      </c>
+      <c r="G125" s="38" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" spans="1:7">
       <c r="A126" s="24">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C126" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D126" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" s="35" t="s">
-        <v>10</v>
+      <c r="D126" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E126" s="36" t="s">
+        <v>134</v>
       </c>
       <c r="F126" s="19" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G126" s="38" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="127" ht="15.75" hidden="1" spans="1:7">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" spans="1:7">
       <c r="A127" s="24">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C127" s="25" t="s">
         <v>8</v>
@@ -5284,41 +5294,38 @@
         <v>134</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G127" s="38" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="128" ht="15.75" hidden="1" spans="1:7">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" spans="1:7">
       <c r="A128" s="24">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B128" s="25" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C128" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="36" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E128" s="36" t="s">
         <v>29</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>329</v>
-      </c>
-      <c r="G128" s="38" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" hidden="1" spans="1:7">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" spans="1:7">
       <c r="A129" s="24">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C129" s="25" t="s">
         <v>8</v>
@@ -5330,18 +5337,18 @@
         <v>134</v>
       </c>
       <c r="F129" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="G129" s="38" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="130" ht="15.75" hidden="1" spans="1:7">
+      <c r="G129" s="20" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="130" ht="15.75" spans="1:7">
       <c r="A130" s="24">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B130" s="25" t="s">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="C130" s="25" t="s">
         <v>8</v>
@@ -5353,39 +5360,40 @@
         <v>134</v>
       </c>
       <c r="F130" s="19" t="s">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="G130" s="38" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="131" ht="15.75" hidden="1" spans="1:7">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" spans="1:7">
       <c r="A131" s="24">
+        <v>130</v>
+      </c>
+      <c r="B131" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="C131" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E131" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="B131" s="25" t="s">
-        <v>335</v>
-      </c>
-      <c r="C131" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D131" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="E131" s="36" t="s">
-        <v>29</v>
-      </c>
       <c r="F131" s="19" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="132" ht="15.75" hidden="1" spans="1:7">
+        <v>339</v>
+      </c>
+      <c r="G131" s="38" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" spans="1:7">
       <c r="A132" s="24">
-        <v>135</v>
-      </c>
-      <c r="B132" s="25" t="s">
-        <v>337</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="B132" s="25"/>
       <c r="C132" s="25" t="s">
         <v>8</v>
       </c>
@@ -5396,41 +5404,38 @@
         <v>134</v>
       </c>
       <c r="F132" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="G132" s="20" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="133" ht="15.75" hidden="1" spans="1:7">
+        <v>341</v>
+      </c>
+      <c r="G132" s="38" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="133" ht="15.75" spans="1:7">
       <c r="A133" s="24">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C133" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="36" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E133" s="36" t="s">
-        <v>134</v>
+        <v>344</v>
       </c>
       <c r="F133" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="G133" s="38" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" hidden="1" spans="1:7">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" spans="1:7">
       <c r="A134" s="24">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B134" s="25" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C134" s="25" t="s">
         <v>8</v>
@@ -5442,17 +5447,19 @@
         <v>134</v>
       </c>
       <c r="F134" s="19" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="G134" s="38" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="135" ht="15.75" hidden="1" spans="1:7">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="135" ht="15.75" spans="1:7">
       <c r="A135" s="24">
-        <v>138</v>
-      </c>
-      <c r="B135" s="25"/>
+        <v>134</v>
+      </c>
+      <c r="B135" s="25" t="s">
+        <v>349</v>
+      </c>
       <c r="C135" s="25" t="s">
         <v>8</v>
       </c>
@@ -5460,21 +5467,21 @@
         <v>126</v>
       </c>
       <c r="E135" s="36" t="s">
-        <v>134</v>
+        <v>231</v>
       </c>
       <c r="F135" s="19" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G135" s="38" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="136" ht="15.75" hidden="1" spans="1:7">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="136" ht="15.75" spans="1:7">
       <c r="A136" s="24">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B136" s="25" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C136" s="25" t="s">
         <v>8</v>
@@ -5483,127 +5490,124 @@
         <v>9</v>
       </c>
       <c r="E136" s="36" t="s">
-        <v>349</v>
+        <v>29</v>
       </c>
       <c r="F136" s="19" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="137" ht="15.75" hidden="1" spans="1:7">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="137" ht="15.75" spans="1:7">
       <c r="A137" s="24">
+        <v>136</v>
+      </c>
+      <c r="B137" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="C137" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E137" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="F137" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="G137" s="20" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="138" ht="15.75" spans="1:7">
+      <c r="A138" s="24">
+        <v>137</v>
+      </c>
+      <c r="B138" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="C138" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="E138" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" s="19" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="139" ht="15.75" spans="1:7">
+      <c r="A139" s="24">
+        <v>138</v>
+      </c>
+      <c r="B139" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="C139" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E139" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F139" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="G139" s="20" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="140" ht="19" customHeight="1" spans="1:7">
+      <c r="A140" s="24">
+        <v>139</v>
+      </c>
+      <c r="B140" s="25" t="s">
+        <v>362</v>
+      </c>
+      <c r="C140" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" s="19" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" spans="1:7">
+      <c r="A141" s="24">
         <v>140</v>
       </c>
-      <c r="B137" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="C137" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D137" s="36" t="s">
+      <c r="B141" s="25" t="s">
+        <v>364</v>
+      </c>
+      <c r="C141" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D141" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E137" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F137" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="G137" s="38" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="138" ht="15.75" hidden="1" spans="1:7">
-      <c r="A138" s="24">
+      <c r="E141" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F141" s="19" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" spans="1:7">
+      <c r="A142" s="24">
         <v>141</v>
       </c>
-      <c r="B138" s="25" t="s">
-        <v>354</v>
-      </c>
-      <c r="C138" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D138" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E138" s="36" t="s">
-        <v>234</v>
-      </c>
-      <c r="F138" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="G138" s="38" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="139" ht="15.75" hidden="1" spans="1:7">
-      <c r="A139" s="24">
-        <v>142</v>
-      </c>
-      <c r="B139" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="C139" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E139" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="F139" s="19" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="140" ht="15.75" hidden="1" spans="1:7">
-      <c r="A140" s="24">
-        <v>143</v>
-      </c>
-      <c r="B140" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="C140" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E140" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="F140" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="G140" s="20" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="141" ht="15.75" hidden="1" spans="1:7">
-      <c r="A141" s="24">
-        <v>144</v>
-      </c>
-      <c r="B141" s="25" t="s">
-        <v>359</v>
-      </c>
-      <c r="C141" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D141" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E141" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F141" s="19" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="142" ht="15.75" hidden="1" spans="1:7">
-      <c r="A142" s="24">
-        <v>145</v>
-      </c>
       <c r="B142" s="25" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="C142" s="25" t="s">
         <v>8</v>
@@ -5611,62 +5615,63 @@
       <c r="D142" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E142" s="28" t="s">
+      <c r="E142" s="28"/>
+      <c r="F142" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="G142" s="38" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" spans="1:7">
+      <c r="A143" s="24">
+        <v>142</v>
+      </c>
+      <c r="B143" s="25" t="s">
+        <v>369</v>
+      </c>
+      <c r="C143" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E143" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="F142" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="G142" s="20" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="143" ht="19" hidden="1" customHeight="1" spans="1:7">
-      <c r="A143" s="24">
-        <v>145</v>
-      </c>
-      <c r="B143" s="25" t="s">
-        <v>364</v>
-      </c>
-      <c r="C143" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="28" t="s">
+      <c r="F143" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="G143" s="38" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="144" ht="15.75" spans="1:7">
+      <c r="A144" s="24">
+        <v>143</v>
+      </c>
+      <c r="B144" s="25" t="s">
+        <v>372</v>
+      </c>
+      <c r="C144" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E143" s="28" t="s">
+      <c r="E144" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F143" s="19" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="144" ht="15.75" hidden="1" spans="1:7">
-      <c r="A144" s="24">
-        <v>146</v>
-      </c>
-      <c r="B144" s="25" t="s">
-        <v>366</v>
-      </c>
-      <c r="C144" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D144" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E144" s="28" t="s">
-        <v>138</v>
-      </c>
       <c r="F144" s="19" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="145" ht="15.75" hidden="1" spans="1:7">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="145" ht="15.75" spans="1:7">
       <c r="A145" s="24">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B145" s="25" t="s">
-        <v>300</v>
+        <v>374</v>
       </c>
       <c r="C145" s="25" t="s">
         <v>8</v>
@@ -5674,20 +5679,19 @@
       <c r="D145" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E145" s="28"/>
+      <c r="E145" s="28" t="s">
+        <v>138</v>
+      </c>
       <c r="F145" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="G145" s="38" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="146" ht="15.75" hidden="1" spans="1:7">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" spans="1:7">
       <c r="A146" s="24">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C146" s="25" t="s">
         <v>8</v>
@@ -5695,42 +5699,37 @@
       <c r="D146" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E146" s="28" t="s">
-        <v>134</v>
-      </c>
+      <c r="E146" s="28"/>
       <c r="F146" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="G146" s="38" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="147" ht="15.75" hidden="1" spans="1:7">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" spans="1:7">
       <c r="A147" s="24">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C147" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="28" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="E147" s="28" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="F147" s="19" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="148" ht="15.75" hidden="1" spans="1:7">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" spans="1:7">
       <c r="A148" s="24">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C148" s="25" t="s">
         <v>8</v>
@@ -5742,15 +5741,15 @@
         <v>138</v>
       </c>
       <c r="F148" s="19" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="149" ht="15.75" hidden="1" spans="1:7">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="149" ht="15.75" spans="1:7">
       <c r="A149" s="24">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C149" s="25" t="s">
         <v>8</v>
@@ -5758,57 +5757,62 @@
       <c r="D149" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E149" s="28"/>
+      <c r="E149" s="28" t="s">
+        <v>138</v>
+      </c>
       <c r="F149" s="19" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="150" ht="15.75" hidden="1" spans="1:7">
+        <v>383</v>
+      </c>
+      <c r="G149" s="38" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" spans="1:7">
       <c r="A150" s="24">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="C150" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="28" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E150" s="28" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="F150" s="19" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="151" ht="15.75" hidden="1" spans="1:7">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" spans="1:7">
       <c r="A151" s="24">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="C151" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="28" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E151" s="28" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="F151" s="19" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="152" ht="15.75" hidden="1" spans="1:7">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" spans="1:7">
       <c r="A152" s="24">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="C152" s="25" t="s">
         <v>8</v>
@@ -5817,61 +5821,64 @@
         <v>126</v>
       </c>
       <c r="E152" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F152" s="19" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="153" ht="15.75" spans="1:7">
+      <c r="A153" s="24">
+        <v>152</v>
+      </c>
+      <c r="B153" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="C153" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E153" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="F153" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="G153" s="38" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" spans="1:7">
+      <c r="A154" s="24">
+        <v>153</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="C154" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E154" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F152" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="G152" s="38" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="153" ht="15.75" hidden="1" spans="1:7">
-      <c r="A153" s="24">
+      <c r="F154" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="G154" s="38" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" spans="1:7">
+      <c r="A155" s="24">
         <v>154</v>
       </c>
-      <c r="B153" s="25" t="s">
-        <v>385</v>
-      </c>
-      <c r="C153" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D153" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F153" s="19" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="154" ht="15.75" hidden="1" spans="1:7">
-      <c r="A154" s="24">
-        <v>155</v>
-      </c>
-      <c r="B154" s="25" t="s">
-        <v>387</v>
-      </c>
-      <c r="C154" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D154" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="F154" s="19" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="155" ht="15.75" hidden="1" spans="1:7">
-      <c r="A155" s="24">
-        <v>156</v>
-      </c>
       <c r="B155" s="25" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C155" s="25" t="s">
         <v>8</v>
@@ -5880,18 +5887,21 @@
         <v>126</v>
       </c>
       <c r="E155" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F155" s="19" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="156" ht="15.75" hidden="1" spans="1:7">
+        <v>398</v>
+      </c>
+      <c r="G155" s="38" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" spans="1:7">
       <c r="A156" s="24">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C156" s="25" t="s">
         <v>8</v>
@@ -5900,21 +5910,21 @@
         <v>126</v>
       </c>
       <c r="E156" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F156" s="19" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="G156" s="38" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="157" ht="15.75" hidden="1" spans="1:7">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" spans="1:7">
       <c r="A157" s="24">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="C157" s="25" t="s">
         <v>8</v>
@@ -5923,21 +5933,18 @@
         <v>126</v>
       </c>
       <c r="E157" s="28" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F157" s="19" t="s">
-        <v>395</v>
-      </c>
-      <c r="G157" s="38" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="158" ht="15.75" hidden="1" spans="1:7">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="158" ht="15.75" spans="1:7">
       <c r="A158" s="24">
         <v>157</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C158" s="25" t="s">
         <v>8</v>
@@ -5949,18 +5956,18 @@
         <v>138</v>
       </c>
       <c r="F158" s="19" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="G158" s="38" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="159" ht="15.75" hidden="1" spans="1:7">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="159" ht="15.75" spans="1:7">
       <c r="A159" s="24">
         <v>158</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C159" s="25" t="s">
         <v>8</v>
@@ -5971,19 +5978,19 @@
       <c r="E159" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F159" s="19" t="s">
-        <v>401</v>
+      <c r="F159" s="37" t="s">
+        <v>409</v>
       </c>
       <c r="G159" s="38" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="160" ht="15.75" hidden="1" spans="1:7">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="160" s="16" customFormat="1" ht="31.5" spans="1:7">
       <c r="A160" s="24">
         <v>159</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C160" s="25" t="s">
         <v>8</v>
@@ -5992,18 +5999,21 @@
         <v>126</v>
       </c>
       <c r="E160" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F160" s="19" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="161" ht="15.75" hidden="1" spans="1:7">
+        <v>412</v>
+      </c>
+      <c r="G160" s="38" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" spans="1:7">
       <c r="A161" s="24">
         <v>160</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C161" s="25" t="s">
         <v>8</v>
@@ -6012,21 +6022,21 @@
         <v>126</v>
       </c>
       <c r="E161" s="28" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F161" s="19" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="G161" s="38" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="162" ht="15.75" hidden="1" spans="1:7">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="162" ht="15.75" spans="1:7">
       <c r="A162" s="24">
         <v>161</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C162" s="25" t="s">
         <v>8</v>
@@ -6037,42 +6047,42 @@
       <c r="E162" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F162" s="37" t="s">
-        <v>409</v>
+      <c r="F162" s="19" t="s">
+        <v>418</v>
       </c>
       <c r="G162" s="38" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="163" s="16" customFormat="1" ht="31.5" hidden="1" spans="1:7">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="163" ht="15.75" spans="1:7">
       <c r="A163" s="24">
         <v>162</v>
       </c>
       <c r="B163" s="25" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C163" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="28" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E163" s="28" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="F163" s="19" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="G163" s="38" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="164" ht="15.75" hidden="1" spans="1:7">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" spans="1:7">
       <c r="A164" s="24">
         <v>163</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="C164" s="25" t="s">
         <v>8</v>
@@ -6081,21 +6091,18 @@
         <v>126</v>
       </c>
       <c r="E164" s="28" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F164" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="G164" s="38" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="165" ht="15.75" hidden="1" spans="1:7">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" spans="1:7">
       <c r="A165" s="24">
         <v>164</v>
       </c>
       <c r="B165" s="25" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="C165" s="25" t="s">
         <v>8</v>
@@ -6107,41 +6114,30 @@
         <v>138</v>
       </c>
       <c r="F165" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="G165" s="38" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="166" ht="15.75" hidden="1" spans="1:7">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" spans="1:7">
       <c r="A166" s="24">
         <v>165</v>
       </c>
       <c r="B166" s="25" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="C166" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E166" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="F166" s="19" t="s">
-        <v>421</v>
-      </c>
-      <c r="G166" s="38" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="167" ht="15.75" hidden="1" spans="1:7">
+        <v>126</v>
+      </c>
+      <c r="E166" s="28"/>
+    </row>
+    <row r="167" ht="15.75" spans="1:7">
       <c r="A167" s="24">
         <v>166</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C167" s="25" t="s">
         <v>8</v>
@@ -6149,19 +6145,14 @@
       <c r="D167" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E167" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="F167" s="19" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="168" ht="15.75" hidden="1" spans="1:7">
+      <c r="E167" s="28"/>
+    </row>
+    <row r="168" ht="15.75" spans="1:7">
       <c r="A168" s="24">
         <v>167</v>
       </c>
       <c r="B168" s="25" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C168" s="25" t="s">
         <v>8</v>
@@ -6169,19 +6160,17 @@
       <c r="D168" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E168" s="28" t="s">
-        <v>138</v>
-      </c>
+      <c r="E168" s="28"/>
       <c r="F168" s="19" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="169" ht="15.75" hidden="1" spans="1:7">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" spans="1:7">
       <c r="A169" s="24">
         <v>168</v>
       </c>
       <c r="B169" s="25" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C169" s="25" t="s">
         <v>8</v>
@@ -6189,76 +6178,37 @@
       <c r="D169" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E169" s="28"/>
-    </row>
-    <row r="170" ht="15.75" hidden="1" spans="1:7">
+      <c r="E169" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F169" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="G169" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" spans="1:7">
       <c r="A170" s="24">
         <v>169</v>
       </c>
       <c r="B170" s="25" t="s">
-        <v>428</v>
-      </c>
-      <c r="C170" s="25" t="s">
-        <v>8</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="C170" s="25"/>
       <c r="D170" s="28" t="s">
         <v>126</v>
       </c>
       <c r="E170" s="28"/>
     </row>
-    <row r="171" ht="15.75" hidden="1" spans="1:7">
-      <c r="A171" s="24">
-        <v>170</v>
-      </c>
-      <c r="B171" s="25" t="s">
-        <v>429</v>
-      </c>
-      <c r="C171" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D171" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E171" s="28"/>
-      <c r="F171" s="19" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="172" ht="15.75" hidden="1" spans="1:7">
-      <c r="A172" s="24">
-        <v>171</v>
-      </c>
-      <c r="B172" s="25" t="s">
-        <v>431</v>
-      </c>
-      <c r="C172" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D172" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E172" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="F172" s="19" t="s">
-        <v>432</v>
-      </c>
-      <c r="G172" s="20" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="173" ht="15.75" hidden="1" spans="1:7">
-      <c r="A173" s="24">
-        <v>172</v>
-      </c>
-      <c r="B173" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="C173" s="25"/>
-      <c r="D173" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E173" s="28"/>
+    <row r="171" spans="1:7">
+      <c r="D171" s="18"/>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="D172" s="18"/>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="D173" s="18"/>
     </row>
     <row r="174" spans="1:7">
       <c r="D174" s="18"/>
@@ -9212,28 +9162,9 @@
     <row r="1157" spans="4:4">
       <c r="D1157" s="18"/>
     </row>
-    <row r="1158" spans="4:4">
-      <c r="D1158" s="18"/>
-    </row>
-    <row r="1159" spans="4:4">
-      <c r="D1159" s="18"/>
-    </row>
-    <row r="1160" spans="4:4">
-      <c r="D1160" s="18"/>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G173" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="BENSALEM Mohammed Mustapha"/>
-        <filter val="BRAHAMI MOHAMED NADJIB"/>
-        <filter val="ZERDANI MOHAMMED"/>
-        <filter val="REZOUG MOHAMMED"/>
-        <filter val="ZAREB Mohammed Amine"/>
-        <filter val="FELLAH MOHAMMED KARIM"/>
-      </filters>
-    </filterColumn>
-    <sortState ref="A1:G173">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G170" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:G170">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9242,67 +9173,64 @@
     <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
     <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
     <hyperlink ref="F54" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
-    <hyperlink ref="F105" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
-    <hyperlink ref="F106" r:id="rId5" display="aliaissani97@gmail.com"/>
-    <hyperlink ref="F123" r:id="rId6" display="medzerdani@gmail.com"/>
-    <hyperlink ref="F120" r:id="rId7" display="turkibilal22@gmail.com"/>
-    <hyperlink ref="F119" r:id="rId8" display="sacihamza40@gmail.com"/>
-    <hyperlink ref="F118" r:id="rId9" display="Boba1620@hotmail.com"/>
-    <hyperlink ref="F95" r:id="rId10" display="khelifa-mir@outlook.fr"/>
-    <hyperlink ref="F76" r:id="rId11" display="fethi22miloua@gmail.com"/>
-    <hyperlink ref="F74" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
-    <hyperlink ref="F93" r:id="rId13" display="mehadjiameslem@gmail.com"/>
-    <hyperlink ref="F91" r:id="rId14" display="mekhalefleila@gmail.com"/>
-    <hyperlink ref="F90" r:id="rId15" display="khalidamet4@gmail.com"/>
-    <hyperlink ref="F117" r:id="rId16" display="layatimedi@gmail.com"/>
-    <hyperlink ref="F85" r:id="rId17" display="m_latreche@yahoo.com"/>
-    <hyperlink ref="F116" r:id="rId18" display="kadrirania51@gmail.com"/>
-    <hyperlink ref="F81" r:id="rId19" display="protoboy9999@gmail.com"/>
-    <hyperlink ref="F75" r:id="rId20" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F72" r:id="rId21" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
-    <hyperlink ref="F67" r:id="rId22" display="douaaboularaf@gmail.com"/>
-    <hyperlink ref="F111" r:id="rId23" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F109" r:id="rId24" display="bkbhbb22@gmail.com"/>
-    <hyperlink ref="F59" r:id="rId25" display="bendida65@gmail.com"/>
-    <hyperlink ref="F58" r:id="rId26" display="sarrabencella@gmail.com"/>
-    <hyperlink ref="F60" r:id="rId27" display="ri123hab@gmail.com"/>
-    <hyperlink ref="F108" r:id="rId28" display="meriembelabed5@gmail.com"/>
-    <hyperlink ref="F45" r:id="rId29" display="rezoug.med@gmail.com"/>
-    <hyperlink ref="F84" r:id="rId30" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
-    <hyperlink ref="F57" r:id="rId31" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
-    <hyperlink ref="F100" r:id="rId32" display="zarebmohammedamine@gmail.com"/>
-    <hyperlink ref="F101" r:id="rId33" display="djamel71ziani@gmail.com"/>
-    <hyperlink ref="F65" r:id="rId34" display="ahmedboudali32@gmail.com"/>
-    <hyperlink ref="F69" r:id="rId35" display="chaouche.abdallah@gmail.com"/>
-    <hyperlink ref="F61" r:id="rId36" display="lakhdar_belhallouche@hotmail.fr"/>
-    <hyperlink ref="F80" r:id="rId37" display="ahmed.hadji22@yahoo.com"/>
-    <hyperlink ref="F103" r:id="rId38" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F32" r:id="rId39" display="khatir.mohamed1977@gmail.com"/>
-    <hyperlink ref="F2" r:id="rId40" display="irecom_abid@yahoo.fr"/>
-    <hyperlink ref="F7" r:id="rId41" display="karis483@hotmail.fr"/>
-    <hyperlink ref="F8" r:id="rId42" display="bahlilmounir@yahoo.fr"/>
-    <hyperlink ref="F10" r:id="rId43" display="beddadboucif@gmail.com"/>
-    <hyperlink ref="F9" r:id="rId44" display="seyfeddine.electrotechnique@gmail.com"/>
-    <hyperlink ref="F126" r:id="rId45" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
-    <hyperlink ref="F112" r:id="rId46" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
-    <hyperlink ref="F140" r:id="rId20" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F141" r:id="rId47" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
-    <hyperlink ref="F143" r:id="rId48" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
-    <hyperlink ref="F142" r:id="rId49" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
-    <hyperlink ref="F146" r:id="rId50" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
-    <hyperlink ref="F149" r:id="rId51" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
-    <hyperlink ref="F150" r:id="rId52" display="walid.sebastien@gmail.com"/>
-    <hyperlink ref="F151" r:id="rId53" display="bensenadanadia3@gmail.com"/>
-    <hyperlink ref="F152" r:id="rId54" display="imedmedles@gmail.com"/>
-    <hyperlink ref="F155" r:id="rId55" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
-    <hyperlink ref="F159" r:id="rId56" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
-    <hyperlink ref="F161" r:id="rId57" display="moh@medbnr.com"/>
-    <hyperlink ref="F163" r:id="rId58" display="hadilyamoune@gmail.com"/>
-    <hyperlink ref="F164" r:id="rId59" display="megdz100@gmail.com"/>
-    <hyperlink ref="F158" r:id="rId60" display="ikkachenarimen.2017@gmail.com"/>
-    <hyperlink ref="F160" r:id="rId61" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
-    <hyperlink ref="F165" r:id="rId62" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
-    <hyperlink ref="F144" r:id="rId63" display="inesfilali2003@gmail.com"/>
+    <hyperlink ref="F104" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
+    <hyperlink ref="F105" r:id="rId5" display="aliaissani97@gmail.com"/>
+    <hyperlink ref="F120" r:id="rId6" display="medzerdani@gmail.com"/>
+    <hyperlink ref="F117" r:id="rId7" display="sacihamza40@gmail.com"/>
+    <hyperlink ref="F116" r:id="rId8" display="Boba1620@hotmail.com"/>
+    <hyperlink ref="F94" r:id="rId9" display="khelifa-mir@outlook.fr"/>
+    <hyperlink ref="F75" r:id="rId10" display="fethi22miloua@gmail.com"/>
+    <hyperlink ref="F74" r:id="rId11" display="wahibaelmestarii@gmail.com"/>
+    <hyperlink ref="F92" r:id="rId12" display="mehadjiameslem@gmail.com"/>
+    <hyperlink ref="F90" r:id="rId13" display="mekhalefleila@gmail.com"/>
+    <hyperlink ref="F89" r:id="rId14" display="khalidamet4@gmail.com"/>
+    <hyperlink ref="F115" r:id="rId15" display="layatimedi@gmail.com"/>
+    <hyperlink ref="F84" r:id="rId16" display="m_latreche@yahoo.com"/>
+    <hyperlink ref="F80" r:id="rId17" display="protoboy9999@gmail.com"/>
+    <hyperlink ref="F72" r:id="rId18" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F67" r:id="rId19" display="douaaboularaf@gmail.com"/>
+    <hyperlink ref="F110" r:id="rId20" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F108" r:id="rId21" display="bkbhbb22@gmail.com"/>
+    <hyperlink ref="F59" r:id="rId22" display="bendida65@gmail.com"/>
+    <hyperlink ref="F58" r:id="rId23" display="sarrabencella@gmail.com"/>
+    <hyperlink ref="F60" r:id="rId24" display="ri123hab@gmail.com"/>
+    <hyperlink ref="F107" r:id="rId25" display="meriembelabed5@gmail.com"/>
+    <hyperlink ref="F45" r:id="rId26" display="rezoug.med@gmail.com"/>
+    <hyperlink ref="F83" r:id="rId27" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
+    <hyperlink ref="F57" r:id="rId28" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
+    <hyperlink ref="F99" r:id="rId29" display="zarebmohammedamine@gmail.com"/>
+    <hyperlink ref="F100" r:id="rId30" display="djamel71ziani@gmail.com"/>
+    <hyperlink ref="F65" r:id="rId31" display="ahmedboudali32@gmail.com"/>
+    <hyperlink ref="F69" r:id="rId32" display="chaouche.abdallah@gmail.com"/>
+    <hyperlink ref="F61" r:id="rId33" display="lakhdar_belhallouche@hotmail.fr"/>
+    <hyperlink ref="F79" r:id="rId34" display="ahmed.hadji22@yahoo.com"/>
+    <hyperlink ref="F102" r:id="rId35" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F32" r:id="rId36" display="khatir.mohamed1977@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId37" display="irecom_abid@yahoo.fr"/>
+    <hyperlink ref="F7" r:id="rId38" display="karis483@hotmail.fr"/>
+    <hyperlink ref="F8" r:id="rId39" display="bahlilmounir@yahoo.fr"/>
+    <hyperlink ref="F10" r:id="rId40" display="beddadboucif@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId41" display="seyfeddine.electrotechnique@gmail.com"/>
+    <hyperlink ref="F123" r:id="rId42" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F111" r:id="rId43" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F137" r:id="rId44" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F138" r:id="rId45" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
+    <hyperlink ref="F140" r:id="rId46" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
+    <hyperlink ref="F139" r:id="rId47" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
+    <hyperlink ref="F143" r:id="rId48" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
+    <hyperlink ref="F146" r:id="rId49" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
+    <hyperlink ref="F147" r:id="rId50" display="walid.sebastien@gmail.com"/>
+    <hyperlink ref="F148" r:id="rId51" display="bensenadanadia3@gmail.com"/>
+    <hyperlink ref="F149" r:id="rId52" display="imedmedles@gmail.com"/>
+    <hyperlink ref="F152" r:id="rId53" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
+    <hyperlink ref="F156" r:id="rId54" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
+    <hyperlink ref="F158" r:id="rId55" display="moh@medbnr.com"/>
+    <hyperlink ref="F160" r:id="rId56" display="hadilyamoune@gmail.com"/>
+    <hyperlink ref="F161" r:id="rId57" display="megdz100@gmail.com"/>
+    <hyperlink ref="F155" r:id="rId58" display="ikkachenarimen.2017@gmail.com"/>
+    <hyperlink ref="F157" r:id="rId59" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
+    <hyperlink ref="F162" r:id="rId60" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
+    <hyperlink ref="F141" r:id="rId61" display="inesfilali2003@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="475">
   <si>
     <t>N°</t>
   </si>
@@ -610,6 +610,15 @@
     <t>0556130770</t>
   </si>
   <si>
+    <t>ELGHODASSE ABDEL MADJID</t>
+  </si>
+  <si>
+    <t>elghodasseabdelmadjid@gmail.com</t>
+  </si>
+  <si>
+    <t>05 41 77 21 68</t>
+  </si>
+  <si>
     <t>MILOUA FETHI</t>
   </si>
   <si>
@@ -925,6 +934,12 @@
     <t>ikram.kadazair@gmail.com</t>
   </si>
   <si>
+    <t>KADRI RANIA</t>
+  </si>
+  <si>
+    <t>kadrirania51@gmail.com</t>
+  </si>
+  <si>
     <t>LAYATI TAYEB MEHDI</t>
   </si>
   <si>
@@ -943,6 +958,12 @@
     <t>sacihamza40@gmail.com</t>
   </si>
   <si>
+    <t>TURKI BILAL MEROUANE</t>
+  </si>
+  <si>
+    <t>turkibilal22@gmail.com</t>
+  </si>
+  <si>
     <t>RAIS ABDELMAJID</t>
   </si>
   <si>
@@ -1015,12 +1036,6 @@
     <t>0553714385</t>
   </si>
   <si>
-    <t>TURKI BILAL MEROUANE</t>
-  </si>
-  <si>
-    <t>turkibilal22@gmail.com</t>
-  </si>
-  <si>
     <t>0655206865</t>
   </si>
   <si>
@@ -1096,15 +1111,6 @@
     <t>hicham.zatla@gmail.com</t>
   </si>
   <si>
-    <t>ELGHODASSE ABDEL MADJID</t>
-  </si>
-  <si>
-    <t>elghodasseabdelmadjid@gmail.com</t>
-  </si>
-  <si>
-    <t>05 41 77 21 68</t>
-  </si>
-  <si>
     <t>BENSEDDIK NADIA</t>
   </si>
   <si>
@@ -1132,12 +1138,6 @@
     <t>inesfilali2003@gmail.com</t>
   </si>
   <si>
-    <t>KADRI RANIA</t>
-  </si>
-  <si>
-    <t>kadrirania51@gmail.com</t>
-  </si>
-  <si>
     <t>0794297709</t>
   </si>
   <si>
@@ -1337,6 +1337,12 @@
   </si>
   <si>
     <t>TALEB SOUMIA</t>
+  </si>
+  <si>
+    <t>BENDAOUD SALAHEDDINE</t>
+  </si>
+  <si>
+    <t>salahbnd31@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2654,7 +2660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:G1157"/>
+  <dimension ref="A1:G1160"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="7" style="17" customWidth="1"/>
@@ -4223,9 +4229,14 @@
       <c r="D75" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E75" s="24"/>
+      <c r="E75" s="24" t="s">
+        <v>127</v>
+      </c>
       <c r="F75" s="19" t="s">
         <v>193</v>
+      </c>
+      <c r="G75" s="20" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="76" ht="15.75" spans="1:7">
@@ -4233,7 +4244,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C76" s="25" t="s">
         <v>8</v>
@@ -4241,13 +4252,8 @@
       <c r="D76" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E76" s="24" t="s">
-        <v>127</v>
-      </c>
+      <c r="E76" s="24"/>
       <c r="F76" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="G76" s="38" t="s">
         <v>196</v>
       </c>
     </row>
@@ -4265,12 +4271,12 @@
         <v>126</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F77" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="G77" s="20" t="s">
+      <c r="G77" s="38" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4288,10 +4294,13 @@
         <v>126</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F78" s="19" t="s">
         <v>201</v>
+      </c>
+      <c r="G78" s="20" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="79" ht="15.75" spans="1:7">
@@ -4299,7 +4308,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C79" s="25" t="s">
         <v>8</v>
@@ -4307,11 +4316,10 @@
       <c r="D79" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E79" s="24"/>
+      <c r="E79" s="24" t="s">
+        <v>138</v>
+      </c>
       <c r="F79" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="G79" s="20" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4328,9 +4336,7 @@
       <c r="D80" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E80" s="24" t="s">
-        <v>127</v>
-      </c>
+      <c r="E80" s="24"/>
       <c r="F80" s="19" t="s">
         <v>206</v>
       </c>
@@ -4351,9 +4357,14 @@
       <c r="D81" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E81" s="28"/>
+      <c r="E81" s="24" t="s">
+        <v>127</v>
+      </c>
       <c r="F81" s="19" t="s">
         <v>209</v>
+      </c>
+      <c r="G81" s="20" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="82" ht="15.75" spans="1:7">
@@ -4361,7 +4372,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C82" s="25" t="s">
         <v>8</v>
@@ -4369,13 +4380,8 @@
       <c r="D82" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E82" s="28" t="s">
-        <v>138</v>
-      </c>
+      <c r="E82" s="28"/>
       <c r="F82" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="G82" s="20" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4389,12 +4395,17 @@
       <c r="C83" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D83" s="26" t="s">
+      <c r="D83" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E83" s="28"/>
+      <c r="E83" s="28" t="s">
+        <v>138</v>
+      </c>
       <c r="F83" s="19" t="s">
         <v>214</v>
+      </c>
+      <c r="G83" s="20" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="84" ht="15.75" spans="1:7">
@@ -4402,19 +4413,16 @@
         <v>83</v>
       </c>
       <c r="B84" s="25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C84" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D84" s="24" t="s">
+      <c r="D84" s="26" t="s">
         <v>126</v>
       </c>
       <c r="E84" s="28"/>
       <c r="F84" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="G84" s="20" t="s">
         <v>217</v>
       </c>
     </row>
@@ -4431,7 +4439,7 @@
       <c r="D85" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E85" s="30"/>
+      <c r="E85" s="28"/>
       <c r="F85" s="19" t="s">
         <v>219</v>
       </c>
@@ -4452,11 +4460,11 @@
       <c r="D86" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E86" s="24"/>
+      <c r="E86" s="30"/>
       <c r="F86" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="G86" s="38" t="s">
+      <c r="G86" s="20" t="s">
         <v>223</v>
       </c>
     </row>
@@ -4473,13 +4481,11 @@
       <c r="D87" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E87" s="24" t="s">
-        <v>138</v>
-      </c>
+      <c r="E87" s="24"/>
       <c r="F87" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="G87" s="20" t="s">
+      <c r="G87" s="38" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4496,11 +4502,13 @@
       <c r="D88" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E88" s="24"/>
+      <c r="E88" s="24" t="s">
+        <v>138</v>
+      </c>
       <c r="F88" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="G88" s="38" t="s">
+      <c r="G88" s="20" t="s">
         <v>229</v>
       </c>
     </row>
@@ -4517,14 +4525,12 @@
       <c r="D89" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E89" s="24" t="s">
+      <c r="E89" s="24"/>
+      <c r="F89" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="F89" s="19" t="s">
+      <c r="G89" s="38" t="s">
         <v>232</v>
-      </c>
-      <c r="G89" s="38" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="90" ht="15.75" spans="1:7">
@@ -4532,7 +4538,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C90" s="25" t="s">
         <v>8</v>
@@ -4540,11 +4546,13 @@
       <c r="D90" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E90" s="24"/>
+      <c r="E90" s="24" t="s">
+        <v>234</v>
+      </c>
       <c r="F90" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="G90" s="20" t="s">
+      <c r="G90" s="38" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4561,13 +4569,11 @@
       <c r="D91" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E91" s="24" t="s">
-        <v>134</v>
-      </c>
+      <c r="E91" s="24"/>
       <c r="F91" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="G91" s="38" t="s">
+      <c r="G91" s="20" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4584,15 +4590,17 @@
       <c r="D92" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E92" s="24"/>
+      <c r="E92" s="24" t="s">
+        <v>134</v>
+      </c>
       <c r="F92" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="G92" s="20" t="s">
+      <c r="G92" s="38" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="93" ht="31.5" spans="1:7">
+    <row r="93" ht="15.75" spans="1:7">
       <c r="A93" s="24">
         <v>92</v>
       </c>
@@ -4602,34 +4610,32 @@
       <c r="C93" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D93" s="26" t="s">
+      <c r="D93" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E93" s="24" t="s">
+      <c r="E93" s="24"/>
+      <c r="F93" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="F93" s="19" t="s">
+      <c r="G93" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="G93" s="20" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" spans="1:7">
+    </row>
+    <row r="94" ht="31.5" spans="1:7">
       <c r="A94" s="24">
         <v>93</v>
       </c>
       <c r="B94" s="25" t="s">
+        <v>246</v>
+      </c>
+      <c r="C94" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E94" s="24" t="s">
         <v>247</v>
-      </c>
-      <c r="C94" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E94" s="24" t="s">
-        <v>138</v>
       </c>
       <c r="F94" s="19" t="s">
         <v>248</v>
@@ -4652,7 +4658,7 @@
         <v>126</v>
       </c>
       <c r="E95" s="24" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F95" s="19" t="s">
         <v>251</v>
@@ -4674,14 +4680,22 @@
       <c r="D96" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E96" s="24"/>
+      <c r="E96" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>254</v>
+      </c>
+      <c r="G96" s="20" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="97" ht="15.75" spans="1:7">
       <c r="A97" s="24">
         <v>96</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C97" s="25" t="s">
         <v>8</v>
@@ -4689,13 +4703,7 @@
       <c r="D97" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E97" s="30"/>
-      <c r="F97" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="G97" s="20" t="s">
-        <v>256</v>
-      </c>
+      <c r="E97" s="24"/>
     </row>
     <row r="98" ht="15.75" spans="1:7">
       <c r="A98" s="24">
@@ -4710,9 +4718,12 @@
       <c r="D98" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E98" s="28"/>
+      <c r="E98" s="30"/>
       <c r="F98" s="19" t="s">
         <v>258</v>
+      </c>
+      <c r="G98" s="20" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="99" ht="15.75" spans="1:7">
@@ -4720,7 +4731,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C99" s="25" t="s">
         <v>8</v>
@@ -4728,11 +4739,8 @@
       <c r="D99" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E99" s="30"/>
+      <c r="E99" s="28"/>
       <c r="F99" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="G99" s="20" t="s">
         <v>261</v>
       </c>
     </row>
@@ -4749,9 +4757,7 @@
       <c r="D100" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E100" s="24" t="s">
-        <v>134</v>
-      </c>
+      <c r="E100" s="30"/>
       <c r="F100" s="19" t="s">
         <v>263</v>
       </c>
@@ -4772,7 +4778,9 @@
       <c r="D101" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E101" s="30"/>
+      <c r="E101" s="24" t="s">
+        <v>134</v>
+      </c>
       <c r="F101" s="19" t="s">
         <v>266</v>
       </c>
@@ -4793,13 +4801,11 @@
       <c r="D102" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E102" s="24" t="s">
-        <v>138</v>
-      </c>
+      <c r="E102" s="30"/>
       <c r="F102" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="G102" s="38" t="s">
+      <c r="G102" s="20" t="s">
         <v>270</v>
       </c>
     </row>
@@ -4817,9 +4823,12 @@
         <v>126</v>
       </c>
       <c r="E103" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F103" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="F103" s="19" t="s">
+      <c r="G103" s="38" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4833,14 +4842,13 @@
       <c r="C104" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D104" s="34" t="s">
+      <c r="D104" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="E104" s="35"/>
+      <c r="E104" s="24" t="s">
+        <v>275</v>
+      </c>
       <c r="F104" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="G104" s="38" t="s">
         <v>276</v>
       </c>
     </row>
@@ -4861,13 +4869,16 @@
       <c r="F105" s="19" t="s">
         <v>278</v>
       </c>
+      <c r="G105" s="38" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="106" ht="15.75" spans="1:7">
       <c r="A106" s="24">
         <v>105</v>
       </c>
       <c r="B106" s="25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C106" s="25" t="s">
         <v>8</v>
@@ -4877,7 +4888,7 @@
       </c>
       <c r="E106" s="35"/>
       <c r="F106" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="107" ht="15.75" spans="1:7">
@@ -4885,7 +4896,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C107" s="25" t="s">
         <v>8</v>
@@ -4895,15 +4906,15 @@
       </c>
       <c r="E107" s="35"/>
       <c r="F107" s="19" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="108" ht="31.5" spans="1:7">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" spans="1:7">
       <c r="A108" s="24">
         <v>107</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C108" s="25" t="s">
         <v>8</v>
@@ -4913,15 +4924,15 @@
       </c>
       <c r="E108" s="35"/>
       <c r="F108" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="109" ht="15.75" spans="1:7">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="109" ht="31.5" spans="1:7">
       <c r="A109" s="24">
         <v>108</v>
       </c>
       <c r="B109" s="25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C109" s="25" t="s">
         <v>8</v>
@@ -4931,9 +4942,6 @@
       </c>
       <c r="E109" s="35"/>
       <c r="F109" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="G109" s="20" t="s">
         <v>287</v>
       </c>
     </row>
@@ -4952,15 +4960,18 @@
       </c>
       <c r="E110" s="35"/>
       <c r="F110" s="19" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="111" s="15" customFormat="1" ht="15.75" spans="1:7">
+        <v>289</v>
+      </c>
+      <c r="G110" s="20" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" spans="1:7">
       <c r="A111" s="24">
         <v>110</v>
       </c>
       <c r="B111" s="25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C111" s="25" t="s">
         <v>8</v>
@@ -4970,16 +4981,15 @@
       </c>
       <c r="E111" s="35"/>
       <c r="F111" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="G111" s="20"/>
-    </row>
-    <row r="112" ht="15.75" spans="1:7">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="112" s="15" customFormat="1" ht="15.75" spans="1:7">
       <c r="A112" s="24">
         <v>111</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C112" s="25" t="s">
         <v>8</v>
@@ -4987,19 +4997,18 @@
       <c r="D112" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="E112" s="34" t="s">
-        <v>138</v>
-      </c>
+      <c r="E112" s="35"/>
       <c r="F112" s="19" t="s">
-        <v>292</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="G112" s="20"/>
     </row>
     <row r="113" ht="15.75" spans="1:7">
       <c r="A113" s="24">
         <v>112</v>
       </c>
       <c r="B113" s="25" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C113" s="25" t="s">
         <v>8</v>
@@ -5007,9 +5016,11 @@
       <c r="D113" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="E113" s="35"/>
+      <c r="E113" s="34" t="s">
+        <v>138</v>
+      </c>
       <c r="F113" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="114" ht="15.75" spans="1:7">
@@ -5017,7 +5028,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="25" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C114" s="25" t="s">
         <v>8</v>
@@ -5027,7 +5038,7 @@
       </c>
       <c r="E114" s="35"/>
       <c r="F114" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="115" ht="15.75" spans="1:7">
@@ -5035,7 +5046,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C115" s="25" t="s">
         <v>8</v>
@@ -5045,7 +5056,7 @@
       </c>
       <c r="E115" s="35"/>
       <c r="F115" s="19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="116" ht="15.75" spans="1:7">
@@ -5053,7 +5064,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C116" s="25" t="s">
         <v>8</v>
@@ -5063,7 +5074,7 @@
       </c>
       <c r="E116" s="35"/>
       <c r="F116" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="117" ht="15.75" spans="1:7">
@@ -5071,7 +5082,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="25" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C117" s="25" t="s">
         <v>8</v>
@@ -5081,7 +5092,7 @@
       </c>
       <c r="E117" s="35"/>
       <c r="F117" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="118" ht="15.75" spans="1:7">
@@ -5089,7 +5100,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="25" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C118" s="25" t="s">
         <v>8</v>
@@ -5097,17 +5108,12 @@
       <c r="D118" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="E118" s="34" t="s">
-        <v>10</v>
-      </c>
+      <c r="E118" s="35"/>
       <c r="F118" s="19" t="s">
-        <v>304</v>
-      </c>
-      <c r="G118" s="20" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="119" ht="31.5" spans="1:7">
+    <row r="119" ht="15.75" spans="1:7">
       <c r="A119" s="24">
         <v>118</v>
       </c>
@@ -5118,13 +5124,11 @@
         <v>8</v>
       </c>
       <c r="D119" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E119" s="35"/>
+      <c r="F119" s="19" t="s">
         <v>307</v>
-      </c>
-      <c r="E119" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="F119" s="19" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="120" ht="15.75" spans="1:7">
@@ -5132,7 +5136,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C120" s="25" t="s">
         <v>8</v>
@@ -5142,7 +5146,7 @@
       </c>
       <c r="E120" s="35"/>
       <c r="F120" s="19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="121" ht="15.75" spans="1:7">
@@ -5150,22 +5154,25 @@
         <v>120</v>
       </c>
       <c r="B121" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="E121" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="C121" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D121" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="F121" s="19" t="s">
+      <c r="G121" s="20" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="122" ht="15.75" spans="1:7">
+    <row r="122" ht="31.5" spans="1:7">
       <c r="A122" s="24">
         <v>121</v>
       </c>
@@ -5176,13 +5183,13 @@
         <v>8</v>
       </c>
       <c r="D122" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="E122" s="34" t="s">
         <v>29</v>
       </c>
       <c r="F122" s="19" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="123" ht="15.75" spans="1:7">
@@ -5190,21 +5197,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="25" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C123" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" s="35" t="s">
-        <v>10</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="E123" s="35"/>
       <c r="F123" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="G123" s="38" t="s">
         <v>317</v>
       </c>
     </row>
@@ -5218,17 +5220,14 @@
       <c r="C124" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D124" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E124" s="36" t="s">
-        <v>134</v>
+      <c r="D124" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="35" t="s">
+        <v>29</v>
       </c>
       <c r="F124" s="19" t="s">
         <v>319</v>
-      </c>
-      <c r="G124" s="38" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="125" ht="15.75" spans="1:7">
@@ -5236,22 +5235,19 @@
         <v>124</v>
       </c>
       <c r="B125" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="C125" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" s="19" t="s">
         <v>321</v>
-      </c>
-      <c r="C125" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="F125" s="19" t="s">
-        <v>322</v>
-      </c>
-      <c r="G125" s="38" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="126" ht="15.75" spans="1:7">
@@ -5259,22 +5255,22 @@
         <v>125</v>
       </c>
       <c r="B126" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="C126" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="G126" s="38" t="s">
         <v>324</v>
-      </c>
-      <c r="C126" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="36" t="s">
-        <v>126</v>
-      </c>
-      <c r="E126" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="F126" s="19" t="s">
-        <v>325</v>
-      </c>
-      <c r="G126" s="38" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="127" ht="15.75" spans="1:7">
@@ -5282,7 +5278,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="25" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C127" s="25" t="s">
         <v>8</v>
@@ -5294,10 +5290,10 @@
         <v>134</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G127" s="38" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="128" ht="15.75" spans="1:7">
@@ -5305,19 +5301,22 @@
         <v>127</v>
       </c>
       <c r="B128" s="25" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C128" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="36" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E128" s="36" t="s">
         <v>29</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>331</v>
+        <v>329</v>
+      </c>
+      <c r="G128" s="38" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="129" ht="15.75" spans="1:7">
@@ -5325,7 +5324,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C129" s="25" t="s">
         <v>8</v>
@@ -5337,10 +5336,10 @@
         <v>134</v>
       </c>
       <c r="F129" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="G129" s="38" t="s">
         <v>333</v>
-      </c>
-      <c r="G129" s="20" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="130" ht="15.75" spans="1:7">
@@ -5348,7 +5347,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="25" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="C130" s="25" t="s">
         <v>8</v>
@@ -5360,10 +5359,10 @@
         <v>134</v>
       </c>
       <c r="F130" s="19" t="s">
-        <v>336</v>
+        <v>309</v>
       </c>
       <c r="G130" s="38" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="131" ht="15.75" spans="1:7">
@@ -5371,29 +5370,28 @@
         <v>130</v>
       </c>
       <c r="B131" s="25" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C131" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="36" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E131" s="36" t="s">
-        <v>134</v>
+        <v>29</v>
       </c>
       <c r="F131" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="G131" s="38" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="132" ht="15.75" spans="1:7">
       <c r="A132" s="24">
         <v>131</v>
       </c>
-      <c r="B132" s="25"/>
+      <c r="B132" s="25" t="s">
+        <v>337</v>
+      </c>
       <c r="C132" s="25" t="s">
         <v>8</v>
       </c>
@@ -5404,10 +5402,10 @@
         <v>134</v>
       </c>
       <c r="F132" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="G132" s="38" t="s">
-        <v>342</v>
+        <v>338</v>
+      </c>
+      <c r="G132" s="20" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="133" ht="15.75" spans="1:7">
@@ -5415,19 +5413,22 @@
         <v>132</v>
       </c>
       <c r="B133" s="25" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C133" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="36" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="E133" s="36" t="s">
-        <v>344</v>
+        <v>134</v>
       </c>
       <c r="F133" s="19" t="s">
-        <v>345</v>
+        <v>341</v>
+      </c>
+      <c r="G133" s="38" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="134" ht="15.75" spans="1:7">
@@ -5435,7 +5436,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="25" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C134" s="25" t="s">
         <v>8</v>
@@ -5447,19 +5448,17 @@
         <v>134</v>
       </c>
       <c r="F134" s="19" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G134" s="38" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="135" ht="15.75" spans="1:7">
       <c r="A135" s="24">
         <v>134</v>
       </c>
-      <c r="B135" s="25" t="s">
-        <v>349</v>
-      </c>
+      <c r="B135" s="25"/>
       <c r="C135" s="25" t="s">
         <v>8</v>
       </c>
@@ -5467,13 +5466,13 @@
         <v>126</v>
       </c>
       <c r="E135" s="36" t="s">
-        <v>231</v>
+        <v>134</v>
       </c>
       <c r="F135" s="19" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G135" s="38" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="136" ht="15.75" spans="1:7">
@@ -5481,7 +5480,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="25" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C136" s="25" t="s">
         <v>8</v>
@@ -5490,10 +5489,10 @@
         <v>9</v>
       </c>
       <c r="E136" s="36" t="s">
-        <v>29</v>
+        <v>349</v>
       </c>
       <c r="F136" s="19" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="137" ht="15.75" spans="1:7">
@@ -5501,22 +5500,22 @@
         <v>136</v>
       </c>
       <c r="B137" s="25" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C137" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D137" s="24" t="s">
+      <c r="D137" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="E137" s="24" t="s">
-        <v>127</v>
+      <c r="E137" s="36" t="s">
+        <v>134</v>
       </c>
       <c r="F137" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="G137" s="20" t="s">
-        <v>356</v>
+        <v>352</v>
+      </c>
+      <c r="G137" s="38" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="138" ht="15.75" spans="1:7">
@@ -5524,19 +5523,22 @@
         <v>137</v>
       </c>
       <c r="B138" s="25" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C138" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D138" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E138" s="28" t="s">
-        <v>10</v>
+      <c r="D138" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E138" s="36" t="s">
+        <v>234</v>
       </c>
       <c r="F138" s="19" t="s">
-        <v>358</v>
+        <v>355</v>
+      </c>
+      <c r="G138" s="38" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="139" ht="15.75" spans="1:7">
@@ -5544,42 +5546,42 @@
         <v>138</v>
       </c>
       <c r="B139" s="25" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C139" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D139" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E139" s="28" t="s">
-        <v>134</v>
+      <c r="D139" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="36" t="s">
+        <v>29</v>
       </c>
       <c r="F139" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="G139" s="20" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="140" ht="19" customHeight="1" spans="1:7">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="140" ht="15.75" spans="1:7">
       <c r="A140" s="24">
         <v>139</v>
       </c>
       <c r="B140" s="25" t="s">
-        <v>362</v>
+        <v>192</v>
       </c>
       <c r="C140" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D140" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E140" s="28" t="s">
-        <v>10</v>
+      <c r="D140" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E140" s="24" t="s">
+        <v>127</v>
       </c>
       <c r="F140" s="19" t="s">
-        <v>363</v>
+        <v>193</v>
+      </c>
+      <c r="G140" s="20" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="141" ht="15.75" spans="1:7">
@@ -5587,19 +5589,19 @@
         <v>140</v>
       </c>
       <c r="B141" s="25" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C141" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="28" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E141" s="28" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="F141" s="19" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="142" ht="15.75" spans="1:7">
@@ -5607,7 +5609,7 @@
         <v>141</v>
       </c>
       <c r="B142" s="25" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C142" s="25" t="s">
         <v>8</v>
@@ -5615,35 +5617,34 @@
       <c r="D142" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E142" s="28"/>
+      <c r="E142" s="28" t="s">
+        <v>134</v>
+      </c>
       <c r="F142" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="G142" s="38" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="143" ht="15.75" spans="1:7">
+        <v>362</v>
+      </c>
+      <c r="G142" s="20" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="143" ht="19" customHeight="1" spans="1:7">
       <c r="A143" s="24">
         <v>142</v>
       </c>
       <c r="B143" s="25" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C143" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="28" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E143" s="28" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="F143" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="G143" s="38" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="144" ht="15.75" spans="1:7">
@@ -5651,19 +5652,19 @@
         <v>143</v>
       </c>
       <c r="B144" s="25" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C144" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="28" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="E144" s="28" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="F144" s="19" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="145" ht="15.75" spans="1:7">
@@ -5671,7 +5672,7 @@
         <v>144</v>
       </c>
       <c r="B145" s="25" t="s">
-        <v>374</v>
+        <v>300</v>
       </c>
       <c r="C145" s="25" t="s">
         <v>8</v>
@@ -5679,11 +5680,12 @@
       <c r="D145" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E145" s="28" t="s">
-        <v>138</v>
-      </c>
+      <c r="E145" s="28"/>
       <c r="F145" s="19" t="s">
-        <v>375</v>
+        <v>301</v>
+      </c>
+      <c r="G145" s="38" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="146" ht="15.75" spans="1:7">
@@ -5691,7 +5693,7 @@
         <v>145</v>
       </c>
       <c r="B146" s="25" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C146" s="25" t="s">
         <v>8</v>
@@ -5699,9 +5701,14 @@
       <c r="D146" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E146" s="28"/>
+      <c r="E146" s="28" t="s">
+        <v>134</v>
+      </c>
       <c r="F146" s="19" t="s">
-        <v>377</v>
+        <v>370</v>
+      </c>
+      <c r="G146" s="38" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="147" ht="15.75" spans="1:7">
@@ -5709,19 +5716,19 @@
         <v>146</v>
       </c>
       <c r="B147" s="25" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C147" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="28" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E147" s="28" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="F147" s="19" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="148" ht="15.75" spans="1:7">
@@ -5729,7 +5736,7 @@
         <v>147</v>
       </c>
       <c r="B148" s="25" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C148" s="25" t="s">
         <v>8</v>
@@ -5741,7 +5748,7 @@
         <v>138</v>
       </c>
       <c r="F148" s="19" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="149" ht="15.75" spans="1:7">
@@ -5749,7 +5756,7 @@
         <v>148</v>
       </c>
       <c r="B149" s="25" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C149" s="25" t="s">
         <v>8</v>
@@ -5757,14 +5764,9 @@
       <c r="D149" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E149" s="28" t="s">
-        <v>138</v>
-      </c>
+      <c r="E149" s="28"/>
       <c r="F149" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="G149" s="38" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="150" ht="15.75" spans="1:7">
@@ -5772,19 +5774,19 @@
         <v>149</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
       <c r="C150" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="28" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="E150" s="28" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="F150" s="19" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="151" ht="15.75" spans="1:7">
@@ -5792,19 +5794,19 @@
         <v>150</v>
       </c>
       <c r="B151" s="25" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
       <c r="C151" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="28" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="E151" s="28" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="F151" s="19" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="152" ht="15.75" spans="1:7">
@@ -5812,7 +5814,7 @@
         <v>151</v>
       </c>
       <c r="B152" s="25" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="C152" s="25" t="s">
         <v>8</v>
@@ -5821,10 +5823,13 @@
         <v>126</v>
       </c>
       <c r="E152" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F152" s="19" t="s">
-        <v>390</v>
+        <v>383</v>
+      </c>
+      <c r="G152" s="38" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="153" ht="15.75" spans="1:7">
@@ -5832,22 +5837,19 @@
         <v>152</v>
       </c>
       <c r="B153" s="25" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C153" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D153" s="28" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E153" s="28" t="s">
-        <v>134</v>
+        <v>10</v>
       </c>
       <c r="F153" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="G153" s="38" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="154" ht="15.75" spans="1:7">
@@ -5855,22 +5857,19 @@
         <v>153</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="C154" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D154" s="28" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="E154" s="28" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="F154" s="19" t="s">
-        <v>395</v>
-      </c>
-      <c r="G154" s="38" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="155" ht="15.75" spans="1:7">
@@ -5878,7 +5877,7 @@
         <v>154</v>
       </c>
       <c r="B155" s="25" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C155" s="25" t="s">
         <v>8</v>
@@ -5887,13 +5886,10 @@
         <v>126</v>
       </c>
       <c r="E155" s="28" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F155" s="19" t="s">
-        <v>398</v>
-      </c>
-      <c r="G155" s="38" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="156" ht="15.75" spans="1:7">
@@ -5901,7 +5897,7 @@
         <v>155</v>
       </c>
       <c r="B156" s="25" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C156" s="25" t="s">
         <v>8</v>
@@ -5910,13 +5906,13 @@
         <v>126</v>
       </c>
       <c r="E156" s="28" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F156" s="19" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="G156" s="38" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="157" ht="15.75" spans="1:7">
@@ -5924,7 +5920,7 @@
         <v>156</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="C157" s="25" t="s">
         <v>8</v>
@@ -5933,10 +5929,13 @@
         <v>126</v>
       </c>
       <c r="E157" s="28" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F157" s="19" t="s">
-        <v>404</v>
+        <v>395</v>
+      </c>
+      <c r="G157" s="38" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="158" ht="15.75" spans="1:7">
@@ -5944,7 +5943,7 @@
         <v>157</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C158" s="25" t="s">
         <v>8</v>
@@ -5956,10 +5955,10 @@
         <v>138</v>
       </c>
       <c r="F158" s="19" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="G158" s="38" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="159" ht="15.75" spans="1:7">
@@ -5967,7 +5966,7 @@
         <v>158</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C159" s="25" t="s">
         <v>8</v>
@@ -5978,19 +5977,19 @@
       <c r="E159" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F159" s="37" t="s">
-        <v>409</v>
+      <c r="F159" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="G159" s="38" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="160" s="16" customFormat="1" ht="31.5" spans="1:7">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" spans="1:7">
       <c r="A160" s="24">
         <v>159</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="C160" s="25" t="s">
         <v>8</v>
@@ -5999,13 +5998,10 @@
         <v>126</v>
       </c>
       <c r="E160" s="28" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F160" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="G160" s="38" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
     </row>
     <row r="161" ht="15.75" spans="1:7">
@@ -6013,7 +6009,7 @@
         <v>160</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="C161" s="25" t="s">
         <v>8</v>
@@ -6022,13 +6018,13 @@
         <v>126</v>
       </c>
       <c r="E161" s="28" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F161" s="19" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="G161" s="38" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" ht="15.75" spans="1:7">
@@ -6036,7 +6032,7 @@
         <v>161</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C162" s="25" t="s">
         <v>8</v>
@@ -6047,34 +6043,34 @@
       <c r="E162" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="F162" s="19" t="s">
-        <v>418</v>
+      <c r="F162" s="37" t="s">
+        <v>409</v>
       </c>
       <c r="G162" s="38" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="163" ht="15.75" spans="1:7">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="163" s="16" customFormat="1" ht="31.5" spans="1:7">
       <c r="A163" s="24">
         <v>162</v>
       </c>
       <c r="B163" s="25" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C163" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D163" s="28" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="E163" s="28" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="F163" s="19" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="G163" s="38" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164" ht="15.75" spans="1:7">
@@ -6082,7 +6078,7 @@
         <v>163</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="C164" s="25" t="s">
         <v>8</v>
@@ -6091,10 +6087,13 @@
         <v>126</v>
       </c>
       <c r="E164" s="28" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F164" s="19" t="s">
-        <v>424</v>
+        <v>415</v>
+      </c>
+      <c r="G164" s="38" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="165" ht="15.75" spans="1:7">
@@ -6102,7 +6101,7 @@
         <v>164</v>
       </c>
       <c r="B165" s="25" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C165" s="25" t="s">
         <v>8</v>
@@ -6114,7 +6113,10 @@
         <v>138</v>
       </c>
       <c r="F165" s="19" t="s">
-        <v>426</v>
+        <v>418</v>
+      </c>
+      <c r="G165" s="38" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="166" ht="15.75" spans="1:7">
@@ -6122,22 +6124,30 @@
         <v>165</v>
       </c>
       <c r="B166" s="25" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C166" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D166" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="E166" s="28"/>
+        <v>9</v>
+      </c>
+      <c r="E166" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F166" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G166" s="38" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="167" ht="15.75" spans="1:7">
       <c r="A167" s="24">
         <v>166</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="C167" s="25" t="s">
         <v>8</v>
@@ -6145,14 +6155,19 @@
       <c r="D167" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E167" s="28"/>
+      <c r="E167" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F167" s="19" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="168" ht="15.75" spans="1:7">
       <c r="A168" s="24">
         <v>167</v>
       </c>
       <c r="B168" s="25" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C168" s="25" t="s">
         <v>8</v>
@@ -6160,9 +6175,11 @@
       <c r="D168" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E168" s="28"/>
+      <c r="E168" s="28" t="s">
+        <v>138</v>
+      </c>
       <c r="F168" s="19" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="169" ht="15.75" spans="1:7">
@@ -6170,7 +6187,7 @@
         <v>168</v>
       </c>
       <c r="B169" s="25" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C169" s="25" t="s">
         <v>8</v>
@@ -6178,40 +6195,98 @@
       <c r="D169" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E169" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="F169" s="19" t="s">
-        <v>432</v>
-      </c>
-      <c r="G169" s="20" t="s">
-        <v>433</v>
-      </c>
+      <c r="E169" s="28"/>
     </row>
     <row r="170" ht="15.75" spans="1:7">
       <c r="A170" s="24">
         <v>169</v>
       </c>
       <c r="B170" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="C170" s="25"/>
+        <v>428</v>
+      </c>
+      <c r="C170" s="25" t="s">
+        <v>8</v>
+      </c>
       <c r="D170" s="28" t="s">
         <v>126</v>
       </c>
       <c r="E170" s="28"/>
     </row>
-    <row r="171" spans="1:7">
-      <c r="D171" s="18"/>
-    </row>
-    <row r="172" spans="1:7">
-      <c r="D172" s="18"/>
-    </row>
-    <row r="173" spans="1:7">
-      <c r="D173" s="18"/>
-    </row>
-    <row r="174" spans="1:7">
-      <c r="D174" s="18"/>
+    <row r="171" ht="15.75" spans="1:7">
+      <c r="A171" s="24">
+        <v>170</v>
+      </c>
+      <c r="B171" s="25" t="s">
+        <v>429</v>
+      </c>
+      <c r="C171" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E171" s="28"/>
+      <c r="F171" s="19" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" spans="1:7">
+      <c r="A172" s="24">
+        <v>171</v>
+      </c>
+      <c r="B172" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="C172" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E172" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="F172" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="G172" s="20" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="173" ht="15.75" spans="1:7">
+      <c r="A173" s="24">
+        <v>172</v>
+      </c>
+      <c r="B173" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="C173" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D173" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E173" s="28"/>
+    </row>
+    <row r="174" ht="15.75" spans="1:7">
+      <c r="A174" s="24">
+        <v>173</v>
+      </c>
+      <c r="B174" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="C174" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D174" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="E174" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F174" s="19" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="175" spans="1:7">
       <c r="D175" s="18"/>
@@ -9162,9 +9237,18 @@
     <row r="1157" spans="4:4">
       <c r="D1157" s="18"/>
     </row>
+    <row r="1158" spans="4:4">
+      <c r="D1158" s="18"/>
+    </row>
+    <row r="1159" spans="4:4">
+      <c r="D1159" s="18"/>
+    </row>
+    <row r="1160" spans="4:4">
+      <c r="D1160" s="18"/>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G170" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:G170">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G174" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:G174">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9173,64 +9257,67 @@
     <hyperlink ref="F20" r:id="rId1" display="bentaallah65@yahoo.fr"/>
     <hyperlink ref="F24" r:id="rId2" display="djeriri_youcef@yahoo.fr"/>
     <hyperlink ref="F54" r:id="rId3" display="abbasmohammed.com@gmail.com" tooltip="mailto:abbasmohammed.com@gmail.com"/>
-    <hyperlink ref="F104" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
-    <hyperlink ref="F105" r:id="rId5" display="aliaissani97@gmail.com"/>
-    <hyperlink ref="F120" r:id="rId6" display="medzerdani@gmail.com"/>
-    <hyperlink ref="F117" r:id="rId7" display="sacihamza40@gmail.com"/>
-    <hyperlink ref="F116" r:id="rId8" display="Boba1620@hotmail.com"/>
-    <hyperlink ref="F94" r:id="rId9" display="khelifa-mir@outlook.fr"/>
-    <hyperlink ref="F75" r:id="rId10" display="fethi22miloua@gmail.com"/>
-    <hyperlink ref="F74" r:id="rId11" display="wahibaelmestarii@gmail.com"/>
-    <hyperlink ref="F92" r:id="rId12" display="mehadjiameslem@gmail.com"/>
-    <hyperlink ref="F90" r:id="rId13" display="mekhalefleila@gmail.com"/>
-    <hyperlink ref="F89" r:id="rId14" display="khalidamet4@gmail.com"/>
-    <hyperlink ref="F115" r:id="rId15" display="layatimedi@gmail.com"/>
-    <hyperlink ref="F84" r:id="rId16" display="m_latreche@yahoo.com"/>
-    <hyperlink ref="F80" r:id="rId17" display="protoboy9999@gmail.com"/>
-    <hyperlink ref="F72" r:id="rId18" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
-    <hyperlink ref="F67" r:id="rId19" display="douaaboularaf@gmail.com"/>
-    <hyperlink ref="F110" r:id="rId20" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F108" r:id="rId21" display="bkbhbb22@gmail.com"/>
-    <hyperlink ref="F59" r:id="rId22" display="bendida65@gmail.com"/>
-    <hyperlink ref="F58" r:id="rId23" display="sarrabencella@gmail.com"/>
-    <hyperlink ref="F60" r:id="rId24" display="ri123hab@gmail.com"/>
-    <hyperlink ref="F107" r:id="rId25" display="meriembelabed5@gmail.com"/>
-    <hyperlink ref="F45" r:id="rId26" display="rezoug.med@gmail.com"/>
-    <hyperlink ref="F83" r:id="rId27" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
-    <hyperlink ref="F57" r:id="rId28" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
-    <hyperlink ref="F99" r:id="rId29" display="zarebmohammedamine@gmail.com"/>
-    <hyperlink ref="F100" r:id="rId30" display="djamel71ziani@gmail.com"/>
-    <hyperlink ref="F65" r:id="rId31" display="ahmedboudali32@gmail.com"/>
-    <hyperlink ref="F69" r:id="rId32" display="chaouche.abdallah@gmail.com"/>
-    <hyperlink ref="F61" r:id="rId33" display="lakhdar_belhallouche@hotmail.fr"/>
-    <hyperlink ref="F79" r:id="rId34" display="ahmed.hadji22@yahoo.com"/>
-    <hyperlink ref="F102" r:id="rId35" display="berhenen@yahoo.fr"/>
-    <hyperlink ref="F32" r:id="rId36" display="khatir.mohamed1977@gmail.com"/>
-    <hyperlink ref="F2" r:id="rId37" display="irecom_abid@yahoo.fr"/>
-    <hyperlink ref="F7" r:id="rId38" display="karis483@hotmail.fr"/>
-    <hyperlink ref="F8" r:id="rId39" display="bahlilmounir@yahoo.fr"/>
-    <hyperlink ref="F10" r:id="rId40" display="beddadboucif@gmail.com"/>
-    <hyperlink ref="F9" r:id="rId41" display="seyfeddine.electrotechnique@gmail.com"/>
-    <hyperlink ref="F123" r:id="rId42" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
-    <hyperlink ref="F111" r:id="rId43" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
-    <hyperlink ref="F137" r:id="rId44" display="elghodasseabdelmadjid@gmail.com"/>
-    <hyperlink ref="F138" r:id="rId45" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
-    <hyperlink ref="F140" r:id="rId46" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
-    <hyperlink ref="F139" r:id="rId47" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
-    <hyperlink ref="F143" r:id="rId48" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
-    <hyperlink ref="F146" r:id="rId49" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
-    <hyperlink ref="F147" r:id="rId50" display="walid.sebastien@gmail.com"/>
-    <hyperlink ref="F148" r:id="rId51" display="bensenadanadia3@gmail.com"/>
-    <hyperlink ref="F149" r:id="rId52" display="imedmedles@gmail.com"/>
-    <hyperlink ref="F152" r:id="rId53" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
-    <hyperlink ref="F156" r:id="rId54" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
-    <hyperlink ref="F158" r:id="rId55" display="moh@medbnr.com"/>
-    <hyperlink ref="F160" r:id="rId56" display="hadilyamoune@gmail.com"/>
-    <hyperlink ref="F161" r:id="rId57" display="megdz100@gmail.com"/>
-    <hyperlink ref="F155" r:id="rId58" display="ikkachenarimen.2017@gmail.com"/>
-    <hyperlink ref="F157" r:id="rId59" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
-    <hyperlink ref="F162" r:id="rId60" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
-    <hyperlink ref="F141" r:id="rId61" display="inesfilali2003@gmail.com"/>
+    <hyperlink ref="F105" r:id="rId4" display="zoulikhaabed3@gmail.com"/>
+    <hyperlink ref="F106" r:id="rId5" display="aliaissani97@gmail.com"/>
+    <hyperlink ref="F123" r:id="rId6" display="medzerdani@gmail.com"/>
+    <hyperlink ref="F120" r:id="rId7" display="turkibilal22@gmail.com"/>
+    <hyperlink ref="F119" r:id="rId8" display="sacihamza40@gmail.com"/>
+    <hyperlink ref="F118" r:id="rId9" display="Boba1620@hotmail.com"/>
+    <hyperlink ref="F95" r:id="rId10" display="khelifa-mir@outlook.fr"/>
+    <hyperlink ref="F76" r:id="rId11" display="fethi22miloua@gmail.com"/>
+    <hyperlink ref="F74" r:id="rId12" display="wahibaelmestarii@gmail.com"/>
+    <hyperlink ref="F93" r:id="rId13" display="mehadjiameslem@gmail.com"/>
+    <hyperlink ref="F91" r:id="rId14" display="mekhalefleila@gmail.com"/>
+    <hyperlink ref="F90" r:id="rId15" display="khalidamet4@gmail.com"/>
+    <hyperlink ref="F117" r:id="rId16" display="layatimedi@gmail.com"/>
+    <hyperlink ref="F85" r:id="rId17" display="m_latreche@yahoo.com"/>
+    <hyperlink ref="F116" r:id="rId18" display="kadrirania51@gmail.com"/>
+    <hyperlink ref="F81" r:id="rId19" display="protoboy9999@gmail.com"/>
+    <hyperlink ref="F75" r:id="rId20" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F72" r:id="rId21" display="Lamia_du22@hotmail.com" tooltip="mailto:Lamia_du22@hotmail.com"/>
+    <hyperlink ref="F67" r:id="rId22" display="douaaboularaf@gmail.com"/>
+    <hyperlink ref="F111" r:id="rId23" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F109" r:id="rId24" display="bkbhbb22@gmail.com"/>
+    <hyperlink ref="F59" r:id="rId25" display="bendida65@gmail.com"/>
+    <hyperlink ref="F58" r:id="rId26" display="sarrabencella@gmail.com"/>
+    <hyperlink ref="F60" r:id="rId27" display="ri123hab@gmail.com"/>
+    <hyperlink ref="F108" r:id="rId28" display="meriembelabed5@gmail.com"/>
+    <hyperlink ref="F45" r:id="rId29" display="rezoug.med@gmail.com"/>
+    <hyperlink ref="F84" r:id="rId30" display="azddinelahcene@gmail.com" tooltip="mailto:azddinelahcene@gmail.com"/>
+    <hyperlink ref="F57" r:id="rId31" display="Mouffok.arezki22@gmail.com " tooltip="mailto:Mouffok.arezki22@gmail.com"/>
+    <hyperlink ref="F100" r:id="rId32" display="zarebmohammedamine@gmail.com"/>
+    <hyperlink ref="F101" r:id="rId33" display="djamel71ziani@gmail.com"/>
+    <hyperlink ref="F65" r:id="rId34" display="ahmedboudali32@gmail.com"/>
+    <hyperlink ref="F69" r:id="rId35" display="chaouche.abdallah@gmail.com"/>
+    <hyperlink ref="F61" r:id="rId36" display="lakhdar_belhallouche@hotmail.fr"/>
+    <hyperlink ref="F80" r:id="rId37" display="ahmed.hadji22@yahoo.com"/>
+    <hyperlink ref="F103" r:id="rId38" display="berhenen@yahoo.fr"/>
+    <hyperlink ref="F32" r:id="rId39" display="khatir.mohamed1977@gmail.com"/>
+    <hyperlink ref="F2" r:id="rId40" display="irecom_abid@yahoo.fr"/>
+    <hyperlink ref="F7" r:id="rId41" display="karis483@hotmail.fr"/>
+    <hyperlink ref="F8" r:id="rId42" display="bahlilmounir@yahoo.fr"/>
+    <hyperlink ref="F10" r:id="rId43" display="beddadboucif@gmail.com"/>
+    <hyperlink ref="F9" r:id="rId44" display="seyfeddine.electrotechnique@gmail.com"/>
+    <hyperlink ref="F126" r:id="rId45" display="milouaf@yahoo.fr" tooltip="mailto:milouaf@yahoo.fr"/>
+    <hyperlink ref="F112" r:id="rId46" display="chikhi_nawel75@yahoo.fr" tooltip="mailto:chikhi_nawel75@yahoo.fr"/>
+    <hyperlink ref="F140" r:id="rId20" display="elghodasseabdelmadjid@gmail.com"/>
+    <hyperlink ref="F141" r:id="rId47" display="n_benseddik@yahoo.fr" tooltip="mailto:n_benseddik@yahoo.fr"/>
+    <hyperlink ref="F143" r:id="rId48" display="yamanimassim@yahoo.fr" tooltip="mailto:yamanimassim@yahoo.fr"/>
+    <hyperlink ref="F142" r:id="rId49" display="neilabekhchiberrahma@gmail.com" tooltip="mailto:neilabekhchiberrahma@gmail.com"/>
+    <hyperlink ref="F146" r:id="rId50" display="belkacemKadari@gmail.com" tooltip="mailto:belkacemKadari@gmail.com"/>
+    <hyperlink ref="F149" r:id="rId51" display="soumiaaiboudi27@gmail.com" tooltip="mailto:soumiaaiboudi27@gmail.com"/>
+    <hyperlink ref="F150" r:id="rId52" display="walid.sebastien@gmail.com"/>
+    <hyperlink ref="F151" r:id="rId53" display="bensenadanadia3@gmail.com"/>
+    <hyperlink ref="F152" r:id="rId54" display="imedmedles@gmail.com"/>
+    <hyperlink ref="F155" r:id="rId55" display="laidabdelali@gmail.com" tooltip="mailto:laidabdelali@gmail.com"/>
+    <hyperlink ref="F159" r:id="rId56" display="attarimad3@gmail.com" tooltip="mailto:attarimad3@gmail.com"/>
+    <hyperlink ref="F161" r:id="rId57" display="moh@medbnr.com"/>
+    <hyperlink ref="F163" r:id="rId58" display="hadilyamoune@gmail.com"/>
+    <hyperlink ref="F164" r:id="rId59" display="megdz100@gmail.com"/>
+    <hyperlink ref="F158" r:id="rId60" display="ikkachenarimen.2017@gmail.com"/>
+    <hyperlink ref="F160" r:id="rId61" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
+    <hyperlink ref="F165" r:id="rId62" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
+    <hyperlink ref="F144" r:id="rId63" display="inesfilali2003@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -9253,202 +9340,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>447</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>447</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="477">
   <si>
     <t>N°</t>
   </si>
@@ -1343,6 +1343,12 @@
   </si>
   <si>
     <t>salahbnd31@gmail.com</t>
+  </si>
+  <si>
+    <t>KACHA ARSLANE HATEM</t>
+  </si>
+  <si>
+    <t>arslane.kacha@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2206,7 +2212,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2311,6 +2317,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2815,7 +2824,7 @@
       <c r="F7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="39" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2838,7 +2847,7 @@
       <c r="F8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="39" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2881,7 +2890,7 @@
       <c r="F10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3064,7 +3073,7 @@
       <c r="F19" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="39" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3407,7 +3416,7 @@
       <c r="F36" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="39" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3450,7 +3459,7 @@
       <c r="F38" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="38" t="s">
+      <c r="G38" s="39" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3733,7 +3742,7 @@
       <c r="F52" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G52" s="38" t="s">
+      <c r="G52" s="39" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3776,7 +3785,7 @@
       <c r="F54" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G54" s="38" t="s">
+      <c r="G54" s="39" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3954,7 +3963,7 @@
       <c r="F62" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="G62" s="38" t="s">
+      <c r="G62" s="39" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4017,7 +4026,7 @@
       <c r="F65" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="G65" s="38" t="s">
+      <c r="G65" s="39" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4061,7 +4070,7 @@
       <c r="F67" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="G67" s="38" t="s">
+      <c r="G67" s="39" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4082,7 +4091,7 @@
       <c r="F68" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="G68" s="38" t="s">
+      <c r="G68" s="39" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4103,7 +4112,7 @@
       <c r="F69" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="G69" s="38" t="s">
+      <c r="G69" s="39" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4124,7 +4133,7 @@
       <c r="F70" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G70" s="38" t="s">
+      <c r="G70" s="39" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4147,7 +4156,7 @@
       <c r="F71" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G71" s="38" t="s">
+      <c r="G71" s="39" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4212,7 +4221,7 @@
       <c r="F74" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="G74" s="38" t="s">
+      <c r="G74" s="39" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4276,7 +4285,7 @@
       <c r="F77" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="G77" s="38" t="s">
+      <c r="G77" s="39" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4485,7 +4494,7 @@
       <c r="F87" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="G87" s="38" t="s">
+      <c r="G87" s="39" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4529,7 +4538,7 @@
       <c r="F89" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="G89" s="38" t="s">
+      <c r="G89" s="39" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4552,7 +4561,7 @@
       <c r="F90" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="G90" s="38" t="s">
+      <c r="G90" s="39" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4596,7 +4605,7 @@
       <c r="F92" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="G92" s="38" t="s">
+      <c r="G92" s="39" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4828,7 +4837,7 @@
       <c r="F103" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="G103" s="38" t="s">
+      <c r="G103" s="39" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4869,7 +4878,7 @@
       <c r="F105" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="G105" s="38" t="s">
+      <c r="G105" s="39" t="s">
         <v>279</v>
       </c>
     </row>
@@ -5269,7 +5278,7 @@
       <c r="F126" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="G126" s="38" t="s">
+      <c r="G126" s="39" t="s">
         <v>324</v>
       </c>
     </row>
@@ -5292,7 +5301,7 @@
       <c r="F127" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="G127" s="38" t="s">
+      <c r="G127" s="39" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5315,7 +5324,7 @@
       <c r="F128" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G128" s="38" t="s">
+      <c r="G128" s="39" t="s">
         <v>330</v>
       </c>
     </row>
@@ -5338,7 +5347,7 @@
       <c r="F129" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="G129" s="38" t="s">
+      <c r="G129" s="39" t="s">
         <v>333</v>
       </c>
     </row>
@@ -5361,7 +5370,7 @@
       <c r="F130" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="G130" s="38" t="s">
+      <c r="G130" s="39" t="s">
         <v>334</v>
       </c>
     </row>
@@ -5427,7 +5436,7 @@
       <c r="F133" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="G133" s="38" t="s">
+      <c r="G133" s="39" t="s">
         <v>342</v>
       </c>
     </row>
@@ -5450,7 +5459,7 @@
       <c r="F134" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="G134" s="38" t="s">
+      <c r="G134" s="39" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5471,7 +5480,7 @@
       <c r="F135" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="G135" s="38" t="s">
+      <c r="G135" s="39" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5514,7 +5523,7 @@
       <c r="F137" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="G137" s="38" t="s">
+      <c r="G137" s="39" t="s">
         <v>353</v>
       </c>
     </row>
@@ -5537,7 +5546,7 @@
       <c r="F138" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="G138" s="38" t="s">
+      <c r="G138" s="39" t="s">
         <v>356</v>
       </c>
     </row>
@@ -5684,7 +5693,7 @@
       <c r="F145" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="G145" s="38" t="s">
+      <c r="G145" s="39" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5707,7 +5716,7 @@
       <c r="F146" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="G146" s="38" t="s">
+      <c r="G146" s="39" t="s">
         <v>371</v>
       </c>
     </row>
@@ -5828,7 +5837,7 @@
       <c r="F152" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="G152" s="38" t="s">
+      <c r="G152" s="39" t="s">
         <v>384</v>
       </c>
     </row>
@@ -5911,7 +5920,7 @@
       <c r="F156" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="G156" s="38" t="s">
+      <c r="G156" s="39" t="s">
         <v>393</v>
       </c>
     </row>
@@ -5934,7 +5943,7 @@
       <c r="F157" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="G157" s="38" t="s">
+      <c r="G157" s="39" t="s">
         <v>396</v>
       </c>
     </row>
@@ -5957,7 +5966,7 @@
       <c r="F158" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="G158" s="38" t="s">
+      <c r="G158" s="39" t="s">
         <v>399</v>
       </c>
     </row>
@@ -5980,7 +5989,7 @@
       <c r="F159" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="G159" s="38" t="s">
+      <c r="G159" s="39" t="s">
         <v>402</v>
       </c>
     </row>
@@ -6023,7 +6032,7 @@
       <c r="F161" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="G161" s="38" t="s">
+      <c r="G161" s="39" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6046,7 +6055,7 @@
       <c r="F162" s="37" t="s">
         <v>409</v>
       </c>
-      <c r="G162" s="38" t="s">
+      <c r="G162" s="39" t="s">
         <v>410</v>
       </c>
     </row>
@@ -6069,7 +6078,7 @@
       <c r="F163" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="G163" s="38" t="s">
+      <c r="G163" s="39" t="s">
         <v>413</v>
       </c>
     </row>
@@ -6092,7 +6101,7 @@
       <c r="F164" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="G164" s="38" t="s">
+      <c r="G164" s="39" t="s">
         <v>416</v>
       </c>
     </row>
@@ -6115,7 +6124,7 @@
       <c r="F165" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="G165" s="38" t="s">
+      <c r="G165" s="39" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6138,7 +6147,7 @@
       <c r="F166" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="G166" s="38" t="s">
+      <c r="G166" s="39" t="s">
         <v>422</v>
       </c>
     </row>
@@ -6281,15 +6290,32 @@
       <c r="D174" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E174" s="17" t="s">
+      <c r="E174" s="38" t="s">
         <v>138</v>
       </c>
       <c r="F174" s="19" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
-      <c r="D175" s="18"/>
+    <row r="175" ht="15.75" spans="1:7">
+      <c r="A175" s="24">
+        <v>174</v>
+      </c>
+      <c r="B175" s="25" t="s">
+        <v>437</v>
+      </c>
+      <c r="C175" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" s="19" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="176" spans="1:7">
       <c r="D176" s="18"/>
@@ -9340,202 +9366,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>449</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>449</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="479">
   <si>
     <t>N°</t>
   </si>
@@ -1349,6 +1349,12 @@
   </si>
   <si>
     <t>arslane.kacha@gmail.com</t>
+  </si>
+  <si>
+    <t>LACHABI ABDELHADI</t>
+  </si>
+  <si>
+    <t>lachabi22@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2212,7 +2218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2317,9 +2323,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2824,7 +2827,7 @@
       <c r="F7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="39" t="s">
+      <c r="G7" s="38" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2847,7 +2850,7 @@
       <c r="F8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="39" t="s">
+      <c r="G8" s="38" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2890,7 +2893,7 @@
       <c r="F10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="39" t="s">
+      <c r="G10" s="38" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3073,7 +3076,7 @@
       <c r="F19" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="39" t="s">
+      <c r="G19" s="38" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3416,7 +3419,7 @@
       <c r="F36" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="38" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3459,7 +3462,7 @@
       <c r="F38" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="39" t="s">
+      <c r="G38" s="38" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3742,7 +3745,7 @@
       <c r="F52" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G52" s="39" t="s">
+      <c r="G52" s="38" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3785,7 +3788,7 @@
       <c r="F54" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G54" s="39" t="s">
+      <c r="G54" s="38" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3963,7 +3966,7 @@
       <c r="F62" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="G62" s="39" t="s">
+      <c r="G62" s="38" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4026,7 +4029,7 @@
       <c r="F65" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="G65" s="39" t="s">
+      <c r="G65" s="38" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4070,7 +4073,7 @@
       <c r="F67" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="G67" s="39" t="s">
+      <c r="G67" s="38" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4091,7 +4094,7 @@
       <c r="F68" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="G68" s="39" t="s">
+      <c r="G68" s="38" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4112,7 +4115,7 @@
       <c r="F69" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="G69" s="39" t="s">
+      <c r="G69" s="38" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4133,7 +4136,7 @@
       <c r="F70" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G70" s="39" t="s">
+      <c r="G70" s="38" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4156,7 +4159,7 @@
       <c r="F71" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G71" s="39" t="s">
+      <c r="G71" s="38" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4221,7 +4224,7 @@
       <c r="F74" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="G74" s="39" t="s">
+      <c r="G74" s="38" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4285,7 +4288,7 @@
       <c r="F77" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="G77" s="39" t="s">
+      <c r="G77" s="38" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4494,7 +4497,7 @@
       <c r="F87" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="G87" s="39" t="s">
+      <c r="G87" s="38" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4538,7 +4541,7 @@
       <c r="F89" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="G89" s="39" t="s">
+      <c r="G89" s="38" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4561,7 +4564,7 @@
       <c r="F90" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="G90" s="39" t="s">
+      <c r="G90" s="38" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4605,7 +4608,7 @@
       <c r="F92" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="G92" s="39" t="s">
+      <c r="G92" s="38" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4837,7 +4840,7 @@
       <c r="F103" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="G103" s="39" t="s">
+      <c r="G103" s="38" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4878,7 +4881,7 @@
       <c r="F105" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="G105" s="39" t="s">
+      <c r="G105" s="38" t="s">
         <v>279</v>
       </c>
     </row>
@@ -5278,7 +5281,7 @@
       <c r="F126" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="G126" s="39" t="s">
+      <c r="G126" s="38" t="s">
         <v>324</v>
       </c>
     </row>
@@ -5301,7 +5304,7 @@
       <c r="F127" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="G127" s="39" t="s">
+      <c r="G127" s="38" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5324,7 +5327,7 @@
       <c r="F128" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G128" s="39" t="s">
+      <c r="G128" s="38" t="s">
         <v>330</v>
       </c>
     </row>
@@ -5347,7 +5350,7 @@
       <c r="F129" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="G129" s="39" t="s">
+      <c r="G129" s="38" t="s">
         <v>333</v>
       </c>
     </row>
@@ -5370,7 +5373,7 @@
       <c r="F130" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="G130" s="39" t="s">
+      <c r="G130" s="38" t="s">
         <v>334</v>
       </c>
     </row>
@@ -5436,7 +5439,7 @@
       <c r="F133" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="G133" s="39" t="s">
+      <c r="G133" s="38" t="s">
         <v>342</v>
       </c>
     </row>
@@ -5459,7 +5462,7 @@
       <c r="F134" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="G134" s="39" t="s">
+      <c r="G134" s="38" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5480,7 +5483,7 @@
       <c r="F135" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="G135" s="39" t="s">
+      <c r="G135" s="38" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5523,7 +5526,7 @@
       <c r="F137" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="G137" s="39" t="s">
+      <c r="G137" s="38" t="s">
         <v>353</v>
       </c>
     </row>
@@ -5546,7 +5549,7 @@
       <c r="F138" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="G138" s="39" t="s">
+      <c r="G138" s="38" t="s">
         <v>356</v>
       </c>
     </row>
@@ -5693,7 +5696,7 @@
       <c r="F145" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="G145" s="39" t="s">
+      <c r="G145" s="38" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5716,7 +5719,7 @@
       <c r="F146" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="G146" s="39" t="s">
+      <c r="G146" s="38" t="s">
         <v>371</v>
       </c>
     </row>
@@ -5837,7 +5840,7 @@
       <c r="F152" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="G152" s="39" t="s">
+      <c r="G152" s="38" t="s">
         <v>384</v>
       </c>
     </row>
@@ -5920,7 +5923,7 @@
       <c r="F156" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="G156" s="39" t="s">
+      <c r="G156" s="38" t="s">
         <v>393</v>
       </c>
     </row>
@@ -5943,7 +5946,7 @@
       <c r="F157" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="G157" s="39" t="s">
+      <c r="G157" s="38" t="s">
         <v>396</v>
       </c>
     </row>
@@ -5966,7 +5969,7 @@
       <c r="F158" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="G158" s="39" t="s">
+      <c r="G158" s="38" t="s">
         <v>399</v>
       </c>
     </row>
@@ -5989,7 +5992,7 @@
       <c r="F159" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="G159" s="39" t="s">
+      <c r="G159" s="38" t="s">
         <v>402</v>
       </c>
     </row>
@@ -6032,7 +6035,7 @@
       <c r="F161" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="G161" s="39" t="s">
+      <c r="G161" s="38" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6055,7 +6058,7 @@
       <c r="F162" s="37" t="s">
         <v>409</v>
       </c>
-      <c r="G162" s="39" t="s">
+      <c r="G162" s="38" t="s">
         <v>410</v>
       </c>
     </row>
@@ -6078,7 +6081,7 @@
       <c r="F163" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="G163" s="39" t="s">
+      <c r="G163" s="38" t="s">
         <v>413</v>
       </c>
     </row>
@@ -6101,7 +6104,7 @@
       <c r="F164" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="G164" s="39" t="s">
+      <c r="G164" s="38" t="s">
         <v>416</v>
       </c>
     </row>
@@ -6124,7 +6127,7 @@
       <c r="F165" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="G165" s="39" t="s">
+      <c r="G165" s="38" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6147,7 +6150,7 @@
       <c r="F166" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="G166" s="39" t="s">
+      <c r="G166" s="38" t="s">
         <v>422</v>
       </c>
     </row>
@@ -6290,7 +6293,7 @@
       <c r="D174" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E174" s="38" t="s">
+      <c r="E174" s="28" t="s">
         <v>138</v>
       </c>
       <c r="F174" s="19" t="s">
@@ -6310,15 +6313,29 @@
       <c r="D175" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="E175" s="38" t="s">
+      <c r="E175" s="28" t="s">
         <v>10</v>
       </c>
       <c r="F175" s="19" t="s">
         <v>438</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
-      <c r="D176" s="18"/>
+    <row r="176" ht="15.75" spans="1:7">
+      <c r="B176" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="C176" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="19" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="177" spans="4:4">
       <c r="D177" s="18"/>
@@ -9273,8 +9290,8 @@
       <c r="D1160" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G174" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:G174">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G175" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:G175">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9366,202 +9383,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>451</v>
-      </c>
       <c r="D5" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>451</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$176</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1354,7 +1354,7 @@
     <t>LACHABI ABDELHADI</t>
   </si>
   <si>
-    <t>lachabi22@gmail.com</t>
+    <t>abdelhadilachabi@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -2218,7 +2218,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2323,6 +2323,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
@@ -2827,7 +2830,7 @@
       <c r="F7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="39" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2850,7 +2853,7 @@
       <c r="F8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="39" t="s">
         <v>27</v>
       </c>
     </row>
@@ -2893,7 +2896,7 @@
       <c r="F10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="G10" s="38" t="s">
+      <c r="G10" s="39" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3076,7 +3079,7 @@
       <c r="F19" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="39" t="s">
         <v>53</v>
       </c>
     </row>
@@ -3419,7 +3422,7 @@
       <c r="F36" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="G36" s="39" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3462,7 +3465,7 @@
       <c r="F38" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="G38" s="38" t="s">
+      <c r="G38" s="39" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3745,7 +3748,7 @@
       <c r="F52" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="G52" s="38" t="s">
+      <c r="G52" s="39" t="s">
         <v>122</v>
       </c>
     </row>
@@ -3788,7 +3791,7 @@
       <c r="F54" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="G54" s="38" t="s">
+      <c r="G54" s="39" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3966,7 +3969,7 @@
       <c r="F62" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="G62" s="38" t="s">
+      <c r="G62" s="39" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4029,7 +4032,7 @@
       <c r="F65" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="G65" s="38" t="s">
+      <c r="G65" s="39" t="s">
         <v>164</v>
       </c>
     </row>
@@ -4073,7 +4076,7 @@
       <c r="F67" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="G67" s="38" t="s">
+      <c r="G67" s="39" t="s">
         <v>170</v>
       </c>
     </row>
@@ -4094,7 +4097,7 @@
       <c r="F68" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="G68" s="38" t="s">
+      <c r="G68" s="39" t="s">
         <v>173</v>
       </c>
     </row>
@@ -4115,7 +4118,7 @@
       <c r="F69" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="G69" s="38" t="s">
+      <c r="G69" s="39" t="s">
         <v>176</v>
       </c>
     </row>
@@ -4136,7 +4139,7 @@
       <c r="F70" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="G70" s="38" t="s">
+      <c r="G70" s="39" t="s">
         <v>179</v>
       </c>
     </row>
@@ -4159,7 +4162,7 @@
       <c r="F71" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="G71" s="38" t="s">
+      <c r="G71" s="39" t="s">
         <v>182</v>
       </c>
     </row>
@@ -4224,7 +4227,7 @@
       <c r="F74" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="G74" s="38" t="s">
+      <c r="G74" s="39" t="s">
         <v>191</v>
       </c>
     </row>
@@ -4288,7 +4291,7 @@
       <c r="F77" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="G77" s="38" t="s">
+      <c r="G77" s="39" t="s">
         <v>199</v>
       </c>
     </row>
@@ -4497,7 +4500,7 @@
       <c r="F87" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="G87" s="38" t="s">
+      <c r="G87" s="39" t="s">
         <v>226</v>
       </c>
     </row>
@@ -4541,7 +4544,7 @@
       <c r="F89" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="G89" s="38" t="s">
+      <c r="G89" s="39" t="s">
         <v>232</v>
       </c>
     </row>
@@ -4564,7 +4567,7 @@
       <c r="F90" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="G90" s="38" t="s">
+      <c r="G90" s="39" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4608,7 +4611,7 @@
       <c r="F92" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="G92" s="38" t="s">
+      <c r="G92" s="39" t="s">
         <v>242</v>
       </c>
     </row>
@@ -4840,7 +4843,7 @@
       <c r="F103" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="G103" s="38" t="s">
+      <c r="G103" s="39" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4881,7 +4884,7 @@
       <c r="F105" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="G105" s="38" t="s">
+      <c r="G105" s="39" t="s">
         <v>279</v>
       </c>
     </row>
@@ -5281,7 +5284,7 @@
       <c r="F126" s="19" t="s">
         <v>323</v>
       </c>
-      <c r="G126" s="38" t="s">
+      <c r="G126" s="39" t="s">
         <v>324</v>
       </c>
     </row>
@@ -5304,7 +5307,7 @@
       <c r="F127" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="G127" s="38" t="s">
+      <c r="G127" s="39" t="s">
         <v>327</v>
       </c>
     </row>
@@ -5327,7 +5330,7 @@
       <c r="F128" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="G128" s="38" t="s">
+      <c r="G128" s="39" t="s">
         <v>330</v>
       </c>
     </row>
@@ -5350,7 +5353,7 @@
       <c r="F129" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="G129" s="38" t="s">
+      <c r="G129" s="39" t="s">
         <v>333</v>
       </c>
     </row>
@@ -5373,7 +5376,7 @@
       <c r="F130" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="G130" s="38" t="s">
+      <c r="G130" s="39" t="s">
         <v>334</v>
       </c>
     </row>
@@ -5439,7 +5442,7 @@
       <c r="F133" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="G133" s="38" t="s">
+      <c r="G133" s="39" t="s">
         <v>342</v>
       </c>
     </row>
@@ -5462,7 +5465,7 @@
       <c r="F134" s="19" t="s">
         <v>344</v>
       </c>
-      <c r="G134" s="38" t="s">
+      <c r="G134" s="39" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5483,7 +5486,7 @@
       <c r="F135" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="G135" s="38" t="s">
+      <c r="G135" s="39" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5526,7 +5529,7 @@
       <c r="F137" s="19" t="s">
         <v>352</v>
       </c>
-      <c r="G137" s="38" t="s">
+      <c r="G137" s="39" t="s">
         <v>353</v>
       </c>
     </row>
@@ -5549,7 +5552,7 @@
       <c r="F138" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="G138" s="38" t="s">
+      <c r="G138" s="39" t="s">
         <v>356</v>
       </c>
     </row>
@@ -5696,7 +5699,7 @@
       <c r="F145" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="G145" s="38" t="s">
+      <c r="G145" s="39" t="s">
         <v>368</v>
       </c>
     </row>
@@ -5719,7 +5722,7 @@
       <c r="F146" s="19" t="s">
         <v>370</v>
       </c>
-      <c r="G146" s="38" t="s">
+      <c r="G146" s="39" t="s">
         <v>371</v>
       </c>
     </row>
@@ -5840,7 +5843,7 @@
       <c r="F152" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="G152" s="38" t="s">
+      <c r="G152" s="39" t="s">
         <v>384</v>
       </c>
     </row>
@@ -5923,7 +5926,7 @@
       <c r="F156" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="G156" s="38" t="s">
+      <c r="G156" s="39" t="s">
         <v>393</v>
       </c>
     </row>
@@ -5946,7 +5949,7 @@
       <c r="F157" s="19" t="s">
         <v>395</v>
       </c>
-      <c r="G157" s="38" t="s">
+      <c r="G157" s="39" t="s">
         <v>396</v>
       </c>
     </row>
@@ -5969,7 +5972,7 @@
       <c r="F158" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="G158" s="38" t="s">
+      <c r="G158" s="39" t="s">
         <v>399</v>
       </c>
     </row>
@@ -5992,7 +5995,7 @@
       <c r="F159" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="G159" s="38" t="s">
+      <c r="G159" s="39" t="s">
         <v>402</v>
       </c>
     </row>
@@ -6035,7 +6038,7 @@
       <c r="F161" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="G161" s="38" t="s">
+      <c r="G161" s="39" t="s">
         <v>407</v>
       </c>
     </row>
@@ -6058,7 +6061,7 @@
       <c r="F162" s="37" t="s">
         <v>409</v>
       </c>
-      <c r="G162" s="38" t="s">
+      <c r="G162" s="39" t="s">
         <v>410</v>
       </c>
     </row>
@@ -6081,7 +6084,7 @@
       <c r="F163" s="19" t="s">
         <v>412</v>
       </c>
-      <c r="G163" s="38" t="s">
+      <c r="G163" s="39" t="s">
         <v>413</v>
       </c>
     </row>
@@ -6104,7 +6107,7 @@
       <c r="F164" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="G164" s="38" t="s">
+      <c r="G164" s="39" t="s">
         <v>416</v>
       </c>
     </row>
@@ -6127,7 +6130,7 @@
       <c r="F165" s="19" t="s">
         <v>418</v>
       </c>
-      <c r="G165" s="38" t="s">
+      <c r="G165" s="39" t="s">
         <v>419</v>
       </c>
     </row>
@@ -6150,7 +6153,7 @@
       <c r="F166" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="G166" s="38" t="s">
+      <c r="G166" s="39" t="s">
         <v>422</v>
       </c>
     </row>
@@ -6333,7 +6336,7 @@
       <c r="E176" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F176" s="19" t="s">
+      <c r="F176" s="38" t="s">
         <v>440</v>
       </c>
     </row>
@@ -9290,8 +9293,8 @@
       <c r="D1160" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G175" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:G175">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G176" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:G176">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9361,6 +9364,7 @@
     <hyperlink ref="F160" r:id="rId61" display="rachid.hadjboulenouar@gmail.com" tooltip="mailto:rachid.hadjboulenouar@gmail.com"/>
     <hyperlink ref="F165" r:id="rId62" display="didaouikawthar331@gmail.com" tooltip="mailto:didaouikawthar331@gmail.com"/>
     <hyperlink ref="F144" r:id="rId63" display="inesfilali2003@gmail.com"/>
+    <hyperlink ref="F176" r:id="rId64" display="abdelhadilachabi@gmail.com" tooltip="mailto:abdelhadilachabi@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
